--- a/data/outputs/model_disagreements.xlsx
+++ b/data/outputs/model_disagreements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Disagreements" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Model Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Explanations" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disagreements" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Explanations" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,59 +444,1092 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>gpt</t>
+          <t>o3</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>claude</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>gemini</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I visit homes and share information about clean water. People now recognize me as a health worker.</t>
+          <t>Abortion Abortion is very deadly because one can bleed to death. Some have been able to heal from post abortion hemorrhage, but some end up having anemia. This topic has been left out, yet it is very important because we have many of our young girls are dying from excess bleeding from abortion. I talked to a group of young girls who agreed to open up about their abortion experience and none of them enjoyed even a bit of it. I agreed with them that there would be no more abortion. Those above 20, they should go for family planning and the rest to practice ---</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>Referrals and Advocacy</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I visit homes and share information about clean water. People now recognize me as a health worker.</t>
+          <t>Abortion Abortion is very deadly because one can bleed to death. Some have been able to heal from post abortion hemorrhage, but some end up having anemia. This topic has been left out, yet it is very important because we have many of our young girls are dying from excess bleeding from abortion. I talked to a group of young girls who agreed to open up about their abortion experience and none of them enjoyed even a bit of it. I agreed with them that there would be no more abortion. Those above 20, they should go for family planning and the rest to practice ---</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>Disease Burden</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Abortion Abortion is very deadly because one can bleed to death. Some have been able to heal from post abortion hemorrhage, but some end up having anemia. This topic has been left out, yet it is very important because we have many of our young girls are dying from excess bleeding from abortion. I talked to a group of young girls who agreed to open up about their abortion experience and none of them enjoyed even a bit of it. I agreed with them that there would be no more abortion. Those above 20, they should go for family planning and the rest to practice ---</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Stigma or Discrimination</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Asthma Asthma is a chronic disease which can affect everyone. I spotted a young child wheezing and as I inquired from the mother, she told me that she was suspecting that the child might be having common cold as the child was coughing due to change of weather. But to me as a CHW I thought that it would be best if the child was to be taken to the hospital for medical examination so that the mother could know what was wrong with the child. With my help, I referred the ??? to take the child to the hospital. The child was tested and was found to be ailing from asthma. The child was put onto medication and as now the child showing some improvements. Though asthma is a chronic disease, if proper medication and continuous taking of the drugs is well conducted, it can help in reducing chances of child fatality. ---</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Asthma Asthma is a chronic disease which can affect everyone. I spotted a young child wheezing and as I inquired from the mother, she told me that she was suspecting that the child might be having common cold as the child was coughing due to change of weather. But to me as a CHW I thought that it would be best if the child was to be taken to the hospital for medical examination so that the mother could know what was wrong with the child. With my help, I referred the ??? to take the child to the hospital. The child was tested and was found to be ailing from asthma. The child was put onto medication and as now the child showing some improvements. Though asthma is a chronic disease, if proper medication and continuous taking of the drugs is well conducted, it can help in reducing chances of child fatality. ---</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Women Served</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tuberculosis People living in ????? settlements tend to not be concerned about their health. Many are first concerned with how they can attend to their daily labor to make some money which can help them put some food on the table. People are coughing and just take it as a normal cough. During my field work, I came across two people who were coughing as I was training them. I asked them when they started coughing and advised them to see the doctor for a tuberculosis test. They went for the test and one of them was found positive for tuberculosis. She has begun treatment and hopefully she will be okay. As CHW, I am now talking to many and also refer them for tuberculosis test at ???? ---</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tuberculosis People living in ????? settlements tend to not be concerned about their health. Many are first concerned with how they can attend to their daily labor to make some money which can help them put some food on the table. People are coughing and just take it as a normal cough. During my field work, I came across two people who were coughing as I was training them. I asked them when they started coughing and advised them to see the doctor for a tuberculosis test. They went for the test and one of them was found positive for tuberculosis. She has begun treatment and hopefully she will be okay. As CHW, I am now talking to many and also refer them for tuberculosis test at ???? ---</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Monitoring and Follow-Up</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tuberculosis People living in ????? settlements tend to not be concerned about their health. Many are first concerned with how they can attend to their daily labor to make some money which can help them put some food on the table. People are coughing and just take it as a normal cough. During my field work, I came across two people who were coughing as I was training them. I asked them when they started coughing and advised them to see the doctor for a tuberculosis test. They went for the test and one of them was found positive for tuberculosis. She has begun treatment and hopefully she will be okay. As CHW, I am now talking to many and also refer them for tuberculosis test at ???? ---</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Trust and Cultural Mediation</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Tuberculosis During my fieldwork engagement with my participants in a training, one of my participants approached me after I had completed my training—and asked me if I could be able to allow him share with me something. I first thought what could he wanted to tell me, yet I gave time for questions during the sessions. And he could not ask anything. Bravely enough, I heeded to his request and he shared with me that he was diagnosed with tuberculosis and he was put into medication but unfortunately, he defaulted. He wanted to know if I could help him get back to medication but was not happy to go back to Thramogi Agmga Teaching and Referral Hospital since they could not help him. I managed to refer him to KNAP and he got helped and now his life is improving day by day. I am doing close follow-up on him to make sure he has taken his drugs. ---</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Tuberculosis During my fieldwork engagement with my participants in a training, one of my participants approached me after I had completed my training—and asked me if I could be able to allow him share with me something. I first thought what could he wanted to tell me, yet I gave time for questions during the sessions. And he could not ask anything. Bravely enough, I heeded to his request and he shared with me that he was diagnosed with tuberculosis and he was put into medication but unfortunately, he defaulted. He wanted to know if I could help him get back to medication but was not happy to go back to Thramogi Agmga Teaching and Referral Hospital since they could not help him. I managed to refer him to KNAP and he got helped and now his life is improving day by day. I am doing close follow-up on him to make sure he has taken his drugs. ---</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Trust and Cultural Mediation</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>COVID-19 Coronavirus continues to be a menace not only to the country but also to our work, as it restricts large gatherings and restricts people to minimal contact with each other to avoid the spread of the virus. The country is currently battling the third Indian wave which has shown more devastating effects of the new strain of the virus. This has led to more restrictions and also has led to the imposed curfews within Kisumu County and the environs. There is a possibility of even more stringent measures to curb the third wave. Having trained as a Community Health Worker, I have been actively sensitizing and creating awareness to my community members on the preventive measures against the COVID-19 pandemic. I have been emphasizing a lot on the benefits of putting on masks, washing hands with clean running water and soap, sanitizing and also keeping social distance. Through this, the members of the community have embraced and also adopted the teachings and are always doing what I have trained them to do. This has made me very happy because there is no single case that has been reported from this community I live and work in. Were it by any chance that the people were not sensitized, then this community could be a COVID-19 hotspot and many people could have died. There’s a big change on how people wash their hands and also put on masks compared to other previous years where people did not take washing hands with soap and running water very important. Initially, many people could even take or rather eat fruits or any other food stuffs without washing their hands but since COVID-19 hit us, many people have adopted the trend of washing hands regularly. This is a great change that has manifested in my community. ---</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Personal Disease Management and Adherence</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>COVID-19 Coronavirus continues to be a menace not only to the country but also to our work, as it restricts large gatherings and restricts people to minimal contact with each other to avoid the spread of the virus. The country is currently battling the third Indian wave which has shown more devastating effects of the new strain of the virus. This has led to more restrictions and also has led to the imposed curfews within Kisumu County and the environs. There is a possibility of even more stringent measures to curb the third wave. Having trained as a Community Health Worker, I have been actively sensitizing and creating awareness to my community members on the preventive measures against the COVID-19 pandemic. I have been emphasizing a lot on the benefits of putting on masks, washing hands with clean running water and soap, sanitizing and also keeping social distance. Through this, the members of the community have embraced and also adopted the teachings and are always doing what I have trained them to do. This has made me very happy because there is no single case that has been reported from this community I live and work in. Were it by any chance that the people were not sensitized, then this community could be a COVID-19 hotspot and many people could have died. There’s a big change on how people wash their hands and also put on masks compared to other previous years where people did not take washing hands with soap and running water very important. Initially, many people could even take or rather eat fruits or any other food stuffs without washing their hands but since COVID-19 hit us, many people have adopted the trend of washing hands regularly. This is a great change that has manifested in my community. ---</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Trust and Cultural Mediation</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>COVID-19 Coronavirus continues to be a menace not only to the country but also to our work, as it restricts large gatherings and restricts people to minimal contact with each other to avoid the spread of the virus. The country is currently battling the third Indian wave which has shown more devastating effects of the new strain of the virus. This has led to more restrictions and also has led to the imposed curfews within Kisumu County and the environs. There is a possibility of even more stringent measures to curb the third wave. Having trained as a Community Health Worker, I have been actively sensitizing and creating awareness to my community members on the preventive measures against the COVID-19 pandemic. I have been emphasizing a lot on the benefits of putting on masks, washing hands with clean running water and soap, sanitizing and also keeping social distance. Through this, the members of the community have embraced and also adopted the teachings and are always doing what I have trained them to do. This has made me very happy because there is no single case that has been reported from this community I live and work in. Were it by any chance that the people were not sensitized, then this community could be a COVID-19 hotspot and many people could have died. There’s a big change on how people wash their hands and also put on masks compared to other previous years where people did not take washing hands with soap and running water very important. Initially, many people could even take or rather eat fruits or any other food stuffs without washing their hands but since COVID-19 hit us, many people have adopted the trend of washing hands regularly. This is a great change that has manifested in my community. ---</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Disease Burden</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>COVID-19 Regarding the COVID-19 new variant, since most of the community members took vaccines, many people have left the common practices which were given by the Ministry of Health such as washing hands, putting on masks, avoiding crowded places, and keeping social distance. Political rallies in Kenya have attracted so many crowds that has contributed to many people contracting the disease. Omicron wave was reported in Kenya some few weeks back and we have seen cases of the Omicron is rising day by day. As a CHW, I have been emphasizing on training the community members on how to continue practicing the COVID-19 measures and about mobilizing these who have not been vaccinated to go for vaccinations. ---</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Personal Disease Management and Adherence</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>COVID-19 Regarding the COVID-19 new variant, since most of the community members took vaccines, many people have left the common practices which were given by the Ministry of Health such as washing hands, putting on masks, avoiding crowded places, and keeping social distance. Political rallies in Kenya have attracted so many crowds that has contributed to many people contracting the disease. Omicron wave was reported in Kenya some few weeks back and we have seen cases of the Omicron is rising day by day. As a CHW, I have been emphasizing on training the community members on how to continue practicing the COVID-19 measures and about mobilizing these who have not been vaccinated to go for vaccinations. ---</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Community Empowerment Through Education</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>COVID-19 Regarding the COVID-19 new variant, since most of the community members took vaccines, many people have left the common practices which were given by the Ministry of Health such as washing hands, putting on masks, avoiding crowded places, and keeping social distance. Political rallies in Kenya have attracted so many crowds that has contributed to many people contracting the disease. Omicron wave was reported in Kenya some few weeks back and we have seen cases of the Omicron is rising day by day. As a CHW, I have been emphasizing on training the community members on how to continue practicing the COVID-19 measures and about mobilizing these who have not been vaccinated to go for vaccinations. ---</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Disease Burden</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>COVID-19 Regarding the COVID-19 new variant, since most of the community members took vaccines, many people have left the common practices which were given by the Ministry of Health such as washing hands, putting on masks, avoiding crowded places, and keeping social distance. Political rallies in Kenya have attracted so many crowds that has contributed to many people contracting the disease. Omicron wave was reported in Kenya some few weeks back and we have seen cases of the Omicron is rising day by day. As a CHW, I have been emphasizing on training the community members on how to continue practicing the COVID-19 measures and about mobilizing these who have not been vaccinated to go for vaccinations. ---</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Systemic Barriers</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Malaria Having malaria is a very bad experience that personally I would not like to get sick again. Physical symptoms that I had was fatigue, vomiting, fever, and sometimes diarrhea. In the evening a strong headache and chills appeared as if it had been stirred up or triggered by something. Sincerely speaking, when I felt symptoms coming on, I used to go over the counter and buy malaria drugs—e.g., ACTM—because I thought that every symptom as such could be malaria which I realized after becoming a CHW that it was not a good idea. Malaria could return again and again because I was not adhering to the instructions of completing doses, I was not treating malaria well, not sleeping under mosquito treated net. As a CHW, what I can do to help people with malaria is to advise them to go to the hospital and get tested and also to be treated well whenever the symptoms occur. ---</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Lack of Knowledge</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Malaria Malaria is a bacterial infection caused by plasmodium vale that affects the blood stream of human body. It is spread through anopheles mosquito bite from one person to another. People who have malaria usually feel sick with high fever and shaking chills. Some people may experience signs in the abdomen or muscles, fatigue, fever, night sweats, shivering, nausea, diarrhea, vomiting, headache, and coldness. The physical symptoms of malaria may include vomiting, tiredness, shivering, body weakness, sweating, children might be restless. The immediate action I take as a Community Health Worker when I see the symptoms coming is to do the sponging to reduce temperature, drink a lot of water due to vomiting and diarrhea. This are the first aid you do before going to the hospital. The malaria infection may return time and again if the patient does not follow the preventive measures like sleeping under the treated mosquito nets and vector control. As a Community Health Worker, if you once identify someone suffering from malaria, I immediately refer to the nearest health center. Many people have died from malaria due to late diagnosis that might lead to anemia, enlarged spleen that leads to ????????? that have similar symptoms as malaria. Disease like typhoid, dysentery. So, if not careful, you might miss the diagnosis, so you must thoroughly and probe the client. You should be well conversant with the signs and symptoms of malaria. And thus, the slogan “ZERO MALARIA STARTS WITH ME.” ---</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Malaria The weather in Kisumu has totally changed, there is a lot of rains and floodings experienced everywhere. This rain has also brought a lot of stagnant water which helps mosquitoes breed. During the week I took my training emphasizing on how to use nets to help in preventing the spread of malaria. I also came across one of my participants who was having malaria but was just using over-the-counter drugs. I referred the person to Thoamogi Oginga Teaching and Referral Hospital for the malaria test which later turned positive and he was treated and given prescriptions of the medicines. As a CHW, I am very happy that the person is responding well to medications. ---</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Community Empowerment Through Education</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Malaria The weather in Kisumu has totally changed, there is a lot of rains and floodings experienced everywhere. This rain has also brought a lot of stagnant water which helps mosquitoes breed. During the week I took my training emphasizing on how to use nets to help in preventing the spread of malaria. I also came across one of my participants who was having malaria but was just using over-the-counter drugs. I referred the person to Thoamogi Oginga Teaching and Referral Hospital for the malaria test which later turned positive and he was treated and given prescriptions of the medicines. As a CHW, I am very happy that the person is responding well to medications. ---</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Disease Burden</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Malaria This story is all about my personal experience with malaria in the past and also sharing on what I have been doing to help people to not get malaria. My first diagnosis on malaria was in four years back. I fell sick and could not know what I was suffering from. My body was very weak, mostly my body joints. My heart was almost bursting. My body temperature was very high. I was sweating a lot and during morning hours I was feeling a lot of cold which made me to sit outside my room to find heat from the sun. It was unbearable. This time I was not a trained Community Health Worker, so I had no information about malaria. The only treatment I was able to go for was only pain killers which I was buying through over-the-counter. And this was ?????? blood sample was taken to the lab, here is where I got myself diagnosed the malaria. I was treated and got better within two weeks and a half. By all this time, I was not sleeping under the net so the mosquitos were enjoying sucking my blood. Now that I am a trained Community Health Worker, I have been training my community members on how they can prevent contacting malaria. In my training, I share with them on the importance of sleeping under treated mosquito nets, clearing of bushy surroundings, draining stagnant waters, and also keeping the surroundings clean so as keep away mosquitoes from breeding. ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Water Quality, Sanitation, and Hygiene</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Malaria This story is all about my personal experience with malaria in the past and also sharing on what I have been doing to help people to not get malaria. My first diagnosis on malaria was in four years back. I fell sick and could not know what I was suffering from. My body was very weak, mostly my body joints. My heart was almost bursting. My body temperature was very high. I was sweating a lot and during morning hours I was feeling a lot of cold which made me to sit outside my room to find heat from the sun. It was unbearable. This time I was not a trained Community Health Worker, so I had no information about malaria. The only treatment I was able to go for was only pain killers which I was buying through over-the-counter. And this was ?????? blood sample was taken to the lab, here is where I got myself diagnosed the malaria. I was treated and got better within two weeks and a half. By all this time, I was not sleeping under the net so the mosquitos were enjoying sucking my blood. Now that I am a trained Community Health Worker, I have been training my community members on how they can prevent contacting malaria. In my training, I share with them on the importance of sleeping under treated mosquito nets, clearing of bushy surroundings, draining stagnant waters, and also keeping the surroundings clean so as keep away mosquitoes from breeding. ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Community Empowerment Through Education</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Malaria This story is all about my personal experience with malaria in the past and also sharing on what I have been doing to help people to not get malaria. My first diagnosis on malaria was in four years back. I fell sick and could not know what I was suffering from. My body was very weak, mostly my body joints. My heart was almost bursting. My body temperature was very high. I was sweating a lot and during morning hours I was feeling a lot of cold which made me to sit outside my room to find heat from the sun. It was unbearable. This time I was not a trained Community Health Worker, so I had no information about malaria. The only treatment I was able to go for was only pain killers which I was buying through over-the-counter. And this was ?????? blood sample was taken to the lab, here is where I got myself diagnosed the malaria. I was treated and got better within two weeks and a half. By all this time, I was not sleeping under the net so the mosquitos were enjoying sucking my blood. Now that I am a trained Community Health Worker, I have been training my community members on how they can prevent contacting malaria. In my training, I share with them on the importance of sleeping under treated mosquito nets, clearing of bushy surroundings, draining stagnant waters, and also keeping the surroundings clean so as keep away mosquitoes from breeding. ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Successful Outcomes</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Malaria During my health education at Bandani Slums-Kisumu County, giving malaria talk to the residents, I narrowed down on the signs and symptoms of malaria, the treatment and causes. Some of the causes like not sleeping under the treated mosquito nets, vector control. The signs and symptoms like high ever, shaking, chills, pain in the muscles and abdomen. Some people feel very sick, fatigue, fever, night sweats, nausea, shivering diarrhea, vomiting, headache and coldness. Upon completion, one Mrs. Mary Onyango approached me and requested that I visit her home. On our way to her homestead, she narrated to me some of the signs we talked about earlier that she has been seeing little girl experiencing. On reaching her homestead a few kilometers from where we were, I met the little girl. She was sweating all over her body. She told me she had headache; I saw her shivering and was vomiting. Based on what I saw, I concluded the child might have been suffering from malaria. I told the mother to do the sponging to reduce the temperature due to the high fever. I advised the mother to take her to the nearest health facility for further management. After two days, I did a follow-up home visit to see how the little girl was. She was given anti-malaria tablets and was responding well to the treatment. ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Malaria During my health education at Bandani Slums-Kisumu County, giving malaria talk to the residents, I narrowed down on the signs and symptoms of malaria, the treatment and causes. Some of the causes like not sleeping under the treated mosquito nets, vector control. The signs and symptoms like high ever, shaking, chills, pain in the muscles and abdomen. Some people feel very sick, fatigue, fever, night sweats, nausea, shivering diarrhea, vomiting, headache and coldness. Upon completion, one Mrs. Mary Onyango approached me and requested that I visit her home. On our way to her homestead, she narrated to me some of the signs we talked about earlier that she has been seeing little girl experiencing. On reaching her homestead a few kilometers from where we were, I met the little girl. She was sweating all over her body. She told me she had headache; I saw her shivering and was vomiting. Based on what I saw, I concluded the child might have been suffering from malaria. I told the mother to do the sponging to reduce the temperature due to the high fever. I advised the mother to take her to the nearest health facility for further management. After two days, I did a follow-up home visit to see how the little girl was. She was given anti-malaria tablets and was responding well to the treatment. ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Community Empowerment Through Education</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Menstrual Hygiene/Teenage Pregnancy Many teenage adolescent girls and young women suffer from what we call menstrual poverty. Menstrual poverty is an incidence whereby a girl is not able to get access to menstrual aids such as sanitary towels and menstrual cups. At the beginning of December, teenage pregnancy rapid growth raised an alarm whereby many individuals and like-minded individuals came together to find out why most of our teenage girls are getting pregnant. The 16-day activism and activism that brought about ??????? for Google meets and physical meetings helped me reach out to more than 50 girls and had some chit chats. From the interactions, I found out that menstrual poverty is a major leading factor in this lack of sanitary towels during this time of the month forcing some girls to engage in transactional sex which back to these unwanted teenage pregnancies. From this I, as a CHW, decided to partner with other ??? and individuals to fundraise for pads to give these girls. This has helped reduce and prevent some if not all. Most men and adults too have been sensitized by me that menstruation is not a woman issue but a human issue and we should all support our girls during this time of the month. ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Health Literacy and Misconceptions</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Menstrual Hygiene/Teenage Pregnancy Many teenage adolescent girls and young women suffer from what we call menstrual poverty. Menstrual poverty is an incidence whereby a girl is not able to get access to menstrual aids such as sanitary towels and menstrual cups. At the beginning of December, teenage pregnancy rapid growth raised an alarm whereby many individuals and like-minded individuals came together to find out why most of our teenage girls are getting pregnant. The 16-day activism and activism that brought about ??????? for Google meets and physical meetings helped me reach out to more than 50 girls and had some chit chats. From the interactions, I found out that menstrual poverty is a major leading factor in this lack of sanitary towels during this time of the month forcing some girls to engage in transactional sex which back to these unwanted teenage pregnancies. From this I, as a CHW, decided to partner with other ??? and individuals to fundraise for pads to give these girls. This has helped reduce and prevent some if not all. Most men and adults too have been sensitized by me that menstruation is not a woman issue but a human issue and we should all support our girls during this time of the month. ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Men Served</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Malaria Malaria is a disease caused by a parasite called plasmodium parasite, transmitted by the bite of infected Anopheles mosquitos. Malaria spreads by animal or insect bites or stings and by blood products (unclean needles or unscreened blood). The physical symptoms are like fever, vomiting, headache, yellow skin, diarrhea, fatigue, kidney failure, seizure/confusion, sweating, muscle aches, chest pain, chills that shake the whole body, dizziness and severe symptoms such as paralysis. Therefore, in any case I feel these symptoms, some of them, not all because I may not go through all of the symptoms. Why? It may happen from time to time. It is advisable that the moment it starts, I will force myself to go to the hospital for a check-up because that is the right place for me to get treatment. Hence, it will also help me to avoid it to become severe. Malaria even treated can re-occur again and again, so it is good to take action immediately before danger. I do advise people with malaria symptoms to go for a test before taking any painkiller, because this can cause danger. I also take an action by taking some of them in hospitals so that they can get treatment. I assure them to finish the malaria dose and treatment to avoid it from reoccurring again after a short time. On the prevention side part of it, I avoid mosquito bites by using insect repellent, hence tell the community to do net. You also have to wear long-sleeved clothing and long pants if you are outdoors at night. For pregnant mothers, I tell them to go for check-up whenever they feel the symptoms because malaria affects her and the fetus. It can lead to maternal anemia, fetal loss, premature delivery, and delivery of low-birth-weight infants. So many people have died because of malaria and what causes this is ignorance. Some of the patients ignore the symptoms and also take wrong medication before tests, leading to severe infections hence death. It is good to love yourself, love and protect your life because it is given once by our creator who is God. Observe cleanliness at all cost to prevent more infections from occurring. ---</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Community Empowerment Through Education</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Malaria Malaria is a disease caused by a parasite called plasmodium parasite, transmitted by the bite of infected Anopheles mosquitos. Malaria spreads by animal or insect bites or stings and by blood products (unclean needles or unscreened blood). The physical symptoms are like fever, vomiting, headache, yellow skin, diarrhea, fatigue, kidney failure, seizure/confusion, sweating, muscle aches, chest pain, chills that shake the whole body, dizziness and severe symptoms such as paralysis. Therefore, in any case I feel these symptoms, some of them, not all because I may not go through all of the symptoms. Why? It may happen from time to time. It is advisable that the moment it starts, I will force myself to go to the hospital for a check-up because that is the right place for me to get treatment. Hence, it will also help me to avoid it to become severe. Malaria even treated can re-occur again and again, so it is good to take action immediately before danger. I do advise people with malaria symptoms to go for a test before taking any painkiller, because this can cause danger. I also take an action by taking some of them in hospitals so that they can get treatment. I assure them to finish the malaria dose and treatment to avoid it from reoccurring again after a short time. On the prevention side part of it, I avoid mosquito bites by using insect repellent, hence tell the community to do net. You also have to wear long-sleeved clothing and long pants if you are outdoors at night. For pregnant mothers, I tell them to go for check-up whenever they feel the symptoms because malaria affects her and the fetus. It can lead to maternal anemia, fetal loss, premature delivery, and delivery of low-birth-weight infants. So many people have died because of malaria and what causes this is ignorance. Some of the patients ignore the symptoms and also take wrong medication before tests, leading to severe infections hence death. It is good to love yourself, love and protect your life because it is given once by our creator who is God. Observe cleanliness at all cost to prevent more infections from occurring. ---</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Trust and Cultural Mediation</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Malaria Malaria is a disease caused by a parasite called plasmodium parasite, transmitted by the bite of infected Anopheles mosquitos. Malaria spreads by animal or insect bites or stings and by blood products (unclean needles or unscreened blood). The physical symptoms are like fever, vomiting, headache, yellow skin, diarrhea, fatigue, kidney failure, seizure/confusion, sweating, muscle aches, chest pain, chills that shake the whole body, dizziness and severe symptoms such as paralysis. Therefore, in any case I feel these symptoms, some of them, not all because I may not go through all of the symptoms. Why? It may happen from time to time. It is advisable that the moment it starts, I will force myself to go to the hospital for a check-up because that is the right place for me to get treatment. Hence, it will also help me to avoid it to become severe. Malaria even treated can re-occur again and again, so it is good to take action immediately before danger. I do advise people with malaria symptoms to go for a test before taking any painkiller, because this can cause danger. I also take an action by taking some of them in hospitals so that they can get treatment. I assure them to finish the malaria dose and treatment to avoid it from reoccurring again after a short time. On the prevention side part of it, I avoid mosquito bites by using insect repellent, hence tell the community to do net. You also have to wear long-sleeved clothing and long pants if you are outdoors at night. For pregnant mothers, I tell them to go for check-up whenever they feel the symptoms because malaria affects her and the fetus. It can lead to maternal anemia, fetal loss, premature delivery, and delivery of low-birth-weight infants. So many people have died because of malaria and what causes this is ignorance. Some of the patients ignore the symptoms and also take wrong medication before tests, leading to severe infections hence death. It is good to love yourself, love and protect your life because it is given once by our creator who is God. Observe cleanliness at all cost to prevent more infections from occurring. ---</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mother and Infant Care</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Malaria Malaria is a disease caused by a parasite called plasmodium parasite, transmitted by the bite of infected Anopheles mosquitos. Malaria spreads by animal or insect bites or stings and by blood products (unclean needles or unscreened blood). The physical symptoms are like fever, vomiting, headache, yellow skin, diarrhea, fatigue, kidney failure, seizure/confusion, sweating, muscle aches, chest pain, chills that shake the whole body, dizziness and severe symptoms such as paralysis. Therefore, in any case I feel these symptoms, some of them, not all because I may not go through all of the symptoms. Why? It may happen from time to time. It is advisable that the moment it starts, I will force myself to go to the hospital for a check-up because that is the right place for me to get treatment. Hence, it will also help me to avoid it to become severe. Malaria even treated can re-occur again and again, so it is good to take action immediately before danger. I do advise people with malaria symptoms to go for a test before taking any painkiller, because this can cause danger. I also take an action by taking some of them in hospitals so that they can get treatment. I assure them to finish the malaria dose and treatment to avoid it from reoccurring again after a short time. On the prevention side part of it, I avoid mosquito bites by using insect repellent, hence tell the community to do net. You also have to wear long-sleeved clothing and long pants if you are outdoors at night. For pregnant mothers, I tell them to go for check-up whenever they feel the symptoms because malaria affects her and the fetus. It can lead to maternal anemia, fetal loss, premature delivery, and delivery of low-birth-weight infants. So many people have died because of malaria and what causes this is ignorance. Some of the patients ignore the symptoms and also take wrong medication before tests, leading to severe infections hence death. It is good to love yourself, love and protect your life because it is given once by our creator who is God. Observe cleanliness at all cost to prevent more infections from occurring. ---</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Successful Outcomes</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Malaria My personal experience about malaria has been very challenging as it affects me periodically and comes unexpectedly. There is a day I fell ill at night while asleep and my symptoms were for malaria because I felt cold with shivering, then developed a high temperature accompanied by severe sweating and headache. In my case, I normally use thermometer to know if am having malaria by checking on my temperature level. If my temperature exceeds 38C or above, then I take painkillers to relief pain, only at night but if I have malaria during the day I go to the hospital. There was a time I had malaria and took Coartem as it is known to reduce malaria faster, then again visited the hospital and it did not reflect that I have malaria as compared to the time when I take painkillers. My advice to people is always to avoid using Coartem without visiting the hospital at first and rather use painkillers to relief pain. After visiting the hospital my eating a bit usually changes, I eat a lot so as to heal faster. In most cases, when I have malaria, it usually comes with migraine, so when I experience such, I take hot strong tea with a lot of sugar, then relax my mind and sleep. When I wake up, I am always free from migraine because I believe my malaria comes with headache followed by migraine. ---</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Health Literacy and Misconceptions</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Teenage Pregnancy/HIV AIDS Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners, they have which is not healthy. ---</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Health Literacy and Misconceptions</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Teenage Pregnancy/HIV AIDS Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners, they have which is not healthy. ---</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Referrals and Advocacy</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Teenage Pregnancy/HIV AIDS Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners, they have which is not healthy. ---</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Community Empowerment Through Education</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Teenage Pregnancy/HIV AIDS Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners, they have which is not healthy. ---</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Successful Outcomes</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Teenage Pregnancy/HIV AIDS Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners, they have which is not healthy. ---</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Disease Burden</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Malaria People who have malaria usually feel very sick with high fever and shaking chills. However, the introduction malaria vaccine as a preventive measure for the disease has been seen as a huge step in the fight against the disease. Although WHO has approved the vaccine to be used in children in countries with high number of cases, the disease still remains the number one killer of children. According to a client whom I met during our health education session, her experience with malaria was that she lost her appetite after the attack. She further stated that she had alternating body temperature which was at times cold and at times very hot. She noted that the alternating body temperatures were accompanied by high fever, vomiting of yellowish substance, body aches and fatigue. The client observed that she also lost a significant body weight due to her missing meals because of lost appetite. She later went to seek medical attention a few days when the symptoms persisted. Her experience with malaria is not different from mine. I had encounter with malaria a year ago where the symptoms included high body temperature, fatigue, body ache and high fever. As CHWs, we urge people to prevent themselves from malaria by visiting health centers whenever they experience such symptoms. ---</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Personal Disease Management and Adherence</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Malaria People who have malaria usually feel very sick with high fever and shaking chills. However, the introduction malaria vaccine as a preventive measure for the disease has been seen as a huge step in the fight against the disease. Although WHO has approved the vaccine to be used in children in countries with high number of cases, the disease still remains the number one killer of children. According to a client whom I met during our health education session, her experience with malaria was that she lost her appetite after the attack. She further stated that she had alternating body temperature which was at times cold and at times very hot. She noted that the alternating body temperatures were accompanied by high fever, vomiting of yellowish substance, body aches and fatigue. The client observed that she also lost a significant body weight due to her missing meals because of lost appetite. She later went to seek medical attention a few days when the symptoms persisted. Her experience with malaria is not different from mine. I had encounter with malaria a year ago where the symptoms included high body temperature, fatigue, body ache and high fever. As CHWs, we urge people to prevent themselves from malaria by visiting health centers whenever they experience such symptoms. ---</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Referrals and Advocacy</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Malaria People who have malaria usually feel very sick with high fever and shaking chills. However, the introduction malaria vaccine as a preventive measure for the disease has been seen as a huge step in the fight against the disease. Although WHO has approved the vaccine to be used in children in countries with high number of cases, the disease still remains the number one killer of children. According to a client whom I met during our health education session, her experience with malaria was that she lost her appetite after the attack. She further stated that she had alternating body temperature which was at times cold and at times very hot. She noted that the alternating body temperatures were accompanied by high fever, vomiting of yellowish substance, body aches and fatigue. The client observed that she also lost a significant body weight due to her missing meals because of lost appetite. She later went to seek medical attention a few days when the symptoms persisted. Her experience with malaria is not different from mine. I had encounter with malaria a year ago where the symptoms included high body temperature, fatigue, body ache and high fever. As CHWs, we urge people to prevent themselves from malaria by visiting health centers whenever they experience such symptoms. ---</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Successful Outcomes</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Malaria People who have malaria usually feel very sick with high fever and shaking chills. However, the introduction malaria vaccine as a preventive measure for the disease has been seen as a huge step in the fight against the disease. Although WHO has approved the vaccine to be used in children in countries with high number of cases, the disease still remains the number one killer of children. According to a client whom I met during our health education session, her experience with malaria was that she lost her appetite after the attack. She further stated that she had alternating body temperature which was at times cold and at times very hot. She noted that the alternating body temperatures were accompanied by high fever, vomiting of yellowish substance, body aches and fatigue. The client observed that she also lost a significant body weight due to her missing meals because of lost appetite. She later went to seek medical attention a few days when the symptoms persisted. Her experience with malaria is not different from mine. I had encounter with malaria a year ago where the symptoms included high body temperature, fatigue, body ache and high fever. As CHWs, we urge people to prevent themselves from malaria by visiting health centers whenever they experience such symptoms. ---</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Children Served</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>First Aid for Nose Bleed During nose bleed, blood flows from one or both nostrils. It can be heavy or light and last from a few seconds to 15 minutes or more. I came across a patient who had nose bleeding each time and she did not know what to do. I told her how to stop it by: sitting down and firmly pinch the soft part of your nose, just above your nostrils, for at least 10-15 minutes. Lean forward and breathe through your mouth. This will drain blood into your nose instead of down the back of your throat. Place an ice pack/bag or frozen vegetables covered by a towel on the bridge of your nose. Stay upright rather than lying down, as this reduces blood pressure in the blood vessels of your nose and will discourage further bleeding. At least she got relieved after doing all these leading to nose bleed occurring rarely. ---</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Personal Disease Management and Adherence</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>First Aid for Nose Bleed During nose bleed, blood flows from one or both nostrils. It can be heavy or light and last from a few seconds to 15 minutes or more. I came across a patient who had nose bleeding each time and she did not know what to do. I told her how to stop it by: sitting down and firmly pinch the soft part of your nose, just above your nostrils, for at least 10-15 minutes. Lean forward and breathe through your mouth. This will drain blood into your nose instead of down the back of your throat. Place an ice pack/bag or frozen vegetables covered by a towel on the bridge of your nose. Stay upright rather than lying down, as this reduces blood pressure in the blood vessels of your nose and will discourage further bleeding. At least she got relieved after doing all these leading to nose bleed occurring rarely. ---</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Community Empowerment Through Education</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>First Aid for Nose Bleed During nose bleed, blood flows from one or both nostrils. It can be heavy or light and last from a few seconds to 15 minutes or more. I came across a patient who had nose bleeding each time and she did not know what to do. I told her how to stop it by: sitting down and firmly pinch the soft part of your nose, just above your nostrils, for at least 10-15 minutes. Lean forward and breathe through your mouth. This will drain blood into your nose instead of down the back of your throat. Place an ice pack/bag or frozen vegetables covered by a towel on the bridge of your nose. Stay upright rather than lying down, as this reduces blood pressure in the blood vessels of your nose and will discourage further bleeding. At least she got relieved after doing all these leading to nose bleed occurring rarely. ---</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Clinical Interventions by CHWs</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Malaria I know about two children who died from malaria (???????). Their parents kept them in the house, buying them drugs over-the-counter which did not go well with them at the time. They were taken to hospital. It was too late for they did not make it. As a CHW in my dealing with malaria, I do clear bushes in my surroundings and also to clear mosquito breeding sites, sleeping under treated mosquito net. Also, I do go for check-ups whenever I experience malaria symptom. As I do all this, I also advise people to do the same. ---</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Water Quality, Sanitation, and Hygiene</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Malaria I know about two children who died from malaria (???????). Their parents kept them in the house, buying them drugs over-the-counter which did not go well with them at the time. They were taken to hospital. It was too late for they did not make it. As a CHW in my dealing with malaria, I do clear bushes in my surroundings and also to clear mosquito breeding sites, sleeping under treated mosquito net. Also, I do go for check-ups whenever I experience malaria symptom. As I do all this, I also advise people to do the same. ---</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Referrals and Advocacy</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Malaria I know about two children who died from malaria (???????). Their parents kept them in the house, buying them drugs over-the-counter which did not go well with them at the time. They were taken to hospital. It was too late for they did not make it. As a CHW in my dealing with malaria, I do clear bushes in my surroundings and also to clear mosquito breeding sites, sleeping under treated mosquito net. Also, I do go for check-ups whenever I experience malaria symptom. As I do all this, I also advise people to do the same. ---</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Community Empowerment Through Education</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Malaria I know about two children who died from malaria (???????). Their parents kept them in the house, buying them drugs over-the-counter which did not go well with them at the time. They were taken to hospital. It was too late for they did not make it. As a CHW in my dealing with malaria, I do clear bushes in my surroundings and also to clear mosquito breeding sites, sleeping under treated mosquito net. Also, I do go for check-ups whenever I experience malaria symptom. As I do all this, I also advise people to do the same. ---</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Families Served</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Malaria I know about two children who died from malaria (???????). Their parents kept them in the house, buying them drugs over-the-counter which did not go well with them at the time. They were taken to hospital. It was too late for they did not make it. As a CHW in my dealing with malaria, I do clear bushes in my surroundings and also to clear mosquito breeding sites, sleeping under treated mosquito net. Also, I do go for check-ups whenever I experience malaria symptom. As I do all this, I also advise people to do the same. ---</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Disease Burden</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Teenage Pregnancy Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners they have which is not healthy. ---</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Personal Disease Management and Adherence</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Teenage Pregnancy Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners they have which is not healthy. ---</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Health Literacy and Misconceptions</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Teenage Pregnancy Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners they have which is not healthy. ---</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Referrals and Advocacy</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Teenage Pregnancy Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners they have which is not healthy. ---</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Community Empowerment Through Education</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Teenage Pregnancy Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners they have which is not healthy. ---</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Successful Outcomes</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Teenage Pregnancy Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners they have which is not healthy. ---</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Marginalized Groups Served</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Child Nutrition Access to adequate and nutritious food is important for good health. The convention provides for the application of readily available technology for the provision of adequate nutritious food and clear drinking water. Both the state and the parent of the child have to participate in ensuring that children are now nourished nutrition support programs by the government and non-governmental organizations such as the school feeding programs in arid and semi-arid areas plays on essential role nutrition awareness programs that educate parents on how to supplement the staple food with easily available nutrients are also important. As CHW, I am thankful to KUAP, as they offer nutrition programs and teaching to young mothers on how they can handle their little ones. ---</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Child Nutrition Access to adequate and nutritious food is important for good health. The convention provides for the application of readily available technology for the provision of adequate nutritious food and clear drinking water. Both the state and the parent of the child have to participate in ensuring that children are now nourished nutrition support programs by the government and non-governmental organizations such as the school feeding programs in arid and semi-arid areas plays on essential role nutrition awareness programs that educate parents on how to supplement the staple food with easily available nutrients are also important. As CHW, I am thankful to KUAP, as they offer nutrition programs and teaching to young mothers on how they can handle their little ones. ---</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Successful Outcomes</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CHW Training Having been in Nyalenda for the last five years, health information in the community was not taken seriously. But after the training and we started working in the community giving health information, now they can go to the nearest facility and at the same time we do referrals. In the training, I got more information about COVID-19 even before the government COVID lockdown and how to manage COVID-19. Before training, I could not do first aid. But after the training, I have some skills and now am in a position to perform first aid before I do referrals to the facility. Patient assessment was quite challenging to me. But after being trained by Madam Winnie and Mr. Kituli, I can now do it on my own and know how to handle some of the problems and refer. With the information I have from the training and my knowledge, the community I am in today is changing gradually. They are very eager to be taught more and more about the health issues, because they have been lacking information for so long. But thanks to WiRED International for the training they gave us, because now we are able to give back to the community the information we get, and the community is impressed so much, and they are requesting that we keep on giving them the information that they had lacked for some time. I would like to thank Madam Winnie and Mr. Kituli so much for the training they gave us. It is just on another level. Thanks to Lilian for believing in us and giving us a chance to be trained. Thanks to Mr. Gary for the support you gave us during the training up to now. May God bless you. ---</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Marginalized Groups Served</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CHW Training Having been in Nyalenda for the last five years, health information in the community was not taken seriously. But after the training and we started working in the community giving health information, now they can go to the nearest facility and at the same time we do referrals. In the training, I got more information about COVID-19 even before the government COVID lockdown and how to manage COVID-19. Before training, I could not do first aid. But after the training, I have some skills and now am in a position to perform first aid before I do referrals to the facility. Patient assessment was quite challenging to me. But after being trained by Madam Winnie and Mr. Kituli, I can now do it on my own and know how to handle some of the problems and refer. With the information I have from the training and my knowledge, the community I am in today is changing gradually. They are very eager to be taught more and more about the health issues, because they have been lacking information for so long. But thanks to WiRED International for the training they gave us, because now we are able to give back to the community the information we get, and the community is impressed so much, and they are requesting that we keep on giving them the information that they had lacked for some time. I would like to thank Madam Winnie and Mr. Kituli so much for the training they gave us. It is just on another level. Thanks to Lilian for believing in us and giving us a chance to be trained. Thanks to Mr. Gary for the support you gave us during the training up to now. May God bless you. ---</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Lack of Resources</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -511,7 +1544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,28 +1577,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>Referrals and Advocacy</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>gpt</t>
+          <t>o3</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>Referrals and Advocacy</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -574,97 +1607,853 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>Disease Burden</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>o3</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>Disease Burden</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>gpt</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>Stigma or Discrimination</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>o3</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>Stigma or Discrimination</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Women Served</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Women Served</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Monitoring and Follow-Up</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Monitoring and Follow-Up</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Trust and Cultural Mediation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Trust and Cultural Mediation</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Personal Disease Management and Adherence</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Personal Disease Management and Adherence</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Community Empowerment Through Education</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Community Empowerment Through Education</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Systemic Barriers</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Systemic Barriers</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Lack of Knowledge</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Lack of Knowledge</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Water Quality, Sanitation, and Hygiene</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Water Quality, Sanitation, and Hygiene</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Successful Outcomes</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Successful Outcomes</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>6</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Health Literacy and Misconceptions</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Health Literacy and Misconceptions</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Men Served</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Men Served</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Mother and Infant Care</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Mother and Infant Care</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Children Served</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Children Served</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Clinical Interventions by CHWs</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Clinical Interventions by CHWs</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Families Served</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Families Served</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Marginalized Groups Served</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Marginalized Groups Served</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Lack of Resources</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Lack of Resources</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -678,7 +2467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -711,28 +2500,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>Referrals and Advocacy</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>gpt</t>
+          <t>o3</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>Referrals and Advocacy</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -741,97 +2530,853 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>Disease Burden</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>o3</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>Disease Burden</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>gpt</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>Stigma or Discrimination</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>o3</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>Stigma or Discrimination</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
         <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Women Served</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Women Served</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Monitoring and Follow-Up</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Monitoring and Follow-Up</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Trust and Cultural Mediation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Trust and Cultural Mediation</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Personal Disease Management and Adherence</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Personal Disease Management and Adherence</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Community Empowerment Through Education</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>22.22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Community Empowerment Through Education</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" t="n">
+        <v>77.78</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Systemic Barriers</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Systemic Barriers</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Lack of Knowledge</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Lack of Knowledge</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Water Quality, Sanitation, and Hygiene</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Water Quality, Sanitation, and Hygiene</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Successful Outcomes</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Successful Outcomes</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>6</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Health Literacy and Misconceptions</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Health Literacy and Misconceptions</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Men Served</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Men Served</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Mother and Infant Care</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Mother and Infant Care</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Children Served</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Children Served</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Clinical Interventions by CHWs</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Clinical Interventions by CHWs</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Families Served</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Families Served</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Marginalized Groups Served</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Marginalized Groups Served</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Lack of Resources</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Lack of Resources</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -845,7 +3390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,35 +3418,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>After receiving training from WiRED, I was able to teach others in my village about malaria prevention. The community now trusts me and people ask me for advice all the time.</t>
+          <t>Abortion Abortion is very deadly because one can bleed to death. Some have been able to heal from post abortion hemorrhage, but some end up having anemia. This topic has been left out, yet it is very important because we have many of our young girls are dying from excess bleeding from abortion. I talked to a group of young girls who agreed to open up about their abortion experience and none of them enjoyed even a bit of it. I agreed with them that there would be no more abortion. Those above 20, they should go for family planning and the rest to practice ---</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>gpt</t>
+          <t>o3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>{
-  "training": 1.0,
-  "trust": 0.8,
-  "community impact": 1.0,
-  "confidence": 0.6,
-  "knowledge sharing": 1.0
+  "CHW Empowerment Through Training": 0.05,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.0,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.15,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.8,
+  "Gender-Based Violence (GBV) and Child Protection": 0.05,
+  "Health Literacy and Misconceptions": 0.3,
+  "Mental Health Awareness and Support": 0.2,
+  "Referrals and Advocacy": 0.5,
+  "Community Empowerment Through Education": 0.6,
+  "Resource and Material Distribution": 0.0,
+  "Monitoring and Follow-Up": 0.05,
+  "Trust and Cultural Mediation": 0.6,
+  "Clinical Interventions by CHWs": 0.05,
+  "Mother and Infant Care": 0.2,
+  "Successful Outcomes": 0.6,
+  "Material or Training Requests": 0.15,
+  "Children Served": 0.8,
+  "Elderly Served": 0.0,
+  "Women Served": 0.9,
+  "Men Served": 0.0,
+  "Families Served": 0.05,
+  "Marginalized Groups Served": 0.6,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.05,
+  "Disease Burden": 0.5,
+  "Stigma or Discrimination": 0.55,
+  "Mental or Emotional Distress": 0.3,
+  "Lack of Resources": 0.1,
+  "Systemic Barriers": 0.2,
+  "Overburdened CHWs": 0.05,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.1
 }</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The testimonial clearly mentions receiving training and sharing that knowledge with others in the community, hence the high scores for 'training', 'community impact', and 'knowledge sharing'. The person also mentions being trusted and asked for advice, indicating 'trust'. The 'confidence' aspect is somewhat implied, hence a lower score.</t>
+          <t>CHW Empowerment Through Training: The testimonial describes the speaker discussing abortion with young girls but does not mention the CHW receiving any form of training, attending workshops, or gaining new knowledge through a structured program. Therefore, there is only a negligible indication (if any) of empowerment through training. | Menstrual Hygiene Education and Challenges: The testimonial discusses abortion, post-abortion bleeding, and family planning but does not address menstruation, menstrual hygiene products, or education about menstruation. Therefore, it does not align with the concept. | Drug Abuse: Environment and Awareness: The testimonial discusses abortion, hemorrhage, and family planning, but contains no mention of substance abuse, addiction, alcohol, or related social/environmental factors. Therefore the concept does not apply. | CHW-Led Infectious Disease Management: The testimonial focuses on abortion, hemorrhage, and family planning, with no mention of CHWs addressing infectious diseases or providing relevant outreach or education. Therefore, the concept does not apply. | Water Quality, Sanitation, and Hygiene: The testimonial discusses abortion, hemorrhage, and family planning. There is no mention of clean water, sanitation practices, or hygiene education related to water, so the concept does not apply. | Personal Disease Management and Adherence: The testimonial focuses on preventing unsafe abortions and the dangers of post-abortion hemorrhage, rather than describing ongoing disease management, medication use, or adherence to a treatment regimen. While it touches on a health complication (hemorrhage/anemia), there is no clear discussion of managing a diagnosed condition or sticking to treatment, so only a very weak alignment with the concept exists. | Nutrition Education and Food Access: The testimonial discusses abortion, bleeding, and family planning, with no mention of food, nutrition education, or access to healthy meals. Therefore the concept is not present. | Sexual and Reproductive Health Education: The CHW discusses abortion risks and advises girls over 20 to seek family planning—both topics squarely within reproductive health education. While explicit details on condoms or STI prevention are absent, the testimonial clearly provides education on reproductive choices and dangers, meeting the inclusion criteria for the concept. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses on unsafe abortions and related health risks, without mentioning abuse, exploitation, or violence against the girls. While it does involve young girls’ health, it does not describe GBV or child protection interventions, so alignment with the concept is minimal. | Health Literacy and Misconceptions: The speaker presents abortion as uniformly “very deadly,” implying potential exaggeration or misconception about its risks, but does not clearly describe correcting misinformation or discussing misunderstood medical facts. There is a hint of limited health literacy around abortion complications, giving weak evidence that misconceptions influence decisions, so a low-moderate score is appropriate. | Mental Health Awareness and Support: The testimonial focuses on the physical dangers of abortion (bleeding, anemia) and prevention. While it notes that girls 'opened up' and did not 'enjoy' the experience—hinting at some emotional distress—there is no explicit reference to depression, anxiety, counseling, or psychological support from the CHW. Thus, only minimal indirect evidence of mental-health awareness is present. | Referrals and Advocacy: The CHW advises girls over 20 to \ | Community Empowerment Through Education: The CHW describes educating a group of young girls about the dangers of abortion, leading the group to openly share experiences and collectively agree \ | Resource and Material Distribution: The testimonial only describes speaking with young girls about abortion and advising on family planning; it does not mention giving out any supplies or materials. According to the concept definition, material distribution is required, so the concept is not present. | Monitoring and Follow-Up: The testimonial describes a single discussion with a group of young girls about abortion and family planning but provides no indication of returning to check on them or continuing interactions. This fits the exclusion criterion of a one-time educational session, showing almost no evidence of ongoing monitoring or follow-up. | Trust and Cultural Mediation: The CHW facilitated a sensitive discussion about abortion in which young girls 'agreed to open up' about their experiences—evidence that she had built sufficient trust to overcome social stigma and barriers around the topic. However, there is no explicit mention of linguistic translation or detailed cultural mediation activities, so alignment is moderate rather than strong. | Clinical Interventions by CHWs: The testimonial describes talking to a group of girls about abortion and encouraging family planning—this is health education/counseling. There is no mention of the CHW administering medication, treating wounds, or performing any hands-on clinical tasks. Thus, it falls under the exclusion criteria for the concept, warranting a near-zero score. | Mother and Infant Care: The testimonial concerns complications and counseling around abortion—a pregnancy-related issue—so it minimally touches maternal health. However, it does not discuss prenatal care, childbirth, postpartum follow-up, or infant health/nutrition. Therefore alignment with the Mother and Infant Care concept is weak. | Successful Outcomes: The CHW reports discussing abortion with a group of young girls who then \ | Material or Training Requests: The CHW notes that abortion as a topic \ | Children Served: The CHW speaks directly to \ | Elderly Served: The testimonial discusses abortion issues among young girls; it does not mention older adults, seniors, or any assistance provided to them. | Women Served: The testimonial describes the CHW speaking with a group of young girls and women (those above 20) about abortion, hemorrhage risks, and family-planning options—directly providing education and assistance tailored to females. This fits the inclusion criteria (support for women’s health) and is a clear, specific instance, warranting a strong score. | Men Served: The testimonial focuses entirely on abortion experiences among young girls and does not mention men or boys, nor does it address any gender-specific issues faced by them. Therefore, the concept 'Men Served' is not present. | Families Served: The testimonial describes counseling a group of young girls about abortion and recommending family planning, but it does not mention households, parents with children, or any family units being served. The reference to \ | Parsing failed for concept 'Families Served' | Marginalized Groups Served: The CHW is working with young girls who are experiencing unsafe abortions, a group subject to social stigma and limited access to safe reproductive services, suggesting they are underserved. This shows moderate alignment with the concept, though the testimonial does not explicitly frame them as structurally marginalized beyond implication. | Financial Hardship: The testimonial discusses health risks of abortion and counseling young girls but does not mention poverty, lack of income, transportation costs, or any material scarcity. Therefore, the Financial Hardship concept is not present. | Social Isolation: The testimonial focuses on abortion-related health risks and discussions with a group of young girls; it does not mention living alone, loneliness, or lack of social support. Minimal to no evidence of social isolation. | Disease Burden: The testimonial discusses serious health consequences (post-abortion hemorrhage and resulting anemia). While hemorrhage is acute, anemia can represent an ongoing condition, hinting at longer-term illness. This provides some, but not strong, evidence of chronic or disabling disease burden, warranting a moderate score. | Stigma or Discrimination: The speaker frames abortion as deadly and agrees with the girls that they should never do it again, which conveys moral judgment toward the behavior and implicitly toward those who had abortions. This suggests some social stigma, but there is no explicit mention of being shunned or excluded, so the alignment is moderate rather than strong. | Mental or Emotional Distress: The testimonial hints that the young girls had an unpleasant, possibly traumatic abortion experience (\ | Lack of Resources: The testimonial highlights that abortion care is a neglected topic and young girls are dying from hemorrhage, suggesting a general gap in services, but it does NOT explicitly state that the community health worker lacks medicine, supplies, or other concrete resources. Therefore, evidence for the specific concept of CHWs lacking resources is minimal. | Systemic Barriers: The testimonial primarily discusses the dangers of abortion and the CHW’s conversation with young girls. The only possible systemic element is the statement that the issue ‘has been left out,’ which vaguely implies neglect by larger institutions, but there is no clear mention of health-facility shortages, policy barriers, or other explicit systemic obstacles. Therefore, evidence of systemic barriers is weak. | Overburdened CHWs: The testimonial discusses health risks of abortion and counseling young girls but does not mention the CHW’s workload, exhaustion, or being overwhelmed. Any inference of overburdening is speculative, so alignment is minimal. | Lack of Follow-Through: The testimonial describes the CHW discussing abortion risks and advising girls, but there is no mention of starting an intervention that was then abandoned or left unresolved. Therefore, no evidence of lack of follow-through is present. | Lack of Knowledge: The testimonial notes that abortion as a topic 'has been left out,' but the CHW does not express personal uncertainty or request additional training. There is only a vague suggestion that the issue is neglected, so evidence of the CHW’s own lack of knowledge is minimal.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>After receiving training from WiRED, I was able to teach others in my village about malaria prevention. The community now trusts me and people ask me for advice all the time.</t>
+          <t>Abortion Abortion is very deadly because one can bleed to death. Some have been able to heal from post abortion hemorrhage, but some end up having anemia. This topic has been left out, yet it is very important because we have many of our young girls are dying from excess bleeding from abortion. I talked to a group of young girls who agreed to open up about their abortion experience and none of them enjoyed even a bit of it. I agreed with them that there would be no more abortion. Those above 20, they should go for family planning and the rest to practice ---</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -912,164 +3488,350 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>{
-  "training": 1.0,
-  "trust": 0.9,
-  "community impact": 0.9,
-  "confidence": 0.7,
-  "knowledge sharing": 1.0
+  "CHW Empowerment Through Training": 0.0,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.0,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.0,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.8,
+  "Gender-Based Violence (GBV) and Child Protection": 0.3,
+  "Health Literacy and Misconceptions": 0.2,
+  "Mental Health Awareness and Support": 0.3,
+  "Referrals and Advocacy": 0.0,
+  "Community Empowerment Through Education": 0.7,
+  "Resource and Material Distribution": 0.0,
+  "Monitoring and Follow-Up": 0.1,
+  "Trust and Cultural Mediation": 0.7,
+  "Clinical Interventions by CHWs": 0.0,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.7,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.7,
+  "Elderly Served": 0.0,
+  "Women Served": 0.9,
+  "Men Served": 0.0,
+  "Families Served": 0.1,
+  "Marginalized Groups Served": 0.7,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.2,
+  "Stigma or Discrimination": 0.2,
+  "Mental or Emotional Distress": 0.3,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.0
 }</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The testimonial explicitly mentions receiving training and teaching others (knowledge sharing), making these clear 1.0 scores. Trust is directly stated as something gained from the community (0.9). Community impact is evident through the village-wide education and behavioral change (0.9). Confidence is implied through the person's ability to teach and advise others, though not explicitly stated (0.7).</t>
+          <t>CHW Empowerment Through Training: The testimonial describes a CHW discussing abortion risks with young girls but contains no mention of the CHW receiving training, attending workshops, or gaining knowledge through formal CHW programs. The speaker appears to be sharing information based on existing knowledge rather than describing empowerment through training. | Menstrual Hygiene Education and Challenges: This testimonial focuses entirely on abortion and its health risks, not menstruation. While it discusses reproductive health issues affecting young girls and women, it does not address menstrual hygiene, education about menstruation, access to menstrual products, or menstruation-related stigma. The content is explicitly about abortion experiences and family planning, which falls outside the concept's definition. | Drug Abuse: Environment and Awareness: The testimonial focuses entirely on abortion and its health consequences, with no mention of drug abuse, substance use, addiction, or any related environmental factors. The concept requires content about substance abuse and its social/environmental contributors, which is completely absent from this testimonial. | CHW-Led Infectious Disease Management: The testimonial focuses entirely on abortion-related health issues and reproductive health education, not infectious diseases. While it shows CHW involvement in health education, abortion and post-abortion hemorrhage are not infectious diseases. The concept explicitly requires focus on infectious diseases like TB or COVID-19, which are completely absent from this testimonial. | Water Quality, Sanitation, and Hygiene: The testimonial focuses entirely on abortion, its health risks, and family planning education. There is no mention of water quality, sanitation practices, handwashing, or hygiene education. The content explicitly deals with reproductive health issues, which falls outside the scope of this concept. | Personal Disease Management and Adherence: This testimonial focuses on abortion prevention and reproductive health education, not on managing chronic or infectious diseases. While it discusses health consequences (hemorrhage, anemia), these are presented as risks to avoid rather than conditions being actively managed through treatment adherence or lifestyle adjustments. The CHW is providing preventive education, not guiding disease management. | Nutrition Education and Food Access: The testimonial focuses entirely on abortion, its health risks, and family planning education. There is no mention of nutrition, food security, healthy eating, or food access. The content explicitly deals with reproductive health issues, which falls outside the scope of the nutrition education and food access concept. | Sexual and Reproductive Health Education: Strong alignment with the concept as the testimonial directly addresses reproductive health education through discussing abortion risks with young girls and recommending family planning as an alternative. The CHW is providing health education about reproductive choices and safer alternatives, which aligns with the inclusion criteria of 'family planning' and reproductive health education, though it doesn't explicitly mention STIs or condoms. | Gender-Based Violence (GBV) and Child Protection: The testimonial discusses abortion and its health consequences among young girls, which has weak alignment with child protection concerns. While it addresses a serious health issue affecting young people and mentions counseling/intervention with girls, it does not explicitly reference abuse, violence, or exploitation. The focus is on the medical dangers of abortion rather than GBV or protection from harm. | Health Literacy and Misconceptions: The testimonial focuses on educating about the health risks of abortion (hemorrhage, anemia) and promoting family planning alternatives. While there is an educational component about health consequences, there is no clear evidence of correcting misconceptions or addressing misinformation. The CHW appears to be providing accurate health information rather than correcting false beliefs, which aligns with the exclusion criteria of 'accurate health discussions with no misunderstanding present.' | Mental Health Awareness and Support: The testimonial shows weak alignment with mental health support. While the CHW discusses abortion experiences with young girls who 'agreed to open up' about traumatic experiences, and mentions that 'none of them enjoyed even a bit of it' (suggesting emotional distress), the focus remains primarily on physical health risks (bleeding, anemia, death) rather than psychological well-being or emotional support. The counseling appears more educational about physical dangers than addressing mental health needs. | Parsing failed for concept 'Mental Health Awareness and Support' | Referrals and Advocacy: The testimonial describes educating young girls about abortion risks and encouraging family planning, but contains no evidence of referrals, helping with appointments, or navigating healthcare systems. The speaker provides health education and counseling but does not act as an intermediary or advocate within the health system as defined by the concept. | Community Empowerment Through Education: The testimonial shows moderate alignment with community empowerment through education. The CHW conducted group education with young girls about abortion risks, leading to a collective agreement to avoid abortion and adopt family planning. This demonstrates peer education and group action with intended behavior change. However, the score is not higher because there's no evidence yet of actual long-term change or self-reliance - only an agreement to change behavior. | Resource and Material Distribution: The testimonial describes a CHW conducting education and counseling about abortion risks with young girls, but contains no mention of distributing any physical resources, materials, or supplies. The CHW only provided advice and facilitated discussion, which falls under the exclusion criteria of 'education or advice without material support.' | Monitoring and Follow-Up: The testimonial describes a one-time group discussion about abortion experiences with young girls. While the CHW mentions reaching an agreement with them about future behavior, there is no evidence of planned follow-up visits, ongoing monitoring, or checking back on their progress. This aligns with the exclusion criteria of 'one-time visits or initial health education sessions with no follow-up.' | Trust and Cultural Mediation: The CHW demonstrates trust-building by creating a safe space where young girls felt comfortable opening up about their sensitive abortion experiences. This shows the CHW successfully navigated social barriers around a taboo topic and earned enough trust for the girls to share personal stories. However, the focus is primarily on health education rather than cultural mediation or translation between communities and health systems. | Parsing failed for concept 'Trust and Cultural Mediation' | Clinical Interventions by CHWs: The testimonial describes health education about abortion risks and counseling young girls, but contains no evidence of direct clinical interventions. The CHW is providing education and advice about family planning options, which falls under the exclusion criteria of 'health education or referrals without direct clinical interaction.' There is no mention of administering medication, treating wounds, or any other hands-on medical tasks. | Mother and Infant Care: This testimonial focuses on abortion prevention and family planning education for young women, not on prenatal, childbirth, postpartum, or infant care. While it addresses reproductive health, it explicitly excludes the mother-infant care elements defined in the concept and instead discusses preventing pregnancy and abortion risks. | Successful Outcomes: The testimonial shows moderate alignment with successful outcomes. The CHW engaged young girls in discussion about abortion, and they 'agreed to open up' and ultimately agreed 'there would be no more abortion.' This represents a positive behavioral change commitment. Additionally, the CHW provided guidance on family planning alternatives. While the outcome is promising, it lacks concrete evidence of actual behavior change or health improvements, making it similar to the 0.4 example but stronger due to the explicit agreement reached. | Material or Training Requests: The testimonial discusses the serious health risks of abortion and describes educational work with young girls, but contains no explicit requests for materials, supplies, or training. While the CHW identifies abortion as an important topic that 'has been left out,' this is a description of a gap rather than a direct request for help, which falls under the exclusion criteria. | Children Served: The testimonial describes direct engagement with 'young girls' about abortion experiences and health education. While not all may be under 18, the reference to 'young girls' and the distinction made for 'those above 20' suggests many were likely minors. The CHW provided health education and counseling, which aligns with the inclusion criteria of 'support for children or adolescents in health.' The score is not higher because the exact ages are not specified. | Elderly Served: The testimonial focuses exclusively on abortion education and counseling with young girls. There is no mention of elderly people, seniors, or grandparents, nor any assistance provided to older adults. The CHW's work described here is entirely centered on reproductive health issues affecting young women, which clearly falls outside the scope of the 'Elderly Served' concept. | Parsing failed for concept 'Elderly Served' | Women Served: Strong direct alignment with the concept. The CHW directly engaged with 'a group of young girls' about abortion experiences and provided guidance on family planning. This matches the inclusion criteria of 'assistance or education for women, especially around health or safety.' The testimonial describes specific CHW interaction addressing a critical women's health issue, similar to the 0.9-scored example about talking with young women about pregnancy protection. | Men Served: The testimonial focuses exclusively on young girls and women's experiences with abortion. There is no mention of men or boys being served, supported, or addressed in any capacity. The CHW describes counseling 'a group of young girls' about abortion experiences, with no reference to male involvement or support. | Parsing failed for concept 'Men Served' | Families Served: The testimonial focuses on individual young girls and women regarding abortion and family planning education. While family planning is mentioned, there is no evidence of CHW support for households, parents with children, or extended family units. The intervention targets individuals rather than family structures, aligning with the exclusion criteria. | Marginalized Groups Served: The testimonial describes CHW support to young girls dealing with abortion-related issues, a stigmatized topic that is 'left out' of discussions. The CHW provided education and support to a group facing both health risks and social stigma around abortion. While not explicitly labeled as marginalized, these young girls represent an underserved population dealing with a highly stigmatized issue, aligning moderately with the concept definition. | Financial Hardship: The testimonial focuses entirely on health risks and experiences related to abortion, with no mention of financial constraints, inability to afford care, transportation costs, or material scarcity. The content is about medical complications and health education, not economic hardship. | Social Isolation: The testimonial focuses on abortion experiences and health education with young girls. There is no mention of living alone, lack of support systems, loneliness, or social abandonment. The CHW describes group discussions with multiple young girls, indicating social interaction rather than isolation. | Disease Burden: The testimonial discusses abortion complications like hemorrhage and anemia, which can have health impacts. However, these are presented as potential acute complications rather than chronic conditions or disabilities. The focus is on prevention and education about abortion risks, not managing ongoing illness. This aligns weakly with the concept as it mentions health conditions (anemia) but doesn't describe chronic illness management or long-term disability care. | Stigma or Discrimination: The testimonial focuses primarily on health risks and consequences of abortion rather than social rejection or judgment. While abortion is often a stigmatized topic, the text doesn't explicitly mention shame, exclusion, or judgment from others. The CHW describes talking to young girls who 'agreed to open up,' which could suggest some social discomfort around the topic, but this is indirect evidence at best. The emphasis is on medical dangers and prevention strategies, not on social stigma. | Mental or Emotional Distress: The testimonial contains weak evidence of mental or emotional distress. While the young girls who 'opened up about their abortion experience' and 'none of them enjoyed even a bit of it' suggests some emotional difficulty, the focus is primarily on physical health consequences (bleeding, death, anemia) rather than explicit mental or emotional suffering. The distress is implied but not directly expressed in terms of depression, hopelessness, trauma, or emotional overwhelm as defined in the concept. | Lack of Resources: The testimonial discusses the serious health consequences of abortion and the CHW's educational efforts with young girls, but contains no mention of lacking medicine, tools, or support. The CHW successfully conducted group discussions and provided guidance without indicating any resource constraints or inability to help due to insufficient supplies. | Systemic Barriers: The testimonial discusses abortion as a health issue and the CHW's educational intervention with young girls, but does not mention any systemic barriers preventing the CHW from helping. There are no references to health facility shortages, institutional problems, or external conditions beyond the CHW's control. The CHW appears able to engage with the community and provide education without systemic obstacles. | Overburdened CHWs: The testimonial focuses entirely on abortion as a health topic and the CHW's educational interaction with young girls. There is no mention of workload, exhaustion, being overwhelmed, or having too many patients. The CHW describes conducting health education successfully without any indication of being overburdened. | Lack of Follow-Through: The testimonial describes a CHW educating young girls about abortion risks and reaching an agreement with them about prevention strategies. There is no evidence of abandonment, interrupted care, or unresolved issues. The CHW appears to have completed the educational intervention successfully, with the girls agreeing to avoid abortion and consider family planning options. | Lack of Knowledge: The CHW demonstrates knowledge about abortion complications and engages confidently with young girls on the topic. There is no mention of being unsure how to proceed, needing additional training, or asking for help. The testimonial shows the CHW actively educating and counseling, not expressing any knowledge gaps.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>After receiving training from WiRED, I was able to teach others in my village about malaria prevention. The community now trusts me and people ask me for advice all the time.</t>
+          <t>Asthma Asthma is a chronic disease which can affect everyone. I spotted a young child wheezing and as I inquired from the mother, she told me that she was suspecting that the child might be having common cold as the child was coughing due to change of weather. But to me as a CHW I thought that it would be best if the child was to be taken to the hospital for medical examination so that the mother could know what was wrong with the child. With my help, I referred the ??? to take the child to the hospital. The child was tested and was found to be ailing from asthma. The child was put onto medication and as now the child showing some improvements. Though asthma is a chronic disease, if proper medication and continuous taking of the drugs is well conducted, it can help in reducing chances of child fatality. ---</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>o3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>{
-  "training": 1.0,
-  "trust": 1.0,
-  "community impact": 1.0,
-  "confidence": 0.8,
-  "knowledge sharing": 1.0
+  "CHW Empowerment Through Training": 0.2,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.05,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.9,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.6,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.9,
+  "Community Empowerment Through Education": 0.2,
+  "Resource and Material Distribution": 0.05,
+  "Monitoring and Follow-Up": 0.4,
+  "Trust and Cultural Mediation": 0.3,
+  "Clinical Interventions by CHWs": 0.4,
+  "Mother and Infant Care": 0.2,
+  "Successful Outcomes": 0.9,
+  "Material or Training Requests": 0.0,
+  "Children Served": 1.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.3,
+  "Men Served": 0.0,
+  "Families Served": 0.7,
+  "Marginalized Groups Served": 0.1,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.9,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.0,
+  "Lack of Resources": 0.05,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.2
 }</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">The testimonial explicitly mentions receiving "training" and then using that training to teach others, which clearly indicates "knowledge sharing."  The statement "The community now trusts me and people ask me for advice" directly reflects increased "trust" and positive "community impact." While "confidence" isn't explicitly stated, the testimonial implies increased confidence due to the newly acquired knowledge and the community's trust, so it's given a high score.  </t>
+          <t>CHW Empowerment Through Training: The testimonial describes the CHW identifying asthma symptoms and referring the child, but it never mentions receiving training, attending workshops, or gaining knowledge through a formal CHW program. The implicit possibility that the CHW knows what to do offers only minimal evidence of empowerment through training, similar to the 0.2 example provided. | Menstrual Hygiene Education and Challenges: The testimonial discusses identifying and referring a child with asthma; it contains no mention of menstruation, menstrual products, stigma, or education. Therefore the concept is not present. | Drug Abuse: Environment and Awareness: The testimonial discusses asthma diagnosis and treatment for a child, with no reference to substance abuse, addiction, alcohol, peer influence, or environmental factors related to drug use. Therefore, the concept is not present. | CHW-Led Infectious Disease Management: The testimonial describes a CHW identifying and referring a child with asthma, which is a chronic non-infectious condition. There is CHW involvement, but no discussion of infectious disease symptoms, prevention, or outreach. Therefore, alignment with the infectious disease management concept is negligible. | Water Quality, Sanitation, and Hygiene: The testimonial focuses on identifying and referring a child with asthma; it contains no discussion of clean water, sanitation, or hygiene practices. | Personal Disease Management and Adherence: Testimonial discusses identifying a chronic disease (asthma), referring the child for diagnosis, initiation of medication, and emphasizes ongoing drug use to manage the condition—directly reflecting disease management and adherence guidance provided by a CHW. | Nutrition Education and Food Access: The testimonial focuses on identifying asthma and referring the child for medical treatment; it does not mention food, nutrition education, or access to adequate nutrition. | Sexual and Reproductive Health Education: The testimonial discusses identifying and referring a child with asthma; it contains no content related to family planning, STI prevention, HIV, or any sexual and reproductive health topic. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses on identifying and referring a child with asthma for medical care. There is no mention of abuse, exploitation, violence, or related CHW interventions, so the concept of GBV and Child Protection is not present. | Health Literacy and Misconceptions: The mother believed the child’s wheezing and cough were just a common cold due to weather changes, indicating a misunderstanding of symptoms and potential severity. The CHW intervened to clarify and refer for proper diagnosis. This reflects a moderate instance of limited health literacy influencing care‐seeking behavior, fitting the concept though not as strongly as cases with overt misinformation. | Mental Health Awareness and Support: The testimonial focuses solely on identifying and referring a child with asthma, a physical health issue. There is no mention of psychological well-being, emotional distress, or mental health support, so the concept does not apply. | Parsing failed for concept 'Mental Health Awareness and Support' | Referrals and Advocacy: The CHW explicitly states they \ | Community Empowerment Through Education: The story centers on an individual referral for medical care. While the CHW likely informed the mother about asthma management, there is no evidence of broader health education leading to community or peer change, nor mention of lasting behavior change beyond this one case. Fits the exclusion for isolated intervention, so only weak alignment. | Resource and Material Distribution: The CHW identifies a health issue and refers the child to the hospital but does not mention giving out medication, supplies, or other materials. Thus, there is virtually no evidence of resource distribution. | Monitoring and Follow-Up: The CHW refers the child to the hospital and later notes that the child is “now showing some improvements,” implying awareness of the child’s progress. However, there is no explicit description of repeated visits or ongoing checks; the account centers on a single referral event. This provides only minimal evidence of sustained monitoring or follow-up, so a weak alignment score (0.4) is appropriate. | Trust and Cultural Mediation: The CHW advises the mother to seek hospital care after the mother misattributes the child’s symptoms, suggesting some knowledge mediation. However, there is no explicit discussion of cultural, linguistic barriers, or conscious trust-building efforts; the testimonial focuses mainly on clinical referral. Therefore alignment with the concept is weak. | Clinical Interventions by CHWs: The CHW observed the child and referred the mother to take the child to the hospital, with no mention of administering medication or performing any hands-on treatment. This is similar to the exclusion example (referral only) scored at 0.4, indicating weak alignment with clinical intervention. | Mother and Infant Care: The story involves advising a mother about her young child’s wheezing and referring the child to a hospital. While this touches on child health, it is not specifically about prenatal care, childbirth, postpartum support, or typical infant-focused topics (feeding, immunization, growth monitoring). Thus, there is only minimal relevance to the defined Mother and Infant Care concept. | Successful Outcomes: The CHW identified a health issue, referred the child to the hospital, the child was diagnosed, placed on medication, and is now showing improvements—clearly demonstrating a positive outcome directly attributable to the CHW’s action. This matches the concept’s definition and inclusion criteria for improved conditions after CHW intervention, warranting a strong score. | Material or Training Requests: The testimonial recounts identifying a child's asthma and facilitating referral, but makes no request for additional materials, supplies, or training. Therefore, the concept does not apply. | Children Served: The CHW directly identifies a young child in distress, refers the mother to the hospital, and discusses treatment and outcomes for that child. This is a clear, unambiguous instance of providing health support to a minor, fitting the inclusion criteria perfectly. | Elderly Served: The testimonial discusses assisting a young child with asthma; there is no mention of seniors or older adults, so the concept does not apply. | Women Served: A woman (the child’s mother) received advice and a referral from the CHW, so some assistance was provided to an adult female in her caregiving role. However, the focus of the testimonial is the child’s asthma, not a gender-specific need or challenge, so alignment with the concept is weak to moderate. | Men Served: Testimonial discusses a young child (gender unspecified) and their mother with no mention of adult males or boys receiving support or facing gendered challenges. Therefore, the concept 'Men Served' is not present. | Families Served: The testimonial describes the CHW working with a mother to address her young child’s health issue, indicating support that involves at least two family members (parent and child). This is a direct instance of family-oriented care, though it focuses only on one child rather than the whole household, so alignment is moderate rather than perfect. | Marginalized Groups Served: The testimonial discusses helping a young child with asthma but does not indicate that the child belongs to a structurally excluded or stigmatized group. It is a generic community health interaction, similar to the example scored 0.1. | Financial Hardship: The testimonial discusses identifying asthma and referring the child to hospital care, but it contains no mention of cost, poverty, transportation barriers, or any other financial difficulty. Therefore, the Financial Hardship concept is not present. | Social Isolation: The testimonial focuses on identifying and treating a child's asthma; there is no mention of the mother or child being socially isolated, lacking support systems, or experiencing loneliness. | Disease Burden: Asthma is explicitly identified as a chronic disease requiring ongoing treatment, matching the inclusion criterion of long-term illness. The CHW addresses continuous medication and monitoring, demonstrating a strong, unambiguous alignment with the Disease Burden concept. | Stigma or Discrimination: The testimonial describes recognizing asthma symptoms and facilitating medical referral; it does not mention any social judgment, shame, or exclusion related to the condition, so the stigma/discrimination concept is absent. | Mental or Emotional Distress: The testimonial focuses solely on a child's physical condition (asthma) and the referral for medical treatment. There are no expressions of depression, stress, hopelessness, or other emotional strain, so the concept of Mental or Emotional Distress is not present. | Lack of Resources: The testimonial describes observing symptoms and referring the child to a hospital; it does not mention insufficient medicines, tools, or other resource constraints for the CHW. Thus, evidence of a lack of resources is essentially absent. | Systemic Barriers: The testimonial describes the CHW identifying asthma and successfully referring the child to a hospital without mentioning any institutional shortages, distance, cost, overcrowding, or other systemic obstacles. Therefore, no systemic barrier is evidenced. | Overburdened CHWs: The testimonial describes a specific case of identifying and referring a child for asthma care, with no mention of excessive workload, exhaustion, or being overwhelmed. Therefore, the concept of overburdened CHWs is not present. | Lack of Follow-Through: The CHW took action, referred the child to the hospital, and the child received treatment and improved. There is no indication of abandonment or unresolved issue, so the concept of Lack of Follow-Through does not apply. | Lack of Knowledge: The CHW does not explicitly state ignorance or request additional training, but the decision to refer the child because the CHW could not determine the exact illness hints at limited knowledge. This is only indirect evidence, so the alignment with the concept is weak.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I visit homes and share information about clean water. People now recognize me as a health worker.</t>
+          <t>Asthma Asthma is a chronic disease which can affect everyone. I spotted a young child wheezing and as I inquired from the mother, she told me that she was suspecting that the child might be having common cold as the child was coughing due to change of weather. But to me as a CHW I thought that it would be best if the child was to be taken to the hospital for medical examination so that the mother could know what was wrong with the child. With my help, I referred the ??? to take the child to the hospital. The child was tested and was found to be ailing from asthma. The child was put onto medication and as now the child showing some improvements. Though asthma is a chronic disease, if proper medication and continuous taking of the drugs is well conducted, it can help in reducing chances of child fatality. ---</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>gpt</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>{
-  "training": 0.1,
-  "trust": 0.8,
-  "community impact": 0.9,
-  "confidence": 0.7,
-  "knowledge sharing": 1.0
+  "CHW Empowerment Through Training": 0.6,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.0,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.8,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.7,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.9,
+  "Community Empowerment Through Education": 0.2,
+  "Resource and Material Distribution": 0.0,
+  "Monitoring and Follow-Up": 0.2,
+  "Trust and Cultural Mediation": 0.3,
+  "Clinical Interventions by CHWs": 0.1,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.8,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.9,
+  "Elderly Served": 0.0,
+  "Women Served": 0.5,
+  "Men Served": 0.0,
+  "Families Served": 0.7,
+  "Marginalized Groups Served": 0.1,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.9,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.0,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.0
 }</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The testimonial indicates that the person is recognized as a health worker, suggesting trust from the community. They are also sharing information about clean water, which is a clear example of knowledge sharing. The impact on the community is high as they are educating people about health. Confidence is inferred from the person's ability to visit homes and share information. Training is less relevant as there is no explicit mention of it.</t>
+          <t>CHW Empowerment Through Training: The testimonial shows moderate alignment with CHW empowerment through training. The CHW demonstrates applied knowledge by recognizing symptoms beyond what the mother suspected and making an appropriate referral. The phrase 'to me as a CHW' suggests role-based knowledge, and their understanding of asthma as a chronic disease requiring proper medication indicates training. However, there is no explicit mention of receiving training, attending workshops, or how this knowledge was acquired, which prevents a higher score. | Menstrual Hygiene Education and Challenges: The testimonial is entirely focused on identifying and managing asthma in a child. There is no mention of menstruation, menstrual hygiene, products, or related education. The content explicitly deals with a respiratory condition (asthma) and has no connection to the concept of menstrual hygiene education and challenges. | Drug Abuse: Environment and Awareness: This testimonial focuses entirely on identifying and managing asthma in a child. There is no mention of substance abuse, addiction, alcohol, peer influence, or drug education. The only reference to 'drugs' is in the medical context of asthma medication, which is explicitly excluded by the concept's criteria. The testimonial is about chronic disease management, not substance abuse or its environmental factors. | CHW-Led Infectious Disease Management: This testimonial describes a CHW identifying and referring a child with asthma, which is a chronic respiratory condition, not an infectious disease. While the CHW demonstrates health education and referral skills, the concept specifically requires management of infectious diseases like TB or COVID-19. Asthma is explicitly non-infectious, making this a clear exclusion. | Water Quality, Sanitation, and Hygiene: The testimonial focuses entirely on identifying and managing asthma in a child. There is no mention of water quality, sanitation practices, hygiene education, handwashing, or any water-related disease prevention measures. The content is exclusively about respiratory health and medical referral, which falls outside the scope of this concept. | Personal Disease Management and Adherence: Strong alignment with the concept. The testimonial describes a CHW identifying potential asthma symptoms, facilitating proper diagnosis at a hospital, and the child being put on medication with improvements shown. It explicitly mentions 'continuous taking of the drugs' as important for managing this chronic disease, which directly relates to treatment adherence. The score is 0.8 rather than higher because while disease management and adherence are clearly present, the focus is more on the diagnosis process than ongoing adherence support. | Nutrition Education and Food Access: The testimonial focuses entirely on identifying and managing asthma in a child. There is no mention of nutrition education, food access, healthy eating, or any food-related topics. The content is exclusively about respiratory health and medical referral, which clearly falls outside the concept's inclusion criteria. | Sexual and Reproductive Health Education: The testimonial focuses entirely on identifying and managing asthma in a child. There is no mention of family planning, STI prevention, HIV awareness, reproductive rights, or any sexual health topics. This clearly falls outside the concept's inclusion criteria. | Gender-Based Violence (GBV) and Child Protection: This testimonial describes a CHW identifying potential asthma in a child and referring them for medical care. There is no mention of abuse, violence, exploitation, or any form of GBV or child protection issues. The story focuses entirely on a respiratory health condition and appropriate medical referral, which clearly falls outside the concept's inclusion criteria. | Health Literacy and Misconceptions: The testimonial shows moderate alignment with health literacy issues. The mother misunderstood her child's symptoms, attributing wheezing and coughing to a common cold due to weather changes, when the child actually had asthma. This represents a clear misconception about symptom interpretation and disease recognition. The CHW corrected this by facilitating proper medical diagnosis. The score is not higher because the misconception was about symptom misinterpretation rather than more severe issues like disease origin myths or medical mistrust. | Mental Health Awareness and Support: This testimonial focuses entirely on identifying and addressing a physical health condition (asthma) in a child. There is no mention of psychological well-being, emotional support, or mental health concerns. The CHW's intervention was purely medical in nature - recognizing respiratory symptoms and facilitating hospital care for a chronic physical condition. This clearly falls under the exclusion criteria of 'medical diagnoses without a mental/emotional context.' | Referrals and Advocacy: Strong direct alignment with the concept. The CHW explicitly states 'I referred the ??? to take the child to the hospital' after identifying concerning symptoms (wheezing). This matches the first example of identifying disease symptoms and referring for testing, demonstrating the CHW's role as an intermediary who facilitated access to healthcare services. | Community Empowerment Through Education: This testimonial describes a one-time referral of a child with asthma symptoms to a hospital. While the CHW demonstrated health knowledge by recognizing potential asthma symptoms, there is no evidence of community education, behavior change, or empowerment. The focus is on individual medical intervention rather than educational activities that lead to self-reliance or improved community health habits. This aligns with the exclusion criteria of 'one-time events' without lasting behavior change. | Resource and Material Distribution: The testimonial describes a CHW identifying potential asthma symptoms and referring a child to the hospital for medical examination. While medication was eventually prescribed by the hospital, the CHW did not distribute any materials, supplies, or resources themselves. The CHW's role was limited to assessment and referral, which falls under the exclusion criteria of 'education or advice without material support.' | Monitoring and Follow-Up: The testimonial describes a one-time referral where the CHW identified symptoms and helped the mother take the child to the hospital. While the CHW mentions the child is 'now showing some improvements,' there is no evidence of the CHW personally conducting follow-up visits or ongoing monitoring. The improvement update appears to be information received indirectly rather than through active follow-up care by the CHW. | Trust and Cultural Mediation: The testimonial shows weak alignment with trust and cultural mediation. While the CHW does bridge a knowledge gap by recognizing potential asthma symptoms that the mother attributed to a common cold, and successfully refers the family to the hospital, there is no explicit mention of building trust, navigating cultural barriers, or addressing any hesitation about seeking medical care. The interaction appears primarily clinical and educational rather than focused on trust-building or cultural mediation. | Clinical Interventions by CHWs: The CHW only referred the mother to take the child to the hospital for medical examination. There is no mention of the CHW providing any direct clinical intervention such as administering medication, treating wounds, or managing physical symptoms. This aligns with the exclusion criteria of 'referrals without direct clinical interaction' and is similar to the example 'I told a mother to take her child to the hospital for their rash' which scores 0.4, though this case involves even less direct guidance about a specific condition. | Mother and Infant Care: While this testimonial involves a mother and child, it focuses on diagnosing and managing asthma, which is a general pediatric health issue. The concept specifically excludes 'general family or women's health support not specific to mother/infant,' and there is no mention of prenatal, childbirth, postpartum care, or infant-specific health concerns like feeding or immunizations. | Successful Outcomes: Strong alignment with successful outcomes. The CHW identified a wheezing child, referred them to the hospital where asthma was diagnosed, and the child was put on medication and is 'showing some improvements.' This demonstrates a clear positive change resulting from the CHW's intervention, though not a complete resolution since asthma is chronic. Similar to the 0.9 example but with partial rather than full recovery. | Material or Training Requests: The testimonial describes a CHW's experience identifying and referring a child with asthma symptoms, but contains no requests for materials, supplies, or training. The CHW narrates their successful intervention without expressing any needs or asking for additional resources to better serve their community. | Children Served: Strong direct alignment with the concept. The testimonial clearly describes a CHW identifying a young child with breathing difficulties, providing health guidance to the mother, and facilitating a hospital referral that led to an asthma diagnosis and treatment. This demonstrates direct health support and intervention for a minor, matching the inclusion criteria of 'support for children in health.' The score is 0.9 rather than 1.0 due to the redacted word that might have provided additional context. | Elderly Served: The testimonial explicitly describes helping a young child with asthma symptoms. There is no mention of elderly individuals, seniors, or grandparents. The focus is entirely on pediatric care, which clearly falls outside the concept of serving elderly populations. | Women Served: The testimonial describes a CHW interacting with a mother about her child's health condition. While the mother is clearly a woman who received assistance (referral and health education), she is mentioned primarily in her role as a parent rather than as someone receiving gender-specific services. This represents moderate alignment with the concept - there is CHW interaction with a woman addressing a specific need, but the focus is on the child's asthma rather than women-specific health or safety issues. | Men Served: The testimonial describes a CHW helping a mother and child with asthma diagnosis and treatment. There is no mention of adult males or boys, nor any gendered roles or challenges. The focus is entirely on a child (gender unspecified) and their mother, making this concept clearly not present in the testimonial. | Families Served: The testimonial describes a CHW helping a mother and her child, which constitutes a family unit. The CHW identified health concerns in the child, communicated with the mother, and facilitated medical care that benefited both family members. This aligns moderately well with the concept as it shows family-focused intervention, though it's limited to just mother and child rather than a larger household or extended family. | Marginalized Groups Served: The testimonial describes helping a child with asthma, but there is no indication that the child or family belongs to a marginalized or structurally excluded group. The CHW provided important health support, but the case appears to be standard healthcare assistance without evidence of addressing stigma, discrimination, or serving an underserved population. This aligns with the example 'helped someone with common health issues, but the person was not from a marginalized or underserved group.' | Parsing failed for concept 'Marginalized Groups Served' | Financial Hardship: The testimonial describes a CHW identifying potential asthma in a child and referring them to a hospital. There is no mention of financial difficulties, inability to afford care, transportation costs, or any material scarcity. The referral appears to be based solely on medical need, not financial constraints. | Social Isolation: The testimonial describes a CHW helping a mother get medical care for her child with asthma. There is no mention of loneliness, living alone, lack of support systems, or abandonment. The child has a present and engaged mother, indicating an existing support system. The focus is entirely on medical intervention for a respiratory condition, not social isolation. | Disease Burden: Strong direct alignment with the concept. The testimonial explicitly identifies asthma as a 'chronic disease' multiple times and describes a case where a child was diagnosed with this long-term condition requiring ongoing medication. The CHW emphasizes the chronic nature of asthma and the need for 'continuous taking of the drugs' to manage it, which clearly represents a chronic illness requiring long-term management. | Stigma or Discrimination: The testimonial describes a CHW helping a mother get proper medical care for a child with asthma. There is no mention of social rejection, shame, exclusion, or judgment from others. The focus is entirely on medical diagnosis and treatment, with no evidence of stigma or discrimination related to the child's condition. | Mental or Emotional Distress: This testimonial focuses entirely on a physical health condition (asthma) and medical intervention. There is no mention of depression, hopelessness, trauma, stress, or any emotional distress. The narrative describes respiratory symptoms, medical referral, and treatment - all physical health concerns that fall under the exclusion criteria. | Lack of Resources: The testimonial describes a successful referral where the CHW identified symptoms, advised the mother, and facilitated hospital care. There is no mention of lacking medicine, tools, or support. The CHW was able to fulfill their role effectively by referring the child for proper diagnosis and treatment. | Systemic Barriers: The testimonial describes a successful referral where the CHW identified symptoms, advised the mother to seek hospital care, and the child received proper diagnosis and treatment. There is no mention of any systemic barriers preventing care - the hospital was accessible, testing was available, and medication was provided. The narrative focuses on the CHW's successful intervention without any obstacles from larger institutions or systemic forces. | Overburdened CHWs: The testimonial describes a successful case where the CHW identified a child with asthma symptoms and facilitated proper medical care. There is no mention of exhaustion, being overwhelmed, or having too many patients. The CHW appears to have had adequate time to properly assess the situation and provide appropriate referral, indicating they were not overburdened. | Lack of Follow-Through: The CHW successfully identified a potential health issue, referred the child to the hospital, and the child received proper diagnosis and treatment for asthma. The testimonial indicates the child is now showing improvements with medication. This represents completed care with successful follow-through, not abandonment or unresolved issues. | Lack of Knowledge: The CHW demonstrates competent knowledge by recognizing potential asthma symptoms (wheezing) that the mother misidentified as a common cold. The CHW appropriately referred the child to the hospital, which led to proper diagnosis and treatment. There is no mention of uncertainty, need for training, or inability to proceed due to knowledge gaps. The CHW acted confidently within their scope of practice.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I visit homes and share information about clean water. People now recognize me as a health worker.</t>
+          <t>Tuberculosis People living in ????? settlements tend to not be concerned about their health. Many are first concerned with how they can attend to their daily labor to make some money which can help them put some food on the table. People are coughing and just take it as a normal cough. During my field work, I came across two people who were coughing as I was training them. I asked them when they started coughing and advised them to see the doctor for a tuberculosis test. They went for the test and one of them was found positive for tuberculosis. She has begun treatment and hopefully she will be okay. As CHW, I am now talking to many and also refer them for tuberculosis test at ???? ---</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>o3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>{
-  "training": 0.7,
-  "trust": 0.9,
-  "community impact": 0.8,
-  "confidence": 0.6,
-  "knowledge sharing": 1.0
+  "CHW Empowerment Through Training": 0.2,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 1.0,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.85,
+  "Nutrition Education and Food Access": 0.25,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.7,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 1.0,
+  "Community Empowerment Through Education": 0.4,
+  "Resource and Material Distribution": 0.05,
+  "Monitoring and Follow-Up": 0.5,
+  "Trust and Cultural Mediation": 0.3,
+  "Clinical Interventions by CHWs": 0.3,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.8,
+  "Material or Training Requests": 0.05,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.6,
+  "Men Served": 0.0,
+  "Families Served": 0.1,
+  "Marginalized Groups Served": 0.65,
+  "Financial Hardship": 0.7,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.9,
+  "Stigma or Discrimination": 0.05,
+  "Mental or Emotional Distress": 0.1,
+  "Lack of Resources": 0.05,
+  "Systemic Barriers": 0.5,
+  "Overburdened CHWs": 0.2,
+  "Lack of Follow-Through": 0.05,
+  "Lack of Knowledge": 0.05
 }</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The testimonial clearly shows knowledge sharing (1.0) as the person visits homes to share information. High trust (0.9) is evident as people recognize them as a health worker. Community impact (0.8) is strong through their outreach work. Training (0.7) is implied as they have knowledge to share. Confidence (0.6) is moderately present as they actively engage with the community.</t>
+          <t>CHW Empowerment Through Training: The testimonial describes the CHW providing training and referrals, but there is no explicit mention that the CHW themselves received training that enhanced their capacity. Any inference that the CHW must have been trained is indirect and weak, so only minimal evidence supports the concept. | Menstrual Hygiene Education and Challenges: The testimonial focuses solely on tuberculosis awareness and referrals; it contains no mention of menstruation, menstrual products, stigma, or education related to menstrual hygiene. | Drug Abuse: Environment and Awareness: The testimonial discusses tuberculosis awareness and referrals, with no references to substance use, addiction, alcohol, or related social/environmental factors. Therefore the concept is not present. | CHW-Led Infectious Disease Management: The testimonial clearly describes a CHW identifying potential tuberculosis cases, advising individuals to get tested, and referring others for testing—direct actions that match the definition of CHW-led outreach and management of an infectious disease. | Water Quality, Sanitation, and Hygiene: The testimonial focuses on identifying and referring tuberculosis cases; it contains no mention of clean water, sanitation practices, or hygiene education. Therefore, the Water Quality, Sanitation, and Hygiene concept does not apply. | Personal Disease Management and Adherence: The CHW encourages symptomatic individuals to get tested for tuberculosis; one is diagnosed and has begun treatment. This directly involves disease diagnosis and initiation of treatment, fitting the concept’s focus on managing infectious diseases through CHW guidance. Limited detail on long-term adherence keeps the score below a perfect match. | Nutrition Education and Food Access: The testimonial briefly notes that community members focus on daily labor to \ | Sexual and Reproductive Health Education: The testimonial focuses on tuberculosis awareness and referral, with no mention of family planning, STI prevention, HIV, condoms, or reproductive rights, so the concept is not present. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses solely on tuberculosis awareness and testing; it does not mention any abuse, exploitation, violence, or related CHW interventions. Therefore, the GBV and Child Protection concept is not applicable. | Health Literacy and Misconceptions: Residents assume persistent coughing is just a normal cough and are not concerned, showing lack of knowledge about tuberculosis symptoms. The CHW intervenes to correct this, fitting the concept of misinformation / low health literacy, though no explicit false belief about disease origin is stated. | Parsing failed for concept 'Health Literacy and Misconceptions' | Mental Health Awareness and Support: The testimonial exclusively discusses physical health (tuberculosis), screening, and treatment. It contains no mention of emotional well-being, depression, anxiety, or any mental health support, so the concept does not apply. | Referrals and Advocacy: The CHW explicitly states advising and referring individuals for tuberculosis testing after identifying symptoms, directly matching the concept of acting as an intermediary and making referrals within the health system. This is an unambiguous example identical to the provided high-score example ('I identified disease symptoms and referred the person for testing'), so it warrants a perfect score. | Community Empowerment Through Education: The CHW provides health education and referrals for TB testing, but the narrative centers on her individual actions rather than evidence of the community adopting self-sustaining behaviors or peer-driven change. This resembles the example of a one-time teaching session with uncertain impact (scored 0.4), so alignment with long-term community empowerment is weak to moderate. | Resource and Material Distribution: The testimonial describes advising and referring individuals for tuberculosis testing but does not mention providing or distributing any physical supplies (medication, food, hygiene kits, etc.). According to the definition and exclusion criteria, education or referral without material support does not constitute resource distribution, so only a minimal score is assigned. | Monitoring and Follow-Up: The CHW advises two coughing individuals to get tested, later reports that one tested positive and has started treatment—indicating she obtained information after the initial encounter, suggesting some follow-up. However, there is no explicit description of repeated visits or ongoing monitoring of the patient’s treatment, so alignment is moderate rather than strong. | Trust and Cultural Mediation: The CHW persuades community members who were unconcerned about their cough to seek TB testing, implying some level of earned trust, but there is no explicit discussion of overcoming cultural, linguistic, or social barriers. Evidence of trust-building is minimal and indirect, so alignment is weak. | Clinical Interventions by CHWs: The CHW primarily advises and refers people for tuberculosis testing; there is no description of administering medication or performing direct clinical care. This aligns weakly with the concept (similar to the referral example scored 0.4) but lacks the direct clinical intervention required for a higher score. | Mother and Infant Care: The testimonial focuses solely on identifying and referring adults with potential tuberculosis; there is no mention of pregnancy, childbirth, postpartum issues, or infant health. Therefore, the Mother and Infant Care concept does not apply. | Successful Outcomes: The CHW advised two coughing individuals to get tested; they followed through, one was diagnosed with TB and has started treatment. This shows a clear, positive result (diagnosis and initiation of care) directly attributable to the CHW’s intervention, fitting the inclusion criteria for successful outcomes, though full recovery is not yet confirmed, so slightly less than a perfect score. | Material or Training Requests: The testimonial talks about the CHW advising and referring people for tuberculosis tests but does not contain any explicit request for additional materials, supplies, or training. Therefore, only minimal alignment (if any) with the concept. | Children Served: The testimonial discusses tuberculosis awareness and referrals among adults; no mention or implication of minors under 18 receiving services. | Elderly Served: The testimonial discusses advising community members about tuberculosis testing, with no mention of older adults or seniors being served. Therefore, the concept is not present. | Women Served: The CHW describes providing care to a woman ('She has begun treatment') who tested positive for tuberculosis, indicating direct assistance to an adult female. However, the focus is largely on the community in general rather than women-specific issues, so alignment is moderate rather than strong. | Men Served: The testimonial discusses people in general and gives an example of a woman who tested positive for tuberculosis. There is no specific mention of adult males or boys being served, nor any gender-specific challenges or support directed to men. Therefore the concept is not present. | Families Served: The testimonial mentions helping two individuals and talking to many others, but there is no indication they are members of the same household or part of a family unit. This is individual-level assistance, so only a minimal connection to the Families Served concept is present. | Marginalized Groups Served: The CHW is working in ????? settlements where residents prioritize daily labor for food and neglect health, implying poverty and social exclusion. This suggests service to an underserved population, fitting the concept, but marginalization is only implied, not explicitly stated; hence a moderate alignment. | Financial Hardship: The testimonial notes that residents focus on daily labor to “make some money which can help them put some food on the table,” indicating material scarcity and limited income. This matches the inclusion criterion of statements about poverty or lack of resources, though it is not the central focus of the story, so a moderate score is appropriate. | Parsing failed for concept 'Financial Hardship' | Social Isolation: The testimonial discusses health behaviors regarding tuberculosis testing and economic priorities, but does not mention living alone, loneliness, lack of support systems, or abandonment. Therefore it does not fit the Social Isolation concept. | Disease Burden: The testimonial focuses on tuberculosis—an infectious disease that represents a significant and ongoing health burden. The CHW identifies coughing individuals, sends them for TB tests, and one patient begins treatment, fulfilling the inclusion criterion of chronic or serious disease references. This is a strong direct alignment with the concept. | Stigma or Discrimination: Testimonial talks about low health prioritization and encouraging TB testing, but does not mention any social rejection, shame, or judgment due to illness. Virtually no evidence of stigma, so only a negligible score. | Mental or Emotional Distress: The testimonial focuses on physical illness (tuberculosis) and the community’s prioritization of earning money. While poverty could imply stress, there is no explicit mention of depression, hopelessness, or emotional overwhelm. Thus, only minimal evidence of mental or emotional distress is present. | Lack of Resources: The testimonial describes educating community members and referring them for TB tests, but it does not mention shortages of medicine, tools, or other resources for the CHW. Therefore, there is virtually no evidence of a Lack of Resources, warranting only a minimal score. | Systemic Barriers: The testimonial notes that residents of impoverished settlements prioritize daily labor and earning money over seeking care, reflecting a socioeconomic condition outside the CHW’s control that hinders timely health-seeking. This fits the concept of systemic barriers (larger structural conditions limiting care). However, there is no mention of health-facility shortages, corruption, or other explicit institutional obstacles, so alignment is moderate rather than strong. | Overburdened CHWs: The CHW mentions \ | Lack of Follow-Through: The CHW advised coughing individuals to get tested, one received a diagnosis and started treatment. There is no indication that the CHW abandoned the case or that the issue remained unresolved, so evidence for Lack of Follow-Through is essentially absent. | Lack of Knowledge: The CHW confidently identified possible tuberculosis, advised testing, and continues referring others—no mention of uncertainty or need for additional training. Thus, evidence for lack of knowledge is virtually absent.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I visit homes and share information about clean water. People now recognize me as a health worker.</t>
+          <t>Tuberculosis People living in ????? settlements tend to not be concerned about their health. Many are first concerned with how they can attend to their daily labor to make some money which can help them put some food on the table. People are coughing and just take it as a normal cough. During my field work, I came across two people who were coughing as I was training them. I asked them when they started coughing and advised them to see the doctor for a tuberculosis test. They went for the test and one of them was found positive for tuberculosis. She has begun treatment and hopefully she will be okay. As CHW, I am now talking to many and also refer them for tuberculosis test at ???? ---</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>{
-  "training": 0.1,
-  "trust": 0.6,
-  "community impact": 0.8,
-  "confidence": 0.2,
-  "knowledge sharing": 0.7
+  "CHW Empowerment Through Training": 0.7,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.9,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.8,
+  "Nutrition Education and Food Access": 0.1,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.6,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.9,
+  "Community Empowerment Through Education": 0.3,
+  "Resource and Material Distribution": 0.1,
+  "Monitoring and Follow-Up": 0.2,
+  "Trust and Cultural Mediation": 0.7,
+  "Clinical Interventions by CHWs": 0.1,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.8,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.8,
+  "Men Served": 0.0,
+  "Families Served": 0.0,
+  "Marginalized Groups Served": 0.8,
+  "Financial Hardship": 0.8,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.8,
+  "Stigma or Discrimination": 0.1,
+  "Mental or Emotional Distress": 0.0,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.6,
+  "Overburdened CHWs": 0.1,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.0
 }</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The testimonial focuses on the impact of the person's work in the community by sharing information about clean water. This directly relates to 'community impact' and 'knowledge sharing'.  The phrase "People now recognize me as a health worker" suggests a degree of trust built within the community.  'Training' and 'confidence' are less prominent as the testimonial doesn't directly address those aspects, although some training may have been implied to enable the work.</t>
+          <t>CHW Empowerment Through Training: The testimonial shows moderate alignment with CHW empowerment through training. The CHW mentions 'during my field work, I came across two people who were coughing as I was training them,' indicating they conduct training activities. They also demonstrate knowledge application by identifying TB symptoms and making appropriate referrals. However, the testimonial doesn't explicitly mention the CHW receiving training themselves or attending workshops, which would strengthen the alignment. The focus is more on their current practice rather than how training empowered them to serve. | Menstrual Hygiene Education and Challenges: The testimonial focuses entirely on tuberculosis awareness, testing, and treatment. There is no mention of menstruation, menstrual hygiene, products, or related education. The content explicitly deals with a respiratory health issue (tuberculosis) and does not address any aspect of menstrual health or hygiene. | Drug Abuse: Environment and Awareness: The testimonial focuses entirely on tuberculosis awareness and healthcare access issues in settlements. There is no mention of drug abuse, addiction, alcohol, or substance-related topics. The environmental factors discussed (poverty, prioritizing work over health) relate to TB testing and treatment, not substance abuse. This clearly falls under the exclusion criteria as it contains no content about drugs or alcohol. | CHW-Led Infectious Disease Management: Strong direct alignment with the concept. The CHW actively identifies potential TB cases during fieldwork, educates community members about the importance of testing, and successfully refers them for diagnosis and treatment. This demonstrates clear CHW involvement in TB management through symptom recognition, health education, and facilitating access to care. The testimonial shows the CHW addressing the community's tendency to dismiss symptoms and helping them understand the importance of TB testing. | Water Quality, Sanitation, and Hygiene: The testimonial focuses entirely on tuberculosis detection, testing, and treatment. There is no mention of water quality, sanitation practices, handwashing, or hygiene education. The CHW discusses coughing, TB testing, and referrals, which are health concerns but not related to water, sanitation, or hygiene interventions. | Personal Disease Management and Adherence: Strong alignment with the concept. The testimonial describes a CHW identifying potential TB cases through symptoms (coughing), advising individuals to get tested, and one person testing positive and beginning treatment. This directly relates to disease diagnosis and treatment initiation, which are key components of disease management. The score is not higher because the focus is more on diagnosis and referral rather than ongoing adherence support or lifestyle adjustments. | Nutrition Education and Food Access: The testimonial mentions that people prioritize 'daily labor to make some money which can help them put some food on the table,' indicating food insecurity concerns. However, this is a passing reference within a testimonial focused on tuberculosis detection and treatment. There is no discussion of nutrition education, healthy eating promotion, or direct food access interventions, which are core to the concept definition. | Sexual and Reproductive Health Education: The testimonial focuses entirely on tuberculosis awareness, testing, and treatment. There is no mention of family planning, STI prevention, HIV awareness, reproductive rights, or any sexual health topics. The content explicitly deals with respiratory health issues and does not align with the concept definition. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses entirely on tuberculosis detection and treatment, with no mention of abuse, violence, exploitation, or any form of GBV or child protection issues. The CHW describes health screening and referral services for TB, which falls completely outside the scope of this concept. | Health Literacy and Misconceptions: The testimonial shows moderate alignment with health literacy issues. People dismissing persistent coughing as 'normal' and prioritizing work over health concerns indicates a lack of understanding about tuberculosis symptoms and the importance of early detection. However, there's no explicit mention of false beliefs about disease origins or active mistrust in medicine, which would warrant a higher score. | Mental Health Awareness and Support: The testimonial focuses entirely on physical health (tuberculosis) and economic concerns about daily labor. While it mentions people's priorities and health-seeking behavior, there is no reference to psychological well-being, emotional states, or mental health support. The concept explicitly excludes medical diagnoses without a mental/emotional context, which applies here. | Referrals and Advocacy: Strong direct alignment with the concept. The CHW explicitly states 'I asked them when they started coughing and advised them to see the doctor for a tuberculosis test' and 'I am now talking to many and also refer them for tuberculosis test.' This demonstrates clear referral activities and advocacy for healthcare access, matching the first example of identifying symptoms and referring for testing. | Community Empowerment Through Education: This testimonial shows weak alignment with community empowerment through education. While the CHW is conducting training and health education about tuberculosis, there's no evidence of lasting behavior change or community self-reliance. The focus is on individual referrals and one-time interventions rather than sustained community transformation. The CHW notes that people 'tend to not be concerned about their health' without indicating this attitude has changed through education. This aligns with the example 'I gave a talk once about health' (0.2) but shows slightly more engagement through active referrals. | Parsing failed for concept 'Community Empowerment Through Education' | Resource and Material Distribution: The testimonial focuses entirely on health education, advice, and referrals for tuberculosis testing. The CHW mentions 'training' people and 'talking to many,' but there is no mention of distributing any physical resources, materials, medication, or supplies. This aligns with the exclusion criteria of 'discussions of education or advice without material support.' | Monitoring and Follow-Up: The testimonial primarily describes initial identification and referral of potential TB cases, with minimal evidence of ongoing monitoring. While the CHW mentions 'I am now talking to many,' this appears to be continued outreach rather than follow-up with specific individuals. The one patient who tested positive 'has begun treatment,' but there's no mention of the CHW checking on their progress or providing ongoing support, which would be key indicators of monitoring and follow-up activities. | Trust and Cultural Mediation: The testimonial shows moderate alignment with cultural mediation. The CHW demonstrates understanding of cultural/social barriers (people prioritizing daily labor over health concerns) and works to bridge the gap between community health behaviors and medical care. They successfully convinced community members to seek testing despite initial reluctance. However, there's no explicit mention of trust-building or linguistic translation, making this a partial rather than strong match. | Clinical Interventions by CHWs: The testimonial describes health education and referral activities, not direct clinical interventions. The CHW advised people to see a doctor and get tested for tuberculosis, which aligns with the exclusion criteria of 'referrals without direct clinical interaction.' There is no mention of the CHW administering medication, treating wounds, or performing any hands-on medical tasks. | Mother and Infant Care: The testimonial focuses entirely on tuberculosis screening and treatment in a community setting. There is no mention of pregnancy, childbirth, postpartum care, infant health, or any mother/infant-specific support. The CHW discusses general community health concerns and tuberculosis case finding, which falls outside the scope of Mother and Infant Care. | Successful Outcomes: Strong alignment with successful outcomes. The CHW identified symptomatic individuals, provided referrals for TB testing, and one person tested positive and began treatment. While the outcome is not fully resolved (patient is still in treatment), there is clear positive progress from identification to treatment initiation, which represents a significant health intervention success. | Material or Training Requests: The testimonial describes the CHW's field work and successful identification of a tuberculosis case, but contains no requests for materials, supplies, or training. The CHW describes their current activities without expressing any needs or asking for additional resources to better serve their community. | Children Served: The testimonial focuses on adults with tuberculosis concerns and makes no mention of children, adolescents, or minors. The CHW describes working with 'people' who are concerned about 'daily labor to make money,' which suggests adult clients rather than children. | Elderly Served: The testimonial focuses on tuberculosis screening and referral in a settlement community. While it mentions helping people who were coughing and referring them for TB testing, there is no mention of elderly individuals, seniors, or grandparents. The CHW's work appears to be with the general population concerned about daily labor and income, without any age-specific references that would indicate service to elderly populations. | Women Served: Strong direct alignment. The testimonial describes a specific woman who was coughing, was advised by the CHW to get tested for tuberculosis, tested positive, and began treatment. This shows direct CHW assistance to a woman with a specific health need, though the focus is on tuberculosis care rather than gendered health issues. | Men Served: The testimonial describes two people who were coughing and referred for TB testing, with one (identified as 'she') testing positive. While the testimonial mentions 'people' and 'many,' there is no specific reference to men or boys, nor any discussion of gendered roles or challenges. The one person whose gender is identified is female ('she'). Therefore, the concept of serving men is not present in this testimonial. | Families Served: The testimonial describes interactions with individuals (two people who were coughing) but makes no mention of households, parents with children, or extended family units. The CHW's support appears focused on individual health interventions rather than family-focused care, which aligns with the exclusion criteria. | Marginalized Groups Served: Strong alignment with the concept. The testimonial describes serving people in settlements who prioritize daily labor/survival over health, indicating economic marginalization. The CHW provides education and referrals to this underserved population who may not otherwise seek care. While not explicitly naming the group as 'marginalized,' the context clearly indicates structural barriers to healthcare access. | Financial Hardship: Strong direct alignment with the concept. The testimonial explicitly states that people prioritize 'daily labor to make some money which can help them put some food on the table' over health concerns, indicating financial hardship drives their behavior. This matches the inclusion criteria of 'statements of poverty, lack of income' and shows inability to prioritize basic medical needs due to financial constraints. | Social Isolation: The testimonial focuses on health awareness and tuberculosis screening in a settlement community. While it mentions economic hardship and people prioritizing work over health, there is no evidence of social isolation, loneliness, lack of support systems, or abandonment. The CHW describes interacting with multiple people during training sessions, indicating social connections exist within the community. | Disease Burden: Strong alignment with Disease Burden concept. The testimonial directly references tuberculosis, a chronic infectious disease requiring long-term treatment. The CHW identified someone who tested positive for TB and began treatment, which aligns with the inclusion criteria of 'long-term or recurrent illness.' The score is 0.8 rather than higher because the focus is on detection and referral rather than ongoing management of chronic illness. | Stigma or Discrimination: The testimonial focuses on health-seeking behavior barriers related to economic priorities and lack of health awareness, not social rejection or judgment. While people are not seeking care for their coughs, there's no mention of shame, exclusion, or discrimination. The CHW successfully refers people for testing without encountering stigma-related resistance. | Mental or Emotional Distress: The testimonial focuses entirely on physical health concerns (tuberculosis, coughing) and economic priorities. There is no mention of depression, hopelessness, trauma, stress, or any emotional distress. The exclusion criteria specifically states 'physical complaints or stress unrelated to emotional wellbeing,' which directly applies here. | Lack of Resources: The testimonial does not mention any lack of resources. The CHW successfully identifies potential TB cases, provides advice, makes referrals, and the patients are able to get tested and receive treatment. There is no indication of insufficient supplies, tools, or capacity limitations preventing the CHW from doing their work. | Systemic Barriers: The testimonial describes people prioritizing daily labor and income over health concerns, which represents a moderate systemic barrier. The economic conditions that force people to choose between earning money for food and seeking healthcare are structural issues outside the CHW's control. However, the CHW was still able to refer patients and one received treatment, suggesting the barriers are not completely preventing access to care. | Overburdened CHWs: The testimonial describes a CHW actively conducting field work, training people, and making referrals, but contains no evidence of being overwhelmed or exhausted. The CHW appears to be managing their workload effectively and successfully delivering care, similar to the 0.1 example where the CHW has 'seen multiple people... without difficulties.' | Lack of Follow-Through: The testimonial shows complete follow-through by the CHW. They identified people with symptoms, advised them to get tested, confirmed one positive case started treatment, and continue to educate and refer others. There is no evidence of abandonment, interrupted care, or unresolved issues - rather the opposite, showing successful completion of care. | Lack of Knowledge: The CHW demonstrates competent knowledge throughout the testimonial - they recognized TB symptoms, knew to advise testing, successfully referred patients, and one received treatment. There is no mention of uncertainty, need for training, or inability to address the issue due to knowledge gaps. The CHW appears confident and knowledgeable in their approach to TB screening and referral.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I had no previous experience, but after training I felt confident talking to people about disease prevention.</t>
+          <t>Tuberculosis During my fieldwork engagement with my participants in a training, one of my participants approached me after I had completed my training—and asked me if I could be able to allow him share with me something. I first thought what could he wanted to tell me, yet I gave time for questions during the sessions. And he could not ask anything. Bravely enough, I heeded to his request and he shared with me that he was diagnosed with tuberculosis and he was put into medication but unfortunately, he defaulted. He wanted to know if I could help him get back to medication but was not happy to go back to Thramogi Agmga Teaching and Referral Hospital since they could not help him. I managed to refer him to KNAP and he got helped and now his life is improving day by day. I am doing close follow-up on him to make sure he has taken his drugs. ---</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>gpt</t>
+          <t>o3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>{
-  "training": 1.0,
-  "trust": 0.0,
-  "community impact": 0.0,
-  "confidence": 1.0,
-  "knowledge sharing": 1.0
+  "CHW Empowerment Through Training": 0.15,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.9,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 1.0,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.2,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 1.0,
+  "Community Empowerment Through Education": 0.3,
+  "Resource and Material Distribution": 0.1,
+  "Monitoring and Follow-Up": 1.0,
+  "Trust and Cultural Mediation": 0.4,
+  "Clinical Interventions by CHWs": 0.3,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 1.0,
+  "Material or Training Requests": 0.05,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.0,
+  "Men Served": 0.9,
+  "Families Served": 0.0,
+  "Marginalized Groups Served": 0.55,
+  "Financial Hardship": 0.1,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.9,
+  "Stigma or Discrimination": 0.1,
+  "Mental or Emotional Distress": 0.1,
+  "Lack of Resources": 0.05,
+  "Systemic Barriers": 0.6,
+  "Overburdened CHWs": 0.1,
+  "Lack of Follow-Through": 0.05,
+  "Lack of Knowledge": 0.05
 }</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>The testimonial talks about the person's training experience, which led to increased confidence and ability to share knowledge about disease prevention. There is no mention of trust or community impact.</t>
+          <t>CHW Empowerment Through Training: The testimonial describes the speaker conducting a training session and then helping a participant with tuberculosis. It does not explicitly state that the CHW themselves received training that empowered them; rather, they were providing the training. Any implication that they once received such training is indirect and weak, so alignment with the concept is minimal. | Menstrual Hygiene Education and Challenges: The testimonial focuses on tuberculosis treatment adherence and referral, with no mention of menstruation, menstrual products, or related education or stigma. | Drug Abuse: Environment and Awareness: The testimonial discusses a patient's adherence to tuberculosis medication, not substance abuse or environmental/social factors related to drug or alcohol misuse. This falls outside the concept’s scope. | CHW-Led Infectious Disease Management: The CHW identifies and assists a participant with tuberculosis, arranging referral for treatment and conducting close follow-up to ensure medication adherence. This is a clear example of CHW involvement in managing an infectious disease (TB) through outreach and follow-up, fitting the concept’s definition and inclusion criteria. | Water Quality, Sanitation, and Hygiene: The testimonial focuses on helping a tuberculosis patient resume medication and includes no discussion of clean water, sanitation, or hygiene practices. Therefore, the concept is not present. | Personal Disease Management and Adherence: The testimonial explicitly describes helping a person diagnosed with tuberculosis resume medication and conducting close follow-up to ensure drug adherence—an unambiguous example of disease management and adherence facilitated by the CHW. | Nutrition Education and Food Access: The testimonial focuses on helping a participant resume tuberculosis medication and follow-up care; it contains no mention of healthy eating, food insecurity, or nutrition-related education or access. | Sexual and Reproductive Health Education: The testimonial focuses on tuberculosis treatment adherence and contains no mention of family planning, STIs, HIV, condoms, or any other sexual or reproductive health education topics. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses on helping a tuberculosis patient resume treatment; there is no mention of abuse, violence, child protection, or related CHW interventions, so the concept does not apply. | Health Literacy and Misconceptions: The story notes that the participant stopped (defaulted) tuberculosis medication and sought guidance on restarting treatment, hinting at possible gaps in understanding or adherence. However, no explicit misinformation or false beliefs about TB are described; the issue seems more related to dissatisfaction with a specific facility. Therefore, only minimal evidence of limited health literacy is present. | Mental Health Awareness and Support: The testimonial focuses solely on physical illness (tuberculosis) and medication adherence. It does not mention depression, anxiety, emotional distress, or any form of psychological support, so the concept is not present. | Referrals and Advocacy: The CHW explicitly states, “I managed to refer him to KNAP and he got helped,” which is a clear instance of arranging a referral and navigating the health system for the participant—exactly matching the definition and inclusion criteria for Referrals and Advocacy. | Community Empowerment Through Education: The testimonial mentions that the CHW conducted a training, but the only documented outcome is a single participant privately seeking individual help for TB treatment. There is no evidence of broader community behavior change, peer education, or collective action. This reflects isolated education with limited demonstrated impact, aligning weakly with the concept. | Resource and Material Distribution: The CHW referred the participant to a facility and followed up on medication adherence but did not personally hand out medication or other supplies. Since no direct distribution of material resources occurred, alignment with the concept is minimal. | Monitoring and Follow-Up: The testimonial explicitly states the CHW is \ | Trust and Cultural Mediation: The participant privately disclosed his TB status and requested help, implying a level of trust in the CHW. However, the testimonial does not explicitly describe translation, cultural mediation, or deliberate trust-building activities; it mainly recounts referral and follow-up. Thus, evidence of trust is present but limited, meriting a weak-to-moderate score. | Clinical Interventions by CHWs: The CHW did not administer medication or perform hands-on clinical care; she primarily referred the client to another facility and is following up on medication adherence. This is indirect clinical support rather than the direct provision of treatment described in the concept, so alignment is weak (exclusion notes referrals without direct clinical interaction). | Mother and Infant Care: The testimonial focuses solely on supporting an adult client with tuberculosis treatment adherence and contains no mention of pregnancy, childbirth, postpartum issues, or infant health. Therefore, it does not meet the inclusion criteria for Mother and Infant Care. | Successful Outcomes: The CHW referred a TB patient to a different facility, the patient received help, and his condition is 'improving day by day' with ongoing follow-up. This clearly demonstrates a CHW-driven resolution and health improvement, fitting the definition and inclusion criteria for Successful Outcomes. | Material or Training Requests: The testimonial recounts a patient seeking help to resume TB medication; there is no instance of the community health worker requesting materials, supplies, or training. Hence only negligible alignment with the concept. | Children Served: The testimonial discusses assisting an individual with tuberculosis treatment, with no mention of children or adolescents. Therefore the concept 'Children Served' is not present. | Elderly Served: The testimonial discusses assisting a tuberculosis patient with medication adherence, but there is no mention or implication that the individual is an older adult. Therefore, the concept of serving the elderly does not apply. | Women Served: The testimonial only discusses a male participant with tuberculosis and provides no mention of women or gender-specific issues. Therefore the concept “Women Served” is not applicable. | Men Served: The testimonial centers on providing direct support to an adult male participant who defaulted on tuberculosis treatment. This fits the inclusion criterion of offering health assistance specifically for a man, showing strong, unambiguous alignment with the concept. | Families Served: The testimonial describes assistance provided to a single individual with tuberculosis and does not reference any household, parents with children, or broader family unit. According to the exclusion criteria, individual help unconnected to a family structure means the concept is not present. | Marginalized Groups Served: The CHW helps a person with tuberculosis who had defaulted on treatment. While TB patients often experience stigma and can be considered underserved, the testimonial does not explicitly mention discrimination or social exclusion—only that the client was dissatisfied with a particular hospital. This provides some, but not strong, evidence of serving a marginalized or stigmatized group, warranting a moderate score. | Parsing failed for concept 'Marginalized Groups Served' | Financial Hardship: The testimonial mentions a participant who defaulted on TB medication and sought assistance to resume treatment, but no explicit reason of cost, poverty, or inability to pay is given. There is only minimal, indirect suggestion that resources or access might be an issue, so alignment with the Financial Hardship concept is weak. | Social Isolation: The testimonial focuses on a participant seeking assistance to restart tuberculosis treatment. There is no mention of living alone, lack of social support, loneliness, or abandonment, so the concept of Social Isolation does not apply. | Disease Burden: The testimonial centers on a participant diagnosed with tuberculosis who defaulted on treatment and required re-engagement and ongoing follow-up—clearly describing a long-term, serious illness. This matches the definition and inclusion criteria for Disease Burden (chronic or recurrent illness). The alignment is direct and unambiguous, warranting a high score (0.9). | Stigma or Discrimination: The testimonial describes a client seeking help to restart tuberculosis medication and being dissatisfied with a particular hospital, but there is no explicit mention of shame, social rejection, judgment, or discrimination. Any sense of reluctance is not clearly tied to stigma, so alignment with the concept is minimal. | Mental or Emotional Distress: The testimonial focuses on getting medical help for tuberculosis and mentions the participant was 'not happy' with a specific hospital. There is no explicit description of depression, hopelessness, or significant emotional overwhelm, so only minimal indirect evidence of distress is present. | Lack of Resources: The testimonial focuses on referring a TB patient to another facility and following up on treatment. It does not describe the CHW lacking medicines, tools, or support; the hospital’s inability to help the patient is mentioned, but this is not framed as the CHW’s resource shortage. Therefore, alignment with the 'Lack of Resources' concept is negligible. | Systemic Barriers: The client avoided returning to a specific hospital because \ | Overburdened CHWs: The testimonial describes the CHW conducting training and helping an individual patient, but there is no mention of feeling exhausted, overwhelmed, or having too many clients. Thus, only minimal implicit evidence of workload is present, aligning weakly with the concept. | Lack of Follow-Through: The CHW not only referred the participant for appropriate care but also continues close follow-up. The issue was addressed and is improving, so there is no indication of abandonment or unresolved assistance. Minimal to no evidence of lack of follow-through. | Lack of Knowledge: The CHW describes confidently referring the participant to an appropriate service and following up on treatment. There is no statement of uncertainty, lack of know-how, or request for additional training. Thus evidence for the 'Lack of Knowledge' concept is essentially absent.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I had no previous experience, but after training I felt confident talking to people about disease prevention.</t>
+          <t>Tuberculosis During my fieldwork engagement with my participants in a training, one of my participants approached me after I had completed my training—and asked me if I could be able to allow him share with me something. I first thought what could he wanted to tell me, yet I gave time for questions during the sessions. And he could not ask anything. Bravely enough, I heeded to his request and he shared with me that he was diagnosed with tuberculosis and he was put into medication but unfortunately, he defaulted. He wanted to know if I could help him get back to medication but was not happy to go back to Thramogi Agmga Teaching and Referral Hospital since they could not help him. I managed to refer him to KNAP and he got helped and now his life is improving day by day. I am doing close follow-up on him to make sure he has taken his drugs. ---</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1080,45 +3842,2526 @@
       <c r="C9" t="inlineStr">
         <is>
           <t>{
-  "training": 0.9,
-  "trust": 0.1,
-  "community impact": 0.3,
-  "confidence": 0.95,
-  "knowledge sharing": 0.7
+  "CHW Empowerment Through Training": 0.8,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.8,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.9,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.2,
+  "Mental Health Awareness and Support": 0.2,
+  "Referrals and Advocacy": 0.9,
+  "Community Empowerment Through Education": 0.2,
+  "Resource and Material Distribution": 0.1,
+  "Monitoring and Follow-Up": 0.9,
+  "Trust and Cultural Mediation": 0.8,
+  "Clinical Interventions by CHWs": 0.2,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.9,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.0,
+  "Men Served": 0.8,
+  "Families Served": 0.0,
+  "Marginalized Groups Served": 0.8,
+  "Financial Hardship": 0.1,
+  "Social Isolation": 0.1,
+  "Disease Burden": 0.9,
+  "Stigma or Discrimination": 0.3,
+  "Mental or Emotional Distress": 0.2,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.7,
+  "Overburdened CHWs": 0.1,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.0
 }</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The testimonial strongly emphasizes confidence (0.95) gained through training (0.9). Knowledge sharing (0.7) is evident as they now talk to people about disease prevention. Community impact (0.3) is implied through their disease prevention work. Trust (0.1) is minimally present as confidence in communication suggests some level of trust-building.</t>
+          <t>CHW Empowerment Through Training: The testimonial shows strong evidence of CHW empowerment through training. The CHW explicitly mentions conducting 'training' with participants and completing 'my training,' indicating they received preparation that enabled them to educate others. The CHW demonstrates increased capacity to serve by successfully identifying a TB case, providing referral services, and conducting follow-up care. While the specific content or type of training isn't detailed, the outcome clearly shows the CHW gained knowledge and skills that empowered them to effectively help a community member with a serious health issue. | Parsing failed for concept 'CHW Empowerment Through Training' | Menstrual Hygiene Education and Challenges: This testimonial is entirely focused on tuberculosis treatment and medication adherence. There is no mention of menstruation, menstrual hygiene, sanitary products, or any related education. The content explicitly deals with a different health issue (TB), making it a clear non-match for the menstrual hygiene concept. | Drug Abuse: Environment and Awareness: This testimonial focuses entirely on tuberculosis treatment adherence and healthcare access. While it mentions 'drugs' in the context of TB medication compliance, there is no reference to substance abuse, addiction, alcohol, peer influence, or drug education. The concept explicitly excludes clinical descriptions without social/environmental context related to substance abuse, which this testimonial exemplifies. | CHW-Led Infectious Disease Management: Strong alignment with the concept. The CHW directly manages a tuberculosis case by: 1) receiving disclosure from a community member about TB diagnosis and treatment default, 2) providing referral services to get the patient back on medication, and 3) conducting ongoing follow-up to ensure medication adherence. While the testimonial doesn't explicitly mention education about TB symptoms or prevention, it demonstrates active CHW involvement in infectious disease management through case finding, referral, and treatment support. | Water Quality, Sanitation, and Hygiene: The testimonial focuses entirely on tuberculosis case management, medication adherence, and referral services. There is no mention of water quality, sanitation practices, hygiene education, handwashing, or any water-related disease prevention activities. The content explicitly deals with TB treatment support, which falls outside the scope of this concept. | Personal Disease Management and Adherence: This testimonial is a strong match for Personal Disease Management and Adherence. It explicitly describes a TB patient who defaulted on medication, sought help to resume treatment, and is now being monitored for adherence. The CHW facilitated re-engagement with treatment and provides ongoing follow-up to ensure medication compliance, which directly aligns with the concept's focus on disease management through treatment adherence and CHW guidance. | Nutrition Education and Food Access: The testimonial focuses entirely on tuberculosis diagnosis, medication adherence, and healthcare referral. There is no mention of nutrition education, food security, healthy eating, or food access issues. The content is exclusively about medical treatment and follow-up care, which falls outside the scope of this concept. | Sexual and Reproductive Health Education: The testimonial focuses entirely on tuberculosis diagnosis, treatment defaulting, and medication adherence. There is no mention of family planning, STI prevention, HIV awareness, reproductive rights, or any sexual health education topics. This clearly falls outside the concept's scope. | Gender-Based Violence (GBV) and Child Protection: This testimonial describes a CHW helping someone with tuberculosis medication adherence and referral services. There is no mention of abuse, violence, exploitation, or any form of GBV or child protection issues. The case involves a health condition (TB) and medication compliance, which clearly falls outside the concept's inclusion criteria. | Health Literacy and Misconceptions: The testimonial shows minimal evidence of health literacy issues. While the participant defaulted on TB medication and was reluctant to return to the hospital, there's no clear indication of misinformation or misconceptions about the disease itself. The defaulting could be due to various factors unrelated to health literacy, and the testimonial doesn't mention any misbeliefs about TB origins or treatment. | Mental Health Awareness and Support: The testimonial primarily focuses on tuberculosis treatment and medication adherence. While the participant's reluctance to return to the hospital and need for support could suggest some emotional distress, there is no explicit mention of mental health issues like depression, anxiety, or emotional trauma. The CHW's support is mainly medical rather than psychological. | Parsing failed for concept 'Mental Health Awareness and Support' | Referrals and Advocacy: Strong direct alignment with the concept. The CHW explicitly states 'I managed to refer him to KNAP' after a participant approached them about defaulting on TB medication. The CHW acted as an intermediary by connecting the patient to a different healthcare facility when the original hospital wasn't helping, and continues advocacy through 'close follow-up on him to make sure he has taken his drugs.' This matches the first example of identifying symptoms and referring for care. | Community Empowerment Through Education: This testimonial describes a one-time intervention where the CHW helped an individual TB patient get back on medication through referral. While education/training was mentioned as the context where they met, there's no evidence of community-wide change, peer education, group action, or lasting behavior change beyond this single patient. The focus is on individual case management rather than community empowerment through education, aligning with the exclusion criteria of 'one-time events or isolated education without lasting behavior change.' | Resource and Material Distribution: The testimonial describes a CHW providing referral services and follow-up support for a tuberculosis patient, but does not mention distributing any physical resources or materials. While the CHW helped the patient access medication through a referral to KNAP, they did not directly provide or distribute the medication themselves. The focus is on counseling, referral, and monitoring adherence rather than material distribution, which aligns with the exclusion criteria. | Monitoring and Follow-Up: Strong direct alignment with the concept. The CHW explicitly states 'I am doing close follow-up on him to make sure he has taken his drugs,' which perfectly matches the definition of ongoing interactions to check progress and reinforce guidance. This represents continuous monitoring after the initial referral, specifically focused on medication adherence for a tuberculosis patient who had previously defaulted on treatment. | Trust and Cultural Mediation: Strong alignment with trust-building. The participant specifically approached the CHW privately after training, indicating trust in the CHW over the formal healthcare system. The CHW successfully mediated between the participant who 'was not happy to go back' to the hospital and alternative care at KNAP, demonstrating navigation of barriers between the community member and health systems. The ongoing follow-up shows continued trust-based relationship. | Parsing failed for concept 'Trust and Cultural Mediation' | Clinical Interventions by CHWs: The CHW primarily provided referral services and follow-up support rather than direct clinical interventions. While they mention doing 'close follow-up on him to make sure he has taken his drugs,' this is medication adherence monitoring rather than administering medication or performing clinical tasks like wound care. The main action was referring the patient to KNAP for treatment, which aligns with the exclusion criteria of 'referrals without direct clinical interaction.' | Mother and Infant Care: This testimonial is entirely focused on tuberculosis treatment and medication adherence support. There is no mention of pregnancy, childbirth, postpartum care, infant health, or any mother/infant-related topics. The CHW is helping an adult patient with TB treatment, which falls outside the scope of mother and infant care. | Successful Outcomes: Strong direct alignment with successful outcomes. The testimonial clearly describes a CHW helping a tuberculosis patient who had defaulted on treatment get back on medication through a referral to KNAP. The outcome is explicitly positive: 'he got helped and now his life is improving day by day.' The CHW also mentions ongoing follow-up to ensure medication adherence. This matches the example of escorting someone to the hospital who recovered (0.9 score). | Material or Training Requests: This testimonial describes a CHW helping a participant with tuberculosis get back on medication through a referral. There is no mention of the CHW requesting any materials, supplies, or training. The CHW successfully handled the situation using existing resources and referral networks, without expressing any need for additional support or education. | Children Served: The testimonial describes helping an adult participant with tuberculosis treatment. There is no mention of children, minors, or anyone under 18 years old. The participant is clearly an adult who approached the CHW after training and discussed their medical condition independently. | Elderly Served: The testimonial describes helping a participant with tuberculosis medication adherence and referral services, but contains no indication that this person was elderly, a senior, or a grandparent. The concept requires specific reference to older adults receiving assistance, which is absent from this testimonial. | Women Served: The testimonial describes a male participant ('him', 'he') who was helped with tuberculosis treatment. There is no mention of women, girls, or any gendered roles or challenges related to females. The CHW interaction was exclusively with a male participant. | Men Served: Strong alignment with the concept. The testimonial describes direct support provided to a male participant who had tuberculosis and defaulted on treatment. The CHW provided counseling, referral services, and ongoing follow-up care to help him resume medication. While the gender isn't explicitly emphasized as a factor, this clearly shows individualized health support for a man facing a serious health challenge, which aligns with the inclusion criteria of 'support for men regarding health.' | Families Served: The testimonial describes a CHW helping an individual participant with tuberculosis treatment. There is no mention of family members, household context, or family-focused interventions. The support provided is entirely focused on one person's individual health needs, which falls under the exclusion criteria of 'individual help not connected to a family unit or structure.' | Marginalized Groups Served: Strong alignment with the concept. The testimonial describes supporting someone with tuberculosis who had defaulted on treatment and was reluctant to return to the hospital system. TB patients often face stigma and marginalization, and the person's fear of returning to the hospital and need for confidential support through alternative channels (KNAP referral) suggests they were experiencing barriers typical of marginalized individuals. The CHW provided direct support through referral and ongoing follow-up care. | Parsing failed for concept 'Marginalized Groups Served' | Financial Hardship: The testimonial describes a tuberculosis patient who defaulted on medication and needed help getting back to treatment. While there's no explicit mention of financial constraints, poverty, or inability to afford care, the fact that the patient defaulted on medication and was reluctant to return to the hospital could potentially suggest underlying financial barriers, though this is speculative. The score remains very low because financial hardship is not directly stated or clearly implied. | Social Isolation: The testimonial focuses on a tuberculosis patient who defaulted on medication and needed help getting back into treatment. While the person approached the CHW privately and seemed reluctant to return to the hospital, there is no explicit mention of living alone, loneliness, lack of support systems, or abandonment. The CHW's follow-up care suggests some level of support need, but this appears to be medical adherence support rather than addressing social isolation. | Disease Burden: Strong direct alignment with the concept. The testimonial describes a participant with tuberculosis who defaulted on medication - a chronic infectious disease requiring long-term treatment. The CHW is providing ongoing follow-up to ensure medication adherence, which aligns with the example of monitoring a person with diabetes (0.9). Tuberculosis clearly represents a chronic illness with significant life impact requiring sustained medical intervention. | Stigma or Discrimination: The testimonial shows weak alignment with stigma or discrimination. While the participant's reluctance to return to the hospital and private approach after training suggests possible shame or fear of judgment related to TB, there is no explicit mention of social rejection, exclusion, or discrimination from others. The secretive behavior could indicate internalized stigma, but the text lacks clear evidence of external social judgment or rejection that would warrant a higher score. | Mental or Emotional Distress: The testimonial primarily focuses on a physical health condition (tuberculosis) and medication adherence. While there are subtle hints of emotional distress (the participant's hesitation to share, unhappiness about returning to the hospital), these are secondary to the medical issue and not explicitly described as mental or emotional overwhelm, depression, or hopelessness. | Lack of Resources: The testimonial does not indicate any lack of resources. The CHW successfully referred the patient to KNAP where he received help and medication. There is no mention of the CHW lacking medicine, tools, or support to address the tuberculosis case. The issue was the patient's dissatisfaction with the previous hospital, not a resource limitation on the CHW's part. | Systemic Barriers: The testimonial shows moderate alignment with systemic barriers. The participant explicitly states that Thramogi Agmga Teaching and Referral Hospital 'could not help him,' suggesting institutional failure that led to treatment default. This aligns with the concept's focus on health facility issues preventing CHWs from helping. However, the score is not higher because the specific nature of the hospital's failure is not detailed, and the CHW was ultimately able to find an alternative solution through KNAP. | Overburdened CHWs: The testimonial describes a CHW successfully managing a single TB case with appropriate referral and follow-up. There is no evidence of being overwhelmed, exhausted, or having excessive workload. The CHW appears to have adequate time for training, individual consultations, and ongoing follow-up care, similar to the example 'I've seen multiple people in my community, and I haven't run into any difficulties.' which scores 0.1. | Lack of Follow-Through: This testimonial demonstrates the opposite of lack of follow-through. The CHW successfully referred the patient to KNAP, the patient received help, and the CHW continues to do 'close follow-up' to ensure medication adherence. The issue was resolved with ongoing support, which directly contradicts the concept of abandonment or unresolved care. | Lack of Knowledge: The CHW demonstrates competent handling of the tuberculosis case. They successfully referred the patient to KNAP and provided ongoing follow-up care. There is no mention of uncertainty, need for training, or inability to address the issue due to knowledge gaps. The CHW knew exactly how to proceed with the referral and follow-up process.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I had no previous experience, but after training I felt confident talking to people about disease prevention.</t>
+          <t>COVID-19 Coronavirus continues to be a menace not only to the country but also to our work, as it restricts large gatherings and restricts people to minimal contact with each other to avoid the spread of the virus. The country is currently battling the third Indian wave which has shown more devastating effects of the new strain of the virus. This has led to more restrictions and also has led to the imposed curfews within Kisumu County and the environs. There is a possibility of even more stringent measures to curb the third wave. Having trained as a Community Health Worker, I have been actively sensitizing and creating awareness to my community members on the preventive measures against the COVID-19 pandemic. I have been emphasizing a lot on the benefits of putting on masks, washing hands with clean running water and soap, sanitizing and also keeping social distance. Through this, the members of the community have embraced and also adopted the teachings and are always doing what I have trained them to do. This has made me very happy because there is no single case that has been reported from this community I live and work in. Were it by any chance that the people were not sensitized, then this community could be a COVID-19 hotspot and many people could have died. There’s a big change on how people wash their hands and also put on masks compared to other previous years where people did not take washing hands with soap and running water very important. Initially, many people could even take or rather eat fruits or any other food stuffs without washing their hands but since COVID-19 hit us, many people have adopted the trend of washing hands regularly. This is a great change that has manifested in my community. ---</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>o3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>{
-  "training": 0.9,
-  "trust": 0.1,
-  "community impact": 0.2,
-  "confidence": 0.8,
-  "knowledge sharing": 0.5
+  "CHW Empowerment Through Training": 0.9,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 1.0,
+  "Water Quality, Sanitation, and Hygiene": 0.85,
+  "Personal Disease Management and Adherence": 0.6,
+  "Nutrition Education and Food Access": 0.1,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.3,
+  "Mental Health Awareness and Support": 0.05,
+  "Referrals and Advocacy": 0.2,
+  "Community Empowerment Through Education": 0.9,
+  "Resource and Material Distribution": 0.0,
+  "Monitoring and Follow-Up": 0.25,
+  "Trust and Cultural Mediation": 0.3,
+  "Clinical Interventions by CHWs": 0.05,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.9,
+  "Material or Training Requests": 0.05,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.0,
+  "Men Served": 0.0,
+  "Families Served": 0.1,
+  "Marginalized Groups Served": 0.1,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.2,
+  "Disease Burden": 0.3,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.1,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.7,
+  "Overburdened CHWs": 0.1,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.0
 }</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>The testimonial directly mentions "training" and the resulting "confidence". The gained confidence relates to discussing disease prevention, which can be interpreted as a form of "knowledge sharing", although not explicitly stated.  "Trust" and "community impact" are less relevant as the testimonial focuses on personal growth from the training.</t>
+          <t>CHW Empowerment Through Training: The testimonial explicitly states, “Having trained as a Community Health Worker, I have been actively sensitizing …,” which directly mentions CHW training and how it enables the speaker to educate the community. This fits the definition and inclusion criteria for CHW Empowerment Through Training, yielding a strong, unambiguous match. | Parsing failed for concept 'CHW Empowerment Through Training' | Menstrual Hygiene Education and Challenges: The testimonial solely discusses COVID-19 prevention (mask-wearing, handwashing, social distancing). It contains no reference to menstruation, menstrual products, or related stigma, so the concept is not applicable. | Drug Abuse: Environment and Awareness: The testimonial focuses solely on COVID-19 prevention efforts and does not mention substance use, addiction, peer influence, or any environmental factors related to drug abuse. Therefore, the concept is not applicable. | CHW-Led Infectious Disease Management: The testimonial explicitly states that, as a trained Community Health Worker, the speaker has been 'sensitizing and creating awareness' about COVID-19 preventive measures (masking, hand-washing, distancing). This is a textbook example of CHWs educating the community to reduce the spread of an infectious disease, matching the definition and inclusion criteria exactly with no ambiguity. | Water Quality, Sanitation, and Hygiene: The CHW repeatedly describes teaching and promoting handwashing with clean running water and soap as a key COVID-19 preventive measure, and notes community adoption of this practice. This aligns directly with the concept’s inclusion criteria (handwashing education) and mirrors the 0.8–0.9 example provided, so a strong score of 0.85 is warranted. | Personal Disease Management and Adherence: The CHW describes guiding community members to adopt preventive lifestyle behaviors (mask wearing, hand-washing, social distancing) to control an infectious disease (COVID-19). This fits the concept’s mention of lifestyle adjustments for managing disease, but there is no discussion of diagnosis or medication adherence, so alignment is moderate rather than strong. | Nutrition Education and Food Access: The testimonial focuses on COVID-19 prevention (masking, hand-washing, distancing). The only food-related reference is that people now wash hands before eating fruits or other foods, which pertains to hygiene rather than nutrition education or food access. Thus, there is only a minimal, indirect link to the concept. | Sexual and Reproductive Health Education: The testimonial focuses exclusively on COVID-19 prevention measures (mask use, handwashing, social distancing) and contains no mention of family planning, condoms, STIs, HIV, or any other sexual and reproductive health education topics; therefore the concept is not present. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses solely on COVID-19 prevention activities and community sensitization. It contains no reference to abuse, exploitation, violence, or child protection issues, so the GBV/Child Protection concept does not apply. | Health Literacy and Misconceptions: The CHW describes sensitizing the community and creating awareness of COVID-19 preventive measures, implying they addressed a lack of prior knowledge. However, there is no explicit discussion of specific misconceptions or misinformation being corrected, so the alignment with the concept is weak-to-moderate rather than strong. | Parsing failed for concept 'Health Literacy and Misconceptions' | Mental Health Awareness and Support: The testimonial focuses on COVID-19 prevention activities and community behavioral change, with no mention of depression, anxiety, emotional support, or other mental-health related themes. Only a brief personal statement of being 'very happy' appears, which does not constitute mental health support. Therefore alignment with the concept is negligible. | Referrals and Advocacy: The CHW is advocating for preventive behaviors (mask wearing, hand-washing) but the testimonial does not mention making referrals, booking appointments, or helping people navigate the health system. This is weak evidence of the Concept, similar to the 0.2 example “I sometimes tell others to get help.” | Community Empowerment Through Education: The CHW describes sustained community behavior change (regular hand-washing, consistent mask use) that resulted from ongoing education about COVID-19 prevention. This reflects group adoption of healthier habits and self-reliance, matching the definition and inclusion criteria for community empowerment through education. The narrative goes beyond a single event and shows measurable, lasting impact, warranting a strong score. | Resource and Material Distribution: The testimonial describes education and awareness activities (encouraging mask use, handwashing, etc.) but does not mention giving out any physical supplies. Advice without material support is explicitly excluded from this concept. | Monitoring and Follow-Up: The CHW describes repeated sensitization about COVID-19 prevention, but there is no explicit mention of returning to specific households, checking individual health status, or adjusting care. The activity sounds more like ongoing public education than structured follow-up, giving only weak evidence for the Monitoring and Follow-Up concept. | Trust and Cultural Mediation: The CHW describes educating community members about COVID-19 precautions, and notes that people have \ | Clinical Interventions by CHWs: The testimonial describes health education and community sensitization about COVID-19 prevention (mask wearing, handwashing, social distancing). It does not mention the CHW administering medication, bandaging wounds, or performing any direct clinical tasks. Therefore, alignment with the “Clinical Interventions by CHWs” concept is minimal. | Mother and Infant Care: The testimonial focuses exclusively on COVID-19 prevention (mask wearing, handwashing, social distancing) for the general community. There is no mention of pregnancy, childbirth, postpartum issues, or infant health, so the Mother and Infant Care concept is not applicable. | Successful Outcomes: The CHW reports that after her sensitization efforts, community members adopted preventive behaviors (mask wearing, hand-washing) and that no COVID-19 cases have been reported in her area. This directly attributes improved health conditions and behavior change to the CHW’s work, matching the concept’s definition and inclusion criteria. The alignment is strong and unambiguous, warranting a high score (0.9). | Material or Training Requests: The testimonial describes the CHW’s COVID-19 sensitization activities but contains no explicit request for additional supplies, materials, or training. It only recounts what they have done, so alignment with the concept is minimal. | Children Served: The testimonial discusses COVID-19 awareness activities with community members in general but never specifically mentions children or adolescents, so the concept 'Children Served' is not present. | Elderly Served: The testimonial discusses general COVID-19 prevention efforts in the community but does not mention older adults, seniors, or grandparents specifically, nor any assistance directed toward them. | Women Served: The testimonial discusses educating the general community about COVID-19 prevention but does not mention women or girls specifically, nor any gender-specific challenges or assistance. Therefore, the concept “Women Served” is not present. | Men Served: The testimonial discusses general COVID-19 sensitization for the community without mentioning men or boys specifically, nor any gender-specific challenges or support. Therefore, the concept does not apply. | Families Served: The testimonial describes community-wide education on COVID-19 prevention but makes no explicit mention of households, parents with children, or family-focused support. Any link to families is only implicit through the term “community members,” so alignment with the Families Served concept is minimal. | Parsing failed for concept 'Families Served' | Marginalized Groups Served: The testimonial describes general COVID-19 education for the whole community without identifying any structurally excluded or stigmatized subgroup. This aligns with the example of a generic community reference (score 0.1). | Financial Hardship: The testimonial discusses COVID-19 restrictions and community health education but contains no mention of poverty, lack of income, or inability to afford basic needs; therefore, the Financial Hardship concept is not present. | Social Isolation: The testimonial mentions that COVID-19 restrictions limit large gatherings and reduce contact between people, hinting at potential reduced social interaction, but it does not describe anyone living alone, feeling lonely, or lacking support. Therefore evidence for social isolation is minimal and indirect, warranting a low score. | Disease Burden: The testimonial discusses COVID-19 as a serious, ongoing public-health problem, indicating some level of disease burden in the community (recurrent waves, curfews, restrictions). However, it does not describe specific individuals with chronic or long-term illness, disability, or frequent personal illness episodes. Thus the alignment with the concept is weak-to-moderate rather than strong. | Stigma or Discrimination: The testimonial discusses COVID-19 prevention efforts and community behavior change, but it does not mention social rejection, shame, judgment, or any form of discrimination. Therefore, the concept is not present. | Mental or Emotional Distress: The testimonial discusses COVID-19 restrictions and the CHW’s preventive efforts but does not describe feelings of depression, hopelessness, trauma, or emotional overwhelm. The only emotion mentioned is being “very happy,” which is opposite of distress, so evidence for mental or emotional distress is minimal. | Lack of Resources: The testimonial focuses on COVID-19 restrictions and successful community sensitization efforts, with no mention of insufficient medicine, tools, or support. Therefore, the concept 'Lack of Resources' is not present. | Systemic Barriers: The CHW describes external, policy-level factors—COVID-19 curfews and bans on large gatherings—that limit how they can carry out community work. These restrictions are outside the CHW’s control and fit the definition of systemic barriers. However, the testimonial doesn’t show a complete inability to help (the CHW still manages to sensitize the community), so alignment is moderate rather than perfect. | Overburdened CHWs: The CHW describes actively educating the community during COVID-19, but does not mention exhaustion, feeling overwhelmed, or having too many clients. Workload strain is not explicitly stated, so only minimal implicit evidence exists. | Lack of Follow-Through: The testimonial describes successful, ongoing efforts by the CHW (sensitizing the community, observing positive results). There is no indication that the CHW abandoned a task or that any issue remained unresolved, so the concept of Lack of Follow-Through is not present. | Lack of Knowledge: The CHW describes confidently conducting community sensitization on COVID-19 prevention measures and reports success; there is no mention of uncertainty, insufficient knowledge, or requests for further training.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>COVID-19 Coronavirus continues to be a menace not only to the country but also to our work, as it restricts large gatherings and restricts people to minimal contact with each other to avoid the spread of the virus. The country is currently battling the third Indian wave which has shown more devastating effects of the new strain of the virus. This has led to more restrictions and also has led to the imposed curfews within Kisumu County and the environs. There is a possibility of even more stringent measures to curb the third wave. Having trained as a Community Health Worker, I have been actively sensitizing and creating awareness to my community members on the preventive measures against the COVID-19 pandemic. I have been emphasizing a lot on the benefits of putting on masks, washing hands with clean running water and soap, sanitizing and also keeping social distance. Through this, the members of the community have embraced and also adopted the teachings and are always doing what I have trained them to do. This has made me very happy because there is no single case that has been reported from this community I live and work in. Were it by any chance that the people were not sensitized, then this community could be a COVID-19 hotspot and many people could have died. There’s a big change on how people wash their hands and also put on masks compared to other previous years where people did not take washing hands with soap and running water very important. Initially, many people could even take or rather eat fruits or any other food stuffs without washing their hands but since COVID-19 hit us, many people have adopted the trend of washing hands regularly. This is a great change that has manifested in my community. ---</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.85,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.9,
+  "Water Quality, Sanitation, and Hygiene": 0.8,
+  "Personal Disease Management and Adherence": 0.2,
+  "Nutrition Education and Food Access": 0.1,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.0,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.1,
+  "Community Empowerment Through Education": 0.8,
+  "Resource and Material Distribution": 0.1,
+  "Monitoring and Follow-Up": 0.2,
+  "Trust and Cultural Mediation": 0.7,
+  "Clinical Interventions by CHWs": 0.0,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.9,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.0,
+  "Men Served": 0.0,
+  "Families Served": 0.1,
+  "Marginalized Groups Served": 0.1,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.1,
+  "Disease Burden": 0.7,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.0,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.8,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: Strong direct alignment. The testimonial explicitly states 'Having trained as a Community Health Worker' and demonstrates how this training empowered the CHW to actively sensitize and create awareness about COVID-19 prevention. The CHW is teaching community members specific health practices (mask-wearing, handwashing, sanitizing, social distancing) based on their training, showing clear capacity building through CHW-specific training. | Menstrual Hygiene Education and Challenges: The testimonial focuses entirely on COVID-19 prevention measures, including handwashing, mask-wearing, sanitizing, and social distancing. There is no mention of menstruation, menstrual hygiene, sanitary products, or any related education. The hygiene practices discussed are general preventive measures against COVID-19, not menstrual hygiene, which falls under the exclusion criteria. | Drug Abuse: Environment and Awareness: The testimonial focuses entirely on COVID-19 prevention measures and community health education about pandemic safety protocols. There is no mention of substance abuse, addiction, alcohol, drugs, or any related social/environmental factors that contribute to drug abuse. The content is exclusively about COVID-19 awareness and preventive behaviors like handwashing and mask-wearing. | CHW-Led Infectious Disease Management: Strong direct alignment with the concept. The testimonial explicitly describes a CHW actively educating their community about COVID-19 prevention measures (masks, handwashing, sanitizing, social distancing). The CHW reports conducting sensitization and awareness campaigns, and notes positive behavioral changes in the community. The testimonial demonstrates clear CHW involvement in infectious disease management, matching the first example's score of 0.9. | Water Quality, Sanitation, and Hygiene: Strong direct alignment with the concept. The testimonial explicitly discusses 'washing hands with clean running water and soap' as a COVID-19 prevention measure, and notes the community's adoption of regular handwashing practices. The CHW emphasizes how people now wash hands before eating, showing a clear connection between hygiene education and disease prevention. While focused on COVID-19 rather than waterborne diseases, the handwashing education with clean water and soap directly matches the concept's inclusion criteria. | Personal Disease Management and Adherence: The testimonial focuses on COVID-19 prevention through community education about preventive measures (masks, handwashing, social distancing) rather than disease management or treatment adherence. While COVID-19 is mentioned as a disease context, the CHW's work centers on prevention and awareness, not helping individuals manage diagnosed cases or adhere to treatment regimens. This represents minimal alignment with the concept's focus on disease management and adherence. | Nutrition Education and Food Access: The testimonial focuses entirely on COVID-19 prevention measures (masks, handwashing, sanitizing, social distancing). While it mentions people eating fruits without washing hands previously, this is discussed only in the context of hygiene practices, not nutrition education or food access. There is no content about teaching healthy eating, addressing food insecurity, or improving nutritional awareness. | Sexual and Reproductive Health Education: The testimonial focuses entirely on COVID-19 prevention measures (masks, handwashing, sanitizing, social distancing) with no mention of sexual health, reproductive health, family planning, STIs, or any related topics. This clearly falls outside the concept's definition and inclusion criteria. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses entirely on COVID-19 prevention efforts and community health education about hygiene practices. There is no mention of abuse, violence, exploitation, or any GBV-related issues. The CHW discusses pandemic response, preventive measures, and behavioral changes in handwashing and mask-wearing, which falls completely outside the scope of GBV and child protection. | Health Literacy and Misconceptions: The testimonial describes successful health education about COVID-19 prevention measures with no evidence of misinformation or misconceptions. The CHW reports that community members have 'embraced and adopted the teachings' and are following proper health protocols. The narrative shows accurate health information being shared and understood, with positive behavioral changes resulting. This aligns with the exclusion criteria of 'accurate health discussions with no misunderstanding present.' | Mental Health Awareness and Support: The testimonial focuses entirely on COVID-19 prevention measures (handwashing, masks, social distancing) and community health education. There is no mention of psychological well-being, emotional support, or mental health issues like depression, anxiety, or loneliness. The CHW discusses only physical health prevention and behavioral changes related to hygiene practices. | Referrals and Advocacy: The testimonial focuses on COVID-19 prevention education and community sensitization, but does not mention helping with referrals, appointments, or navigating healthcare systems. The CHW describes teaching preventive measures (masks, handwashing, social distancing) rather than acting as an intermediary or advocate within the health system. This represents minimal alignment with the concept. | Community Empowerment Through Education: Strong alignment with the concept. The CHW describes conducting ongoing COVID-19 education that led to sustained behavior change in the community - regular handwashing, mask-wearing, and social distancing. The testimonial explicitly states 'members of the community have embraced and also adopted the teachings' and notes a 'big change' in hygiene habits compared to previous years. The community's zero COVID cases suggests effective empowerment through education. Score is not higher because the focus is on a specific health crisis rather than broader community self-reliance. | Resource and Material Distribution: The testimonial focuses entirely on COVID-19 education and awareness activities (sensitizing about masks, handwashing, sanitizing, social distancing) without any mention of distributing physical resources or materials. The CHW describes teaching and training community members but does not indicate providing masks, soap, sanitizers, or any other supplies. This aligns with the exclusion criteria of 'discussions of education or advice without material support.' | Monitoring and Follow-Up: The testimonial describes ongoing community sensitization about COVID-19 prevention, but lacks clear evidence of systematic follow-up visits or monitoring of specific individuals. The CHW mentions 'actively sensitizing' and that community members 'are always doing what I have trained them to do,' suggesting some ongoing observation, but this appears to be general community engagement rather than targeted follow-up with individuals to check progress or adjust care. | Trust and Cultural Mediation: The testimonial shows moderate alignment with trust-building themes. The CHW successfully gained community trust to implement COVID-19 preventive measures, evidenced by the community embracing and adopting the teachings. The statement 'the members of the community have embraced and also adopted the teachings' indicates trust was established. However, there's no explicit mention of navigating cultural or linguistic barriers, and the focus is primarily on health education rather than mediating between the community and health systems. | Parsing failed for concept 'Trust and Cultural Mediation' | Clinical Interventions by CHWs: The testimonial focuses entirely on COVID-19 prevention education and awareness activities (emphasizing masks, handwashing, sanitizing, social distancing). There is no mention of the CHW providing any direct clinical care such as administering medication, treating wounds, or managing physical injuries. This falls under the exclusion criteria of 'health education without direct clinical interaction.' | Mother and Infant Care: The testimonial focuses entirely on COVID-19 prevention activities including mask-wearing, handwashing, sanitizing, and social distancing. There is no mention of prenatal care, childbirth, postpartum support, infant health, nutrition, or any mother/infant-specific services. The CHW discusses general community health education related to pandemic prevention, which clearly falls outside the concept definition. | Successful Outcomes: Strong direct alignment with successful outcomes. The CHW's COVID-19 prevention efforts resulted in clear positive changes: community members 'embraced and adopted the teachings,' there is 'no single case that has been reported from this community,' and there's a 'big change' in hand washing and mask wearing behaviors. The testimonial explicitly attributes these improvements to the CHW's training and sensitization work, demonstrating successful problem resolution and community impact. | Material or Training Requests: The testimonial describes the CHW's activities in COVID-19 prevention education and the positive community response, but contains no explicit requests for materials, supplies, or training. The CHW reports on their work and community impact without asking for any additional resources or support, which aligns with the exclusion criteria. | Children Served: The testimonial focuses on COVID-19 prevention work with 'community members' and 'people' in general, with no specific mention of children, minors, or youth. While the CHW's work likely benefits children as part of the community, there is no direct evidence of targeted services or interactions with children that would meet the inclusion criteria. | Elderly Served: The testimonial focuses entirely on COVID-19 prevention education and community-wide sensitization efforts. While the CHW mentions working with 'community members' and 'people,' there is no specific mention of elderly individuals, seniors, or grandparents, nor any description of providing targeted assistance to older adults. The work described is general public health education without age-specific focus. | Women Served: The testimonial describes COVID-19 prevention education provided to 'community members' and 'people' without any specific mention of women, girls, or gender-specific services. While women may have been included in the general community outreach, there is no evidence of targeted assistance or education for women, nor any mention of gendered roles or challenges. This aligns with the exclusion criteria of no specific CHW interaction with women. | Men Served: The testimonial focuses on COVID-19 prevention education for the general community without any specific mention of men, boys, or gender-related issues. While men are presumably included in the 'community members' being served, there is no explicit reference to supporting men with health challenges, violence, or stigma as required by the inclusion criteria. | Families Served: The testimonial focuses on community-wide COVID-19 prevention efforts without specific mention of households, parents with children, or family units. The CHW describes working with 'community members' and 'people' in general terms, which aligns with the exclusion criteria of 'individual help not connected to a family unit or structure.' While the work likely benefited families, there is no explicit family-focused intervention or mention of supporting multiple family members together. | Marginalized Groups Served: The testimonial describes COVID-19 prevention work with the general community but makes no reference to marginalized or underserved groups. The CHW mentions working with 'community members' and 'people' without indicating any structural exclusion, stigma, or special vulnerabilities. This aligns with the example 'I spoke with people in the community' (0.1) - general community work without marginalization context. | Financial Hardship: The testimonial focuses entirely on COVID-19 prevention measures and community health education. There is no mention of poverty, inability to afford transportation, food, medical care, or any other financial struggles. The CHW discusses behavioral changes around hygiene and mask-wearing, but makes no reference to economic hardship or material scarcity. | Social Isolation: The testimonial focuses on COVID-19 prevention measures and community health education, with only minimal relevance to social isolation through mentions of 'restrictions' and 'minimal contact.' However, these are presented as public health measures rather than instances of people living alone or lacking support systems. The CHW describes an engaged community that has embraced health teachings, suggesting social connection rather than isolation. | Disease Burden: The testimonial focuses on COVID-19, which represents a significant disease burden as a pandemic causing chronic community health challenges. While it doesn't describe individual chronic illness or disability cases, it references the 'devastating effects' of the virus, multiple waves, deaths, and the ongoing threat to the community. This represents a moderate alignment with the concept as it describes a long-term, recurrent illness affecting the population rather than individual chronic conditions. | Stigma or Discrimination: The testimonial focuses entirely on COVID-19 prevention measures and community health education. There is no mention of social rejection, judgment, shame, or exclusion related to health conditions or identity. The CHW describes positive community engagement and adoption of health practices, which is the opposite of stigma or discrimination. | Mental or Emotional Distress: The testimonial focuses entirely on COVID-19 prevention measures and community health education. While it mentions the pandemic as a 'menace' and describes restrictions, there are no expressions of depression, hopelessness, trauma, or emotional overwhelm. The CHW expresses happiness about their community's response, and the content is about physical health measures (handwashing, masks, social distancing) rather than mental or emotional wellbeing. | Lack of Resources: The testimonial does not mention any lack of resources. The CHW describes successfully conducting COVID-19 awareness and prevention training, with positive community adoption of preventive measures. There is no mention of insufficient supplies, tools, or capacity limitations. The CHW appears to have been able to effectively carry out their sensitization work without resource constraints. | Systemic Barriers: Strong alignment with systemic barriers. The testimonial describes COVID-19 restrictions, curfews, and gathering limitations imposed by authorities - all systemic issues outside the CHW's control that affect their ability to conduct normal community health work. While the CHW has adapted by focusing on prevention education, the pandemic and government restrictions represent clear institutional/systemic barriers to their usual activities. | Overburdened CHWs: The testimonial shows no evidence of the CHW being overburdened. Instead, they express satisfaction and happiness with their work, stating 'This has made me very happy.' They describe successfully sensitizing their community about COVID-19 prevention without mentioning exhaustion, being overwhelmed, or having excessive workloads. The CHW appears to be managing their responsibilities effectively despite the pandemic challenges. | Lack of Follow-Through: The testimonial describes ongoing, sustained community health work focused on COVID-19 prevention. The CHW reports actively and continuously sensitizing community members, with successful adoption of preventive measures and no reported cases. There is no evidence of abandonment, interrupted care, or unresolved issues - rather, the work appears effective and ongoing. | Lack of Knowledge: The testimonial shows no evidence of the CHW lacking knowledge. Instead, it demonstrates the opposite - the CHW describes being trained and actively using that knowledge to educate the community about COVID-19 prevention measures. The CHW confidently shares preventive measures and reports successful outcomes, with no mentions of uncertainty, need for additional training, or inability to address issues due to knowledge gaps. | Parsing failed for concept 'Lack of Knowledge'</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>COVID-19 Regarding the COVID-19 new variant, since most of the community members took vaccines, many people have left the common practices which were given by the Ministry of Health such as washing hands, putting on masks, avoiding crowded places, and keeping social distance. Political rallies in Kenya have attracted so many crowds that has contributed to many people contracting the disease. Omicron wave was reported in Kenya some few weeks back and we have seen cases of the Omicron is rising day by day. As a CHW, I have been emphasizing on training the community members on how to continue practicing the COVID-19 measures and about mobilizing these who have not been vaccinated to go for vaccinations. ---</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.05,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.95,
+  "Water Quality, Sanitation, and Hygiene": 0.55,
+  "Personal Disease Management and Adherence": 0.6,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.3,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.6,
+  "Community Empowerment Through Education": 0.3,
+  "Resource and Material Distribution": 0.1,
+  "Monitoring and Follow-Up": 0.3,
+  "Trust and Cultural Mediation": 0.2,
+  "Clinical Interventions by CHWs": 0.0,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.2,
+  "Material or Training Requests": 0.05,
+  "Children Served": 0.05,
+  "Elderly Served": 0.0,
+  "Women Served": 0.0,
+  "Men Served": 0.0,
+  "Families Served": 0.0,
+  "Marginalized Groups Served": 0.05,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.55,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.05,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.4,
+  "Overburdened CHWs": 0.05,
+  "Lack of Follow-Through": 0.05,
+  "Lack of Knowledge": 0.05
+}</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial describes the CHW providing training to community members but does not mention the CHW receiving any training themselves, which is required for this concept. Hence, only minimal indirect evidence exists, resulting in a very low score. | Menstrual Hygiene Education and Challenges: The testimonial focuses solely on COVID-19 prevention and vaccination efforts; it does not mention menstruation, menstrual products, stigma, or related education. Therefore, the concept is not applicable. | Drug Abuse: Environment and Awareness: The testimonial solely discusses COVID-19 precautions and vaccination efforts; it contains no reference to substance abuse, addiction, peer influence on drug use, or related environmental factors. | CHW-Led Infectious Disease Management: The speaker explicitly states they are a CHW who trains community members on COVID-19 preventive measures (hand-washing, masking, social distancing) and mobilizes vaccination uptake. This directly matches the definition and inclusion criteria of CHWs educating communities about infectious-disease prevention, making it a strong, nearly perfect alignment. | Water Quality, Sanitation, and Hygiene: The testimonial references hand-washing as a recommended COVID-19 prevention measure and the CHW’s efforts to remind people to keep practicing it. This fits the concept’s inclusion of discussions about hand-washing, but it is only one brief mention within a broader focus on vaccination and social distancing, so alignment is moderate rather than strong. | Personal Disease Management and Adherence: The CHW describes encouraging community members to maintain COVID-19 preventive behaviors (hand-washing, masking, distancing) and to get vaccinated. These actions relate to adherence to disease-management guidelines for an infectious disease. However, the testimonial does not give concrete evidence of individuals actually following or sustaining these practices—only that the CHW promotes them—so the alignment is moderate rather than strong. | Nutrition Education and Food Access: The testimonial discusses COVID-19 preventive behaviors and vaccination efforts with no mention of food, nutrition education, or access to adequate nutrition. Therefore, the concept is not present. | Sexual and Reproductive Health Education: The testimonial focuses solely on COVID-19 prevention and vaccination; it contains no mention of family planning, STIs, HIV, condoms, or any reproductive-health education topics. | Gender-Based Violence (GBV) and Child Protection: The testimonial only discusses COVID-19 prevention and vaccination efforts; it makes no mention of abuse, violence, or child protection issues, so the concept is not applicable. | Health Literacy and Misconceptions: Testimonial notes that community members have stopped following preventive measures after vaccination, implying some lack of understanding about ongoing risk. However, it does not explicitly describe concrete misinformation or false beliefs; it mainly highlights behavior change and the CHW’s effort to re-educate. Therefore, only weak evidence of health literacy issues or misconceptions is present. | Mental Health Awareness and Support: The testimonial focuses solely on COVID-19 prevention measures and vaccination mobilization. It contains no mention of psychological well-being, emotional states, or mental health support, so the concept does not apply. | Referrals and Advocacy: The CHW describes mobilizing unvaccinated community members to go for COVID-19 vaccinations, which represents advocacy for utilizing health services. While no formal referral or navigation details are given, the encouragement to seek vaccination aligns moderately with the concept’s inclusion criteria. Hence a mid-level score is appropriate. | Community Empowerment Through Education: The CHW describes providing training and mobilizing people for vaccination, but there is no clear evidence that this education has led to lasting community-driven change or self-reliant habits; in fact, behaviors are slipping. This fits the exclusion of isolated education efforts without demonstrated long-term impact, so the alignment is weak. | Resource and Material Distribution: The CHW only describes training community members and encouraging vaccination—educational and mobilization activities without giving out any tangible supplies. This fits the exclusion criterion (education/advice without material support), so only minimal alignment is scored. | Monitoring and Follow-Up: The testimonial describes providing ongoing education and mobilization about COVID-19 precautions and vaccination, but it does not mention returning to specific individuals to check progress or health status. This fits more with initial or repeated health education rather than the defined ongoing monitoring/follow-up activities, so only weak alignment is present. | Trust and Cultural Mediation: The CHW describes educating and mobilizing community members to follow COVID-19 precautions and get vaccinated. While this involves communication, the testimonial does not specifically highlight overcoming cultural, linguistic, or trust barriers—no mention of translating, addressing mistrust, or mediating between health systems and community beliefs. Therefore only weak evidence of the trust/cultural mediation concept is present. | Clinical Interventions by CHWs: The testimonial describes educating the community about COVID-19 preventive measures and encouraging vaccination uptake—activities classified as health education and mobilization, not direct clinical interventions such as administering medication or treating injuries. Therefore, the concept is not present. | Mother and Infant Care: The testimonial exclusively discusses COVID-19 prevention and vaccination efforts for the general community with no mention of pregnancy, childbirth, postpartum issues, or infant health. Therefore, it does not align with the Mother and Infant Care concept. | Successful Outcomes: The CHW describes ongoing efforts to train and mobilize the community, but there is no evidence of resolved problems or measurable positive change; in fact, cases are said to be rising. This provides only minimal alignment with the concept of Successful Outcomes. | Material or Training Requests: The CHW describes emphasizing training community members, but does not request additional materials or personal training. Only mentions their own actions, so very weak alignment. | Children Served: The testimonial only mentions 'community members' without specifying children or adolescents. There is no explicit evidence of services directed toward minors, so alignment with the Children Served concept is minimal. | Elderly Served: The testimonial discusses COVID-19 precautions and vaccination efforts for the general community, without any mention of older adults or specific assistance to seniors, so the 'Elderly Served' concept is not present. | Women Served: The testimonial discusses COVID-19 prevention efforts for the general community without any mention of women or gender-specific challenges, so the concept does not apply. | Men Served: The testimonial discusses COVID-19 prevention efforts for the community in general without any mention of men or boys or gender-specific support. Therefore, the concept 'Men Served' is not present. | Families Served: The testimonial discusses COVID-19 prevention efforts directed at community members in general, with no mention of households, parents, children, or any family-focused intervention. Therefore, the concept 'Families Served' is not present. | Parsing failed for concept 'Families Served' | Marginalized Groups Served: The testimonial discusses educating and mobilizing general community members about COVID-19 prevention and vaccination but does not specify work with any structurally excluded or stigmatized group. Therefore, evidence for serving marginalized groups is minimal. | Financial Hardship: The testimonial discusses COVID-19 preventive practices and vaccination mobilization but contains no mention of inability to afford necessities, poverty, or material scarcity. | Social Isolation: The testimonial focuses on COVID-19 prevention measures and vaccine mobilization. It does not mention individuals living alone, feeling lonely, lacking support, or being socially neglected. Therefore, the Social Isolation concept is not present. | Disease Burden: The testimonial focuses on the continuing impact of COVID-19 and rising Omicron cases in the community, indicating an ongoing and significant disease presence. While COVID-19 is not necessarily a chronic condition for each individual, the repeated waves and sustained community spread suggest a persistent health burden. This fits the concept’s inclusion of recurrent illness, though it is not as clear-cut as a chronic illness example, so a moderate score is appropriate. | Stigma or Discrimination: The testimonial discusses COVID-19 prevention practices, vaccination, and community training but does not mention any social rejection, shame, or judgment toward individuals. Therefore, the stigma or discrimination concept is not present. | Mental or Emotional Distress: The testimonial focuses on COVID-19 prevention behaviors and vaccination efforts; it does not mention feelings of depression, stress, or emotional overwhelm. Therefore there is only negligible evidence for mental or emotional distress. | Lack of Resources: The testimonial discusses community adherence to COVID-19 precautions and the CHW’s efforts to educate and mobilize residents, but it does not mention insufficient supplies, medicine, or support. Therefore, the concept ‘Lack of Resources’ is not present. | Systemic Barriers: The testimonial notes that large political rallies—an external, institutional factor outside the CHW’s control—are drawing crowds and accelerating COVID-19 transmission, which complicates her prevention efforts. This reflects a systemic condition hampering her work, but the reference is brief and not framed as an explicit obstacle to providing services, so alignment is weak-to-moderate. | Overburdened CHWs: The testimonial notes that the CHW is educating and mobilizing the community, but it does not state that the CHW feels exhausted, overwhelmed, or that workloads are unmanageable. Any inference of burden is speculative, so alignment with the concept is minimal. | Lack of Follow-Through: The testimonial describes ongoing efforts by the CHW to train and mobilize the community about COVID-19 measures; there is no mention of abandoning an intervention or failing to complete assistance. Therefore, there is virtually no evidence of lack of follow-through. | Lack of Knowledge: The testimonial describes the CHW actively educating the community and does not mention any uncertainty, need for additional training, or inability to address issues due to a knowledge gap. Therefore, evidence for 'Lack of Knowledge' is essentially absent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>COVID-19 Regarding the COVID-19 new variant, since most of the community members took vaccines, many people have left the common practices which were given by the Ministry of Health such as washing hands, putting on masks, avoiding crowded places, and keeping social distance. Political rallies in Kenya have attracted so many crowds that has contributed to many people contracting the disease. Omicron wave was reported in Kenya some few weeks back and we have seen cases of the Omicron is rising day by day. As a CHW, I have been emphasizing on training the community members on how to continue practicing the COVID-19 measures and about mobilizing these who have not been vaccinated to go for vaccinations. ---</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.2,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.9,
+  "Water Quality, Sanitation, and Hygiene": 0.5,
+  "Personal Disease Management and Adherence": 0.3,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.3,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.7,
+  "Community Empowerment Through Education": 0.6,
+  "Resource and Material Distribution": 0.1,
+  "Monitoring and Follow-Up": 0.2,
+  "Trust and Cultural Mediation": 0.2,
+  "Clinical Interventions by CHWs": 0.0,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.2,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.0,
+  "Men Served": 0.0,
+  "Families Served": 0.0,
+  "Marginalized Groups Served": 0.1,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.2,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.0,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.7,
+  "Overburdened CHWs": 0.1,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial shows a CHW actively training community members on COVID-19 measures, but there is no mention of the CHW receiving training themselves. The CHW demonstrates knowledge and teaching capacity, but the concept specifically requires evidence of CHWs receiving training that increases their capacity to serve. This aligns with the example 'I started giving advice to neighbors based on what I learned informally' (0.2), where the CHW is sharing knowledge without clear evidence of formal training received. | Menstrual Hygiene Education and Challenges: The testimonial focuses entirely on COVID-19 prevention measures, vaccination efforts, and community health practices related to the pandemic. There is no mention of menstruation, menstrual hygiene, products, or any related education. The content clearly falls outside the concept's definition and inclusion criteria. | Drug Abuse: Environment and Awareness: The testimonial focuses entirely on COVID-19 prevention measures, vaccination efforts, and public health compliance. There is no mention of substance abuse, addiction, alcohol, drugs, or any related social/environmental factors that contribute to drug abuse. The content is exclusively about pandemic response and does not align with the drug abuse concept. | CHW-Led Infectious Disease Management: Strong direct alignment with the concept. The CHW explicitly describes educating community members about COVID-19 prevention measures (handwashing, masks, avoiding crowds, social distancing) and mobilizing for vaccinations. This directly matches the definition of CHWs helping communities understand and reduce disease spread through outreach and education, similar to the 0.9 example. | Water Quality, Sanitation, and Hygiene: The testimonial mentions 'washing hands' as one of the COVID-19 prevention practices that people have abandoned, and the CHW emphasizes training on COVID-19 measures which would include handwashing. This aligns moderately with the concept as it discusses handwashing in a disease prevention context, similar to the example 'People now wash hands more due to COVID-19' (0.5). However, the focus is primarily on COVID-19 prevention rather than water quality or sanitation infrastructure. | Personal Disease Management and Adherence: The testimonial focuses on community-level COVID-19 prevention measures and vaccination mobilization rather than individual disease management or treatment adherence. While it mentions disease (COVID-19) and preventive practices, it lacks specific examples of helping individuals manage their condition, adhere to treatment, or make lifestyle adjustments after diagnosis. The CHW's role is primarily educational and preventive at the population level, which aligns weakly with the concept's focus on personal disease management. | Nutrition Education and Food Access: The testimonial focuses entirely on COVID-19 prevention measures, vaccination efforts, and public health practices related to the pandemic. There is no mention of nutrition education, food access, food insecurity, healthy eating, or any nutrition-related topics. The content explicitly deals with disease prevention through hygiene practices and vaccination, which falls outside the scope of the nutrition concept. | Sexual and Reproductive Health Education: The testimonial focuses entirely on COVID-19 prevention measures, vaccination, and public health practices related to the pandemic. There is no mention of family planning, STI prevention, HIV awareness, reproductive rights, or any sexual health topics. The content clearly falls outside the scope of sexual and reproductive health education. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses entirely on COVID-19 prevention measures, vaccination efforts, and public health practices. There is no mention of abuse, violence, exploitation, or any GBV/child protection issues. The content is about disease prevention and community health education, which clearly falls outside the scope of this concept. | Health Literacy and Misconceptions: The testimonial shows weak alignment with health literacy issues. While the CHW describes people abandoning COVID-19 preventive measures after vaccination, this represents a behavioral lapse rather than explicit misinformation or misconceptions about disease. The CHW is addressing the need for continued education about COVID-19 measures, but there's no clear evidence of correcting false beliefs or addressing specific misconceptions about the disease's origins or transmission. | Mental Health Awareness and Support: The testimonial focuses entirely on COVID-19 prevention measures, vaccination efforts, and public health compliance. There is no mention of psychological well-being, emotional support, or mental health issues like depression, anxiety, or loneliness. The CHW discusses only physical health measures and disease prevention, which falls under the exclusion criteria. | Referrals and Advocacy: The testimonial shows moderate alignment with advocacy work. The CHW is actively advocating for COVID-19 preventive measures and mobilizing community members to get vaccinated, which aligns with the advocacy aspect of the concept. However, there is no explicit mention of referrals, appointments, or helping people navigate the healthcare system, which prevents a higher score. | Community Empowerment Through Education: The testimonial shows moderate alignment with the concept. The CHW is actively conducting training and mobilizing community members for vaccinations, which demonstrates ongoing education efforts. However, the testimonial indicates that people have abandoned previously learned health practices, suggesting limited lasting behavior change. While there is evidence of continued educational efforts, the lack of sustained community self-reliance or improved habits prevents a higher score. | Resource and Material Distribution: The testimonial focuses entirely on education and training about COVID-19 measures and vaccine mobilization. There is no mention of the CHW distributing any physical resources like masks, hygiene kits, vaccines, or other materials. This aligns with the exclusion criteria of 'discussions of education or advice without material support' and matches the example 'I gave general advice that day; I didn't bring any supplies.' → 0.1 | Monitoring and Follow-Up: The testimonial describes ongoing community education efforts about COVID-19 prevention and vaccine mobilization, but lacks clear evidence of monitoring specific individuals or following up on their progress. The CHW mentions 'emphasizing on training' and 'mobilizing,' which suggests repeated interactions but not the systematic follow-up or progress checking described in the concept definition. | Trust and Cultural Mediation: The testimonial shows minimal evidence of trust-building or cultural mediation. While the CHW mentions 'training the community members' and 'mobilizing' for vaccinations, there's no explicit mention of building trust, navigating cultural barriers, or addressing community hesitations. The focus is on information dissemination rather than the trust-building or cultural bridging aspects that define this concept. | Clinical Interventions by CHWs: The testimonial describes only health education activities (training community members on COVID-19 measures) and mobilization for vaccinations. There is no mention of the CHW directly administering medications, treating wounds, or performing any hands-on clinical tasks. This falls under the exclusion criteria of 'health education or referrals without direct clinical interaction.' | Mother and Infant Care: The testimonial focuses entirely on COVID-19 prevention, vaccination, and community health measures. There is no mention of prenatal care, childbirth, postpartum support, infant health, or any mother/infant-specific services. The content explicitly deals with general community health education about pandemic response, which falls outside the concept's definition. | Successful Outcomes: The testimonial describes CHW efforts to train community members and mobilize for vaccinations, but provides no evidence of actual outcomes or improvements. The CHW mentions what they 'have been emphasizing' but doesn't indicate whether people followed the advice, got vaccinated, or if conditions improved. This aligns with the example 'I told people to take care of their health, but it's hard to know if they listened' (0.1), though slightly higher due to more specific actions mentioned. | Material or Training Requests: The testimonial describes the CHW's current activities (emphasizing training and mobilizing community members) but contains no explicit requests for materials, supplies, or training. The CHW discusses what they are already doing rather than asking for resources to better serve their community. | Children Served: The testimonial focuses on COVID-19 prevention measures and vaccination efforts for 'community members' in general, with no specific mention of children, minors, or youth. The CHW discusses training and mobilizing the community broadly but does not indicate any particular focus on or involvement with children under 18. | Elderly Served: The testimonial focuses entirely on COVID-19 education and vaccination efforts for the general community. There is no mention of elderly people, seniors, or grandparents, nor any specific assistance provided to older adults. The CHW describes working with 'community members' broadly without any age-specific focus. | Women Served: The testimonial describes COVID-19 education and vaccination mobilization for 'community members' without any specific mention of women, girls, or gender-specific services. The CHW's activities appear to target the general population without addressing women's particular needs or challenges, which aligns with the exclusion criteria. | Men Served: The testimonial discusses COVID-19 prevention measures and vaccination efforts for the general community without any specific mention of men, boys, or gender-related issues. There is no evidence of support specifically targeted at men or addressing male-specific health challenges, which is required by the concept definition. | Families Served: The testimonial focuses on community-wide COVID-19 education and vaccination mobilization without any mention of households, parents with children, or family units. The CHW discusses training 'community members' broadly and addressing crowds at political rallies, but there is no evidence of family-focused interventions or support for multiple family members, which are required by the inclusion criteria. | Marginalized Groups Served: The testimonial describes general COVID-19 education and vaccination mobilization for the broader community, but does not mention serving any specific marginalized or stigmatized groups. While the CHW is providing important public health services, there is no reference to structural exclusion, social stigma, or underserved populations that would align with the concept definition. | Financial Hardship: The testimonial focuses entirely on COVID-19 prevention measures, vaccination efforts, and public health behaviors. There is no mention of poverty, inability to afford transportation, food, medical care, or any other financial constraints. The content is about health education and disease prevention, not economic hardship. | Social Isolation: The testimonial focuses on COVID-19 prevention measures and community health education. While it mentions 'social distance' as a public health measure, this refers to physical distancing for disease prevention, not social isolation as defined by the concept (loneliness, lack of support systems, or abandonment). There is no mention of individuals living alone, lacking support, or experiencing loneliness. | Disease Burden: The testimonial discusses COVID-19 prevention and rising cases but does not reference chronic illness, disability, or frequent illness episodes at the individual level. It focuses on community-wide prevention measures and vaccination efforts rather than managing long-term or recurrent illness in specific patients, which is central to the Disease Burden concept. | Stigma or Discrimination: The testimonial focuses on COVID-19 prevention measures, vaccination efforts, and community health practices. There is no mention of social rejection, judgment, shame, or exclusion related to health conditions or identity. The CHW discusses general public health behaviors and compliance issues, not stigma or discrimination. | Mental or Emotional Distress: The testimonial focuses entirely on COVID-19 prevention measures, vaccination efforts, and public health practices. There is no mention of depression, hopelessness, trauma, stress, or any emotional/mental health concerns. The CHW discusses physical health prevention and community education about disease transmission, which falls under the exclusion criteria. | Lack of Resources: The testimonial does not mention any lack of resources. The CHW describes conducting training and mobilization activities without indicating insufficient supplies, tools, or capacity. The focus is on community behavior and education efforts, with no evidence of resource constraints limiting the CHW's ability to address the COVID-19 situation. | Systemic Barriers: The testimonial describes systemic issues beyond the CHW's control - specifically political rallies creating crowded conditions that spread COVID-19, and the broader community abandoning health practices. These are institutional/societal conditions preventing the CHW from effectively protecting community health, aligning with the definition of 'issues outside CHW control.' The score is not higher because the CHW is still able to provide training and mobilize vaccinations, suggesting the barriers are significant but not completely preventing their work. | Overburdened CHWs: The testimonial describes a CHW actively conducting training and mobilization activities during the COVID-19 pandemic, but contains no evidence of being overburdened, exhausted, or overwhelmed. The CHW appears to be functioning effectively in their role without mentioning excessive workloads or inability to meet demands. This aligns with the example of seeing multiple people without difficulties (0.1). | Lack of Follow-Through: The testimonial describes ongoing CHW efforts to train community members and mobilize vaccinations, with no indication of abandoned care or unresolved issues. The CHW is actively continuing their work rather than starting and stopping assistance. | Lack of Knowledge: The testimonial shows no evidence of knowledge gaps. The CHW demonstrates clear understanding of COVID-19 prevention measures, identifies community behavioral issues, and actively conducts training and vaccination mobilization. There are no mentions of uncertainty, requests for training, or inability to address issues due to lack of knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Malaria Having malaria is a very bad experience that personally I would not like to get sick again. Physical symptoms that I had was fatigue, vomiting, fever, and sometimes diarrhea. In the evening a strong headache and chills appeared as if it had been stirred up or triggered by something. Sincerely speaking, when I felt symptoms coming on, I used to go over the counter and buy malaria drugs—e.g., ACTM—because I thought that every symptom as such could be malaria which I realized after becoming a CHW that it was not a good idea. Malaria could return again and again because I was not adhering to the instructions of completing doses, I was not treating malaria well, not sleeping under mosquito treated net. As a CHW, what I can do to help people with malaria is to advise them to go to the hospital and get tested and also to be treated well whenever the symptoms occur. ---</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.6,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.25,
+  "CHW-Led Infectious Disease Management": 0.8,
+  "Water Quality, Sanitation, and Hygiene": 0.05,
+  "Personal Disease Management and Adherence": 0.9,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.9,
+  "Mental Health Awareness and Support": 0.05,
+  "Referrals and Advocacy": 0.6,
+  "Community Empowerment Through Education": 0.3,
+  "Resource and Material Distribution": 0.0,
+  "Monitoring and Follow-Up": 0.1,
+  "Trust and Cultural Mediation": 0.1,
+  "Clinical Interventions by CHWs": 0.05,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.1,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.0,
+  "Men Served": 0.0,
+  "Families Served": 0.05,
+  "Marginalized Groups Served": 0.05,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.65,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.1,
+  "Lack of Resources": 0.05,
+  "Systemic Barriers": 0.05,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.05,
+  "Lack of Knowledge": 0.2
+}</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The speaker notes that \ | Menstrual Hygiene Education and Challenges: The testimonial focuses solely on malaria symptoms, treatment, and prevention. It contains no mention of menstruation, menstrual products, stigma, or education, which are required for the concept. | Drug Abuse: Environment and Awareness: Testimonial describes self-medicating with malaria drugs and not completing doses, reflecting a lack of drug-use education. However, it does not address addiction, alcohol abuse, or social/peer influences that typically define substance abuse. Therefore, only a weak alignment to the concept is present. | CHW-Led Infectious Disease Management: The speaker discusses malaria (an infectious disease) and, as a CHW, describes advising people to seek testing, complete treatment, and use preventive measures (sleeping under insecticide-treated nets). This fits the concept’s inclusion criteria of CHWs explaining symptoms, prevention, and follow-up. The alignment is strong but not exhaustive of wide community outreach, so 0.8 is appropriate. | Water Quality, Sanitation, and Hygiene: Testimonial focuses on malaria symptoms, treatment adherence, and mosquito-net use; it does not discuss clean water, sanitation practices, or hygiene education. Minimal relevance to the concept. | Personal Disease Management and Adherence: The testimonial centers on malaria management: the speaker describes self-treating, failing to complete medication doses, not using a bed net, and now—as a CHW—advising others to get tested and adhere to proper treatment. This directly addresses diagnosis, treatment adherence, and lifestyle adjustments, fitting the concept definition very well, with clear, specific evidence. | Nutrition Education and Food Access: The testimonial focuses on malaria symptoms, treatment, and prevention, with no mention of food, nutrition education, or access to adequate nutrition, so the concept does not apply. | Sexual and Reproductive Health Education: The testimonial focuses solely on malaria symptoms, treatment adherence, and mosquito net use, with no mention of condoms, family planning, STIs, HIV, or other reproductive health education topics. Therefore the concept is not present. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses solely on personal experiences with malaria and advice on proper treatment and prevention. It contains no references to abuse, exploitation, violence, or child protection issues, which are required for this concept. | Health Literacy and Misconceptions: The speaker admits to the misconception that any occurrence of fatigue, vomiting, fever, etc. automatically meant malaria and self-medicated without testing or completing doses. This shows misinformation and lack of knowledge influencing health decisions, fitting the definition and inclusion criteria of the concept very well. | Parsing failed for concept 'Health Literacy and Misconceptions' | Mental Health Awareness and Support: The testimonial focuses on physical symptoms and treatment behaviors related to malaria. There is no discussion of psychological well-being, depression, anxiety, or emotional support, so alignment with the mental health concept is minimal. | Referrals and Advocacy: The CHW states they \ | Community Empowerment Through Education: The CHW mentions advising people to seek testing and proper treatment, showing some intent to educate, but there is no description of sustained community-wide behavior change, peer education, or collective action. This is closer to an isolated educational effort, fitting weak alignment with the concept. | Resource and Material Distribution: The testimonial only describes advising people to seek testing and treatment; it does not mention providing or distributing any physical supplies (e.g., medication, bed nets, kits). Therefore, the concept of Resource and Material Distribution is not present. | Monitoring and Follow-Up: The testimonial focuses on advising people to get tested and treated and to follow preventive measures, but it does not mention returning to check on patients or ongoing follow-up. This fits the exclusion criteria of a one-time educational interaction, hence only weak alignment. | Trust and Cultural Mediation: The testimonial focuses on personal experience with malaria and advising others to seek treatment; it does not describe the CHW building trust, translating, or addressing cultural or linguistic barriers. Any alignment with trust-building is implicit and minimal. | Clinical Interventions by CHWs: The testimonial describes advising people to seek testing and treatment at the hospital—education/referral rather than administering medication or treating injuries directly. Any drug use mentioned was self-medication before becoming a CHW. This falls under the concept’s exclusion criteria, so alignment is minimal. | Mother and Infant Care: The testimonial discusses malaria experiences and advice on testing, treatment adherence, and mosquito nets; it does not mention pregnancy, childbirth, postpartum issues, or infant health, so it does not align with the Mother and Infant Care concept. | Successful Outcomes: The testimonial describes past personal illness and advises what the CHW could do (encourage testing and treatment), but provides no evidence that these actions have yet led to any problem resolution or health improvement. Therefore, it only weakly aligns with the concept of Successful Outcomes. | Material or Training Requests: The testimonial discusses personal experiences with malaria and advice given as a CHW, but contains no explicit request for materials, supplies, or additional training. | Children Served: The testimonial discusses personal experiences with malaria and how the CHW advises people in general but never mentions children or adolescents, so the concept is not present. | Elderly Served: The testimonial discusses malaria symptoms, self-medication, and CHW advice to seek testing, but it never references older adults or services specifically for seniors. | Women Served: The testimonial discusses personal experiences with malaria and general advice to the community; it contains no mention of women, girls, or gender-specific issues. Therefore the concept “Women Served” is not applicable. | Men Served: The testimonial discusses malaria symptoms and proper treatment, with no reference to men or boys, gender-specific challenges, or support activities directed toward them. | Families Served: The testimonial discusses the CHW’s personal malaria experience and general advice to “people,” but it does not mention households, parents, children, or any family-focused intervention. Thus, only a negligible connection to the concept exists. | Marginalized Groups Served: The testimonial discusses helping 'people with malaria' in general, without identifying them as structurally excluded or stigmatized groups. Therefore there is almost no evidence of serving marginalized populations, only a generic reference to community members. | Financial Hardship: The testimonial focuses on malaria symptoms, self-treatment habits, and CHW advice. It contains no mention of poverty, inability to pay, transportation costs, or other material scarcity, so the Financial Hardship concept is not present. | Social Isolation: The testimonial discusses personal experiences with malaria and advice about proper treatment and prevention but makes no mention of living alone, lack of support, loneliness, or abandonment. Therefore, the Social Isolation concept is not present. | Disease Burden: The testimonial discusses experiencing malaria multiple times ('malaria could return again and again') and the significant physical symptoms it caused, indicating recurrent illness episodes. While malaria is not typically classified as a chronic illness, the repeated bouts show ongoing disease burden, giving a moderate alignment with the concept. | Stigma or Discrimination: The testimonial discusses personal illness experiences and advice for malaria treatment, but contains no mention of social rejection, judgment, shame, or discrimination. Therefore, the concept is not present. | Mental or Emotional Distress: The testimonial focuses on physical symptoms of malaria and actions taken; it contains only a mild statement that having malaria was a 'very bad experience' and not wanting to get sick again. There is no clear expression of depression, hopelessness, or marked emotional strain, so alignment with the mental or emotional distress concept is minimal. | Lack of Resources: The testimonial discusses personal experiences with malaria and advises others to seek proper treatment, but it does not mention shortages of medicine, tools, or support faced by the CHW. Therefore, evidence for a lack of resources is essentially absent. | Systemic Barriers: The testimonial focuses on the speaker’s past self-medication habits and the advice they now give to seek testing and treatment. It does not mention health-system shortages, corruption, distance, overcrowding, or any other larger institutional factor that prevents care. Thus there is essentially no evidence of systemic barriers. | Overburdened CHWs: The testimonial discusses personal experience with malaria and what the speaker, as a CHW, can advise others to do. It does not mention workload, exhaustion, or being overwhelmed. Therefore, the concept of overburdened CHWs is not present. | Lack of Follow-Through: The testimonial recounts personal experiences with malaria and future intentions to advise patients, but it does not describe any situation where the CHW began assistance and then left the issue unresolved. There is no abandonment or interrupted care, so alignment with the concept is negligible. | Lack of Knowledge: The speaker notes that before becoming a CHW they misunderstood malaria treatment (an earlier lack of knowledge), but they do not express current uncertainty or need for more training as a CHW. Since the concept targets present gaps that hinder the CHW’s ability to act, only minimal, indirect evidence is present, warranting a low score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Malaria Having malaria is a very bad experience that personally I would not like to get sick again. Physical symptoms that I had was fatigue, vomiting, fever, and sometimes diarrhea. In the evening a strong headache and chills appeared as if it had been stirred up or triggered by something. Sincerely speaking, when I felt symptoms coming on, I used to go over the counter and buy malaria drugs—e.g., ACTM—because I thought that every symptom as such could be malaria which I realized after becoming a CHW that it was not a good idea. Malaria could return again and again because I was not adhering to the instructions of completing doses, I was not treating malaria well, not sleeping under mosquito treated net. As a CHW, what I can do to help people with malaria is to advise them to go to the hospital and get tested and also to be treated well whenever the symptoms occur. ---</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.7,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.7,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.9,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.8,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.8,
+  "Community Empowerment Through Education": 0.3,
+  "Resource and Material Distribution": 0.0,
+  "Monitoring and Follow-Up": 0.1,
+  "Trust and Cultural Mediation": 0.2,
+  "Clinical Interventions by CHWs": 0.1,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.1,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.0,
+  "Men Served": 0.0,
+  "Families Served": 0.0,
+  "Marginalized Groups Served": 0.0,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.7,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.1,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.8
+}</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial shows moderate alignment with CHW empowerment through training. The speaker explicitly mentions 'becoming a CHW' and demonstrates knowledge gained through this role - specifically learning that self-medicating with over-the-counter malaria drugs without proper testing 'was not a good idea.' They also show capacity to serve by advising community members to seek proper testing and treatment. However, the testimonial doesn't explicitly mention formal training, workshops, or the training process itself, which prevents a higher score. | Menstrual Hygiene Education and Challenges: The testimonial focuses entirely on malaria - its symptoms, personal experience with the disease, and advice for treatment. There is no mention of menstruation, menstrual hygiene, products, or any related education. The content explicitly excludes the concept as it discusses a completely different health topic. | Drug Abuse: Environment and Awareness: The testimonial focuses entirely on malaria symptoms, treatment, and prevention. There is no mention of substance abuse, addiction, alcohol, peer influence, or drug education. The only reference to 'drugs' is in the context of malaria medication (ACTM), which is a legitimate medical treatment, not substance abuse. This clearly falls under the exclusion criteria as it lacks any social/environmental context related to drug abuse. | CHW-Led Infectious Disease Management: The testimonial shows moderate alignment with CHW-led infectious disease management. The speaker explicitly identifies as a CHW and describes how they now advise people with malaria to seek proper testing and treatment at hospitals. They demonstrate understanding of proper disease management versus their previous self-medication practices. However, the focus is more on personal experience with malaria and lessons learned rather than active community education or outreach programs, which prevents a higher score. | Water Quality, Sanitation, and Hygiene: The testimonial focuses entirely on malaria symptoms, treatment, and prevention through mosquito nets and proper medication adherence. There is no mention of water quality, sanitation practices, or hygiene education. While diarrhea is mentioned as a symptom, it's presented as a malaria symptom rather than linked to water or sanitation issues. | Personal Disease Management and Adherence: Strong direct alignment with the concept. The testimonial explicitly describes personal experience managing malaria, including poor adherence practices (not completing doses, self-medicating with over-the-counter drugs) and the consequences (recurring malaria). The speaker acknowledges learning proper disease management through CHW training and now advises others on proper diagnosis and treatment adherence. This closely matches the concept's focus on disease management through diagnosis, treatment adherence, and CHW guidance. | Nutrition Education and Food Access: The testimonial focuses entirely on malaria symptoms, treatment, and prevention. There is no mention of nutrition education, food access, healthy eating, or any food-related topics. The content is exclusively about a communicable disease and medical adherence, which falls outside the scope of the nutrition concept. | Sexual and Reproductive Health Education: The testimonial focuses entirely on malaria - its symptoms, treatment, and prevention through mosquito nets and proper medication adherence. There is no mention of any sexual or reproductive health topics such as family planning, STIs, HIV, condoms, or reproductive rights. The content is exclusively about malaria education and prevention. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses entirely on the CHW's personal experience with malaria, its symptoms, and their role in advising others about proper malaria treatment. There is no mention of violence, abuse, exploitation, or any form of GBV or child protection issues. This clearly falls under the exclusion criteria as it discusses physical health symptoms without any reference to violence or abuse. | Health Literacy and Misconceptions: Strong alignment with the concept. The testimonial explicitly describes a health misconception where the CHW used to self-medicate with malaria drugs for any symptoms, believing 'every symptom as such could be malaria.' They acknowledge this was 'not a good idea' after becoming a CHW, showing a clear correction of previous health literacy gaps. The testimonial also mentions improper treatment adherence and prevention practices, demonstrating multiple aspects of health misconceptions that were later corrected through education. | Mental Health Awareness and Support: The testimonial focuses entirely on physical symptoms of malaria (fatigue, vomiting, fever, diarrhea, headache, chills) and medical treatment approaches. There is no mention of psychological well-being, emotional states, or mental health aspects. The content is purely about physical illness and medical care, which falls under the exclusion criteria of 'medical diagnoses without a mental/emotional context.' | Referrals and Advocacy: Strong direct alignment. The CHW explicitly states they 'advise them to go to the hospital and get tested' when people have malaria symptoms, which is a clear example of helping with referrals to healthcare facilities. This matches the inclusion criteria of 'helping with referrals' and aligns with the 0.9 example of referring for testing, though slightly less direct since it's advice rather than active referral. | Community Empowerment Through Education: The testimonial shows personal learning and behavior change in the CHW themselves (stopped self-medicating, learned proper malaria treatment), but provides minimal evidence of community-wide education or empowerment. The CHW mentions advising people to seek proper testing and treatment, which suggests some educational activity, but there's no indication of sustained community change, peer education, or group action. This aligns with weak alignment as there's minimal evidence of community empowerment through education. | Resource and Material Distribution: The testimonial contains no evidence of the CHW distributing any physical resources or materials. The CHW only mentions advising people to go to the hospital for testing and treatment. This falls under the exclusion criteria of 'discussions of education or advice without material support.' The testimonial is entirely focused on personal experience with malaria and providing advice, with no mention of distributing nets, medicine, or any other supplies. | Monitoring and Follow-Up: The testimonial primarily describes personal malaria experiences and mentions advising people to seek hospital care, but contains no evidence of ongoing monitoring or follow-up activities. The CHW only mentions giving advice to seek testing and treatment, which aligns with the example 'I visited homes to tell people about disease prevention' (0.1) - a one-time educational interaction without follow-up. | Trust and Cultural Mediation: The testimonial shows minimal alignment with trust and cultural mediation. While the CHW mentions advising people to go to the hospital for testing and treatment, there is no evidence of building trust, navigating cultural barriers, or addressing community hesitancy about healthcare. The focus is primarily on the CHW's personal malaria experience and clinical advice, without any mention of translating information, explaining unfamiliar practices, or earning community trust. | Clinical Interventions by CHWs: The testimonial primarily describes personal experience with malaria and mentions advising people to go to the hospital for testing and treatment, which aligns with the exclusion criteria of 'referrals without direct clinical interaction.' There is no mention of the CHW directly administering medication, treating wounds, or providing any hands-on clinical care. The score of 0.1 reflects minimal alignment, similar to the example 'I spoke to the group about taking care of wounds.' | Mother and Infant Care: The testimonial focuses entirely on malaria - its symptoms, personal experience with the disease, and advice for malaria prevention and treatment. There is no mention of pregnancy, childbirth, postpartum care, infant health, breastfeeding, or any other mother/infant-specific topics. The content is about general disease management and prevention, not maternal or infant care. | Successful Outcomes: The testimonial primarily describes personal experiences with malaria and lessons learned after becoming a CHW. While the CHW mentions advising people to go to the hospital for testing and treatment, there is no mention of actual outcomes from these efforts or any specific instances where their advice led to improvements. This aligns with the example 'I told people to take care of their health, but it's hard to know if they listened' which scores 0.1. | Material or Training Requests: The testimonial describes personal experiences with malaria and what the CHW learned about proper treatment, but contains no requests for materials, supplies, or training. The CHW only discusses past behaviors and current advisory practices without asking for any resources or additional education. | Children Served: The testimonial focuses entirely on the CHW's personal experience with malaria and their general advice to people about seeking proper treatment. There is no mention of children, minors, or any age-specific population being served. The CHW discusses helping 'people' in general but makes no reference to working with children specifically. | Elderly Served: The testimonial focuses entirely on the CHW's personal experience with malaria and their role in advising people about malaria treatment. There is no mention of elderly people, seniors, or grandparents, nor any indication of providing services specifically to older adults. The content is about malaria education and treatment adherence for the general population. | Women Served: The testimonial is a personal account of the CHW's own experience with malaria and general advice they would give to people. There is no mention of women, girls, or any gender-specific interactions or services provided. The CHW discusses helping 'people' in general, without any reference to women or gendered health challenges. | Men Served: The testimonial is a personal account of the CHW's own experience with malaria and does not mention serving, supporting, or addressing any men or boys. There are no references to male individuals in any context, let alone in relation to health support, violence, or stigma as required by the inclusion criteria. | Families Served: The testimonial is entirely focused on the CHW's personal experience with malaria and their individual learning journey. There is no mention of households, parents with children, or any family units. The CHW discusses helping 'people' in general terms but does not reference any family-focused interventions or support for multiple family members, meeting the exclusion criteria of 'individual help not connected to a family unit or structure.' | Marginalized Groups Served: The testimonial describes the CHW's personal experience with malaria and general advice they would give to anyone with malaria symptoms. There is no mention of serving marginalized, stigmatized, or structurally excluded groups. The CHW discusses helping 'people with malaria' in general terms without any reference to specific vulnerable populations or those facing social exclusion. | Financial Hardship: The testimonial focuses entirely on the physical symptoms and personal experience with malaria, along with treatment behaviors. There is no mention of financial constraints, inability to afford care, transportation costs, or material scarcity. The person describes buying over-the-counter drugs, which suggests some ability to purchase medication rather than financial hardship. | Social Isolation: The testimonial focuses entirely on the CHW's personal experience with malaria symptoms and treatment practices. There is no mention of living alone, lack of support systems, loneliness, or social neglect. The narrative is about medical self-treatment and proper healthcare practices, not social circumstances or isolation. | Disease Burden: The testimonial describes recurrent malaria episodes ('Malaria could return again and again') due to poor treatment adherence, indicating a pattern of repeated illness. While malaria episodes can be acute, the speaker's experience of multiple recurring episodes and the significant impact on their life ('very bad experience that personally I would not like to get sick again') suggests a moderate disease burden. However, it doesn't reach the highest scores as malaria is typically episodic rather than a continuous chronic condition like diabetes. | Stigma or Discrimination: The testimonial focuses entirely on personal malaria symptoms, treatment experiences, and medical advice. There is no mention of social rejection, shame, exclusion, or judgment from others due to the health condition. The narrative is purely medical and educational without any social stigma elements. | Mental or Emotional Distress: The testimonial focuses entirely on physical symptoms of malaria (fatigue, vomiting, fever, diarrhea, headache, chills) and medical treatment approaches. While the person describes malaria as a 'very bad experience,' this refers to physical suffering rather than mental or emotional distress. There is no expression of depression, hopelessness, trauma, or emotional overwhelm. The exclusion criteria specifically mentions 'physical complaints' which is what this testimonial primarily contains. | Lack of Resources: The testimonial does not mention any lack of resources. The CHW describes personal experiences with malaria and their role in advising people to seek hospital care, but there is no indication of insufficient supplies, medicine, tools, or capacity limitations in their CHW work. The focus is on education and referral rather than resource constraints. | Systemic Barriers: The testimonial focuses entirely on personal experiences with malaria and the CHW's role in advising patients. There is no mention of systemic issues like health facility shortages, overcrowding, distance to hospitals, or institutional barriers that would prevent the CHW from helping patients. The narrative is about personal health experiences and education, not systemic obstacles. | Overburdened CHWs: The testimonial focuses entirely on the CHW's personal experience with malaria and their role in advising community members about proper malaria treatment. There is no mention of workload, being overwhelmed, having too many patients, or feeling exhausted from CHW duties. The CHW describes their educational role without any indication of being overburdened. | Lack of Follow-Through: This testimonial does not describe any instance where the CHW started helping someone but left the issue unresolved. The speaker discusses their personal experience with malaria before becoming a CHW and mentions incomplete treatment adherence as a patient, but this is not about the CHW failing to follow through on helping others. The testimonial ends with the CHW's commitment to advise people to seek proper testing and treatment, with no indication of abandonment or interrupted care. | Lack of Knowledge: Strong alignment with the concept. The CHW explicitly admits to past incorrect practices due to lack of knowledge ('I thought that every symptom as such could be malaria which I realized after becoming a CHW that it was not a good idea'). They describe self-medicating without proper diagnosis and not following treatment protocols before gaining CHW training. This directly demonstrates how lack of knowledge led to improper treatment approaches, though the testimonial focuses on past ignorance rather than current knowledge gaps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Malaria Malaria is a bacterial infection caused by plasmodium vale that affects the blood stream of human body. It is spread through anopheles mosquito bite from one person to another. People who have malaria usually feel sick with high fever and shaking chills. Some people may experience signs in the abdomen or muscles, fatigue, fever, night sweats, shivering, nausea, diarrhea, vomiting, headache, and coldness. The physical symptoms of malaria may include vomiting, tiredness, shivering, body weakness, sweating, children might be restless. The immediate action I take as a Community Health Worker when I see the symptoms coming is to do the sponging to reduce temperature, drink a lot of water due to vomiting and diarrhea. This are the first aid you do before going to the hospital. The malaria infection may return time and again if the patient does not follow the preventive measures like sleeping under the treated mosquito nets and vector control. As a Community Health Worker, if you once identify someone suffering from malaria, I immediately refer to the nearest health center. Many people have died from malaria due to late diagnosis that might lead to anemia, enlarged spleen that leads to ????????? that have similar symptoms as malaria. Disease like typhoid, dysentery. So, if not careful, you might miss the diagnosis, so you must thoroughly and probe the client. You should be well conversant with the signs and symptoms of malaria. And thus, the slogan “ZERO MALARIA STARTS WITH ME.” ---</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.1,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 1.0,
+  "Water Quality, Sanitation, and Hygiene": 0.05,
+  "Personal Disease Management and Adherence": 0.8,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.8,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.9,
+  "Community Empowerment Through Education": 0.2,
+  "Resource and Material Distribution": 0.05,
+  "Monitoring and Follow-Up": 0.1,
+  "Trust and Cultural Mediation": 0.1,
+  "Clinical Interventions by CHWs": 0.8,
+  "Mother and Infant Care": 0.05,
+  "Successful Outcomes": 0.25,
+  "Material or Training Requests": 0.05,
+  "Children Served": 0.1,
+  "Elderly Served": 0.0,
+  "Women Served": 0.0,
+  "Men Served": 0.0,
+  "Families Served": 0.1,
+  "Marginalized Groups Served": 0.0,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.65,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.05,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.1,
+  "Overburdened CHWs": 0.05,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.05
+}</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial demonstrates the CHW’s knowledge about malaria and appropriate actions, but it never mentions receiving training, attending workshops, or any learning event that explicitly increased their capacity. Any alignment is speculative, so only a minimal score is warranted. | Menstrual Hygiene Education and Challenges: The testimonial focuses solely on malaria causes, symptoms, and first-aid; it contains no discussion of menstruation, menstrual products, education, or related stigma. | Drug Abuse: Environment and Awareness: The testimonial solely discusses malaria symptoms, prevention, and first aid. It contains no references to substance use, addiction, or environmental/educational factors related to drug abuse, so the concept is not applicable. | CHW-Led Infectious Disease Management: The testimonial is written by a Community Health Worker who describes identifying malaria symptoms, providing first-aid, educating on preventive measures (treated mosquito nets, vector control), and referring patients for treatment. This directly matches the concept definition and inclusion criteria of CHWs helping communities understand and reduce the spread of an infectious disease. | Water Quality, Sanitation, and Hygiene: The testimonial briefly advises patients to \ | Personal Disease Management and Adherence: The testimonial focuses on recognizing malaria symptoms, giving immediate first-aid, stressing timely referral, and encouraging preventive practices (e.g., sleeping under treated nets). This directly concerns managing an infectious disease and promoting adherence to preventive measures, matching the concept definition. While it does not detail a specific patient’s medication schedule, it clearly describes disease management guidance from a CHW, warranting a strong but not perfect score. | Nutrition Education and Food Access: The testimonial focuses exclusively on malaria symptoms, first aid, and prevention, with no discussion of healthy eating, food insecurity, or nutrition education. | Sexual and Reproductive Health Education: The testimonial focuses exclusively on malaria symptoms, prevention, and first aid. It contains no content related to family planning, STI prevention, HIV awareness, or any other aspect of sexual and reproductive health education. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses exclusively on malaria symptoms, first aid, and referral procedures. There is no mention of abuse, exploitation, violence, or child protection concerns, so the concept does not apply. | Health Literacy and Misconceptions: The testimonial states that “Malaria is a bacterial infection caused by plasmodium,” which is factually incorrect (malaria is caused by a protozoan parasite). This represents a clear misbelief about disease origin, directly fitting the concept’s inclusion of “misbeliefs about disease origins.” Therefore there is strong alignment, though the entire piece is not solely about combating misinformation, hence 0.8 rather than 1.0. | Mental Health Awareness and Support: The testimonial focuses entirely on physical symptoms, prevention, and treatment of malaria with no mention of emotional well-being, depression, anxiety, or any psychological support. Therefore, the concept of Mental Health Awareness and Support is not present. | Referrals and Advocacy: The CHW explicitly states, “I immediately refer to the nearest health center,” which directly matches the concept of providing referrals and navigating patients to care. This is a clear, unambiguous example of advocacy and referral, aligning strongly with the definition and example (“I identified disease symptoms and referred the person for testing.” → 0.9). | Community Empowerment Through Education: The testimonial provides health information about malaria and advises preventive measures, but it does not describe community-level change, peer education, or evidence of sustained behavior shifts. It is closer to an isolated educational message, which the concept’s exclusion criteria note. Hence only weak alignment. | Resource and Material Distribution: The testimonial focuses on recognizing malaria symptoms, giving first-aid advice (sponging, drinking water) and referring patients to a health center. It does not describe the CHW handing out supplies such as nets, medication, food, or kits, so material distribution is essentially absent. Assigned a very low score to reflect minimal to no evidence of the concept. | Monitoring and Follow-Up: The testimonial primarily describes initial assessment, immediate first-aid, and referral actions. It does not mention returning to the patient, checking progress, or other ongoing follow-up activities. Thus it only weakly aligns with the monitoring and follow-up concept. | Trust and Cultural Mediation: The testimonial primarily provides factual health education about malaria and outlines first-aid steps and referrals. It does not describe efforts to build trust, translate, or navigate cultural or linguistic barriers. Any alignment to the concept is minimal and indirect, hence a low score. | Clinical Interventions by CHWs: The CHW describes direct first-aid actions—“do the sponging to reduce temperature” and encouraging fluid intake before referral. Sponging is a hands-on clinical measure to manage fever, fitting the inclusion criterion of CHWs performing basic medical tasks. No meds are given, but the physical intervention provides a strong, though not exhaustive, alignment. | Mother and Infant Care: The testimonial centers on malaria symptoms, first-aid, referral and prevention for the general population. It does not reference pregnancy, childbirth, postpartum needs, infant feeding, or other specific mother/infant services. A fleeting mention of children being restless is not linked to maternal or infant care, so alignment with the concept is minimal. | Successful Outcomes: The testimonial describes the CHW’s typical actions (first aid, referring patients with malaria to a health center) but does not provide a concrete story showing that these actions led to a resolved case or improved health. The only relevant element is a general statement that the CHW ‘immediately refer[s] to the nearest health center,’ which offers minimal evidence of a completed referral without any documented result. According to the concept definition, successful outcomes require clear indications of problem resolution or positive change, which are absent here. Hence, the alignment is weak. | Material or Training Requests: The testimonial describes malaria symptoms and CHW actions but makes no explicit request for materials, supplies, or additional training. According to the concept definition, without an explicit ask it should score very low. | Children Served: The testimonial only briefly mentions that 'children might be restless' as a symptom, without describing any CHW action directed specifically toward minors. This is a minimal, incidental reference to children with no clear service or support provided, fitting the exclusion criteria for mere mention without CHW involvement. | Elderly Served: The testimonial discusses malaria symptoms and CHW actions but makes no reference to older adults, seniors, or any specific assistance provided to them. | Women Served: The testimonial discusses general malaria symptoms and CHW actions without any mention of women or gender-specific issues, so the concept is not present. | Men Served: The testimonial discusses malaria prevention and first aid without mentioning adult males or boys, nor any gender-specific support or challenges. Therefore, the concept “Men Served” is not present. | Families Served: The testimonial briefly references children when listing malaria symptoms, but it does not describe serving a household, parents with children, or any family-focused intervention. This provides only a minimal, indirect connection to the concept. | Parsing failed for concept 'Families Served' | Marginalized Groups Served: The testimonial discusses malaria symptoms and CHW actions but does not mention any specific marginalized or underserved groups nor does it describe providing support to such populations. | Financial Hardship: The testimonial focuses on malaria symptoms, prevention, and CHW actions. It contains no mention of costs, poverty, transportation barriers, or any material scarcity, so the Financial Hardship concept is not present. | Social Isolation: The testimonial solely discusses malaria symptoms, first aid, and referral practices; it contains no mention of loneliness, living alone, lack of support, or social neglect. | Disease Burden: The testimonial centers on malaria, noting that the infection \ | Stigma or Discrimination: The testimonial solely discusses malaria symptoms, treatment, and prevention without any reference to social rejection, shame, or discriminatory behavior. Therefore the concept of stigma or discrimination is not present. | Mental or Emotional Distress: The testimonial is almost entirely about physical symptoms, prevention, and treatment of malaria. It contains no clear expressions of depression, hopelessness, trauma, or emotional overwhelm. At most, the brief mention of children being 'restless' could hint at minor discomfort, but this is insufficient to demonstrate mental or emotional distress. Therefore, alignment with the concept is minimal. | Lack of Resources: The testimonial describes malaria symptoms and the CHW’s response (sponging, giving water, and referring to a health center) but does not mention missing medicines, supplies, or any other resource constraints. Therefore, the concept of Lack of Resources is not present. | Systemic Barriers: The testimonial mostly describes malaria symptoms and CHW first-aid actions. The only potentially relevant line is that 'many people have died from malaria due to late diagnosis,' but no specific systemic cause (e.g., facility shortage, distance, corruption) is identified. Thus evidence for systemic barriers is minimal, warranting a very low score. | Overburdened CHWs: The testimonial focuses on malaria signs, symptoms, and first-aid steps, with no statements about workload, exhaustion, or being overwhelmed. Little to no evidence of CHW overburden, so score is near zero. | Lack of Follow-Through: The testimonial outlines typical steps the CHW takes (first aid and immediate referral) but does not describe any situation where assistance was initiated and then abandoned or left unresolved, so the concept of Lack of Follow-Through is not present. | Lack of Knowledge: The CHW confidently explains malaria’s cause, symptoms, first-aid steps, and referral process, showing competence rather than uncertainty. No mention of needing more training or being unsure how to proceed. Minimal evidence of lack of knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Malaria Malaria is a bacterial infection caused by plasmodium vale that affects the blood stream of human body. It is spread through anopheles mosquito bite from one person to another. People who have malaria usually feel sick with high fever and shaking chills. Some people may experience signs in the abdomen or muscles, fatigue, fever, night sweats, shivering, nausea, diarrhea, vomiting, headache, and coldness. The physical symptoms of malaria may include vomiting, tiredness, shivering, body weakness, sweating, children might be restless. The immediate action I take as a Community Health Worker when I see the symptoms coming is to do the sponging to reduce temperature, drink a lot of water due to vomiting and diarrhea. This are the first aid you do before going to the hospital. The malaria infection may return time and again if the patient does not follow the preventive measures like sleeping under the treated mosquito nets and vector control. As a Community Health Worker, if you once identify someone suffering from malaria, I immediately refer to the nearest health center. Many people have died from malaria due to late diagnosis that might lead to anemia, enlarged spleen that leads to ????????? that have similar symptoms as malaria. Disease like typhoid, dysentery. So, if not careful, you might miss the diagnosis, so you must thoroughly and probe the client. You should be well conversant with the signs and symptoms of malaria. And thus, the slogan “ZERO MALARIA STARTS WITH ME.” ---</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.6,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.9,
+  "Water Quality, Sanitation, and Hygiene": 0.1,
+  "Personal Disease Management and Adherence": 0.8,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.8,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.9,
+  "Community Empowerment Through Education": 0.2,
+  "Resource and Material Distribution": 0.0,
+  "Monitoring and Follow-Up": 0.1,
+  "Trust and Cultural Mediation": 0.1,
+  "Clinical Interventions by CHWs": 0.7,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.2,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.3,
+  "Elderly Served": 0.0,
+  "Women Served": 0.0,
+  "Men Served": 0.0,
+  "Families Served": 0.0,
+  "Marginalized Groups Served": 0.0,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.7,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.0,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial demonstrates moderate alignment with CHW empowerment through training. The CHW shows detailed knowledge about malaria (symptoms, first aid, referral procedures) and uses professional terminology, suggesting they have received training. However, there is no explicit mention of attending workshops, receiving formal CHW training, or how they gained this knowledge. The systematic approach and medical understanding implies training but lacks direct evidence. | Parsing failed for concept 'CHW Empowerment Through Training' | Menstrual Hygiene Education and Challenges: The testimonial is entirely focused on malaria - its causes, symptoms, treatment, and prevention. There is no mention of menstruation, menstrual hygiene, sanitary products, or any related education or challenges. The content explicitly discusses a different health topic (malaria) and does not address any aspect of the menstrual hygiene concept. | Drug Abuse: Environment and Awareness: The testimonial focuses entirely on malaria - its causes, symptoms, treatment, and prevention. There is no mention of drug abuse, addiction, alcohol, substance use, or any social/environmental factors related to substance abuse. The content is purely about a mosquito-borne disease and does not align with the concept of drug abuse awareness at all. | CHW-Led Infectious Disease Management: Strong direct alignment. The testimonial clearly demonstrates CHW-led management of malaria (an infectious disease). The CHW describes educating about symptoms, prevention measures (mosquito nets, vector control), providing first aid before hospital referral, and emphasizing proper diagnosis. The narrative explicitly shows the CHW's active role in disease management, matching the concept's focus on how CHWs help communities understand and reduce disease spread. | Water Quality, Sanitation, and Hygiene: The testimonial focuses primarily on malaria symptoms, diagnosis, and treatment. The only mention related to water is 'drink a lot of water due to vomiting and diarrhea' which is about hydration for symptom management, not water quality, sanitation, or hygiene education. There is no discussion of water treatment, handwashing, or sanitation practices that would align with this concept. | Personal Disease Management and Adherence: Strong alignment with the concept. The testimonial extensively discusses malaria management, including immediate first aid actions (sponging, hydration), referral to health centers, and preventive measures (mosquito nets). While it focuses more on disease recognition and initial response rather than long-term adherence to treatment, it clearly demonstrates the CHW's role in guiding disease management, which aligns well with the concept definition. | Nutrition Education and Food Access: The testimonial focuses entirely on malaria - its causes, symptoms, treatment, and prevention. There is no mention of nutrition education, food access, healthy eating, or any food-related topics. The only tangentially related content is the mention of drinking water as first aid, but this is for medical treatment of dehydration from vomiting/diarrhea, not nutrition education or food access. | Sexual and Reproductive Health Education: The testimonial is entirely focused on malaria - its causes, symptoms, treatment, and prevention. There is no mention of family planning, STI prevention, HIV awareness, reproductive rights, or any sexual health topics. The content exclusively discusses a vector-borne disease and its management, which clearly falls outside the scope of sexual and reproductive health education. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses entirely on malaria - its causes, symptoms, treatment, and prevention. There is no mention of abuse, violence, exploitation, or any GBV-related issues. The content is purely about a medical condition and the CHW's response to it, which clearly falls outside the scope of the GBV and Child Protection concept. | Health Literacy and Misconceptions: Strong alignment due to a significant factual error: the CHW incorrectly states malaria is a 'bacterial infection' when it is actually caused by a parasite. This demonstrates a fundamental misconception about disease etiology, directly matching the inclusion criteria of 'misbeliefs about disease origins.' The rest of the testimonial shows good health knowledge, preventing a perfect 1.0 score. | Mental Health Awareness and Support: The testimonial focuses entirely on malaria as a physical disease - its causes, symptoms (fever, chills, vomiting, etc.), and medical treatment. There is no mention of psychological well-being, emotional support, or mental health aspects. The CHW discusses only physical symptoms and medical interventions, with no reference to depression, anxiety, or emotional trauma that would align with the concept. | Referrals and Advocacy: Strong direct alignment with the concept. The CHW explicitly states 'As a Community Health Worker, if you once identify someone suffering from malaria, I immediately refer to the nearest health center.' This demonstrates the CHW acting as an intermediary by identifying symptoms and making referrals, which directly matches the inclusion criteria and the first example ('I identified disease symptoms and referred the person for testing.' → 0.9). | Community Empowerment Through Education: This testimonial primarily describes malaria symptoms and treatment protocols from a clinical perspective. While the CHW demonstrates knowledge that could be shared educationally, there is no evidence of community education activities, behavior change, or empowerment. The content reads more as a medical reference than a story of community transformation through education. The closing slogan suggests potential for education but doesn't describe actual implementation or impact. | Resource and Material Distribution: The testimonial focuses entirely on malaria education, symptoms, first aid advice, and referral procedures. There is no mention of the CHW distributing any physical resources such as mosquito nets, medication, or other materials. While the CHW mentions treated mosquito nets as a preventive measure, they do not indicate distributing them. This aligns with the exclusion criteria of 'discussions of education or advice without material support.' | Monitoring and Follow-Up: The testimonial focuses on malaria education, symptoms, and immediate actions but does not describe ongoing monitoring or follow-up activities. The CHW mentions immediate referral to health centers and first aid measures, but there is no evidence of returning to check on patients, following up after diagnosis, or ongoing interactions. The content is primarily about initial response and education rather than sustained monitoring. | Trust and Cultural Mediation: This testimonial focuses primarily on clinical knowledge about malaria (symptoms, first aid, referral procedures) without mentioning trust-building, cultural barriers, or community mediation. While the CHW describes patient interactions and care delivery, there is no evidence of navigating cultural, linguistic, or social barriers, nor earning community trust. The content is purely educational and clinical, matching the exclusion criteria of 'clinical interactions without cultural or trust-related themes.' | Clinical Interventions by CHWs: The testimonial describes direct clinical interventions including 'sponging to reduce temperature' and ensuring the patient 'drink a lot of water due to vomiting and diarrhea' as first aid measures. These are hands-on medical interventions that go beyond education or referral. However, the score is not higher because these are basic first aid measures rather than more involved clinical tasks like administering medication or treating wounds, and the CHW emphasizes referral to health centers for actual treatment. | Mother and Infant Care: The testimonial focuses entirely on malaria - its causes, symptoms, and treatment. There is no mention of prenatal care, childbirth, postpartum support, infant health, or any mother/infant-specific content. The discussion is about general malaria management applicable to all populations, not specifically mothers or infants. | Successful Outcomes: The testimonial primarily describes malaria symptoms, first aid procedures, and the CHW's protocol for referrals. While it mentions referring patients to health centers, there is no indication of actual successful outcomes, recoveries, or positive changes resulting from these actions. The content is educational and procedural rather than outcome-focused. This aligns with the low-scoring example where the CHW describes their actions but cannot confirm impact. | Material or Training Requests: The testimonial provides detailed information about malaria symptoms, treatment, and the CHW's current practices, but contains no explicit requests for materials, supplies, or training. The CHW describes what they currently do (sponging, encouraging water intake, referrals) without asking for additional resources or education to improve their service. | Children Served: The testimonial mentions 'children might be restless' as one physical symptom of malaria, indicating some awareness of how the disease affects children specifically. However, there is no direct evidence of the CHW actively serving, treating, or providing care to children. The reference is minimal and only acknowledges children as a demographic that can experience malaria symptoms, without describing any actual CHW involvement with children. | Elderly Served: The testimonial focuses entirely on malaria - its causes, symptoms, and treatment. There is no mention of elderly people, seniors, or grandparents, nor any indication of providing services specifically to older adults. The content is about general malaria education and treatment applicable to all age groups. | Women Served: The testimonial discusses malaria symptoms, prevention, and treatment in general terms without any specific mention of women, girls, or gender-related health issues. There is no evidence of CHW interaction with women or addressing women-specific needs, which clearly excludes this concept. | Men Served: The testimonial focuses entirely on malaria education, symptoms, and treatment protocols. There is no mention of men, boys, or any gender-specific context. The content is gender-neutral and discusses general malaria prevention and treatment without reference to serving or supporting men specifically. | Families Served: The testimonial focuses entirely on malaria as a disease, its symptoms, transmission, and treatment protocols. There is no mention of households, parents with children, extended family units, or CHW support for multiple family members. The content is educational about malaria management rather than describing actual family-focused interventions or services provided to family units. | Marginalized Groups Served: The testimonial focuses on malaria education, symptoms, and treatment protocols without any mention of marginalized or underserved groups. The CHW describes general community health practices and medical procedures but does not reference providing support to stigmatized populations, minorities, migrants, disabled individuals, or any structurally excluded groups. The content is purely clinical and educational without addressing social exclusion or marginalization. | Financial Hardship: The testimonial focuses entirely on malaria symptoms, treatment, and prevention from a medical perspective. There is no mention of financial constraints, inability to afford care, transportation costs, or any economic barriers to healthcare access. The CHW discusses medical protocols and referrals but does not indicate any financial hardship experienced by patients or communities. | Social Isolation: The testimonial focuses entirely on malaria as a disease - its causes, symptoms, treatment, and prevention. There is no mention of loneliness, living alone, lack of support systems, or social neglect. The CHW discusses medical interventions and disease management, not social circumstances or isolation of patients. | Disease Burden: The testimonial describes malaria as a disease that 'may return time and again' and mentions that 'many people have died from malaria,' indicating its potential for recurrence and serious impact. While malaria can be episodic rather than chronic, the emphasis on repeated infections and the need for ongoing preventive measures suggests a moderate alignment with the concept of disease burden. | Stigma or Discrimination: The testimonial focuses entirely on the medical aspects of malaria - its causes, symptoms, treatment, and prevention. There is no mention of social rejection, shame, exclusion, or judgment related to having malaria. The CHW discusses clinical management and public health approaches without any reference to stigma or discrimination faced by malaria patients. | Mental or Emotional Distress: The testimonial focuses entirely on malaria as a physical disease, describing symptoms like fever, chills, vomiting, and physical weakness. While it mentions children being 'restless,' this is presented as a physical symptom of malaria rather than emotional distress. There is no mention of depression, hopelessness, trauma, stress, or any mental/emotional struggles, making this concept clearly not present in the testimonial. | Lack of Resources: The testimonial describes malaria symptoms, prevention measures, and the CHW's response protocol (first aid and referral to health centers). There is no mention of lacking medicine, tools, or support. The CHW describes actions they can and do take, without indicating any resource constraints or inability to help due to insufficient supplies. | Systemic Barriers: The testimonial focuses entirely on malaria symptoms, treatment protocols, and the CHW's direct actions in managing cases. There is no mention of systemic issues like health facility shortages, lack of resources, or institutional barriers that would prevent the CHW from helping patients. The CHW describes their ability to provide first aid and refer patients to health centers without indicating any systemic obstacles. | Parsing failed for concept 'Systemic Barriers' | Overburdened CHWs: The testimonial is an educational description of malaria symptoms, prevention, and treatment protocols. There is no mention of the CHW being exhausted, overextended, or overwhelmed. The CHW describes their professional duties and knowledge without any indication of excessive workload or being overburdened. | Lack of Follow-Through: The testimonial describes the CHW's knowledge about malaria and their standard protocol for handling cases, including immediate first aid and referral to health centers. There is no mention of starting to help someone and then abandoning the case or leaving issues unresolved. The CHW describes a complete care pathway from identification through referral, without any indication of interrupted or failed care attempts. | Lack of Knowledge: The testimonial demonstrates comprehensive knowledge about malaria, including its causes, symptoms, first aid measures, and referral procedures. The CHW shows confidence in diagnosis and treatment protocols. While there's a minor unclear word ('???????'), this appears to be a transcription issue rather than a knowledge gap. The CHW explicitly states 'You should be well conversant with the signs and symptoms' and demonstrates this knowledge throughout, making this clearly excluded from the concept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Malaria The weather in Kisumu has totally changed, there is a lot of rains and floodings experienced everywhere. This rain has also brought a lot of stagnant water which helps mosquitoes breed. During the week I took my training emphasizing on how to use nets to help in preventing the spread of malaria. I also came across one of my participants who was having malaria but was just using over-the-counter drugs. I referred the person to Thoamogi Oginga Teaching and Referral Hospital for the malaria test which later turned positive and he was treated and given prescriptions of the medicines. As a CHW, I am very happy that the person is responding well to medications. ---</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.9,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.9,
+  "Water Quality, Sanitation, and Hygiene": 0.1,
+  "Personal Disease Management and Adherence": 0.9,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.35,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 1.0,
+  "Community Empowerment Through Education": 0.3,
+  "Resource and Material Distribution": 0.2,
+  "Monitoring and Follow-Up": 0.8,
+  "Trust and Cultural Mediation": 0.2,
+  "Clinical Interventions by CHWs": 0.1,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.9,
+  "Material or Training Requests": 0.1,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.0,
+  "Men Served": 0.8,
+  "Families Served": 0.0,
+  "Marginalized Groups Served": 0.1,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.4,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.0,
+  "Lack of Resources": 0.05,
+  "Systemic Barriers": 0.2,
+  "Overburdened CHWs": 0.05,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.1
+}</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The CHW explicitly states, “During the week I took my training emphasizing on how to use nets to help in preventing the spread of malaria.” This is a clear mention of receiving CHW-specific training that enhances their ability to serve, matching the concept’s inclusion criteria. No conflicting exclusions are present. | Menstrual Hygiene Education and Challenges: The testimonial focuses solely on malaria prevention and treatment with no mention of menstruation, menstrual products, or related education or stigma. | Drug Abuse: Environment and Awareness: The testimonial focuses on malaria prevention and treatment with no mention of substance abuse, addiction, or related social/environmental factors; therefore, the concept is not applicable. | CHW-Led Infectious Disease Management: The CHW describes educating participants on malaria prevention (use of nets) and referring an infected individual for testing and treatment, directly aligning with CHW-led outreach, education, and follow-up for an infectious disease. This is a clear, unambiguous example matching the concept’s definition and inclusion criteria. | Water Quality, Sanitation, and Hygiene: The testimonial briefly mentions stagnant water created by flooding, but the focus is on malaria prevention (mosquito nets, referrals). There is no discussion of clean water, sanitation practices, or hygiene education as defined by the concept, so alignment is minimal. | Personal Disease Management and Adherence: The CHW recounts identifying a participant self-medicating for malaria, facilitating proper diagnostic testing, and ensuring they receive prescribed treatment, noting that the person is now responding well. This directly reflects guidance leading to formal diagnosis, treatment initiation, and adherence—core elements of the concept. | Nutrition Education and Food Access: The testimonial only discusses malaria prevention and treatment; it does not mention food, nutrition education, or access to adequate nutrition. | Sexual and Reproductive Health Education: The testimonial discusses malaria prevention (use of nets), diagnosis, and treatment. It contains no mention of family planning, condoms, STI/HIV prevention, or reproductive rights. Therefore, the concept of Sexual and Reproductive Health Education is not present. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses solely on malaria prevention and treatment with no mention of abuse, exploitation, violence, or child protection issues, which are required for this concept. | Health Literacy and Misconceptions: There is a hint of limited health literacy: the participant self-medicated with over-the-counter drugs instead of seeking a test and proper treatment, implying incomplete understanding of correct malaria management. However, no explicit misinformation or stated false beliefs are described, so alignment with the concept is weak-to-moderate rather than strong. | Mental Health Awareness and Support: The testimonial focuses solely on malaria prevention and treatment with no reference to emotional well-being, depression, anxiety, or any kind of psychological support, which are required for this concept. | Referrals and Advocacy: The CHW explicitly states, “I referred the person to Thoamogi Oginga Teaching and Referral Hospital for the malaria test,” which perfectly matches the concept’s definition of acting as an intermediary and making referrals within the health system. This is a clear, unambiguous example of referrals and advocacy. | Community Empowerment Through Education: The CHW mentions giving a training on bed-net use, but the testimonial does not describe any sustained community-level behavior change or peer education that followed. It is essentially a single educational intervention and an individual referral for treatment, which fits the exclusion criteria of isolated education without demonstrated long-term impact. | Resource and Material Distribution: The CHW provided training on how to use mosquito nets and referred a patient to the hospital, but there is no clear statement that nets, medicine, or any other materials were actually distributed. This gives only weak alignment with the concept, which requires provision of tangible supplies. | Monitoring and Follow-Up: The CHW not only referred the participant for testing but later notes that the test was positive and that the person 'is responding well to medications.' This indicates the CHW obtained follow-up information on the patient’s progress, fitting the definition of ongoing interaction/checking progress. It is not merely a one-time visit, so it aligns strongly, though the exact nature of the follow-up is not extensively detailed. | Trust and Cultural Mediation: The CHW persuades a participant who was self-medicating to go to a hospital for proper testing and treatment, suggesting some implicit trust-building. However, there is no explicit mention of overcoming cultural, linguistic, or social barriers, nor of translating or mediating practices. Therefore, alignment with the concept is weak. | Clinical Interventions by CHWs: The CHW mainly conducted health education on bed-net use and referred a person with suspected malaria to the hospital. No direct clinical actions such as giving medicine or treating wounds were performed by the CHW, and referrals alone are excluded, so only minimal alignment exists. | Mother and Infant Care: The testimonial focuses solely on malaria prevention and referral for treatment; it contains no mention of pregnancy, childbirth, postpartum issues, or infant care, which are required for the Mother and Infant Care concept. | Successful Outcomes: Testimonial describes CHW identifying a malaria case, referring to hospital where diagnosis was confirmed and treatment given; CHW notes the patient is \ | Material or Training Requests: The testimonial mentions that the CHW recently took training on net use, but there is no explicit request for additional materials or further training. Therefore, only a very weak alignment is present. | Children Served: The testimonial discusses malaria prevention and a referral for an adult participant, with no mention of minors or services directed toward children, so the concept is not present. | Elderly Served: The testimonial talks about malaria prevention and treatment for an unspecified participant; it contains no mention of older adults or seniors, nor any indication that the assistance was directed toward them. | Women Served: The testimonial discusses malaria prevention and treatment but never mentions women or gender-specific issues. Therefore, the concept 'Women Served' is not present. | Men Served: The CHW identifies a male participant ('he') who was self-treating malaria and directly supports him by referring him to the hospital, aligning with the concept’s inclusion of providing health support to men. Although only one man is mentioned, the assistance is clear and gender-specific, warranting a strong (but not perfect) score. | Families Served: The testimonial only describes assisting a single participant with malaria treatment; there is no mention of households, parents with children, or any family unit. Therefore, the concept of 'Families Served' is not present. | Parsing failed for concept 'Families Served' | Marginalized Groups Served: The testimonial describes malaria prevention and referral for a community member but does not indicate the person belongs to a structurally excluded or stigmatized group. Similar to the example of simply speaking with people in the community, there is minimal evidence of serving a marginalized population. | Financial Hardship: The testimonial discusses malaria prevention and treatment but does not mention any inability to afford transportation, food, or medical care, nor any statement of poverty or material scarcity. | Social Isolation: The testimonial discusses malaria prevention and treatment, with no mention of the participant living alone, lacking support, or experiencing loneliness. Therefore, it does not align with the Social Isolation concept. | Disease Burden: Malaria is mentioned, and the CHW deals with a client who tests positive and is treated, indicating illness in the community. However, the testimonial focuses on a single acute episode rather than a chronic or recurrent condition. Thus, evidence of sustained or long-term disease burden is limited, giving a weak-to-moderate alignment. | Stigma or Discrimination: The testimonial discusses malaria prevention, referral, and treatment without any mention of social rejection, judgment, shame, or exclusion related to the condition. Therefore, stigma or discrimination is not present. | Mental or Emotional Distress: The testimonial focuses on physical illness (malaria) and treatment; it contains no expressions of depression, stress, hopelessness, or other emotional strain. Therefore, the concept is not present. | Lack of Resources: The testimonial describes providing education on bed-net use and successfully referring a malaria case to a hospital; it does not mention insufficient supplies, medicines, or other resource shortages for the CHW. Thus alignment with 'Lack of Resources' is minimal. | Systemic Barriers: The testimonial mentions environmental conditions (heavy rains, stagnant water) that increase malaria risk—factors outside the CHW’s control—so there is a weak indication of systemic-level issues. However, there is no mention of health-system shortages, corruption, overcrowding, or other institutional barriers that directly impeded the CHW’s work. Therefore only minimal evidence of systemic barriers is present. | Overburdened CHWs: The testimonial focuses on malaria prevention activities and a successful referral. It does not mention workload, exhaustion, or an imbalance between CHWs and patient needs. Thus, evidence for overburdened CHWs is virtually absent. | Lack of Follow-Through: The CHW identified the issue, referred the participant for proper testing, and confirmed that the person is now responding well to treatment—indicating complete follow-through. No evidence of abandonment or unresolved care. | Lack of Knowledge: The CHW states they completed training on mosquito net use, but there is no indication they previously lacked knowledge or were unsure how to proceed. They successfully identified malaria risk and made an appropriate referral. Mentioning training alone does not demonstrate a knowledge gap, so only minimal alignment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Malaria The weather in Kisumu has totally changed, there is a lot of rains and floodings experienced everywhere. This rain has also brought a lot of stagnant water which helps mosquitoes breed. During the week I took my training emphasizing on how to use nets to help in preventing the spread of malaria. I also came across one of my participants who was having malaria but was just using over-the-counter drugs. I referred the person to Thoamogi Oginga Teaching and Referral Hospital for the malaria test which later turned positive and he was treated and given prescriptions of the medicines. As a CHW, I am very happy that the person is responding well to medications. ---</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.8,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.85,
+  "Water Quality, Sanitation, and Hygiene": 0.1,
+  "Personal Disease Management and Adherence": 0.8,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.3,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.9,
+  "Community Empowerment Through Education": 0.5,
+  "Resource and Material Distribution": 0.1,
+  "Monitoring and Follow-Up": 0.7,
+  "Trust and Cultural Mediation": 0.2,
+  "Clinical Interventions by CHWs": 0.1,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.9,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.0,
+  "Men Served": 0.8,
+  "Families Served": 0.0,
+  "Marginalized Groups Served": 0.1,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.5,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.0,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial shows strong alignment with CHW empowerment through training. The CHW explicitly mentions 'I took my training' and demonstrates applying that training by 'emphasizing on how to use nets to help in preventing the spread of malaria.' This shows both receiving training and using it to increase their capacity to serve the community. The score is 0.8 rather than higher because while training is clearly mentioned and applied, there's no detail about the specific training program or knowledge gained. | Menstrual Hygiene Education and Challenges: The testimonial focuses entirely on malaria prevention and treatment, including mosquito net usage and referring a patient for malaria testing. There is no mention of menstruation, menstrual hygiene, products, or related education, making this concept clearly not present. | Drug Abuse: Environment and Awareness: The testimonial focuses entirely on malaria prevention and treatment in the context of environmental factors (flooding, stagnant water). While it mentions 'over-the-counter drugs,' this refers to inappropriate self-medication for malaria, not substance abuse or addiction. There is no mention of alcohol abuse, peer influence, or drug education related to substance abuse, which are the core elements of this concept. | CHW-Led Infectious Disease Management: Strong alignment with the concept. The CHW actively manages malaria (an infectious disease) through multiple interventions: conducting training on prevention methods (mosquito nets), identifying a community member with malaria symptoms, making a referral for proper testing and treatment, and following up on the patient's recovery. This demonstrates comprehensive CHW-led disease management including education, case identification, and care coordination. | Water Quality, Sanitation, and Hygiene: The testimonial mentions stagnant water only in the context of mosquito breeding for malaria transmission, not for water quality, sanitation, or hygiene purposes. There is no discussion of water treatment, handwashing, or sanitation practices. The focus is entirely on malaria prevention through bed nets and medical treatment. | Personal Disease Management and Adherence: Strong alignment with the concept. The testimonial describes a CHW who identified a participant self-medicating for malaria with over-the-counter drugs, referred them for proper testing and diagnosis, and ensured they received appropriate treatment. The person is now 'responding well to medications,' indicating successful disease management through proper diagnosis and treatment adherence. This closely matches the concept's focus on managing infectious diseases through CHW guidance. | Nutrition Education and Food Access: The testimonial focuses entirely on malaria prevention and treatment, with no mention of nutrition education, food access, healthy eating, or any food-related topics. The content explicitly deals with mosquito nets, malaria testing, and medical treatment, which falls outside the scope of the nutrition concept. | Sexual and Reproductive Health Education: The testimonial focuses entirely on malaria prevention and treatment, including mosquito net usage and referring a patient for malaria testing. There is no mention of family planning, STI prevention, HIV awareness, reproductive rights, or any sexual health topics. This clearly falls outside the concept's inclusion criteria. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses entirely on malaria prevention and treatment, with no mention of violence, abuse, exploitation, or child protection issues. The CHW discusses weather conditions, mosquito breeding, malaria testing, and medical treatment - none of which relate to GBV or child protection concerns. | Health Literacy and Misconceptions: The testimonial shows weak alignment with health literacy issues. While the participant was self-medicating with over-the-counter drugs instead of seeking proper testing and treatment for malaria, this represents a mild form of inadequate health knowledge rather than explicit misinformation or misconceptions about disease origins. The CHW corrected this behavior through referral, but there's no evidence of deeper misbeliefs or mistrust in medicine. | Mental Health Awareness and Support: The testimonial focuses entirely on malaria prevention and treatment, with no mention of psychological well-being, emotional support, or mental health issues. The CHW discusses weather conditions, mosquito breeding, malaria testing, and medical treatment - all physical health concerns without any mental or emotional context. | Referrals and Advocacy: Strong direct alignment with the concept. The CHW explicitly states 'I referred the person to Thoamogi Oginga Teaching and Referral Hospital for the malaria test' which directly matches the inclusion criteria of helping with referrals and navigating healthcare. This aligns with the example 'I identified disease symptoms and referred the person for testing' which scores 0.9. | Community Empowerment Through Education: The testimonial shows moderate alignment. The CHW conducted training on malaria prevention through net usage, which is educational outreach. However, there's no evidence of lasting behavior change, community-wide adoption, or self-reliance. The focus shifts to a single referral case rather than demonstrating how the education led to community empowerment or sustained preventive practices. | Parsing failed for concept 'Community Empowerment Through Education' | Resource and Material Distribution: The testimonial focuses on malaria prevention education and referral services. While the CHW mentions training on 'how to use nets,' there is no indication they actually distributed nets or any other materials. The CHW referred a patient to a hospital where the patient received prescriptions, but the CHW themselves did not provide any physical resources. This aligns with the exclusion criteria of 'education or advice without material support.' | Monitoring and Follow-Up: The testimonial shows moderate alignment with monitoring and follow-up. The CHW states 'I am very happy that the person is responding well to medications,' which indicates they have checked on the patient's progress after the referral and treatment. However, the testimonial doesn't explicitly describe return visits or systematic follow-up activities, making it less clear than a perfect match would require. | Trust and Cultural Mediation: The testimonial shows minimal evidence of trust-building or cultural mediation. While the CHW successfully referred a participant to the hospital and the person accepted the referral, there's no explicit mention of overcoming trust barriers, cultural concerns, or linguistic challenges. The interaction appears primarily clinical without cultural or trust-related themes emphasized in the concept definition. | Clinical Interventions by CHWs: The CHW provided health education about malaria prevention and made a referral to the hospital for testing and treatment. While the testimonial mentions over-the-counter drugs and eventual treatment, the CHW did not directly administer medication or perform any clinical tasks - they only referred the patient to the hospital where medical professionals provided the actual clinical care. This aligns with the exclusion criteria of 'referrals without direct clinical interaction.' | Mother and Infant Care: The testimonial focuses entirely on malaria prevention and treatment, with no mention of prenatal care, childbirth, postpartum support, infant health, or any mother/infant-specific services. The CHW discusses mosquito nets, malaria testing, and treatment for a general participant, not specifically mothers or infants. | Successful Outcomes: Strong direct alignment with successful outcomes. The testimonial clearly describes a CHW referring a malaria patient to a hospital, where they received proper testing, treatment, and prescriptions. The CHW explicitly states the patient 'is responding well to medications,' indicating a positive health outcome directly attributed to the CHW's intervention. This closely matches the 0.9 example of escorting someone to the hospital who then recovered. | Material or Training Requests: The testimonial describes CHW activities including training delivery and patient referral for malaria, but contains no requests for materials, supplies, or additional training. The CHW discusses conducting training and making a successful referral without expressing any needs or making any requests for resources. | Children Served: The testimonial describes malaria prevention training and helping a participant with malaria, but contains no mention of children or minors under 18. The participant is referred to as 'person' and 'he' without any indication of age or that they were a child. The focus is on general community health education about malaria prevention through mosquito nets. | Elderly Served: The testimonial describes malaria prevention education and helping a participant with malaria treatment, but contains no mention of elderly individuals, seniors, or grandparents. The participant's age is not specified, and there are no indicators suggesting they were an older adult. The concept clearly requires serving elderly/senior populations, which is not present in this testimonial. | Women Served: The testimonial describes a participant with malaria who was referred for testing and treatment, but uses 'he' to refer to this person, indicating the participant was male. There is no mention of women, girls, or any gendered roles or challenges being addressed by the CHW in this case. | Men Served: The testimonial describes a CHW who referred a participant with malaria to a hospital, where 'he was treated and given prescriptions.' The use of the pronoun 'he' indicates the participant was male, and the CHW provided direct health support by identifying the need for proper testing and facilitating access to appropriate medical care. This aligns strongly with the concept's inclusion criteria of 'support for men or boys, especially regarding health.' | Families Served: The testimonial describes helping an individual participant with malaria, with no mention of family members, household context, or family-focused interventions. The CHW refers to 'the person' and 'he' throughout, clearly indicating individual-level support rather than family-based care. | Marginalized Groups Served: The testimonial describes malaria prevention education and helping someone access proper medical care, but there is no indication that the person or community served faces structural or social exclusion. The focus is on general public health issues (malaria) affecting the broader community due to weather conditions, without reference to marginalized or stigmatized groups. | Financial Hardship: The testimonial focuses on malaria prevention and treatment but contains no evidence of financial hardship. While the patient was using over-the-counter drugs before referral, there's no indication this was due to inability to afford proper care rather than lack of awareness. The successful referral and treatment suggest no financial barriers prevented access to healthcare. | Social Isolation: The testimonial focuses entirely on malaria prevention and treatment in the context of weather changes and flooding. There is no mention of the patient living alone, lacking support systems, experiencing loneliness, or being socially neglected. The CHW describes a medical intervention for malaria, not addressing any social isolation issues. | Disease Burden: The testimonial describes a malaria case, which is an acute infectious disease rather than a chronic illness or disability. While malaria can be recurrent in endemic areas, this specific case appears to be a single episode that was successfully treated. The person responded well to medication, suggesting this was not a long-term or debilitating condition. This aligns with the moderate scoring range as it involves illness but lacks evidence of chronicity or recurring episodes. | Stigma or Discrimination: The testimonial focuses on malaria prevention, treatment, and environmental factors affecting mosquito breeding. There is no mention of social rejection, shame, exclusion, or judgment related to the health condition or any other factor. The CHW describes a straightforward medical referral and treatment process without any indication of stigma or discrimination. | Mental or Emotional Distress: The testimonial focuses entirely on malaria prevention and treatment, with no mention of mental or emotional distress. The CHW describes environmental conditions, disease prevention education, and medical referral for a physical illness (malaria). There are no expressions of depression, hopelessness, trauma, stress, or any emotional overwhelm mentioned in the testimonial. | Lack of Resources: The testimonial does not indicate any lack of resources. The CHW successfully conducted training on malaria prevention, identified a case, and was able to refer the patient to a hospital where they received testing and treatment. There is no mention of insufficient supplies, medicine, or capacity limitations that prevented the CHW from addressing the problem. | Systemic Barriers: The testimonial does not mention any systemic barriers. While it discusses environmental conditions (flooding, stagnant water) that contribute to malaria spread, the CHW successfully provides education, makes a referral, and the patient receives proper testing and treatment at the hospital. The healthcare system appears to be functioning well in this case, with no mention of facility shortages, overcrowding, or other institutional obstacles preventing care. | Overburdened CHWs: The testimonial shows no evidence of the CHW being overburdened. The CHW describes conducting training, encountering a patient with malaria, making a successful referral, and expressing happiness about the patient's recovery. There is no mention of exhaustion, being overwhelmed, or having too many patients to manage. The CHW appears to be functioning effectively within their capacity. | Lack of Follow-Through: The testimonial describes a complete care cycle where the CHW identified a patient with malaria, referred them to a hospital, the patient received testing and treatment, and is now responding well to medications. This represents successful follow-through rather than abandonment or unresolved issues. | Lack of Knowledge: The CHW demonstrates competent knowledge throughout the testimonial. They understand the connection between weather conditions and malaria transmission, effectively conduct training on prevention methods, recognize when a participant needs proper medical testing rather than self-medication, and appropriately refer the patient to a hospital. There is no mention of uncertainty, need for additional training, or inability to address the situation due to knowledge gaps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Malaria This story is all about my personal experience with malaria in the past and also sharing on what I have been doing to help people to not get malaria. My first diagnosis on malaria was in four years back. I fell sick and could not know what I was suffering from. My body was very weak, mostly my body joints. My heart was almost bursting. My body temperature was very high. I was sweating a lot and during morning hours I was feeling a lot of cold which made me to sit outside my room to find heat from the sun. It was unbearable. This time I was not a trained Community Health Worker, so I had no information about malaria. The only treatment I was able to go for was only pain killers which I was buying through over-the-counter. And this was ?????? blood sample was taken to the lab, here is where I got myself diagnosed the malaria. I was treated and got better within two weeks and a half. By all this time, I was not sleeping under the net so the mosquitos were enjoying sucking my blood. Now that I am a trained Community Health Worker, I have been training my community members on how they can prevent contacting malaria. In my training, I share with them on the importance of sleeping under treated mosquito nets, clearing of bushy surroundings, draining stagnant waters, and also keeping the surroundings clean so as keep away mosquitoes from breeding. ---</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.95,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.9,
+  "Water Quality, Sanitation, and Hygiene": 0.6,
+  "Personal Disease Management and Adherence": 0.8,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.75,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.1,
+  "Community Empowerment Through Education": 0.4,
+  "Resource and Material Distribution": 0.15,
+  "Monitoring and Follow-Up": 0.1,
+  "Trust and Cultural Mediation": 0.2,
+  "Clinical Interventions by CHWs": 0.05,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.3,
+  "Material or Training Requests": 0.05,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.0,
+  "Men Served": 0.0,
+  "Families Served": 0.1,
+  "Marginalized Groups Served": 0.1,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.2,
+  "Stigma or Discrimination": 0.05,
+  "Mental or Emotional Distress": 0.05,
+  "Lack of Resources": 0.05,
+  "Systemic Barriers": 0.05,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.8
+}</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial explicitly states: “Now that I am a trained Community Health Worker…,” indicating the speaker has undergone CHW‐specific training which now enables them to teach the community about malaria prevention. This is a clear, direct instance of CHW empowerment through training, matching the inclusion criteria perfectly. | Menstrual Hygiene Education and Challenges: The testimonial focuses exclusively on malaria experiences and prevention methods (mosquito nets, environmental cleanliness). It does not mention menstruation, menstrual products, or related education, so the concept is not present. | Drug Abuse: Environment and Awareness: The testimonial focuses solely on malaria experiences and prevention with no mention of substance abuse, addiction, or related social/environmental factors. | CHW-Led Infectious Disease Management: The speaker explicitly states that, as a trained Community Health Worker, they now train community members on malaria prevention—explaining the importance of mosquito nets, clearing bushes, draining stagnant water, etc. This is a clear, direct example of a CHW educating the community to reduce the spread of an infectious disease, fitting the inclusion criteria. No conflicting information is present, so alignment is strong (0.9). | Water Quality, Sanitation, and Hygiene: The CHW describes educating the community to drain stagnant water and keep surroundings clean—actions that fall under environmental sanitation/hygiene practices aimed at disease prevention. While the testimonial is centered on malaria rather than hand-washing or drinking-water treatment, it still contains clear, though partial, alignment with the sanitation aspect of the concept. | Personal Disease Management and Adherence: The testimonial recounts the speaker’s own malaria diagnosis, treatment, and recovery, as well as subsequent prevention guidance given to others. This clearly involves disease management (diagnosis, treatment, preventive lifestyle adjustments), matching the concept definition, though it mentions adherence only briefly, so a strong but not perfect score is appropriate. | Nutrition Education and Food Access: The testimonial discusses malaria experiences and prevention strategies (mosquito nets, clearing bushes, draining stagnant water) without any mention of healthy eating, food insecurity, or nutrition education. Therefore, the concept does not apply. | Sexual and Reproductive Health Education: The testimonial focuses solely on malaria prevention (mosquito nets, environmental cleanliness) and contains no mention of family planning, STIs, HIV, condoms, or any other sexual or reproductive health education topics. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses solely on malaria illness and preventive measures. It contains no references to abuse, exploitation, violence, or child protection issues, which are required for the GBV and Child Protection concept. | Health Literacy and Misconceptions: The narrator explicitly says they \ | Mental Health Awareness and Support: The testimonial discusses physical illness (malaria) and preventive measures but provides no mention of psychological well-being, depression, anxiety, or emotional support. Therefore, the mental health concept is not present. | Referrals and Advocacy: The testimonial focuses on providing health education about malaria prevention (e.g., using bed nets, clearing bushes). It does not describe helping anyone navigate the health system, making appointments, or referring individuals for care. Thus there is only very weak, indirect alignment with the ‘Referrals and Advocacy’ concept. | Community Empowerment Through Education: The CHW describes giving ongoing trainings to community members on malaria prevention (education component), but the testimonial does not mention evidence of lasting community behavior change, peer education, or self-initiated group action. Thus it shows weak-to-moderate alignment—education is present, but empowerment outcomes are uncertain. | Resource and Material Distribution: The CHW describes educating community members about malaria prevention (e.g., sleeping under treated nets) but never states that she actually distributed mosquito nets or other physical supplies. According to the concept, education without material support is excluded, so only a minimal, indirect connection exists. | Monitoring and Follow-Up: The testimonial discusses providing preventive education on malaria but does not describe returning to individuals to check progress or ongoing follow-up after illness. It fits the exclusion of one-time education sessions, so evidence for monitoring and follow-up is minimal. | Trust and Cultural Mediation: The CHW describes educating community members on malaria prevention, which implies some level of information sharing, but there is no explicit mention of building trust, translating, or overcoming cultural or linguistic barriers. This provides only weak evidence for the concept. | Clinical Interventions by CHWs: The testimonial describes the CHW providing malaria prevention education (nets, clearing bushes, draining water) but does not mention administering medication, bandaging, or any direct clinical care to others. Education without direct clinical interaction is explicitly excluded, so alignment with the concept is minimal. | Mother and Infant Care: The testimonial focuses solely on malaria prevention and personal experience; it does not mention pregnancy, childbirth, postpartum issues, infant feeding, or any other mother/infant care topics. | Successful Outcomes: The narrator reports having recovered from malaria after receiving treatment, which represents a positive health outcome, but this occurred before they became a CHW. The later description of training community members does not include evidence of resulting improvements. Because positive change is mentioned but not clearly tied to CHW efforts or community impact, the alignment with the Successful Outcomes concept is weak. | Material or Training Requests: The testimonial describes the CHW’s past experience with malaria and the education they now provide to the community, but it does not include any explicit request for additional materials, supplies, or training. Therefore, alignment with the concept is minimal. | Children Served: The testimonial discusses malaria prevention efforts directed at community members in general without any explicit mention of children or adolescents. Therefore, the concept of 'Children Served' is not present. | Elderly Served: The testimonial focuses on malaria prevention efforts and does not mention older adults or any assistance specifically directed toward seniors. | Women Served: The testimonial discusses malaria prevention training for community members in general without any mention of women or gender-specific issues. Therefore, the concept is not present. | Men Served: The testimonial discusses malaria prevention efforts and personal experience, but it never references men or boys specifically, nor any gender-specific challenges or support. Therefore, the concept is not present. | Families Served: The testimonial describes providing malaria prevention education to \ | Marginalized Groups Served: The testimonial describes providing malaria prevention education to general community members but does not specify that these individuals are from structurally excluded or stigmatized groups. According to the concept’s exclusion criteria, generic community references without mention of marginalization warrant only minimal alignment. | Financial Hardship: The testimonial focuses on the author’s malaria experience and subsequent preventive education as a CHW. It contains no explicit mention of inability to afford care, lack of income, or other material scarcity. Therefore, the Financial Hardship concept does not apply. | Social Isolation: The testimonial focuses on the author’s experience with malaria and subsequent community education efforts. There is no mention of living alone, loneliness, abandonment, or lack of social support. Therefore, the concept of Social Isolation is not present. | Disease Burden: The testimonial describes an acute episode of malaria that resolved after treatment; it does not mention chronic, recurrent, or long-term illness. This aligns only weakly with the concept of Disease Burden, which focuses on chronic or frequent conditions. | Stigma or Discrimination: The testimonial focuses on personal illness with malaria and subsequent health education efforts; it contains no references to social judgment, shame, or exclusion related to the illness. Thus, evidence for stigma or discrimination is essentially absent. | Mental or Emotional Distress: The testimonial focuses on physical symptoms and malaria prevention. No explicit feelings of depression, hopelessness, or emotional overwhelm are described; physical complaints are specifically listed as exclusions for this concept. Thus, only negligible evidence of mental or emotional distress is present. | Lack of Resources: The testimonial focuses on personal experience with malaria and how, as a CHW, the speaker now educates others on prevention. It does not mention shortages of medicine, supplies, or other resources in their current CHW role. Only a past reliance on over-the-counter painkillers is noted, but this precedes their CHW work and is not framed as a CHW resource gap. Therefore, evidence for ‘Lack of Resources’ is minimal. | Systemic Barriers: Testimonial focuses on personal illness experience and later preventive education as a CHW. It does not describe larger institutional shortages, corruption, or external conditions preventing care; therefore systemic barriers are essentially absent, warranting a near-zero score. | Overburdened CHWs: The testimonial discusses the speaker’s personal malaria experience and their educational activities as a CHW, but it contains no mention of excessive workload, exhaustion, or feeling overwhelmed. Therefore, the concept of overburdened CHWs is not present. | Lack of Follow-Through: The testimonial describes the speaker’s past experience with malaria and their current activities training community members on prevention. There is no mention of beginning assistance and then abandoning it or leaving an issue unresolved, which is required for the 'Lack of Follow-Through' concept. | Lack of Knowledge: The narrator recounts that, prior to being trained as a CHW, they 'had no information about malaria' and could only resort to over-the-counter painkillers. This demonstrates an inability to address the illness due to insufficient knowledge, directly matching the concept definition. Because the lack of knowledge is clear and explicitly stated—though it refers to a time before formal CHW training rather than current practice—the alignment is strong but not perfectly unambiguous, warranting a score of about 0.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Malaria This story is all about my personal experience with malaria in the past and also sharing on what I have been doing to help people to not get malaria. My first diagnosis on malaria was in four years back. I fell sick and could not know what I was suffering from. My body was very weak, mostly my body joints. My heart was almost bursting. My body temperature was very high. I was sweating a lot and during morning hours I was feeling a lot of cold which made me to sit outside my room to find heat from the sun. It was unbearable. This time I was not a trained Community Health Worker, so I had no information about malaria. The only treatment I was able to go for was only pain killers which I was buying through over-the-counter. And this was ?????? blood sample was taken to the lab, here is where I got myself diagnosed the malaria. I was treated and got better within two weeks and a half. By all this time, I was not sleeping under the net so the mosquitos were enjoying sucking my blood. Now that I am a trained Community Health Worker, I have been training my community members on how they can prevent contacting malaria. In my training, I share with them on the importance of sleeping under treated mosquito nets, clearing of bushy surroundings, draining stagnant waters, and also keeping the surroundings clean so as keep away mosquitoes from breeding. ---</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.85,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.85,
+  "Water Quality, Sanitation, and Hygiene": 0.3,
+  "Personal Disease Management and Adherence": 0.8,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.7,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.0,
+  "Community Empowerment Through Education": 0.7,
+  "Resource and Material Distribution": 0.0,
+  "Monitoring and Follow-Up": 0.1,
+  "Trust and Cultural Mediation": 0.2,
+  "Clinical Interventions by CHWs": 0.0,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.6,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.0,
+  "Men Served": 0.0,
+  "Families Served": 0.1,
+  "Marginalized Groups Served": 0.0,
+  "Financial Hardship": 0.2,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.3,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.1,
+  "Lack of Resources": 0.1,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.8
+}</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: Strong direct alignment. The testimonial explicitly states 'Now that I am a trained Community Health Worker' and describes how the CHW is now 'training my community members on how they can prevent contacting malaria.' This shows a clear transformation from having 'no information about malaria' before training to actively educating others about prevention methods after becoming a trained CHW. The score is not 1.0 because the testimonial doesn't detail the specific training received, but the empowerment through training is clearly demonstrated. | Parsing failed for concept 'CHW Empowerment Through Training' | Menstrual Hygiene Education and Challenges: The testimonial is entirely focused on malaria - personal experience with the disease, symptoms, diagnosis, treatment, and prevention education. There is no mention of menstruation, menstrual hygiene, products, or any related topics. The content explicitly excludes the concept as it deals with mosquito-borne disease prevention rather than menstrual health. | Drug Abuse: Environment and Awareness: This testimonial focuses entirely on malaria prevention and the CHW's personal experience with the disease. There is no mention of substance abuse, addiction, alcohol, drugs, or any related social/environmental factors. The testimonial discusses mosquito nets, clearing bushes, and draining stagnant water - all malaria prevention strategies with no connection to drug abuse. | CHW-Led Infectious Disease Management: Strong alignment with the concept. The testimonial clearly describes the CHW's role in educating community members about malaria prevention, including specific measures like using mosquito nets, clearing bushes, draining stagnant water, and maintaining clean surroundings. The CHW explicitly states they are 'training my community members on how they can prevent contacting malaria,' which directly matches the concept's focus on CHWs helping communities understand and reduce the spread of infectious diseases through education. | Water Quality, Sanitation, and Hygiene: The testimonial mentions 'draining stagnant waters' and 'keeping the surroundings clean' as malaria prevention measures, which have some connection to sanitation practices. However, these are primarily focused on mosquito control rather than water quality or hygiene education for disease prevention. There is no discussion of water treatment, handwashing, or sanitation practices as defined in the concept. | Personal Disease Management and Adherence: Strong alignment with the concept. The testimonial describes personal experience with malaria diagnosis and treatment, including adherence to prescribed treatment that led to recovery within 2.5 weeks. It also shows how the CHW now guides others in disease prevention and management. The score is not higher because while it covers diagnosis and treatment, it doesn't emphasize ongoing medication adherence or chronic disease management as strongly as the concept examples suggest. | Nutrition Education and Food Access: The testimonial is entirely focused on malaria prevention and treatment, with no mention of nutrition, food access, healthy eating, or any food-related topics. The CHW discusses mosquito nets, clearing bushes, and draining water - all malaria prevention strategies unrelated to nutrition education or food access. | Sexual and Reproductive Health Education: The testimonial is entirely focused on malaria prevention and the CHW's personal experience with the disease. There is no mention of family planning, STI prevention, HIV awareness, reproductive rights, or any sexual health topics. The content exclusively discusses mosquito nets, environmental cleanliness, and malaria symptoms/treatment, which clearly falls outside the scope of sexual and reproductive health education. | Gender-Based Violence (GBV) and Child Protection: This testimonial focuses entirely on the CHW's personal experience with malaria and their subsequent work in malaria prevention education. There is no mention of abuse, violence, exploitation, or any form of GBV or child protection issues. The story discusses physical illness, medical treatment, and preventive health measures related to malaria, which clearly falls outside the scope of this concept. | Health Literacy and Misconceptions: The testimonial demonstrates moderate alignment with health literacy issues. The CHW explicitly states they 'had no information about malaria' when they fell ill, leading to inappropriate self-treatment with only painkillers instead of proper diagnosis and treatment. This lack of knowledge directly affected their health decisions and prolonged their suffering. The narrative shows a clear transformation from someone with limited health literacy to an educated CHW who now teaches prevention methods, highlighting the impact of health education. | Parsing failed for concept 'Health Literacy and Misconceptions' | Mental Health Awareness and Support: This testimonial focuses entirely on the physical symptoms and prevention of malaria. While the CHW describes physical suffering (weakness, high temperature, joint pain), there is no mention of psychological well-being, emotional support, or mental health aspects. The narrative is purely about a medical condition and its physical manifestations, which falls under the exclusion criteria of 'medical diagnoses without a mental/emotional context.' | Referrals and Advocacy: The testimonial describes the CHW's personal malaria experience and their current role in educating community members about malaria prevention. While they mention being a trained CHW who provides health education, there is no mention of helping with referrals, appointments, or navigating healthcare systems. The focus is entirely on preventive education rather than advocacy or intermediary activities. | Community Empowerment Through Education: The testimonial shows moderate alignment with community empowerment through education. The CHW describes actively training community members on malaria prevention methods (sleeping under nets, clearing bushes, draining water, keeping surroundings clean), which demonstrates ongoing educational efforts. However, there's no clear evidence of lasting behavior change, community self-reliance, or peer education resulting from these trainings. The focus is more on the CHW's personal transformation and current teaching activities rather than documented community-wide change or empowerment outcomes. | Parsing failed for concept 'Community Empowerment Through Education' | Resource and Material Distribution: The testimonial describes the CHW's personal experience with malaria and their current role in training community members on malaria prevention. While they mention mosquito nets and their importance, there is no indication that they are distributing nets or any other materials. The CHW explicitly states they are 'training' and 'sharing' information about prevention methods, which falls under education/advice without material support - an exclusion criterion for this concept. | Monitoring and Follow-Up: The testimonial primarily describes the CHW's personal malaria experience and their current role in training community members on malaria prevention. While they mention conducting training sessions, there is no evidence of ongoing monitoring, returning to check on individuals, or following up after initial education. The focus is on preventive education delivery rather than continuous care management, aligning with the exclusion criteria of 'one-time visits or initial health education sessions with no follow-up.' | Trust and Cultural Mediation: The testimonial shows minimal evidence of trust-building or cultural mediation. While the CHW mentions training community members on malaria prevention, there is no explicit mention of building trust, navigating cultural barriers, or addressing community skepticism. The focus is primarily on sharing health information and personal experience rather than mediating between the community and health systems or overcoming trust issues. | Parsing failed for concept 'Trust and Cultural Mediation' | Clinical Interventions by CHWs: The testimonial describes the CHW's personal experience with malaria and their current role in educating community members about malaria prevention. While they mention buying over-the-counter painkillers for themselves before becoming a CHW, there is no evidence of them administering medication, treating wounds, or providing any direct clinical care to others as a CHW. Their work focuses exclusively on health education and prevention training, which is explicitly excluded from this concept. | Mother and Infant Care: The testimonial focuses entirely on malaria prevention and the CHW's personal experience with malaria. There is no mention of prenatal care, childbirth, postpartum support, infant health, or any mother/infant-specific activities. The CHW discusses general community health education about malaria prevention, which does not align with the Mother and Infant Care concept. | Successful Outcomes: The testimonial shows moderate alignment with successful outcomes. The CHW describes personal recovery from malaria (a positive outcome) and mentions actively training community members on malaria prevention. However, there's no specific evidence of community members actually implementing the advice or any measurable impact from the training efforts. This aligns with the example 'I told people to take care of their health, but it's hard to know if they listened' which scores low, but the active training component elevates this to moderate alignment. | Material or Training Requests: The testimonial describes the CHW's personal experience with malaria and their current work educating the community about malaria prevention. While they mention being a 'trained Community Health Worker,' there are no explicit requests for materials, supplies, or additional training. The CHW describes what they are already doing rather than asking for resources to better serve their community. | Children Served: The testimonial focuses on the CHW's personal experience with malaria and their general community training activities. There is no mention of children, minors, or youth-specific services. The CHW describes training 'community members' but does not specify working with children or providing child-focused health education. | Elderly Served: The testimonial focuses entirely on the CHW's personal experience with malaria and their subsequent work educating community members about malaria prevention. There is no mention of elderly people, seniors, or grandparents, nor any specific assistance provided to older adults. The CHW discusses general community education without any age-specific focus. | Women Served: The testimonial describes the CHW's personal experience with malaria and their general community training on malaria prevention. There is no mention of women, girls, or gender-specific interactions. The CHW refers to training 'community members' without any gender specification or focus on women's particular needs or challenges. | Men Served: The testimonial describes the CHW's personal experience with malaria and their subsequent community education efforts. There is no mention of serving men or boys specifically, nor any reference to gendered roles, challenges, or support. The community training mentioned appears to be general and not targeted at or inclusive of any specific gender-related context. | Families Served: The testimonial focuses on the CHW's personal malaria experience and general community training, with no specific mention of households, parents with children, or family units. The phrase 'community members' refers to individuals in general rather than family-focused interventions. This aligns with the exclusion criteria of 'individual help not connected to a family unit or structure.' | Marginalized Groups Served: The testimonial describes the CHW's personal experience with malaria and their general community education efforts on malaria prevention. There is no mention of serving any marginalized, stigmatized, or structurally excluded groups. The CHW discusses training 'community members' in general without any reference to specific vulnerable populations or those facing social exclusion. | Financial Hardship: The testimonial shows minimal evidence of financial hardship. While the CHW mentions buying pain killers 'over-the-counter' before proper diagnosis, this suggests self-medication rather than clear inability to afford medical care. The person eventually received lab testing and treatment. The focus is on lack of health knowledge rather than financial barriers to care. | Parsing failed for concept 'Financial Hardship' | Social Isolation: The testimonial focuses entirely on the CHW's personal experience with malaria and their subsequent work educating the community about malaria prevention. There is no mention of living alone, lack of support systems, loneliness, or social neglect. The narrative describes active community engagement and training activities, which indicates social connection rather than isolation. | Disease Burden: The testimonial describes a single malaria episode from four years ago that lasted about 2.5 weeks. While the illness was severe with significant symptoms (weakness, joint pain, high fever), it was a short-term acute illness that resolved with treatment. The narrative focuses on prevention education rather than ongoing disease management. This aligns with the exclusion criteria of 'short-term illness without major life impact or context' rather than the inclusion criteria of 'long-term or recurrent illness or disability.' | Stigma or Discrimination: The testimonial describes a personal experience with malaria and subsequent community education efforts. There is no mention of social rejection, shame, exclusion, or judgment from others related to the health condition. The narrative focuses on physical symptoms, medical treatment, and preventive education without any indication of stigma or discrimination. | Mental or Emotional Distress: The testimonial focuses primarily on physical symptoms of malaria (weakness, joint pain, high temperature, sweating) and the CHW's experience with diagnosis and treatment. While the phrase 'It was unbearable' suggests some distress, this appears to be physical discomfort rather than mental or emotional distress. The narrative is educational and factual rather than expressing emotional overwhelm, depression, or psychological strain. | Lack of Resources: The testimonial primarily describes a personal malaria experience before becoming a CHW and current prevention education efforts. There is minimal evidence of lacking resources - the CHW mentions they now train community members but doesn't indicate any shortage of supplies, tools, or support needed for this work. The only resource-related mention is historical (buying over-the-counter painkillers before being a CHW), which doesn't reflect current CHW resource constraints. | Systemic Barriers: The testimonial does not mention any systemic barriers. The CHW describes their personal experience with malaria before becoming trained, and their current prevention work. There are no references to health facility shortages, institutional problems, or external conditions preventing them from helping community members. The narrative focuses on personal experience and successful prevention education, not systemic obstacles. | Overburdened CHWs: The testimonial does not indicate the CHW is overburdened. The narrative focuses on their personal malaria experience and current prevention education work. There is no mention of being exhausted, overwhelmed, having too many patients, or excessive workload. The CHW appears to be successfully conducting community training without expressing any burden. | Lack of Follow-Through: This testimonial does not demonstrate lack of follow-through. The CHW describes their personal experience with malaria before becoming a CHW, where they received complete treatment and recovered. Now as a trained CHW, they actively conduct training sessions for community members on malaria prevention. There is no evidence of abandoned care, interrupted assistance, or unresolved issues in their work as a CHW. | Lack of Knowledge: Strong alignment with the concept. The CHW explicitly states 'I had no information about malaria' when describing their experience before training. They were unable to properly address their malaria symptoms due to lack of knowledge, resorting only to over-the-counter painkillers. The testimonial clearly contrasts their lack of knowledge before training with their current ability to educate others, demonstrating that knowledge gap was the primary barrier to proper treatment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Malaria During my health education at Bandani Slums-Kisumu County, giving malaria talk to the residents, I narrowed down on the signs and symptoms of malaria, the treatment and causes. Some of the causes like not sleeping under the treated mosquito nets, vector control. The signs and symptoms like high ever, shaking, chills, pain in the muscles and abdomen. Some people feel very sick, fatigue, fever, night sweats, nausea, shivering diarrhea, vomiting, headache and coldness. Upon completion, one Mrs. Mary Onyango approached me and requested that I visit her home. On our way to her homestead, she narrated to me some of the signs we talked about earlier that she has been seeing little girl experiencing. On reaching her homestead a few kilometers from where we were, I met the little girl. She was sweating all over her body. She told me she had headache; I saw her shivering and was vomiting. Based on what I saw, I concluded the child might have been suffering from malaria. I told the mother to do the sponging to reduce the temperature due to the high fever. I advised the mother to take her to the nearest health facility for further management. After two days, I did a follow-up home visit to see how the little girl was. She was given anti-malaria tablets and was responding well to the treatment. ---</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.1,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 1.0,
+  "Water Quality, Sanitation, and Hygiene": 0.05,
+  "Personal Disease Management and Adherence": 0.9,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.25,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.9,
+  "Community Empowerment Through Education": 0.5,
+  "Resource and Material Distribution": 0.1,
+  "Monitoring and Follow-Up": 1.0,
+  "Trust and Cultural Mediation": 0.6,
+  "Clinical Interventions by CHWs": 0.25,
+  "Mother and Infant Care": 0.15,
+  "Successful Outcomes": 0.9,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.95,
+  "Elderly Served": 0.0,
+  "Women Served": 0.65,
+  "Men Served": 0.0,
+  "Families Served": 0.7,
+  "Marginalized Groups Served": 0.7,
+  "Financial Hardship": 0.1,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.3,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.05,
+  "Lack of Resources": 0.15,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.05,
+  "Lack of Knowledge": 0.05
+}</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial shows the CHW delivering health education and applying malaria knowledge, but it never states that the CHW attended training or gained new skills through a formal program. Any inference of training is speculative, so alignment with the concept is very weak. | Menstrual Hygiene Education and Challenges: The testimonial focuses exclusively on malaria education and follow-up; it does not mention menstruation, menstrual products, stigma, or related challenges. Therefore, the concept is not present. | Drug Abuse: Environment and Awareness: The testimonial focuses exclusively on malaria education, symptoms, and treatment without any mention of substance abuse, addiction, alcohol, or related social/environmental factors. | CHW-Led Infectious Disease Management: The testimonial describes the CHW delivering malaria education on signs, symptoms, causes, prevention (treated nets, vector control), advising a caregiver, referring the child to a health facility, and conducting a follow-up visit—an unambiguous, comprehensive example of CHW-led outreach and management for an infectious disease. | Water Quality, Sanitation, and Hygiene: The testimonial focuses on malaria education, symptoms, mosquito nets, and referral for treatment. It does not discuss clean water, handwashing, sanitation practices, or hygiene education related to water, which are required for this concept. Any connection to hygiene is indirect and minimal, so alignment is very weak. | Personal Disease Management and Adherence: The testimonial centers on identifying malaria symptoms, advising the caregiver to seek treatment, and following up to ensure the child is taking antimalarial tablets and responding well. This is a direct example of facilitating diagnosis, treatment initiation, and adherence for malaria—exactly what the concept describes. | Nutrition Education and Food Access: The testimonial focuses solely on malaria education, prevention, and treatment; it contains no discussion of healthy eating, food insecurity, or access to nutrition. | Sexual and Reproductive Health Education: The testimonial focuses exclusively on malaria education—signs, symptoms, prevention and treatment. It contains no references to family planning, STI/HIV prevention, condoms, or any other sexual or reproductive health topics; therefore the concept is absent. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses solely on malaria education, symptoms, and treatment for a child without any mention of abuse, exploitation, violence, or protective interventions. Therefore, the GBV and Child Protection concept does not apply. | Health Literacy and Misconceptions: The CHW delivers a malaria education session, suggesting an underlying need to improve residents' knowledge, but the narrative does not describe any specific misinformation or mistaken beliefs that influence decisions. Because only a general health‐education context (possible low literacy) is present without explicit misconceptions, alignment with the concept is weak. | Mental Health Awareness and Support: Testimonial focuses exclusively on malaria education, symptoms, and treatment; no mention of psychological well-being, depression, anxiety, or emotional support. | Referrals and Advocacy: The CHW directly advised the caregiver to take the child to the nearest health facility for further management and then conducted a follow-up visit. This is a clear instance of acting as a navigator/advocate within the health system, matching the concept’s inclusion criteria of helping with referrals or appointments. | Community Empowerment Through Education: The CHW delivered a malaria talk and a community member subsequently recognized symptoms in her child and sought care, indicating some immediate application of the education. However, the account centers on a single household rather than broader, sustained community change or peer-led action. Thus it shows partial alignment—more than a one-off talk with no effect, but less than clear long-term empowerment—meriting a moderate score. | Resource and Material Distribution: The testimonial describes providing health education and advice, with no mention of giving out supplies or materials. This fits the exclusion criteria (education without material support). Similar to the example that scored 0.1, a minimal score is assigned. | Monitoring and Follow-Up: The CHW explicitly states, “After two days, I did a follow-up home visit to see how the little girl was,” which matches the definition and inclusion criteria of ongoing follow-up visits to check progress and adjust care. This is an unambiguous example of Monitoring and Follow-Up. | Trust and Cultural Mediation: The CHW provides a community health talk explaining malaria causes, symptoms, prevention and treatment, which demonstrates mediation of health information to residents. A mother subsequently trusts the CHW enough to request a home visit and follow-up guidance, indicating some degree of trust built between the CHW and community members. However, the narrative does not describe overcoming specific cultural or linguistic barriers, so alignment is moderate rather than strong. | Clinical Interventions by CHWs: The CHW assessed the child, suggested that the mother sponge her to lower fever, and referred her to a health facility. While this shows some clinical judgement and minimal home-care advice, the CHW did not personally administer medication or perform a hands-on treatment such as bandaging or giving drugs. Therefore, alignment with direct clinical intervention is weak and mostly falls under referral and education, which the concept’s exclusion criteria note. | Mother and Infant Care: The testimonial focuses on malaria education and advising a mother to seek treatment for her ‘little girl.’ While it involves a caregiver and a young child, it does not address prenatal, childbirth, postpartum issues, or infant-specific care such as breastfeeding or immunizations. Therefore, only minimal, indirect relevance to the Mother and Infant Care concept is present. | Successful Outcomes: The CHW identified malaria symptoms, advised immediate care and referral, and on follow-up the child was taking antimalarials and \ | Material or Training Requests: The testimonial recounts a health education session and a home visit but contains no explicit request from the CHW for additional materials, supplies, or training. Therefore the concept does not apply. | Children Served: The CHW directly assessed and advised treatment for a 'little girl' (a minor), showing clear involvement in providing health support to a child. This is an unambiguous match with the concept definition and inclusion criteria. | Elderly Served: The testimonial focuses on a child with malaria and her mother; there is no mention of older adults, seniors, or grandparents, nor any assistance directed toward them. | Women Served: The CHW directly assists an adult woman (Mrs. Onyango) and her young daughter by providing advice and follow-up care for suspected malaria. Although the education session was for all residents and the health issue is not uniquely gender-specific, there is clear interaction and service to female beneficiaries, satisfying inclusion but not with a strong gender-focused angle; therefore a moderate score is appropriate. | Men Served: The testimonial only discusses a mother (Mrs. Mary Onyango) and her young daughter; no adult males or boys are referenced in the context of support or health challenges, so the concept does not apply. | Families Served: The CHW visited a household and worked with a mother and her child, fitting the definition of supporting a parent–child family unit. This goes beyond a passing mention (so higher than 0.4) but does not involve multiple family members or a broad family-wide intervention seen in the 0.9 example, making a moderate–strong alignment appropriate (~0.7). | Marginalized Groups Served: The CHW conducted health education and a home visit in Bandani Slums, an area that implies socioeconomic disadvantage and limited access to services. This suggests support to an underserved, structurally marginalized population, though the testimonial does not explicitly discuss marginalization. Therefore, the alignment is moderate-to-strong rather than perfect. | Financial Hardship: The story takes place in a slum area, which indirectly suggests poverty, but there is no explicit statement that the family cannot afford transportation, food, or medical care. No barriers to care due to cost are mentioned. Hence, only a very weak, indirect alignment with financial hardship. | Social Isolation: The testimonial describes a mother seeking help for her child with malaria and receiving follow-up support. There is no mention of the individuals living alone, lacking support systems, or experiencing social neglect. Hence, the concept of Social Isolation is not present. | Disease Burden: The testimonial describes an acute episode of malaria in a child. While malaria is a serious disease, the narrative focuses on a single, short-term bout rather than a chronic or recurrent condition. According to the concept definition, disease burden emphasizes chronic or long-term illness; short, self-limited illnesses are largely excluded. Thus there is only weak alignment (similar to the cold example scored 0.4), warranting a low score. | Stigma or Discrimination: The testimonial describes health education and clinical follow-up for a child with malaria; it contains no mention of shame, social judgment, exclusion, or discriminatory attitudes. Therefore the stigma or discrimination concept does not apply. | Mental or Emotional Distress: The testimonial focuses on physical symptoms of malaria and medical guidance. There is no explicit mention of depression, stress, or emotional overwhelm, so alignment with mental or emotional distress is minimal. | Lack of Resources: The CHW refers the child to a health facility instead of testing or treating on the spot, which might hint at limited supplies, but there is no explicit mention of missing medicines, tools, or support. Because the testimonial does not state a clear shortage, alignment with “Lack of Resources” is very weak. | Systemic Barriers: The testimonial describes successful identification, referral, and treatment of a malaria case with no mention of facility shortages, distance problems, cost, corruption, or other institutional obstacles. Nothing outside the CHW’s control hindered her ability to help, so the concept of systemic barriers is not present. | Overburdened CHWs: The testimonial focuses on providing malaria education and a single home visit; it contains no references to excessive workload, exhaustion, or being overwhelmed. Therefore, the concept of overburdened CHWs is not present. | Lack of Follow-Through: The CHW provided advice, referred the child to a health facility, and conducted a follow-up visit confirming the child was improving. This demonstrates follow-through, not abandonment or unresolved care, so the concept is essentially absent. | Lack of Knowledge: The CHW confidently identified malaria symptoms, provided initial advice, and referred the child for treatment—indicating sufficient knowledge. No mention of uncertainty, lack of training, or need for additional guidance, so the concept is essentially absent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Malaria During my health education at Bandani Slums-Kisumu County, giving malaria talk to the residents, I narrowed down on the signs and symptoms of malaria, the treatment and causes. Some of the causes like not sleeping under the treated mosquito nets, vector control. The signs and symptoms like high ever, shaking, chills, pain in the muscles and abdomen. Some people feel very sick, fatigue, fever, night sweats, nausea, shivering diarrhea, vomiting, headache and coldness. Upon completion, one Mrs. Mary Onyango approached me and requested that I visit her home. On our way to her homestead, she narrated to me some of the signs we talked about earlier that she has been seeing little girl experiencing. On reaching her homestead a few kilometers from where we were, I met the little girl. She was sweating all over her body. She told me she had headache; I saw her shivering and was vomiting. Based on what I saw, I concluded the child might have been suffering from malaria. I told the mother to do the sponging to reduce the temperature due to the high fever. I advised the mother to take her to the nearest health facility for further management. After two days, I did a follow-up home visit to see how the little girl was. She was given anti-malaria tablets and was responding well to the treatment. ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.8,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.9,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.8,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.0,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.8,
+  "Community Empowerment Through Education": 0.3,
+  "Resource and Material Distribution": 0.1,
+  "Monitoring and Follow-Up": 0.9,
+  "Trust and Cultural Mediation": 0.7,
+  "Clinical Interventions by CHWs": 0.3,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.9,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.9,
+  "Elderly Served": 0.0,
+  "Women Served": 0.8,
+  "Men Served": 0.0,
+  "Families Served": 0.8,
+  "Marginalized Groups Served": 0.7,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.3,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.0,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial demonstrates strong evidence of CHW empowerment through training. The CHW is conducting health education sessions on malaria, demonstrating detailed knowledge of signs, symptoms, causes, and treatment. They apply this knowledge practically by assessing a child's condition and providing appropriate advice. While the testimonial doesn't explicitly mention receiving training, the structured knowledge and professional approach to health education strongly suggests formal CHW training has occurred, aligning with the concept's definition of 'CHWs gaining knowledge' and 'increasing their capacity to serve.' | Menstrual Hygiene Education and Challenges: This testimonial is entirely focused on malaria education, symptoms, and treatment. There is no mention of menstruation, menstrual hygiene, products, or related education. The content explicitly deals with a different health topic (malaria), making it a clear non-match for the menstrual hygiene concept. | Drug Abuse: Environment and Awareness: The testimonial focuses entirely on malaria education, symptoms, and treatment. There is no mention of substance abuse, addiction, alcohol, peer influence, or drug education. The content explicitly deals with a communicable disease (malaria) rather than any social or environmental factors related to drug abuse. | CHW-Led Infectious Disease Management: Strong direct alignment with the concept. The CHW conducted health education specifically about malaria (an infectious disease), explaining symptoms, prevention, and treatment to the community. They provided direct intervention by assessing a sick child, giving immediate care advice (sponging), referring to a health facility, and conducting follow-up. This demonstrates comprehensive CHW-led management of an infectious disease case, matching the first example's score of 0.9. | Water Quality, Sanitation, and Hygiene: The testimonial focuses entirely on malaria education, symptoms, and treatment. While it mentions vector control and mosquito nets as prevention methods, there is no discussion of water quality, sanitation practices, or hygiene education. The concept is clearly not present in this testimonial. | Personal Disease Management and Adherence: Strong alignment with the concept. The testimonial describes a specific case of malaria management, including diagnosis based on symptoms (fever, shivering, vomiting), immediate care advice (sponging for fever), referral to health facility, and follow-up showing treatment adherence with anti-malaria tablets. While the CHW facilitated the management rather than the patient self-managing, the case clearly demonstrates disease management and treatment adherence guidance, similar to the 0.7 example of 'advice on managing high blood pressure with daily treatment.' | Nutrition Education and Food Access: The testimonial focuses entirely on malaria education, symptoms, and treatment. There is no mention of nutrition, food security, healthy eating, or any food-related topics. The content explicitly deals with disease management rather than nutrition education or food access. | Sexual and Reproductive Health Education: The testimonial focuses entirely on malaria education, symptoms, and treatment. There is no mention of family planning, STI prevention, HIV awareness, reproductive rights, or any sexual health topics. This clearly falls outside the concept's inclusion criteria. | Gender-Based Violence (GBV) and Child Protection: This testimonial focuses entirely on malaria education and treatment of a sick child. There is no mention of abuse, violence, exploitation, or any form of GBV. The CHW intervention is purely medical in nature, addressing physical illness symptoms rather than violence-related issues. | Health Literacy and Misconceptions: The testimonial describes accurate health education about malaria with no evidence of misinformation or misconceptions. The CHW provided correct information about causes, symptoms, and treatment. The mother recognized symptoms after the education and sought appropriate care. This represents accurate health discussions with no misunderstanding present, which falls under the exclusion criteria. | Mental Health Awareness and Support: This testimonial focuses entirely on physical health symptoms and treatment of malaria. There is no mention of psychological well-being, emotional support, or mental health concerns. The CHW addresses only medical symptoms (fever, shivering, vomiting) and provides medical advice, which falls under the exclusion criteria of 'medical diagnoses without a mental/emotional context.' | Referrals and Advocacy: Strong direct alignment. The CHW clearly advised the mother to take her child to the nearest health facility for further management after identifying malaria symptoms. This demonstrates the CHW acting as an intermediary by connecting the family to healthcare services. The follow-up visit also shows advocacy through ensuring the child received and responded to treatment. Similar to the 0.9 example of identifying symptoms and referring for testing. | Community Empowerment Through Education: This testimonial shows a one-time educational session that led to immediate action by one individual (Mrs. Mary Onyango), but lacks evidence of lasting community-wide behavior change or self-reliance. While the education enabled recognition of symptoms and appropriate healthcare seeking, it represents an isolated incident rather than sustained community empowerment or peer education spreading through the community. | Resource and Material Distribution: The testimonial describes health education about malaria and providing advice to take a sick child to a health facility. While the CHW provided valuable education and guidance, there is no mention of distributing any physical resources like mosquito nets, medicine, or other materials. This aligns with the exclusion criteria of 'discussions of education or advice without material support' and matches the example 'I gave general advice that day; I didn't bring any supplies.' → 0.1 | Monitoring and Follow-Up: Strong direct alignment with the concept. The CHW explicitly states 'After two days, I did a follow-up home visit to see how the little girl was' and checked on her progress after the initial intervention. This demonstrates ongoing interaction to check progress and monitor the child's response to treatment, which directly matches the definition and inclusion criteria. | Trust and Cultural Mediation: The testimonial shows moderate alignment with trust-building. Mrs. Mary Onyango trusted the CHW enough to request a home visit and share her daughter's health concerns after the education session. The CHW successfully bridged the gap between community health education and healthcare access by advising the mother to seek facility care, which was followed. However, there's no explicit mention of cultural barriers, translation needs, or community mistrust that needed to be overcome. | Clinical Interventions by CHWs: The CHW provided health education about malaria and advised sponging to reduce fever, which is a basic physical intervention. However, the CHW did not directly administer medication or perform hands-on clinical tasks. The primary actions were assessment, basic advice (sponging), and referral to a health facility, which aligns weakly with the concept's focus on direct clinical interventions. | Mother and Infant Care: This testimonial focuses on malaria education and treatment for a child, not on prenatal, childbirth, postpartum, or infant-specific care. While it involves caring for a young girl, there is no mention of mother-infant relationship, pregnancy, breastfeeding, immunizations, or other elements specific to the Mother and Infant Care concept. The care provided is general pediatric health support rather than mother/infant-specific care. | Successful Outcomes: Strong direct alignment with successful outcomes. The CHW identified malaria symptoms, advised the mother to take the child to a health facility, and confirmed through follow-up that the child received anti-malaria treatment and was 'responding well to the treatment.' This shows a clear positive health improvement directly resulting from the CHW's intervention, matching the first example's score of 0.9. | Material or Training Requests: The testimonial describes a CHW providing malaria education and helping a sick child, but contains no requests for materials, supplies, or training. The CHW demonstrates existing knowledge and capability without expressing any needs or asking for additional resources to better serve the community. | Children Served: Strong direct alignment. The testimonial describes a CHW providing direct health intervention for a 'little girl' suffering from malaria symptoms. The CHW assessed her condition, provided immediate care advice (sponging for fever), referred her to a health facility, and conducted follow-up care. This clearly demonstrates support for a minor's health needs, matching the inclusion criteria of 'support for children in health.' | Elderly Served: The testimonial focuses on a CHW helping a little girl with malaria symptoms. There is no mention of elderly individuals, seniors, or grandparents. The only adults mentioned are the mother (Mrs. Mary Onyango) and the CHW themselves. Since the concept requires direct assistance to elderly individuals and this testimonial explicitly describes helping a child, the concept is clearly not present. | Women Served: Strong alignment as the CHW directly served Mrs. Mary Onyango by responding to her request for help with her daughter's health issue. The CHW provided health education, conducted a home visit, assessed the child's condition, gave medical advice (sponging for fever), and made a referral to a health facility. While the primary patient was a girl, the mother was the adult woman who received education and support from the CHW, fitting the concept's inclusion criteria of 'assistance or education for women, especially around health.' | Men Served: The testimonial focuses entirely on providing health education about malaria and helping a mother (Mrs. Mary Onyango) and her little girl. There is no mention of adult males or boys, nor any discussion of gendered roles or challenges related to men. The concept clearly does not apply to this testimonial. | Families Served: Strong alignment with the concept. The testimonial describes a CHW visiting a household where both mother (Mrs. Mary Onyango) and child (little girl) are present, with the CHW providing health support that affects both family members. The mother is actively involved in the child's care, and the CHW provides guidance to the parent about caring for the sick child, demonstrating family-focused intervention. | Marginalized Groups Served: The testimonial describes serving residents of Bandani Slums in Kisumu County. Slum communities typically face structural exclusion and limited access to healthcare, making them a marginalized population. The CHW provided direct health education and home visit support to this underserved community. However, the focus is primarily on the health condition (malaria) rather than explicitly addressing marginalization-related barriers, which prevents a higher score. | Financial Hardship: The testimonial describes a CHW providing health education about malaria and visiting a sick child, but contains no evidence of financial hardship. There is no mention of inability to afford transportation, medical care, or basic needs. The mother was able to take the child to a health facility and obtain anti-malaria tablets without any indicated financial barriers. | Social Isolation: The testimonial describes a CHW providing malaria education and visiting a family to help a sick child. There is no mention of loneliness, living alone, lack of support systems, or abandonment. The child has a mother (Mrs. Mary Onyango) who is actively caring for her and seeking help. The focus is entirely on malaria symptoms and treatment, not social isolation. | Disease Burden: This testimonial describes an acute malaria case in a child, which is a short-term illness episode. While malaria can be serious, this specific case shows a single episode that was quickly treated and resolved within days. The narrative doesn't indicate chronic malaria, recurring episodes, or long-term disability. According to the exclusion criteria, 'short-term illness without major life impact' scores low, similar to the cold recovery example (0.4). | Stigma or Discrimination: The testimonial describes a CHW providing malaria education and helping a sick child get treatment. There is no mention of social rejection, shame, exclusion, or judgment from others. The mother actively sought help and the community appeared receptive to health education. The focus is entirely on medical symptoms and treatment, with no evidence of stigma or discrimination present. | Mental or Emotional Distress: The testimonial focuses entirely on physical symptoms of malaria (fever, shivering, vomiting, headache) and medical treatment. There is no mention of depression, hopelessness, trauma, stress, or any emotional distress. The exclusion criteria specifically states 'physical complaints or stress unrelated to emotional wellbeing,' which directly applies to this malaria case. | Lack of Resources: The CHW successfully provided health education and appropriate advice. They did not mention lacking any resources - no shortage of medicine, tools, or support is indicated. The CHW was able to assess the situation and refer the child to a health facility where treatment was successfully provided. This testimonial shows the system working as intended, not a lack of resources. | Systemic Barriers: The testimonial describes a successful health education session and home visit where the CHW was able to help a child with malaria symptoms. The mother was advised to take the child to a health facility, which she did, and the child received treatment and recovered. There is no mention of any systemic barriers preventing care - no facility shortages, no access issues, no institutional problems. The healthcare system worked as intended in this case. | Overburdened CHWs: The testimonial describes a CHW conducting health education and providing care to a single patient with appropriate follow-up. There is no mention of exhaustion, being overwhelmed, or having too many patients. The CHW appears to be functioning effectively within their capacity, successfully delivering education and care without any indication of being overburdened. | Lack of Follow-Through: The CHW completed their intervention fully - they provided health education, visited the home, gave immediate advice (sponging), referred to a health facility, and conducted a follow-up visit after two days to confirm the child received treatment and was recovering. This represents complete follow-through with no abandonment or unresolved issues. | Lack of Knowledge: The CHW demonstrates competent knowledge throughout the testimonial. They correctly identified malaria symptoms, provided appropriate first aid advice (sponging for fever), and made the proper referral to a health facility. There is no indication of uncertainty, need for additional training, or inability to address the issue due to knowledge gaps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Menstrual Hygiene/Teenage Pregnancy Many teenage adolescent girls and young women suffer from what we call menstrual poverty. Menstrual poverty is an incidence whereby a girl is not able to get access to menstrual aids such as sanitary towels and menstrual cups. At the beginning of December, teenage pregnancy rapid growth raised an alarm whereby many individuals and like-minded individuals came together to find out why most of our teenage girls are getting pregnant. The 16-day activism and activism that brought about ??????? for Google meets and physical meetings helped me reach out to more than 50 girls and had some chit chats. From the interactions, I found out that menstrual poverty is a major leading factor in this lack of sanitary towels during this time of the month forcing some girls to engage in transactional sex which back to these unwanted teenage pregnancies. From this I, as a CHW, decided to partner with other ??? and individuals to fundraise for pads to give these girls. This has helped reduce and prevent some if not all. Most men and adults too have been sensitized by me that menstruation is not a woman issue but a human issue and we should all support our girls during this time of the month. ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.2,
+  "Menstrual Hygiene Education and Challenges": 1.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.0,
+  "Water Quality, Sanitation, and Hygiene": 0.15,
+  "Personal Disease Management and Adherence": 0.05,
+  "Nutrition Education and Food Access": 0.05,
+  "Sexual and Reproductive Health Education": 0.5,
+  "Gender-Based Violence (GBV) and Child Protection": 0.75,
+  "Health Literacy and Misconceptions": 0.3,
+  "Mental Health Awareness and Support": 0.05,
+  "Referrals and Advocacy": 0.7,
+  "Community Empowerment Through Education": 0.85,
+  "Resource and Material Distribution": 0.8,
+  "Monitoring and Follow-Up": 0.2,
+  "Trust and Cultural Mediation": 0.6,
+  "Clinical Interventions by CHWs": 0.2,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.75,
+  "Material or Training Requests": 0.3,
+  "Children Served": 0.9,
+  "Elderly Served": 0.0,
+  "Women Served": 1.0,
+  "Men Served": 0.5,
+  "Families Served": 0.1,
+  "Marginalized Groups Served": 0.8,
+  "Financial Hardship": 0.9,
+  "Social Isolation": 0.1,
+  "Disease Burden": 0.1,
+  "Stigma or Discrimination": 0.25,
+  "Mental or Emotional Distress": 0.1,
+  "Lack of Resources": 0.7,
+  "Systemic Barriers": 0.8,
+  "Overburdened CHWs": 0.1,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial references activism events and meetings that \ | Menstrual Hygiene Education and Challenges: The testimonial focuses extensively on menstrual poverty, lack of sanitary towels, fundraising for pads, and community sensitization about menstruation, directly matching the concept’s definition and inclusion criteria. | Drug Abuse: Environment and Awareness: The testimonial discusses menstrual hygiene, teenage pregnancy, and menstrual poverty with no mention of substance abuse, addiction, alcohol, or related social/environmental drug factors. Therefore, the concept is not present. | CHW-Led Infectious Disease Management: The testimonial describes a CHW addressing menstrual poverty and teenage pregnancy, which are not infectious diseases. There is no mention of CHWs educating about or managing infectious diseases, so the concept does not apply. | Water Quality, Sanitation, and Hygiene: The testimonial centers on menstrual poverty and providing sanitary pads—an aspect of personal hygiene—not on water quality, sanitation systems, or hygiene education related to water/hand-washing. Since the concept explicitly excludes personal hygiene not tied to water or community sanitation, alignment is weak. | Personal Disease Management and Adherence: The testimonial focuses on menstrual hygiene access and preventing teenage pregnancy, not on managing a diagnosed disease or adhering to treatment. There is no discussion of medication schedules, chronic or infectious disease management, or adherence guidance from CHWs, so alignment with the concept is minimal. | Nutrition Education and Food Access: The testimonial focuses on menstrual poverty and teenage pregnancy; there is no discussion of healthy eating, food insecurity, or nutrition education. Thus, only a negligible alignment (virtually absent) with the Nutrition Education and Food Access concept. | Sexual and Reproductive Health Education: The CHW describes reaching out to adolescent girls, discussing menstrual hygiene, the link between lack of sanitary products and transactional sex, and efforts to prevent teenage pregnancy. This constitutes some reproductive-health education (addressing menstruation and pregnancy prevention). However, there is no explicit discussion of family planning methods, condoms, STI/HIV prevention, or detailed safe-sex instruction. Therefore the alignment is moderate rather than strong. | Gender-Based Violence (GBV) and Child Protection: The testimonial highlights teenage girls engaging in transactional sex because of menstrual poverty, which constitutes sexual exploitation of minors—a child protection concern. The CHW responds by mobilizing resources (pads) to prevent this exploitation, aligning with the concept’s inclusion criteria around CHW interventions for abuse/exploitation. Although explicit violence is not described, the focus on protecting adolescents from exploitative situations justifies a moderate-to-strong score. | Health Literacy and Misconceptions: The testimonial mainly discusses material barriers (lack of menstrual products) but briefly notes that many men consider menstruation solely a “woman issue,” prompting the CHW to educate them. This reflects a minor misconception being addressed, giving weak but present alignment with the concept. | Mental Health Awareness and Support: The testimonial focuses on menstrual poverty, teenage pregnancy, and distribution of sanitary products. There is no explicit discussion of psychological well-being, feelings of depression, anxiety, or emotional support. Any mental health implications are only implicit and not articulated, resulting in a very weak alignment. | Referrals and Advocacy: The CHW describes advocating for adolescent girls by partnering with others to fund-raise for sanitary pads and sensitizing the community, which fits the concept of acting as an advocate or intermediary. However, there is no clear mention of formal healthcare referrals or navigation, so alignment is moderate rather than perfect. | Community Empowerment Through Education: The CHW describes organizing outreach (Google Meets, physical meetings) with more than 50 girls, sensitizing men and adults, and partnering with others to fund-raise for sanitary pads. This reflects group action and community-wide education that is reported to have already reduced teenage pregnancies—evidence of community change beyond a one-time event. Therefore the testimonial strongly aligns with the concept of Community Empowerment Through Education, though the long-term sustainability is not fully demonstrated, so the score is slightly below a perfect match. | Resource and Material Distribution: The CHW describes partnering with others to fund-raise for sanitary pads and \ | Monitoring and Follow-Up: The testimonial focuses on raising awareness and providing menstrual pads, describing meetings and sensitization activities. It does not explicitly mention returning to check on individual girls’ situations or continuous tracking of outcomes. Any implication of progress (‘this has helped reduce…’) is indirect, so evidence for ongoing monitoring/follow-up is weak. | Trust and Cultural Mediation: The CHW describes holding meetings, ‘chit-chats,’ and ‘sensitizing’ men and adults that menstruation is a human issue—actions aimed at overcoming cultural stigma around menstruation and teenage pregnancy. This shows mediation of cultural barriers and efforts to gain community trust, but there is no explicit mention of language translation or a direct statement that trust was a problem that she solved, so alignment is moderate rather than strong. | Clinical Interventions by CHWs: The testimonial describes the CHW fundraising for and distributing sanitary pads, which is provision of a health-related supply but does not involve administering medication, treating injuries, or performing other clinical tasks outlined in the concept definition. Therefore there is only minimal overlap with the intended clinical interventions. | Mother and Infant Care: The testimonial focuses on menstrual hygiene and preventing teenage pregnancy, which falls under general women’s reproductive health. It does not mention prenatal care, childbirth, postpartum support, or infant health, which are required for the Mother and Infant Care concept. | Successful Outcomes: The CHW states that fundraising for sanitary pads \ | Material or Training Requests: The testimonial highlights a shortage of sanitary pads and describes efforts to fund-raise for them, indicating awareness of a material need. However, the CHW does not explicitly ask an external party for supplies or training; instead, they recount actions already taken. This is closer to describing what is lacking than making a direct request, so the alignment with the concept is weak. | Children Served: The CHW describes reaching out to more than 50 teenage girls, addressing menstrual poverty and preventing teenage pregnancies—direct support activities for minors. This matches the inclusion criteria of providing help to adolescents, giving a strong but not absolute alignment (some girls could be 18–19), hence 0.9. | Elderly Served: The testimonial focuses on adolescent girls, menstrual hygiene, and teenage pregnancy. There is no mention of older adults or CHW assistance directed toward seniors; therefore, the Elderly Served concept is not present. | Women Served: The testimonial centers on teenage girls and young women, highlighting gender-specific challenges (menstrual poverty, teenage pregnancy) and describing concrete CHW actions—education, fundraising for pads, community sensitization. This is a direct, unambiguous instance of assisting women around health issues, fitting the concept definition and inclusion criteria perfectly. | Men Served: The CHW describes actively sensitizing “most men and adults” about menstruation, addressing their gendered role in supporting girls’ menstrual health. This goes beyond a casual mention and involves outreach to men, but the primary beneficiaries remain adolescent girls, not the men themselves. Therefore, the alignment is moderate. | Families Served: The testimonial focuses on helping adolescent girls with menstrual hygiene and sensitizing the broader community, but it does not describe support directed at households or family units. Any reference to men or adults is general community outreach rather than family-focused intervention, so only minimal alignment with the ‘Families Served’ concept. | Parsing failed for concept 'Families Served' | Marginalized Groups Served: The CHW describes supporting adolescent girls who experience 'menstrual poverty'—a form of structural exclusion that limits their access to basic hygiene products and exposes them to transactional sex and teenage pregnancy. The testimonial explicitly focuses on providing resources (pads) and advocacy for this underserved, stigmatized group, matching the concept’s inclusion criteria. The alignment is strong but not absolutely unambiguous (no mention of other recognized marginalized categories), hence 0.8 rather than 1.0. | Financial Hardship: The testimonial describes 'menstrual poverty'—girls who are unable to obtain basic menstrual products. This is a clear case of material scarcity and inability to afford essential health items, matching the concept definition and inclusion criteria for Financial Hardship. | Social Isolation: The testimonial focuses on menstrual poverty and its consequences rather than on girls being lonely, abandoned, or cut off socially. While there is some implicit lack of material support, there is no explicit mention of living alone, loneliness, or absence of social networks, so only a very weak alignment with the social-isolation concept. | Disease Burden: The testimonial discusses menstrual poverty and teenage pregnancy—social and reproductive health challenges, but not chronic illnesses or disabilities as defined by the Disease Burden concept. There is no reference to long-term disease management (e.g., diabetes, HIV) or recurrent illness episodes. Thus, only a very weak alignment, mainly because menstruation recurs, but it is not classified here as an illness. | Stigma or Discrimination: The testimonial hints that menstruation is often viewed solely as a “woman issue,” leading the CHW to sensitize men and adults—suggesting an undercurrent of stigma toward menstruation. However, there is no explicit description of girls being shamed, rejected, or discriminated against; the focus is primarily on poverty and lack of supplies. Therefore, only minimal, indirect evidence of stigma is present, warranting a low score. | Mental or Emotional Distress: The testimonial focuses on menstrual poverty, teenage pregnancy, and community action. While the term \ | Lack of Resources: The CHW describes ‘menstrual poverty,’ noting that girls lack sanitary towels and that she had to partner with others to fund-raise for pads. This indicates insufficient supplies to address the problem, fitting the definition of lacking resources. The alignment is moderate–strong because the need for supplies is clear, but it is not as explicit or urgent as the medicine shortage example. | Systemic Barriers: The testimonial highlights 'menstrual poverty'—a broader socioeconomic condition where girls lack access to sanitary products—leading them to transactional sex and unwanted pregnancies. This shortage of essential health supplies is outside the CHW’s control and represents a systemic issue impeding health, matching the concept’s definition and inclusion criteria. Hence, a strong (but not perfect) alignment score of 0.8 is appropriate. | Overburdened CHWs: The CHW recounts reaching more than 50 girls, but never expresses feeling exhausted, overextended, or overwhelmed. There is no clear statement of excessive workload; thus evidence for CHW overburden is minimal to none, warranting a very low score. | Lack of Follow-Through: The CHW describes identifying menstrual poverty, partnering with others, fundraising for pads, and seeing positive impact. There is no indication that the efforts were abandoned or left unresolved; rather, the activities continued and yielded results. Therefore, the concept of 'Lack of Follow-Through' is not present. | Lack of Knowledge: The testimonial discusses menstrual poverty and actions taken by the CHW (fund-raising, sensitization), but it does not indicate that the CHW lacked knowledge or requested additional training. Therefore, the concept is not present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Menstrual Hygiene/Teenage Pregnancy Many teenage adolescent girls and young women suffer from what we call menstrual poverty. Menstrual poverty is an incidence whereby a girl is not able to get access to menstrual aids such as sanitary towels and menstrual cups. At the beginning of December, teenage pregnancy rapid growth raised an alarm whereby many individuals and like-minded individuals came together to find out why most of our teenage girls are getting pregnant. The 16-day activism and activism that brought about ??????? for Google meets and physical meetings helped me reach out to more than 50 girls and had some chit chats. From the interactions, I found out that menstrual poverty is a major leading factor in this lack of sanitary towels during this time of the month forcing some girls to engage in transactional sex which back to these unwanted teenage pregnancies. From this I, as a CHW, decided to partner with other ??? and individuals to fundraise for pads to give these girls. This has helped reduce and prevent some if not all. Most men and adults too have been sensitized by me that menstruation is not a woman issue but a human issue and we should all support our girls during this time of the month. ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.2,
+  "Menstrual Hygiene Education and Challenges": 0.9,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.0,
+  "Water Quality, Sanitation, and Hygiene": 0.3,
+  "Personal Disease Management and Adherence": 0.0,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.7,
+  "Gender-Based Violence (GBV) and Child Protection": 0.6,
+  "Health Literacy and Misconceptions": 0.7,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.8,
+  "Community Empowerment Through Education": 0.7,
+  "Resource and Material Distribution": 0.7,
+  "Monitoring and Follow-Up": 0.2,
+  "Trust and Cultural Mediation": 0.7,
+  "Clinical Interventions by CHWs": 0.0,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.7,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.9,
+  "Elderly Served": 0.0,
+  "Women Served": 0.9,
+  "Men Served": 0.3,
+  "Families Served": 0.2,
+  "Marginalized Groups Served": 0.8,
+  "Financial Hardship": 0.9,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.1,
+  "Stigma or Discrimination": 0.3,
+  "Mental or Emotional Distress": 0.2,
+  "Lack of Resources": 0.8,
+  "Systemic Barriers": 0.7,
+  "Overburdened CHWs": 0.1,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial shows a CHW taking initiative and conducting outreach activities, but there is no mention of receiving training, attending workshops, or gaining knowledge through formal CHW programs. The CHW appears to be learning through direct community interactions and self-directed investigation rather than structured training. This aligns with the example 'I started giving advice to neighbors based on what I learned informally' which scores 0.2. | Menstrual Hygiene Education and Challenges: Strong direct alignment with the concept. The testimonial explicitly discusses 'menstrual poverty' as lack of access to menstrual products (sanitary towels, menstrual cups), describes education efforts reaching 50+ girls, addresses the stigma by sensitizing men that 'menstruation is not a woman issue but a human issue,' and details community awareness initiatives. The CHW's fundraising for pads and education efforts directly match the inclusion criteria. | Drug Abuse: Environment and Awareness: The testimonial focuses entirely on menstrual poverty and teenage pregnancy, with no mention of drug abuse, substance use, addiction, or alcohol. While it discusses social and environmental factors contributing to a health issue (transactional sex due to lack of sanitary products), these factors are unrelated to substance abuse. The concept specifically requires content about drugs, alcohol, or addiction in a social/environmental context, which is completely absent from this testimonial. | CHW-Led Infectious Disease Management: This testimonial focuses entirely on menstrual hygiene, menstrual poverty, and teenage pregnancy prevention. There is no mention of infectious diseases, disease symptoms, prevention measures, or any content related to TB, COVID-19, or other communicable diseases. The CHW's work involves reproductive health education and providing menstrual products, which falls outside the scope of infectious disease management. | Water Quality, Sanitation, and Hygiene: The testimonial discusses menstrual hygiene and sanitary products, which relates to hygiene but not specifically to water quality, water treatment, or community sanitation practices. While menstrual hygiene is a form of sanitation, the focus is on access to menstrual products rather than water-based hygiene practices or sanitation infrastructure, placing it in the weak alignment range. | Personal Disease Management and Adherence: This testimonial focuses on menstrual poverty and teenage pregnancy prevention through education and resource provision. There is no mention of disease diagnosis, treatment adherence, or management of chronic/infectious conditions. The work described is about reproductive health education and providing menstrual products, which falls outside the disease management context required by this concept. | Nutrition Education and Food Access: The testimonial focuses entirely on menstrual hygiene, menstrual poverty, and teenage pregnancy prevention. There is no mention of food, nutrition, healthy eating, or food access issues. The content explicitly deals with access to menstrual products and reproductive health education, which falls outside the scope of nutrition education and food access. | Sexual and Reproductive Health Education: The testimonial demonstrates moderate alignment with sexual and reproductive health education. While it doesn't explicitly mention STI prevention or condoms, it addresses teenage pregnancy prevention through tackling menstrual poverty, which leads to transactional sex. The CHW's work in sensitizing communities about menstruation and its connection to unwanted pregnancies shows reproductive health education, though the focus is more on the social determinants rather than direct education about safe sex practices or family planning methods. | Gender-Based Violence (GBV) and Child Protection: The testimonial discusses teenage girls engaging in transactional sex due to menstrual poverty, which leads to unwanted pregnancies. While this involves exploitation and vulnerability of minors, it doesn't explicitly describe direct violence, abuse, or CHW interventions specifically for GBV. The focus is primarily on menstrual health and poverty as root causes, with the exploitative situations being a consequence rather than the main topic. | Health Literacy and Misconceptions: The testimonial reveals a significant misconception that menstruation is 'a woman issue' rather than 'a human issue,' which the CHW actively corrects through sensitization. This directly aligns with the concept's focus on correcting misbeliefs and improving health literacy. The CHW educates men and adults about menstruation, addressing knowledge gaps that affect health support systems. While not about disease origins or medical mistrust, it demonstrates how lack of knowledge (viewing menstruation as only a women's concern) impacts health outcomes and support. | Parsing failed for concept 'Health Literacy and Misconceptions' | Mental Health Awareness and Support: The testimonial focuses entirely on menstrual poverty, teenage pregnancy, and physical health needs (access to sanitary products). While these issues may have mental health implications, the CHW does not mention any psychological well-being aspects, emotional support, or mental health concerns like depression, anxiety, or trauma. The intervention described is purely about providing material support (sanitary pads) and education about menstruation, not mental health awareness or support. | Referrals and Advocacy: Strong alignment with advocacy role. The CHW advocates for teenage girls facing menstrual poverty, organizes meetings to address the issue, partners with others to fundraise for sanitary products, and sensitizes the community about menstruation as a human issue. While not traditional healthcare referrals, this demonstrates clear advocacy and navigation of resources to address a health-related problem. | Community Empowerment Through Education: The testimonial shows moderate alignment with community empowerment through education. The CHW conducted educational outreach to over 50 girls about menstrual health and sensitized men and adults that menstruation is a 'human issue.' This demonstrates community-wide education efforts. However, while the CHW mentions helping 'reduce and prevent some if not all' teenage pregnancies through pad distribution, there's limited evidence of sustained behavior change or community self-reliance beyond the immediate intervention. The focus is more on addressing immediate needs (pad distribution) than creating long-term educational empowerment. | Resource and Material Distribution: The testimonial shows moderate alignment with resource distribution. The CHW identifies menstrual poverty and lack of sanitary products as a critical issue, and explicitly mentions partnering with others to 'fundraise for pads to give these girls.' While the actual distribution is implied rather than directly described (unlike the example 'I distributed malaria nets'), the intent and action to provide material resources (sanitary pads) is clear. The score is not higher because the testimonial focuses more on the problem identification and fundraising efforts rather than detailing the actual distribution process. | Parsing failed for concept 'Resource and Material Distribution' | Monitoring and Follow-Up: The testimonial describes initial outreach and interactions with teenage girls about menstrual poverty, but provides no evidence of ongoing monitoring or follow-up visits. The CHW mentions having 'chit chats' with over 50 girls and fundraising for pads, but these appear to be one-time interventions rather than sustained follow-up care. There is no mention of returning to check on the girls' progress or adjusting support based on their needs over time. | Trust and Cultural Mediation: The testimonial shows moderate alignment with trust-building and cultural mediation. The CHW engaged in sensitive conversations with over 50 girls about menstrual poverty and teenage pregnancy, which requires establishing trust. They also worked to change cultural attitudes by sensitizing men and adults that 'menstruation is not a woman issue but a human issue,' demonstrating cultural mediation. However, the focus is more on addressing a social/economic barrier (menstrual poverty) than explicitly navigating cultural or linguistic barriers or building community trust in health systems. | Parsing failed for concept 'Trust and Cultural Mediation' | Clinical Interventions by CHWs: The testimonial describes health education, advocacy, and resource distribution (fundraising for sanitary pads) but contains no evidence of direct clinical interventions. The CHW conducts meetings, conversations, and sensitization activities - all of which fall under health education rather than clinical care. According to the exclusion criteria, 'health education or referrals without direct clinical interaction' are explicitly excluded from this concept. | Parsing failed for concept 'Clinical Interventions by CHWs' | Mother and Infant Care: This testimonial focuses on menstrual hygiene and teenage pregnancy prevention, not on prenatal, childbirth, postpartum, or infant care. While it mentions pregnancy, it's about preventing unwanted teenage pregnancies rather than supporting mothers during pregnancy or caring for infants. The content falls under general women's health support, which is explicitly excluded from this concept. | Successful Outcomes: The testimonial shows moderate alignment with successful outcomes. The CHW identified menstrual poverty as a root cause of teenage pregnancy, reached out to 50+ girls, partnered with others to fundraise for pads, and reports this 'helped reduce and prevent some if not all' pregnancies. While there's clear positive action and some impact mentioned, the outcomes are somewhat vague ('some if not all') and lack specific metrics of improvement, preventing a higher score. | Material or Training Requests: While the testimonial describes a lack of menstrual aids and the CHW's fundraising efforts to address this need, there is no explicit request for materials or training. The CHW describes actions already taken (partnering and fundraising) rather than asking for help. Per the exclusion criteria, descriptions of what CHWs lack without an explicit request do not qualify. | Children Served: Strong direct alignment. The CHW explicitly mentions reaching out to 'more than 50 girls' who are 'teenage adolescent girls' (minors under 18). The testimonial describes direct support provided through education about menstrual hygiene, addressing teenage pregnancy issues, and fundraising for sanitary pads. This clearly demonstrates CHW involvement in health and safety support for children/adolescents. | Elderly Served: The testimonial focuses exclusively on teenage girls and young women experiencing menstrual poverty and teenage pregnancy. There is no mention of elderly people, seniors, or grandparents, nor any CHW assistance provided to older adults. The entire narrative centers on adolescent reproductive health issues. | Women Served: Strong direct alignment with the concept. The CHW directly served over 50 teenage girls and young women through education and support around menstrual health. The testimonial describes specific CHW interactions including 'chit chats' with girls about menstrual poverty, fundraising for sanitary products, and sensitizing the community about menstruation. This clearly demonstrates assistance and education for women around health challenges, matching the inclusion criteria perfectly. | Men Served: The testimonial mentions that 'most men and adults too have been sensitized by me that menstruation is not a woman issue but a human issue.' This shows the CHW educated men about menstrual health support, but men are not the primary beneficiaries - they are being educated to support girls/women. This represents weak alignment as men are mentioned in a support context but not as direct service recipients. | Families Served: The testimonial focuses on individual teenage girls and young women rather than family units. While the CHW mentions sensitizing 'men and adults' who could be family members, there's no explicit mention of working with families, parents, or household units. The intervention is primarily targeted at individuals (50+ girls) rather than family-focused support. | Marginalized Groups Served: Strong alignment with the concept. The testimonial describes CHW support for teenage girls experiencing 'menstrual poverty' - a form of structural exclusion where girls lack access to basic menstrual products. This marginalization leads to transactional sex and unwanted pregnancies. The CHW provided direct support through education, fundraising for sanitary products, and community sensitization to reduce stigma around menstruation. While not explicitly using terms like 'marginalized,' the description clearly shows support for an underserved, vulnerable population facing both economic barriers and social stigma. | Financial Hardship: The testimonial directly describes 'menstrual poverty' where girls cannot afford basic sanitary products, leading them to engage in transactional sex. This clearly demonstrates inability to afford basic needs (menstrual aids), which aligns strongly with the concept definition of being unable to afford basic necessities. The CHW's response of fundraising for pads further confirms the financial nature of the hardship. | Social Isolation: The testimonial focuses on menstrual poverty and teenage pregnancy issues, with no mention of loneliness, living alone, lack of support systems, or abandonment. The CHW describes community engagement, meetings, and partnerships - indicating social connection rather than isolation. The concept of Social Isolation is not present in this testimonial. | Disease Burden: The testimonial focuses on menstrual poverty and teenage pregnancy prevention, which are public health issues but not chronic illnesses or disabilities. While these issues have significant health impacts, they don't align with the concept's definition of 'chronic illness, disability, or frequent illness episodes.' The score of 0.1 reflects minimal alignment, similar to the example 'I spoke with community members about general wellness.' | Stigma or Discrimination: The testimonial indirectly touches on stigma through the mention of menstruation being viewed as 'a woman issue' that needs to be reframed as 'a human issue,' suggesting some social judgment exists around menstruation. However, the focus is primarily on poverty and lack of resources rather than social rejection or shame. The testimonial does not explicitly describe girls being shunned, excluded, or judged by their communities for menstruation or pregnancy. | Parsing failed for concept 'Stigma or Discrimination' | Mental or Emotional Distress: While the testimonial focuses primarily on menstrual poverty and teenage pregnancy as public health issues, there is minimal direct evidence of mental or emotional distress. The CHW describes practical challenges (lack of sanitary products) and behavioral outcomes (transactional sex), but does not explicitly mention feelings of depression, hopelessness, trauma, or emotional overwhelm among the affected girls. The distress implied is more situational and physical rather than explicitly emotional or mental. | Lack of Resources: Strong alignment with the concept. The testimonial explicitly describes 'menstrual poverty' where girls cannot access menstrual aids like sanitary towels and cups. While the CHW found a solution through fundraising and partnerships, the core issue identified is the lack of resources (sanitary products) that forces girls into transactional sex. This directly matches the inclusion criteria of 'CHWs having insufficient supplies.' | Systemic Barriers: The testimonial describes menstrual poverty as a systemic issue where girls cannot access menstrual aids, leading to transactional sex and teenage pregnancy. This represents a moderate alignment with systemic barriers - the lack of access to basic hygiene products is a structural/institutional failure beyond CHW control. However, the CHW was able to organize fundraising and partnerships to address it, suggesting the barriers were not completely insurmountable, which prevents a higher score. | Overburdened CHWs: The testimonial describes a CHW who identified a community problem and took initiative to address it through partnerships and fundraising. While they reached out to 50+ girls and conducted sensitization activities, there is no indication of being overwhelmed, exhausted, or having excessive workload. The CHW appears proactive and capable of managing their activities successfully, which aligns with the exclusion criteria of 'busy CHWs who were still able to deliver care successfully.' | Lack of Follow-Through: The testimonial describes a CHW who identified a problem (menstrual poverty leading to teenage pregnancy), took action through meetings and outreach, and successfully partnered with others to fundraise for pads. The CHW reached over 50 girls and sensitized the community. This shows completed action and ongoing support, not abandonment or unresolved issues. The concept explicitly excludes cases where care was ultimately provided. | Lack of Knowledge: The testimonial shows no evidence of the CHW lacking knowledge or being unable to address issues due to skill gaps. Instead, the CHW demonstrates competence by identifying the root cause of teenage pregnancy (menstrual poverty), conducting outreach to over 50 girls, and implementing solutions through fundraising and sensitization. The CHW shows initiative and problem-solving skills rather than any knowledge deficits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Malaria Malaria is a disease caused by a parasite called plasmodium parasite, transmitted by the bite of infected Anopheles mosquitos. Malaria spreads by animal or insect bites or stings and by blood products (unclean needles or unscreened blood). The physical symptoms are like fever, vomiting, headache, yellow skin, diarrhea, fatigue, kidney failure, seizure/confusion, sweating, muscle aches, chest pain, chills that shake the whole body, dizziness and severe symptoms such as paralysis. Therefore, in any case I feel these symptoms, some of them, not all because I may not go through all of the symptoms. Why? It may happen from time to time. It is advisable that the moment it starts, I will force myself to go to the hospital for a check-up because that is the right place for me to get treatment. Hence, it will also help me to avoid it to become severe. Malaria even treated can re-occur again and again, so it is good to take action immediately before danger. I do advise people with malaria symptoms to go for a test before taking any painkiller, because this can cause danger. I also take an action by taking some of them in hospitals so that they can get treatment. I assure them to finish the malaria dose and treatment to avoid it from reoccurring again after a short time. On the prevention side part of it, I avoid mosquito bites by using insect repellent, hence tell the community to do net. You also have to wear long-sleeved clothing and long pants if you are outdoors at night. For pregnant mothers, I tell them to go for check-up whenever they feel the symptoms because malaria affects her and the fetus. It can lead to maternal anemia, fetal loss, premature delivery, and delivery of low-birth-weight infants. So many people have died because of malaria and what causes this is ignorance. Some of the patients ignore the symptoms and also take wrong medication before tests, leading to severe infections hence death. It is good to love yourself, love and protect your life because it is given once by our creator who is God. Observe cleanliness at all cost to prevent more infections from occurring. ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.2,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.9,
+  "Water Quality, Sanitation, and Hygiene": 0.1,
+  "Personal Disease Management and Adherence": 0.9,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.1,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.6,
+  "Mental Health Awareness and Support": 0.05,
+  "Referrals and Advocacy": 0.9,
+  "Community Empowerment Through Education": 0.4,
+  "Resource and Material Distribution": 0.2,
+  "Monitoring and Follow-Up": 0.3,
+  "Trust and Cultural Mediation": 0.2,
+  "Clinical Interventions by CHWs": 0.2,
+  "Mother and Infant Care": 0.55,
+  "Successful Outcomes": 0.4,
+  "Material or Training Requests": 0.05,
+  "Children Served": 0.2,
+  "Elderly Served": 0.0,
+  "Women Served": 0.85,
+  "Men Served": 0.0,
+  "Families Served": 0.2,
+  "Marginalized Groups Served": 0.1,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.75,
+  "Stigma or Discrimination": 0.05,
+  "Mental or Emotional Distress": 0.0,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.05,
+  "Lack of Knowledge": 0.05
+}</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial shows the speaker providing malaria education and advice, but it never mentions the CHW having attended any training, workshop, or other capacity-building event. The knowledge could be informal. This fits only minimal evidence of the concept, similar to the provided 0.2 example where advice is given without training. | Menstrual Hygiene Education and Challenges: The testimonial focuses solely on malaria symptoms, treatment, and prevention. It does not mention menstruation, menstrual products, or related stigma or education; thus the concept is not applicable. | Drug Abuse: Environment and Awareness: The testimonial focuses solely on malaria symptoms, treatment, and prevention without any mention of substance abuse, addiction, alcohol, peer pressure, or environmental/social factors related to drug use. Therefore the concept is not present. | CHW-Led Infectious Disease Management: The speaker describes advising community members about malaria symptoms, promoting testing, escorting them to hospitals, ensuring completion of treatment, and teaching preventive measures such as nets and repellents. These actions align directly with CHW-led outreach and education for an infectious disease. While the role ‘CHW’ is not named explicitly, the activities match the inclusion criteria (explaining symptoms, prevention, follow-up), warranting a strong but slightly less than perfect score. | Water Quality, Sanitation, and Hygiene: The testimonial focuses on malaria prevention, symptoms, testing, and mosquito-bite avoidance. Apart from a vague statement urging people to 'observe cleanliness,' there is no discussion of water quality, hand-washing, sanitation practices, or hygiene education linked to water. According to the concept’s exclusion criteria, generic personal cleanliness without a water or sanitation context provides only minimal evidence. | Personal Disease Management and Adherence: The speaker focuses on managing malaria: recognizing symptoms, seeking prompt diagnosis at the hospital, ensuring patients \ | Nutrition Education and Food Access: The testimonial focuses exclusively on malaria symptoms, treatment, and prevention without any mention of healthy eating, food insecurity, or nutrition education, so the concept is not present. | Sexual and Reproductive Health Education: The testimonial focuses on malaria symptoms, treatment, and prevention. It briefly references pregnant mothers being affected by malaria, but provides no education on family planning, STIs, HIV, condoms, or reproductive rights. This is only a tangential mention of pregnancy without sexual/reproductive health education content, giving a very weak alignment with the concept. | Gender-Based Violence (GBV) and Child Protection: The testimonial exclusively discusses malaria symptoms, treatment, and prevention with no reference to abuse, violence, exploitation, or child protection issues, which are required for this concept. | Health Literacy and Misconceptions: The speaker notes that many people die because of 'ignorance,' that some patients ignore symptoms, and that they take the wrong medication before proper testing—illustrating how lack of knowledge or misconceptions affect health outcomes. While the testimonial mainly gives correct information, these references provide moderate evidence of the concept. | Parsing failed for concept 'Health Literacy and Misconceptions' | Mental Health Awareness and Support: The testimonial focuses entirely on the physical aspects, prevention, and treatment of malaria. There is no mention of psychological well-being, depression, anxiety, or emotional support. The brief encouragement to \ | Referrals and Advocacy: The speaker explicitly advises community members with malaria symptoms to go for testing and states that they sometimes take people to the hospital so they can receive treatment, which matches the concept of CHWs facilitating referrals and navigating care. This is a strong, direct example of advocacy and referral within the health system, aligning closely with the definition and highest-scoring example. | Community Empowerment Through Education: The testimonial centers on the CHW giving malaria information and advice (e.g., urging testing, bed-net use, hospital visits). This fits the inclusion of providing health education to the community, but there is no evidence that the community has adopted new habits, engaged in peer education, or shown long-term change. Thus it shows isolated education without demonstrated empowerment, corresponding to a weak–moderate alignment (similar to the 0.4 example in the guideline). | Resource and Material Distribution: The testimonial focuses mostly on advising people to seek testing, complete treatment, and use preventive measures like bed nets and insect repellent. While nets and repellent are mentioned, there is no clear statement that the CHW actually hands out these items. This provides only minimal evidence of material distribution, so a low score (weak alignment) is appropriate. | Monitoring and Follow-Up: The testimonial mainly provides health education and urges people to seek testing and complete treatment. Apart from saying the CHW \ | Trust and Cultural Mediation: The CHW provides health education and advises community members to seek testing and complete treatment, but there are no explicit references to translating, overcoming cultural or linguistic barriers, or specific actions aimed at building trust. The testimonial shows some general encouragement and reassurance, which gives minimal evidence of trust‐building, hence a weak alignment. | Clinical Interventions by CHWs: The testimonial mainly describes educating others about malaria symptoms and advising them to seek care. It lacks clear statements that the CHW personally administers medicine, performs tests, or treats wounds. The only potentially relevant sentence—\ | Mother and Infant Care: The testimonial primarily discusses malaria prevention and treatment, but it contains a clear segment advising pregnant mothers to seek check-ups because malaria harms both mother and fetus (maternal anemia, fetal loss, low-birth-weight). This aligns with the concept’s inclusion criteria of support during pregnancy, yet the focus on mother/infant care is brief and secondary to the broader malaria content, so a moderate score is appropriate. | Successful Outcomes: The testimonial describes advising people with malaria symptoms, escorting some to the hospital, and encouraging them to complete treatment, but it does not report specific recoveries or measurable improvements. This is similar to the inclusion example where a referral is made without confirmed outcome (scored 0.4), indicating only weak-to-moderate evidence of successful outcomes. | Material or Training Requests: The testimonial provides information about malaria symptoms, treatment, and prevention but contains no explicit requests for supplies, materials, or additional training. Thus it shows virtually no alignment with the concept. | Children Served: The testimonial focuses on general malaria education and advises pregnant mothers about risks to the fetus and low-birth-weight infants. This only indirectly references children and does not describe direct service or support to minors, giving weak evidence for the concept. | Elderly Served: The testimonial discusses malaria education and prevention generally and specific advice for pregnant mothers, without any mention of older adults or seniors. Therefore, the concept of 'Elderly Served' is not present. | Women Served: The CHW explicitly describes advising pregnant mothers—adult women—about malaria symptoms, check-ups, and risks to mother and fetus. This is direct health education targeted to women, matching the concept’s inclusion criteria. Although women are not the sole focus of the testimonial, the clear, gender-specific guidance warrants a strong alignment score. | Men Served: The testimonial discusses malaria prevention and treatment generally and specifically addresses pregnant mothers, but it does not mention adult males or boys or provide gender-specific support for men. Therefore, the concept is not present. | Families Served: The testimonial is largely about malaria education and prevention in the general community. The only family-related reference is advising pregnant mothers for the sake of both mother and fetus, which lightly implies a parent–child unit. There is no direct mention of households or supporting multiple family members, so evidence of a family-focused intervention is minimal, warranting a low score. | Marginalized Groups Served: The testimonial discusses general malaria education and mentions the community and pregnant mothers, but it does not identify these populations as marginalized or describe structural or social exclusion. Minimal evidence that the CHW is specifically serving a stigmatized or underserved group. | Financial Hardship: The testimonial discusses malaria symptoms, treatment, and prevention but makes no reference to inability to afford care, lack of income, transportation costs, or any material scarcity. Therefore, the Financial Hardship concept is not present. | Social Isolation: The testimonial focuses solely on malaria symptoms, treatment, and prevention advice. It does not mention living alone, loneliness, lack of support, or abandonment, so the Social Isolation concept is not applicable. | Disease Burden: The testimonial focuses on malaria, describing how it can \ | Stigma or Discrimination: The testimonial focuses on malaria symptoms, treatment, and prevention without mentioning social judgment, shame, or exclusion toward people with malaria. There is essentially no evidence of stigma or discrimination, so the score is very low. | Mental or Emotional Distress: The testimonial focuses on physical symptoms, treatment, and prevention of malaria with no mention of feelings of depression, stress, hopelessness, or any other emotional distress. Therefore, the concept is not present. | Lack of Resources: The testimonial discusses malaria education, prevention, and encouraging hospital visits but never mentions lacking medicines, tools, or support. Therefore, the concept of resource shortages is not present. | Systemic Barriers: The testimonial focuses on malaria education, personal preventive actions, and encouraging timely hospital visits. It does not describe shortages, institutional obstacles, distance, corruption, or any other larger systemic conditions that hinder care. Therefore the concept of Systemic Barriers is not present. | Overburdened CHWs: The testimonial discusses malaria education and advising patients but does not mention workload, exhaustion, or feeling overwhelmed. Therefore, there is no evidence of CHWs being overburdened. | Lack of Follow-Through: The testimonial mainly provides malaria education and encourages complete treatment. It mentions accompanying some patients to the hospital and ensuring they finish their dose, suggesting follow-through rather than abandonment. There is virtually no evidence of a started but unresolved intervention, so alignment with the concept is minimal. | Lack of Knowledge: The testimonial demonstrates the CHW providing detailed information and advice about malaria; there is no statement that the CHW is unsure, lacks knowledge, or needs additional training. The only reference to \</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Malaria Malaria is a disease caused by a parasite called plasmodium parasite, transmitted by the bite of infected Anopheles mosquitos. Malaria spreads by animal or insect bites or stings and by blood products (unclean needles or unscreened blood). The physical symptoms are like fever, vomiting, headache, yellow skin, diarrhea, fatigue, kidney failure, seizure/confusion, sweating, muscle aches, chest pain, chills that shake the whole body, dizziness and severe symptoms such as paralysis. Therefore, in any case I feel these symptoms, some of them, not all because I may not go through all of the symptoms. Why? It may happen from time to time. It is advisable that the moment it starts, I will force myself to go to the hospital for a check-up because that is the right place for me to get treatment. Hence, it will also help me to avoid it to become severe. Malaria even treated can re-occur again and again, so it is good to take action immediately before danger. I do advise people with malaria symptoms to go for a test before taking any painkiller, because this can cause danger. I also take an action by taking some of them in hospitals so that they can get treatment. I assure them to finish the malaria dose and treatment to avoid it from reoccurring again after a short time. On the prevention side part of it, I avoid mosquito bites by using insect repellent, hence tell the community to do net. You also have to wear long-sleeved clothing and long pants if you are outdoors at night. For pregnant mothers, I tell them to go for check-up whenever they feel the symptoms because malaria affects her and the fetus. It can lead to maternal anemia, fetal loss, premature delivery, and delivery of low-birth-weight infants. So many people have died because of malaria and what causes this is ignorance. Some of the patients ignore the symptoms and also take wrong medication before tests, leading to severe infections hence death. It is good to love yourself, love and protect your life because it is given once by our creator who is God. Observe cleanliness at all cost to prevent more infections from occurring. ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.0,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.85,
+  "Water Quality, Sanitation, and Hygiene": 0.1,
+  "Personal Disease Management and Adherence": 0.8,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.1,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.7,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.8,
+  "Community Empowerment Through Education": 0.6,
+  "Resource and Material Distribution": 0.1,
+  "Monitoring and Follow-Up": 0.2,
+  "Trust and Cultural Mediation": 0.7,
+  "Clinical Interventions by CHWs": 0.4,
+  "Mother and Infant Care": 0.3,
+  "Successful Outcomes": 0.7,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.8,
+  "Men Served": 0.0,
+  "Families Served": 0.1,
+  "Marginalized Groups Served": 0.0,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.8,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.0,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial describes malaria symptoms, prevention methods, and the speaker's role in advising and helping community members seek treatment. However, there is no mention of the speaker receiving any CHW training, attending workshops, or gaining knowledge through formal or informal CHW programs. The speaker demonstrates knowledge and community health activities but does not reference how this capacity was developed through training. | Menstrual Hygiene Education and Challenges: The testimonial focuses entirely on malaria - its causes, symptoms, treatment, and prevention. There is no mention of menstruation, menstrual hygiene, sanitary products, or any related education or challenges. The content explicitly excludes the concept as it discusses a completely different health topic. | Drug Abuse: Environment and Awareness: The testimonial focuses entirely on malaria - its causes, symptoms, treatment, and prevention. There is no mention of drug abuse, addiction, alcohol, peer influence, or substance-related education. The only reference to 'drugs' is in the context of proper medical treatment (avoiding painkillers before testing). This is a clinical health education piece about an infectious disease, not about substance abuse or its social/environmental factors. | CHW-Led Infectious Disease Management: Strong direct alignment. The testimonial clearly demonstrates CHW involvement in malaria management through: educating the community about symptoms and prevention ('I do advise people with malaria symptoms'), taking direct action by accompanying patients to hospitals ('I also take an action by taking some of them in hospitals'), providing follow-up guidance on treatment completion, and educating on prevention methods (insect repellent, nets, protective clothing). The CHW shows comprehensive engagement in disease education, prevention, and care coordination, matching the concept's focus on CHW-led infectious disease management. | Water Quality, Sanitation, and Hygiene: The testimonial focuses almost entirely on malaria transmission, symptoms, and treatment. The only mention related to this concept is a brief statement to 'Observe cleanliness at all cost to prevent more infections from occurring' at the very end. This is a vague reference to cleanliness without specific connection to water, sanitation practices, or hygiene education, matching the example 'I tell people to stay clean' which scores 0.1. | Personal Disease Management and Adherence: Strong alignment with the concept. The testimonial extensively discusses malaria management including: seeking immediate medical care when symptoms appear, completing full treatment doses to prevent recurrence, avoiding self-medication before testing, and helping community members access treatment. While the CHW focuses more on advising others rather than personal disease management, the emphasis on treatment adherence and proper disease management through medical consultation aligns well with the concept definition. | Nutrition Education and Food Access: The testimonial focuses entirely on malaria - its causes, symptoms, treatment, and prevention. There is no mention of nutrition education, food access, healthy eating, or any food-related topics. The content is exclusively about disease management and prevention, making it a clear non-match for the Nutrition Education and Food Access concept. | Sexual and Reproductive Health Education: The testimonial focuses entirely on malaria education, prevention, and treatment. The only tangential connection to reproductive health is a brief mention of malaria's effects on pregnant mothers and fetuses, but this is presented as a medical complication rather than reproductive health education. There is no discussion of family planning, STI prevention, HIV awareness, reproductive rights, or any of the inclusion criteria specified in the concept definition. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses entirely on malaria - its causes, symptoms, treatment, and prevention. There is no mention of abuse, violence, exploitation, or any form of GBV or child protection issues. The content is purely about a communicable disease and public health education, which clearly falls outside the scope of this concept. | Health Literacy and Misconceptions: The testimonial demonstrates moderate alignment with health literacy issues. The CHW explicitly mentions that 'many people have died because of malaria and what causes this is ignorance' and describes problematic behaviors like patients taking 'wrong medication before tests.' The CHW actively corrects these misconceptions by advising against taking painkillers before testing and emphasizing proper medical care. While not as direct as the 0.9 example about witchcraft beliefs, this shows clear engagement with health misconceptions and their dangerous consequences. | Mental Health Awareness and Support: This testimonial focuses entirely on malaria as a physical disease - its transmission, symptoms, treatment, and prevention. While it mentions physical symptoms like fever, vomiting, and seizures, there is no discussion of psychological well-being, emotional support, or mental health issues like depression, anxiety, or loneliness. The testimonial is purely medical/physical in nature without any mental or emotional context. | Referrals and Advocacy: Strong direct alignment with the concept. The testimonial explicitly mentions 'I also take an action by taking some of them in hospitals so that they can get treatment' which demonstrates direct referral activity. Additionally, the speaker advises people with malaria symptoms to go for tests and tells pregnant mothers to go for check-ups, showing advocacy for healthcare navigation. While not explicitly identifying as a CHW, the speaker clearly acts as an intermediary helping people access healthcare services. | Community Empowerment Through Education: The testimonial shows moderate alignment with community empowerment through education. The CHW demonstrates educational efforts by advising people about malaria symptoms, proper testing before medication, and prevention methods. They also take direct action by accompanying community members to hospitals. However, there's no clear evidence of long-term behavior change, self-reliance development, or community-wide transformation. The focus is more on individual interventions and advice-giving rather than sustained community empowerment or peer education networks. | Resource and Material Distribution: The testimonial focuses entirely on malaria education, symptoms, prevention advice, and encouraging hospital visits. While the CHW mentions 'taking some of them in hospitals' (accompanying people), there is no mention of distributing any physical resources like mosquito nets, medication, or health kits. The content is purely educational and advisory, which falls under the exclusion criteria. | Monitoring and Follow-Up: The testimonial shows minimal evidence of monitoring and follow-up. While the CHW mentions 'I assure them to finish the malaria dose and treatment to avoid it from reoccurring again,' this appears to be advice given during initial interactions rather than ongoing follow-up visits. The CHW describes taking people to hospitals and providing education, but there's no clear indication of returning to check on patients' progress or adjusting care based on follow-up visits. The focus is primarily on initial intervention and education rather than sustained monitoring. | Trust and Cultural Mediation: The testimonial shows moderate alignment with trust-building and cultural mediation. The CHW mentions 'I do advise people with malaria symptoms' and 'I also take an action by taking some of them in hospitals,' indicating direct community engagement. The phrase 'I assure them to finish the malaria dose' suggests trust-building through reassurance. However, there's no explicit mention of overcoming cultural barriers, translating, or addressing community mistrust of healthcare systems, which prevents a higher score. | Parsing failed for concept 'Trust and Cultural Mediation' | Clinical Interventions by CHWs: The testimonial shows weak alignment with clinical interventions. While the CHW mentions 'taking some of them in hospitals' which suggests physical assistance, there is no description of direct medical tasks like administering medication, treating wounds, or managing injuries. The focus is primarily on health education about malaria, advising people to seek medical care, and prevention strategies, which aligns with the exclusion criteria of 'health education or referrals without direct clinical interaction.' | Mother and Infant Care: The testimonial primarily focuses on malaria prevention and treatment in the general population. There is only one specific mention of pregnant mothers and the effects of malaria on pregnancy (maternal anemia, fetal loss, premature delivery, low-birth-weight infants). While this shows some alignment with prenatal care concerns, it represents a small portion of the overall content and is presented in the context of malaria education rather than comprehensive mother/infant care support. | Successful Outcomes: The testimonial shows moderate alignment with successful outcomes. The CHW describes taking concrete actions like 'taking some of them in hospitals so that they can get treatment' and ensuring patients 'finish the malaria dose and treatment.' While specific recovery stories aren't provided, the CHW demonstrates active intervention and follow-through with patients, suggesting positive impact even without explicit outcome details. | Material or Training Requests: The testimonial provides detailed information about malaria symptoms, prevention, and the CHW's advisory role, but contains no explicit requests for materials, supplies, or training. While the CHW describes their work educating the community about malaria, they do not ask for any resources to better serve their community, which is required by the concept definition. | Children Served: The testimonial focuses entirely on malaria education and prevention for the general community and pregnant mothers. There is no mention of children, adolescents, or minors under 18 being specifically served or targeted by the CHW's activities. While the content could potentially benefit children, there is no direct evidence of CHW involvement with this age group. | Elderly Served: The testimonial focuses entirely on malaria education, prevention, and treatment. While it mentions helping community members and pregnant mothers, there is no reference to elderly people, seniors, or grandparents. The CHW discusses taking people to hospitals and providing health education, but does not specify working with older adults or addressing age-related needs. | Women Served: Strong direct alignment. The testimonial specifically mentions pregnant mothers as a group the CHW educates about malaria risks and prevention, advising them to seek check-ups when experiencing symptoms. The CHW describes the specific health risks malaria poses to pregnant women and their fetuses (maternal anemia, fetal loss, premature delivery, low-birth-weight infants), demonstrating targeted assistance and education for women around a critical health issue. | Men Served: The testimonial focuses entirely on malaria education, prevention, and treatment without any specific mention of men or boys. While the CHW discusses helping 'people' and 'patients' in general, and mentions pregnant mothers specifically, there is no reference to adult males or boys in any context, let alone in relation to gendered roles, challenges, or support services. | Families Served: The testimonial focuses primarily on malaria education and individual patient care. While there is a brief mention of pregnant mothers and their fetuses, this represents potential family impact rather than direct CHW support for multiple family members or family-focused interventions. The testimonial does not describe visiting households or working with parents and children together, which would align with the concept definition. | Marginalized Groups Served: The testimonial focuses on malaria education and general community health support without any mention of marginalized or stigmatized groups. While the CHW mentions helping pregnant mothers and taking people to hospitals, these are general health services provided to the broader community rather than targeted support for structurally excluded populations. There is no reference to disabled individuals, migrants, minority groups, or any population facing social exclusion or stigma. | Financial Hardship: The testimonial focuses entirely on malaria education, symptoms, treatment, and prevention. There is no mention of financial constraints, inability to afford care, transportation costs, or any economic barriers to healthcare access. The CHW discusses taking people to hospitals and encouraging treatment but does not indicate any financial difficulties faced by patients. | Social Isolation: The testimonial focuses entirely on malaria education, symptoms, treatment, and prevention. There is no mention of loneliness, living alone, lack of support systems, or social abandonment. The CHW discusses medical information and community health practices but does not reference any aspects of social isolation or related care barriers. | Parsing failed for concept 'Social Isolation' | Disease Burden: Strong alignment with Disease Burden concept. The testimonial extensively discusses malaria as a disease that 'can re-occur again and again,' indicating chronic/recurrent illness patterns. The CHW describes serious long-term impacts including death, maternal complications, and the need for ongoing monitoring and treatment. While malaria episodes can be acute, the emphasis on recurrence, severe complications, and ongoing community health management aligns well with the chronic illness aspect of the definition. | Stigma or Discrimination: The testimonial focuses entirely on malaria education, symptoms, treatment, and prevention. There is no mention of social rejection, shame, exclusion, or judgment from others related to having malaria or any other condition. The text is purely informational and supportive, encouraging people to seek medical care without any reference to stigma or discrimination. | Mental or Emotional Distress: This testimonial focuses entirely on malaria as a physical disease - its transmission, symptoms, treatment, and prevention. While it mentions physical symptoms like fever, headache, and fatigue, there is no expression of mental strain, emotional overwhelm, depression, hopelessness, or trauma. The content is educational about malaria management rather than addressing any mental or emotional wellbeing concerns. | Lack of Resources: The testimonial does not mention any lack of resources. The CHW describes educating people about malaria, advising them to seek hospital treatment, and even taking some patients to hospitals. There is no mention of insufficient medicine, tools, or support that would prevent the CHW from addressing the problem. The focus is entirely on education and referral to appropriate medical facilities. | Systemic Barriers: The testimonial focuses entirely on malaria education, symptoms, treatment advice, and prevention strategies. There is no mention of systemic barriers such as health facility shortages, overcrowding, lack of resources, or institutional problems that would prevent the CHW from helping patients. The CHW describes taking patients to hospitals and advising them on treatment without indicating any systemic obstacles to care delivery. | Parsing failed for concept 'Systemic Barriers' | Overburdened CHWs: The testimonial focuses entirely on malaria education, symptoms, treatment, and prevention. There is no mention of the CHW's workload, exhaustion, or being overwhelmed. The CHW describes taking patients to hospitals and providing advice, but gives no indication of being overburdened or having too many patients to manage effectively. | Lack of Follow-Through: The testimonial describes the CHW's comprehensive approach to malaria education and care, including taking patients to hospitals and ensuring they complete treatment. There is no evidence of abandonment, interrupted care, or unresolved issues. The CHW explicitly states they 'assure them to finish the malaria dose and treatment,' indicating follow-through rather than lack thereof. | Lack of Knowledge: The testimonial demonstrates comprehensive knowledge about malaria, including its causes, transmission, symptoms, treatment protocols, and prevention methods. The CHW provides detailed guidance and takes appropriate actions like referring patients to hospitals and ensuring treatment completion. There is no evidence of uncertainty, knowledge gaps, or requests for additional training. The CHW appears confident and well-informed about the condition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Malaria My personal experience about malaria has been very challenging as it affects me periodically and comes unexpectedly. There is a day I fell ill at night while asleep and my symptoms were for malaria because I felt cold with shivering, then developed a high temperature accompanied by severe sweating and headache. In my case, I normally use thermometer to know if am having malaria by checking on my temperature level. If my temperature exceeds 38C or above, then I take painkillers to relief pain, only at night but if I have malaria during the day I go to the hospital. There was a time I had malaria and took Coartem as it is known to reduce malaria faster, then again visited the hospital and it did not reflect that I have malaria as compared to the time when I take painkillers. My advice to people is always to avoid using Coartem without visiting the hospital at first and rather use painkillers to relief pain. After visiting the hospital my eating a bit usually changes, I eat a lot so as to heal faster. In most cases, when I have malaria, it usually comes with migraine, so when I experience such, I take hot strong tea with a lot of sugar, then relax my mind and sleep. When I wake up, I am always free from migraine because I believe my malaria comes with headache followed by migraine. ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.05,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.3,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.85,
+  "Nutrition Education and Food Access": 0.1,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.7,
+  "Mental Health Awareness and Support": 0.05,
+  "Referrals and Advocacy": 0.2,
+  "Community Empowerment Through Education": 0.2,
+  "Resource and Material Distribution": 0.0,
+  "Monitoring and Follow-Up": 0.0,
+  "Trust and Cultural Mediation": 0.0,
+  "Clinical Interventions by CHWs": 0.0,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.15,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.0,
+  "Men Served": 0.0,
+  "Families Served": 0.0,
+  "Marginalized Groups Served": 0.0,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.8,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.1,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.05,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial is a personal account of managing malaria and offering lay advice, but it contains no reference to the speaker being a CHW or receiving any form of training. Thus, alignment with the concept is essentially absent. | Menstrual Hygiene Education and Challenges: The testimonial focuses solely on personal experiences and advice related to malaria management. It contains no mention of menstruation, menstrual products, stigma, or education. Therefore, the concept of Menstrual Hygiene Education and Challenges is not applicable. | Drug Abuse: Environment and Awareness: The testimonial focuses solely on personal experiences with malaria, its symptoms, and treatment decisions (painkillers, Coartem). It contains no mention of substance misuse, addiction, peer influence, or environmental factors related to drug abuse, so the concept is not present. | CHW-Led Infectious Disease Management: The testimonial contains advice about managing an infectious disease (malaria) but does not explicitly state that the speaker is a community health worker providing organized outreach or education. Because CHW involvement is unclear, alignment with the CHW-Led Infectious Disease Management concept is weak. | Water Quality, Sanitation, and Hygiene: The testimonial focuses on personal experiences and treatment of malaria, with no mention of clean water, sanitation practices, hand-washing, or other hygiene education topics. Therefore, the concept is not present. | Personal Disease Management and Adherence: The testimonial centers on how the speaker manages recurring malaria: self-diagnosis with a thermometer, decisions about taking Coartem or painkillers, visiting the hospital, dietary changes, and advice to others on proper treatment. This directly matches the concept’s focus on managing an infectious disease through diagnosis and treatment adherence. The alignment is strong but not perfect (no explicit mention of CHW guidance), hence 0.85. | Nutrition Education and Food Access: The testimonial briefly mentions that the narrator eats more and drinks sweet tea when recovering from malaria, but it does not provide nutrition education, discuss healthy eating, or address food access. This is only a tangential reference to food, so alignment with the concept is very weak. | Sexual and Reproductive Health Education: The testimonial discusses personal experiences with malaria, its symptoms, treatment, and advice on medication. It does not mention condoms, family planning, STI prevention, HIV awareness, or any reproductive-health education topics; therefore, the concept is not present. | Gender-Based Violence (GBV) and Child Protection: The testimonial solely discusses personal experiences with malaria treatment and gives advice on medication; it contains no reference to abuse, violence, child protection issues, or related CHW interventions. | Health Literacy and Misconceptions: The speaker shows partial misinformation about malaria diagnosis and treatment: equating fever alone with malaria, recommending painkillers instead of antimalarials at night, and advising others to avoid using Coartem unless after a hospital visit. These statements reflect misunderstandings affecting health decisions, fitting the concept’s inclusion criteria, though no explicit mention of broader community myths. Hence a moderate alignment score. | Mental Health Awareness and Support: The testimonial focuses on physical experiences and self-management of malaria, with only a fleeting mention of ‘relax my mind’ in relation to migraine relief. There is no discussion of emotional well-being, depression, anxiety, or psychological support, so alignment with the mental health concept is minimal. | Referrals and Advocacy: The speaker offers generic advice urging others to visit the hospital before taking Coartem, which shows minimal advocacy, but there is no clear indication they are acting as a CHW or formally navigating/referring patients within the health system. Aligns weakly with the concept similar to the 0.2 example. | Community Empowerment Through Education: The testimonial offers personal advice about malaria treatment (a form of isolated health education), but it does not describe community-level change, peer education, or evidence of lasting improved habits among others. Therefore, it only weakly aligns with the concept. | Resource and Material Distribution: The testimonial is a personal account of managing malaria and offers advice but does not describe providing or distributing any supplies to others. Therefore, it does not meet the definition or inclusion criteria for Resource and Material Distribution. | Monitoring and Follow-Up: The testimonial is a personal narrative about the author’s own malaria management practices; it does not describe any CHW engaging in ongoing follow-up or returning to check on the individual’s health. Therefore, the concept of Monitoring and Follow-Up is not present. | Trust and Cultural Mediation: The testimonial is a personal account of managing malaria symptoms and offers self-care advice, with no mention of CHWs, trust-building, translation, or cultural mediation activities. | Clinical Interventions by CHWs: The testimonial describes the speaker’s personal self-treatment for malaria (using a thermometer, taking painkillers, Coartem, etc.) without any mention of a community health worker administering or assisting with these clinical tasks. Therefore the concept of Clinical Interventions by CHWs is not present. | Mother and Infant Care: The testimonial exclusively discusses an adult's personal experience with malaria treatment and self-care; it contains no references to pregnancy, childbirth, postpartum issues, or infant health, so the concept is not present. | Successful Outcomes: The speaker describes feeling better (free from migraine) after self-treatment, showing some positive outcome, but there is no indication that the result stemmed from CHW actions or referrals. Since successful outcomes are expected to be linked to CHW efforts, alignment is weak and scored low. | Material or Training Requests: The testimonial discusses personal experiences with malaria and offers advice, but it contains no explicit request for materials, supplies, or training. Therefore, the concept does not apply. | Children Served: The testimonial discusses the speaker's personal experience with malaria and self-care practices; it contains no reference to minors or services provided to children, so the concept is not present. | Elderly Served: The testimonial discusses the speaker’s personal experience with malaria and gives advice about medication use, without any mention of assisting or serving elderly individuals. Therefore, the concept of 'Elderly Served' is not present. | Women Served: The testimonial discusses personal experiences with malaria and offers general advice but never references women, girls, or gender-specific challenges or services. Therefore, the concept “Women Served” is not applicable. | Men Served: The testimonial discusses personal experiences with malaria without any mention of men, boys, or gender-specific issues. Therefore, it does not align with the concept of 'Men Served'. | Families Served: The testimonial focuses solely on the individual’s own experience with malaria and offers general advice to ‘people’ without any mention of households, parents, children, or family‐focused support. Therefore, the concept of families served is not present. | Parsing failed for concept 'Families Served' | Marginalized Groups Served: The testimonial focuses solely on the speaker’s personal experiences and self-care practices for malaria, without mentioning any support provided to marginalized or underserved groups. Therefore, the concept is not present. | Financial Hardship: The testimonial describes personal experiences with malaria and choices of treatment but contains no explicit or implicit mention of lack of money, poverty, or inability to afford transportation, food, or medical care. | Social Isolation: The testimonial solely discusses the speaker’s personal experience with malaria symptoms and treatment; it does not mention living alone, lacking support, or feelings of loneliness. Therefore, the Social Isolation concept is not present. | Disease Burden: The speaker describes malaria episodes that occur \ | Stigma or Discrimination: The testimonial discusses personal experiences and treatment choices for malaria but contains no mention of social judgment, shame, exclusion, or discrimination due to the illness. Hence, the concept is not present. | Mental or Emotional Distress: The testimonial focuses almost entirely on physical symptoms of malaria and strategies for treatment. Apart from calling the experience 'very challenging,' there is no clear expression of depression, hopelessness, or emotional overwhelm. Thus, only minimal, indirect evidence of mental or emotional distress is present. | Lack of Resources: The testimonial describes an individual's personal experience managing malaria and their choice of treatments. It does not mention CHWs, insufficient supplies, or any resource constraints. Therefore, the concept of 'Lack of Resources' does not apply. | Systemic Barriers: The testimonial discusses the speaker’s personal experience with malaria, self-medication, and hospital visits, but does not describe any institutional shortage, distance, cost, or other systemic condition that prevented care. Hospital is mentioned, yet no barrier linked to the health system is articulated. Minimal evidence for systemic barriers, so a near-zero score is appropriate. | Overburdened CHWs: The testimonial discusses personal experiences with malaria and self-treatment; it contains no mention of community health workers or their workload. | Lack of Follow-Through: The testimonial describes personal self-care and hospital visits for malaria, with no mention of a community health worker beginning assistance and failing to complete it. Therefore, the concept of Lack of Follow-Through is not present. | Lack of Knowledge: The testimonial describes personal experiences and gives advice on malaria treatment without expressing uncertainty or a need for additional training. There is no mention of the speaker being unable to address an issue because of insufficient knowledge, so the concept does not apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Malaria My personal experience about malaria has been very challenging as it affects me periodically and comes unexpectedly. There is a day I fell ill at night while asleep and my symptoms were for malaria because I felt cold with shivering, then developed a high temperature accompanied by severe sweating and headache. In my case, I normally use thermometer to know if am having malaria by checking on my temperature level. If my temperature exceeds 38C or above, then I take painkillers to relief pain, only at night but if I have malaria during the day I go to the hospital. There was a time I had malaria and took Coartem as it is known to reduce malaria faster, then again visited the hospital and it did not reflect that I have malaria as compared to the time when I take painkillers. My advice to people is always to avoid using Coartem without visiting the hospital at first and rather use painkillers to relief pain. After visiting the hospital my eating a bit usually changes, I eat a lot so as to heal faster. In most cases, when I have malaria, it usually comes with migraine, so when I experience such, I take hot strong tea with a lot of sugar, then relax my mind and sleep. When I wake up, I am always free from migraine because I believe my malaria comes with headache followed by migraine. ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.0,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.0,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.9,
+  "Nutrition Education and Food Access": 0.1,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.3,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.0,
+  "Community Empowerment Through Education": 0.0,
+  "Resource and Material Distribution": 0.0,
+  "Monitoring and Follow-Up": 0.0,
+  "Trust and Cultural Mediation": 0.0,
+  "Clinical Interventions by CHWs": 0.0,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.0,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.0,
+  "Men Served": 0.0,
+  "Families Served": 0.0,
+  "Marginalized Groups Served": 0.0,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.8,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.1,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial describes personal experiences with malaria and self-treatment strategies but contains no mention of CHW training, workshops, or gaining knowledge in a CHW capacity. The speaker discusses personal health management rather than serving others as a trained CHW. | Menstrual Hygiene Education and Challenges: The testimonial is entirely focused on the author's personal experience with malaria, including symptoms, treatment approaches, and advice about medication. There is no mention of menstruation, menstrual hygiene, products, or related education. The content explicitly excludes this concept as it discusses a completely different health topic. | Drug Abuse: Environment and Awareness: The testimonial focuses entirely on personal experiences with malaria symptoms and treatment, including medication use (painkillers, Coartem) in a medical context. There is no mention of substance abuse, addiction, alcohol, peer influence, or environmental factors contributing to drug abuse. The discussion of medication is purely therapeutic and clinical, which falls under the exclusion criteria. | CHW-Led Infectious Disease Management: This testimonial describes a personal experience with malaria but contains no evidence of CHW involvement. The speaker discusses their own symptoms, self-treatment methods, and personal advice about malaria management, but there is no mention of community health work, education, or outreach activities. This falls under the exclusion criteria of 'mentions of diseases without CHW involvement.' | Water Quality, Sanitation, and Hygiene: The testimonial focuses entirely on personal malaria experiences, symptoms, and treatment approaches. There is no mention of water quality, sanitation practices, hygiene education, or any preventive measures related to water or sanitation. The content is about medical treatment and symptom management, not disease prevention through water/sanitation/hygiene practices. | Personal Disease Management and Adherence: This testimonial demonstrates strong personal disease management of malaria through multiple strategies: self-monitoring with a thermometer, using painkillers for symptom relief, taking Coartem medication, seeking hospital care, dietary adjustments for recovery, and managing associated symptoms like migraines with hot tea. The detailed description of diagnosis methods, treatment adherence, and lifestyle adjustments aligns directly with the concept definition, similar to the 0.9 example of helping someone stick to medication. | Nutrition Education and Food Access: The testimonial contains minimal evidence related to nutrition education or food access. The only relevant mention is a brief comment about eating more after hospital visits to 'heal faster' from malaria. This represents a personal eating behavior change related to illness recovery rather than nutrition education or addressing food access issues. The testimonial primarily focuses on malaria symptoms and treatment, not on promoting healthy eating awareness or addressing food security. | Sexual and Reproductive Health Education: The testimonial is entirely focused on personal experiences with malaria, including symptoms, treatment approaches, and advice about medication. There is no mention of any sexual or reproductive health topics such as family planning, STIs, HIV, condoms, or reproductive rights. The content clearly falls outside the scope of this concept. | Gender-Based Violence (GBV) and Child Protection: The testimonial is entirely focused on personal experiences with malaria symptoms, treatment, and management strategies. There is no mention of violence, abuse, exploitation, or any form of GBV or child protection issues. The content discusses physical health symptoms and medical treatment, which clearly falls outside the scope of this concept. | Health Literacy and Misconceptions: The testimonial shows some problematic health practices and potential misconceptions. The person self-diagnoses malaria based on temperature alone, takes painkillers instead of seeking immediate medical care, and advises against using antimalarial medication (Coartem) without hospital visits - which could be seen as both cautious and potentially problematic. However, these appear to be personal health management choices rather than clear misinformation about disease origins or fundamental misunderstandings about how malaria works. The score is in the weak alignment range because while there are questionable practices, there's no explicit misinformation or misconceptions about the disease itself. | Mental Health Awareness and Support: The testimonial focuses entirely on physical symptoms and medical management of malaria (fever, shivering, headache, temperature monitoring, medication). While the person mentions 'relax my mind,' this is in the context of treating physical migraine symptoms, not addressing psychological well-being. There is no mention of depression, anxiety, loneliness, emotional trauma, or any mental health concerns. | Referrals and Advocacy: This testimonial describes a personal experience with malaria and self-care practices. There is no mention of the speaker being a CHW, helping others navigate healthcare, making referrals, or advocating for others. The advice given is general public health guidance rather than CHW-specific advocacy work. | Community Empowerment Through Education: This testimonial describes a personal experience with malaria and individual coping strategies, but contains no evidence of community education, empowerment, or behavior change. The CHW shares personal health management techniques and advice but does not mention teaching others, conducting health education sessions, or fostering community-level change. This is an individual health narrative without any educational or empowerment components. | Resource and Material Distribution: The testimonial is a personal account of the CHW's own experience with malaria and their self-treatment methods. There is no mention of distributing any materials, supplies, or resources to community members. The narrative focuses entirely on personal health management and advice-giving without any reference to providing physical resources like medication, nets, or health kits to others. | Monitoring and Follow-Up: This testimonial describes a personal experience with malaria and self-care practices, but contains no evidence of CHW monitoring or follow-up activities. The speaker discusses their own symptoms, self-treatment methods, and hospital visits, but makes no mention of a CHW checking on them, returning to assess progress, or providing ongoing care. This is a first-person account of managing illness independently, not a CHW testimonial about monitoring patients. | Trust and Cultural Mediation: This testimonial is a personal account of the CHW's own experience with malaria and self-treatment practices. There is no mention of the CHW building trust with community members, navigating cultural barriers, translating information, or mediating between communities and health systems. The narrative focuses entirely on personal health management without any trust-building or cultural mediation activities. | Parsing failed for concept 'Trust and Cultural Mediation' | Clinical Interventions by CHWs: The testimonial describes personal experiences with malaria self-management, including taking temperature readings and self-administering painkillers and Coartem. However, there is no mention of the speaker being a CHW or providing clinical interventions to others. The narrative is entirely about personal illness management, not about administering medical care to community members, which is required by the concept definition. | Mother and Infant Care: The testimonial is entirely focused on the CHW's personal experience with malaria, including symptoms, self-treatment, and advice about malaria management. There is no mention of prenatal care, childbirth, postpartum support, infant health, or any mother/infant-related topics. The content explicitly excludes this concept. | Successful Outcomes: This testimonial describes personal experiences with malaria but contains no evidence of CHW efforts or any outcomes related to community health work. The narrator discusses their own self-care practices and hospital visits, but there is no mention of helping others, making referrals, or achieving any positive changes in a CHW capacity. This clearly falls under the exclusion criteria as it only describes personal health problems without any CHW-related progress or outcomes. | Material or Training Requests: The testimonial describes personal experiences with malaria and provides advice on treatment approaches, but contains no requests for materials, supplies, or training. The CHW discusses their own health management strategies without asking for any resources or educational support to better serve their community. | Children Served: The testimonial is entirely focused on the CHW's personal experience with malaria and their self-care practices. There is no mention of children, minors, or any services provided to young people. The narrative is about personal health management and advice to 'people' in general, not specifically children. | Elderly Served: The testimonial is entirely about the speaker's personal experience with malaria and their self-care strategies. There is no mention of elderly people, seniors, or grandparents, nor any indication of the speaker serving as a CHW helping older adults. The content focuses solely on personal health management without any reference to assisting elderly individuals. | Women Served: The testimonial is a personal account of the CHW's own experience with malaria. There is no mention of women, girls, or any gendered roles or challenges. The CHW does not describe serving, assisting, or educating any women. This is purely a self-focused narrative about personal health management, which clearly falls under the exclusion criteria. | Men Served: The testimonial is a first-person account of the CHW's personal experience with malaria. There is no mention of serving, supporting, or counseling men or boys in any capacity. The narrative focuses entirely on the CHW's own health management strategies and does not describe providing services to others, regardless of gender. | Families Served: The testimonial is entirely focused on the CHW's personal experience with malaria and their individual treatment approach. There is no mention of households, parents with children, extended family units, or CHW support for multiple family members. The narrative is exclusively about individual self-care, which falls under the exclusion criteria. | Marginalized Groups Served: The testimonial is a personal account of the CHW's own experience with malaria, not about serving others. There is no mention of providing support to any community members, let alone marginalized or underserved groups. The narrative focuses entirely on self-care and personal health management strategies. | Financial Hardship: The testimonial describes personal experiences with malaria symptoms and treatment approaches but contains no evidence of financial hardship. The person discusses accessing hospitals, medications (Coartem, painkillers), thermometers, and food without mentioning any financial constraints, inability to afford care, or material scarcity. The focus is entirely on medical symptoms and treatment preferences rather than economic challenges. | Social Isolation: The testimonial focuses entirely on the individual's personal experience with malaria symptoms and treatment approaches. There is no mention of living alone, lack of support systems, loneliness, or social neglect. The narrative describes self-care practices and hospital visits but does not indicate any social isolation or abandonment issues. | Disease Burden: Strong alignment with the concept. The testimonial describes malaria that 'affects me periodically and comes unexpectedly,' indicating a recurrent illness pattern. The speaker details multiple episodes and has developed personal management strategies, suggesting this is a chronic, recurring health issue that significantly impacts their life. While malaria episodes are acute, the periodic and recurring nature aligns with the inclusion criteria of 'recurrent illness.' | Stigma or Discrimination: The testimonial focuses entirely on personal malaria symptoms, treatment approaches, and medical advice. There is no mention of social rejection, shame, exclusion, or judgment from others due to the health condition. The narrative is purely about the physical experience of malaria and self-care strategies, without any social stigma component. | Mental or Emotional Distress: The testimonial focuses primarily on physical symptoms of malaria (fever, shivering, sweating, headache, migraine) and medical management strategies. While the person mentions 'relax my mind' as part of their treatment approach, this appears to be a physical remedy for migraine rather than addressing emotional distress. The challenges described are medical/physical in nature, not expressions of depression, hopelessness, trauma, or emotional overwhelm. | Lack of Resources: The testimonial describes a personal experience with malaria and self-treatment strategies, but contains no evidence of lacking resources as a CHW. The speaker discusses having access to thermometers, painkillers, Coartem, and hospital services. There is no mention of insufficient supplies, tools, or capacity limitations in a CHW role. The narrative focuses on personal health management rather than resource constraints in providing care to others. | Systemic Barriers: The testimonial describes a personal experience with malaria and self-treatment strategies. There is no mention of systemic barriers such as health facility shortages, overcrowding, distance to hospitals, or institutional problems preventing care. The person actually mentions going to the hospital when needed during the day, indicating access to healthcare is available. The focus is entirely on personal health management rather than external systemic obstacles. | Overburdened CHWs: This testimonial is a personal account of someone's experience with malaria as a patient, not a CHW discussing their workload. There is no mention of being a healthcare worker, having too many patients, or experiencing work-related exhaustion or overwhelm. The concept clearly does not apply. | Lack of Follow-Through: This testimonial describes the person's personal experience managing their own malaria, not a CHW helping someone else. There is no mention of a CHW starting to help and then abandoning care or leaving issues unresolved. The narrative is about self-care strategies and personal medical experiences, which falls outside the concept's focus on CHW service delivery failures. | Lack of Knowledge: The testimonial shows no evidence of lack of knowledge. The CHW demonstrates clear understanding of malaria symptoms, treatment protocols, and self-care strategies. They know to use a thermometer for diagnosis, understand when to use painkillers versus seeking hospital care, and provide specific advice about avoiding Coartem without medical consultation. This is a personal experience narrative showing competent knowledge, not a case where the CHW was unable to address an issue due to knowledge gaps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Teenage Pregnancy/HIV AIDS Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners, they have which is not healthy. ---</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.2,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.05,
+  "CHW-Led Infectious Disease Management": 0.9,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.8,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.95,
+  "Gender-Based Violence (GBV) and Child Protection": 0.1,
+  "Health Literacy and Misconceptions": 0.65,
+  "Mental Health Awareness and Support": 0.05,
+  "Referrals and Advocacy": 0.6,
+  "Community Empowerment Through Education": 0.3,
+  "Resource and Material Distribution": 0.05,
+  "Monitoring and Follow-Up": 0.15,
+  "Trust and Cultural Mediation": 0.55,
+  "Clinical Interventions by CHWs": 0.05,
+  "Mother and Infant Care": 0.15,
+  "Successful Outcomes": 0.3,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.9,
+  "Elderly Served": 0.0,
+  "Women Served": 0.9,
+  "Men Served": 0.1,
+  "Families Served": 0.0,
+  "Marginalized Groups Served": 0.6,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.2,
+  "Stigma or Discrimination": 0.1,
+  "Mental or Emotional Distress": 0.1,
+  "Lack of Resources": 0.05,
+  "Systemic Barriers": 0.2,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.1,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial describes the CHW educating teenagers about HIV prevention, but it does not explicitly mention the CHW attending a training, workshop, or other capacity-building session. Any learning seems implicit or informal (e.g., possibly gained during World AIDS Day), which fits only weakly with the concept. Therefore, a low score (minimal evidence) is appropriate. | Menstrual Hygiene Education and Challenges: The testimonial focuses on teenage pregnancy and HIV/AIDS prevention (PREP), with no mention of menstruation, menstrual products, or related stigma or education. Therefore, it does not align with the menstrual hygiene concept. | Drug Abuse: Environment and Awareness: The testimonial discusses peer pressure and health education, but entirely in the context of teenage pregnancy and HIV prevention. There is no mention of substances, addiction, alcohol, or drug‐related environments, so alignment with the drug abuse concept is minimal. | CHW-Led Infectious Disease Management: The testimonial describes the CHW educating teenagers about HIV prevention, promoting testing, and explaining PrEP usage—direct actions to help the community understand and reduce the spread of an infectious disease. This aligns closely with the concept’s definition and inclusion criteria (CHWs explaining prevention and follow-up for diseases), so a strong score of 0.9 is warranted. | Water Quality, Sanitation, and Hygiene: The testimonial discusses teenage pregnancy and HIV prevention through testing and PrEP, with no reference to water quality, sanitation, or hygiene practices. Therefore, the concept is absent. | Personal Disease Management and Adherence: The CHW describes counselling teens on HIV testing and encouraging consistent use of PrEP, an antiretroviral medication taken daily to prevent HIV infection. This directly concerns infectious-disease prevention and requires treatment adherence, matching the concept’s focus on managing or preventing disease through diagnosis and medication adherence. Though it is more preventive than treating an existing infection, it still strongly aligns with personal disease management guided by the CHW. | Nutrition Education and Food Access: The testimonial focuses exclusively on teenage pregnancy, HIV testing, and PREP usage. It contains no discussion of healthy eating, food insecurity, or access to nutrition, which are required for this concept. | Sexual and Reproductive Health Education: The testimonial describes educating teenagers about HIV testing, the use of PrEP, and clarifies that it does not prevent pregnancy or other STIs—directly addressing STI/HIV prevention and reproductive health. This strongly matches the concept’s definition and inclusion criteria (family planning, STI prevention, HIV awareness). There is clear, detailed health education content with no disqualifying factors. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses on teenage pregnancy prevention and HIV counseling. While teenagers are a potentially vulnerable group, there is no explicit mention of abuse, exploitation, or violence, nor of CHW actions addressing such issues. Thus, only minimal indirect relevance to child protection yields a very low score. | Health Literacy and Misconceptions: The CHW identifies that teens and their partners often avoid HIV testing and may not understand PREP. She provides detailed education about how PREP works, what it does and does not do, addressing gaps in knowledge. While no explicit false belief is quoted, the narrative revolves around limited understanding and the CHW’s corrective teaching, fitting the inclusion of misinformation/lack of knowledge, hence a moderate alignment. | Mental Health Awareness and Support: The testimonial focuses on sexual health education (HIV testing, PrEP) and teenage pregnancy. Although it briefly mentions peer pressure and misunderstandings with partners, it does not discuss depression, anxiety, emotional trauma, or any psychological support provided. Therefore, there is only minimal, indirect relevance to mental health. | Referrals and Advocacy: The CHW advocates for teens to get HIV tests and start PrEP, guiding them toward specific health services. This is consistent with the concept’s inclusion of helping with referrals or navigating care, but there is no explicit mention of arranging appointments or formal referrals, so alignment is moderate rather than strong. | Community Empowerment Through Education: The CHW describes giving HIV-prevention education and advising teens to use PrEP, but the story is limited to a single post–World AIDS Day session. There is no evidence of sustained behavior change, peer-led action, or broader community transformation. Therefore the alignment is weak, closer to a one-time educational event than to long-term community empowerment. | Resource and Material Distribution: The CHW only educates and encourages teenagers about HIV testing and PrEP; there is no mention of actually providing PrEP pills, test kits, or any other tangible materials. According to the concept definition, mere advice without handing out supplies is excluded, so alignment is minimal. | Monitoring and Follow-Up: The testimonial describes a single educational session where the CHW advised teens about HIV testing and PrEP. There is no mention of returning to check progress, repeated visits, or ongoing tracking of the teens’ status, which would constitute monitoring and follow-up. Thus, only minimal evidence of the concept is present. | Trust and Cultural Mediation: The CHW explains PREP and HIV testing to teenagers, helping them understand an unfamiliar preventive practice and addressing social barriers (partners refusing tests). This shows some cultural mediation and effort to build confidence in health services, but direct statements about earning trust or bridging linguistic/cultural gaps are limited, so alignment is moderate rather than strong. | Clinical Interventions by CHWs: The testimonial describes the CHW educating teens about HIV testing and recommending PREP, which is health education and advice rather than directly administering medication or performing a clinical task. According to the concept definition, education alone is excluded from clinical interventions, so only minimal alignment is present. | Mother and Infant Care: Pregnancy is mentioned, but the CHW’s activities focus on HIV testing and PrEP uptake rather than prenatal care, birth preparation, postpartum support, or infant health. Thus, alignment with the Mother and Infant Care concept is minimal. | Successful Outcomes: The CHW describes educating teens about HIV testing and recommending PrEP, but there is no clear evidence that teens actually got tested, started PrEP, or experienced improved health outcomes. This reflects an attempted intervention without confirmed results, giving only weak alignment with the Successful Outcomes concept. | Material or Training Requests: The testimonial discusses educating teenagers about HIV prevention and recommending PREP, but it does not contain any request for additional supplies, materials, or training. Therefore, the concept is not present. | Children Served: The testimonial centers on educating teenagers (adolescents) about HIV testing and PrEP, which is direct support for minors under 18. This matches the inclusion criteria of providing health education to children/adolescents, so strong alignment (0.9). | Elderly Served: The testimonial exclusively discusses educating teenagers about HIV prevention and PrEP; it contains no references to seniors or assistance provided to elderly individuals. | Women Served: The testimonial focuses on educating teenage girls about HIV testing, PrEP, and preventing teenage pregnancies—clearly addressing gender-specific health challenges and providing direct assistance. This matches the concept’s inclusion criteria of assisting or educating women on health matters, hence a strong alignment (0.9). | Men Served: The testimonial focuses on educating teenage girls about HIV prevention and PrEP in the context of teenage pregnancy. Men are only indirectly referenced as partners who resist testing; no direct support or intervention for men or boys is described. This provides only minimal, indirect relevance to the concept. | Families Served: The testimonial focuses on educating teenagers about HIV prevention and PrEP usage. It does not mention households, parents, or any family-focused intervention, so the Families Served concept is not present. | Marginalized Groups Served: The CHW works with teenagers experiencing or at risk of teenage pregnancy and HIV. Adolescents in this context face stigma and limited access to sexual-health services, making them an underserved, socially excluded group. The testimonial describes direct support and education to address that vulnerability, fitting the inclusion criteria, but the group is not as clearly marginalized as examples like migrants or people living with HIV, so alignment is moderate rather than strong. | Financial Hardship: The testimonial discusses teenage pregnancy, HIV prevention, and PrEP education but contains no references to lack of money, inability to afford care, transportation costs, or other material scarcity. Therefore, the Financial Hardship concept is not present. | Social Isolation: The testimonial discusses teenage pregnancy and HIV prevention education with references to peer pressure, partners, and social interactions. There is no mention of living alone, lack of support systems, loneliness, or being cut off from others, so the concept of Social Isolation is not present. | Disease Burden: The testimonial discusses HIV/AIDS—a chronic illness—but only in the context of prevention (encouraging testing and PrEP). It does not describe clients already living with HIV or managing a chronic condition. Therefore, evidence of actual long-term or recurrent illness is minimal, warranting a low score. | Stigma or Discrimination: The testimonial focuses on educating teenagers about HIV testing and PrEP. Although peer pressure and partners’ unwillingness to test are mentioned, there is no clear statement of social rejection, judgment, or exclusion tied to a health condition. Any link to stigma is only implicit and weak, so the alignment with the concept is minimal. | Mental or Emotional Distress: The testimonial focuses on sexual health education and HIV prevention. While it mentions peer pressure and misunderstandings with partners, it does not explicitly describe feelings of depression, hopelessness, or significant emotional strain. Thus, there is only minimal evidence of mental or emotional distress. | Lack of Resources: The testimonial focuses on educating teenagers about HIV testing and PrEP. It does not mention the CHW lacking medicines, supplies, or support; therefore, evidence for a resource shortage is virtually absent. A very low score is assigned to reflect the minimal alignment with the concept. | Systemic Barriers: The testimonial mainly describes interpersonal challenges (partners refusing HIV testing, peer pressure) rather than health-system shortages, institutional policies, or corruption. These obstacles lie largely within social or personal dynamics, which the concept definition treats as outside the scope of true systemic barriers. Therefore, only minimal alignment is present. | Overburdened CHWs: The testimonial focuses on educating teenagers about HIV testing and PrEP, with no mention of workload, exhaustion, or being overwhelmed. Therefore, the concept of overburdened CHWs is not present. | Lack of Follow-Through: The CHW describes providing education and recommending PREP; there is no mention of starting an intervention and then abandoning it. The outcome for the teens is not detailed, but absence of follow-through is not explicitly indicated, so only minimal evidence applies. | Lack of Knowledge: The CHW confidently provides detailed information on HIV testing and PrEP use, showing no sign of uncertainty or need for additional training. Therefore, the concept of lack of knowledge is not present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Teenage Pregnancy/HIV AIDS Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners, they have which is not healthy. ---</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.0,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.8,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.6,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.9,
+  "Gender-Based Violence (GBV) and Child Protection": 0.2,
+  "Health Literacy and Misconceptions": 0.3,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.3,
+  "Community Empowerment Through Education": 0.6,
+  "Resource and Material Distribution": 0.1,
+  "Monitoring and Follow-Up": 0.2,
+  "Trust and Cultural Mediation": 0.7,
+  "Clinical Interventions by CHWs": 0.0,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.7,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.9,
+  "Elderly Served": 0.0,
+  "Women Served": 0.7,
+  "Men Served": 0.0,
+  "Families Served": 0.1,
+  "Marginalized Groups Served": 0.8,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.7,
+  "Stigma or Discrimination": 0.2,
+  "Mental or Emotional Distress": 0.2,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.1,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial describes a CHW educating teenagers about HIV prevention and PREP, but contains no mention of the CHW receiving training, attending workshops, or gaining knowledge through formal programs. The focus is entirely on the CHW's educational activities with community members, not on their own training or capacity building. | Menstrual Hygiene Education and Challenges: The testimonial focuses entirely on teenage pregnancy, HIV/AIDS education, and PREP (pre-exposure prophylaxis) for HIV prevention. There is no mention of menstruation, menstrual hygiene, menstrual products, or any related education. The content is about sexual health and HIV prevention, not menstrual hygiene, making this a clear non-match for the concept. | Drug Abuse: Environment and Awareness: The testimonial focuses entirely on teenage pregnancy, HIV/AIDS prevention, and sexual health education. There is no mention of drug abuse, substance use, alcohol, or addiction. While peer pressure is mentioned as a contributing factor, it's specifically in the context of sexual behavior, not substance abuse. The concept clearly requires content about drugs or alcohol, which is completely absent from this testimonial. | CHW-Led Infectious Disease Management: Strong alignment with the concept. The CHW directly educates teenagers about HIV/AIDS prevention, explains testing importance, and provides detailed information about PrEP as a prevention method. While focused specifically on HIV/AIDS rather than multiple infectious diseases, this represents clear CHW-led management of an infectious disease through education and outreach, matching the definition's emphasis on helping communities understand and reduce disease spread. | Water Quality, Sanitation, and Hygiene: The testimonial focuses entirely on teenage pregnancy and HIV/AIDS prevention through education about testing and PrEP medication. There is no mention of water quality, sanitation practices, handwashing, or hygiene education related to water or community sanitation. The content explicitly deals with sexual health education, which falls outside the scope of this concept. | Personal Disease Management and Adherence: The testimonial shows moderate alignment with disease management through HIV prevention. While it focuses on preventing HIV rather than managing an existing disease, it includes key elements like adherence to PrEP medication ('effective only after 7 days of using it') and guidance on a medical intervention for at-risk individuals. The CHW is helping teens manage their HIV risk through a specific treatment protocol, which partially aligns with the concept's focus on treatment adherence and health management. | Nutrition Education and Food Access: The testimonial focuses entirely on teenage pregnancy, HIV/AIDS education, and PREP (pre-exposure prophylaxis) medication. There is no mention of food, nutrition, healthy eating, food insecurity, or any nutrition-related topics. The content explicitly deals with sexual health education and HIV prevention, which falls outside the scope of the Nutrition Education and Food Access concept. | Sexual and Reproductive Health Education: Strong direct alignment with the concept. The testimonial explicitly covers HIV awareness and prevention education through PREP, addresses teenage pregnancy issues, and discusses HIV testing with partners. While it doesn't mention condoms or STI prevention beyond HIV, it provides comprehensive sexual health education to teenagers about HIV prevention methods, which aligns closely with the concept's definition and inclusion criteria. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses on teenage pregnancy and HIV/AIDS education, with only a weak connection to the GBV concept. While it mentions that teens 'end up giving in to their demands' and that 'insisting to go for check-ups always leads to misunderstandings,' this suggests potential coercion or unhealthy relationship dynamics but does not explicitly discuss abuse, violence, or exploitation. The primary focus is on sexual health education rather than addressing violence or protection issues. | Health Literacy and Misconceptions: The testimonial shows weak alignment with health literacy issues. While there's no explicit misinformation or misconceptions mentioned, the teens' partners refusing HIV testing due to 'excuses' and the resulting 'misunderstandings' suggest some underlying knowledge gaps or mistrust around HIV testing. However, the CHW's response focuses on accurate health education about PrEP rather than correcting specific misconceptions, making this only a minimal match to the concept. | Mental Health Awareness and Support: The testimonial focuses entirely on teenage pregnancy, HIV/AIDS education, and PREP (pre-exposure prophylaxis) as preventive measures. While the CHW mentions relationship challenges and peer pressure, these are discussed in the context of sexual health education, not mental or emotional well-being. There is no mention of depression, anxiety, loneliness, or emotional trauma, nor any discussion of psychological support provided to the teenagers. | Referrals and Advocacy: The testimonial shows weak alignment with referrals and advocacy. While the CHW educates teens about HIV testing and PREP, there is no explicit mention of helping with referrals, making appointments, or actively navigating the healthcare system. The CHW encourages teens to 'go for PREP' and testing, which is similar to the example 'I asked someone to consider going to the clinic' (0.5), but lacks the direct advocacy or navigation component, making it weaker than that example. | Community Empowerment Through Education: The testimonial shows moderate alignment with community empowerment through education. The CHW conducted education about HIV testing and PREP following World AIDS Day, targeting teenagers facing challenges with partner testing. While there is evidence of sustained educational effort and problem-solving (adapting advice when initial guidance faced barriers), the impact on long-term behavior change or community self-reliance is unclear. The education appears ongoing rather than a one-time event, but there's no clear evidence of peer education, group action, or community-wide transformation that would warrant a higher score. | Resource and Material Distribution: The testimonial focuses entirely on education and advice about HIV testing and PrEP usage for teenagers. While the CHW mentions PrEP (a medication), they only educated about it rather than actually distributing it. The text explicitly states 'I educated,' 'I advised,' and 'I solved this by encouraging' - all educational activities without any mention of providing actual materials or medications. This aligns with the exclusion criteria of 'discussions of education or advice without material support.' | Monitoring and Follow-Up: The testimonial describes a one-time educational session after World AIDS Day with no mention of returning to check on the teens' progress, following up on whether they got tested, or monitoring their use of PREP. While the CHW provided advice and solutions, there is no evidence of ongoing interactions or follow-up visits, which are core to this concept. | Trust and Cultural Mediation: The testimonial shows moderate alignment with trust-building and cultural mediation. The CHW navigates sensitive social barriers around HIV testing in teenage relationships, where partners resist testing due to cultural stigma. The CHW builds trust by listening to teens share intimate details about multiple partners and provides culturally appropriate solutions (PREP) when abstinence isn't realistic. However, the focus is more on health education than explicit trust-building or cultural translation, preventing a higher score. | Clinical Interventions by CHWs: The testimonial describes health education about HIV testing and PrEP (pre-exposure prophylaxis), but contains no evidence of the CHW directly administering medication, treating wounds, or performing any clinical tasks. The CHW only educated teens about PrEP and encouraged them to seek testing and treatment from healthcare facilities. This falls under the exclusion criteria of 'health education or referrals without direct clinical interaction.' | Mother and Infant Care: This testimonial focuses entirely on teenage pregnancy prevention, HIV/AIDS education, and PREP (pre-exposure prophylaxis) for sexually active teens. While it mentions teenage pregnancy, it does not discuss any prenatal care, childbirth support, postpartum care, or infant health services. The content is about preventing pregnancy and HIV transmission among teenagers, not about caring for mothers or infants, which clearly falls under the exclusion criteria. | Successful Outcomes: The testimonial shows moderate alignment with successful outcomes. The CHW successfully educated teens about HIV testing and PREP after World AIDS Day, and provided a solution (PREP) when teens faced resistance from partners about testing. While there's clear evidence of problem-solving and education delivery, the testimonial doesn't explicitly state whether teens actually adopted PREP or if health outcomes improved, making it a partial rather than complete success story. | Material or Training Requests: The testimonial describes the CHW's educational activities regarding teenage pregnancy and HIV/AIDS prevention, including their solution of recommending PrEP. However, there is no explicit request for materials, supplies, or training. The CHW describes what they did to address the problem but does not ask for any resources or additional education to better serve their community. | Children Served: Strong direct alignment. The testimonial explicitly describes the CHW educating and providing health guidance to teenagers (minors under 18) about HIV prevention, testing, and PrEP usage. The CHW directly engaged with teens, listened to their concerns about partners and testing, and provided tailored health education and solutions. This clearly demonstrates serving children/adolescents in a health capacity, matching the inclusion criteria perfectly. | Elderly Served: The testimonial focuses exclusively on teenage pregnancy and HIV/AIDS education for teenagers. There is no mention of elderly people, seniors, or grandparents, nor any CHW assistance provided to older adults. The entire narrative centers on educating teens about HIV testing and PREP, which clearly falls outside the scope of serving elderly populations. | Women Served: The testimonial describes CHW education provided to teenagers about HIV prevention and sexual health, which likely includes teenage girls given the focus on pregnancy. While not exclusively about women/girls, the content addresses gendered health challenges (teenage pregnancy) and provides health education relevant to young women. The score is moderate rather than high because the testimonial uses gender-neutral language ('teens/teenagers') and doesn't specifically highlight women-focused interventions. | Men Served: The testimonial focuses on teenage pregnancy and HIV/AIDS education for teens in general, with no specific mention of adult males or boys in the context of gendered roles or challenges. While male partners are indirectly referenced (teens mentioning their partners give excuses), these partners are not the direct recipients of the CHW's support or services. The CHW is serving teenagers broadly, not specifically men or boys. | Families Served: The testimonial focuses on educating teenagers about HIV/AIDS and PREP, with no mention of households, parents, or family units. While teenagers could potentially be part of families, the CHW's intervention is directed at individuals (teens) rather than family-focused support. The only indirect family connection might be implied through teenage pregnancy, but this is not explicitly linked to family support or intervention. | Marginalized Groups Served: Strong alignment with the concept. The testimonial describes CHW support for teenagers facing teenage pregnancy and HIV/AIDS risks - groups that often experience social stigma and marginalization. The CHW provides education, confidential support, and practical solutions (PREP) to teens who face barriers to healthcare access due to partner resistance and social pressures. While not explicitly labeled as 'marginalized,' teenagers dealing with sexual health issues, multiple partners, and HIV risk clearly face structural exclusion and stigma, matching the inclusion criteria of 'support provided to stigmatized or underserved groups.' | Financial Hardship: The testimonial focuses entirely on teenage pregnancy, HIV/AIDS education, and sexual health counseling. There is no mention of poverty, inability to afford transportation, food, medical care, or any other financial constraints. The challenges described relate to relationship dynamics and health education, not economic hardship. | Social Isolation: The testimonial focuses on teenage pregnancy and HIV/AIDS education, with no mention of living alone, loneliness, lack of support systems, or abandonment. The teens described have partners and peer groups, indicating social connections rather than isolation. The concept of social isolation is not present in this testimonial. | Disease Burden: The testimonial focuses on HIV/AIDS prevention and risk, which represents a chronic disease burden in the community. While it doesn't describe individuals currently living with HIV/AIDS, it addresses the ongoing threat and high-risk behaviors that could lead to chronic illness. The emphasis on PREP for high-risk individuals and the context of multiple partners creating disease risk aligns moderately with the concept of disease burden as a persistent health challenge affecting the community. | Stigma or Discrimination: The testimonial contains minimal evidence of stigma or discrimination. While it mentions that some partners refuse HIV testing and that 'insisting to go for check-ups always leads to misunderstandings,' this reflects relationship dynamics and avoidance rather than social rejection or judgment. The CHW's approach is educational and non-judgmental, and there's no mention of teens being shamed, excluded, or discriminated against by their community for their sexual activity or health status. | Mental or Emotional Distress: The testimonial focuses primarily on teenage pregnancy and HIV/AIDS education rather than mental or emotional distress. While there are indirect references to emotional challenges (teens giving in to demands to avoid misunderstandings, peer pressure), these are not explicitly framed as mental strain or emotional overwhelm. The content is more about risky behaviors and health education than expressions of depression, hopelessness, or trauma. | Lack of Resources: The testimonial does not mention any lack of medicine, tools, or support. The CHW successfully educated teens about HIV testing and PREP, and was able to provide advice and solutions. There is no indication of insufficient supplies or capacity to address the teenage pregnancy/HIV issue. | Systemic Barriers: The testimonial does not mention any systemic barriers outside the CHW's control. The challenges described (partner reluctance to get tested, peer pressure) are interpersonal issues rather than institutional failures. The CHW successfully provides education and solutions (PREP) without being hindered by health facility shortages, corruption, or other systemic forces. This aligns with the exclusion criteria as these are personal/interpersonal limits rather than systemic barriers. | Overburdened CHWs: The testimonial describes a CHW educating teenagers about HIV prevention and PREP, but contains no evidence of being overburdened. The CHW appears to be successfully delivering education and solving problems (finding alternative solutions when teens face resistance from partners). There is no mention of exhaustion, being overwhelmed, having too many patients, or struggling with workload - key indicators of the 'Overburdened CHWs' concept. | Lack of Follow-Through: The CHW educated teens about HIV testing and when faced with the challenge of partners refusing to test, provided an alternative solution (PREP). The issue was addressed with a practical workaround rather than abandoned. This aligns with the exclusion criteria as there was no abandonment or interrupted care - the CHW completed their intervention by providing education and an alternative solution. | Lack of Knowledge: The CHW demonstrates comprehensive knowledge throughout the testimonial. They successfully educated teens about HIV testing, identified barriers (partner reluctance), and provided an appropriate solution (PrEP). The CHW shows detailed understanding of PrEP including eligibility criteria, effectiveness timeline, and limitations. There is no evidence of knowledge gaps or requests for training.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Malaria People who have malaria usually feel very sick with high fever and shaking chills. However, the introduction malaria vaccine as a preventive measure for the disease has been seen as a huge step in the fight against the disease. Although WHO has approved the vaccine to be used in children in countries with high number of cases, the disease still remains the number one killer of children. According to a client whom I met during our health education session, her experience with malaria was that she lost her appetite after the attack. She further stated that she had alternating body temperature which was at times cold and at times very hot. She noted that the alternating body temperatures were accompanied by high fever, vomiting of yellowish substance, body aches and fatigue. The client observed that she also lost a significant body weight due to her missing meals because of lost appetite. She later went to seek medical attention a few days when the symptoms persisted. Her experience with malaria is not different from mine. I had encounter with malaria a year ago where the symptoms included high body temperature, fatigue, body ache and high fever. As CHWs, we urge people to prevent themselves from malaria by visiting health centers whenever they experience such symptoms. ---</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.1,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.85,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.4,
+  "Nutrition Education and Food Access": 0.1,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.05,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.5,
+  "Community Empowerment Through Education": 0.2,
+  "Resource and Material Distribution": 0.05,
+  "Monitoring and Follow-Up": 0.1,
+  "Trust and Cultural Mediation": 0.2,
+  "Clinical Interventions by CHWs": 0.05,
+  "Mother and Infant Care": 0.25,
+  "Successful Outcomes": 0.2,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.2,
+  "Elderly Served": 0.0,
+  "Women Served": 0.6,
+  "Men Served": 0.0,
+  "Families Served": 0.1,
+  "Marginalized Groups Served": 0.05,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.3,
+  "Stigma or Discrimination": 0.05,
+  "Mental or Emotional Distress": 0.0,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.05,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.05,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial describes CHWs conducting a health education session and giving prevention advice, but it never states that they received training, attended workshops, or gained new knowledge through a training program. Because the definition requires an explicit mention of CHWs receiving training, alignment is minimal and only inferred, yielding a weak score. | Menstrual Hygiene Education and Challenges: The testimonial exclusively discusses malaria symptoms, prevention, and the vaccine; it contains no mention of menstruation, menstrual products, stigma, or education. Therefore the concept is not applicable. | Drug Abuse: Environment and Awareness: The testimonial focuses solely on malaria symptoms, vaccination, and prevention with no mention of addiction, substance use, peer influence, or drug‐related education; therefore the concept is not present. | CHW-Led Infectious Disease Management: The testimonial is delivered from the perspective of a CHW who, during health education sessions, explains malaria symptoms and urges preventive actions (e.g., visiting health centers, awareness of vaccine). This matches the concept’s focus on CHWs providing outreach and education about infectious disease symptoms and prevention. The alignment is strong but not exhaustive (limited detail on broader community strategies), hence 0.85 instead of a perfect score. | Water Quality, Sanitation, and Hygiene: The testimonial focuses on malaria symptoms, vaccination, and seeking medical care. It does not mention clean water, handwashing, sanitation practices, or hygiene education related to water, so the concept is not present. | Personal Disease Management and Adherence: The testimonial describes an individual recognizing malaria symptoms and eventually seeking medical attention, and CHWs advising people to visit health centers. This shows some engagement with disease management (seeking diagnosis and care). However, there is no detail about ongoing treatment adherence or specific management practices; most of the text focuses on symptoms and general prevention. Therefore alignment with the concept is weak-to-moderate rather than strong. | Nutrition Education and Food Access: Testimonial briefly mentions loss of appetite and missed meals during malaria illness, but does not discuss healthy eating education or access to food. Weight loss is specifically excluded when unrelated to nutrition education or food access, so only a very weak, incidental connection exists. | Sexual and Reproductive Health Education: The testimonial focuses solely on malaria symptoms, vaccination, and general prevention advice. It contains no references to family planning, STI/HIV prevention, condoms, or reproductive rights. Therefore, the concept is not present. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses solely on malaria symptoms, prevention, and vaccination with no reference to violence, abuse, exploitation, or child protection issues. Therefore, the GBV and Child Protection concept is not applicable. | Health Literacy and Misconceptions: The testimonial provides accurate information about malaria symptoms, vaccine approval, and advice to seek care; it does not describe misinformation, misunderstandings, or mistrust. Therefore, only a negligible alignment with the concept exists. | Mental Health Awareness and Support: The testimonial discusses physical symptoms and preventive measures for malaria without any mention of psychological well-being, emotional distress, or mental health support, which are required for this concept. | Parsing failed for concept 'Mental Health Awareness and Support' | Referrals and Advocacy: The CHW states, “we urge people to ... visit health centers whenever they experience such symptoms,” which shows advocacy for seeking care but does not describe a specific referral or direct navigation support. This matches the moderate example ('asked someone to consider going to the clinic' → 0.5), so a mid-range score is appropriate. | Community Empowerment Through Education: The testimonial mentions a health education session and CHWs urging people to seek care, but it does not describe any sustained community-level change, peer education, or evidence that people have become more self-reliant. This resembles a one-time educational interaction without documented long-term behavior change, fitting weak alignment with the concept. | Resource and Material Distribution: The testimonial focuses on health education about malaria symptoms and urging people to seek care. It does not describe the CHW giving out medicine, bed nets, vaccines, or any other physical supplies. Therefore, material distribution is essentially absent, warranting a very low score. | Monitoring and Follow-Up: The testimonial describes a single health education session and general encouragement to seek care, with no indication that the CHW returned to the client or continued to track her progress. This fits the exclusion of one-time visits, so only minimal evidence of monitoring or follow-up is present. | Trust and Cultural Mediation: The testimonial mainly recounts malaria symptoms, the vaccine, and general advice to seek care. While it mentions a health education session, it does not describe translating, addressing cultural barriers, or specific actions to build or earn trust. Therefore, only minimal indirect evidence of trust‐related activity is present. | Clinical Interventions by CHWs: The testimonial only describes CHWs providing health education and encouraging clients to visit health centers; it contains no mention of CHWs giving medication, bandaging, or performing any direct clinical tasks. This falls under the exclusion criteria, so alignment with the concept is minimal. | Mother and Infant Care: The testimonial briefly references the malaria vaccine being approved for children, which touches on child immunization (an inclusion criterion for Mother and Infant Care). However, there is no discussion of pregnancy, childbirth, postpartum issues, or specific infant care guidance, so the alignment is weak and incidental rather than central. | Successful Outcomes: Testimonial mainly describes malaria symptoms and CHW advice to seek care; it notes that the client eventually went for medical attention but provides no evidence of recovery or measurable improvement attributable to CHW action. This offers only minimal evidence of a positive outcome, thus weak alignment with the concept. | Material or Training Requests: The testimonial discusses malaria symptoms and prevention advice but contains no requests for additional materials, supplies, or training. | Children Served: The testimonial references children as the target population for the malaria vaccine and notes that malaria is a major killer of children, but it does not describe the CHW directly providing services or support specifically to children. This is only a brief mention without evidence of direct involvement, so alignment is weak. | Elderly Served: The testimonial discusses malaria, children, and personal experiences without any mention of older adults, seniors, or specific assistance to them. Therefore the Elderly Served concept does not apply. | Parsing failed for concept 'Elderly Served' | Women Served: The testimonial describes a female client (“her experience”) who received health education about malaria from the CHW. This is direct assistance/education provided to an adult woman, satisfying the inclusion criteria. However, the content is not specifically about gender-specific health challenges, so the alignment is moderate rather than strong. | Men Served: The testimonial discusses malaria prevention and individual experiences, referring only to female clients and children. There is no mention of adult males or boys, so the concept does not apply. | Families Served: The testimonial contains only a passing, generic reference to children (approval of a vaccine for children) without describing support to a household, parents, or a family unit. This provides very weak evidence for the Families Served concept. | Parsing failed for concept 'Families Served' | Marginalized Groups Served: The testimonial discusses malaria prevention and treatment for children and the community in general, without identifying any group as structurally excluded or stigmatized. There is no indication that the client belongs to a marginalized population nor that the CHW provided specialized support for such a group. Thus, alignment with the concept is minimal. | Financial Hardship: The testimonial describes malaria symptoms, vaccination efforts, and urges seeking medical care, but contains no mention of poverty, lack of income, or inability to afford transportation, food, or medical services. Therefore it does not align with the Financial Hardship concept. | Social Isolation: The testimonial focuses solely on malaria symptoms, vaccination, and advice; it contains no mention of living alone, lack of support, loneliness, or abandonment. Therefore, the concept of Social Isolation is not present. | Disease Burden: The testimonial describes acute episodes of malaria with severe symptoms, but does not indicate a chronic or recurring condition or long-term disability. While malaria can impose a health burden, the account centers on a single short-term illness event, which falls under the concept’s exclusion criteria. Therefore, only weak alignment with the Disease Burden concept is present. | Stigma or Discrimination: The testimonial focuses on malaria symptoms, vaccination, and prevention without any mention of social rejection, judgment, shame, or discrimination. Therefore the stigma concept is essentially absent, warranting a near-zero score. | Mental or Emotional Distress: The testimonial only discusses physical symptoms of malaria (fever, chills, vomiting, weight loss) and prevention measures. It contains no mention of depression, hopelessness, stress, or any emotional strain, which are required for the Mental or Emotional Distress concept. Therefore the concept is not present. | Lack of Resources: The testimonial discusses malaria symptoms, vaccine introduction, and advice to seek medical attention but does not mention CHWs lacking medicine, tools, or any other resources. Therefore, the concept is not present. | Systemic Barriers: The testimonial discusses malaria symptoms, WHO’s vaccine approval, and general advice but does not describe institutional shortages, corruption, distance, or any external condition that prevented the CHW or client from obtaining care. Therefore, evidence for systemic barriers is virtually absent. | Overburdened CHWs: The testimonial focuses on malaria symptoms, prevention, and vaccine introduction. It does not mention CHWs being exhausted, overextended, or facing excessive workloads, so the concept of overburdened CHWs is not present. | Lack of Follow-Through: The testimonial describes general health education about malaria and encourages patients to seek care; it does not mention any instance where a CHW began assistance and then failed to complete it. Therefore, evidence for lack of follow-through is essentially absent. | Lack of Knowledge: The testimonial demonstrates knowledge about malaria symptoms, vaccines, and advice to clients; there is no statement indicating the CHW was unsure how to proceed or lacked training, so the concept is not present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Malaria People who have malaria usually feel very sick with high fever and shaking chills. However, the introduction malaria vaccine as a preventive measure for the disease has been seen as a huge step in the fight against the disease. Although WHO has approved the vaccine to be used in children in countries with high number of cases, the disease still remains the number one killer of children. According to a client whom I met during our health education session, her experience with malaria was that she lost her appetite after the attack. She further stated that she had alternating body temperature which was at times cold and at times very hot. She noted that the alternating body temperatures were accompanied by high fever, vomiting of yellowish substance, body aches and fatigue. The client observed that she also lost a significant body weight due to her missing meals because of lost appetite. She later went to seek medical attention a few days when the symptoms persisted. Her experience with malaria is not different from mine. I had encounter with malaria a year ago where the symptoms included high body temperature, fatigue, body ache and high fever. As CHWs, we urge people to prevent themselves from malaria by visiting health centers whenever they experience such symptoms. ---</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.2,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.8,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.8,
+  "Nutrition Education and Food Access": 0.2,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.0,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.3,
+  "Community Empowerment Through Education": 0.3,
+  "Resource and Material Distribution": 0.0,
+  "Monitoring and Follow-Up": 0.1,
+  "Trust and Cultural Mediation": 0.1,
+  "Clinical Interventions by CHWs": 0.1,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.5,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.5,
+  "Elderly Served": 0.0,
+  "Women Served": 0.5,
+  "Men Served": 0.0,
+  "Families Served": 0.0,
+  "Marginalized Groups Served": 0.0,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.2,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.0,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial shows minimal evidence of CHW empowerment through training. While the author identifies as a CHW and mentions conducting 'health education sessions,' there is no explicit mention of receiving training, attending workshops, or gaining knowledge through formal CHW programs. The knowledge shared appears to come from personal experience with malaria and general awareness rather than structured training. This aligns with the example 'I started giving advice to neighbors based on what I learned informally' which scores 0.2. | Menstrual Hygiene Education and Challenges: The testimonial focuses entirely on malaria symptoms, prevention, and treatment. There is no mention of menstruation, menstrual hygiene, products, or related education. The content explicitly discusses a different health topic (malaria), making it a clear non-match for the menstrual hygiene concept. | Drug Abuse: Environment and Awareness: The testimonial focuses entirely on malaria symptoms, prevention, and treatment. There is no mention of substance abuse, addiction, alcohol, peer influence, or drug education. The content is exclusively about a communicable disease and its medical management, which clearly falls outside the scope of the Drug Abuse concept. | CHW-Led Infectious Disease Management: Strong direct alignment. The testimonial clearly shows a CHW educating about malaria (an infectious disease) during health education sessions and urging people to seek medical attention when experiencing symptoms. The CHW shares both a client's experience and their own to educate about malaria symptoms and prevention, which directly aligns with the concept of CHWs helping communities understand infectious diseases through outreach and education. | Water Quality, Sanitation, and Hygiene: The testimonial focuses entirely on malaria symptoms, vaccine prevention, and seeking medical treatment. There is no mention of water quality, sanitation practices, handwashing, or hygiene education related to disease prevention. The content explicitly discusses malaria prevention through vaccines and medical care, not through water/sanitation measures. | Personal Disease Management and Adherence: Strong alignment with the concept. The testimonial describes detailed personal experiences with malaria management, including symptom recognition (fever, chills, fatigue, body aches) and the critical step of seeking medical attention when symptoms persisted. Both the client's and CHW's experiences demonstrate disease management through diagnosis and treatment-seeking behavior. The CHW also provides guidance on prevention and early medical consultation, which aligns with the concept's focus on CHW guidance for disease management. | Nutrition Education and Food Access: The testimonial mentions appetite loss and missing meals due to malaria, which relates to food intake but not to nutrition education or improving food access. The weight loss described is a symptom of illness rather than a food security issue. This aligns with the exclusion criteria of 'weight gain/loss issues unrelated to nutrition education or food access.' | Sexual and Reproductive Health Education: The testimonial focuses entirely on malaria symptoms, prevention, and treatment. There is no mention of family planning, STI prevention, HIV awareness, reproductive rights, or any sexual health topics. The content is exclusively about malaria as an infectious disease, making it clearly outside the scope of sexual and reproductive health education. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses entirely on malaria symptoms, prevention, and treatment experiences. There is no mention of violence, abuse, exploitation, or any form of GBV or child protection issues. The content discusses physical health symptoms and medical care seeking behavior related to malaria, which clearly falls outside the scope of this concept. | Health Literacy and Misconceptions: The testimonial presents accurate medical information about malaria symptoms and prevention. Both the CHW and client describe legitimate symptoms (fever, chills, fatigue, body aches) and appropriate health-seeking behavior (visiting health centers). There is no evidence of misinformation, misbeliefs about disease origins, or mistrust in medicine. The discussion reflects proper health literacy with no misunderstandings present. | Mental Health Awareness and Support: This testimonial focuses entirely on the physical symptoms and medical aspects of malaria (fever, body aches, fatigue, loss of appetite, vomiting). While the client experienced physical suffering, there is no mention of psychological well-being, emotional trauma, depression, anxiety, or any mental health context. The content is purely about medical symptoms and treatment, which falls under the exclusion criteria of 'medical diagnoses without a mental/emotional context.' | Referrals and Advocacy: The testimonial shows weak alignment with referrals and advocacy. While the CHW mentions urging people to 'visit health centers whenever they experience such symptoms,' this is general health education rather than direct referral or advocacy work. The client's story mentions seeking medical attention independently, not through CHW assistance. The CHW's role appears limited to preventive education rather than actively helping with referrals or navigating healthcare systems. | Community Empowerment Through Education: This testimonial shows weak alignment with community empowerment through education. While the CHW mentions conducting a 'health education session' and urging people to seek medical care for malaria symptoms, there is no evidence of lasting behavior change, community-wide impact, or self-reliance. The focus is primarily on sharing personal experiences with malaria rather than demonstrating how education led to community transformation or sustained preventive practices. | Resource and Material Distribution: The testimonial describes a health education session about malaria and personal experiences with the disease, but contains no mention of distributing any physical resources or materials. The CHW only discusses symptoms and urges people to visit health centers, which falls under education/advice without material support - an explicit exclusion criterion for this concept. | Monitoring and Follow-Up: This testimonial describes a one-time health education session where the CHW met a client and discussed malaria experiences. There is no evidence of ongoing interactions, returning to check on the client, or any follow-up activities. The CHW only urges people to visit health centers when experiencing symptoms, which is general advice rather than personalized monitoring. This aligns with the exclusion criteria of 'one-time visits or initial health education sessions with no follow-up.' | Trust and Cultural Mediation: The testimonial primarily focuses on clinical aspects of malaria and symptom education. While the CHW mentions conducting health education sessions and urging people to visit health centers, there is no evidence of building trust, navigating cultural barriers, or mediating between communities and health systems. The interaction described is purely informational without any cultural or trust-building elements, similar to the example 'I gave out leaflets about nutrition.' → 0.1 | Parsing failed for concept 'Trust and Cultural Mediation' | Clinical Interventions by CHWs: The testimonial primarily describes malaria symptoms and experiences, with the CHW conducting health education sessions and urging people to visit health centers. There is no mention of the CHW directly administering medication, treating wounds, or performing any clinical tasks. The CHW's role is limited to education and referral, which the exclusion criteria specifically states does not count as clinical intervention. | Mother and Infant Care: The testimonial focuses entirely on malaria symptoms, prevention, and general health education. There is no mention of prenatal care, childbirth, postpartum support, infant health, or any mother/infant-specific services. The content is about general disease management and prevention, not mother and infant care. | Successful Outcomes: The testimonial shows moderate alignment with successful outcomes. While the client sought medical attention after experiencing malaria symptoms (suggesting CHW education may have influenced this action), there's no clear indication of recovery or positive health outcomes. The CHW mentions urging people to visit health centers for symptoms, but doesn't provide evidence of actual impact or completed referrals. This aligns with the example scoring of 0.4 for referrals without known outcomes. | Material or Training Requests: The testimonial describes malaria symptoms and experiences but contains no requests for materials, supplies, or training. The CHW discusses educating people about malaria prevention and seeking medical attention, but does not ask for any resources or additional training to better serve their community. This clearly falls under the exclusion criteria as it describes the situation without making explicit requests for help. | Children Served: The testimonial mentions that WHO approved the malaria vaccine for use in children and states that malaria 'remains the number one killer of children.' However, the CHW's direct work focuses on adult clients and general health education sessions, with no specific mention of serving or interacting with children. The reference to children is contextual rather than indicating direct CHW involvement with minors. | Elderly Served: The testimonial focuses entirely on malaria education and experiences, with no mention of elderly individuals, seniors, or grandparents. The client mentioned is not identified as elderly, and there is no indication of CHW assistance specifically targeted at older adults. The content is about general malaria prevention and treatment, not elderly-focused care. | Women Served: The testimonial mentions 'a client whom I met during our health education session' and refers to this client as 'her' throughout, indicating the client is female. The CHW provided health education to this woman about malaria. However, the focus is on malaria education broadly rather than women-specific health challenges or gendered roles, which limits the score to moderate alignment. | Men Served: The testimonial discusses malaria experiences from a female client ('her experience', 'she lost her appetite') and the CHW's personal experience, but contains no references to men or boys being served, supported, or addressed in any context. The focus is entirely on malaria prevention and symptoms without any gender-specific support for males. | Families Served: The testimonial focuses entirely on individual experiences with malaria - one client's personal symptoms and the CHW's own experience. There is no mention of households, parents with children, or family units. The CHW describes a one-on-one health education session with a single client, which aligns with the exclusion criteria of 'individual help not connected to a family unit or structure.' | Marginalized Groups Served: The testimonial describes malaria education and experiences but makes no reference to marginalized or underserved groups. The client mentioned appears to be a general community member attending a health education session, with no indication of belonging to a stigmatized, excluded, or structurally disadvantaged population. The CHW's work described is general health education about malaria prevention, not targeted support for marginalized communities. | Financial Hardship: The testimonial focuses entirely on malaria symptoms, prevention, and medical experiences without any mention of financial constraints, inability to afford care, transportation costs, or material scarcity. The client sought medical attention without any indication of financial barriers, and there is no evidence of poverty or income-related issues in the narrative. | Social Isolation: The testimonial focuses entirely on malaria symptoms, prevention, and medical experiences. There is no mention of living alone, lack of support systems, loneliness, or social neglect. The client discussed their medical condition during a health education session, indicating social interaction rather than isolation. | Disease Burden: While malaria is discussed extensively, the testimonial focuses on acute episodes rather than chronic illness or disability. The client's experience describes temporary symptoms that resolved with medical attention, and the CHW's own malaria experience from a year ago was also an acute episode. There's no indication of recurrent malaria or long-term health impacts, which would be needed for a higher score according to the concept definition. | Stigma or Discrimination: The testimonial focuses entirely on the medical symptoms and experiences of malaria without any mention of social rejection, shame, exclusion, or judgment from others. The client and CHW discuss physical symptoms (fever, body aches, fatigue) and medical treatment, but there is no evidence of stigma or discrimination related to having malaria. The concept is clearly not present in this testimonial. | Mental or Emotional Distress: The testimonial focuses entirely on physical symptoms of malaria (fever, chills, body aches, fatigue, loss of appetite) and preventive health education. There is no mention of depression, hopelessness, trauma, stress, or any emotional/mental strain. The content is exclusively about physical illness and medical treatment, which falls under the exclusion criteria. | Lack of Resources: The testimonial describes malaria symptoms and experiences but contains no evidence of the CHW lacking resources. The CHW discusses educating clients and urging them to visit health centers, without mentioning any shortage of medicine, tools, or capacity constraints. The focus is on disease education and prevention messaging, not resource limitations. | Systemic Barriers: The testimonial describes malaria symptoms and personal experiences with the disease, but contains no mention of systemic barriers preventing CHW assistance. The CHW successfully conducts health education and encourages people to visit health centers. There are no references to facility shortages, overcrowding, distance issues, or other institutional obstacles that would prevent the CHW from helping patients. | Overburdened CHWs: The testimonial does not contain any evidence of CHW overburden. The CHW describes conducting health education sessions and shares experiences with malaria (both their own and a client's), but there is no mention of being exhausted, overwhelmed, having too many patients, or struggling with workload. The narrative focuses entirely on malaria symptoms and prevention education, with no indication of work-related stress or burden. | Lack of Follow-Through: The testimonial does not describe any instance where the CHW started to help but left an issue unresolved. The narrative focuses on malaria education and personal experiences with the disease, with both the client and CHW completing their medical treatment. The client 'went to seek medical attention' and received care, and the CHW describes their own completed experience with malaria. There is no evidence of abandonment, interrupted care, or failed attempts to help. | Lack of Knowledge: The testimonial shows no evidence of the CHW lacking knowledge. The CHW demonstrates understanding of malaria symptoms, prevention measures, and appropriate actions (urging people to visit health centers). They share personal and client experiences with malaria but never indicate uncertainty about how to proceed or need for additional training. This is a clear case where the concept is not present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Fibroids In the field I came across this woman who was suffering from fibroids, and she had very low self-esteem because she believed she had cancer and cancers are untreatable. I was touched when she told me she was only awaiting her death. I don’t know much about fibroids, but the little I know about it managed to cheer her up and build up her self-esteem once again. When I assured her that fibroids are non-cancerous growths, she said that the doctor also told her the same, but she could not believe it because doctors love telling people good lies so that they don’t give up in life. But since I also said the same, she promised to start going to treatment and also work on her self-esteem. I will be checking up on her just to lift up her spirits. ---</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.2,
+  "Menstrual Hygiene Education and Challenges": 0.05,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.0,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.65,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.4,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.9,
+  "Mental Health Awareness and Support": 0.85,
+  "Referrals and Advocacy": 0.6,
+  "Community Empowerment Through Education": 0.3,
+  "Resource and Material Distribution": 0.0,
+  "Monitoring and Follow-Up": 0.6,
+  "Trust and Cultural Mediation": 0.9,
+  "Clinical Interventions by CHWs": 0.1,
+  "Mother and Infant Care": 0.05,
+  "Successful Outcomes": 0.8,
+  "Material or Training Requests": 0.1,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.9,
+  "Men Served": 0.0,
+  "Families Served": 0.0,
+  "Marginalized Groups Served": 0.2,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.05,
+  "Disease Burden": 0.9,
+  "Stigma or Discrimination": 0.1,
+  "Mental or Emotional Distress": 0.9,
+  "Lack of Resources": 0.15,
+  "Systemic Barriers": 0.2,
+  "Overburdened CHWs": 0.05,
+  "Lack of Follow-Through": 0.1,
+  "Lack of Knowledge": 0.6
+}</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The CHW uses some knowledge about fibroids to reassure a client, but there is no mention of attending training or workshops. The statement “the little I know” suggests informal or limited knowledge rather than formal CHW training, matching the weak-alignment example (0.2). | Menstrual Hygiene Education and Challenges: The testimonial discusses supporting a woman with fibroids and improving her self-esteem; it does not address menstruation education, access to menstrual products, or related stigma. Therefore alignment with the menstrual hygiene concept is minimal. | Drug Abuse: Environment and Awareness: The testimonial discusses a woman's fear of fibroids and cancer, focusing on self-esteem and reassurance about her condition. There is no mention of substance abuse, addiction, alcohol, peer influence, or drug education, so the concept does not apply. | CHW-Led Infectious Disease Management: The testimonial describes a CHW supporting a woman with fibroids, a non-infectious condition. No discussion of infectious disease symptoms, prevention, or outreach is present, so the concept is not applicable. | Water Quality, Sanitation, and Hygiene: The testimonial focuses on counseling a woman about fibroids and encouraging treatment, with no mention of clean water, sanitation practices, or hygiene education. Therefore, the concept is not present. | Personal Disease Management and Adherence: The testimonial involves a specific health condition (fibroids) and describes the CHW encouraging the woman to seek and adhere to treatment, which reflects disease management guidance. However, it does not detail concrete, ongoing adherence behaviors (e.g., taking medication on schedule), so the alignment is moderate rather than strong. | Nutrition Education and Food Access: The testimonial focuses on reassuring a client about fibroids and encouraging treatment; it contains no discussion of healthy eating, food insecurity, or access to nutrition. Therefore, the concept is not present. | Sexual and Reproductive Health Education: The CHW gives the woman information about uterine fibroids—a condition related to reproductive organs—thus delivering some reproductive health education. However, it does not touch on the core topics highlighted in the concept (family planning, STI/HIV prevention, reproductive rights). Because the alignment is tangential and not a direct match to the specified inclusion areas, the fit is weak to moderate. | Gender-Based Violence (GBV) and Child Protection: The testimonial addresses a woman’s health concern (fibroids) and her emotional distress, but it does not mention abuse, exploitation, violence, or child protection issues. Therefore, it does not align with the GBV and Child Protection concept. | Health Literacy and Misconceptions: The woman falsely believes her fibroids are untreatable cancer and distrusts the doctor’s reassurance, displaying clear misinformation and mistrust in medicine. The CHW addresses this misconception. This is a strong, direct example of the concept. | Mental Health Awareness and Support: The CHW recognizes the woman’s emotional distress (low self-esteem, hopelessness, believing she is awaiting death) and provides reassurance and ongoing encouragement to improve her psychological well-being. This aligns strongly with mental health support, though it does not explicitly mention formal counseling or depression, hence slightly below a perfect score. | Parsing failed for concept 'Mental Health Awareness and Support' | Referrals and Advocacy: The CHW encouraged the woman to begin treatment and plans to follow up, acting as a motivator for navigating care. This aligns moderately with the concept (similar to example of asking someone to go to the clinic). However, there is no explicit formal referral or direct advocacy action mentioned, so alignment is partial rather than strong. | Community Empowerment Through Education: The CHW provides health information that may encourage the woman to seek treatment and improve self-esteem, suggesting potential behavior change. However, the story involves a single individual rather than broader community or peer education, and lasting change is not yet demonstrated, so alignment with community-level empowerment is weak. | Resource and Material Distribution: The testimonial describes providing emotional support and information, but there is no mention of giving any physical supplies (medication, food, kits, educational leaflets, etc.). Therefore, the concept of Resource and Material Distribution is not present. | Monitoring and Follow-Up: The CHW states, “I will be checking up on her,” indicating an intention for ongoing interaction to monitor the woman’s emotional well-being. This shows anticipated follow-up, aligning with the concept, but no concrete example of a completed return visit is given, so the match is moderate rather than strong. | Trust and Cultural Mediation: The CHW restores the woman’s confidence in medical advice after she distrusted doctors, directly illustrating the CHW’s role in building trust between the community member and the health system. This aligns closely with the concept’s definition and inclusion criteria. | Clinical Interventions by CHWs: The CHW provides emotional reassurance and encourages the woman to seek treatment, but does not administer medication, treat a wound, or perform any hands-on medical task. This is mainly health education/counseling, which is explicitly excluded from the concept, so only a very weak alignment. | Mother and Infant Care: Testimonial centers on supporting a woman with uterine fibroids and self-esteem; it does not mention pregnancy, childbirth, postpartum issues, or infant health. Therefore, alignment with the Mother and Infant Care concept is very weak. | Successful Outcomes: The CHW’s reassurance led to an immediate positive change: the woman’s self-esteem improved and she committed to begin treatment. This reflects a clear, though partial, successful outcome attributable to the CHW’s effort, aligning strongly with the concept’s definition of problem resolution or positive change. | Material or Training Requests: The CHW notes limited knowledge about fibroids (“I don’t know much about fibroids”), but does not explicitly ask for additional materials or training. Per the exclusion criteria, simply stating a lack without a direct request should not count; therefore alignment is very weak and scored low. | Children Served: The testimonial only discusses helping an adult woman with fibroids and contains no reference to minors or services directed at children or adolescents, so the concept does not apply. | Elderly Served: The testimonial discusses assisting a woman with fibroids, without any indication that she is an older adult or senior. Therefore, the concept of serving the elderly is not present. | Women Served: The testimonial centers on a CHW helping an adult woman with a gender-specific health concern (fibroids). The CHW provides information, emotional support, and follow-up, fitting the inclusion criteria of assisting women around health issues. This is a strong, direct alignment with the concept. | Men Served: The testimonial only discusses helping a woman with fibroids; no adult males or boys are mentioned. Therefore the concept of 'Men Served' is not present. | Families Served: The testimonial discusses assisting an individual woman with fibroids; it contains no mention of her household, parents, children, or any family-focused support. Therefore, the concept of 'Families Served' is not present. | Parsing failed for concept 'Families Served' | Marginalized Groups Served: The testimonial describes helping a woman with health misinformation and low self-esteem, but it does not indicate that she belongs to a structurally marginalized or socially excluded group (no mention of disability, minority status, poverty, stigma, etc.). There is minimal evidence of serving a marginalized population, hence a weak alignment. | Financial Hardship: The testimonial discusses emotional distress and misconceptions about fibroids but provides no indication of financial difficulties, lack of income, or material scarcity. | Social Isolation: The testimonial focuses on a woman’s misunderstanding of her medical condition and low self-esteem. There is no clear mention that she lives alone, lacks social support, or feels lonely. A slight score is given only because the CHW plans to ‘check up on her,’ which could suggest limited support, but this is not explicit. | Disease Burden: The testimonial centers on a woman living with fibroids, a non-cancerous but chronic gynecological condition that requires ongoing care. This fits the concept’s inclusion of long-term or recurrent illness. The story discusses her condition’s impact on her life and her need for treatment, showing strong, direct alignment with Disease Burden. | Stigma or Discrimination: The story focuses on the woman’s personal fear and low self-esteem about having what she thought was cancer; there is no clear reference to her being rejected, judged, or discriminated against by others. Any ‘shame’ is implied and internal, not socially imposed, so evidence for stigma is minimal. | Mental or Emotional Distress: The woman expresses severe hopelessness (“awaiting her death”) and very low self-esteem linked to her health fears. These are clear signs of emotional distress fitting the concept definition. The testimonial centers on alleviating this distress, matching the inclusion criteria. No physical-only complaints without emotional component are highlighted, so alignment is strong and unambiguous. | Lack of Resources: The CHW notes, “I don’t know much about fibroids,” implying limited knowledge/training—a minor resource gap analogous to the example “I need more training.” However, there is no mention of missing medicines, tools, or systemic support. Hence only a weak alignment to the Lack of Resources concept. | Systemic Barriers: The only potential systemic element is the patient’s mistrust of doctors (“doctors love telling people good lies”), which hints at a broader confidence gap in the health system. However, there are no clear references to institutional shortages, corruption, or structural obstacles preventing care. Thus alignment with the ‘Systemic Barriers’ concept is weak and receives a low score. | Overburdened CHWs: The testimonial describes assisting a single patient and does not mention heavy workload, exhaustion, or being overwhelmed. Therefore, alignment with the 'Overburdened CHWs' concept is virtually absent, warranting a very low score. | Lack of Follow-Through: The CHW provided emotional support and stated an intention to continue checking on the woman. There is no indication that the CHW abandoned the case or that help was interrupted; the outcome is simply not yet known. This aligns with the exclusion (waiting period without abandonment), so only minimal evidence for lack of follow-through. | Lack of Knowledge: The CHW explicitly says, “I don’t know much about fibroids,” indicating limited knowledge. While she was still able to reassure the woman, the statement reflects uncertainty and a potential knowledge gap, fitting the inclusion criteria for Lack of Knowledge, though not as strongly as an outright inability to act, hence a moderate score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Fibroids In the field I came across this woman who was suffering from fibroids, and she had very low self-esteem because she believed she had cancer and cancers are untreatable. I was touched when she told me she was only awaiting her death. I don’t know much about fibroids, but the little I know about it managed to cheer her up and build up her self-esteem once again. When I assured her that fibroids are non-cancerous growths, she said that the doctor also told her the same, but she could not believe it because doctors love telling people good lies so that they don’t give up in life. But since I also said the same, she promised to start going to treatment and also work on her self-esteem. I will be checking up on her just to lift up her spirits. ---</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.2,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.0,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.8,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.3,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.8,
+  "Mental Health Awareness and Support": 0.8,
+  "Referrals and Advocacy": 0.6,
+  "Community Empowerment Through Education": 0.3,
+  "Resource and Material Distribution": 0.0,
+  "Monitoring and Follow-Up": 0.7,
+  "Trust and Cultural Mediation": 0.8,
+  "Clinical Interventions by CHWs": 0.1,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.7,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.9,
+  "Men Served": 0.0,
+  "Families Served": 0.0,
+  "Marginalized Groups Served": 0.3,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.2,
+  "Disease Burden": 0.8,
+  "Stigma or Discrimination": 0.2,
+  "Mental or Emotional Distress": 0.8,
+  "Lack of Resources": 0.1,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.6
+}</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial shows a CHW providing health education about fibroids, but explicitly states 'I don't know much about fibroids, but the little I know about it managed to cheer her up.' This indicates minimal formal training on the topic. The CHW is serving their community based on limited knowledge rather than comprehensive training, aligning with the example 'I started giving advice to neighbors based on what I learned informally.' → 0.2 | Menstrual Hygiene Education and Challenges: The testimonial focuses on a woman with fibroids and the CHW's counseling about the non-cancerous nature of the condition. While fibroids are a gynecological condition, the testimonial does not mention menstruation, menstrual hygiene, education about periods, or access to menstrual products. The focus is entirely on medical counseling about fibroids and building the patient's self-esteem, which falls outside the concept's definition. | Drug Abuse: Environment and Awareness: The testimonial focuses entirely on a woman with fibroids and her misconceptions about cancer. There is no mention of substance abuse, addiction, alcohol, drugs, or any social/environmental factors related to drug use. The concept clearly does not apply to this testimonial. | CHW-Led Infectious Disease Management: The testimonial describes a CHW helping a woman with fibroids, which is a non-infectious condition (benign uterine tumors). While the CHW provides health education and emotional support, this does not involve infectious disease management, prevention, or education about communicable diseases like TB or COVID-19. The concept explicitly requires focus on infectious diseases, which is not present in this case. | Water Quality, Sanitation, and Hygiene: The testimonial focuses entirely on counseling a woman with fibroids about her medical condition and self-esteem. There is no mention of water quality, sanitation practices, hygiene education, handwashing, or any water-related health interventions. The content is exclusively about providing emotional support and medical information about fibroids. | Personal Disease Management and Adherence: Strong alignment with the concept. The testimonial describes a CHW helping a woman manage her fibroid condition by addressing misconceptions, building confidence in the diagnosis, and encouraging treatment adherence. The woman explicitly promises to 'start going to treatment' as a result of the CHW's guidance, which directly relates to disease management and treatment adherence. The score is not higher because the actual adherence hasn't occurred yet - it's a commitment rather than demonstrated adherence. | Nutrition Education and Food Access: The testimonial focuses entirely on a CHW counseling a woman about fibroids and addressing her misconceptions about cancer. There is no mention of nutrition education, food access, healthy eating, or any food-related topics. The content is exclusively about medical counseling and emotional support regarding a health condition unrelated to nutrition. | Sexual and Reproductive Health Education: The testimonial discusses fibroids, which are a reproductive health condition, but focuses on emotional support and correcting misconceptions about cancer rather than education about sexual/reproductive health topics like family planning, STIs, or safe sex. While fibroids are related to the reproductive system, the content doesn't align with the concept's core focus areas or examples. | Gender-Based Violence (GBV) and Child Protection: The testimonial describes a CHW helping a woman with fibroids who has low self-esteem due to health concerns. There is no mention of abuse, violence, exploitation, or any form of GBV or child protection issues. The emotional distress described is explicitly related to a medical condition (fibroids) and fear of cancer, not violence or abuse. | Health Literacy and Misconceptions: Strong alignment with the concept. The testimonial clearly describes a health misconception where the woman mistakenly believed fibroids were cancer and that 'cancers are untreatable.' Additionally, she demonstrated mistrust in medicine, believing 'doctors love telling people good lies.' The CHW corrected this misinformation by explaining that fibroids are non-cancerous growths, directly addressing both the misbelief about disease nature and medical mistrust. | Mental Health Awareness and Support: Strong alignment with mental health support. The testimonial describes a woman with 'very low self-esteem' who 'believed she had cancer' and was 'awaiting her death' - clear indicators of emotional distress and anxiety. The CHW provided emotional support by cheering her up, building her self-esteem, and committing to follow-up visits to 'lift up her spirits.' While the medical condition (fibroids) is mentioned, the focus is on addressing her psychological well-being and emotional trauma. | Referrals and Advocacy: The testimonial shows moderate alignment with advocacy. The CHW advocates for the woman's health by reinforcing medical information about fibroids, encouraging her to continue treatment, and committing to follow-up support. However, there's no explicit mention of making referrals, helping with appointments, or navigating the healthcare system. The advocacy is more emotional/educational support rather than system navigation. | Community Empowerment Through Education: This testimonial shows a one-on-one educational interaction where the CHW provided reassurance about fibroids being non-cancerous. While this helped restore the woman's self-esteem and motivated her to seek treatment, it represents an isolated education event with an individual rather than community-wide change or group action. The CHW plans to follow up, but there's no evidence yet of lasting behavior change or community empowerment. This aligns with the exclusion criteria of 'one-time events or isolated education without lasting behavior change.' | Resource and Material Distribution: The testimonial describes a CHW providing emotional support and health education to a woman with fibroids, but contains no mention of distributing any physical resources, materials, medication, or supplies. The interaction was purely educational and supportive in nature, which explicitly falls under the exclusion criteria of 'discussions of education or advice without material support.' | Monitoring and Follow-Up: The testimonial shows moderate alignment with monitoring and follow-up. While the CHW explicitly states 'I will be checking up on her just to lift up her spirits,' indicating planned future follow-up visits, this is a statement of intent rather than describing actual ongoing monitoring that has already occurred. The interaction described is primarily a single encounter where the CHW provided reassurance and education about fibroids, which aligns more with initial support than established follow-up care. | Trust and Cultural Mediation: Strong alignment with trust-building. The CHW gained the woman's trust where the doctor could not, with the woman explicitly stating she didn't believe the doctor but would believe the CHW saying the same thing. This demonstrates the CHW's role as a trusted intermediary between the community member and the health system, helping overcome mistrust of medical professionals. | Clinical Interventions by CHWs: The CHW provided emotional support and health education about fibroids being non-cancerous, but did not perform any direct clinical interventions such as administering medication, treating wounds, or managing physical injuries. This aligns with the exclusion criteria of 'health education without direct clinical interaction.' The minimal score reflects that while health-related support was provided, no actual clinical tasks were performed. | Mother and Infant Care: This testimonial focuses on supporting a woman with fibroids, which is a general women's health issue not related to pregnancy, childbirth, postpartum care, or infant health. The concept explicitly excludes 'general family or women's health support not specific to mother/infant,' which directly applies to this case. | Successful Outcomes: The testimonial shows moderate alignment with successful outcomes. The CHW helped improve the woman's mental state and self-esteem by reinforcing medical information about fibroids being non-cancerous. The woman promised to start treatment and work on her self-esteem, indicating positive change. However, the outcome is not fully resolved as the CHW plans future check-ups and the actual treatment hasn't begun yet. This aligns with the partial improvement criteria but lacks the concrete completion seen in higher-scoring examples. | Material or Training Requests: The testimonial describes a CHW's encounter with a woman suffering from fibroids and the CHW's efforts to provide emotional support. While the CHW mentions 'I don't know much about fibroids,' this is merely an acknowledgment of limited knowledge, not an explicit request for training or materials. The concept requires explicit requests for help, which are absent in this testimonial. | Children Served: The testimonial focuses entirely on an adult woman suffering from fibroids. There is no mention of children, adolescents, or minors under 18 years old. The CHW's interaction and support are directed solely at an adult patient, making this concept clearly not present in the testimonial. | Elderly Served: The testimonial describes a CHW helping a woman with fibroids and emotional support, but there is no indication that this woman is elderly, a senior, or a grandparent. The focus is on her medical condition and emotional state, not her age. Without any age-related descriptors, this concept clearly does not apply. | Women Served: Strong direct alignment. The CHW provided specific health education and emotional support to a woman suffering from fibroids, addressing her misconceptions about cancer and helping rebuild her self-esteem. This clearly shows assistance for a woman around a specific health challenge, with ongoing commitment to follow-up care. | Men Served: The testimonial exclusively describes supporting a woman with fibroids and her health concerns. There is no mention of men or boys in any context, making this concept clearly not present in the testimonial. | Families Served: The testimonial describes a CHW's interaction with a single woman suffering from fibroids. There is no mention of her family members, household, children, or any family-focused intervention. The support provided was entirely individual-focused, addressing only the woman's personal health concerns and self-esteem. This clearly falls under the exclusion criteria of 'individual help not connected to a family unit or structure.' | Marginalized Groups Served: The testimonial describes helping a woman with fibroids who had low self-esteem and misconceptions about her condition. While she was experiencing psychological distress and medical anxiety, there's no clear indication she belongs to a structurally marginalized or socially excluded group. The CHW provided emotional support and health education, but the woman's challenges appear to be primarily health-related rather than stemming from social marginalization or stigma. | Financial Hardship: The testimonial focuses entirely on a woman's emotional distress and misconceptions about her fibroid diagnosis, with no mention of financial constraints, inability to afford care, transportation issues, or material scarcity. The woman appears to have access to medical care (she mentions what 'the doctor also told her') and the barriers described are psychological rather than financial. | Social Isolation: The testimonial shows minimal evidence of social isolation. While the woman has low self-esteem and distrust of medical professionals, there's no mention of her living alone, lacking support systems, or being abandoned. The CHW's promise to check up on her suggests she may benefit from additional support, but this alone doesn't indicate social isolation as defined by the concept. | Disease Burden: Strong alignment with the concept. The testimonial describes a woman suffering from fibroids, which represents a chronic condition requiring ongoing medical treatment. While fibroids are benign, they clearly constitute a long-term health issue that has significantly impacted the woman's mental health and quality of life, as evidenced by her low self-esteem and belief she was dying. The CHW's commitment to ongoing check-ups further indicates this is a chronic condition requiring sustained support. | Stigma or Discrimination: The testimonial describes a woman with low self-esteem due to her medical condition (fibroids), but this stems from her personal misconception about having cancer rather than social rejection or judgment from others. There is no mention of shame, exclusion, or discrimination from her community. Her distress is caused by fear of death and mistrust of medical information, not social stigma. | Mental or Emotional Distress: Strong alignment with the concept. The woman exhibits clear emotional distress through 'very low self-esteem,' believing she has cancer and 'awaiting her death,' which demonstrates hopelessness. Her distrust of medical professionals and need for reassurance further indicates emotional overwhelm. While the distress stems from a physical condition (fibroids), the testimonial focuses on the psychological impact and emotional suffering, making it a strong match for mental/emotional distress. | Lack of Resources: The CHW mentions 'I don't know much about fibroids,' which indicates a knowledge gap that could be considered a lack of training resources. However, this is a weak alignment because the CHW was still able to provide support and the testimonial doesn't explicitly discuss lacking medicine, tools, or other resources needed to help the patient. The focus is on providing emotional support and encouragement rather than being unable to help due to resource constraints. | Parsing failed for concept 'Lack of Resources' | Systemic Barriers: The testimonial does not mention any systemic barriers. The CHW successfully provided emotional support and health education to a woman with fibroids. There are no references to health facility shortages, institutional problems, or external conditions preventing the CHW from helping. The issue was the patient's misconceptions and low self-esteem, which the CHW addressed directly. | Overburdened CHWs: The testimonial describes a CHW successfully providing emotional support and education to a patient with fibroids. There is no mention of excessive workload, exhaustion, or being overwhelmed. The CHW appears to have adequate time to engage meaningfully with the patient and even plans follow-up visits. This aligns with the exclusion criteria of CHWs who are able to deliver care successfully. | Lack of Follow-Through: The CHW successfully addressed the patient's concerns about fibroids, helped rebuild her self-esteem, and convinced her to resume treatment. The CHW also commits to future check-ins ('I will be checking up on her'). There is no evidence of abandonment, interrupted care, or unresolved issues - the intervention appears complete and ongoing. | Lack of Knowledge: The CHW explicitly states 'I don't know much about fibroids,' indicating a knowledge gap. However, they were able to provide basic reassurance using 'the little I know,' suggesting partial knowledge rather than complete inability to address the issue. This aligns moderately with the concept as the CHW acknowledges limited knowledge but was still able to help somewhat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>First Aid for Nose Bleed During nose bleed, blood flows from one or both nostrils. It can be heavy or light and last from a few seconds to 15 minutes or more. I came across a patient who had nose bleeding each time and she did not know what to do. I told her how to stop it by: sitting down and firmly pinch the soft part of your nose, just above your nostrils, for at least 10-15 minutes. Lean forward and breathe through your mouth. This will drain blood into your nose instead of down the back of your throat. Place an ice pack/bag or frozen vegetables covered by a towel on the bridge of your nose. Stay upright rather than lying down, as this reduces blood pressure in the blood vessels of your nose and will discourage further bleeding. At least she got relieved after doing all these leading to nose bleed occurring rarely. ---</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.2,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.0,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.5,
+  "Nutrition Education and Food Access": 0.05,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.8,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.05,
+  "Community Empowerment Through Education": 0.6,
+  "Resource and Material Distribution": 0.05,
+  "Monitoring and Follow-Up": 0.2,
+  "Trust and Cultural Mediation": 0.05,
+  "Clinical Interventions by CHWs": 0.8,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.9,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.8,
+  "Men Served": 0.0,
+  "Families Served": 0.0,
+  "Marginalized Groups Served": 0.05,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.6,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.0,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.05,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial shows a CHW providing first-aid advice, but it never mentions receiving training or attending workshops. Knowledge could be informal or pre-existing, so alignment with the concept is weak and similar to the 0.2 example provided. | Menstrual Hygiene Education and Challenges: The testimonial focuses solely on first aid for nosebleeds and contains no mention of menstruation, menstrual products, education, or related stigma. Therefore, the concept does not apply. | Drug Abuse: Environment and Awareness: The testimonial discusses first aid for nosebleeds without any reference to substance abuse, social/environmental factors influencing drug use, or related education. Therefore, the concept is not present. | CHW-Led Infectious Disease Management: The testimonial describes providing first-aid guidance for a nosebleed, which is not an infectious disease topic. There is no mention of CHW activities related to preventing or managing infectious diseases like TB or COVID-19. | Water Quality, Sanitation, and Hygiene: The testimonial focuses on first aid steps for treating a nosebleed and does not mention clean water, sanitation practices, or hygiene education. Therefore the concept is not present. | Personal Disease Management and Adherence: The CHW gives the patient practical steps to manage an acute health condition (nosebleed) and the patient follows these steps to reduce episodes. This reflects guidance on managing a condition, aligning partially with the concept. However, it is not about chronic or infectious disease nor medication adherence, so the alignment is moderate rather than strong. | Nutrition Education and Food Access: The testimonial focuses on first aid techniques for nosebleeds and does not discuss healthy eating, food insecurity, or access to nutrition. The brief mention of frozen vegetables is only as a cooling compress, not related to nutrition education or food access, yielding only negligible relevance. | Sexual and Reproductive Health Education: The testimonial focuses solely on first-aid management of a nosebleed; it contains no content related to family planning, STI/HIV prevention, condoms, or any other reproductive health education topic. Therefore the concept is not present. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses solely on giving first-aid instructions for a nosebleed and does not mention any abuse, violence, exploitation, or child protection issues. Therefore, it does not align with the GBV and Child Protection concept. | Health Literacy and Misconceptions: The testimonial centers on a patient who “did not know what to do” for a nose bleed and received step-by-step guidance from the CHW. This reflects a clear case where lack of knowledge affected how the patient managed a health situation, fitting the concept’s definition (effects of lack of knowledge on health decisions). There is no contradictory accurate understanding present, so alignment is strong though not absolutely focused on correcting explicit misinformation. | Parsing failed for concept 'Health Literacy and Misconceptions' | Mental Health Awareness and Support: Testimonial focuses solely on providing physical first-aid instructions for nosebleeds; there is no mention of psychological well-being, emotional distress, or mental health support. | Parsing failed for concept 'Mental Health Awareness and Support' | Referrals and Advocacy: The CHW provides first-aid instructions directly but does not mention helping the client navigate the health system, arranging appointments, or referring to a facility. Thus, evidence for referrals or advocacy is virtually absent, warranting a very low score. | Community Empowerment Through Education: The CHW provided education that enabled the patient to manage future nosebleeds independently, indicating some self-reliance and lasting behavior change. However, the story involves a single individual rather than wider community or peer education, so the alignment is moderate rather than strong. | Resource and Material Distribution: The testimonial only describes giving advice on stopping a nose bleed; there is no mention of the CHW providing or handing out supplies. According to the concept definition, distribution of physical resources is required, so alignment is minimal. | Monitoring and Follow-Up: The testimonial mainly describes giving first-aid instructions during a single encounter. Although it notes that the client was later relieved, there is no clear statement that the CHW returned, checked progress, or engaged in ongoing follow-up. This offers only minimal evidence of monitoring and follow-up, so the alignment is weak. | Trust and Cultural Mediation: The testimonial describes providing clinical first-aid instructions for a nosebleed with no mention of translating, addressing cultural barriers, or building trust. This is primarily a clinical interaction without cultural or trust-related themes, so alignment with the concept is minimal. | Clinical Interventions by CHWs: The CHW provided immediate first-aid instructions to control an active nosebleed (pinching the nose, leaning forward, applying an ice pack). This constitutes assisting with a basic medical task aimed at treating a minor physical condition, fitting the inclusion criteria for clinical interventions. While the CHW did not physically perform the steps herself, the direct guidance to manage the acute episode goes beyond general health education, warranting a strong (though not perfect) alignment score. | Mother and Infant Care: The testimonial discusses first-aid steps for managing a nosebleed in a patient; it does not mention pregnancy, childbirth, postpartum issues, or infant health. Therefore it falls outside the scope of Mother and Infant Care. | Successful Outcomes: The CHW provided first-aid instructions that the patient followed, resulting in relief and the nosebleeds occurring only rarely. This is a clear, direct example of problem resolution attributed to the CHW’s intervention, fitting the concept’s definition and inclusion criteria. | Material or Training Requests: The testimonial simply describes how the CHW managed a nosebleed and does not include any request for additional materials, supplies, or training. Therefore, the concept does not apply. | Children Served: The testimonial describes advising a patient on treating a nosebleed but does not mention children, adolescents, or any support directed toward minors. Therefore, the concept is not present. | Elderly Served: The testimonial describes providing first-aid guidance for a nosebleed to an unspecified patient; there is no indication that the person is an older adult or that seniors are being specifically served. | Women Served: The CHW provided health assistance to an individual identified as a woman (“she”) by giving first-aid guidance for a nosebleed. This meets the inclusion of assisting a female with a health need. While the issue is not gender-specific, the testimonial clearly depicts a woman being served, warranting a strong alignment (0.8). | Men Served: The testimonial describes providing first-aid instructions to a female patient; there is no mention of males or gender-specific support. Therefore the concept “Men Served” is not present. | Families Served: The testimonial describes assisting a single patient with a nosebleed and contains no reference to households, parents with children, or any family unit. Therefore, the 'Families Served' concept is not present. | Parsing failed for concept 'Families Served' | Marginalized Groups Served: The testimonial describes providing general first-aid advice for a patient with nosebleeds, without indicating that the patient belongs to a structurally excluded or stigmatized group. Therefore there is essentially no evidence of serving a marginalized group. | Financial Hardship: The testimonial focuses on giving first-aid instructions for a nosebleed; it does not mention any inability to afford care, lack of income, or other material scarcity. Therefore, the concept of Financial Hardship is not present. | Social Isolation: The testimonial only discusses first-aid steps for a nosebleed and contains no mention of the patient living alone, lacking support, or feeling lonely. Therefore, the concept of Social Isolation is not present. | Disease Burden: The testimonial mentions a patient experiencing repeated nosebleeds (“each time”), indicating a recurrent health problem rather than a one-off event. This fits the inclusion criterion of long-term or frequent illness episodes. However, nosebleeds are not presented as a chronic disease with major life impact, so the alignment is moderate rather than strong. | Stigma or Discrimination: The testimonial only discusses first-aid steps for managing a nosebleed. There is no mention of social rejection, judgment, shame, or any discriminatory experience, so the concept does not apply. | Mental or Emotional Distress: The testimonial focuses entirely on managing a physical issue (nosebleeds) and provides first-aid instructions. It does not mention any feelings of depression, hopelessness, trauma, or emotional overwhelm, so the concept is not present. | Lack of Resources: The testimonial describes giving first-aid advice for a nosebleed but does not mention any shortage of medicines, tools, or other resources. Therefore, the 'Lack of Resources' concept is not applicable. | Systemic Barriers: The testimonial focuses on providing first-aid advice for a nosebleed and reports successful relief. It does not mention any institutional shortages, distance to care, corruption, or other external systemic obstacles that hindered assistance. Therefore, the concept of systemic barriers is not present. | Overburdened CHWs: The testimonial simply recounts giving first-aid advice for a single patient and contains no indication that the CHW is overwhelmed, exhausted, or facing excessive workload. | Lack of Follow-Through: The CHW provided guidance that successfully relieved the patient's nosebleeds; there is no indication of abandonment or unresolved issue. Therefore, almost no evidence of lack of follow-through. | Lack of Knowledge: The CHW confidently provided correct first-aid steps for a nosebleed; there is no indication that the CHW was unsure or required additional training. The testimonial describes patient ignorance, not CHW lack of knowledge, so the concept does not apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>First Aid for Nose Bleed During nose bleed, blood flows from one or both nostrils. It can be heavy or light and last from a few seconds to 15 minutes or more. I came across a patient who had nose bleeding each time and she did not know what to do. I told her how to stop it by: sitting down and firmly pinch the soft part of your nose, just above your nostrils, for at least 10-15 minutes. Lean forward and breathe through your mouth. This will drain blood into your nose instead of down the back of your throat. Place an ice pack/bag or frozen vegetables covered by a towel on the bridge of your nose. Stay upright rather than lying down, as this reduces blood pressure in the blood vessels of your nose and will discourage further bleeding. At least she got relieved after doing all these leading to nose bleed occurring rarely. ---</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.2,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.0,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.4,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.7,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.0,
+  "Community Empowerment Through Education": 0.3,
+  "Resource and Material Distribution": 0.1,
+  "Monitoring and Follow-Up": 0.2,
+  "Trust and Cultural Mediation": 0.1,
+  "Clinical Interventions by CHWs": 0.2,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.8,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.8,
+  "Men Served": 0.0,
+  "Families Served": 0.0,
+  "Marginalized Groups Served": 0.1,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.7,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.0,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial shows a CHW providing first aid advice for nosebleeds, but there is no explicit mention of formal training, workshops, or structured learning. The knowledge demonstrated could have been acquired informally or through experience. This aligns with the example 'I started giving advice to neighbors based on what I learned informally' which scores 0.2. | Menstrual Hygiene Education and Challenges: This testimonial is about first aid treatment for nosebleeds, which is a general medical condition unrelated to menstruation. There is no mention of menstrual hygiene, products, education, or any gender-specific health issues related to menstruation. The content falls under general medical care rather than menstrual hygiene education. | Drug Abuse: Environment and Awareness: The testimonial focuses entirely on providing first aid instructions for nosebleeds, with no mention of substance abuse, addiction, alcohol, drugs, or any social/environmental factors related to drug use. This is a purely medical/clinical intervention without any connection to the drug abuse concept. | CHW-Led Infectious Disease Management: This testimonial describes first aid treatment for nosebleeds, which is not an infectious disease. While it shows CHW health education and patient care, nosebleeds are a physical condition caused by trauma, dry air, or other non-infectious factors. The concept specifically focuses on infectious diseases like TB or COVID-19, making this testimonial completely outside the scope of the concept. | Water Quality, Sanitation, and Hygiene: The testimonial focuses entirely on first aid treatment for nosebleeds, with no mention of water quality, sanitation, or hygiene practices. The content is about medical first aid procedures (pinching nose, using ice, positioning) rather than disease prevention through clean water, handwashing, or sanitation education. | Personal Disease Management and Adherence: This testimonial describes managing a recurring medical condition (nosebleeds) through specific interventions and lifestyle adjustments. While it involves health management guidance from a CHW that led to improvement ('nose bleed occurring rarely'), it lacks the chronic/infectious disease context and treatment adherence elements emphasized in the concept definition. The focus is on first aid techniques rather than medication adherence or disease management. | Nutrition Education and Food Access: The testimonial is entirely focused on providing first aid instructions for nosebleeds. There is no mention of food, nutrition, healthy eating, food security, or any nutrition-related topics. The content explicitly deals with a medical emergency procedure, which falls outside the scope of nutrition education and food access. | Sexual and Reproductive Health Education: The testimonial is entirely focused on providing first aid instructions for nosebleeds. There is no mention of family planning, STI prevention, HIV awareness, reproductive rights, or any sexual health topics. This is a clear example of general health education that falls outside the scope of sexual and reproductive health. | Gender-Based Violence (GBV) and Child Protection: This testimonial describes a CHW providing first aid instructions for nosebleeds. There is no mention of abuse, violence, exploitation, or any form of GBV or child protection issues. The health issue (nosebleeds) is presented as a medical condition without any connection to violence or abuse. This clearly falls under the exclusion criteria as it's a general health intervention without reference to violence or abuse. | Health Literacy and Misconceptions: The testimonial shows moderate alignment with health literacy issues. The patient 'did not know what to do' about nosebleeds, indicating a clear knowledge gap about basic first aid. The CHW provided education to address this lack of health knowledge, teaching proper techniques. While this isn't about disease misconceptions or mistrust in medicine, it demonstrates how lack of basic health knowledge affected the patient's ability to manage a common health issue. | Parsing failed for concept 'Health Literacy and Misconceptions' | Mental Health Awareness and Support: This testimonial focuses entirely on providing physical first aid for nosebleeds. There is no mention of psychological well-being, emotional support, or mental health concerns. The CHW is addressing a purely physical medical condition without any mental or emotional context, which falls under the exclusion criteria. | Referrals and Advocacy: The testimonial describes providing first aid instructions for nosebleeds but contains no mention of referrals, appointments, or healthcare navigation. The CHW provided direct care advice rather than acting as an intermediary or advocate within the health system. | Community Empowerment Through Education: This testimonial shows a one-on-one educational intervention about managing nosebleeds, with some evidence of behavior change (the patient learned what to do and experienced improvement). However, it lacks the community-wide impact, peer education, or group action that would indicate stronger community empowerment. The education appears isolated to a single patient rather than creating broader community change or self-reliance. | Resource and Material Distribution: The testimonial describes providing first aid instructions and advice for managing nosebleeds, but does not mention distributing any physical materials or supplies. While the CHW mentions using an ice pack/frozen vegetables as part of the treatment advice, there's no indication they actually provided these items. This aligns with the exclusion criteria of 'discussions of education or advice without material support.' | Monitoring and Follow-Up: The testimonial describes a one-time educational intervention where the CHW taught a patient how to manage nosebleeds. While the CHW notes the patient 'got relieved' and nosebleeds occurred 'rarely' afterward, there is no explicit mention of the CHW returning to check on the patient or conducting any follow-up visits. The outcome is observed but not through active monitoring by the CHW, aligning with the exclusion criteria of 'one-time visits or initial health education sessions with no follow-up.' | Trust and Cultural Mediation: This testimonial focuses on clinical first aid instruction without cultural mediation or trust-building elements. While the CHW provided helpful medical guidance to a patient, there's no mention of navigating cultural barriers, translating concepts, or building community trust. The interaction is purely clinical/educational, similar to the example 'I gave out leaflets about nutrition' (0.1). | Clinical Interventions by CHWs: This testimonial describes the CHW providing detailed first aid instructions for nosebleeds, but there is no evidence of direct clinical intervention. The CHW educated the patient on proper techniques (pinching nose, leaning forward, using ice) rather than physically administering treatment themselves. This aligns with health education rather than direct clinical care, similar to the example 'I spoke to the group about taking care of wounds' (0.1). The score is slightly higher (0.2) because the instructions were specific and resulted in symptom improvement, but it still falls under education rather than direct clinical intervention. | Mother and Infant Care: The testimonial describes providing first aid advice for nosebleeds to a patient. There is no mention of pregnancy, childbirth, postpartum care, infant health, or any mother/infant-specific support. The patient is not identified as a mother or pregnant woman, and the health issue (nosebleeds) is unrelated to maternal or infant care. | Successful Outcomes: Strong direct alignment with the concept. The testimonial clearly describes a successful outcome where the CHW's intervention led to positive change - the patient 'got relieved' and nose bleeds now occur 'rarely' instead of 'each time.' This shows both immediate relief and long-term improvement, directly attributable to the CHW's first aid guidance. | Material or Training Requests: The testimonial describes a CHW providing first aid advice to a patient with nosebleeds. There are no requests for materials, supplies, or training. The CHW demonstrates knowledge and successfully helps the patient, but does not ask for any resources or additional education. This clearly falls under the exclusion criteria as it describes CHW actions without any explicit request for help. | Children Served: The testimonial describes providing first aid advice to 'a patient' with nosebleeds, with no indication that this patient was a child or minor under 18. The language used ('patient,' 'she') suggests an adult recipient of care. There is no mention of children, adolescents, or any age-specific indicators that would align with the concept definition. | Elderly Served: The testimonial describes helping a patient with nosebleeds but makes no mention of the patient's age, elderly status, or any characteristics that would identify them as a senior. The focus is entirely on the medical condition and first aid treatment, without any reference to age-related factors or elderly-specific needs. | Women Served: Strong direct alignment. The CHW describes providing specific medical assistance and education to a female patient ('she') who had recurring nosebleeds. The CHW taught her practical first aid techniques, which directly addresses a health need. While not focused on gendered health issues, this clearly shows a woman receiving health education and assistance from the CHW, resulting in improved outcomes ('she got relieved'). | Men Served: The testimonial describes helping a female patient ('she') with nosebleeds through first aid instruction. There is no mention of men or boys, nor any gendered roles or challenges related to males. The concept explicitly requires adult males or boys to be described in the context of support, health issues, or gendered challenges, which is not present in this testimonial. | Families Served: The testimonial describes helping a single patient with nosebleeds. There is no mention of family members, household context, or family-focused interventions. This is individual help not connected to a family unit, which falls under the exclusion criteria. | Marginalized Groups Served: The testimonial describes providing first aid education to a patient with nosebleeds, but there is no indication that this person belongs to a marginalized or underserved group. The CHW is providing general health education without any reference to structural exclusion, stigma, or special vulnerabilities that would characterize marginalized populations. | Financial Hardship: The testimonial describes a medical intervention for nosebleeds with no mention of financial constraints, inability to afford care, or material scarcity. The patient received free advice but there's no indication this was due to financial need rather than simply lack of knowledge about first aid. | Parsing failed for concept 'Financial Hardship' | Social Isolation: The testimonial focuses entirely on providing medical advice for treating nosebleeds. There is no mention of the patient living alone, lacking support systems, experiencing loneliness, or being socially isolated. The interaction appears to be a standard medical consultation about a physical health issue, with no evidence of social isolation or abandonment. | Disease Burden: The testimonial describes a patient with recurrent nosebleeds ('each time'), indicating a chronic or recurring condition. While not as severe as diabetes or major disability, the repeated nature of the problem and its impact on the patient's life (not knowing what to do, needing intervention) aligns moderately with the concept of disease burden. The condition improved but still occurs 'rarely,' suggesting ongoing management of a chronic issue. | Stigma or Discrimination: The testimonial describes a medical first aid intervention for nosebleeds with no mention of social rejection, judgment, shame, or exclusion. The patient's issue was lack of knowledge about treatment, not any form of stigma or discrimination related to their condition. | Parsing failed for concept 'Stigma or Discrimination' | Mental or Emotional Distress: This testimonial focuses entirely on providing physical first aid treatment for nosebleeds. There is no mention of depression, hopelessness, trauma, stress, or any emotional distress. The patient's concern was purely medical (recurring nosebleeds), and the CHW's intervention was strictly physical care instructions. This aligns with the exclusion criteria of 'physical complaints unrelated to emotional wellbeing.' | Lack of Resources: The testimonial describes a CHW successfully providing first aid advice for nosebleeds. There is no mention of lacking medicine, tools, or support. The CHW was able to effectively help the patient using knowledge and simple techniques that don't require special resources. The patient experienced relief after following the advice, indicating the CHW had sufficient capacity to address the problem. | Parsing failed for concept 'Lack of Resources' | Systemic Barriers: The testimonial describes a CHW successfully providing first aid education for nosebleeds. There is no mention of institutional failures, health facility shortages, or any systemic forces preventing the CHW from helping. The CHW was able to effectively assist the patient with practical advice, indicating no systemic barriers were present. | Overburdened CHWs: The testimonial describes a CHW successfully providing first aid education to a patient with nosebleeds. There is no mention of exhaustion, being overwhelmed, having too many patients, or excessive workload. The CHW appears to have had adequate time to provide detailed instructions and follow up with the patient, who experienced positive outcomes. This clearly falls under the exclusion criteria of CHWs who were able to deliver care successfully. | Parsing failed for concept 'Overburdened CHWs' | Lack of Follow-Through: The testimonial describes a complete intervention where the CHW provided first aid instructions for nosebleeds and the patient successfully applied them, resulting in relief and reduced frequency of nosebleeds. There is no evidence of abandonment, interrupted care, or unresolved issues. The CHW followed through with effective guidance that resolved the patient's problem. | Lack of Knowledge: The CHW demonstrates complete knowledge and competence in handling the nosebleed situation. They knew exactly what to do and successfully taught the patient the proper first aid techniques. The testimonial shows the CHW providing detailed, accurate instructions rather than expressing uncertainty or need for additional training. This is the opposite of the concept definition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Obesity I am surprised even with this high cost of living and high oil prices in Kenya some of us still suffer from obesity. Nowadays this is a very rampant disease amongst the community members. I met this woman who cried to me asking me what she can do to cure her obesity. Ever since she realized she is obese, she has been trying every means to kill the fat, but to no avail. Everything, meaning she drank vinegar, traditional medicines, and all other things, but nothing seems to work. I told her the only thing she needed was exercise and a change of diet and she would be okay. She agreed to that and now we are yet to see some changes. And never forget to also have faith in that which she is doing. ---</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.1,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.0,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.65,
+  "Nutrition Education and Food Access": 0.65,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.85,
+  "Mental Health Awareness and Support": 0.25,
+  "Referrals and Advocacy": 0.1,
+  "Community Empowerment Through Education": 0.25,
+  "Resource and Material Distribution": 0.0,
+  "Monitoring and Follow-Up": 0.3,
+  "Trust and Cultural Mediation": 0.25,
+  "Clinical Interventions by CHWs": 0.05,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.2,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.85,
+  "Men Served": 0.0,
+  "Families Served": 0.1,
+  "Marginalized Groups Served": 0.2,
+  "Financial Hardship": 0.2,
+  "Social Isolation": 0.05,
+  "Disease Burden": 0.85,
+  "Stigma or Discrimination": 0.1,
+  "Mental or Emotional Distress": 0.6,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.2,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.2,
+  "Lack of Knowledge": 0.05
+}</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial shows a CHW giving advice on obesity, but there is no mention of the CHW having received any formal or informal training that increased their capacity. Since training is not referenced, alignment with the concept is minimal. | Menstrual Hygiene Education and Challenges: The testimonial focuses solely on obesity, diet, and exercise with no mention of menstruation, menstrual products, stigma, or education. Therefore, the concept is not present. | Drug Abuse: Environment and Awareness: The testimonial discusses obesity management and mentions consuming vinegar and traditional medicines, but there is no reference to addiction, alcohol/drug abuse, peer influence, or lack of drug education. Therefore, the concept of drug abuse related to environment and awareness is not present. | CHW-Led Infectious Disease Management: The testimonial discusses a CHW advising a client about obesity, which is a non-infectious chronic condition. The concept specifically targets CHW activities related to infectious diseases such as TB or COVID-19. Therefore, the testimonial falls outside the concept’s scope. | Water Quality, Sanitation, and Hygiene: The testimonial discusses obesity, exercise, and diet without any mention of clean water, sanitation, or hygiene education. Therefore, the concept is not present. | Personal Disease Management and Adherence: The testimonial centers on advising an individual with obesity on lifestyle changes (exercise, diet) to manage her condition. This fits the concept’s scope of managing a chronic disease through guidance from a CHW. However, there is no clear evidence of ongoing adherence or monitoring of a treatment regimen, so the alignment is moderate rather than strong. | Nutrition Education and Food Access: The CHW counsels a woman with obesity to implement “exercise and a change of diet,” which constitutes guidance on healthy eating. This fits the inclusion criterion of learning about healthy meals. However, the testimonial offers limited detail about specific nutrition education or food‐access efforts, so alignment is moderate rather than strong. | Sexual and Reproductive Health Education: The testimonial focuses solely on obesity management (diet and exercise) without any reference to family planning, STI prevention, HIV awareness, condoms, or other reproductive health topics. Therefore, it does not align with the Sexual and Reproductive Health Education concept. | Gender-Based Violence (GBV) and Child Protection: The testimonial discusses obesity management and lifestyle advice with no mention of abuse, exploitation, violence, or child protection issues, which are required for this concept. | Health Literacy and Misconceptions: The woman tried drinking vinegar and traditional medicines to “cure” obesity, indicating misinformation or lack of knowledge about effective weight-management strategies. The CHW corrected this by recommending exercise and diet. This is a clear instance of misconceptions affecting health decisions, matching the concept definition, hence a strong (but not absolute) alignment. | Parsing failed for concept 'Health Literacy and Misconceptions' | Mental Health Awareness and Support: The testimonial briefly mentions the woman crying and feeling distressed about her obesity, which hints at an emotional component, but the CHW’s response focuses on physical solutions (exercise, diet) rather than explicitly addressing psychological well-being or offering mental health support. This provides only minimal evidence of mental health awareness, warranting a low score. | Parsing failed for concept 'Mental Health Awareness and Support' | Referrals and Advocacy: The CHW only offers general lifestyle advice (exercise, diet) and does not facilitate a referral, appointment, or navigation within the health system. This is minimal evidence of the intermediary or advocacy role defined for this concept. | Community Empowerment Through Education: The CHW offers health advice (education) to an individual, but there is no evidence of broader community change, peer education, or sustained behavior change yet. This is closer to a one-time counseling interaction, which the concept definition treats as weak alignment. | Resource and Material Distribution: The testimonial only describes giving advice on exercise and diet; it does not mention providing any physical supplies or materials. According to the concept definition and exclusion criteria, education or advice without material support does not count as resource distribution. | Monitoring and Follow-Up: Testimonial mostly describes giving advice about exercise and diet (initial guidance). The phrase “now we are yet to see some changes” hints at an expectation of future progress but does not clearly state that the CHW will return or actively check on the woman’s status. Therefore, only weak evidence of ongoing monitoring or follow-up is present. | Trust and Cultural Mediation: The woman approaches the CHW for guidance after unsuccessfully trying traditional remedies, suggesting some trust in the CHW’s advice. The CHW counters these cultural practices with guidance on exercise and diet, hinting at mild cultural mediation. However, there is no explicit discussion of overcoming linguistic barriers or deliberate efforts to build or negotiate trust, so alignment with the concept is weak. | Clinical Interventions by CHWs: The CHW only gives lifestyle advice (exercise and diet) without administering medicine, performing a procedure, or directly treating a physical ailment. This falls under health education, which is explicitly excluded from the concept, so alignment with clinical intervention is minimal. | Mother and Infant Care: The testimonial discusses advising an adult woman on managing obesity through diet and exercise. It does not mention pregnancy, childbirth, postpartum issues, or infant health, which are required for the Mother and Infant Care concept. | Successful Outcomes: The CHW gave advice on exercise and diet, but explicitly states they are \ | Material or Training Requests: The testimonial discusses advising a community member on obesity management but does not include any request from the CHW for additional materials, supplies, or training. | Children Served: The testimonial discusses advising an adult woman on obesity management; it contains no mention of minors or services directed toward children. Therefore, the concept 'Children Served' is not present. | Elderly Served: The testimonial describes helping a woman with obesity through exercise and diet advice, but it does not mention that she is an older adult or provide any context of serving seniors. Therefore, the concept 'Elderly Served' is not applicable. | Women Served: The CHW directly interacts with an adult female, providing diet and exercise advice to address obesity. This is clear assistance tailored to a woman’s health need, fitting the inclusion criteria for ‘Women Served’. | Men Served: The testimonial discusses helping a woman with obesity; no adult males or boys are mentioned in the context of receiving support or facing gender-specific challenges. | Families Served: The testimonial describes helping a single woman with obesity; no household or family unit is mentioned. Similar to the example where advice was given to one individual (scored 0.1), there is minimal to no evidence of family-focused support. | Marginalized Groups Served: The testimonial describes helping a woman with obesity, but it does not explicitly frame the woman as part of a structurally excluded or stigmatized group, nor highlight social exclusion the CHW is addressing. Any marginalization due to obesity is only implied, so alignment with the concept is weak. | Financial Hardship: The narrative mentions the general “high cost of living and high oil prices in Kenya,” which hints at an economic context, but there is no explicit statement that the woman or others cannot afford food, transport, or medical care. Thus, only minimal, indirect evidence of financial hardship is present. | Social Isolation: The testimonial focuses on a woman seeking help for obesity and does not describe her living alone, lacking support systems, or feeling socially neglected. There is no explicit mention of loneliness or abandonment, so evidence for Social Isolation is negligible. | Disease Burden: The testimonial centers on obesity, described as an ongoing condition that the woman has struggled with for some time and tried many remedies for. This fits the definition of a chronic illness and meets the inclusion criterion of long-term or recurrent illness, so strong alignment (but not perfect certainty) merits a high score. | Stigma or Discrimination: The testimonial focuses on the woman’s struggle with obesity and her attempts to lose weight. There is no explicit mention that she is being judged, excluded, or shunned by others; hence social stigma is not clearly described. At most, her distress could imply some internal discomfort, but without evidence of external judgment the alignment is very weak. | Mental or Emotional Distress: The woman is described as having cried and desperately tried multiple remedies without success, indicating emotional strain and frustration about her obesity. This fits the inclusion of expressions of mental or emotional overwhelm, though depth of distress (e.g., diagnosed depression or hopelessness) is not fully detailed, so a moderate score is appropriate. | Lack of Resources: The testimonial describes advising a woman with obesity on exercise and diet; there is no mention of lacking medicine, supplies, or other resources. Therefore the concept does not apply. | Systemic Barriers: The CHW briefly references the ‘high cost of living and high oil prices,’ which are systemic economic conditions, but they are not directly framed as obstacles that prevented the CHW from assisting the client. The main issue discussed is individual behavior change (exercise and diet). Thus, only minimal evidence of a systemic barrier is present. | Overburdened CHWs: The testimonial describes interacting with a single client about obesity and provides advice, but it contains no mention of heavy workload, exhaustion, or feeling overwhelmed. Therefore the concept of overburdened CHWs is not present. | Lack of Follow-Through: The CHW provided advice but there is no indication of abandonment or that care was interrupted; the outcome is simply not yet visible. The issue is currently unresolved, which gives minimal, indirect evidence of potential lack of follow-through, but it does not clearly meet the concept’s criteria. | Lack of Knowledge: The CHW confidently advises the client to exercise and change diet; there is no mention of being unsure, lacking information, or requesting training. This largely excludes the concept, resulting in a near-zero score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Obesity I am surprised even with this high cost of living and high oil prices in Kenya some of us still suffer from obesity. Nowadays this is a very rampant disease amongst the community members. I met this woman who cried to me asking me what she can do to cure her obesity. Ever since she realized she is obese, she has been trying every means to kill the fat, but to no avail. Everything, meaning she drank vinegar, traditional medicines, and all other things, but nothing seems to work. I told her the only thing she needed was exercise and a change of diet and she would be okay. She agreed to that and now we are yet to see some changes. And never forget to also have faith in that which she is doing. ---</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.1,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.0,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.8,
+  "Nutrition Education and Food Access": 0.7,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.8,
+  "Mental Health Awareness and Support": 0.3,
+  "Referrals and Advocacy": 0.0,
+  "Community Empowerment Through Education": 0.3,
+  "Resource and Material Distribution": 0.0,
+  "Monitoring and Follow-Up": 0.3,
+  "Trust and Cultural Mediation": 0.3,
+  "Clinical Interventions by CHWs": 0.1,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.3,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.8,
+  "Men Served": 0.0,
+  "Families Served": 0.0,
+  "Marginalized Groups Served": 0.2,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.8,
+  "Stigma or Discrimination": 0.2,
+  "Mental or Emotional Distress": 0.6,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.2,
+  "Lack of Knowledge": 0.1
+}</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial shows a CHW providing health advice about obesity management (exercise and diet), but contains no mention of formal training, workshops, or knowledge gained through CHW programs. The advice given appears to be based on general knowledge rather than specific training received. This represents minimal alignment with the concept. | Menstrual Hygiene Education and Challenges: The testimonial focuses entirely on obesity, diet, and exercise counseling. There is no mention of menstruation, menstrual hygiene, products, or related education. The content explicitly excludes this concept as it deals with a completely different health topic. | Drug Abuse: Environment and Awareness: The testimonial focuses entirely on obesity, diet, and exercise - there is no mention of drug abuse, substance abuse, addiction, alcohol, or any related social/environmental factors. The concept clearly does not apply to this content. | CHW-Led Infectious Disease Management: The testimonial focuses entirely on obesity, which is a non-communicable disease/condition, not an infectious disease. While the CHW provides health education and guidance, the concept specifically requires involvement with infectious diseases like TB or COVID-19. The exclusion criteria states 'mentions of diseases without CHW involvement' - but more importantly, obesity is not an infectious disease at all, making this a clear non-match for the concept. | Water Quality, Sanitation, and Hygiene: The testimonial focuses entirely on obesity management through diet and exercise. There is no mention of water quality, sanitation practices, handwashing, or hygiene education. The concept is clearly not present in this testimonial. | Personal Disease Management and Adherence: Strong alignment with the concept. The testimonial describes a CHW providing guidance to manage obesity (a chronic condition) through lifestyle adjustments (exercise and diet change). While not about medication adherence, it clearly shows disease management through CHW-recommended interventions. The individual is actively seeking help and following the CHW's advice for managing their condition. | Nutrition Education and Food Access: The testimonial shows moderate alignment with nutrition education. The CHW directly advises a community member about dietary changes as a solution to obesity, which constitutes nutrition education. However, the focus is primarily on weight management rather than broader nutrition education or food access issues. The advice about 'change of diet' aligns with the inclusion criteria of teaching about healthy eating, but the context is specifically about obesity treatment rather than general nutrition awareness or food security. | Sexual and Reproductive Health Education: The testimonial focuses entirely on obesity management through diet and exercise. There is no mention of family planning, STI prevention, HIV awareness, reproductive rights, or any sexual health topics. This clearly falls outside the concept's inclusion criteria. | Gender-Based Violence (GBV) and Child Protection: The testimonial discusses obesity management and lifestyle counseling with no mention of violence, abuse, exploitation, or child protection issues. While the woman expressed emotional distress (crying), this was specifically about her obesity condition, not related to GBV or abuse. This clearly falls under the exclusion criteria of 'general emotional distress without reference to violence or abuse.' | Health Literacy and Misconceptions: Strong alignment with the concept. The testimonial describes a woman who misunderstood how to treat obesity, trying ineffective remedies like drinking vinegar and traditional medicines instead of proper diet and exercise. This demonstrates a clear lack of health literacy about weight management, which the CHW corrected by providing accurate information about exercise and dietary changes. | Mental Health Awareness and Support: The testimonial shows weak alignment with mental health support. While the woman's crying and distress about her obesity suggests emotional suffering, the focus remains primarily on the physical condition and its treatment through diet and exercise. The CHW's response addresses the physical aspects rather than providing psychological support or recognizing the emotional trauma associated with her condition. | Parsing failed for concept 'Mental Health Awareness and Support' | Referrals and Advocacy: The testimonial describes a CHW providing direct health advice (exercise and diet change) to someone with obesity, but contains no mention of referrals, helping with appointments, or navigating the healthcare system. The CHW is acting as a direct advisor rather than an intermediary or advocate within the health system. | Community Empowerment Through Education: This testimonial shows weak alignment with community empowerment through education. While the CHW provided health education about exercise and diet to address obesity, this represents an individual consultation rather than community-wide change. The story focuses on one person's struggle, and the outcome is uncertain ('we are yet to see some changes'). There's no evidence of peer education, group action, or broader community transformation. The educational intervention is recent with no demonstrated lasting behavior change yet. | Resource and Material Distribution: The testimonial describes a CHW providing advice about exercise and diet change to help with obesity, but there is no mention of distributing any physical resources, materials, or supplies. This aligns with the exclusion criteria of 'discussions of education or advice without material support.' The CHW only offered guidance and recommendations, not tangible items like medication, food, or health kits. | Monitoring and Follow-Up: The testimonial shows weak alignment with monitoring and follow-up. While the CHW provided initial advice about exercise and diet, the phrase 'we are yet to see some changes' suggests potential future monitoring but no actual follow-up has occurred yet. This represents an initial consultation with implied but not demonstrated ongoing interaction, similar to the 0.4 example of giving advice without confirmed follow-up. | Trust and Cultural Mediation: The testimonial shows weak alignment with trust and cultural mediation. While the CHW provides health guidance to someone who 'cried to me' (suggesting some trust), the interaction is primarily clinical advice about diet and exercise. There's minimal evidence of navigating cultural barriers or building community trust beyond this individual consultation. The mention of 'traditional medicines' hints at cultural practices but the CHW doesn't actively mediate between these and modern healthcare approaches. | Clinical Interventions by CHWs: The CHW provided health advice about exercise and diet change for obesity, which is health education rather than a direct clinical intervention. No mention of administering medication, treating wounds, or performing any hands-on medical tasks. This aligns with the exclusion criteria of 'health education without direct clinical interaction.' | Mother and Infant Care: The testimonial focuses entirely on helping a woman with obesity through diet and exercise recommendations. There is no mention of pregnancy, childbirth, postpartum care, infant health, or any mother/infant-specific support. This is general women's health support, which is explicitly excluded from the Mother and Infant Care concept. | Successful Outcomes: The testimonial describes a CHW providing advice (exercise and diet change) to an obese woman, and the woman agreed to follow it. However, the outcome is still pending ('we are yet to see some changes'), indicating no confirmed improvement yet. This aligns with the example of attempted help with uncertain results, warranting a weak alignment score. | Material or Training Requests: The testimonial describes a CHW's encounter with an obese community member and the advice given (exercise and diet change). There is no mention of the CHW requesting any materials, supplies, or training. The CHW appears confident in their ability to provide guidance and does not express any need for additional resources or education to handle this situation. | Children Served: The testimonial focuses entirely on an adult woman suffering from obesity. There is no mention of children, adolescents, or minors under 18 years old. The CHW's interaction and support are directed solely at an adult community member, making this concept clearly not present in the testimonial. | Elderly Served: The testimonial describes a CHW helping a woman with obesity through diet and exercise advice. There is no mention of the woman being elderly, a senior, or a grandparent. The focus is entirely on obesity management without any age-related context that would indicate service to elderly populations. | Women Served: Strong alignment as the CHW directly assisted an adult woman with a specific health challenge (obesity). The testimonial describes providing health education and guidance on diet and exercise, which aligns with 'assistance or education for women, especially around health.' The interaction is personal and addresses a specific need, similar to the 0.9 example but slightly less formal/structured than the pregnancy education example. | Men Served: The testimonial specifically describes working with 'this woman' who is struggling with obesity. There is no mention of men or boys being served, nor any reference to male-specific health challenges or support. The concept clearly requires adult males or boys to be described in the context of support or health issues, which is not present in this testimonial. | Families Served: The testimonial describes a CHW's interaction with a single woman about her obesity concerns. There is no mention of her family members, household, children, or any family-focused intervention. The support provided is entirely individual-focused, which falls under the exclusion criteria of 'Individual help not connected to a family unit or structure.' | Marginalized Groups Served: The testimonial describes helping a woman with obesity, but there is no indication that she belongs to a marginalized or structurally excluded group. The focus is on a common health condition without reference to stigma, discrimination, or social exclusion that would indicate marginalization. While obesity can sometimes carry social stigma, the testimonial does not mention any such marginalization or barriers to care that the CHW helped address. | Parsing failed for concept 'Marginalized Groups Served' | Financial Hardship: The testimonial discusses obesity and various attempted remedies but contains no evidence of financial hardship. While it mentions 'high cost of living and high oil prices in Kenya,' this is presented as context that makes obesity surprising, not as a barrier to care or basic needs. The woman tried various treatments including vinegar and traditional medicines, suggesting she had means to purchase these items. There is no mention of inability to afford transportation, food, or medical care. | Social Isolation: The testimonial focuses entirely on a woman's struggle with obesity and weight loss attempts. There is no mention of living alone, loneliness, lack of support systems, or social neglect. The interaction between the CHW and the woman suggests she has access to support (the CHW) and is actively seeking help, which contradicts social isolation. | Disease Burden: Strong alignment with the concept. The testimonial describes obesity as a chronic condition causing significant distress to the patient, who has been struggling with it for an extended period and trying multiple interventions 'to no avail.' The CHW refers to it as a 'very rampant disease' and describes ongoing management through lifestyle changes, indicating a long-term health issue requiring sustained intervention. | Stigma or Discrimination: The testimonial describes a woman seeking help for obesity but does not explicitly mention social rejection, shame, or judgment from others. While the woman's crying suggests emotional distress about her condition, there is no clear evidence of stigma or discrimination from the community. The focus is on her personal struggle with weight loss attempts rather than social exclusion or judgment. | Mental or Emotional Distress: The testimonial shows moderate alignment with mental/emotional distress. The woman 'cried to me' and expressed desperation about her obesity, having tried 'every means' without success. This indicates emotional overwhelm and distress about her condition. However, the primary focus is on the physical health issue (obesity) rather than mental health itself, which prevents a higher score. | Lack of Resources: The CHW does not mention lacking any resources to help the woman with obesity. They were able to provide advice (exercise and diet change) and ongoing support. There is no indication of insufficient supplies, tools, or capacity to address the problem. | Systemic Barriers: The testimonial describes a CHW helping a woman with obesity through diet and exercise recommendations. There is no mention of systemic barriers like health facility shortages, institutional problems, or external conditions preventing the CHW from helping. The CHW was able to provide guidance directly, and the issue was personal (obesity management) rather than systemic. This clearly falls under the exclusion criteria as it involves personal health management rather than systemic forces. | Overburdened CHWs: The testimonial describes a CHW helping a single patient with obesity management through diet and exercise counseling. There is no mention of excessive workload, being overwhelmed, exhausted, or having too many patients. The CHW appears to be providing standard care without any indication of being overburdened. | Lack of Follow-Through: The testimonial shows the CHW provided advice (exercise and diet change) and the patient agreed to follow it. The phrase 'we are yet to see some changes' suggests ongoing care rather than abandonment. While the outcome is still pending, there's no indication the CHW failed to follow through or abandoned the patient. This represents minimal alignment with the concept. | Lack of Knowledge: The CHW demonstrates clear knowledge about obesity management, confidently advising exercise and dietary changes. There's no indication they were unsure how to proceed or needed additional training. The testimonial shows the CHW providing appropriate guidance rather than expressing uncertainty or knowledge gaps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Malaria Malaria has been very challenging in our community there was active I was called at night that one of my clients was sick upon getting her place I noticed that she had the symptoms like that of malaria as she was shivering and had cold, and the body temperature was high too and she was also complaining of headache. And she sweating too. I took her to the nearest hospital for medication where malaria test was done and the results were positive. She was given antimalarial drugs to reduce the pain and I made sure she completed her dose as was instructed by the doctor. ---</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.05,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.85,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.95,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.05,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.9,
+  "Community Empowerment Through Education": 0.05,
+  "Resource and Material Distribution": 0.1,
+  "Monitoring and Follow-Up": 0.9,
+  "Trust and Cultural Mediation": 0.1,
+  "Clinical Interventions by CHWs": 0.3,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.7,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.8,
+  "Men Served": 0.0,
+  "Families Served": 0.0,
+  "Marginalized Groups Served": 0.1,
+  "Financial Hardship": 0.05,
+  "Social Isolation": 0.05,
+  "Disease Burden": 0.4,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.05,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.05,
+  "Overburdened CHWs": 0.1,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.05
+}</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial describes a CHW helping a malaria patient, but it does not mention receiving any training, workshops, or knowledge-building activities. Therefore, alignment with the concept is minimal. | Menstrual Hygiene Education and Challenges: The testimonial solely discusses diagnosing and treating a client with malaria; it contains no reference to menstruation, menstrual products, stigma, or education. Therefore, the concept does not apply. | Drug Abuse: Environment and Awareness: The testimonial discusses treatment for malaria using prescribed medication, without any mention of substance abuse, addiction, or social/environmental factors related to drug misuse. Therefore, the concept is not present. | CHW-Led Infectious Disease Management: The testimonial describes the CHW recognizing malaria symptoms, taking the client for testing, and ensuring completion of antimalarial medication—direct involvement in managing an infectious disease and performing follow-up. This strongly aligns with the concept (CHWs explaining symptoms and follow-ups), though it lacks broader community education elements, so a score slightly below perfect is appropriate. | Water Quality, Sanitation, and Hygiene: The testimonial focuses on diagnosing and treating a malaria case and ensuring medication adherence. It contains no mention of water quality, sanitation practices, or hygiene education, so the concept is not present. | Personal Disease Management and Adherence: The testimonial explicitly describes diagnosing malaria, obtaining medication, and ensuring the client completed the antimalarial dose—core elements of disease management and adherence guided by the CHW. This is a clear, direct match with the concept. | Nutrition Education and Food Access: The testimonial discusses diagnosing and treating malaria; it does not mention food, diet, nutrition education, or access to food. Therefore, the concept is clearly not present. | Sexual and Reproductive Health Education: The testimonial discusses malaria diagnosis and treatment with no mention of family planning, STI prevention, HIV awareness, or any other sexual or reproductive health education topics. | Gender-Based Violence (GBV) and Child Protection: The testimonial describes diagnosing and treating a client for malaria with no mention of abuse, exploitation, violence, or child protection issues. | Health Literacy and Misconceptions: The testimonial simply describes recognizing malaria symptoms, obtaining a diagnosis, and ensuring treatment adherence. It does not mention any misinformation, misunderstandings, or myths influencing health decisions, so relevance to the concept is minimal. | Mental Health Awareness and Support: The testimonial focuses exclusively on physical symptoms of malaria and medical treatment, with no reference to psychological well-being, emotional states, or mental health support. | Referrals and Advocacy: The CHW recognized malaria symptoms, transported the client to the nearest hospital for testing and treatment, and ensured completion of medication—actions that clearly demonstrate navigation and advocacy within the health system. This closely matches the concept’s definition and inclusion criteria. | Community Empowerment Through Education: The testimonial focuses on escorting an individual patient to the hospital and ensuring medication adherence. It does not describe health education, peer learning, or any broader community behavior change, so alignment with the concept is minimal. | Resource and Material Distribution: The CHW escorted the client to a hospital where medication was provided by medical staff and ensured adherence, but there is no clear statement that the CHW personally distributed or supplied the medication. This is mostly a referral/adherence support scenario, which falls outside the inclusion criteria for material distribution. | Monitoring and Follow-Up: The CHW not only accompanied the client for testing and treatment but also \ | Trust and Cultural Mediation: The testimonial describes a clinical support action—transporting a patient to the hospital and ensuring medication adherence—but does not mention building trust, translating, or addressing cultural/linguistic barriers. Any implied trust (client calling at night) is indirect and minimal, so alignment with the concept is weak. | Clinical Interventions by CHWs: The CHW recognized symptoms and transported the client to the hospital, then monitored medication adherence, but did not personally administer medicine or perform any hands-on treatment. This is primarily referral and follow-up rather than direct clinical intervention, so alignment with the concept is weak. | Mother and Infant Care: The testimonial describes assisting a client with malaria diagnosis and treatment; it contains no mention of pregnancy, childbirth, postpartum issues, or infant health, so it does not align with the Mother and Infant Care concept. | Successful Outcomes: The CHW successfully transported the client to the hospital, obtained a confirmed malaria diagnosis, ensured the client received antimalarial medication, and followed up to make sure the full dose was completed. This indicates a completed referral and concrete actions likely leading to improvement, aligning moderately-strongly with “Successful Outcomes.” However, the narrative does not explicitly state the client’s recovery, so the alignment is not perfect. | Material or Training Requests: The testimonial describes handling a malaria case but contains no explicit request for materials, supplies, or additional training. Therefore, the concept is not present. | Children Served: The testimonial describes assisting a client with malaria but does not mention children or adolescents. Therefore, the concept 'Children Served' is not present. | Elderly Served: The testimonial describes helping a malaria patient but gives no indication that the client is an older adult. Therefore the concept of serving the elderly is not present. | Women Served: The CHW describes assisting a female client ('she') by taking her to the hospital and ensuring completion of malaria treatment. This is direct assistance to an adult woman regarding health, fitting the inclusion criteria. While the health issue is not uniquely gender-specific, the testimonial clearly centers on a woman being served, warranting a strong (though not perfect) alignment. | Men Served: The testimonial discusses helping a female client with malaria; there is no mention of supporting men or boys or addressing male-specific challenges. | Families Served: The testimonial describes assisting a single client with malaria; no households, parents, children, or family units are mentioned. Individual-focused care is explicitly excluded from the concept, so the concept does not apply. | Marginalized Groups Served: The testimonial describes helping a client with malaria but does not indicate that the person belongs to a socially or structurally excluded group. Without any reference to marginalization, the alignment with the concept is minimal. | Financial Hardship: The testimonial describes identifying malaria symptoms and ensuring treatment compliance but does not mention any inability to pay, lack of transportation funds, or other material scarcity. Thus, only extremely weak implicit evidence (if any) of financial hardship is present. | Social Isolation: The testimonial describes a malaria episode and the CHW taking the client to the hospital. It does not mention the client living alone, lacking support, or feeling lonely. Therefore, evidence for social isolation is essentially absent. | Disease Burden: The testimonial describes assisting a client with an acute malaria episode. While malaria is a significant illness, the narrative focuses on a single short-term event rather than chronic or recurrent disease. This parallels the cold example (0.4); thus the alignment is weak but present. | Stigma or Discrimination: The testimonial only describes identifying malaria symptoms, taking the client to the hospital, and ensuring medication adherence. It contains no mention of social rejection, judgment, shame, or exclusion related to the illness, so the stigma/discrimination concept does not apply. | Mental or Emotional Distress: The testimonial focuses exclusively on physical symptoms of malaria (shivering, fever, headache) and medical treatment. There is no mention of feelings of depression, hopelessness, or emotional overwhelm. Only physical complaints are described, which are excluded from the concept. Minimal to no alignment with mental or emotional distress. | Lack of Resources: The testimonial describes identifying malaria symptoms, facilitating a hospital visit, and ensuring medication adherence. There is no mention of insufficient supplies, medicine, tools, or support; thus, the concept of a lack of resources is not present. | Systemic Barriers: The testimonial describes taking the client to the nearest hospital, receiving a test, and obtaining medication without mentioning shortages, distance challenges, overcrowding, or other institutional obstacles. No systemic issue impeded the CHW’s work, so alignment with the concept is minimal. | Overburdened CHWs: The testimonial mentions being called at night and that malaria is challenging, but it does not describe the CHW as exhausted, overwhelmed, or unable to cope with workload. This provides only minimal, indirect evidence of overburden, so a low score is appropriate. | Lack of Follow-Through: The CHW accompanied the client to the hospital, ensured testing, obtained medication, and verified completion of the treatment course. The story reflects successful follow-through, not abandonment or an unresolved issue. | Lack of Knowledge: The CHW confidently recognized malaria symptoms, transported the patient to a hospital, and ensured medication adherence. There is no mention of uncertainty, need for training, or lack of knowledge, so alignment with the concept is negligible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Malaria Malaria has been very challenging in our community there was active I was called at night that one of my clients was sick upon getting her place I noticed that she had the symptoms like that of malaria as she was shivering and had cold, and the body temperature was high too and she was also complaining of headache. And she sweating too. I took her to the nearest hospital for medication where malaria test was done and the results were positive. She was given antimalarial drugs to reduce the pain and I made sure she completed her dose as was instructed by the doctor. ---</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.0,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.8,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.9,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.0,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.8,
+  "Community Empowerment Through Education": 0.0,
+  "Resource and Material Distribution": 0.0,
+  "Monitoring and Follow-Up": 0.8,
+  "Trust and Cultural Mediation": 0.1,
+  "Clinical Interventions by CHWs": 0.1,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.9,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.8,
+  "Men Served": 0.0,
+  "Families Served": 0.1,
+  "Marginalized Groups Served": 0.1,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.4,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.0,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.1,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial describes a CHW responding to a malaria case and facilitating hospital care, but contains no mention of training, workshops, or knowledge gained through formal or informal CHW education. The CHW demonstrates existing knowledge in recognizing symptoms and ensuring medication compliance, but there is no evidence of empowerment through training. | Menstrual Hygiene Education and Challenges: The testimonial exclusively discusses a malaria case - symptoms, diagnosis, and treatment. There is no mention of menstruation, menstrual hygiene, products, or related education. This clearly falls under the exclusion criteria as it's about a completely different health issue. | Drug Abuse: Environment and Awareness: The testimonial focuses entirely on a malaria case and its clinical management. There is no mention of substance abuse, addiction, alcohol, peer influence, or drug education. The only 'drugs' mentioned are antimalarial medications used for treatment. This clearly falls under the exclusion criteria as it's a clinical description without any social/environmental context related to substance abuse. | CHW-Led Infectious Disease Management: Strong alignment with the concept. The CHW demonstrates direct involvement in managing an infectious disease (malaria) by recognizing symptoms, providing immediate care, facilitating hospital treatment, and ensuring medication compliance. While there's no explicit mention of community education or prevention activities, the CHW's active role in disease management and follow-up care aligns well with the concept definition. | Water Quality, Sanitation, and Hygiene: The testimonial focuses entirely on malaria diagnosis and treatment, with no mention of water quality, sanitation, or hygiene practices. The CHW describes symptoms, hospital referral, and medication adherence, but does not discuss any preventive measures related to water, handwashing, or sanitation that could help prevent disease transmission. | Personal Disease Management and Adherence: Strong direct alignment with the concept. The testimonial describes a clear case of malaria diagnosis and treatment management. The CHW identified symptoms, facilitated medical care resulting in positive diagnosis, and crucially ensured medication adherence ('I made sure she completed her dose as was instructed by the doctor'). This directly matches the inclusion criteria of 'sticking to medication' and 'managing malaria' through CHW guidance. | Nutrition Education and Food Access: The testimonial focuses entirely on malaria diagnosis and treatment. There is no mention of nutrition education, food access, healthy eating, or any food-related topics. The content explicitly deals with a medical emergency and antimalarial treatment, which falls outside the scope of this concept. | Sexual and Reproductive Health Education: The testimonial focuses entirely on malaria diagnosis and treatment. There is no mention of family planning, STI prevention, HIV awareness, reproductive rights, or any sexual health education topics. The content is exclusively about malaria symptoms, testing, and treatment, which clearly falls outside the scope of this concept. | Gender-Based Violence (GBV) and Child Protection: The testimonial describes a CHW responding to a malaria case - helping a client with fever, shivering, and other malaria symptoms, then facilitating hospital care and medication compliance. There is no mention of abuse, violence, exploitation, or any form of GBV or child protection issues. This is purely a medical emergency response to an infectious disease. | Health Literacy and Misconceptions: The testimonial describes a straightforward case of malaria diagnosis and treatment with no evidence of misinformation, misconceptions, or misunderstandings. The CHW correctly identified symptoms, sought proper medical care, and ensured medication compliance. This represents accurate health management without any health literacy issues. | Mental Health Awareness and Support: The testimonial focuses entirely on physical symptoms and treatment of malaria (shivering, fever, headache) with no mention of psychological well-being, emotional support, or mental health aspects. This is a purely medical intervention without any mental/emotional context, which falls under the exclusion criteria. | Referrals and Advocacy: Strong direct alignment. The CHW explicitly states 'I took her to the nearest hospital for medication' which demonstrates active referral and navigation of healthcare services. The CHW also ensured follow-up care by making sure the patient completed the prescribed medication, showing advocacy for proper treatment completion. This aligns well with the concept's definition of CHWs acting as intermediaries within the health system. | Community Empowerment Through Education: This testimonial describes a one-time emergency medical intervention where the CHW helped a sick client get malaria treatment. There is no mention of health education, community change, peer education, or lasting behavior change. The CHW acted as a medical facilitator rather than an educator, which aligns with the exclusion criteria of 'one-time events' without educational impact. | Resource and Material Distribution: The testimonial describes a CHW responding to a malaria case and facilitating hospital care, but there is no mention of the CHW directly distributing any materials or resources. The antimalarial drugs were provided by the hospital/doctor, not distributed by the CHW. This aligns with the exclusion criteria as it involves healthcare facilitation without material support from the CHW. | Monitoring and Follow-Up: Strong alignment with the concept. The CHW explicitly states 'I made sure she completed her dose as was instructed by the doctor,' which indicates ongoing monitoring after the initial hospital visit to ensure treatment adherence. This goes beyond a one-time intervention and shows follow-up care, though the testimonial doesn't provide details about multiple visits or extended monitoring periods. | Trust and Cultural Mediation: The testimonial describes a clinical response to a malaria case with minimal evidence of trust-building or cultural mediation. While being called at night suggests some community trust in the CHW, the narrative focuses entirely on clinical symptoms, diagnosis, and treatment without mentioning any cultural barriers, translation needs, or trust-building activities. This aligns with the exclusion criteria of 'clinical interactions without cultural or trust-related themes.' | Clinical Interventions by CHWs: The CHW identified symptoms and transported the client to a hospital where medical professionals conducted tests and prescribed medication. While the CHW ensured medication compliance, they did not directly administer treatment or perform clinical tasks themselves. This aligns with the exclusion criteria as it represents a referral without direct clinical intervention, similar to the 0.1-scored example about speaking about wound care. | Mother and Infant Care: The testimonial describes a CHW responding to a malaria case in an adult client. There is no mention of pregnancy, childbirth, postpartum care, infant health, or any mother/infant-specific support. The case involves general malaria treatment for what appears to be an adult patient, which falls outside the concept's inclusion criteria. | Successful Outcomes: Strong direct alignment with the concept. The CHW identified malaria symptoms, took the client to the hospital, confirmed diagnosis through testing, ensured medication was provided, and followed up to ensure treatment completion. This shows a clear progression from problem identification to resolution, matching the example of escorting someone to the hospital who recovered (0.9). | Material or Training Requests: The testimonial describes a CHW's experience handling a malaria case, including recognizing symptoms and ensuring proper medical care. However, there is no explicit request for materials, supplies, or training. The CHW simply narrates what happened without asking for any resources or additional education to better handle such cases. | Children Served: The testimonial describes caring for a client with malaria symptoms, but there is no indication that this client is a child or minor under 18. The CHW refers to the person as 'one of my clients' and 'she/her' without any age-related descriptors that would suggest the patient is a child. | Elderly Served: The testimonial describes a CHW helping a client with malaria symptoms, but there is no mention of the client being elderly, a senior, or a grandparent. The narrative focuses on malaria treatment without any age-related descriptors that would indicate service to elderly populations. | Women Served: Strong alignment as the CHW directly assisted an adult female client with malaria symptoms, took her to the hospital, and ensured medication compliance. The use of 'she/her' pronouns throughout confirms the client was female, and the CHW provided direct health assistance, matching the inclusion criteria of 'assistance for women, especially around health.' | Men Served: The testimonial describes a female client ('her place', 'she had symptoms', 'she was shivering') receiving malaria treatment. There is no mention of men or boys, nor any gendered roles or challenges related to males. The concept explicitly requires adult males or boys in the context of support or health issues, which is absent here. | Families Served: The testimonial describes helping a single client with malaria symptoms. While the CHW refers to 'one of my clients,' there is no mention of family members, household context, or family-focused intervention. This aligns with the exclusion criteria of 'individual help not connected to a family unit or structure,' similar to the example 'I gave advice to one man who said he lived nearby' which scores 0.1. | Marginalized Groups Served: The testimonial describes providing emergency care to a community member with malaria, but contains no indication that the person belonged to a marginalized or underserved group. The CHW provided standard health support without any reference to structural exclusion, stigma, or special vulnerabilities that would indicate marginalization. | Financial Hardship: The testimonial describes a malaria case and medical response but contains no mention of financial difficulties, inability to afford care, transportation costs, or material scarcity. The patient was taken to the hospital and received treatment without any indication of financial barriers or hardship. | Social Isolation: The testimonial focuses entirely on a malaria case and medical intervention. There is no mention of the client living alone, lacking support systems, experiencing loneliness, or being socially isolated. The CHW was called to help, suggesting the client had means to reach out for assistance. The concept of social isolation is not present in this testimonial. | Disease Burden: This testimonial describes a single acute malaria episode that was successfully treated. While malaria can be serious, this account focuses on one illness event that was resolved with treatment, similar to the 'cold' example (0.4). There's no indication of chronic illness, disability, or recurrent episodes that would constitute a higher disease burden. | Stigma or Discrimination: The testimonial describes a straightforward medical emergency response to malaria symptoms. There is no mention of social rejection, shame, exclusion, or judgment from others. The patient received prompt medical care without any indication of stigma or discrimination related to their health condition. | Mental or Emotional Distress: The testimonial describes a case of malaria with purely physical symptoms (shivering, fever, headache, sweating). There is no mention of depression, hopelessness, trauma, stress, or any emotional distress. This aligns with the exclusion criteria of 'physical complaints or stress unrelated to emotional wellbeing.' | Lack of Resources: The CHW successfully identified symptoms, transported the patient to a hospital, and ensured medication compliance. There is no mention of lacking medicine, tools, or support. The CHW had access to a nearby hospital and the patient received appropriate treatment, indicating resources were available and utilized effectively. | Systemic Barriers: The testimonial describes a successful case where the CHW was able to take the patient to the nearest hospital and get proper treatment. There is no mention of any systemic barriers preventing care - the hospital was accessible, testing was available, medication was provided, and treatment was completed. This represents the healthcare system working as intended, not being hindered by systemic issues. | Overburdened CHWs: The testimonial describes a CHW responding to a nighttime emergency call and successfully managing a malaria case. While being called at night suggests dedication and potentially demanding work, there is no evidence of being overwhelmed, exhausted, or having excessive workload. The CHW effectively handled the situation, similar to the example 'I've seen multiple people in my community, and I haven't run into any difficulties' (0.1). | Lack of Follow-Through: The CHW completed the entire care process: responded to the call, assessed symptoms, took the patient to the hospital, ensured testing and treatment, and followed up to confirm medication completion. This represents full follow-through with no abandonment or unresolved issues. | Lack of Knowledge: The CHW demonstrated competent knowledge throughout the situation. They correctly identified malaria symptoms (shivering, cold, high temperature, headache, sweating), made an appropriate decision to take the patient to the hospital, and ensured proper follow-up care by monitoring medication compliance. There is no mention of uncertainty, need for training, or asking others for help with treatment decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Malaria I know about two children who died from malaria (???????). Their parents kept them in the house, buying them drugs over-the-counter which did not go well with them at the time. They were taken to hospital. It was too late for they did not make it. As a CHW in my dealing with malaria, I do clear bushes in my surroundings and also to clear mosquito breeding sites, sleeping under treated mosquito net. Also, I do go for check-ups whenever I experience malaria symptom. As I do all this, I also advise people to do the same. ---</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.0,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.88,
+  "Water Quality, Sanitation, and Hygiene": 0.6,
+  "Personal Disease Management and Adherence": 0.65,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.6,
+  "Mental Health Awareness and Support": 0.05,
+  "Referrals and Advocacy": 0.5,
+  "Community Empowerment Through Education": 0.4,
+  "Resource and Material Distribution": 0.1,
+  "Monitoring and Follow-Up": 0.1,
+  "Trust and Cultural Mediation": 0.2,
+  "Clinical Interventions by CHWs": 0.1,
+  "Mother and Infant Care": 0.2,
+  "Successful Outcomes": 0.1,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.1,
+  "Elderly Served": 0.0,
+  "Women Served": 0.0,
+  "Men Served": 0.0,
+  "Families Served": 0.35,
+  "Marginalized Groups Served": 0.1,
+  "Financial Hardship": 0.2,
+  "Social Isolation": 0.05,
+  "Disease Burden": 0.6,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.1,
+  "Lack of Resources": 0.05,
+  "Systemic Barriers": 0.2,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.05,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial describes malaria prevention activities performed by the CHW but provides no mention of receiving training, workshops, or knowledge‐building events. Therefore, there is no evidence of empowerment through training. | Menstrual Hygiene Education and Challenges: The testimonial discusses malaria prevention and treatment with no mention of menstruation, menstrual products, stigma, or education. Therefore the concept does not apply. | Drug Abuse: Environment and Awareness: The testimonial discusses malaria prevention and treatment, not substance abuse or social/environmental factors related to drug or alcohol misuse. Therefore, the concept is not present. | CHW-Led Infectious Disease Management: The CHW describes malaria prevention actions (clearing breeding sites, using nets, seeking check-ups) and explicitly states advising others to follow these practices. This is direct outreach/education by a CHW on an infectious disease, fitting the concept’s inclusion criteria; hence a strong alignment. | Water Quality, Sanitation, and Hygiene: The CHW describes environmental sanitation actions—clearing bushes and eliminating mosquito-breeding sites—to prevent malaria, which fits the concept’s inclusion of ‘sanitation practices.’ However, there is no direct mention of water treatment or hand-washing education, so the alignment is moderate rather than strong. | Personal Disease Management and Adherence: The testimonial discusses managing malaria through preventive lifestyle adjustments (clearing breeding sites, sleeping under treated nets) and seeking diagnosis when symptoms appear, aligning with disease management elements of the concept. However, it does not strongly emphasize ongoing treatment adherence or specific medication schedules, so alignment is moderate rather than strong. | Nutrition Education and Food Access: The testimonial focuses entirely on malaria prevention and treatment (clearing bushes, using mosquito nets, seeking medical care). It does not mention food, healthy eating, or access to nutrition. Therefore, the concept of Nutrition Education and Food Access is not present. | Sexual and Reproductive Health Education: The testimonial focuses on malaria prevention and treatment, with no mention of family planning, STIs, HIV, condoms, or any other sexual and reproductive health education topics. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses on malaria prevention and treatment, with no mention of abuse, exploitation, violence, or child protection interventions. Therefore, the concept is not applicable. | Health Literacy and Misconceptions: The testimonial describes parents who kept their children at home and used over-the-counter drugs instead of seeking prompt medical care for malaria, which suggests a gap in health knowledge or misunderstanding of appropriate treatment. This reflects the concept’s focus on how lack of knowledge affects health outcomes. However, the testimonial does not explicitly detail widespread misinformation or specific false beliefs, so the alignment is moderate rather than strong. | Parsing failed for concept 'Health Literacy and Misconceptions' | Mental Health Awareness and Support: The testimonial focuses on malaria prevention and treatment behaviors, with no explicit discussion of psychological well-being, depression, anxiety, or emotional support. Any implied grief over the children’s deaths is not discussed, so mental health content is essentially absent. | Referrals and Advocacy: The CHW describes advising community members to seek check-ups and adopt preventive behaviours, which is a form of advocacy but does not include explicit referrals or navigation of the health system. This aligns moderately with the concept (similar to example “I asked someone to consider going to the clinic” scored 0.5). | Community Empowerment Through Education: The CHW explains that she advises others to clear mosquito breeding sites, use nets, and seek check-ups, indicating some educational effort aimed at the community. However, there is no evidence of long-term community behavior change, peer-led action, or demonstrated self-reliance resulting from this advice. This aligns with the weak-to-moderate example (“I had taught a session... but I’m not sure it changed much” → 0.4), so a score of 0.4 is appropriate. | Resource and Material Distribution: The testimonial describes environmental cleanup, personal preventive practices, and advising others, but it does not mention the CHW giving out nets, medicine, or any other tangible supplies. According to the concept’s exclusion criteria, education or advice without material support does not count, so alignment is minimal. | Monitoring and Follow-Up: The testimonial focuses on preventive actions and advising community members but does not mention returning to check on individuals’ health status or ongoing interactions. This fits the exclusion of one-time education efforts without follow-up, so only minimal evidence of monitoring and follow-up is present. | Trust and Cultural Mediation: The CHW recounts clearing mosquito breeding sites, using nets, and advising neighbors to do the same—general health education. There is no explicit mention of building trust, translating, or overcoming cultural or linguistic barriers. This offers only minimal, indirect evidence of trust-building, so alignment with the concept is weak. | Clinical Interventions by CHWs: The CHW describes preventive actions (clearing mosquito breeding sites, using bed nets) and advising others, but no direct clinical tasks such as giving medicine or treating wounds are mentioned. This falls under health education/prevention rather than clinical intervention, so only a minimal alignment score is assigned. | Mother and Infant Care: The testimonial briefly references two children who died from malaria, showing some concern for child health, but it does not specifically address prenatal care, childbirth, postpartum issues, infant feeding, or other infant-focused services. The primary focus is general malaria prevention for the community. Thus, only minimal, indirect alignment with the mother/infant care concept. | Successful Outcomes: The CHW describes preventive actions they take and advice they give, but provides no evidence of these efforts leading to improved health or resolved problems. The only clear outcome mentioned is the death of two children, which is negative. This falls under the exclusion criterion of describing help with no demonstrated progress, so alignment with the ‘Successful Outcomes’ concept is very weak. | Material or Training Requests: The testimonial describes malaria prevention activities and advice but contains no explicit request for materials, supplies, or training, which the concept definition requires. | Children Served: The testimonial only references two children who died from malaria without describing any direct support or services provided to them by the CHW. This fits the exclusion criterion of merely mentioning youth without CHW involvement, so alignment with the concept is minimal. | Elderly Served: The testimonial discusses malaria prevention and treatment involving children and general community advice, with no reference to older adults or services provided to them. | Women Served: The testimonial discusses malaria prevention efforts and cases involving children, without any mention of women or gender-specific issues. Therefore, the concept of serving women is not present. | Parsing failed for concept 'Women Served' | Men Served: The testimonial discusses malaria prevention and treatment efforts without any specific reference to adult males or boys. Therefore, the concept of 'Men Served' is not applicable. | Families Served: The testimonial references ‘two children’ and ‘their parents,’ indicating a family unit, but the CHW does not describe direct support or intervention with that family—only a general mention of advising the community. This weakly aligns with the concept (similar to the 0.4 example), so a low‐moderate score is appropriate. | Marginalized Groups Served: The testimonial discusses malaria prevention for children and the general community but does not indicate that the beneficiaries are members of a structurally excluded or stigmatized group. Because there is no explicit reference to marginalized status, only a minimal score is warranted. | Financial Hardship: The parents treated the children at home with over-the-counter drugs before seeking hospital care, which could hint at cost concerns, but financial hardship is not explicitly stated. Minimal, indirect evidence only. | Social Isolation: The testimonial focuses on malaria prevention and delayed medical care. While it notes parents kept sick children at home, it does not describe loneliness, abandonment, or lack of social support. Therefore, evidence for social isolation is essentially absent, warranting a very low score. | Disease Burden: The testimonial centers on malaria—describing deaths of two children and the CHW’s ongoing efforts to prevent and monitor the disease. Malaria in endemic areas can involve repeated episodes and represents a significant health burden, fitting the inclusion of recurrent illness. However, it is not explicitly framed as a chronic condition or individual long-term disability, so the alignment is moderate rather than strong. | Stigma or Discrimination: The testimonial discusses malaria prevention, treatment practices, and a tragic outcome, but it contains no mention of social rejection, shame, judgment, or discrimination related to the illness. Therefore, the concept is not present. | Mental or Emotional Distress: The testimonial mentions the death of two children from malaria, which could imply a distressing situation, but it contains no explicit expression of sadness, hopelessness, stress, or other emotional strain by the CHW. Thus, only minimal indirect evidence of emotional distress is present. | Lack of Resources: The testimonial recounts malaria deaths and describes preventive actions the CHW takes, but it does not state that the CHW lacks medicines, tools, or other support. No explicit or implicit resource shortage is mentioned, so alignment with the 'Lack of Resources' concept is minimal. | Systemic Barriers: The testimonial notes that the children were taken to the hospital too late, but attributes this to parental delay rather than problems with the health system itself. There is no clear mention of clinic overcrowding, stock-outs, distance, or other systemic issues preventing care. This provides only weak, indirect evidence of systemic barriers. | Overburdened CHWs: The testimonial describes malaria prevention activities the CHW performs but provides no indication of excessive workload, exhaustion, or feeling overwhelmed. Therefore, the concept of overburdened CHWs is not present. | Lack of Follow-Through: The testimonial describes preventive actions the CHW takes and recounts a tragic case, but there is no indication that the CHW began assisting someone and then abandoned or failed to complete the help. Thus, evidence of lack of follow-through is virtually absent. | Lack of Knowledge: The CHW describes preventive actions for malaria and advising others, with no statement of uncertainty or request for additional training. The testimonial shows competency rather than a lack of knowledge, so the concept does not apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Malaria I know about two children who died from malaria (???????). Their parents kept them in the house, buying them drugs over-the-counter which did not go well with them at the time. They were taken to hospital. It was too late for they did not make it. As a CHW in my dealing with malaria, I do clear bushes in my surroundings and also to clear mosquito breeding sites, sleeping under treated mosquito net. Also, I do go for check-ups whenever I experience malaria symptom. As I do all this, I also advise people to do the same. ---</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.2,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.8,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.7,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.7,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.3,
+  "Community Empowerment Through Education": 0.5,
+  "Resource and Material Distribution": 0.1,
+  "Monitoring and Follow-Up": 0.1,
+  "Trust and Cultural Mediation": 0.2,
+  "Clinical Interventions by CHWs": 0.0,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.2,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.3,
+  "Elderly Served": 0.0,
+  "Women Served": 0.0,
+  "Men Served": 0.0,
+  "Families Served": 0.7,
+  "Marginalized Groups Served": 0.1,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.2,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.0,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial shows the CHW engaging in malaria prevention activities and advising others, but there is no explicit mention of receiving training, attending workshops, or gaining knowledge through formal CHW programs. The CHW demonstrates knowledge and practices, but the source of this knowledge is not stated. This aligns with the example 'I started giving advice to neighbors based on what I learned informally' which scores 0.2. | Menstrual Hygiene Education and Challenges: The testimonial focuses entirely on malaria prevention and treatment, including clearing mosquito breeding sites and using treated nets. There is no mention of menstruation, menstrual hygiene, products, or related education. The content explicitly excludes this concept. | Drug Abuse: Environment and Awareness: The testimonial discusses malaria prevention and treatment, mentioning 'drugs' only in the medical context of over-the-counter medications for treating illness. There is no mention of substance abuse, addiction, alcohol abuse, or drug-related social/environmental factors. The concept explicitly excludes clinical descriptions of drug use without social/environmental context, which is what this testimonial contains. | CHW-Led Infectious Disease Management: Strong alignment with the concept. The CHW explicitly describes their role in malaria prevention through environmental management (clearing bushes and mosquito breeding sites), personal protective measures (sleeping under treated nets), and community education (advising people to do the same). While the testimonial focuses on prevention rather than explaining symptoms or follow-ups, it clearly demonstrates CHW-led infectious disease management activities for malaria. | Water Quality, Sanitation, and Hygiene: The testimonial focuses entirely on malaria prevention through clearing bushes, eliminating mosquito breeding sites, and using mosquito nets. There is no mention of water treatment, handwashing, sanitation practices, or any hygiene education related to water quality. The preventive measures discussed are specific to vector control for malaria, not water/sanitation/hygiene interventions. | Personal Disease Management and Adherence: The testimonial demonstrates moderate alignment with disease management. The CHW describes personal preventive measures for malaria (clearing bushes, eliminating breeding sites, using treated nets, going for check-ups when symptomatic) and advises others to do the same. While this shows disease management through prevention and early detection, it lacks specific examples of treatment adherence or helping individuals manage diagnosed cases, which would warrant a higher score. | Nutrition Education and Food Access: The testimonial focuses entirely on malaria prevention and treatment, including clearing mosquito breeding sites, using mosquito nets, and seeking medical care. There is no mention of food, nutrition, healthy eating, or food access issues. The content clearly falls outside the concept's inclusion criteria. | Sexual and Reproductive Health Education: The testimonial focuses entirely on malaria prevention and treatment, including clearing mosquito breeding sites and using treated nets. There is no mention of family planning, STI prevention, HIV awareness, reproductive rights, or any sexual health topics. This clearly falls outside the concept's inclusion criteria. | Gender-Based Violence (GBV) and Child Protection: The testimonial discusses malaria prevention and treatment, including the tragic death of two children from malaria due to delayed medical care. There is no mention of abuse, exploitation, violence, or any form of GBV or child protection issues. The children's deaths were due to a medical condition (malaria) and delayed treatment, not violence or abuse. | Health Literacy and Misconceptions: The testimonial describes parents who kept children at home and self-medicated with over-the-counter drugs instead of seeking timely medical care, resulting in deaths. This demonstrates a lack of understanding about when professional medical intervention is needed for malaria, which aligns with the concept's focus on how lack of knowledge affects health decisions and outcomes. The score is not higher because the CHW doesn't explicitly identify this as a misconception or directly address correcting misinformation. | Parsing failed for concept 'Health Literacy and Misconceptions' | Mental Health Awareness and Support: The testimonial focuses entirely on malaria prevention and treatment, describing physical health interventions like clearing mosquito breeding sites and using treated nets. While the death of children is mentioned, there is no discussion of psychological impact, emotional support, or mental health aspects. The content is purely about medical/physical health management without any mental or emotional context. | Referrals and Advocacy: The testimonial shows weak alignment with referrals and advocacy. While the CHW mentions advising people about malaria prevention and check-ups, there is no direct mention of helping with referrals, appointments, or navigating healthcare systems. The advocacy present is limited to general health advice rather than acting as an intermediary within the health system. The tragic example of children dying actually highlights a case where CHW intervention/referral did not occur. | Community Empowerment Through Education: The testimonial shows moderate alignment. The CHW describes personal preventive actions (clearing bushes, using mosquito nets) and mentions advising others to do the same, which indicates some educational effort. However, there's no evidence of lasting community behavior change, self-reliance, or group action resulting from the education. The tragic example of children dying suggests the community still lacks empowerment in health decision-making. The education appears ongoing but without clear evidence of community transformation. | Resource and Material Distribution: The testimonial focuses on preventive actions (clearing bushes, using mosquito nets) and giving advice to others, but contains no mention of the CHW actually distributing any physical resources like mosquito nets, medication, or other materials to the community. The CHW describes personal preventive measures and advising others to do the same, which aligns with the exclusion criteria of 'discussions of education or advice without material support.' | Monitoring and Follow-Up: The testimonial primarily describes preventive measures and general advice-giving about malaria, with no evidence of ongoing monitoring or follow-up visits. The CHW mentions advising people and personal check-ups, but there's no indication of returning to check on specific individuals or tracking their progress over time, which is central to the concept definition. | Trust and Cultural Mediation: The testimonial shows minimal evidence of trust-building or cultural mediation. While the CHW mentions advising people about malaria prevention, there's no indication of navigating cultural barriers, building trust, or addressing why parents initially avoided hospitals. The focus is on practical health advice rather than mediating between community beliefs and health systems. | Parsing failed for concept 'Trust and Cultural Mediation' | Clinical Interventions by CHWs: The testimonial describes preventive measures (clearing bushes, mosquito breeding sites) and health education (advising people), but contains no evidence of direct clinical interventions. The CHW mentions children who died after parents gave them over-the-counter drugs, but the CHW themselves did not administer medication or provide any direct medical treatment. This aligns with the exclusion criteria of 'health education or referrals without direct clinical interaction.' | Mother and Infant Care: The testimonial focuses entirely on malaria prevention and treatment, with no mention of prenatal care, childbirth, postpartum support, infant health, or any mother/infant-specific services. While it mentions children who died from malaria, this is about general pediatric health rather than mother and infant care as defined by the concept. | Successful Outcomes: The testimonial describes preventive actions taken by the CHW (clearing bushes, using mosquito nets, advising others) but does not mention any positive outcomes or improvements resulting from these efforts. The only specific outcome mentioned is negative (two children dying). While the CHW describes their ongoing preventive work, there's no evidence of problem resolution or positive changes, similar to the example 'I told people to take care of their health, but it's hard to know if they listened' (0.1). | Material or Training Requests: The testimonial describes the CHW's current practices for malaria prevention and their advice to others, but contains no explicit requests for materials, supplies, or training. While the CHW discusses their work with malaria cases, they do not ask for any resources to better serve their community, which is required by the inclusion criteria. | Children Served: The testimonial mentions knowing about two children who died from malaria, but this is a passive observation rather than direct CHW involvement with children. The CHW describes their malaria prevention activities (clearing bushes, using mosquito nets, advising people) but does not specifically mention working with or serving children. This aligns with the example of passing by children without direct engagement (0.1), though the context shows slightly more relevance to child health outcomes. | Elderly Served: The testimonial focuses entirely on malaria prevention and treatment, specifically mentioning children who died from malaria. There is no mention of elderly people, seniors, or grandparents, nor any assistance provided to older adults. The CHW's activities involve clearing bushes, promoting mosquito nets, and advising on malaria prevention - none of which specifically targets or mentions elderly populations. | Women Served: The testimonial focuses on children who died from malaria and general community health advice about malaria prevention. There is no mention of women or girls, no gendered roles or challenges discussed, and no CHW interaction specifically with women. The advice given appears to be general community guidance rather than targeted assistance to women. | Men Served: The testimonial discusses malaria prevention and mentions children who died from malaria, but contains no specific references to adult males or boys in the context of gendered roles or challenges. The narrative focuses on general malaria prevention practices without any gender-specific support or issues related to men. | Families Served: The testimonial clearly mentions 'two children' and 'their parents' as a family unit affected by malaria, showing CHW awareness of a family situation. While the CHW doesn't explicitly state they directly served this family, they use this family tragedy as context for their community health work. The CHW's preventive actions and advice to 'people' suggests family-inclusive interventions, though not as directly stated as the 0.9 example. | Parsing failed for concept 'Families Served' | Marginalized Groups Served: The testimonial describes general malaria prevention activities and advice to the community but does not mention serving any marginalized or stigmatized groups. The CHW discusses working with the general population on malaria prevention without any indication that these individuals face structural or social exclusion. This aligns with the low-scoring example 'I spoke with people in the community.' | Financial Hardship: The testimonial does not contain any evidence of financial hardship. While the parents bought over-the-counter drugs instead of seeking immediate hospital care, there is no indication this was due to inability to afford treatment. The focus is on delayed medical care and preventive measures for malaria, not financial constraints. | Social Isolation: The testimonial focuses on malaria prevention and a tragic case of children dying from delayed medical care. There is no mention of loneliness, living alone, lack of support systems, or abandonment. The issue described is about inadequate medical treatment rather than social isolation. | Disease Burden: While malaria can be a serious illness, this testimonial focuses on acute malaria cases and prevention strategies rather than chronic illness or disability. The deaths mentioned were from acute episodes, not long-term illness. The CHW discusses prevention and early treatment of malaria symptoms, which aligns more with managing acute illness episodes rather than chronic disease burden. | Stigma or Discrimination: The testimonial describes parents keeping children at home and self-medicating for malaria, which led to tragic outcomes. However, there is no mention of social rejection, shame, exclusion, or judgment from others. The parents' decision to keep children at home appears to be related to healthcare-seeking behavior rather than stigma. The CHW focuses on prevention strategies and early treatment, with no indication of addressing social discrimination. | Mental or Emotional Distress: The testimonial focuses entirely on malaria prevention and treatment, describing physical health interventions and the death of children from malaria. While the death of children is tragic, the CHW does not describe any mental or emotional distress experienced by themselves or others. The narrative is clinical and focused on disease management rather than emotional wellbeing. | Parsing failed for concept 'Mental or Emotional Distress' | Lack of Resources: The testimonial does not mention any lack of resources. The CHW describes preventive actions they take (clearing bushes, using mosquito nets) and advice they give, but there is no indication they lack medicine, tools, or support. The deaths mentioned were due to parents self-medicating and delayed hospital visits, not due to the CHW lacking resources to help. | Systemic Barriers: The testimonial does not mention any systemic barriers. While children died from malaria, this was due to parents' decisions to self-medicate rather than institutional failures. The CHW describes their own preventive actions and advice-giving without mentioning any health facility shortages, access issues, or other systemic obstacles preventing them from helping. | Overburdened CHWs: The testimonial describes a CHW's preventive activities and advice regarding malaria, but contains no evidence of being overburdened, exhausted, or overwhelmed. The CHW describes their routine activities (clearing bushes, advising people) without any indication of excessive workload or inability to manage their responsibilities. | Lack of Follow-Through: The testimonial does not describe any instances where the CHW started to help but left issues unresolved. The CHW describes ongoing preventive actions (clearing bushes, using mosquito nets) and advisory work. The deaths mentioned were due to parents' actions before hospital intervention, not due to the CHW abandoning care or failing to follow through on initiated help. | Lack of Knowledge: The testimonial shows no evidence of the CHW lacking knowledge. Instead, the CHW demonstrates competence by describing preventive measures (clearing bushes, eliminating breeding sites, using mosquito nets) and appropriate actions (going for check-ups). The deaths mentioned were due to parents' actions, not the CHW's lack of knowledge. The CHW appears knowledgeable about malaria prevention and management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Malaria Malaria is a serious disease caused by a parasite. When one contracts malaria, he or she feels that the body functions change gradually from being active to being tired or inactive. Malaria has physical symptoms which are fever and chills which are associated with the rupture of erythrocytic-stage schizonts. Malaria also has signs which one can feel, for example headache, muscle or joint pain, general feeling of discomfort and many others. When one feels that he or she has these signs and symptoms, they should seek medical advice immediately. Self-treatment (over-the-counter drug) is only a temporary measure and immediate medical advice or care is important. Yes, malaria can return. You can get malaria more than once even after taking the precautions that were prescribed to a patient. So one still needs to take precautions regularly to try not to get the disease. As a Community Health Worker, I would first create awareness of the disease to the community. In order the members to be aware of the disease, how it affects people, what are the precautions one needs in order not to get the disease, how one can tackle the disease when he or she has it, and many more unanswered questions. As a victim of contracting the disease more than once, the disease can interfere with your body function totally. One can feel weak and constantly vomiting and also having high fevers and many more symptoms I have not mentioned. One can seek medical care at the medical centers when he or she has these signs and symptoms. I mostly use self-treatment (over-the-counter drug) for temporary measure, but in case it is serious and cannot be contained with the over-the-counter drugs, I seek medical attention. Due to the invention of the malaria vaccines which has been approved by the World Health Organization, I know we will have positive impacts toward malaria. ---</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.1,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.88,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.75,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.1,
+  "Mental Health Awareness and Support": 0.05,
+  "Referrals and Advocacy": 0.4,
+  "Community Empowerment Through Education": 0.3,
+  "Resource and Material Distribution": 0.0,
+  "Monitoring and Follow-Up": 0.1,
+  "Trust and Cultural Mediation": 0.2,
+  "Clinical Interventions by CHWs": 0.05,
+  "Mother and Infant Care": 0.1,
+  "Successful Outcomes": 0.1,
+  "Material or Training Requests": 0.05,
+  "Children Served": 0.05,
+  "Elderly Served": 0.0,
+  "Women Served": 0.05,
+  "Men Served": 0.0,
+  "Families Served": 0.0,
+  "Marginalized Groups Served": 0.05,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.8,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.05,
+  "Lack of Resources": 0.05,
+  "Systemic Barriers": 0.05,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial is written from the perspective of a Community Health Worker who describes how they would create malaria awareness, but it never mentions receiving training, attending workshops, or gaining knowledge through a structured program. Any empowerment is only implied; there is no explicit reference to training, so alignment with the concept is minimal. | Menstrual Hygiene Education and Challenges: The testimonial focuses exclusively on malaria awareness, symptoms, treatment, and prevention; it contains no reference to menstruation, menstrual products, or menstrual education. Therefore, the concept is not applicable. | Drug Abuse: Environment and Awareness: The testimonial focuses exclusively on malaria—its symptoms, prevention, and treatment—with no mention of substance use, addiction, alcohol, or related social/environmental factors. Therefore the concept does not apply. | CHW-Led Infectious Disease Management: The speaker identifies themselves as a Community Health Worker and describes educating the community about malaria symptoms, prevention, and when to seek care. This directly aligns with CHW-led outreach and education on an infectious disease, matching the concept definition. Minor uncertainty because it is partly aspirational rather than a detailed account of completed activities, so scored slightly below a perfect match. | Water Quality, Sanitation, and Hygiene: The testimonial discusses malaria symptoms, treatment, and awareness but makes no reference to water quality, sanitation practices, or hygiene education. Therefore, the concept is not present. | Personal Disease Management and Adherence: The testimonial centers on malaria management: recognizing symptoms, using temporary over-the-counter drugs, seeking medical care, taking ongoing precautions, and mentioning the new vaccine—actions that fall under disease management guidance provided by a CHW. While it discusses general advice rather than a detailed account of strict medication adherence, the focus on how to treat and prevent malaria shows moderate–strong alignment with the concept. | Nutrition Education and Food Access: The testimonial focuses exclusively on malaria awareness, symptoms, treatment, and prevention. It does not mention food insecurity, healthy eating, or any aspect of nutrition education or food access, which are required by the concept definition. | Sexual and Reproductive Health Education: The testimonial focuses exclusively on malaria symptoms, treatment, and prevention. It contains no mention of family planning, STIs, HIV, condoms, or other sexual and reproductive health education topics. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses solely on malaria education, symptoms, prevention, and personal experience with the disease. It contains no discussion of abuse, exploitation, violence, or child protection issues, which are required for this concept. | Health Literacy and Misconceptions: The testimonial mainly provides accurate information about malaria and recommends medical care; it does not describe specific misinformation or misunderstandings among the community. Only a faint implication that awareness is needed suggests minimal relevance, so alignment with the concept is weak. | Mental Health Awareness and Support: The testimonial focuses on physical symptoms, treatment, and prevention of malaria. It does not discuss psychological well-being, feelings of depression, anxiety, or emotional support, so there is virtually no alignment with the mental health concept. | Referrals and Advocacy: The CHW advises that individuals with malaria symptoms \ | Community Empowerment Through Education: The CHW describes plans to \ | Resource and Material Distribution: The testimonial focuses on raising awareness about malaria, discussing symptoms, and seeking medical advice. It does not describe the CHW distributing any physical supplies (e.g., nets, medicine, kits). Therefore, the concept of Resource and Material Distribution is not present. | Monitoring and Follow-Up: The testimonial focuses on raising awareness about malaria symptoms, prevention, and personal experiences, with no explicit description of returning to check on patients or ongoing follow-up interactions. At most, it hints at the need for continuous precautions, but this does not illustrate CHW monitoring behavior, so alignment is minimal. | Trust and Cultural Mediation: The CHW focuses on creating awareness about malaria and advising medical care, which implies some role in communicating health information, but there is no explicit discussion of building trust, translating, or addressing cultural or linguistic barriers. This aligns only weakly with the concept, similar to simply providing information (comparable to the 0.1 leaflet example), so a low score is assigned. | Clinical Interventions by CHWs: The testimonial mainly discusses educating the community about malaria and encourages seeking medical care; it does not describe the CHW directly administering medicine, bandaging, or performing any hands-on clinical task. The only drug use mentioned is the speaker’s own self-treatment, not an intervention delivered to others. Therefore, evidence for the concept is negligible. | Mother and Infant Care: The testimonial focuses on malaria awareness, symptoms, treatment, and mentions a malaria vaccine. While immunization is listed in the concept’s inclusion criteria, here it is discussed broadly and not in the context of prenatal, postpartum, or infant care. There is no explicit reference to pregnancy, childbirth, newborns, or infant nutrition, so alignment with the Mother and Infant Care concept is minimal. | Successful Outcomes: The testimonial discusses intended CHW activities (creating awareness) and expresses hope that vaccines will have positive impacts, but provides no concrete examples of CHW actions leading to resolved problems or documented health improvements. Therefore, only minimal indirect evidence of a successful outcome is present. | Material or Training Requests: The testimonial discusses malaria symptoms, prevention, and the CHW’s approach to creating awareness, but it never explicitly asks for additional materials, supplies, or training. Therefore, alignment with the concept is minimal. | Children Served: The testimonial discusses malaria education and treatment broadly for the community without any explicit reference to children or adolescents. There is only an implicit notion that malaria vaccines exist (which could benefit children), but this is not tied to CHW activities with minors. Thus, alignment with the 'Children Served' concept is minimal. | Elderly Served: The testimonial discusses malaria awareness and personal experience but does not mention older adults, seniors, or grandparents, nor does it describe CHW assistance specifically for them. | Women Served: The testimonial discusses malaria prevention and treatment in general terms, using generic pronouns (“he or she”) and not focusing on adult females or girls, nor describing gender-specific challenges or assistance. Thus there is almost no evidence that women were explicitly served or targeted. | Men Served: The testimonial discusses malaria awareness and treatment in a general, gender-neutral way. References to “he or she” are generic and do not describe specific challenges or support directed at men or boys, which falls under the exclusion criteria. | Families Served: The testimonial discusses malaria awareness and personal experiences but contains no mention of households, parents with children, or any family-focused intervention. Therefore, the Families Served concept is not present. | Parsing failed for concept 'Families Served' | Marginalized Groups Served: The testimonial focuses on general malaria education and personal experience without mentioning any structurally excluded or stigmatized population. There is no indication that the CHW activities target a marginalized group, so alignment with the concept is minimal. | Financial Hardship: The testimonial discusses malaria symptoms, treatment, and awareness efforts but does not mention inability to pay for care, lack of income, or any material scarcity. No financial barriers to seeking medical attention or purchasing medicine are described, so the concept of Financial Hardship is not present. | Social Isolation: The testimonial discusses malaria symptoms, treatment, and community awareness without mentioning loneliness, lack of support systems, or living alone. Therefore, no evidence of social isolation is present. | Disease Burden: The testimonial emphasizes experiencing malaria multiple times (“victim of contracting the disease more than once”) and describes the functional impairment and ongoing need for precautions, aligning with the concept’s focus on recurrent illness and its burden. This is a strong direct alignment, though malaria is episodic rather than strictly chronic, so score is slightly below perfect. | Stigma or Discrimination: The testimonial discusses malaria symptoms, treatment, and community awareness without any mention of social rejection, shame, or judgment from others. Therefore, the stigma or discrimination concept is not present. | Mental or Emotional Distress: The testimonial focuses on physical symptoms and prevention/treatment of malaria. There is no explicit discussion of feelings of depression, hopelessness, or emotional overwhelm; thus only minimal implicit evidence of distress. | Lack of Resources: The testimonial focuses on describing malaria, its symptoms, and the CHW’s intention to create awareness. There is no direct statement that the CHW lacks medicine, tools, or support. The only mention of using over-the-counter drugs is a personal choice, not framed as a shortage. Therefore, evidence for ‘Lack of Resources’ is minimal, meriting a very low score. | Systemic Barriers: The testimonial largely focuses on malaria symptoms, preventive education, and personal care-seeking practices. It does not describe external institutional obstacles such as shortages, distance, corruption, or overcrowding that impede CHWs or patients. Therefore evidence for systemic barriers is essentially absent, warranting a very low score. | Overburdened CHWs: The testimonial discusses malaria symptoms and prevention steps and mentions what the CHW would do, but provides no indication of excessive workload, exhaustion, or feeling overextended. Therefore, the concept of overburdened CHWs is not present. | Lack of Follow-Through: The testimonial discusses malaria education, symptoms, and treatment preferences but provides no narrative where a CHW begins assistance and then fails to see it through. Therefore, the concept of Lack of Follow-Through is not present. | Lack of Knowledge: The testimonial demonstrates confidence and provides detailed information about malaria; it does not express uncertainty, request additional training, or indicate any knowledge gap. Therefore the concept is not present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Malaria Malaria is a serious disease caused by a parasite. When one contracts malaria, he or she feels that the body functions change gradually from being active to being tired or inactive. Malaria has physical symptoms which are fever and chills which are associated with the rupture of erythrocytic-stage schizonts. Malaria also has signs which one can feel, for example headache, muscle or joint pain, general feeling of discomfort and many others. When one feels that he or she has these signs and symptoms, they should seek medical advice immediately. Self-treatment (over-the-counter drug) is only a temporary measure and immediate medical advice or care is important. Yes, malaria can return. You can get malaria more than once even after taking the precautions that were prescribed to a patient. So one still needs to take precautions regularly to try not to get the disease. As a Community Health Worker, I would first create awareness of the disease to the community. In order the members to be aware of the disease, how it affects people, what are the precautions one needs in order not to get the disease, how one can tackle the disease when he or she has it, and many more unanswered questions. As a victim of contracting the disease more than once, the disease can interfere with your body function totally. One can feel weak and constantly vomiting and also having high fevers and many more symptoms I have not mentioned. One can seek medical care at the medical centers when he or she has these signs and symptoms. I mostly use self-treatment (over-the-counter drug) for temporary measure, but in case it is serious and cannot be contained with the over-the-counter drugs, I seek medical attention. Due to the invention of the malaria vaccines which has been approved by the World Health Organization, I know we will have positive impacts toward malaria. ---</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.1,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.8,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.8,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.0,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.3,
+  "Community Empowerment Through Education": 0.3,
+  "Resource and Material Distribution": 0.0,
+  "Monitoring and Follow-Up": 0.1,
+  "Trust and Cultural Mediation": 0.2,
+  "Clinical Interventions by CHWs": 0.1,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.1,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.0,
+  "Men Served": 0.0,
+  "Families Served": 0.0,
+  "Marginalized Groups Served": 0.0,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.7,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.0,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial shows minimal evidence of CHW training. While the person identifies as a Community Health Worker and demonstrates knowledge about malaria, there is no mention of receiving formal training, attending workshops, or gaining knowledge through CHW-specific programs. The knowledge displayed appears to come from personal experience as a malaria patient rather than structured CHW training. The score of 0.1 reflects weak alignment due to the absence of any training references despite the CHW role identification. | Menstrual Hygiene Education and Challenges: The testimonial focuses entirely on malaria - its symptoms, treatment, prevention, and the CHW's role in malaria education. There is no mention of menstruation, menstrual hygiene, products, or related education. The content explicitly excludes the concept as it discusses a completely different health topic. | Drug Abuse: Environment and Awareness: The testimonial focuses entirely on malaria as a disease, its symptoms, treatment, and prevention. There is no mention of drug abuse, addiction, alcohol, peer influence, or substance-related issues. The only reference to drugs is in the context of legitimate medical treatment for malaria (over-the-counter drugs and medical care). This clearly falls under the exclusion criteria as it lacks any social/environmental context related to substance abuse. | CHW-Led Infectious Disease Management: Strong alignment with the concept. The testimonial explicitly states 'As a Community Health Worker, I would first create awareness of the disease to the community' and describes educating community members about malaria symptoms, prevention, and treatment-seeking behavior. While the CHW describes personal experience with malaria and general disease information, they clearly articulate their role in community education about this infectious disease, which directly matches the concept definition. | Water Quality, Sanitation, and Hygiene: The testimonial focuses entirely on malaria - its symptoms, treatment, and prevention through medical means and vaccines. There is no mention of water quality, sanitation practices, hygiene education, handwashing, or any water-related disease prevention measures. The content is exclusively about malaria awareness and medical treatment, which falls outside the scope of this concept. | Personal Disease Management and Adherence: Strong alignment with the concept. The testimonial extensively discusses malaria management, including recognizing symptoms (fever, chills, headache), seeking medical care, and using temporary self-treatment before getting professional help. The CHW describes personal experience managing malaria multiple times and emphasizes the importance of medical consultation. While it focuses more on disease recognition and initial response rather than long-term adherence to treatment regimens, it clearly demonstrates disease management principles through both personal experience and community education efforts. | Nutrition Education and Food Access: The testimonial focuses entirely on malaria - its symptoms, treatment, prevention, and the CHW's role in creating awareness about the disease. There is no mention of nutrition education, food access, healthy eating, or any food-related topics. The content explicitly excludes the concept as it deals solely with malaria as a medical condition. | Sexual and Reproductive Health Education: The testimonial focuses entirely on malaria - its symptoms, treatment, and prevention. There is no mention of family planning, STI prevention, HIV awareness, reproductive rights, or any sexual health topics. The content is exclusively about malaria education and awareness, which falls outside the scope of sexual and reproductive health education. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses entirely on malaria - its symptoms, treatment, prevention, and the CHW's role in disease education. There is no mention of violence, abuse, exploitation, or any form of GBV or child protection issues. The content is exclusively about a communicable disease and medical care, which clearly falls outside the concept's definition. | Health Literacy and Misconceptions: The testimonial demonstrates accurate health knowledge about malaria, including proper understanding of symptoms, causes (parasite), and appropriate medical care. While the CHW mentions self-treatment as temporary, they emphasize seeking proper medical attention. There is no evidence of misinformation, misbeliefs about disease origins, or misunderstood symptoms - rather, the content shows good health literacy and accurate disease understanding. | Mental Health Awareness and Support: The testimonial focuses entirely on malaria as a physical disease, discussing symptoms like fever, chills, headache, and physical discomfort. While it mentions feeling weak and body function interference, these are presented as physical symptoms of malaria rather than mental or emotional concerns. There is no mention of psychological well-being, depression, anxiety, or emotional support, which are the core elements of this concept. | Referrals and Advocacy: The testimonial shows weak alignment with referrals and advocacy. While the CHW mentions creating awareness and that people 'should seek medical advice immediately' and 'seek medical care at the medical centers,' there is no direct mention of actively helping with referrals, making appointments, or navigating healthcare systems. The focus is primarily on education and awareness rather than acting as an intermediary or advocate within the health system. | Community Empowerment Through Education: The testimonial shows weak alignment with community empowerment through education. While the CHW mentions creating awareness about malaria in the community, this is stated as an intention ('I would first create awareness') rather than an actual implemented program. There is no evidence of lasting behavior change, peer education, or community self-reliance. The focus is primarily on describing malaria symptoms and personal treatment experiences rather than demonstrating how education has empowered the community to take action. | Resource and Material Distribution: The testimonial focuses entirely on malaria education, awareness creation, and personal experiences with the disease. While the CHW mentions creating awareness and educating the community about malaria prevention and treatment, there is no mention of distributing any physical resources such as malaria nets, medication, or health kits. This aligns with the exclusion criteria of 'discussions of education or advice without material support.' | Monitoring and Follow-Up: The testimonial focuses on malaria education, symptoms, and general awareness creation but contains no evidence of ongoing monitoring or follow-up activities. The CHW mentions creating awareness and education about malaria but does not describe returning to homes, checking on patients' progress, or following up after diagnoses. This aligns with the exclusion criteria of 'initial health education sessions with no follow-up' and matches the 0.1 example of visiting homes for disease prevention education without follow-up. | Trust and Cultural Mediation: The testimonial shows minimal evidence of trust-building or cultural mediation. While the CHW mentions creating awareness in the community, this is presented as information dissemination rather than navigating cultural barriers or building trust. The testimonial focuses primarily on clinical information about malaria and personal experience with the disease, without mentioning translation, explaining unfamiliar practices, or addressing community mistrust - key elements of the concept. | Clinical Interventions by CHWs: The testimonial primarily focuses on malaria education and awareness rather than direct clinical interventions. While the CHW mentions personal use of over-the-counter drugs for self-treatment, there is no evidence of them administering medication, treating wounds, or providing direct clinical care to community members. The emphasis is on creating awareness and education about malaria, which falls under the exclusion criteria of 'health education without direct clinical interaction.' | Mother and Infant Care: The testimonial focuses entirely on malaria - its symptoms, treatment, prevention, and the CHW's role in malaria education. There is no mention of prenatal care, childbirth, postpartum support, infant health, breastfeeding, or any other mother/infant-specific topics. The content is about general disease management and community health education, not mother and infant care. | Successful Outcomes: The testimonial primarily describes malaria symptoms, prevention, and the CHW's intention to create awareness, but provides no evidence of actual outcomes or positive changes resulting from CHW efforts. While the CHW mentions plans to educate the community and expresses hope about malaria vaccines, there are no specific instances of completed referrals, health improvements, or community impact. This aligns with the example 'I told people to take care of their health, but it's hard to know if they listened' which scores 0.1. | Material or Training Requests: The testimonial describes malaria symptoms, prevention, and the CHW's approach to community education, but contains no explicit requests for materials, supplies, or training. While the CHW discusses their role in creating awareness and mentions self-treatment, they do not ask for any resources or additional training to better serve their community. | Children Served: The testimonial focuses entirely on malaria education and awareness for the general community, with no specific mention of children, minors, or youth. The CHW discusses creating awareness for 'the community' and 'members' without any indication of targeting or serving children specifically. | Elderly Served: The testimonial focuses entirely on malaria education, prevention, and treatment without any mention of elderly individuals, seniors, or grandparents. The CHW discusses general community awareness and personal experience with malaria but does not reference providing assistance to older adults or any age-specific populations. | Women Served: The testimonial discusses malaria education and awareness but makes no specific mention of women, girls, or gender-specific health concerns. The CHW describes general community education without indicating any targeted assistance or education for women, which is required by the inclusion criteria. | Men Served: The testimonial focuses entirely on malaria education and prevention without any specific mention of men, boys, or gender-related contexts. While the CHW uses 'he or she' when discussing patients, this is generic language that doesn't indicate actual service to men or address male-specific health challenges, violence, or stigma as required by the concept definition. | Families Served: The testimonial focuses entirely on malaria as a disease, its symptoms, and the CHW's personal experience with it. There is no mention of households, parents with children, extended family units, or any family-focused interventions. The CHW discusses creating awareness in the community generally but does not reference working with families specifically. This clearly falls under the exclusion criteria as it represents individual-focused health education rather than family unit support. | Marginalized Groups Served: The testimonial focuses on malaria education and the CHW's general community awareness efforts, but makes no mention of serving marginalized, stigmatized, or structurally excluded groups. The CHW discusses their personal experience with malaria and general community education, without any reference to supporting underserved populations or addressing barriers faced by marginalized groups. | Financial Hardship: The testimonial focuses entirely on malaria education, symptoms, and treatment approaches without any mention of financial constraints, inability to afford care, or material scarcity. While the CHW mentions using over-the-counter drugs as a temporary measure, this is presented as a medical choice rather than a financial necessity. There is no evidence of poverty, lack of income, or inability to access care due to cost. | Social Isolation: The testimonial focuses entirely on malaria as a disease - its symptoms, treatment, and prevention. There is no mention of living alone, lack of support systems, loneliness, or social neglect. The CHW discusses their role in community education and their personal experience with malaria, but nothing relates to social isolation or abandonment. | Disease Burden: The testimonial demonstrates moderate alignment with Disease Burden. The CHW describes malaria as a 'serious disease' that 'can return' and explicitly states 'you can get malaria more than once,' indicating recurrence. They share personal experience as 'a victim of contracting the disease more than once,' showing chronic/recurring illness. The description of how 'the disease can interfere with your body function totally' suggests significant life impact. However, the focus is more on general disease education than ongoing management of chronic cases, which prevents a higher score. | Stigma or Discrimination: The testimonial focuses entirely on medical aspects of malaria - symptoms, treatment, prevention, and community education. There is no mention of social rejection, shame, exclusion, or judgment related to having malaria. The CHW discusses their personal experience with malaria without any indication of stigma. The content is purely educational and medical in nature, with no evidence of discrimination or social stigma. | Mental or Emotional Distress: The testimonial focuses entirely on malaria as a physical disease, describing physical symptoms (fever, chills, headache, muscle pain, vomiting) and medical treatment approaches. There is no mention of depression, hopelessness, trauma, stress, or any emotional/mental health concerns. The content is exclusively about physical health education and disease management, which falls under the exclusion criteria. | Lack of Resources: The testimonial does not mention any lack of resources, medicine, tools, or support. The CHW discusses malaria education, prevention, and treatment approaches, including self-treatment and seeking medical care, but never indicates insufficient supplies or capacity to address the problem. The focus is on disease awareness and management strategies rather than resource constraints. | Systemic Barriers: The testimonial focuses entirely on malaria education, symptoms, and personal treatment approaches. There is no mention of systemic barriers like health facility shortages, overcrowding, or institutional problems preventing CHW assistance. The CHW discusses their role in creating awareness and their personal experience with malaria, but does not reference any external systemic obstacles to providing care. | Overburdened CHWs: The testimonial focuses entirely on malaria education, symptoms, and treatment approaches. There is no mention of workload, patient volume, exhaustion, or being overwhelmed. The CHW describes their role in creating awareness and shares personal experience with malaria, but provides no evidence of being overburdened or overextended in their duties. | Lack of Follow-Through: This testimonial does not contain any evidence of lack of follow-through. The CHW describes their approach to malaria education and awareness, but there are no stories of abandonment, interrupted care, or failed attempts to help patients. The testimonial is educational in nature, discussing malaria symptoms, treatment approaches, and prevention, without mentioning any specific patient cases where care was started but left unresolved. | Lack of Knowledge: The testimonial demonstrates comprehensive knowledge about malaria, including its causes, symptoms, treatment approaches, and prevention. The CHW shows no uncertainty or knowledge gaps - they confidently describe the disease, explain when to seek medical care, and outline their role in community education. There are no mentions of being unsure how to proceed or needing additional training, which are the key indicators for this concept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Teenage Pregnancy Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners they have which is not healthy. ---</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.2,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.9,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.7,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.92,
+  "Gender-Based Violence (GBV) and Child Protection": 0.2,
+  "Health Literacy and Misconceptions": 0.55,
+  "Mental Health Awareness and Support": 0.05,
+  "Referrals and Advocacy": 0.65,
+  "Community Empowerment Through Education": 0.35,
+  "Resource and Material Distribution": 0.1,
+  "Monitoring and Follow-Up": 0.05,
+  "Trust and Cultural Mediation": 0.6,
+  "Clinical Interventions by CHWs": 0.1,
+  "Mother and Infant Care": 0.3,
+  "Successful Outcomes": 0.3,
+  "Material or Training Requests": 0.05,
+  "Children Served": 0.9,
+  "Elderly Served": 0.0,
+  "Women Served": 0.9,
+  "Men Served": 0.1,
+  "Families Served": 0.05,
+  "Marginalized Groups Served": 0.3,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.2,
+  "Stigma or Discrimination": 0.05,
+  "Mental or Emotional Distress": 0.2,
+  "Lack of Resources": 0.05,
+  "Systemic Barriers": 0.05,
+  "Overburdened CHWs": 0.05,
+  "Lack of Follow-Through": 0.05,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial shows the speaker educating teens about HIV prevention, but there is no explicit reference to the CHW having received training or attending workshops that enhanced their capacity. The act of educating others offers weak, indirect evidence at best, similar to the 0.2 example provided (giving advice based on informal knowledge). Therefore, only a minimal alignment score is warranted. | Menstrual Hygiene Education and Challenges: The testimonial discusses teenage pregnancy, HIV testing, and PrEP but does not mention menstruation, menstrual products, or related stigma or education. Therefore, the concept of Menstrual Hygiene Education and Challenges is not present. | Drug Abuse: Environment and Awareness: The testimonial discusses teenage pregnancy, peer pressure, HIV testing, and PrEP education, but it does not mention drugs, alcohol, addiction, or substance-abuse-related social/environmental factors. Therefore, the concept is not present. | CHW-Led Infectious Disease Management: The speaker (a CHW) describes educating teenagers about HIV testing and PrEP as preventive measures, fitting the definition and inclusion criteria of CHW-led outreach to reduce the spread of an infectious disease. This is a strong, direct example, warranting a high score. | Water Quality, Sanitation, and Hygiene: The testimonial is about sexual health education (HIV testing, PrEP, teenage pregnancy) and does not mention clean water, sanitation practices, or hygiene activities linked to disease prevention. Therefore the concept is not present. | Personal Disease Management and Adherence: The testimonial centers on HIV prevention through regular testing and daily PrEP usage—an infectious-disease context that involves medication adherence guidance from the CHW. While it does not describe a specific individual already adhering to treatment, it provides concrete counseling on a medication regimen (PrEP) and diagnostic testing, fitting the concept’s inclusion criteria, though less strongly than a clear adherence success story. | Nutrition Education and Food Access: The testimonial focuses on teenage pregnancy, HIV testing, and PrEP usage. It does not mention healthy eating, food insecurity, or any aspect of nutrition education or food access, so the concept is not applicable. | Sexual and Reproductive Health Education: The CHW describes educating teenagers about HIV testing and PrEP, explaining how PrEP works and its limits, which squarely fits STI/HIV prevention and safe-sex education outlined in the concept definition. No contradictory content is present, so alignment is strong and direct. | Gender-Based Violence (GBV) and Child Protection: The testimonial discusses teenage pregnancy and situations where teens \ | Health Literacy and Misconceptions: The CHW describes teenagers making risky sexual decisions because they lack information about partners’ HIV status and about how PREP works. She explicitly clarifies that PREP is only for HIV-negative people, does not prevent pregnancy or STDs, and becomes effective after 7 days—addressing gaps in the youths’ knowledge. While no blatant false beliefs are quoted, the narrative centers on correcting limited health literacy, so the concept is moderately present. | Mental Health Awareness and Support: The testimonial focuses on sexual health education (teen pregnancy, HIV testing, PrEP). Although it briefly mentions peer pressure and misunderstandings with partners, there is no direct discussion of psychological well-being, depression, anxiety, or explicit emotional support. Thus, only a minimal, indirect connection to mental health is present. | Referrals and Advocacy: The CHW encourages teens to go for HIV testing and to obtain PrEP, guiding them on how these services work. This shows navigation/advocacy within the health system, though it stops short of a specific formal referral. Comparable to the example 'I asked someone to consider going to the clinic' (0.5), but a bit stronger because she provides detailed guidance on accessing PrEP and testing, so a moderate-strong score of 0.65 is appropriate. | Community Empowerment Through Education: The CHW describes giving an educational talk to teenagers about HIV testing and PrEP, but the testimonial does not show that the information led to sustained behavior change, peer education, or broader community action. This resembles the example of a single teaching session with uncertain impact (scored 0.4). Therefore, only weak-to-moderate alignment with long-term community empowerment is evident. | Resource and Material Distribution: The testimonial focuses on educating teens about HIV testing and recommending PREP, but does not state that the CHW actually handed out PREP or any other physical supplies. This is primarily advice without material distribution, so alignment with the concept is minimal. | Monitoring and Follow-Up: The testimonial focuses on providing education and advice about HIV testing and PrEP in what appears to be a single session after World AIDS Day. It does not describe returning to check on individuals, tracking their progress, or any other follow-up activity that fits the definition of ongoing monitoring. Thus, only minimal evidence of the concept exists. | Trust and Cultural Mediation: The CHW describes explaining HIV testing and PrEP to teenagers, addressing their misconceptions and social barriers (partners refusing tests). This reflects cultural/social mediation by clarifying unfamiliar preventive practices and helping teens navigate relationship dynamics. However, there is no explicit mention of building or earning trust, translation, or deep cultural negotiation, so alignment is moderate rather than strong. | Clinical Interventions by CHWs: The CHW discusses PREP and HIV testing but only in the context of educating and encouraging teens; there is no description of directly administering medication or performing any clinical task. Education without direct clinical action falls under the exclusion criteria, so only a very weak alignment is present. | Mother and Infant Care: The CHW discusses teenage pregnancies and encourages HIV testing and PrEP use among teens, which touches on health support during pregnancy, but there is no mention of prenatal check-ups, childbirth preparation, postpartum follow-up, or infant care. The link to the concept is therefore weak and indirect. | Successful Outcomes: The CHW describes educating teens about HIV risks and recommending PREP, but there is no clear evidence that the teens actually took PREP or reduced risk. The narrative focuses on advice rather than confirmed improvements, so alignment with a ‘successful outcome’ is weak, similar to providing a referral without knowing the result. | Material or Training Requests: The testimonial describes the CHW educating teenagers about HIV testing and PrEP, but there is no explicit request for supplies, materials, or additional training. Therefore, alignment with the concept is minimal. | Children Served: The testimonial describes the CHW directly educating and advising teenagers (minors) about HIV testing and PrEP, which fits the inclusion criteria of providing support to children/adolescents. Clear, specific involvement, hence a strong alignment (0.9). | Elderly Served: The testimonial exclusively discusses work with teenagers concerning pregnancy and HIV prevention. There is no mention of older adults or services provided to them, so the Elderly Served concept does not apply. | Women Served: The testimonial centers on teenage girls experiencing pregnancy and HIV risk—a gender-specific challenge—and describes the CHW providing education and preventive advice (PrEP, HIV testing). This is direct assistance to female adolescents, matching the inclusion criteria for ‘Women Served.’ | Men Served: Men are only indirectly referenced as partners who resist HIV testing; no direct outreach or support to men is described. This is a general mention without services aimed at them, fitting the weak-alignment example. | Families Served: The testimonial discusses educating teenagers about HIV prevention and PrEP but never references parents, households, or family‐focused support. Since no family unit is mentioned, the alignment with the 'Families Served' concept is negligible. | Marginalized Groups Served: The CHW is working with pregnant teenagers and teens at high risk of HIV—groups that can face stigma and barriers to care—but the testimonial does not explicitly highlight structural exclusion or marginalization; it mainly describes general health education. Thus there is only weak evidence of serving a clearly marginalized population. | Financial Hardship: The testimonial focuses on teenage pregnancy, HIV education, and promoting PrEP. It contains no mention of inability to afford care, lack of income, or material scarcity. Therefore the Financial Hardship concept is not present. | Social Isolation: The testimonial discusses teenage pregnancy, HIV testing, and PREP education but contains no references to living alone, loneliness, lack of support systems, or abandonment, which define social isolation. Therefore the concept is not present. | Disease Burden: The testimonial mentions HIV/AIDS, which is a chronic illness, but focuses on prevention (encouraging HIV testing and PrEP) rather than caring for individuals already living with the disease. There is no clear description of someone experiencing a chronic condition or disability. Therefore, only a weak alignment with the Disease Burden concept is present. | Stigma or Discrimination: The testimonial discusses teenage pregnancy, HIV testing, and use of PrEP, but does not describe social judgment, shame, or exclusion directed at the teens. The barriers mentioned (partners being ‘busy’ or misunderstandings about testing) are not framed as stigma. Therefore, evidence for stigma or discrimination is minimal. | Mental or Emotional Distress: The testimonial discusses peer pressure, misunderstandings with partners, and risky behaviors, which may indirectly suggest stress, but it never explicitly describes feelings of depression, hopelessness, or emotional overwhelm. Therefore, only minimal evidence of mental or emotional distress is present. | Lack of Resources: The testimonial discusses educating teenagers about HIV testing and recommending PrEP, but it does not mention the CHW lacking medicine, tools, or support. No explicit or implicit shortage of supplies or capacity is described, so alignment with the 'Lack of Resources' concept is minimal. | Systemic Barriers: The testimonial discusses partner unwillingness to undergo HIV testing, which is an interpersonal issue, not a systemic barrier like facility shortages or institutional failures. No mention of health-system constraints or larger structural obstacles appears, so alignment with the concept is minimal. | Overburdened CHWs: The testimonial focuses on educating teens about HIV prevention and does not mention workload, exhaustion, or being overwhelmed. There is virtually no evidence of overburden, so alignment with the concept is negligible. | Lack of Follow-Through: The CHW describes educating teenagers and recommending PREP, with no mention of abandoning the effort or an unresolved outcome. This suggests virtually no evidence of lack of follow-through, only a minimal possibility that results are unknown. | Lack of Knowledge: The CHW confidently explains HIV testing and PrEP to teenagers and does not express uncertainty or a need for additional knowledge or training. Therefore, no evidence of lack of knowledge is present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Teenage Pregnancy Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners they have which is not healthy. ---</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.0,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.8,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.3,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.9,
+  "Gender-Based Violence (GBV) and Child Protection": 0.2,
+  "Health Literacy and Misconceptions": 0.3,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.3,
+  "Community Empowerment Through Education": 0.6,
+  "Resource and Material Distribution": 0.0,
+  "Monitoring and Follow-Up": 0.1,
+  "Trust and Cultural Mediation": 0.7,
+  "Clinical Interventions by CHWs": 0.0,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.6,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.9,
+  "Elderly Served": 0.0,
+  "Women Served": 0.7,
+  "Men Served": 0.0,
+  "Families Served": 0.1,
+  "Marginalized Groups Served": 0.8,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.2,
+  "Stigma or Discrimination": 0.2,
+  "Mental or Emotional Distress": 0.2,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.1,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial describes a CHW educating teenagers about HIV testing and PrEP, but contains no mention of the CHW receiving any training, attending workshops, or gaining knowledge through formal or informal CHW programs. The focus is entirely on the CHW's educational activities with teens, not on their own capacity building or empowerment through training. | Menstrual Hygiene Education and Challenges: The testimonial focuses entirely on teenage pregnancy, HIV/AIDS prevention, and PREP education. There is no mention of menstruation, menstrual hygiene, menstrual products, or any related topics. The content explicitly addresses sexual health education and HIV prevention strategies, which falls outside the scope of menstrual hygiene education. | Drug Abuse: Environment and Awareness: The testimonial focuses entirely on teenage pregnancy, HIV/AIDS prevention, and sexual health education. There is no mention of substance abuse, addiction, alcohol, or drug-related issues. While peer pressure is mentioned as a contributing factor, it's in the context of sexual behavior, not substance use. The concept clearly requires content about drug/alcohol abuse and its social/environmental factors, which is completely absent from this testimonial. | CHW-Led Infectious Disease Management: Strong alignment as the CHW actively educates teens about HIV/AIDS prevention, testing, and PrEP usage. The testimonial shows direct CHW involvement in infectious disease management through education about HIV symptoms, prevention methods, and follow-up care. While focused specifically on HIV/AIDS rather than multiple infectious diseases, it clearly demonstrates CHW-led outreach and education about an infectious disease, matching the concept's definition and inclusion criteria. | Water Quality, Sanitation, and Hygiene: The testimonial focuses entirely on teenage pregnancy, HIV prevention, and PrEP education. There is no mention of water quality, sanitation practices, handwashing, or hygiene education related to water or community sanitation. The content explicitly deals with sexual health education, which falls outside the scope of this concept. | Personal Disease Management and Adherence: This testimonial focuses on HIV prevention through PrEP education rather than disease management or treatment adherence. While it discusses a medical intervention (PrEP) and HIV testing, it's about prevention for HIV-negative individuals, not managing an existing disease. The CHW is educating about preventive measures, not helping individuals manage diagnosed conditions or adhere to treatment regimens. This aligns with the example 'I mentioned health issues in the community' which scores 0.3. | Nutrition Education and Food Access: The testimonial focuses entirely on teenage pregnancy, HIV/AIDS education, and PREP (pre-exposure prophylaxis) medication. There is no mention of food, nutrition, healthy eating, food insecurity, or any nutrition-related topics. The content explicitly deals with sexual health education and HIV prevention, which falls outside the scope of the Nutrition Education and Food Access concept. | Sexual and Reproductive Health Education: Strong direct alignment with the concept. The testimonial explicitly covers HIV awareness and prevention education for teenagers, including detailed information about PrEP (Pre-Exposure Prophylaxis) as an HIV prevention method. The CHW discusses HIV testing with partners, addresses the reality of multiple partners among teens, and provides specific health education about PrEP usage. While condoms aren't mentioned and the focus is primarily on HIV prevention rather than broader STI prevention or family planning, the content clearly falls within sexual and reproductive health education as defined by the concept. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses on teenage pregnancy and HIV prevention education, not on violence or abuse. While there is a brief mention of teens 'giving in to their demands' due to fear of 'misunderstandings,' this is presented as relationship pressure rather than explicit violence or abuse. The content primarily addresses sexual health education and risk reduction, which falls under the exclusion criteria of 'general emotional distress without reference to violence or abuse.' | Health Literacy and Misconceptions: The testimonial shows weak alignment with health literacy issues. While there's no explicit misinformation or misconceptions about disease origins, there is evidence of knowledge gaps around HIV testing and prevention. The teens' partners avoiding HIV testing and the teens' lack of awareness about PREP before the CHW's intervention suggest some health literacy challenges. However, the CHW is providing accurate information rather than correcting specific misconceptions or mistrust in medicine. | Parsing failed for concept 'Health Literacy and Misconceptions' | Mental Health Awareness and Support: The testimonial focuses entirely on teenage pregnancy, HIV prevention, and sexual health education. There is no mention of psychological well-being, emotional support, or mental health issues like depression, anxiety, or loneliness. While the topic involves vulnerable teenagers, the CHW's intervention is purely educational about physical health (HIV testing, PREP medication) rather than addressing any mental or emotional aspects. | Referrals and Advocacy: The testimonial shows weak alignment with referrals and advocacy. While the CHW educates teens about HIV testing and PREP, and encourages them to seek these services, there is no explicit mention of making referrals, helping with appointments, or actively navigating the healthcare system. The CHW's role is primarily educational and advisory rather than serving as an intermediary or navigator within the health system. | Community Empowerment Through Education: The testimonial shows moderate alignment with community empowerment through education. The CHW conducted education about HIV testing and PREP following World AIDS Day, targeting teenagers facing pregnancy and HIV risks. While there is evidence of sustained educational effort and problem-solving (adapting advice when teens faced partner resistance), the impact on long-term behavior change or community self-reliance is unclear. The education appears ongoing rather than a one-time event, but there's no clear evidence of peer education, group action, or community-wide transformation that would warrant a higher score. | Resource and Material Distribution: The testimonial focuses entirely on education and advice about HIV testing and PrEP usage for teenagers. While the CHW mentions PrEP medication, they only educated about it rather than distributing it. The exclusion criteria specifically states 'discussions of education or advice without material support,' which perfectly describes this testimonial. No actual distribution of resources, materials, or supplies is mentioned. | Monitoring and Follow-Up: This testimonial describes a one-time educational session about HIV testing and PrEP following World AIDS Day, with no mention of returning to check on the teens' progress, following up on whether they got tested, or monitoring their health status afterward. This aligns with the exclusion criteria of 'one-time visits or initial health education sessions with no follow-up.' | Trust and Cultural Mediation: The testimonial shows moderate alignment with trust-building and cultural mediation. The CHW navigates sensitive social barriers around HIV testing in teenage relationships, where partners resist testing due to cultural stigma. The CHW builds trust by listening to teens share personal information about multiple partners and provides culturally appropriate solutions (PREP) when abstinence isn't realistic. However, the focus is more on health education than explicit trust-building or cultural translation, preventing a higher score. | Clinical Interventions by CHWs: The testimonial describes health education about HIV testing and PrEP (pre-exposure prophylaxis), but contains no evidence of the CHW directly administering medication, treating wounds, or performing any clinical tasks. The CHW only educated teens about PrEP and encouraged them to seek testing and medication from healthcare facilities. This falls under the exclusion criteria of 'health education or referrals without direct clinical interaction.' | Mother and Infant Care: This testimonial focuses on teenage pregnancy prevention, HIV testing, and PrEP education for sexually active teens. While it mentions teenage pregnancy, it does not discuss prenatal care, childbirth, postpartum support, or infant health. The content is about preventing pregnancy and HIV transmission, not supporting mothers or infants, which clearly falls under the exclusion criteria. | Successful Outcomes: The testimonial shows moderate alignment with successful outcomes. The CHW successfully educated teens about HIV testing and PREP, and some teens shared personal information indicating trust was built. However, there's no clear evidence of completed referrals, actual PREP uptake, or measurable health improvements. The CHW provided a solution (PREP education) to address the testing barrier, but the outcome remains uncertain, similar to the 0.4 example where referral was made but outcome unknown. | Material or Training Requests: The testimonial describes a CHW educating teenagers about HIV testing and PrEP, but contains no requests for materials, supplies, or training. The CHW describes actions already taken and advice given, without expressing any needs or asking for additional resources to better serve the community. | Children Served: Strong direct alignment. The testimonial explicitly describes the CHW educating and providing health guidance to teenagers (minors under 18) about HIV prevention, testing, and PREP. The CHW directly engaged with teens, listened to their concerns about partners and relationships, and provided tailored health education and solutions. This clearly demonstrates support for adolescents in health matters, matching the inclusion criteria. | Elderly Served: The testimonial focuses exclusively on teenage pregnancy and HIV/AIDS education for teenagers. There is no mention of elderly people, seniors, or grandparents, nor any CHW assistance provided to older adults. The entire narrative centers on teens and their sexual health education. | Women Served: The testimonial describes CHW education provided to teenagers about HIV prevention and sexual health, which likely includes teenage girls given the focus on pregnancy. While the CHW directly interacted with and educated teens on health matters (PREP, HIV testing), the testimonial uses gender-neutral language ('teens', 'teenagers') rather than explicitly mentioning women or girls. The context of teenage pregnancy inherently involves females, making this a moderate alignment with the concept. | Men Served: The testimonial focuses exclusively on teenage pregnancy and HIV prevention among teenagers/teens, with no specific mention of adult males or boys in gendered contexts. While male partners are implied in the pregnancy context, they are not directly served or supported by the CHW, nor are they discussed in terms of gendered roles or challenges. The focus remains on educating and supporting the teenage population generally. | Families Served: The testimonial focuses on educating teenagers about HIV prevention and PREP, with no mention of households, parents, or family units. While teenage pregnancy affects families, the CHW's intervention specifically targets individual teens rather than family-focused support. This aligns with the exclusion criteria of 'individual help not connected to a family unit or structure.' | Marginalized Groups Served: Strong alignment with the concept. The testimonial describes CHW support for pregnant teenagers, who face social stigma and exclusion. The CHW addresses their specific vulnerabilities (peer pressure, inability to negotiate safe practices with partners, fear of relationship conflict) and provides targeted education and solutions (PREP). While not explicitly using terms like 'marginalized,' the context clearly shows these teens face structural barriers to healthcare access due to age, social position, and stigma around teenage sexuality. | Financial Hardship: The testimonial focuses entirely on teenage pregnancy, HIV prevention education, and PREP medication. There is no mention of poverty, inability to afford transportation, food, medical care, or any other financial constraints. The challenges described are related to health education, partner cooperation, and risky behaviors - not economic hardship. | Social Isolation: The testimonial focuses on teenage pregnancy, HIV education, and sexual health counseling. There is no mention of living alone, loneliness, lack of support systems, or abandonment. The teenagers described have partners and peer groups, indicating social connections rather than isolation. The concept of social isolation is clearly not present in this testimonial. | Disease Burden: The testimonial focuses on HIV/AIDS prevention and teenage pregnancy, which are health risks rather than chronic illnesses or disabilities. While HIV/AIDS could become a chronic condition if contracted, the testimonial is about prevention efforts, not managing existing disease. There's no mention of current chronic illness, disability, or frequent illness episodes among the teens being counseled. | Stigma or Discrimination: The testimonial contains minimal evidence of stigma or discrimination. While it mentions that some partners refuse HIV testing and that 'insisting to go for check-ups always leads to misunderstandings,' this reflects relationship dynamics and avoidance rather than social rejection or judgment due to health conditions. The CHW's approach is educational and supportive without addressing shame or exclusion from the community. | Mental or Emotional Distress: The testimonial focuses primarily on teenage pregnancy and HIV prevention education. While there are indirect references to emotional challenges (teens giving in to demands to avoid misunderstandings, peer pressure), there is no direct expression of depression, hopelessness, trauma, or emotional overwhelm. The distress mentioned is more situational and relationship-based rather than mental or emotional distress as defined by the concept. | Lack of Resources: The testimonial does not mention any lack of medicine, tools, or support. The CHW successfully educated teens about HIV testing and PREP, and was able to provide advice and solutions. There is no indication of insufficient supplies or capacity to address the teenage pregnancy and HIV prevention issues discussed. | Systemic Barriers: The testimonial does not mention any systemic barriers outside the CHW's control. The challenges described (peer pressure, partner reluctance to test, relationship dynamics) are interpersonal issues rather than institutional failures or systemic problems. The CHW successfully provides education and solutions (PREP) without encountering health facility shortages, corruption, or other systemic obstacles. | Overburdened CHWs: The testimonial describes a CHW educating teenagers about HIV prevention and PREP, but contains no evidence of being overburdened. The CHW appears to be successfully delivering education and solving problems without mentioning exhaustion, excessive workload, or being overwhelmed. The focus is entirely on the health issue being addressed rather than any challenges with workload or capacity. | Lack of Follow-Through: The CHW provided education and a concrete solution (PREP) to address the teens' concerns about HIV testing with uncooperative partners. While the original issue of partners refusing testing wasn't fully resolved, the CHW didn't abandon the case but rather offered an alternative approach. This represents a completed intervention with ongoing support, not a lack of follow-through. | Lack of Knowledge: The CHW demonstrates comprehensive knowledge throughout the testimonial. They successfully educated teens about HIV testing, understood the barriers teens faced, and provided an appropriate solution (PrEP) with detailed, accurate information about its use, eligibility criteria, and limitations. There is no evidence of knowledge gaps or uncertainty in how to proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Child Nutrition Access to adequate and nutritious food is important for good health. The convention provides for the application of readily available technology for the provision of adequate nutritious food and clear drinking water. Both the state and the parent of the child have to participate in ensuring that children are now nourished nutrition support programs by the government and non-governmental organizations such as the school feeding programs in arid and semi-arid areas plays on essential role nutrition awareness programs that educate parents on how to supplement the staple food with easily available nutrients are also important. As CHW, I am thankful to KUAP, as they offer nutrition programs and teaching to young mothers on how they can handle their little ones. ---</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.2,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.0,
+  "Water Quality, Sanitation, and Hygiene": 0.2,
+  "Personal Disease Management and Adherence": 0.1,
+  "Nutrition Education and Food Access": 0.9,
+  "Sexual and Reproductive Health Education": 0.05,
+  "Gender-Based Violence (GBV) and Child Protection": 0.05,
+  "Health Literacy and Misconceptions": 0.2,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.15,
+  "Community Empowerment Through Education": 0.6,
+  "Resource and Material Distribution": 0.25,
+  "Monitoring and Follow-Up": 0.1,
+  "Trust and Cultural Mediation": 0.2,
+  "Clinical Interventions by CHWs": 0.05,
+  "Mother and Infant Care": 0.8,
+  "Successful Outcomes": 0.2,
+  "Material or Training Requests": 0.05,
+  "Children Served": 0.85,
+  "Elderly Served": 0.0,
+  "Women Served": 0.85,
+  "Men Served": 0.0,
+  "Families Served": 0.8,
+  "Marginalized Groups Served": 0.5,
+  "Financial Hardship": 0.3,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.2,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.0,
+  "Lack of Resources": 0.05,
+  "Systemic Barriers": 0.1,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.05
+}</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial notes that KUAP provides nutrition programs and teaching to young mothers, with the CHW expressing gratitude. It does not clearly state that the CHW personally received training or gained new skills; any implication of CHW training is indirect and weak. Therefore, only minimal evidence of CHW empowerment through training is present. | Menstrual Hygiene Education and Challenges: The testimonial discusses child nutrition programs and education about feeding, with no mention of menstruation, menstrual products, or stigma related to menstruation. Therefore, the concept does not apply. | Drug Abuse: Environment and Awareness: The testimonial discusses child nutrition programs and does not mention substance abuse, addiction, peer influence, or any related social or environmental factors. Therefore, the concept is not present. | CHW-Led Infectious Disease Management: The testimonial discusses nutrition programs and educating parents on healthy food for children. It does not mention infectious diseases, their symptoms, prevention, or any CHW activities related to managing infectious diseases, so the concept is not applicable. | Water Quality, Sanitation, and Hygiene: The testimonial briefly mentions the provision of 'clear drinking water' alongside nutrition, but there is no detailed discussion of water treatment, hand-washing, or sanitation education. This provides only minimal evidence of the concept. | Personal Disease Management and Adherence: The testimonial focuses on child nutrition programs and educating mothers about feeding practices. It does not discuss managing a specific disease, following a treatment regimen, or adhering to medication. Therefore, there is only very weak relevance to disease management or adherence. | Nutrition Education and Food Access: The testimonial explicitly discusses ensuring children have access to adequate and nutritious food, mentions school feeding programs in food-insecure areas, and highlights nutrition awareness programs that teach parents how to supplement staple foods. As a CHW, the speaker also notes participation in nutrition programs that educate young mothers. These elements directly align with the concept’s focus on food access and nutrition education, providing strong, unambiguous evidence. | Sexual and Reproductive Health Education: The testimonial focuses on child nutrition programs and educating parents about feeding their children. There is no mention of family planning, condoms, STI/HIV prevention, or reproductive rights. Thus, alignment with Sexual and Reproductive Health Education is minimal. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses on child nutrition programs and education for parents. There is no mention of abuse, exploitation, violence, or related CHW interventions. Any reference to children is solely about nutrition, not protection from violence or abuse; therefore alignment with the GBV and Child Protection concept is negligible. | Health Literacy and Misconceptions: The testimonial notes nutrition awareness programs that teach parents, implying a need to improve health knowledge, but it does not describe specific misunderstandings or misinformation affecting decisions. Thus alignment with the concept is weak and only partial. | Mental Health Awareness and Support: The testimonial focuses solely on child nutrition programs and provides no mention of psychological well-being, emotional issues, or mental health support. Therefore, the concept is not present. | Referrals and Advocacy: The testimonial describes nutrition programs and education but does not state that the CHW actively referred clients, scheduled appointments, or advocated within the health system. Presence of CHW is noted, yet no clear intermediary or navigation role is articulated, so only minimal alignment with the concept. | Community Empowerment Through Education: The testimonial highlights education-focused nutrition programs that teach parents and young mothers how to improve their children’s diets, matching the inclusion criterion of community change efforts through peer or group education. However, it does not explicitly describe resulting long-term behavior change or self-reliance; it only states that such teaching is provided. Therefore, alignment is moderate rather than strong. | Resource and Material Distribution: The testimonial talks generally about nutrition support and school feeding programs but does not state that the CHW personally distributed food or other tangible supplies. It focuses more on education and program availability, which falls outside the core inclusion criteria of actually handing out resources. | Monitoring and Follow-Up: The testimonial mentions nutrition programs and education offered to young mothers but provides no indication that the CHW conducts ongoing checks or revisits to track children’s nutritional status. It resembles an informational or educational activity rather than continued monitoring, so only minimal evidence of follow-up is present. | Trust and Cultural Mediation: The testimonial briefly notes that CHWs provide nutrition programs and teach young mothers, which implies some level of community education that may require trust. However, it does not explicitly mention building trust, addressing cultural or linguistic barriers, or mediating between the community and health system. Therefore the alignment with the Trust and Cultural Mediation concept is weak. | Parsing failed for concept 'Trust and Cultural Mediation' | Clinical Interventions by CHWs: The testimonial describes CHWs offering nutrition programs and teaching mothers, which is health education rather than directly administering medicine or treating physical ailments. No clinical tasks such as giving medication or bandaging wounds are mentioned, so alignment with the clinical intervention concept is minimal. | Mother and Infant Care: The testimonial mentions CHW-facilitated nutrition programs that teach young mothers how to care for their \ | Successful Outcomes: The testimonial expresses appreciation for nutrition programs and education provided to mothers, suggesting potential benefits, but it does not cite a clear, concrete result such as improved child health or a completed referral. Therefore, only weak evidence of a successful outcome is present. | Material or Training Requests: The testimonial thanks an organization for existing nutrition programs but does not explicitly request additional materials, supplies, or training. Therefore, alignment with the concept is minimal. | Children Served: The testimonial centers on child nutrition and mentions school feeding programs and teaching young mothers how to care for their children—direct indications of support for minors’ health. This fits the inclusion criteria for Children Served. While the narrative is broad and partly focuses on parents, the primary theme is children’s well-being, warranting a strong but not absolute match. | Elderly Served: The testimonial focuses on child nutrition and programs for young mothers; it never mentions older adults or assistance to seniors. Therefore, the concept 'Elderly Served' is not present. | Women Served: The testimonial explicitly references \ | Men Served: The testimonial focuses on child nutrition programs and education for young mothers; there is no mention of adult males or boys being served or their gender-specific challenges. | Families Served: The testimonial centers on educating parents and young mothers about child nutrition, indicating family-focused interventions rather than help to a lone individual. This aligns strongly with the concept of serving families, though it doesn’t describe a specific household visit, so a score slightly below perfect is appropriate. | Marginalized Groups Served: The testimonial discusses nutrition programs such as school feeding in arid and semi-arid areas and education for young mothers. Children in these regions are typically underserved, suggesting some support to marginalized populations, but the text does not explicitly frame them as structurally excluded or stigmatized. Therefore, there is moderate alignment but not a strong, unambiguous match. | Financial Hardship: The testimonial discusses the need for school feeding and nutrition support programs, implying some scarcity of adequate food for children, which suggests financial or material hardship. However, it never explicitly states that families cannot afford food or are impoverished, so alignment is weak and indirect rather than strong. | Social Isolation: The testimonial discusses child nutrition programs and education for parents, with no mention of loneliness, living alone, lack of support systems, or abandonment. Therefore, the Social Isolation concept does not apply. | Disease Burden: The testimonial focuses on nutrition programs and education to prevent malnutrition in children, which loosely relates to health burden, but it does not explicitly mention chronic or recurrent illness or disability. Thus only weak evidence of disease burden is present. | Stigma or Discrimination: The testimonial discusses nutrition programs and support for children and mothers, with no mention of social rejection, judgment, shame, or exclusion. Therefore, stigma or discrimination is not present. | Mental or Emotional Distress: The testimonial focuses on child nutrition programs and expresses gratitude for educational support; it does not mention feelings of depression, stress, or any other form of emotional distress. | Lack of Resources: The testimonial focuses on existing nutrition programs and expresses gratitude for the support; it does not mention shortages of medicine, tools, or other resources. Therefore there is virtually no evidence of a Lack of Resources, warranting a near-zero score. | Systemic Barriers: The testimonial references government and NGO nutrition programs but does not describe any shortage, corruption, or institutional obstacle that prevents the CHW from helping. Thus, evidence for systemic barriers is minimal. | Overburdened CHWs: The testimonial discusses nutrition programs and expresses gratitude but contains no indication of excessive workload, exhaustion, or being overextended. Therefore, the concept of overburdened CHWs is not present. | Lack of Follow-Through: The testimonial describes successful nutrition programs and expresses gratitude; there is no indication of a CHW starting help and leaving the issue unresolved. This falls outside the concept’s inclusion criteria. | Lack of Knowledge: The testimonial thanks an organization for providing nutrition programs but does not state that the CHW lacked knowledge or needed additional training; there is only an implicit appreciation of resources. Thus alignment with the concept is minimal. | Parsing failed for concept 'Lack of Knowledge'</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Child Nutrition Access to adequate and nutritious food is important for good health. The convention provides for the application of readily available technology for the provision of adequate nutritious food and clear drinking water. Both the state and the parent of the child have to participate in ensuring that children are now nourished nutrition support programs by the government and non-governmental organizations such as the school feeding programs in arid and semi-arid areas plays on essential role nutrition awareness programs that educate parents on how to supplement the staple food with easily available nutrients are also important. As CHW, I am thankful to KUAP, as they offer nutrition programs and teaching to young mothers on how they can handle their little ones. ---</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.7,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.0,
+  "Water Quality, Sanitation, and Hygiene": 0.3,
+  "Personal Disease Management and Adherence": 0.0,
+  "Nutrition Education and Food Access": 0.9,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.0,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.3,
+  "Community Empowerment Through Education": 0.7,
+  "Resource and Material Distribution": 0.2,
+  "Monitoring and Follow-Up": 0.2,
+  "Trust and Cultural Mediation": 0.2,
+  "Clinical Interventions by CHWs": 0.0,
+  "Mother and Infant Care": 0.8,
+  "Successful Outcomes": 0.7,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.8,
+  "Elderly Served": 0.0,
+  "Women Served": 0.8,
+  "Men Served": 0.0,
+  "Families Served": 0.8,
+  "Marginalized Groups Served": 0.6,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.1,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.0,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.0
+}</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial shows moderate alignment with CHW empowerment through training. The CHW explicitly mentions being 'thankful to KUAP, as they offer nutrition programs and teaching,' which suggests they have received training in nutrition education. They demonstrate knowledge about child nutrition, food security, and various nutrition programs, indicating capacity building. However, the testimonial doesn't explicitly state that the CHW personally attended training sessions or workshops, making it less direct than the 0.9 example where training is explicitly mentioned. | Menstrual Hygiene Education and Challenges: The testimonial focuses entirely on child nutrition, food security, and nutritional education for mothers. There is no mention of menstruation, menstrual hygiene, sanitary products, or any related topics. The content explicitly discusses nutrition programs and feeding, which falls outside the scope of menstrual hygiene education. | Drug Abuse: Environment and Awareness: The testimonial focuses entirely on child nutrition, food access, and nutrition education programs. There is no mention of drug abuse, addiction, alcohol, or any substance-related issues. The content explicitly discusses nutrition awareness and feeding programs, which falls outside the scope of the Drug Abuse concept. | Parsing failed for concept 'Drug Abuse: Environment and Awareness' | CHW-Led Infectious Disease Management: The testimonial focuses entirely on child nutrition, food security, and nutrition education programs. There is no mention of infectious diseases, disease prevention, symptoms, or any disease-related outreach. While the CHW mentions educating young mothers, this education is specifically about nutrition and child care, not infectious disease management. This clearly falls under the exclusion criteria as it discusses health topics without any connection to infectious diseases. | Water Quality, Sanitation, and Hygiene: The testimonial mentions 'clear drinking water' as part of adequate nutrition provision, showing a weak connection to water quality. However, the focus is primarily on nutrition and food security rather than water treatment, sanitation practices, or hygiene education. The water reference is incidental to the main nutrition theme, warranting a low score. | Personal Disease Management and Adherence: This testimonial focuses entirely on child nutrition, food access, and nutrition education programs. There is no mention of disease diagnosis, treatment adherence, medication management, or any chronic/infectious disease context. The content is about preventive nutrition and healthy child development, which falls under the exclusion criteria as it lacks a disease management context. | Parsing failed for concept 'Personal Disease Management and Adherence' | Nutrition Education and Food Access: Strong direct alignment with the concept. The testimonial explicitly discusses nutrition education programs for parents, teaching young mothers about child nutrition, school feeding programs, and the importance of adequate nutritious food. The CHW directly mentions being involved in nutrition programs through KUAP, which aligns with the inclusion criteria of 'learning about healthy meals' and 'feeding children'. | Sexual and Reproductive Health Education: The testimonial focuses entirely on child nutrition, food security, and nutritional education for mothers. There is no mention of family planning, STI prevention, HIV awareness, reproductive rights, or any sexual health topics. This clearly falls outside the concept's scope. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses entirely on child nutrition, food security, and nutrition education programs. There is no mention of abuse, violence, exploitation, or any GBV-related issues. The CHW discusses nutrition support programs and teaching young mothers about child nutrition, which falls outside the scope of the GBV and Child Protection concept. | Health Literacy and Misconceptions: The testimonial focuses entirely on accurate health information about child nutrition, government programs, and education initiatives. There is no mention of misinformation, misbeliefs, or misconceptions being addressed or corrected. The CHW describes positive educational programs without indicating any health literacy challenges or misconceptions that needed to be overcome. | Mental Health Awareness and Support: The testimonial focuses entirely on child nutrition, food access, and nutritional education programs. There is no mention of psychological well-being, emotional support, depression, anxiety, or any mental health-related content. The CHW discusses physical health through nutrition rather than mental/emotional aspects. | Parsing failed for concept 'Mental Health Awareness and Support' | Referrals and Advocacy: The testimonial shows weak alignment with referrals and advocacy. While the CHW mentions being thankful for nutrition programs that teach young mothers, there is no explicit mention of the CHW personally helping with referrals, appointments, or navigating healthcare systems. The focus is primarily on nutrition education rather than acting as an intermediary or advocate within the health system. | Community Empowerment Through Education: The testimonial shows moderate alignment with community empowerment through education. The CHW mentions nutrition awareness programs that educate parents on supplementing food with available nutrients, and specifically notes KUAP's nutrition programs and teaching to young mothers. This indicates ongoing educational efforts aimed at behavior change. However, the testimonial doesn't provide clear evidence of actual long-term change, self-reliance achieved, or community-wide transformation resulting from these programs, which prevents a higher score. | Resource and Material Distribution: The testimonial primarily discusses nutrition education and awareness programs rather than direct distribution of materials. While it mentions nutrition programs and teaching young mothers, there is no explicit mention of the CHW distributing food, supplies, or other physical resources. The focus is on education and program facilitation, which aligns with the exclusion criteria of 'discussions of education or advice without material support.' | Monitoring and Follow-Up: The testimonial primarily discusses nutrition programs and education for young mothers, but does not explicitly mention ongoing monitoring, return visits, or follow-up activities. While the CHW mentions teaching programs, there is no clear evidence of checking progress or adjusting care over time, which are key elements of the monitoring and follow-up concept. | Trust and Cultural Mediation: The testimonial primarily focuses on nutrition programs and education without explicitly mentioning trust-building or cultural mediation activities. While the CHW mentions teaching young mothers, there's no clear evidence of navigating cultural barriers, translating information, or building community trust. The content is more aligned with direct health education rather than cultural mediation, similar to the 'gave out leaflets about nutrition' example (0.1). | Clinical Interventions by CHWs: The testimonial focuses entirely on nutrition education and awareness programs. The CHW mentions being thankful for nutrition programs and teaching offered to young mothers, which falls under health education rather than direct clinical intervention. There is no mention of administering medication, treating wounds, or any other direct medical tasks, clearly placing this in the exclusion criteria. | Mother and Infant Care: Strong direct alignment. The testimonial explicitly mentions CHW involvement in 'nutrition programs and teaching to young mothers on how they can handle their little ones,' which directly relates to infant care and nutrition. While the broader context discusses general child nutrition, the specific CHW role focuses on supporting mothers with infant care, aligning well with the concept's inclusion criteria of 'infant health and nutrition' and support for mothers. | Successful Outcomes: The testimonial shows moderate alignment with successful outcomes. The CHW describes positive impacts through nutrition programs and education for young mothers, indicating community benefit. However, it lacks specific examples of individual health improvements or completed interventions, focusing more on the existence of programs rather than concrete results from CHW efforts. | Material or Training Requests: The testimonial describes existing nutrition programs and expresses gratitude for current support from KUAP, but contains no requests for materials, supplies, or training. The CHW is thankful for what is already provided rather than asking for additional resources, which clearly excludes this from the concept. | Children Served: Strong alignment with the concept. The testimonial focuses extensively on child nutrition, mentions 'little ones' being served through nutrition programs, and describes the CHW's involvement in teaching young mothers about child care. While children aren't directly mentioned as receiving services, the entire context revolves around improving child health through nutrition programs and parent education, which clearly benefits children under 18. | Elderly Served: The testimonial focuses exclusively on child nutrition, young mothers, and school feeding programs. There is no mention of elderly people, seniors, or grandparents, nor any CHW assistance to older adults. The concept is clearly not present. | Women Served: Strong alignment as the testimonial explicitly mentions CHW teaching 'young mothers' about nutrition and child care. This directly involves assistance and education for women in their gendered role as mothers, focusing on health-related topics. The score is not higher because the focus is primarily on child nutrition rather than women's health directly. | Men Served: The testimonial focuses entirely on child nutrition and support for young mothers. There is no mention of men or boys being served, nor any discussion of gendered roles or challenges related to males. The only reference to parents is gender-neutral, and the specific mention is of 'young mothers' receiving support. | Families Served: Strong alignment with the concept. The testimonial explicitly mentions 'young mothers' and 'their little ones' (children), clearly indicating family units. The CHW discusses nutrition programs that educate parents about feeding their children, which directly aligns with 'CHW support for multiple members or family-focused interventions.' While not describing specific household visits, the focus on parent-child relationships and family-centered nutrition support strongly matches the concept definition. | Marginalized Groups Served: The testimonial mentions CHW support for young mothers in arid and semi-arid areas through nutrition programs. These geographic regions often face structural exclusion due to limited resources and access to services, suggesting moderate alignment with serving marginalized groups. However, the testimonial lacks explicit reference to stigma, discrimination, or specific marginalized identities, preventing a higher score. | Parsing failed for concept 'Marginalized Groups Served' | Financial Hardship: The testimonial focuses on nutrition programs, education, and support services but contains no statements about poverty, lack of income, or inability to afford food, transportation, or medical care. While it discusses nutrition access in arid/semi-arid areas, it emphasizes available programs and education rather than financial barriers or material scarcity. | Parsing failed for concept 'Financial Hardship' | Social Isolation: The testimonial focuses entirely on child nutrition, food access, and nutrition education programs. There is no mention of loneliness, living alone, lack of support systems, or abandonment. The content discusses community programs and parental involvement, which actually suggests social connection rather than isolation. | Parsing failed for concept 'Social Isolation' | Disease Burden: The testimonial focuses on nutrition programs and preventive education for children and mothers, with no mention of chronic illness, disability, or recurrent health conditions. While malnutrition could lead to disease burden, the text emphasizes prevention and education rather than managing existing chronic conditions, aligning with the example 'spoke with community members about general wellness' (0.1). | Stigma or Discrimination: The testimonial focuses entirely on child nutrition, food access, and educational programs. There is no mention of social rejection, judgment, shame, exclusion, or any form of stigma or discrimination. The content is about positive support programs and education, which clearly falls outside the concept's inclusion criteria. | Parsing failed for concept 'Stigma or Discrimination' | Mental or Emotional Distress: The testimonial focuses entirely on child nutrition, food access, and educational programs. There is no mention of depression, hopelessness, trauma, stress, or any form of mental or emotional distress. The content is about physical health and nutrition support, which falls under the exclusion criteria. | Parsing failed for concept 'Mental or Emotional Distress' | Lack of Resources: The testimonial does not mention any lack of resources. Instead, the CHW expresses gratitude for existing nutrition programs and teaching provided by KUAP. The text discusses available support systems like school feeding programs and nutrition awareness programs, indicating resources are present rather than lacking. | Systemic Barriers: The testimonial does not mention any systemic barriers preventing the CHW from helping. Instead, it describes positive systemic support through government and NGO nutrition programs, school feeding programs, and KUAP's educational initiatives. The CHW expresses gratitude for these resources rather than frustration with institutional obstacles. | Overburdened CHWs: The testimonial focuses on child nutrition programs and expresses gratitude for support received. There is no mention of excessive workloads, exhaustion, or being overwhelmed. The CHW appears satisfied with the resources and support available, which is contrary to the concept of being overburdened. | Lack of Follow-Through: The testimonial describes successful, ongoing nutrition programs and education provided by CHWs and organizations. There is no evidence of abandoned care, interrupted services, or unresolved issues. The CHW expresses gratitude for existing programs that are actively helping mothers and children, indicating sustained support rather than lack of follow-through. | Lack of Knowledge: The testimonial shows no evidence of knowledge gaps. The CHW demonstrates understanding of nutrition principles and explicitly expresses gratitude for KUAP's nutrition programs and teachings. Rather than indicating a lack of knowledge, the CHW appears knowledgeable about nutrition's importance and appreciates the training provided to mothers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CHW Training Having been in Nyalenda for the last five years, health information in the community was not taken seriously. But after the training and we started working in the community giving health information, now they can go to the nearest facility and at the same time we do referrals. In the training, I got more information about COVID-19 even before the government COVID lockdown and how to manage COVID-19. Before training, I could not do first aid. But after the training, I have some skills and now am in a position to perform first aid before I do referrals to the facility. Patient assessment was quite challenging to me. But after being trained by Madam Winnie and Mr. Kituli, I can now do it on my own and know how to handle some of the problems and refer. With the information I have from the training and my knowledge, the community I am in today is changing gradually. They are very eager to be taught more and more about the health issues, because they have been lacking information for so long. But thanks to WiRED International for the training they gave us, because now we are able to give back to the community the information we get, and the community is impressed so much, and they are requesting that we keep on giving them the information that they had lacked for some time. I would like to thank Madam Winnie and Mr. Kituli so much for the training they gave us. It is just on another level. Thanks to Lilian for believing in us and giving us a chance to be trained. Thanks to Mr. Gary for the support you gave us during the training up to now. May God bless you. ---</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 1.0,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.9,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.4,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.6,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.9,
+  "Community Empowerment Through Education": 0.85,
+  "Resource and Material Distribution": 0.0,
+  "Monitoring and Follow-Up": 0.1,
+  "Trust and Cultural Mediation": 0.6,
+  "Clinical Interventions by CHWs": 0.75,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.8,
+  "Material or Training Requests": 0.1,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.0,
+  "Men Served": 0.0,
+  "Families Served": 0.0,
+  "Marginalized Groups Served": 0.2,
+  "Financial Hardship": 0.05,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.1,
+  "Stigma or Discrimination": 0.05,
+  "Mental or Emotional Distress": 0.05,
+  "Lack of Resources": 0.6,
+  "Systemic Barriers": 0.2,
+  "Overburdened CHWs": 0.1,
+  "Lack of Follow-Through": 0.05,
+  "Lack of Knowledge": 0.9
+}</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: The testimonial explicitly focuses on CHWs receiving training (from WiRED International, Madam Winnie, Mr. Kituli) and describes how this training increased their capacity to serve—gaining skills in first aid, patient assessment, COVID-19 management, and conducting referrals. This aligns perfectly with the concept’s definition and inclusion criteria of CHWs gaining knowledge through training. | Menstrual Hygiene Education and Challenges: The testimonial discusses general health training, COVID-19 information, first aid, and patient assessment, but it does not mention menstruation, menstrual products, stigma, or related education. Therefore, the concept is not present. | Drug Abuse: Environment and Awareness: The testimonial discusses CHW training, COVID-19 information, patient assessment, and first aid. It contains no references to substance abuse, addiction, alcohol, peer influence, or lack of drug education. Therefore, the concept is not present. | CHW-Led Infectious Disease Management: The testimonial explicitly states that after training the CHW gained information on COVID-19 \ | Water Quality, Sanitation, and Hygiene: The testimonial discusses training on general health information, COVID-19 management, first aid, and referrals but does not mention water quality, sanitation practices, or hygiene education linked to water. Therefore the concept is not present. | Personal Disease Management and Adherence: The testimonial briefly mentions that the CHW received training on “how to manage COVID-19,” which touches on the idea of managing an infectious disease. However, it does not describe specific instances of patients adhering to treatment, taking medication, or ongoing disease self-management. Most of the narrative is about general health information, first aid, and referrals rather than concrete disease-management behaviors, so alignment is weak to moderate. | Nutrition Education and Food Access: The testimonial discusses CHW training on general health information, COVID-19 management, first aid, and patient assessment. It does not mention nutrition, healthy eating, food insecurity, or food access, so the concept is not applicable. | Sexual and Reproductive Health Education: The testimonial discusses CHW training on general health information, COVID-19, first aid, and patient assessment. It contains no references to family planning, STI prevention, condoms, or other reproductive health education topics defined in the concept. | Gender-Based Violence (GBV) and Child Protection: The testimonial discusses CHW training, health education, and COVID-19 response but does not mention violence, abuse, exploitation, or child protection issues. Therefore, it does not align with the GBV and Child Protection concept. | Health Literacy and Misconceptions: The testimonial stresses that community members previously lacked health information and did not take it seriously, and that training has improved their ability to seek care and accept referrals. This reflects the impact of limited health literacy on health behaviors, fitting the concept’s inclusion of ‘lack of knowledge affecting health decisions.’ However, no concrete examples of specific misconceptions or misinformation are provided, so alignment is moderate rather than strong. | Parsing failed for concept 'Health Literacy and Misconceptions' | Mental Health Awareness and Support: The testimonial focuses on CHW training, health information, first aid, and referrals, with no mention of psychological well-being, depression, anxiety, or other mental health support. | Referrals and Advocacy: The testimonial explicitly states that after training the CHW \ | Community Empowerment Through Education: The CHW describes sustained provision of health information that has led the community to start seeking care at facilities and to request continued education, indicating an ongoing, community-wide change in behavior rather than a one-time event. This aligns strongly with the concept’s focus on long-term empowerment through health education, though the testimonial does not yet provide exhaustive evidence of fully established self-reliance, hence slightly below a perfect score. | Resource and Material Distribution: The testimonial focuses on CHW training, providing health information, and making referrals. It does not mention giving out supplies, medicine, food, or any other material resources. According to the concept definition, education alone without material support is excluded, so the concept is not present. | Monitoring and Follow-Up: The testimonial centers on receiving training, providing health information, and making referrals. It does not describe returning to individuals to check their health status or ongoing follow-up care. Any sense of continued engagement is limited to general community education requests, which falls outside the definition of monitoring and follow-up. Hence, only a minimal alignment score is assigned. | Trust and Cultural Mediation: The CHW describes how previously the community 'did not take health information seriously' but, after the CHW’s training and engagement, community members now listen, seek care at facilities, and actively request more information. This suggests the CHW has succeeded in gaining the community’s trust and facilitating acceptance of health services, fitting the concept of building trust between community and health system. However, there is no explicit mention of navigating linguistic or cultural barriers or of translating, so the alignment is moderate rather than strong. | Parsing failed for concept 'Trust and Cultural Mediation' | Clinical Interventions by CHWs: The testimonial states that after training the CHW is \ | Mother and Infant Care: The testimonial discusses CHW training related to general health information, COVID-19, first aid, and patient assessment, with no mention of pregnancy, childbirth, postpartum issues, or infant health. Therefore, the Mother and Infant Care concept is not present. | Successful Outcomes: The testimonial describes clear positive changes attributed to the CHW’s work after training: community members now visit facilities, referrals are made, first-aid and patient assessment skills are applied, and the community is ‘changing gradually’ and ‘impressed.’ These statements indicate improved conditions and impact, aligning strongly with the concept of Successful Outcomes, though they are general rather than specific case recoveries, so a score slightly below perfect is appropriate. | Material or Training Requests: The testimonial focuses on expressing gratitude for training already received and discusses its impact. There is no explicit request by the CHW for additional materials, supplies, or further training, so the concept is largely absent. A minimal score (0.1) reflects the very weak, indirect mention of the community wanting continued information but no direct CHW request. | Children Served: The testimonial discusses general community health education and CHW training without any explicit mention of children, minors, or adolescents. Therefore, the concept 'Children Served' is not present. | Elderly Served: The testimonial discusses CHW training, health information dissemination, referrals, and first aid skills but makes no mention of elderly people or services specifically directed toward them. | Women Served: The testimonial talks about providing general health information, first aid, and referrals to the community at large, with no mention of women or gender-specific needs. Therefore the concept ‘Women Served’ is not present. | Men Served: The testimonial discusses general community health training and outreach without any mention of men or boys or gender-specific issues. Therefore, the concept is not present. | Families Served: The testimonial discusses CHW training and providing health information to the broader community, but it does not mention households, parents with children, or any family‐focused support. Therefore, the concept “Families Served” is not present. | Parsing failed for concept 'Families Served' | Marginalized Groups Served: The CHW talks about providing health information and referrals to the local community that had 'been lacking information for so long.' This implies some level of underserved status, but there is no explicit reference to structurally marginalized groups (e.g., migrants, disabled, stigmatized). Evidence of serving marginalized populations is therefore weak and indirect. | Financial Hardship: The testimonial focuses on the benefits of CHW training and improved health information. It does not mention poverty, inability to pay for care, transportation costs, or other material scarcity. Only a generic reference to accessing the nearest facility is made, with no indication of financial barriers. Therefore financial hardship is essentially absent. | Social Isolation: The testimonial discusses CHW training, improved health information dissemination, and gratitude to trainers. It contains no mention of individuals living alone, loneliness, lack of support systems, or abandonment, so the Social Isolation concept is not present. | Disease Burden: Testimonial mainly describes training and providing health information. While COVID-19 is mentioned, there is no focus on chronic or recurrent illness or disability, which the concept emphasizes. Therefore, only minimal indirect evidence of disease burden is present. | Stigma or Discrimination: The testimonial focuses on training, increased health knowledge, and community engagement. It does not describe any social rejection, shame, or judgment toward individuals or groups. Therefore, there is virtually no evidence of stigma or discrimination, resulting in a near-zero score. | Mental or Emotional Distress: The testimonial focuses on training, skill acquisition, and community impact without describing feelings of depression, stress, or emotional overwhelm. The brief mention that patient assessment was \ | Lack of Resources: The CHW describes that before the recent training they lacked the knowledge and skills (capacity) to do first-aid, patient assessment and provide accurate health information—indicating an insufficiency in a key resource (training/capacity). After receiving training this gap was filled. This fits the inclusion criterion of having insufficient capacity, but no explicit mention of missing medicines or equipment, so the alignment is moderate rather than strong. | Parsing failed for concept 'Lack of Resources' | Systemic Barriers: The CHW mentions that the community had been “lacking information for so long” and did not take health information seriously—conditions outside the CHW’s control that impeded their work. However, there is no clear reference to institutional shortages, corruption, or facility-level barriers; the focus is on training gains rather than systemic obstacles. Thus, only a weak alignment with the systemic‐barrier concept is present. | Overburdened CHWs: The testimonial focuses on the positive impact of training and improved capability. There is no explicit statement of exhaustion or excessive workload; at most, it notes that the community wants more health information, which is only a faint suggestion of additional work. This provides minimal evidence for overburden, so a very low score is assigned. | Lack of Follow-Through: The testimonial describes successful training and improved ability to provide information, referrals, and first aid. There is no mention of starting an intervention and then abandoning it or leaving issues unresolved. Therefore, evidence for Lack of Follow-Through is virtually absent, warranting a very low score. | Lack of Knowledge: The CHW explicitly states that before the training they could not do first aid and found patient assessment challenging, showing they were unable to address issues because of insufficient knowledge. This aligns directly with the concept definition and inclusion criteria (mentions of needing additional training). The testimonial is clear and unambiguous, so a high score (0.9) is warranted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CHW Training Having been in Nyalenda for the last five years, health information in the community was not taken seriously. But after the training and we started working in the community giving health information, now they can go to the nearest facility and at the same time we do referrals. In the training, I got more information about COVID-19 even before the government COVID lockdown and how to manage COVID-19. Before training, I could not do first aid. But after the training, I have some skills and now am in a position to perform first aid before I do referrals to the facility. Patient assessment was quite challenging to me. But after being trained by Madam Winnie and Mr. Kituli, I can now do it on my own and know how to handle some of the problems and refer. With the information I have from the training and my knowledge, the community I am in today is changing gradually. They are very eager to be taught more and more about the health issues, because they have been lacking information for so long. But thanks to WiRED International for the training they gave us, because now we are able to give back to the community the information we get, and the community is impressed so much, and they are requesting that we keep on giving them the information that they had lacked for some time. I would like to thank Madam Winnie and Mr. Kituli so much for the training they gave us. It is just on another level. Thanks to Lilian for believing in us and giving us a chance to be trained. Thanks to Mr. Gary for the support you gave us during the training up to now. May God bless you. ---</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>{
+  "CHW Empowerment Through Training": 0.9,
+  "Menstrual Hygiene Education and Challenges": 0.0,
+  "Drug Abuse: Environment and Awareness": 0.0,
+  "CHW-Led Infectious Disease Management": 0.8,
+  "Water Quality, Sanitation, and Hygiene": 0.0,
+  "Personal Disease Management and Adherence": 0.3,
+  "Nutrition Education and Food Access": 0.0,
+  "Sexual and Reproductive Health Education": 0.0,
+  "Gender-Based Violence (GBV) and Child Protection": 0.0,
+  "Health Literacy and Misconceptions": 0.7,
+  "Mental Health Awareness and Support": 0.0,
+  "Referrals and Advocacy": 0.9,
+  "Community Empowerment Through Education": 0.85,
+  "Resource and Material Distribution": 0.0,
+  "Monitoring and Follow-Up": 0.1,
+  "Trust and Cultural Mediation": 0.7,
+  "Clinical Interventions by CHWs": 0.7,
+  "Mother and Infant Care": 0.0,
+  "Successful Outcomes": 0.8,
+  "Material or Training Requests": 0.0,
+  "Children Served": 0.0,
+  "Elderly Served": 0.0,
+  "Women Served": 0.0,
+  "Men Served": 0.0,
+  "Families Served": 0.1,
+  "Marginalized Groups Served": 0.5,
+  "Financial Hardship": 0.0,
+  "Social Isolation": 0.0,
+  "Disease Burden": 0.0,
+  "Stigma or Discrimination": 0.0,
+  "Mental or Emotional Distress": 0.0,
+  "Lack of Resources": 0.0,
+  "Systemic Barriers": 0.0,
+  "Overburdened CHWs": 0.0,
+  "Lack of Follow-Through": 0.0,
+  "Lack of Knowledge": 0.8
+}</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CHW Empowerment Through Training: This testimonial strongly aligns with CHW Empowerment Through Training. The CHW explicitly mentions receiving formal training from WiRED International and specific trainers (Madam Winnie and Mr. Kituli). They describe multiple skills gained through this training: COVID-19 management, first aid capabilities, patient assessment, and health information dissemination. The CHW directly states how the training transformed their ability to serve the community, moving from being unable to perform certain tasks to confidently executing them independently. The repeated references to 'after the training' and specific examples of enhanced capacity make this a strong match for the concept. | Menstrual Hygiene Education and Challenges: The testimonial focuses entirely on general CHW training, COVID-19 management, first aid skills, and patient assessment. There is no mention of menstruation, menstrual hygiene, sanitary products, or any gender-specific health issues related to menstruation. The content is about broad community health education and does not address the specific topic of menstrual hygiene education or challenges. | Drug Abuse: Environment and Awareness: The testimonial focuses entirely on general health information dissemination, COVID-19 management, first aid skills, and patient assessment. There is no mention of substance abuse, addiction, alcohol, peer influence, or drug education. The CHW discusses improving health literacy in their community but does not reference any drug-related issues or environmental factors contributing to substance abuse. | CHW-Led Infectious Disease Management: Strong direct alignment. The testimonial explicitly mentions the CHW receiving training about COVID-19 management before the government lockdown and now educating the community about health issues. While COVID-19 is specifically mentioned as an infectious disease the CHW learned to manage, the testimonial focuses more broadly on general health information and referrals rather than detailed disease prevention or symptom education, preventing a perfect score. | Water Quality, Sanitation, and Hygiene: The testimonial focuses on general health information dissemination, COVID-19 management, first aid skills, and patient assessment. There is no mention of water treatment, handwashing, sanitation practices, or hygiene education related to water quality. The CHW discusses health education broadly but does not reference any water, sanitation, or hygiene-specific interventions. | Personal Disease Management and Adherence: The testimonial mentions COVID-19 management capabilities gained through training, but lacks specific examples of helping individuals with disease management or treatment adherence. The focus is primarily on general health education, referrals, and first aid rather than chronic disease management or medication adherence support. The COVID-19 reference is about knowledge gained, not actual disease management implementation. | Parsing failed for concept 'Personal Disease Management and Adherence' | Nutrition Education and Food Access: The testimonial focuses entirely on general health information dissemination, COVID-19 management, first aid skills, and patient assessment. There is no mention of nutrition education, food security, healthy eating, or food access issues. The CHW discusses various health topics but nutrition is not among them. | Sexual and Reproductive Health Education: The testimonial focuses entirely on general health information, COVID-19 management, first aid skills, and patient assessment. There is no mention of family planning, STI prevention, HIV awareness, reproductive rights, or any sexual health topics. The CHW discusses health education broadly but does not reference any components that would align with the Sexual and Reproductive Health Education concept. | Gender-Based Violence (GBV) and Child Protection: The testimonial focuses entirely on general health education, COVID-19 management, first aid skills, and patient assessment training. There is no mention of abuse, violence, exploitation, or any GBV-related interventions. The CHW discusses community health information gaps and medical referrals, but makes no reference to violence or child protection issues. | Health Literacy and Misconceptions: The testimonial strongly indicates that the community previously lacked health information and 'health information in the community was not taken seriously.' This suggests misconceptions or gaps in health literacy that the CHW is now addressing. The community's eagerness to learn 'because they have been lacking information for so long' further supports this. While specific misconceptions aren't detailed, the clear pattern of information deficit leading to poor health decisions (not going to facilities) aligns moderately with the concept. | Mental Health Awareness and Support: The testimonial focuses entirely on physical health training, COVID-19 management, first aid skills, and general health information dissemination. There is no mention of psychological well-being, emotional support, or mental health issues like depression, anxiety, or loneliness. The CHW discusses only medical/physical health topics and community health education, which falls under the exclusion criteria of 'medical diagnoses without a mental/emotional context.' | Referrals and Advocacy: Strong direct alignment with the concept. The CHW explicitly mentions performing referrals multiple times ('we do referrals', 'before I do referrals to the facility', 'refer'), demonstrating their role as an intermediary in the health system. They describe helping community members access healthcare by encouraging them to 'go to the nearest facility' and performing patient assessments before referral, which shows navigation support. This matches the high-scoring example of identifying symptoms and referring for testing. | Community Empowerment Through Education: Strong alignment with the concept. The testimonial describes sustained community change through health education over 5 years, with the community now actively seeking health information and utilizing health facilities. The CHW reports that 'the community I am in today is changing gradually' and residents are 'very eager to be taught more and more about the health issues.' This demonstrates lasting behavior change beyond one-time events, with the community becoming more self-reliant in seeking healthcare and information. | Resource and Material Distribution: The testimonial focuses entirely on health information sharing, training, referrals, and first aid skills. There is no mention of distributing any physical resources like medication, food, hygiene kits, or educational materials. The CHW explicitly states they are 'giving health information' and 'giving back to the community the information,' which falls under the exclusion criteria of 'education or advice without material support.' | Monitoring and Follow-Up: The testimonial focuses on training received and general community health education activities, but contains minimal evidence of ongoing monitoring or follow-up. While the CHW mentions doing referrals and that the community is 'changing gradually' and requesting more information, there is no specific mention of returning to check on individuals, following up after diagnoses, or monitoring health progress. The activities described appear to be ongoing education rather than follow-up care, similar to the 0.1 example about visiting homes for disease prevention. | Trust and Cultural Mediation: The testimonial shows moderate alignment with trust-building themes. The CHW describes how health information was 'not taken seriously' before, but after training and community engagement, the community is now 'impressed' and 'eager to be taught more.' This indicates the CHW has built trust and overcome initial skepticism. However, there's no explicit mention of cultural mediation, translation, or navigating specific cultural barriers, which prevents a higher score. | Clinical Interventions by CHWs: The testimonial shows moderate alignment with clinical interventions. The CHW explicitly states they can now perform first aid before referrals, which directly involves basic medical tasks. However, the testimonial lacks specific examples of clinical actions (like bandaging wounds or giving medicine), focusing more on the ability to perform first aid rather than describing actual clinical interventions performed. | Mother and Infant Care: The testimonial focuses on general health information dissemination, COVID-19 management, first aid skills, and patient assessment. There is no mention of prenatal care, childbirth, postpartum support, infant health, breastfeeding, or any other mother/infant-specific services. The CHW discusses general community health education and referrals but nothing specific to mothers or infants. | Successful Outcomes: Strong alignment with successful outcomes. The testimonial describes multiple positive changes: community members now go to health facilities, successful referrals are being made, the CHW can perform first aid before referrals, and the community is 'changing gradually' with increased eagerness for health information. While not as specific as 'person recovered' (0.9 example), it shows clear community impact and improved conditions attributed to CHW efforts. | Material or Training Requests: While the CHW mentions that the community is 'requesting that we keep on giving them the information,' this is the community requesting continued service, not the CHW requesting materials or training. The testimonial focuses on expressing gratitude for training already received and describing its positive impact, without any explicit requests for additional materials, supplies, or further training. | Children Served: The testimonial focuses entirely on general community health education and does not mention children, minors, or youth at all. The CHW discusses working with 'the community' and providing health information, but there is no specific reference to serving children or adolescents, making this a clear non-match for the concept. | Elderly Served: The testimonial focuses on general community health education, COVID-19 management, first aid skills, and patient assessment training. There is no mention of elderly people, seniors, grandparents, or any specific assistance provided to older adults. The CHW discusses serving 'the community' broadly without any reference to elderly populations or age-specific services. | Women Served: The testimonial describes general community health education and training but makes no specific mention of women, girls, or gender-specific health services. The CHW discusses serving 'the community' broadly without any reference to women's health issues, pregnancy care, or gender-related challenges that would align with the concept definition. | Men Served: The testimonial focuses on general community health education and training experiences without any specific mention of men, boys, or gender-related health issues. The CHW discusses serving 'the community' broadly but provides no evidence of addressing men's health needs, gendered challenges, or male-specific support contexts. | Families Served: The testimonial focuses on community-wide health education and individual patient care, but does not specifically mention households, parents with children, or family units. The CHW discusses giving health information to 'the community' and doing 'patient assessment,' which suggests individual-focused care rather than family-centered interventions. This aligns with the exclusion criteria of 'individual help not connected to a family unit.' | Marginalized Groups Served: The testimonial describes serving a community (Nyalenda) that lacked health information for years and had not taken health seriously, suggesting some level of underservice. However, there is no explicit mention of specific marginalized groups (disabled, migrants, minorities) or structural exclusion. The focus is on general community health education and COVID-19 management rather than targeted support for stigmatized populations. | Financial Hardship: The testimonial focuses entirely on CHW training experiences, knowledge gained, and community health education improvements. There is no mention of poverty, inability to afford care, transportation costs, or any material scarcity. The community's lack of health information is described as an information gap rather than a financial barrier. | Parsing failed for concept 'Financial Hardship' | Social Isolation: The testimonial focuses entirely on CHW training, health information dissemination, and community engagement. There is no mention of individuals living alone, lacking support systems, or experiencing loneliness. The community is described as eager and engaged, which suggests social connection rather than isolation. | Disease Burden: The testimonial focuses on CHW training, health information dissemination, COVID-19 management, first aid skills, and patient assessment. There are no references to chronic illness, disability, or frequent illness episodes. The CHW discusses general health education and emergency response capabilities rather than managing long-term conditions or recurring health issues. | Stigma or Discrimination: The testimonial focuses entirely on positive community engagement, improved health education, and successful CHW training outcomes. There is no mention of social rejection, shame, exclusion, or judgment related to health conditions or identity. The community is described as 'eager' and 'impressed' rather than exhibiting any discriminatory behaviors. | Parsing failed for concept 'Stigma or Discrimination' | Mental or Emotional Distress: The testimonial focuses entirely on CHW training, health information dissemination, COVID-19 management, first aid skills, and community health education. There is no mention of depression, hopelessness, trauma, stress, or any emotional/mental health concerns. The content is about building medical knowledge and skills, not addressing mental or emotional distress. | Lack of Resources: The testimonial does not mention any lack of medicine, tools, or support. Instead, it focuses on how training improved the CHW's capabilities and how the community now has better access to health information. The CHW expresses gratitude for the training and support received, which is the opposite of lacking resources. | Systemic Barriers: The testimonial focuses entirely on positive outcomes from CHW training and improved community health education. There is no mention of systemic barriers like health facility shortages, overcrowding, corruption, or institutional obstacles. The CHW describes successfully making referrals and providing health information without encountering systemic impediments. The narrative emphasizes empowerment and capability rather than external constraints. | Parsing failed for concept 'Systemic Barriers' | Overburdened CHWs: The testimonial shows no evidence of the CHW being overburdened. Instead, it focuses entirely on positive outcomes from training, improved skills, and successful community engagement. The CHW expresses gratitude and enthusiasm rather than exhaustion or being overwhelmed. There is no mention of excessive workloads, too many patients, or feeling overextended. | Parsing failed for concept 'Overburdened CHWs' | Lack of Follow-Through: The testimonial describes successful completion of training and ongoing community health work. The CHW reports actively providing health information, performing first aid, conducting assessments, and making referrals. The community is described as 'changing gradually' and 'eager to be taught more,' indicating sustained engagement rather than abandonment. There is no evidence of interrupted care or unresolved issues. | Lack of Knowledge: Strong alignment with the concept. The CHW explicitly states multiple knowledge gaps before training: couldn't do first aid, found patient assessment 'quite challenging,' and indicates the community had been 'lacking information for so long.' These are clear examples of being unable to address issues due to lack of knowledge, which were resolved through training.</t>
         </is>
       </c>
     </row>

--- a/data/outputs/model_disagreements.xlsx
+++ b/data/outputs/model_disagreements.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,42 +444,42 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>o3</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>anthropic</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Asthma Asthma is a chronic disease which can affect everyone. I spotted a young child wheezing and as I inquired from the mother, she told me that she was suspecting that the child might be having common cold as the child was coughing due to change of weather. But to me as a CHW I thought that it would be best if the child was to be taken to the hospital for medical examination so that the mother could know what was wrong with the child. With my help, I referred the ??? to take the child to the hospital. The child was tested and was found to be ailing from asthma. The child was put onto medication and as now the child showing some improvements. Though asthma is a chronic disease, if proper medication and continuous taking of the drugs is well conducted, it can help in reducing chances of child fatality. ---</t>
+          <t>Tuberculosis People living in ????? settlements tend to not be concerned about their health. Many are first concerned with how they can attend to their daily labor to make some money which can help them put some food on the table. People are coughing and just take it as a normal cough. During my field work, I came across two people who were coughing as I was training them. I asked them when they started coughing and advised them to see the doctor for a tuberculosis test. They went for the test and one of them was found positive for tuberculosis. She has begun treatment and hopefully she will be okay. As CHW, I am now talking to many and also refer them for tuberculosis test at ???? ---</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Community Empowerment Through Education</t>
+          <t>Group Based Health Education</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
         <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>COVID-19 Regarding the COVID-19 new variant, since most of the community members took vaccines, many people have left the common practices which were given by the Ministry of Health such as washing hands, putting on masks, avoiding crowded places, and keeping social distance. Political rallies in Kenya have attracted so many crowds that has contributed to many people contracting the disease. Omicron wave was reported in Kenya some few weeks back and we have seen cases of the Omicron is rising day by day. As a CHW, I have been emphasizing on training the community members on how to continue practicing the COVID-19 measures and about mobilizing these who have not been vaccinated to go for vaccinations. ---</t>
+          <t>Tuberculosis During my fieldwork engagement with my participants in a training, one of my participants approached me after I had completed my training—and asked me if I could be able to allow him share with me something. I first thought what could he wanted to tell me, yet I gave time for questions during the sessions. And he could not ask anything. Bravely enough, I heeded to his request and he shared with me that he was diagnosed with tuberculosis and he was put into medication but unfortunately, he defaulted. He wanted to know if I could help him get back to medication but was not happy to go back to Thramogi Agmga Teaching and Referral Hospital since they could not help him. I managed to refer him to KNAP and he got helped and now his life is improving day by day. I am doing close follow-up on him to make sure he has taken his drugs. ---</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Referrals and Advocacy</t>
+          <t>Tuberculosis Education and Prevention</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -492,30 +492,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Malaria Having malaria is a very bad experience that personally I would not like to get sick again. Physical symptoms that I had was fatigue, vomiting, fever, and sometimes diarrhea. In the evening a strong headache and chills appeared as if it had been stirred up or triggered by something. Sincerely speaking, when I felt symptoms coming on, I used to go over the counter and buy malaria drugs—e.g., ACTM—because I thought that every symptom as such could be malaria which I realized after becoming a CHW that it was not a good idea. Malaria could return again and again because I was not adhering to the instructions of completing doses, I was not treating malaria well, not sleeping under mosquito treated net. As a CHW, what I can do to help people with malaria is to advise them to go to the hospital and get tested and also to be treated well whenever the symptoms occur. ---</t>
+          <t>Malaria The weather in Kisumu has totally changed, there is a lot of rains and floodings experienced everywhere. This rain has also brought a lot of stagnant water which helps mosquitoes breed. During the week I took my training emphasizing on how to use nets to help in preventing the spread of malaria. I also came across one of my participants who was having malaria but was just using over-the-counter drugs. I referred the person to Thoamogi Oginga Teaching and Referral Hospital for the malaria test which later turned positive and he was treated and given prescriptions of the medicines. As a CHW, I am very happy that the person is responding well to medications. ---</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training</t>
+          <t>Group Based Health Education</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
         <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Malaria Having malaria is a very bad experience that personally I would not like to get sick again. Physical symptoms that I had was fatigue, vomiting, fever, and sometimes diarrhea. In the evening a strong headache and chills appeared as if it had been stirred up or triggered by something. Sincerely speaking, when I felt symptoms coming on, I used to go over the counter and buy malaria drugs—e.g., ACTM—because I thought that every symptom as such could be malaria which I realized after becoming a CHW that it was not a good idea. Malaria could return again and again because I was not adhering to the instructions of completing doses, I was not treating malaria well, not sleeping under mosquito treated net. As a CHW, what I can do to help people with malaria is to advise them to go to the hospital and get tested and also to be treated well whenever the symptoms occur. ---</t>
+          <t>Malaria During my health education at Bandani Slums-Kisumu County, giving malaria talk to the residents, I narrowed down on the signs and symptoms of malaria, the treatment and causes. Some of the causes like not sleeping under the treated mosquito nets, vector control. The signs and symptoms like high ever, shaking, chills, pain in the muscles and abdomen. Some people feel very sick, fatigue, fever, night sweats, nausea, shivering diarrhea, vomiting, headache and coldness. Upon completion, one Mrs. Mary Onyango approached me and requested that I visit her home. On our way to her homestead, she narrated to me some of the signs we talked about earlier that she has been seeing little girl experiencing. On reaching her homestead a few kilometers from where we were, I met the little girl. She was sweating all over her body. She told me she had headache; I saw her shivering and was vomiting. Based on what I saw, I concluded the child might have been suffering from malaria. I told the mother to do the sponging to reduce the temperature due to the high fever. I advised the mother to take her to the nearest health facility for further management. After two days, I did a follow-up home visit to see how the little girl was. She was given anti-malaria tablets and was responding well to the treatment. ---</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Community Empowerment Through Education</t>
+          <t>Infectious Disease Prevention</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -528,48 +528,48 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Malaria Malaria is a bacterial infection caused by plasmodium vale that affects the blood stream of human body. It is spread through anopheles mosquito bite from one person to another. People who have malaria usually feel sick with high fever and shaking chills. Some people may experience signs in the abdomen or muscles, fatigue, fever, night sweats, shivering, nausea, diarrhea, vomiting, headache, and coldness. The physical symptoms of malaria may include vomiting, tiredness, shivering, body weakness, sweating, children might be restless. The immediate action I take as a Community Health Worker when I see the symptoms coming is to do the sponging to reduce temperature, drink a lot of water due to vomiting and diarrhea. This are the first aid you do before going to the hospital. The malaria infection may return time and again if the patient does not follow the preventive measures like sleeping under the treated mosquito nets and vector control. As a Community Health Worker, if you once identify someone suffering from malaria, I immediately refer to the nearest health center. Many people have died from malaria due to late diagnosis that might lead to anemia, enlarged spleen that leads to ????????? that have similar symptoms as malaria. Disease like typhoid, dysentery. So, if not careful, you might miss the diagnosis, so you must thoroughly and probe the client. You should be well conversant with the signs and symptoms of malaria. And thus, the slogan “ZERO MALARIA STARTS WITH ME.” ---</t>
+          <t>Teenage Pregnancy/HIV AIDS Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners, they have which is not healthy. ---</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Community Empowerment Through Education</t>
+          <t>Individualized Support and Health Education</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
         <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Malaria The weather in Kisumu has totally changed, there is a lot of rains and floodings experienced everywhere. This rain has also brought a lot of stagnant water which helps mosquitoes breed. During the week I took my training emphasizing on how to use nets to help in preventing the spread of malaria. I also came across one of my participants who was having malaria but was just using over-the-counter drugs. I referred the person to Thoamogi Oginga Teaching and Referral Hospital for the malaria test which later turned positive and he was treated and given prescriptions of the medicines. As a CHW, I am very happy that the person is responding well to medications. ---</t>
+          <t>Teenage Pregnancy/HIV AIDS Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners, they have which is not healthy. ---</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training</t>
+          <t>Infectious Disease Prevention</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
         <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Menstrual Hygiene/Teenage Pregnancy Many teenage adolescent girls and young women suffer from what we call menstrual poverty. Menstrual poverty is an incidence whereby a girl is not able to get access to menstrual aids such as sanitary towels and menstrual cups. At the beginning of December, teenage pregnancy rapid growth raised an alarm whereby many individuals and like-minded individuals came together to find out why most of our teenage girls are getting pregnant. The 16-day activism and activism that brought about ??????? for Google meets and physical meetings helped me reach out to more than 50 girls and had some chit chats. From the interactions, I found out that menstrual poverty is a major leading factor in this lack of sanitary towels during this time of the month forcing some girls to engage in transactional sex which back to these unwanted teenage pregnancies. From this I, as a CHW, decided to partner with other ??? and individuals to fundraise for pads to give these girls. This has helped reduce and prevent some if not all. Most men and adults too have been sensitized by me that menstruation is not a woman issue but a human issue and we should all support our girls during this time of the month. ---</t>
+          <t>Teenage Pregnancy Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners they have which is not healthy. ---</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Referrals and Advocacy</t>
+          <t>Individualized Support and Health Education</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -582,48 +582,48 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Malaria My personal experience about malaria has been very challenging as it affects me periodically and comes unexpectedly. There is a day I fell ill at night while asleep and my symptoms were for malaria because I felt cold with shivering, then developed a high temperature accompanied by severe sweating and headache. In my case, I normally use thermometer to know if am having malaria by checking on my temperature level. If my temperature exceeds 38C or above, then I take painkillers to relief pain, only at night but if I have malaria during the day I go to the hospital. There was a time I had malaria and took Coartem as it is known to reduce malaria faster, then again visited the hospital and it did not reflect that I have malaria as compared to the time when I take painkillers. My advice to people is always to avoid using Coartem without visiting the hospital at first and rather use painkillers to relief pain. After visiting the hospital my eating a bit usually changes, I eat a lot so as to heal faster. In most cases, when I have malaria, it usually comes with migraine, so when I experience such, I take hot strong tea with a lot of sugar, then relax my mind and sleep. When I wake up, I am always free from migraine because I believe my malaria comes with headache followed by migraine. ---</t>
+          <t>Teenage Pregnancy Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners they have which is not healthy. ---</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Community Empowerment Through Education</t>
+          <t>Infectious Disease Prevention</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
         <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Teenage Pregnancy/HIV AIDS Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners, they have which is not healthy. ---</t>
+          <t>Child Nutrition Access to adequate and nutritious food is important for good health. The convention provides for the application of readily available technology for the provision of adequate nutritious food and clear drinking water. Both the state and the parent of the child have to participate in ensuring that children are now nourished nutrition support programs by the government and non-governmental organizations such as the school feeding programs in arid and semi-arid areas plays on essential role nutrition awareness programs that educate parents on how to supplement the staple food with easily available nutrients are also important. As CHW, I am thankful to KUAP, as they offer nutrition programs and teaching to young mothers on how they can handle their little ones. ---</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Referrals and Advocacy</t>
+          <t>Group Based Health Education</t>
         </is>
       </c>
       <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
         <v>1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Malaria People who have malaria usually feel very sick with high fever and shaking chills. However, the introduction malaria vaccine as a preventive measure for the disease has been seen as a huge step in the fight against the disease. Although WHO has approved the vaccine to be used in children in countries with high number of cases, the disease still remains the number one killer of children. According to a client whom I met during our health education session, her experience with malaria was that she lost her appetite after the attack. She further stated that she had alternating body temperature which was at times cold and at times very hot. She noted that the alternating body temperatures were accompanied by high fever, vomiting of yellowish substance, body aches and fatigue. The client observed that she also lost a significant body weight due to her missing meals because of lost appetite. She later went to seek medical attention a few days when the symptoms persisted. Her experience with malaria is not different from mine. I had encounter with malaria a year ago where the symptoms included high body temperature, fatigue, body ache and high fever. As CHWs, we urge people to prevent themselves from malaria by visiting health centers whenever they experience such symptoms. ---</t>
+          <t>CHW Training Having been in Nyalenda for the last five years, health information in the community was not taken seriously. But after the training and we started working in the community giving health information, now they can go to the nearest facility and at the same time we do referrals. In the training, I got more information about COVID-19 even before the government COVID lockdown and how to manage COVID-19. Before training, I could not do first aid. But after the training, I have some skills and now am in a position to perform first aid before I do referrals to the facility. Patient assessment was quite challenging to me. But after being trained by Madam Winnie and Mr. Kituli, I can now do it on my own and know how to handle some of the problems and refer. With the information I have from the training and my knowledge, the community I am in today is changing gradually. They are very eager to be taught more and more about the health issues, because they have been lacking information for so long. But thanks to WiRED International for the training they gave us, because now we are able to give back to the community the information we get, and the community is impressed so much, and they are requesting that we keep on giving them the information that they had lacked for some time. I would like to thank Madam Winnie and Mr. Kituli so much for the training they gave us. It is just on another level. Thanks to Lilian for believing in us and giving us a chance to be trained. Thanks to Mr. Gary for the support you gave us during the training up to now. May God bless you. ---</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Referrals and Advocacy</t>
+          <t>Individualized Support and Health Education</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -631,96 +631,6 @@
       </c>
       <c r="D11" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fibroids In the field I came across this woman who was suffering from fibroids, and she had very low self-esteem because she believed she had cancer and cancers are untreatable. I was touched when she told me she was only awaiting her death. I don’t know much about fibroids, but the little I know about it managed to cheer her up and build up her self-esteem once again. When I assured her that fibroids are non-cancerous growths, she said that the doctor also told her the same, but she could not believe it because doctors love telling people good lies so that they don’t give up in life. But since I also said the same, she promised to start going to treatment and also work on her self-esteem. I will be checking up on her just to lift up her spirits. ---</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Referrals and Advocacy</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Malaria I know about two children who died from malaria (???????). Their parents kept them in the house, buying them drugs over-the-counter which did not go well with them at the time. They were taken to hospital. It was too late for they did not make it. As a CHW in my dealing with malaria, I do clear bushes in my surroundings and also to clear mosquito breeding sites, sleeping under treated mosquito net. Also, I do go for check-ups whenever I experience malaria symptom. As I do all this, I also advise people to do the same. ---</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Referrals and Advocacy</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Malaria Malaria is a serious disease caused by a parasite. When one contracts malaria, he or she feels that the body functions change gradually from being active to being tired or inactive. Malaria has physical symptoms which are fever and chills which are associated with the rupture of erythrocytic-stage schizonts. Malaria also has signs which one can feel, for example headache, muscle or joint pain, general feeling of discomfort and many others. When one feels that he or she has these signs and symptoms, they should seek medical advice immediately. Self-treatment (over-the-counter drug) is only a temporary measure and immediate medical advice or care is important. Yes, malaria can return. You can get malaria more than once even after taking the precautions that were prescribed to a patient. So one still needs to take precautions regularly to try not to get the disease. As a Community Health Worker, I would first create awareness of the disease to the community. In order the members to be aware of the disease, how it affects people, what are the precautions one needs in order not to get the disease, how one can tackle the disease when he or she has it, and many more unanswered questions. As a victim of contracting the disease more than once, the disease can interfere with your body function totally. One can feel weak and constantly vomiting and also having high fevers and many more symptoms I have not mentioned. One can seek medical care at the medical centers when he or she has these signs and symptoms. I mostly use self-treatment (over-the-counter drug) for temporary measure, but in case it is serious and cannot be contained with the over-the-counter drugs, I seek medical attention. Due to the invention of the malaria vaccines which has been approved by the World Health Organization, I know we will have positive impacts toward malaria. ---</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Referrals and Advocacy</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Teenage Pregnancy Teenage pregnancies has really affected many teenagers in the community due to peer pressure and wrong advices they get from their fellow friends. In most cases, the teenagers get pregnant not knowing the status of the people they got involved with. After World AIDS Day celebration on 1st December, I educated the teens on the importance of going for HIV tests with their partners, but some said the partners they have do not buy the idea in most cases because they give excuses of being busy with work or schooling. In such cases, the teens always end up giving in to their demands because at times insisting to go for check-ups always leads to misunderstandings. I solved this by encouraging the teens to go for PREP as it is the only way out to avoid contracting HIV/AIDS since they cannot abstain. I educated the teens how PREP is used by stating that it is only given to individuals who are HIV negative and that before being given PREP a test is always done. PREP is taken by a person who feels they are at high risk of contracting HIV/AIDS, a person with many partners. It does not prevent pregnancies or STD’s and it’s effective only after 7 days of using it. I advised PREP because some teenagers shared with me the numerous partners they have which is not healthy. ---</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Referrals and Advocacy</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Child Nutrition Access to adequate and nutritious food is important for good health. The convention provides for the application of readily available technology for the provision of adequate nutritious food and clear drinking water. Both the state and the parent of the child have to participate in ensuring that children are now nourished nutrition support programs by the government and non-governmental organizations such as the school feeding programs in arid and semi-arid areas plays on essential role nutrition awareness programs that educate parents on how to supplement the staple food with easily available nutrients are also important. As CHW, I am thankful to KUAP, as they offer nutrition programs and teaching to young mothers on how they can handle their little ones. ---</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Community Empowerment Through Education</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -734,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -767,127 +677,169 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Community Empowerment Through Education</t>
+          <t>Group Based Health Education</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>o3</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Community Empowerment Through Education</t>
+          <t>Group Based Health Education</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Referrals and Advocacy</t>
+          <t>Tuberculosis Education and Prevention</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>o3</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Referrals and Advocacy</t>
+          <t>Tuberculosis Education and Prevention</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="D5" t="n">
-        <v>8</v>
-      </c>
       <c r="E5" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training</t>
+          <t>Infectious Disease Prevention</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>o3</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training</t>
+          <t>Infectious Disease Prevention</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Individualized Support and Health Education</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>1</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Individualized Support and Health Education</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>2</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.5</v>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.67</v>
       </c>
     </row>
   </sheetData>
@@ -901,7 +853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -934,127 +886,169 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Community Empowerment Through Education</t>
+          <t>Group Based Health Education</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>o3</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>80</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Community Empowerment Through Education</t>
+          <t>Group Based Health Education</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Referrals and Advocacy</t>
+          <t>Tuberculosis Education and Prevention</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>o3</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Referrals and Advocacy</t>
+          <t>Tuberculosis Education and Prevention</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="D5" t="n">
-        <v>8</v>
-      </c>
       <c r="E5" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training</t>
+          <t>Infectious Disease Prevention</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>o3</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training</t>
+          <t>Infectious Disease Prevention</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>66.67</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Individualized Support and Health Education</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>1</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Individualized Support and Health Education</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>2</v>
       </c>
-      <c r="E7" t="n">
-        <v>50</v>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>66.67</v>
       </c>
     </row>
   </sheetData>
@@ -1107,16 +1101,20 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.0,
-  "Referrals and Advocacy": 0.2,
-  "Community Empowerment Through Education": 0.85,
-  "Handing out Medical Supplies ": 0.05
+  "Group Based Health Education": 0.87,
+  "Individualized Support and Health Education": 0.2,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.0,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial discusses abortion counseling but provides no evidence that the speaker received any CHW training. Therefore, it does not meet the inclusion criteria for the concept. | Referrals and Advocacy: The testimonial mainly describes providing advice against abortion and suggesting that women over 20 \ | Community Empowerment Through Education: The CHW describes talking to a group of young girls about the dangers of abortion and advising on family planning, which is a clear instance of providing health education to a group. This aligns with the concept’s inclusion criteria of group education and health talks. The narrative directly shows knowledge sharing rather than merely performing clinical tasks, warranting a strong but not perfect score. | Handing out Medical Supplies : The testimonial discusses counseling and advising young women about abortion and family planning but gives no indication that the speaker distributed— or directly provided—any physical medical supplies (e.g., contraceptives, medications, equipment). Therefore, alignment with the concept of 'Handing out Medical Supplies' is minimal.</t>
+          <t>[Group Based Health Education] The CHW describes talking "to a group of young girls" about abortion, sharing information and agreeing on actions (family planning, avoiding abortion). This reflects the CHW facilitating a health discussion in a group setting, meeting the inclusion criteria for Group Based Health Education. The account is direct but lacks detailed structure of the session, so scored as strong alignment rather than perfect. [Individualized Support and Health Education] The testimonial describes speaking to a group of young girls about abortion and giving general recommendations (family planning, abstinence). The interaction is primarily group-based and the advice is not clearly tailored to each individual’s specific circumstances, so evidence of individualized support is minimal. [Cholera Education and Prevention] The testimonial discusses abortion, hemorrhage, and family planning without any reference to cholera, water safety, sanitation, or related prevention measures. Therefore it does not align with the Cholera Education and Prevention concept. [Direct Intervention for Cholera Cases] The testimonial discusses abortion-related bleeding and family planning, with no reference to cholera or any direct care actions for cholera cases. [Diabetes Education and Prevention] The testimonial focuses on abortion, hemorrhage, and family planning; it contains no discussion of diabetes, its risk factors, diet, exercise, or blood-sugar monitoring. Therefore, it does not align with the concept of Diabetes Education and Prevention. [HIV/AIDS Education and Prevention] The testimonial discusses abortion dangers, hemorrhage, and family planning; it contains no mention of HIV/AIDS, its transmission, prevention, or testing. Therefore, the concept is not present. [Infectious Disease Prevention] The testimonial discusses abortion, post-abortion hemorrhage, and family planning, which relate to reproductive health rather than preventing communicable diseases. There is no mention of hygiene, sanitation, or other practices aimed at reducing the spread of infectious diseases, so the concept does not apply. [Tuberculosis Education and Prevention] The testimonial discusses abortion, hemorrhage, and family planning, with no mention of tuberculosis symptoms, transmission, or prevention. According to the exclusion criteria, education about other health issues without TB reference does not apply.</t>
         </is>
       </c>
     </row>
@@ -1128,22 +1126,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.0,
-  "Referrals and Advocacy": 0.0,
-  "Community Empowerment Through Education": 0.8,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.8,
+  "Individualized Support and Health Education": 0.2,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.0,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial describes a CHW educating young girls about abortion risks and family planning, but contains no evidence that the CHW received any training. The text only shows the CHW conducting education sessions and counseling, without any mention of having attended training, workshops, or other educational experiences that enhanced their capacity to serve. | Referrals and Advocacy: The testimonial describes health education about abortion risks and a discussion with young girls, but contains no evidence of the CHW making referrals, setting appointments, accompanying anyone to care, or advocating within the health system. While the CHW mentions suggesting family planning for those over 20, this is general advice without any system navigation or connection to services, which the exclusion criteria specifically identifies as not qualifying. | Community Empowerment Through Education: Strong alignment with the concept. The CHW explicitly states 'I talked to a group of young girls' about abortion experiences and its health risks (hemorrhage, anemia, death). This represents direct health education through group discussion. The CHW shared knowledge about abortion dangers and guided them toward safer alternatives (family planning for those over 20). While the testimonial doesn't detail the full educational content, there's clear evidence of active knowledge sharing to improve health practices. | Handing out Medical Supplies : The testimonial focuses entirely on discussing abortion risks and counseling young girls about family planning options. There is no mention of distributing, providing, or handing out any medical supplies, equipment, or materials. The CHW's activities are limited to education and counseling.</t>
+          <t>[Group Based Health Education] Strong direct alignment with the concept. The CHW explicitly states 'I talked to a group of young girls' about abortion and its health risks, which clearly indicates a group education setting. The session involved active facilitation where the CHW discussed the dangers of abortion and the group members shared their experiences. This aligns with the definition of facilitating health education sessions in group settings that allow for collective learning and shared experiences. [Individualized Support and Health Education] The testimonial describes the CHW talking to a group of young girls about abortion, which is group education rather than individualized support. While the CHW engaged with the girls' personal experiences and reached tailored agreements (older girls using family planning, younger ones practicing abstinence), this still represents group-level guidance rather than one-on-one personalized care. The approach shows some adaptation to age groups but lacks the individual-specific tailoring that defines this concept. [Cholera Education and Prevention] The testimonial focuses entirely on abortion-related health education and counseling, with no mention of cholera, water safety, sanitation, or any cholera-related topics. This clearly falls under the exclusion criteria as it is general health education with no reference to cholera. [Direct Intervention for Cholera Cases] The testimonial focuses entirely on abortion-related health education and counseling with young girls. There is no mention of cholera, diarrheal diseases, dehydration, ORS administration, or any cholera-related symptoms or interventions. The content explicitly deals with a different health topic (abortion and family planning), which falls under the exclusion criteria of 'treating unrelated conditions.' [Diabetes Education and Prevention] The testimonial focuses entirely on abortion education and counseling for young women. There is no mention of diabetes, blood sugar, diet, exercise, or any metabolic health topics. The content is explicitly about reproductive health education, which falls under the exclusion criteria of 'health education unrelated to diabetes.' [HIV/AIDS Education and Prevention] The testimonial focuses entirely on abortion-related health education, discussing bleeding risks, anemia, and family planning. There is no mention of HIV/AIDS, transmission, testing, or any HIV-related topics. This clearly falls under the exclusion criteria of 'general health education without a reference to HIV/AIDS.' [Infectious Disease Prevention] The testimonial focuses entirely on abortion complications and reproductive health education, specifically hemorrhage and anemia prevention. There is no mention of communicable diseases, hygiene practices, or disease transmission prevention. The content is about non-communicable health issues (hemorrhage, anemia) and reproductive health counseling, which falls under the exclusion criteria. [Tuberculosis Education and Prevention] The testimonial focuses entirely on abortion-related health education and counseling. There is no mention of tuberculosis, TB symptoms, TB prevention, or any TB-related topics. The content explicitly deals with a different health issue (abortion and family planning), which falls under the exclusion criteria of 'other infectious disease education without mention of TB.'</t>
         </is>
       </c>
     </row>
@@ -1161,16 +1163,20 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.05,
-  "Referrals and Advocacy": 1.0,
-  "Community Empowerment Through Education": 0.5,
-  "Handing out Medical Supplies ": 0.05
+  "Group Based Health Education": 0.05,
+  "Individualized Support and Health Education": 0.85,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.05,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.0,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial describes the CHW recognizing symptoms and making a referral, but it never states that the CHW received any training. Competence alone without mention of training falls under the exclusion criteria, so only minimal, circumstantial alignment exists. | Referrals and Advocacy: The CHW explicitly states that they \ | Community Empowerment Through Education: The CHW recognized wheezing, advised the mother to take the child to the hospital, and implicitly explained the need for medical examination. This is a form of guidance/mobilization for services, which falls under the inclusion criteria. However, there is no detailed description of broader health education or training about asthma, so alignment is only moderate. | Handing out Medical Supplies : The testimonial describes identifying a sick child and referring the caregiver to a hospital; it does not mention distributing any drugs, equipment, or other medical supplies. Thus, there is virtually no evidence of the CHW handing out medical supplies.</t>
+          <t>[Group Based Health Education] The testimonial describes a CHW advising a single mother about her child and referring them to the hospital. There is no mention of a group setting, workshop, or facilitated group discussion, so the evidence for group-based health education is minimal. [Individualized Support and Health Education] The CHW noticed a specific child wheezing, discussed it with the mother, and personally advised that the child be taken to the hospital for evaluation. This is one-on-one, tailored guidance responding to the child’s unique symptoms and the mother’s misunderstanding, matching the concept’s definition and inclusion criteria. It is more than generic advice but not an extensive counseling plan, hence a strong but not perfect score. [Cholera Education and Prevention] The testimonial discusses identification of asthma and referral for treatment, with no mention of cholera, its prevention, or related hygiene education. Therefore, it does not align with the Cholera Education and Prevention concept. [Direct Intervention for Cholera Cases] The testimonial describes identifying and referring a child with asthma (an unrelated condition) and contains no mention of cholera, dehydration management, ORS, or any cholera-specific intervention. According to the concept’s exclusion criteria, treating unrelated conditions does not count toward this concept. [Diabetes Education and Prevention] The testimonial discusses identifying and referring a child with asthma and provides brief education on asthma management. There is no mention of diabetes, its risk factors, diet, exercise, or blood-sugar monitoring, so alignment with diabetes education and prevention is minimal. [HIV/AIDS Education and Prevention] The testimonial discusses identifying and referring a child with asthma and contains no mention of HIV/AIDS information, prevention, testing, or related education. Therefore, the concept is not present. [Infectious Disease Prevention] The testimonial discusses identifying and referring a child with asthma, a non-communicable chronic disease, and emphasizes medication adherence. It does not provide any education or advice about preventing the spread of communicable diseases. Therefore, the concept is not present. [Tuberculosis Education and Prevention] The testimonial discusses asthma identification and referral; there is no mention of TB symptoms, transmission, prevention, or treatment, so the concept does not apply.</t>
         </is>
       </c>
     </row>
@@ -1182,22 +1188,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.4,
-  "Referrals and Advocacy": 0.9,
-  "Community Empowerment Through Education": 0.2,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.0,
+  "Individualized Support and Health Education": 0.7,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.1,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial shows the CHW demonstrating competence in recognizing potential asthma symptoms and making an appropriate referral, but there is no explicit mention of having received CHW training. The phrase 'to me as a CHW' suggests professional knowledge, but this could come from experience rather than formal training. This aligns with the exclusion criteria of 'outcomes or competence without mention of received training,' resulting in a weak alignment score. | Referrals and Advocacy: Strong direct alignment with the concept. The CHW explicitly states 'I referred the ??? to take the child to the hospital' after identifying concerning symptoms. This matches the inclusion criteria of 'assisting with referrals' and the example 'I identified disease symptoms and referred the person for testing' (0.9). The CHW acted as an intermediary by recognizing symptoms beyond what the mother suspected and facilitating access to proper medical care. | Community Empowerment Through Education: The testimonial shows minimal evidence of education or knowledge sharing. While the CHW identified symptoms and advised the mother to seek medical care, there is no clear indication that they explained asthma, its symptoms, or why hospital examination was important. The CHW primarily performed a referral function rather than actively educating. The closing statement about asthma management appears to be the CHW's own reflection rather than information shared with the mother. | Handing out Medical Supplies : The testimonial describes a CHW who identified potential asthma symptoms in a child and referred the family to a hospital for proper medical examination and treatment. There is no mention of the CHW distributing, providing, or handing out any medical supplies. The CHW's role was limited to assessment and referral, with the actual medication being prescribed and provided by the hospital after diagnosis.</t>
+          <t>[Group Based Health Education] This testimonial describes a one-on-one interaction between the CHW and a mother about her child's health condition. The CHW identified symptoms, provided individual guidance, and referred the child to the hospital. There is no mention of any group setting, workshop, or collective education session. This is explicitly excluded by the concept definition which states 'One-on-one education' as an exclusion criterion. [Individualized Support and Health Education] The CHW provided personalized guidance by recognizing concerning symptoms in a specific child, educating the mother about the need for medical examination beyond her assumption of a common cold, and facilitating a referral. While this shows moderate individualized support through one-on-one interaction and tailored advice based on the child's symptoms, it lacks the depth of ongoing personalized care or education seen in higher-scoring examples like developing specific care plans. [Cholera Education and Prevention] The testimonial focuses entirely on identifying and referring a child with asthma symptoms. There is no mention of cholera, cholera prevention, water safety, sanitation, or any cholera-related education. The CHW's actions involved recognizing respiratory symptoms and facilitating medical care for asthma, which is completely unrelated to cholera education and prevention. [Direct Intervention for Cholera Cases] The testimonial describes a CHW intervening in an asthma case, not cholera. The CHW identified symptoms (wheezing, coughing), referred the child to a hospital, and the diagnosis was asthma. This clearly falls under the exclusion criteria as it involves treating an unrelated condition. There is no mention of cholera, diarrhea, dehydration, ORS administration, or any cholera-related symptoms or interventions. [Diabetes Education and Prevention] This testimonial is entirely focused on asthma identification, referral, and management. There is no mention of diabetes, blood sugar, diet, exercise, or any metabolic health topics. The CHW discusses a respiratory condition (asthma) and its treatment, which falls under the exclusion criteria of 'health education unrelated to diabetes.' [HIV/AIDS Education and Prevention] The testimonial focuses entirely on asthma identification, referral, and treatment. There is no mention of HIV/AIDS, HIV prevention, testing, transmission, or any related education. This clearly falls under the exclusion criteria of 'general health education without a reference to HIV/AIDS.' [Infectious Disease Prevention] This testimonial focuses on identifying and referring a child with asthma, which is explicitly a non-communicable chronic disease. While the mother initially suspected a common cold (communicable), the CHW's actions centered on getting proper diagnosis and treatment for asthma rather than providing education about preventing disease transmission. The concept specifically excludes non-communicable disease education, making this a weak alignment. [Tuberculosis Education and Prevention] The testimonial focuses entirely on asthma identification and referral. There is no mention of tuberculosis, TB symptoms, TB prevention, or any TB-related education. While the CHW identified respiratory symptoms (wheezing, coughing), these were correctly associated with asthma, not TB. The concept explicitly excludes other disease education without mention of TB.</t>
         </is>
       </c>
     </row>
@@ -1215,16 +1225,20 @@
       <c r="C6" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.1,
-  "Referrals and Advocacy": 0.9,
-  "Community Empowerment Through Education": 0.8,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.2,
+  "Individualized Support and Health Education": 0.8,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.6,
+  "Tuberculosis Education and Prevention": 1.0
 }</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial describes the CHW providing training to others and referring patients, but there is no explicit statement that the CHW personally received CHW training. Delivering training without evidence of having received it falls under the exclusion criteria, so only minimal alignment is present. | Referrals and Advocacy: The CHW explicitly \ | Community Empowerment Through Education: The CHW explicitly mentions “training” community members and giving advice to coughing individuals to seek tuberculosis testing, indicating active sharing of health knowledge and encouragement of preventive action. This fits the inclusion criteria of providing education and mobilizing for health services. Details are limited, but the presence of training and instruction warrants a strong alignment. | Handing out Medical Supplies : The testimonial discusses identifying coughing individuals, advising them to seek tuberculosis testing, and making referrals, but it contains no mention of distributing or providing any medical supplies (e.g., medications, bed nets, condoms). Therefore, the concept of 'Handing out Medical Supplies' is not present.</t>
+          <t>[Group Based Health Education] The testimonial notes the CHW was “training” people and is now “talking to many,” but the only concrete scenario described involves encountering and advising two individuals. There is no clear description of a structured group session or facilitated group discussion. Therefore, evidence for group-based health education is weak and only minimally present. [Individualized Support and Health Education] The CHW noticed two specific individuals who were coughing during a training session, asked about the onset of their cough, and personally advised each of them to seek a tuberculosis test. This is one-on-one guidance tailored to the individuals’ symptoms, fitting the inclusion criteria for individualized support. Although the testimonial also mentions broader outreach (“talking to many”), the key example revolves around personalized advice, justifying a strong but not perfect score. [Cholera Education and Prevention] The testimonial focuses exclusively on tuberculosis awareness and referrals, with no mention of cholera, its symptoms, prevention, or hygiene practices. According to the concept’s exclusion criteria, general health education not related to cholera should receive a score of 0. [Direct Intervention for Cholera Cases] The testimonial only discusses identifying and referring people for tuberculosis testing; there is no mention of suspected or confirmed cholera cases or related care. According to the exclusion criteria, treating unrelated conditions like TB does not count toward this concept. [Diabetes Education and Prevention] The testimonial focuses exclusively on tuberculosis awareness and referrals for TB testing, with no mention of diabetes, diet, exercise, blood sugar, or metabolic health. Therefore it does not align with the Diabetes Education and Prevention concept. [HIV/AIDS Education and Prevention] The testimonial focuses exclusively on tuberculosis awareness, referral, and testing with no mention of HIV/AIDS, its prevention, or education. Therefore, the HIV/AIDS Education and Prevention concept is not applicable. [Infectious Disease Prevention] The CHW is addressing tuberculosis, an infectious disease, by advising symptomatic individuals to seek testing and thereby limit transmission. This is clearly oriented toward preventing communicable disease spread. However, the activity is focused on a single specific condition (TB) rather than broad, general hygiene or multi-disease prevention, so the alignment with the concept definition is only moderate. [Tuberculosis Education and Prevention] The CHW explicitly discusses recognizing coughing as a possible TB symptom, advises individuals to get a tuberculosis test, and continues to refer others for TB testing—exactly matching the definition and inclusion criteria for TB education and prevention.</t>
         </is>
       </c>
     </row>
@@ -1236,22 +1250,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.2,
-  "Referrals and Advocacy": 0.9,
-  "Community Empowerment Through Education": 0.8,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.8,
+  "Individualized Support and Health Education": 0.7,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.7,
+  "Tuberculosis Education and Prevention": 0.9
 }</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial mentions 'as I was training them,' indicating the CHW was delivering training to others, not receiving it. There is no explicit evidence that the CHW personally received CHW training that enhanced their ability to recognize TB symptoms or make referrals. While the CHW demonstrates competence in identifying potential TB cases and making referrals, this aligns with the exclusion criteria of 'outcomes or competence without mention of received training.' This matches the example 'I conducted a training and later helped a TB patient.' → 0.2 | Referrals and Advocacy: Strong direct alignment with the concept. The CHW explicitly states 'I asked them when they started coughing and advised them to see the doctor for a tuberculosis test' and 'I am now talking to many and also refer them for tuberculosis test.' This demonstrates clear referral activities where the CHW identified symptoms and connected people to testing services. The testimonial shows successful follow-up (one person tested positive and began treatment), which aligns with the inclusion criteria of 'assisting with referrals' and matches the example 'I identified disease symptoms and referred the person for testing' (0.9). | Community Empowerment Through Education: Strong alignment with the concept. The CHW explicitly mentions 'training them' and 'talking to many' about tuberculosis, indicating active knowledge sharing. They educated community members about the importance of getting tested for TB when experiencing persistent coughing, moving beyond just clinical referral to include health education. The score is not higher because the specific content of the training/education is not detailed, but there is clear evidence of the CHW actively sharing health knowledge to empower the community. | Handing out Medical Supplies : The testimonial describes a CHW identifying potential tuberculosis cases and referring people for testing, but contains no mention of distributing or handing out any medical supplies. The CHW's activities are limited to health education, screening, and referrals to medical facilities.</t>
+          <t>[Group Based Health Education] The testimonial describes the CHW 'training them' where 'them' refers to at least two people together, and later mentions 'talking to many,' indicating group interaction. While not explicitly stating a formal health education session, the context of training multiple people simultaneously about health concerns (tuberculosis awareness) aligns strongly with group-based health education activities. [Individualized Support and Health Education] The testimonial shows moderate alignment with individualized support. The CHW identified specific individuals who were coughing during training, asked about their symptoms personally, and provided tailored advice to seek TB testing. This one-on-one interaction led to diagnosis and treatment for at least one person. However, the support is somewhat limited in scope (mainly referral advice) and the testimonial also mentions talking to 'many' people, suggesting a mix of individual and broader community approaches. [Cholera Education and Prevention] The testimonial focuses entirely on tuberculosis education and referral, with no mention of cholera, water safety, sanitation, or cholera-related hygiene practices. While the CHW is conducting health education, it specifically excludes general health education with no reference to cholera, making this a clear non-match. [Direct Intervention for Cholera Cases] The testimonial describes direct intervention for tuberculosis cases, not cholera. The CHW identifies people with coughing symptoms, refers them for TB testing, and follows up on treatment. This falls under the exclusion criteria of 'treating unrelated conditions (e.g., malaria, TB)' and contains no mention of cholera, diarrhea, dehydration, or ORS administration. [Diabetes Education and Prevention] This testimonial is entirely focused on tuberculosis awareness, testing, and referrals. There is no mention of diabetes, metabolic health, diet, exercise, blood sugar, or any diabetes-related education. The CHW is specifically addressing tuberculosis concerns in the community, which falls outside the scope of diabetes education and prevention. [HIV/AIDS Education and Prevention] The testimonial focuses exclusively on tuberculosis awareness, testing, and treatment. There is no mention of HIV/AIDS education, prevention, transmission, or any HIV-related topics. The CHW is educating about TB symptoms and encouraging TB testing, which falls under the exclusion criteria of 'general health education without a reference to HIV/AIDS.' [Infectious Disease Prevention] The testimonial shows strong alignment with infectious disease prevention through the CHW's actions to identify potential TB cases and refer them for testing, which helps prevent transmission. While the focus is specifically on tuberculosis rather than broad disease prevention education, the CHW is actively working to reduce the spread of this communicable disease through early detection and treatment referral. The score is not higher because the testimonial doesn't describe general hygiene education or broad prevention strategies as defined in the concept. [Tuberculosis Education and Prevention] Strong direct alignment with the concept. The CHW explicitly describes advising people with coughs to get tested for tuberculosis, which directly matches the inclusion criteria of 'guidance to get tested.' The testimonial shows the CHW identifying potential TB symptoms (persistent coughing), educating about the need for TB testing, and making referrals. The successful outcome (one person testing positive and beginning treatment) demonstrates effective TB education and prevention work. This aligns closely with the example 'I taught families how to recognize TB symptoms and when to seek help' (0.9).</t>
         </is>
       </c>
     </row>
@@ -1269,16 +1287,20 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.2,
-  "Referrals and Advocacy": 0.9,
-  "Community Empowerment Through Education": 0.85,
-  "Handing out Medical Supplies ": 0.2
+  "Group Based Health Education": 0.8,
+  "Individualized Support and Health Education": 0.85,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.3,
+  "Tuberculosis Education and Prevention": 0.85
 }</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial mentions a \ | Referrals and Advocacy: The CHW explicitly \ | Community Empowerment Through Education: The CHW describes conducting a training session with participants, including allowing time for questions—clear evidence of actively providing health education to a group. This aligns strongly with the concept’s inclusion criteria of workshops or training delivered by CHWs, warranting a high score though not perfect because details of the educational content are limited. | Handing out Medical Supplies : The CHW helped a client re-enter treatment and follows up on drug adherence, but there is no indication that the CHW personally distributed medicines or other medical supplies; they mainly provided referral and support. This shows only a weak, indirect connection to handing out medical supplies.</t>
+          <t>[Group Based Health Education] The CHW describes conducting a "training" with multiple "participants" and mentions having "sessions" with time for questions, indicating a facilitated group health education activity. While details of the session content are limited, the narrative clearly implies a structured group setting, meeting inclusion criteria for Group Based Health Education. Therefore a strong, though not perfect, alignment (0.8) is appropriate. [Individualized Support and Health Education] The CHW responds to an individual participant’s disclosure of TB defaulting, arranges a tailored referral to a preferred facility, and provides close follow-up to ensure medication adherence. This is one-on-one, personalized support adapted to the person’s unique situation, fitting the inclusion criteria. While explicit health education is not detailed, the individualized referral and monitoring justify a strong alignment, though not a perfect score. [Cholera Education and Prevention] The testimonial discusses assisting a client with tuberculosis treatment adherence and referral. There is no mention of cholera, water safety, sanitation, or related education. Thus the concept is not present. [Direct Intervention for Cholera Cases] The testimonial describes helping a participant resume tuberculosis treatment through referral and follow-up. Cholera is never mentioned, and the action pertains to TB care, which is explicitly excluded from the concept. [Diabetes Education and Prevention] The testimonial describes a CHW assisting a client with tuberculosis treatment and follow-up. There is no mention of diabetes, its risk factors, prevention, or related education, so the concept does not apply. [HIV/AIDS Education and Prevention] The testimonial discusses helping a client restart tuberculosis treatment and arranging a referral. There is no mention of HIV/AIDS education, prevention, testing, or related topics, so the concept does not apply. [Infectious Disease Prevention] The CHW helps a client with tuberculosis re-initiate treatment and follows up on medication adherence. While completing TB treatment indirectly prevents further transmission, the testimonial does not mention providing hygiene, cough etiquette, or other preventive education aimed at a broader audience. Therefore the alignment with the general infectious-disease-prevention concept is weak. [Tuberculosis Education and Prevention] The CHW discusses a case where she refers a person who defaulted on TB medication to another facility and performs close follow-up to ensure he takes his drugs. This constitutes guidance on treatment adherence and facilitation of care for TB, fitting the concept's inclusion criteria. While explicit symptom education is not described, the testimonial strongly aligns with TB treatment adherence support.</t>
         </is>
       </c>
     </row>
@@ -1290,22 +1312,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.2,
-  "Referrals and Advocacy": 0.9,
-  "Community Empowerment Through Education": 0.8,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.8,
+  "Individualized Support and Health Education": 0.9,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.2,
+  "Tuberculosis Education and Prevention": 0.4
 }</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial mentions conducting 'a training' and completing 'my training,' but the context suggests the CHW was delivering training to participants, not receiving it. There is no explicit evidence that the CHW personally received CHW training that enhanced their capacity. The referral action described could have been done without formal CHW training. This aligns with the example 'I conducted a training and later helped a TB patient.' → 0.2 | Referrals and Advocacy: Strong direct alignment with the concept. The CHW explicitly states 'I managed to refer him to KNAP' after a participant requested help getting back on TB medication. The testimonial also mentions ongoing follow-up ('I am doing close follow-up on him to make sure he has taken his drugs'), demonstrating continued navigation support. This closely matches the example 'I identified disease symptoms and referred the person for testing' (0.9), though in this case it was re-referral for treatment continuation rather than initial diagnosis. | Community Empowerment Through Education: Strong alignment with the concept. The CHW conducted a training session with participants, which directly demonstrates providing health education to a group. While the specific content of the training isn't detailed, the testimonial clearly states 'my fieldwork engagement with my participants in a training' and 'I had completed my training,' showing active knowledge sharing. The subsequent one-on-one interaction where the CHW helped the participant understand how to get back on TB medication also involves educational guidance, though the focus shifts more toward referral and follow-up support. | Handing out Medical Supplies : The testimonial describes a CHW referring a tuberculosis patient to get back on medication and providing follow-up support, but there is no mention of the CHW directly distributing or handing out any medical supplies. The CHW facilitated access to medication through referral to KNAP rather than personally providing supplies.</t>
+          <t>[Group Based Health Education] The testimonial clearly mentions 'my participants in a training' and 'I had completed my training' with multiple participants present, indicating a group education session. The CHW was conducting a training session where questions were allowed 'during the sessions,' which aligns strongly with the concept of group-based health education. While the focus shifts to a one-on-one interaction afterward, the core activity was a group training session. [Individualized Support and Health Education] Strong direct alignment. The CHW provided personalized support to an individual participant who approached them privately about their tuberculosis treatment default. The CHW tailored their response to the person's specific situation (not wanting to return to the previous hospital), provided a customized referral to KNAP, and continues to provide individualized follow-up care to ensure medication adherence. This represents one-on-one support adapted to the person's unique medical and personal circumstances. [Cholera Education and Prevention] The testimonial focuses entirely on tuberculosis case management and medication adherence support. There is no mention of cholera education, prevention strategies, or any cholera-related activities. The CHW is providing referral services and follow-up for TB treatment, which is completely unrelated to the concept of cholera education and prevention. [Direct Intervention for Cholera Cases] This testimonial describes a CHW's intervention for a tuberculosis patient, not cholera. The CHW helped refer a TB patient who had defaulted on medication to get back on treatment. This clearly falls under the exclusion criteria of 'treating unrelated conditions (e.g., malaria, TB)' and contains no mention of cholera, ORS administration, or cholera-related symptoms. [Diabetes Education and Prevention] The testimonial is entirely focused on tuberculosis case management and medication adherence support. There is no mention of diabetes education, prevention, diet, exercise, blood sugar monitoring, or any metabolic health topics. The CHW's work involves TB patient support and referral, which is completely unrelated to diabetes education and prevention. [HIV/AIDS Education and Prevention] The testimonial focuses entirely on tuberculosis diagnosis, treatment defaulting, and referral for TB medication. There is no mention of HIV/AIDS education, prevention, testing, or any HIV-related topics. The CHW's work involves TB treatment adherence support, which falls outside the scope of HIV/AIDS education and prevention. [Infectious Disease Prevention] This testimonial focuses on helping an individual with tuberculosis treatment adherence and referral, not on providing education or advice about preventing disease transmission. While TB is an infectious disease, the CHW's actions were therapeutic support and care coordination rather than prevention education. The concept specifically requires education about preventing spread of diseases, which is not present in this case. [Tuberculosis Education and Prevention] While this testimonial involves a TB patient and the CHW providing follow-up support for medication adherence, there is no explicit mention of the CHW providing education about TB symptoms, transmission, or prevention. The CHW's role appears to be primarily referral and medication adherence support rather than educational activities as defined in the concept.</t>
         </is>
       </c>
     </row>
@@ -1323,16 +1349,20 @@
       <c r="C10" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.9,
-  "Referrals and Advocacy": 0.2,
-  "Community Empowerment Through Education": 0.95,
-  "Handing out Medical Supplies ": 0.1
+  "Group Based Health Education": 0.2,
+  "Individualized Support and Health Education": 0.1,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.9,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial states, “Having trained as a Community Health Worker, I have been actively sensitizing…,” explicitly indicating the CHW personally received CHW training and that this training enabled them to educate the community about COVID-19 prevention. This directly matches the inclusion criteria of a structured educational experience that improves service delivery, meriting a strong score. | Referrals and Advocacy: The CHW describes sensitizing community members about COVID-19 prevention—general health education. There is no mention of arranging referrals, setting appointments, accompanying clients, or navigating the health system. This aligns only weakly (similar to the example of giving advice without referral), so a low score is assigned. | Community Empowerment Through Education: The CHW explicitly describes actively sensitizing, creating awareness, training, and emphasizing preventive COVID-19 measures (mask wearing, handwashing, sanitizing, social distancing). Community members adopted these teachings. This is a clear, direct instance of providing health education to empower the community, matching the concept’s definition and inclusion criteria almost perfectly. | Handing out Medical Supplies : The testimonial focuses on educating community members about COVID-19 prevention (mask wearing, hand-washing, social distancing). It does not mention actually distributing masks, sanitizer, medicine, or any other medical supplies. Because masks are only discussed as recommendations rather than items the CHW physically handed out, evidence for the concept is very weak.</t>
+          <t>[Group Based Health Education] The CHW states they are "sensitizing and creating awareness" among community members about COVID-19 prevention, but no explicit description of facilitating a group session, workshop, or health talk is given. The narrative could refer to individual or informal interactions, which falls under the exclusion criteria of general education without clear group setting. Therefore only weak evidence for Group Based Health Education is present. [Individualized Support and Health Education] The testimonial describes broad community sensitization about COVID-19 precautions (masking, hand-washing, distancing) delivered to community members in general. There is no mention of tailoring advice or support to a specific individual or household, so it falls under the exclusion criteria of generic group education. Only minimal, indirect evidence of individualized support is present. [Cholera Education and Prevention] The testimonial describes education on COVID-19 prevention (mask wearing, handwashing, social distancing) with no mention of cholera, its symptoms, or cholera-specific prevention. According to the exclusion criteria, general health education that does not reference cholera should receive a score of 0. [Direct Intervention for Cholera Cases] The testimonial focuses on COVID-19 preventive education (mask wearing, hand-washing, social distancing) and does not mention cholera cases or any direct care for cholera patients. According to the concept definition and exclusion criteria, preventive education unrelated to cholera does not qualify. [Diabetes Education and Prevention] The testimonial focuses exclusively on COVID-19 prevention measures (mask wearing, hand-washing, social distancing). There is no mention of diabetes, its risk factors, diet, exercise, or blood-sugar monitoring. Health education unrelated to diabetes is explicitly excluded from the concept. [HIV/AIDS Education and Prevention] The testimonial discusses sensitization and preventive measures for COVID-19 (masking, handwashing, distancing). There is no mention of HIV/AIDS, testing, transmission, or stigma reduction. General health education without HIV reference is excluded in the concept definition. [Infectious Disease Prevention] The CHW describes actively educating the community on masks, hand-washing, sanitizing and social distancing to stop COVID-19 transmission—classic communicable-disease prevention behaviors. This directly matches the concept’s inclusion of hygiene and sanitation advice to prevent spread of infectious illnesses, so alignment is strong and unambiguous. [Tuberculosis Education and Prevention] The testimonial discusses educating the community about COVID-19 prevention (mask usage, handwashing, distancing) without any mention of tuberculosis symptoms, transmission, or treatment. According to the exclusion criteria, education about other infectious diseases without TB reference does not count toward this concept.</t>
         </is>
       </c>
     </row>
@@ -1344,22 +1374,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.9,
-  "Referrals and Advocacy": 0.0,
-  "Community Empowerment Through Education": 0.9,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.3,
+  "Individualized Support and Health Education": 0.1,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.9,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial contains an explicit statement 'Having trained as a Community Health Worker' which directly indicates the CHW received CHW training. The CHW then describes using this training to sensitize and educate community members about COVID-19 prevention measures, demonstrating enhanced capacity to serve. This aligns strongly with the concept definition and mirrors the example 'After CHW training, I began teaching others about disease prevention' which scored 0.9. | Referrals and Advocacy: The testimonial focuses entirely on COVID-19 prevention education and awareness activities. While the CHW mentions training community members on preventive measures (masks, handwashing, social distancing), there is no mention of referring anyone for testing, treatment, or other services. The CHW does not describe helping anyone navigate the healthcare system, set appointments, or advocate on behalf of community members. This is purely health education without system navigation components. | Community Empowerment Through Education: Strong direct alignment. The CHW explicitly states they have been 'actively sensitizing and creating awareness' about COVID-19 preventive measures, 'emphasizing' specific practices (masks, handwashing, sanitizing, social distancing), and that community members 'have embraced and also adopted the teachings.' The testimonial clearly shows knowledge transfer resulting in behavior change, with the CHW noting the community is 'doing what I have trained them to do.' This matches the concept's definition of providing health education to help community members gain knowledge to improve health practices. | Handing out Medical Supplies : The testimonial focuses entirely on COVID-19 education, awareness, and preventive behaviors (mask-wearing, handwashing, sanitizing, social distancing). The CHW explicitly states they have been 'sensitizing and creating awareness' and 'training' community members. There is no mention of distributing, handing out, or providing any physical medical supplies to the community.</t>
+          <t>[Group Based Health Education] The CHW describes 'actively sensitizing and creating awareness to my community members' about COVID-19 prevention, but does not explicitly mention conducting group sessions, workshops, or structured group education. The testimonial uses general language about educating 'community members' and 'people' without clear evidence of group settings. While the community-wide impact suggests possible group activities, the lack of specific mentions of group gatherings (especially given COVID-19 restrictions on 'large gatherings') makes this a weak alignment with the concept. [Individualized Support and Health Education] The testimonial describes community-wide COVID-19 education and sensitization efforts, not individualized support. The CHW is 'actively sensitizing and creating awareness to my community members' and notes that 'members of the community have embraced' the teachings - indicating group-level education. While the work is valuable, it represents general health education delivered to the entire community rather than personalized guidance adapted to individual needs, which aligns with the exclusion criteria. [Cholera Education and Prevention] The testimonial focuses entirely on COVID-19 education and prevention activities (mask-wearing, handwashing, sanitizing, social distancing). While it mentions hygiene practices like handwashing that could also prevent cholera, there is no reference to cholera, waterborne diseases, or cholera-specific prevention strategies. This falls under the exclusion criteria of 'general health education with no reference to cholera.' [Direct Intervention for Cholera Cases] The testimonial focuses entirely on COVID-19 prevention and awareness activities, with no mention of cholera, diarrheal diseases, ORS administration, or any cholera-related interventions. The CHW describes preventive education about COVID-19 (masks, handwashing, social distancing) which falls under the exclusion criteria as it is preventive education without mention of cholera cases. [Diabetes Education and Prevention] The testimonial focuses entirely on COVID-19 prevention education (masks, handwashing, sanitizing, social distancing) with no mention of diabetes, metabolic health, diet, exercise, or blood sugar management. This clearly falls under the exclusion criteria of 'health education unrelated to diabetes.' [HIV/AIDS Education and Prevention] The testimonial focuses exclusively on COVID-19 education and prevention activities, including mask-wearing, handwashing, sanitizing, and social distancing. There is no mention of HIV/AIDS education, prevention, testing, or any related activities. This clearly falls under the exclusion criteria as it represents general health education without any reference to HIV/AIDS. [Infectious Disease Prevention] This testimonial demonstrates strong direct alignment with infectious disease prevention. The CHW describes actively educating community members on COVID-19 preventive measures including mask-wearing, handwashing with soap and water, sanitizing, and social distancing. These are classic examples of general hygiene education and practices to prevent disease transmission. The impact is evident as the community has adopted these practices and reported zero COVID-19 cases. The score is 0.9 rather than 1.0 because while the focus is on COVID-19 prevention, it represents broad communicable disease prevention strategies rather than being overly specific to one condition. [Tuberculosis Education and Prevention] The testimonial focuses exclusively on COVID-19 education and prevention measures (masks, handwashing, sanitizing, social distancing). There is no mention of tuberculosis, TB symptoms, TB transmission, or any TB-related education. This falls under the exclusion criteria of 'other infectious disease education without mention of TB.'</t>
         </is>
       </c>
     </row>
@@ -1377,16 +1411,20 @@
       <c r="C12" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.0,
-  "Referrals and Advocacy": 0.5,
-  "Community Empowerment Through Education": 0.88,
-  "Handing out Medical Supplies ": 0.05
+  "Group Based Health Education": 0.3,
+  "Individualized Support and Health Education": 0.1,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.75,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial describes the CHW providing training to community members on COVID-19 measures but gives no indication that the CHW themselves received any training. Delivering training without evidence of having received training is explicitly excluded by the concept definition. | Referrals and Advocacy: The CHW reports \ | Community Empowerment Through Education: The CHW states they have been \ | Handing out Medical Supplies : The testimonial describes providing education and mobilizing people to be vaccinated, but does not mention the CHW physically distributing vaccines, masks, or any other medical supplies. Therefore, there is only very minimal, indirect relevance to handing out supplies.</t>
+          <t>[Group Based Health Education] The CHW states they have been "training the community members" on COVID-19 precautions, implying some educational activity, but there is no clear indication that this was done in organized group sessions. Because evidence of an actual facilitated group setting is weak and only inferred, the alignment is low (general community education without explicit group context). Hence a score of 0.3. [Individualized Support and Health Education] The testimonial describes general training and mobilization of community members about COVID-19 precautions and vaccination. It does not mention tailoring advice or support to a specific individual or household, so it lacks the personalized element required by the concept. [Cholera Education and Prevention] The testimonial focuses exclusively on COVID-19 preventive measures and vaccination, with no mention of cholera, its symptoms, transmission, or specific prevention strategies. According to the concept’s exclusion criteria, general health education unrelated to cholera does not qualify. [Direct Intervention for Cholera Cases] The testimonial discusses COVID-19 prevention education and vaccination mobilization, with no mention of cholera patients, dehydration assessment, ORS, or cholera-related referrals. This falls under the exclusion criteria of preventive education unrelated to cholera, so the concept is not present. [Diabetes Education and Prevention] The testimonial focuses entirely on COVID-19 prevention and vaccination messaging with no mention of diabetes, diet, exercise, or metabolic health. According to the concept’s exclusion criteria, health education unrelated to diabetes should receive a score of 0. [HIV/AIDS Education and Prevention] The testimonial exclusively discusses COVID-19 precautions and vaccination with no mention of HIV/AIDS transmission, prevention, testing, or related topics. Therefore the concept is not present. [Infectious Disease Prevention] The CHW describes educating community members about hand-washing, mask use, social distancing and avoiding crowds—classic hygiene and isolation measures aimed at limiting the spread of a communicable disease. This aligns with the concept’s inclusion criteria (general hygiene education, advice on preventing transmission). Because the advice is framed specifically around COVID-19 rather than generic disease prevention, the match is strong but not perfect, warranting a score in the upper-moderate range. [Tuberculosis Education and Prevention] The testimonial only discusses COVID-19 prevention measures and vaccination. Tuberculosis is not mentioned, so the concept is not applicable according to the exclusion criteria (education about other infectious diseases without TB reference).</t>
         </is>
       </c>
     </row>
@@ -1398,22 +1436,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.0,
-  "Referrals and Advocacy": 0.2,
-  "Community Empowerment Through Education": 0.8,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.0,
+  "Individualized Support and Health Education": 0.1,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.9,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial shows the CHW conducting training and educating community members about COVID-19 measures, but contains no evidence that the CHW personally received any training. The CHW states 'I have been emphasizing on training the community members' which indicates they are delivering training, not receiving it. This falls under the exclusion criteria of 'Delivering training to others without evidence of having received CHW training.' | Referrals and Advocacy: The testimonial shows minimal alignment with referrals and advocacy. While the CHW mentions 'mobilizing these who have not been vaccinated to go for vaccinations,' this is similar to the example 'I told people they should consider family planning' (0.2). The CHW is encouraging vaccination but there's no evidence of direct system navigation, setting appointments, accompanying patients, or making specific referrals to healthcare facilities. | Community Empowerment Through Education: The testimonial shows strong evidence of education activities. The CHW explicitly states 'I have been emphasizing on training the community members on how to continue practicing the COVID-19 measures' and mentions 'mobilizing these who have not been vaccinated to go for vaccinations.' This demonstrates active knowledge sharing through training and mobilization efforts, which aligns well with the concept definition and inclusion criteria. | Handing out Medical Supplies : The testimonial describes COVID-19 education, training community members on preventive measures, and mobilizing people for vaccinations. There is no mention of distributing, handing out, or providing any physical medical supplies to community members. The CHW's activities are focused on education and mobilization rather than supply distribution.</t>
+          <t>[Group Based Health Education] The testimonial mentions 'training the community members' but provides no evidence of group-based sessions. The CHW describes emphasizing training and mobilizing people for vaccinations, but these activities could be conducted through individual interactions, mass media, or other non-group methods. Without specific mention of workshops, group sessions, or collective gatherings for education, this does not meet the inclusion criteria for Group Based Health Education. [Individualized Support and Health Education] The testimonial describes general community-wide health education about COVID-19 prevention measures and vaccine mobilization. The CHW mentions 'training the community members' and emphasizing preventive measures to the broader population, not providing personalized guidance adapted to individual needs. This aligns with the exclusion criteria of 'general health education' and 'community-wide support' that is not clearly personalized. [Cholera Education and Prevention] The testimonial exclusively discusses COVID-19 education and prevention activities. The CHW describes educating community members about COVID-19 preventive measures (handwashing, masks, social distancing) and vaccine mobilization. There is no mention of cholera, cholera symptoms, or cholera-specific prevention strategies. While handwashing is mentioned, it's clearly in the context of COVID-19 prevention, not cholera. Per the exclusion criteria, general health education with no reference to cholera does not qualify. [Direct Intervention for Cholera Cases] The testimonial exclusively discusses COVID-19 prevention measures, vaccination efforts, and the Omicron variant. There is no mention of cholera, cholera symptoms, ORS administration, or any cholera-related interventions. The CHW's activities focus on COVID-19 education and vaccine mobilization, which falls under the exclusion criteria as it involves treating/preventing an unrelated condition. [Diabetes Education and Prevention] The testimonial exclusively focuses on COVID-19 education, prevention measures, and vaccination efforts. There is no mention of diabetes, metabolic health, diet, exercise for diabetes prevention, or any content related to the concept definition. This clearly falls under the exclusion criteria of 'health education unrelated to diabetes.' [HIV/AIDS Education and Prevention] The testimonial focuses entirely on COVID-19 education and prevention, including vaccination, hand washing, mask wearing, and social distancing. There is no mention of HIV/AIDS, HIV transmission, testing, or any HIV-related topics. This clearly falls under the exclusion criteria of 'general health education without a reference to HIV/AIDS.' [Infectious Disease Prevention] Strong direct alignment with the concept. The CHW explicitly describes training community members on COVID-19 prevention measures including handwashing, mask-wearing, avoiding crowds, and social distancing - all classic examples of infectious disease prevention education. While focused on COVID-19, the testimonial emphasizes general transmission prevention practices rather than disease-specific treatment, aligning with the concept's inclusion criteria for 'advice on preventing transmission of illnesses.' [Tuberculosis Education and Prevention] The testimonial exclusively discusses COVID-19 education and prevention measures, including vaccination, hand washing, mask wearing, and social distancing. There is no mention of tuberculosis, TB symptoms, TB transmission, or any TB-related education activities. This falls under the exclusion criteria as it represents 'other infectious disease education without mention of TB.'</t>
         </is>
       </c>
     </row>
@@ -1431,16 +1473,20 @@
       <c r="C14" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.2,
-  "Referrals and Advocacy": 0.5,
-  "Community Empowerment Through Education": 0.65,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.2,
+  "Individualized Support and Health Education": 0.2,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.4,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The speaker notes that after becoming a CHW they realized self-medicating for malaria was not advisable, implying some increase in knowledge, but there is no explicit statement that they attended or received CHW training. Because training is only implied and not clearly documented, alignment with the concept is weak. | Referrals and Advocacy: The CHW states they will \ | Community Empowerment Through Education: The CHW states that they 'advise [people] to go to the hospital and get tested' and to seek proper treatment when malaria symptoms occur. This indicates active sharing of health guidance aimed at improving community practices, fitting the education/empowerment concept. However, details about actual educational encounters or methods are sparse, so alignment is moderate rather than strong. | Handing out Medical Supplies : The testimonial discusses advising people to seek testing and treatment for malaria but does not mention distributing drugs, bed nets, or any other medical supplies. Therefore, the concept of handing out medical supplies is not present.</t>
+          <t>[Group Based Health Education] The testimonial only states that, as a CHW, the speaker will advise people with malaria to seek testing and treatment. There is no indication that this advising occurs in a group session, workshop, or other facilitated group setting. According to the concept definition, general advising without evidence of a group context is excluded, so alignment is weak. [Individualized Support and Health Education] The CHW describes giving advice about seeking testing and treatment for malaria, but the advice is presented in a general way (“advise them to go to the hospital and get tested”) without evidence that it is tailored to a specific individual’s circumstances. This is more generic health education than personalized support, so alignment with the concept is weak. [Cholera Education and Prevention] The testimonial discusses malaria symptoms, treatment practices, and prevention (mosquito nets), with no mention of cholera, sanitation, water safety, or related education. According to the exclusion criteria, general health or non-cholera topics do not count toward this concept. [Direct Intervention for Cholera Cases] The testimonial discusses malaria experiences and advice for malaria treatment, with no mention of cholera cases or any direct care actions related to cholera. Therefore, it does not align with the concept. [Diabetes Education and Prevention] The testimonial focuses exclusively on malaria symptoms, treatment practices, and prevention (e.g., mosquito nets). There is no mention of diabetes, its risk factors, diet, exercise, or blood-sugar management. Therefore the concept is not present. [HIV/AIDS Education and Prevention] The testimonial focuses solely on malaria symptoms, treatment, and prevention with no mention of HIV/AIDS education, prevention, testing, or related topics. Therefore, it falls under the exclusion criteria of general health education without reference to HIV/AIDS. [Infectious Disease Prevention] The speaker gives advice to sleep under a mosquito-treated net and to seek testing/treatment for malaria, which are prevention actions for a communicable disease. However, the guidance is focused on one specific condition (malaria) rather than general hygiene or broad infection-control practices, which only weakly matches the concept’s definition that emphasizes non-disease-specific prevention. Hence a low–moderate score is assigned. [Tuberculosis Education and Prevention] The testimonial focuses solely on malaria education and prevention with no mention of tuberculosis symptoms, transmission, or treatment; TB is explicitly absent, so the concept does not apply.</t>
         </is>
       </c>
     </row>
@@ -1452,22 +1498,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.7,
-  "Referrals and Advocacy": 0.5,
-  "Community Empowerment Through Education": 0.3,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.0,
+  "Individualized Support and Health Education": 0.2,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.3,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial shows moderate alignment with the concept. The CHW explicitly states 'after becoming a CHW' they realized their previous self-medication practices were not good, indicating they received CHW training that changed their understanding of proper malaria treatment. This aligns with the definition of training increasing their capacity to serve through enhanced ability to recognize conditions and educate others. However, the testimonial lacks explicit mention of attending specific training sessions, courses, or structured educational experiences, which prevents a higher score. | Referrals and Advocacy: The testimonial shows moderate alignment with the concept. The CHW explicitly states they 'advise them to go to the hospital and get tested,' which is similar to the 0.5-scored example 'I encouraged someone to go to the clinic.' However, there's no mention of actively assisting with referrals, setting appointments, accompanying patients, or advocating on their behalf - just general advice to seek care. | Community Empowerment Through Education: The testimonial shows weak alignment with the concept. While the CHW mentions advising people to go to the hospital and get tested when malaria symptoms occur, this represents minimal educational activity. The majority of the testimonial focuses on the CHW's personal experience with malaria and their own learning journey. There is no evidence of active knowledge sharing through explanation, instruction, or demonstration about malaria prevention or treatment beyond basic advice to seek medical care. | Handing out Medical Supplies : The testimonial does not mention the CHW distributing, providing, or handing out any medical supplies. The CHW only mentions advising people to go to the hospital for testing and treatment. The testimonial focuses on personal malaria experience and the CHW's role in providing advice, not distributing supplies.</t>
+          <t>[Group Based Health Education] The testimonial describes personal experiences with malaria and mentions advising people to seek hospital care, but contains no evidence of group-based health education activities. The CHW only mentions individual advice-giving ('advise them to go to the hospital'), which aligns with one-on-one education rather than group sessions. There is no mention of workshops, group talks, or collective learning settings. [Individualized Support and Health Education] The testimonial primarily describes personal malaria experiences and generic advice to 'go to the hospital and get tested.' The CHW mentions what they 'can do to help people' but only offers general recommendations without evidence of tailoring support to individual needs or circumstances. This aligns with the exclusion criteria of 'general health education' and 'advice that is generic or not clearly personalized.' [Cholera Education and Prevention] The testimonial focuses entirely on malaria - its symptoms, personal experience with the disease, and advice about proper testing and treatment. There is no mention of cholera, cholera prevention, water sanitation, or any cholera-related education activities. While the CHW mentions advising people to seek proper medical care, this is specifically about malaria, not cholera. [Direct Intervention for Cholera Cases] The testimonial exclusively discusses malaria experiences and interventions, with no mention of cholera, cholera symptoms, or cholera-related care. While diarrhea is mentioned as a malaria symptom, there is no connection to cholera cases or cholera-specific interventions like ORS administration for cholera patients. This clearly falls under the exclusion criteria of 'treating unrelated conditions.' [Diabetes Education and Prevention] This testimonial is entirely focused on malaria experiences, symptoms, and treatment. There is no mention of diabetes, blood sugar, diet, exercise, or any metabolic health topics. The content explicitly falls under the exclusion criteria as it is 'health education unrelated to diabetes.' [HIV/AIDS Education and Prevention] The testimonial focuses entirely on malaria - its symptoms, treatment, and prevention. There is no mention of HIV/AIDS, HIV transmission, testing, or any related education activities. The CHW discusses educating people about malaria testing and treatment, which falls under general health education but does not reference HIV/AIDS at all. [Infectious Disease Prevention] The testimonial shows weak alignment with infectious disease prevention. While the CHW mentions advising people to 'go to the hospital and get tested' for malaria, this is more about treatment-seeking than prevention education. The testimonial focuses primarily on personal malaria experience and treatment mistakes rather than providing education on preventing disease transmission. The mention of 'not sleeping under mosquito treated net' suggests awareness of prevention methods, but there's no evidence of actively educating others about malaria prevention or general infectious disease prevention practices. [Tuberculosis Education and Prevention] The testimonial focuses entirely on malaria - its symptoms, personal experience with the disease, and advice about malaria testing and treatment. There is no mention of tuberculosis, TB symptoms, TB prevention, or any TB-related education. The content explicitly deals with a different infectious disease (malaria) without any connection to TB.</t>
         </is>
       </c>
     </row>
@@ -1485,16 +1535,20 @@
       <c r="C16" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.0,
-  "Referrals and Advocacy": 0.95,
-  "Community Empowerment Through Education": 0.6,
-  "Handing out Medical Supplies ": 0.05
+  "Group Based Health Education": 0.05,
+  "Individualized Support and Health Education": 0.2,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.3,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial describes the CHW’s knowledge and actions regarding malaria, but never states that the CHW attended, completed, or received any CHW training. Competence alone, without mention of received training, is specifically excluded by the concept definition. | Referrals and Advocacy: The testimonial explicitly states, “if you once identify someone suffering from malaria, I immediately refer to the nearest health center,” which is a clear, unambiguous example of a CHW providing a referral. This directly matches the concept’s inclusion criteria of assisting with referrals, indicating strong alignment. | Community Empowerment Through Education: The testimonial provides explanatory information about malaria—its cause, symptoms, first-aid steps, and preventive measures—using instructional language such as “This are the first aid you do before going to the hospital” and “preventive measures like sleeping under the treated mosquito nets.” This suggests the CHW is conveying health education. However, the text does not explicitly state that these instructions were delivered to community members in a structured session, so the evidence is moderate rather than unequivocal. | Handing out Medical Supplies : The testimonial focuses on recognizing malaria symptoms, giving advice on first-aid measures (sponging, encouraging water intake), and referring patients to a health center. It does not describe the CHW distributing medications, bed nets, or any other medical commodities to clients, so there is virtually no evidence of ‘handing out medical supplies.’</t>
+          <t>[Group Based Health Education] The testimonial provides information about malaria and the CHW’s individual actions, but it does not mention facilitating or conducting a health education session with a group. Therefore, there is virtually no evidence of Group Based Health Education. [Individualized Support and Health Education] The testimonial provides generic information about malaria symptoms, first aid, and referral procedures. It does not describe any specific, tailored guidance given to a particular individual or household. The mention of referring ‘someone’ with symptoms remains general and lacks detail showing personalization, placing it in the weak alignment range. [Cholera Education and Prevention] The testimonial focuses entirely on malaria education, symptoms, and first aid; cholera is never mentioned. According to the concept definition and exclusion criteria, general health education that does not reference cholera receives a score of 0.0. [Direct Intervention for Cholera Cases] The testimonial solely discusses identification and first aid for malaria, which is explicitly excluded from the concept. No cholera cases or cholera-specific actions are mentioned. [Diabetes Education and Prevention] The testimonial focuses entirely on malaria—its symptoms, first aid, referral, and mosquito net prevention—and contains no discussion of diabetes, its risk factors, or related health education. Therefore the concept is not present. [HIV/AIDS Education and Prevention] The testimonial exclusively discusses malaria—its symptoms, transmission via mosquitoes, first aid, and prevention measures. There is no mention of HIV/AIDS, testing, condom use, or related education, so the concept does not apply. [Infectious Disease Prevention] The CHW discusses ways to prevent malaria transmission (treated mosquito nets, vector control). While malaria is a communicable disease, the concept definition emphasizes broad, non-disease-specific hygiene or sanitation advice. Because the testimonial focuses on one specific disease rather than general infectious-disease prevention, alignment is weak but present to a small extent. [Tuberculosis Education and Prevention] The testimonial focuses exclusively on malaria—its symptoms, prevention, and management—and does not mention tuberculosis or provide any TB-related education or guidance, so the concept is not present.</t>
         </is>
       </c>
     </row>
@@ -1506,22 +1560,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.2,
-  "Referrals and Advocacy": 0.8,
-  "Community Empowerment Through Education": 0.0,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.0,
+  "Individualized Support and Health Education": 0.2,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.2,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial demonstrates CHW knowledge and competence in recognizing malaria symptoms and providing first aid, but contains no explicit mention of receiving CHW training. While the detailed understanding suggests some educational background, the concept requires clear evidence of 'attended, completed, or received CHW training.' The knowledge displayed could have been acquired through experience or other means, making this a weak alignment with the concept. | Referrals and Advocacy: The testimonial contains a clear statement of referral action: 'As a Community Health Worker, if you once identify someone suffering from malaria, I immediately refer to the nearest health center.' This directly aligns with the concept's inclusion criteria of 'assisting with referrals.' The score is 0.8 rather than higher because while the referral action is explicitly stated, there's no mention of additional advocacy activities like accompanying patients or navigating the health system beyond the referral itself. | Community Empowerment Through Education: The testimonial describes the CHW's knowledge about malaria (causes, symptoms, first aid measures) but provides no evidence that this knowledge was shared with community members. The CHW only describes what they know and what actions they take, without mentioning any teaching, explaining, or educating activities. This aligns with the exclusion criteria: 'Statements that only describe the CHW's own knowledge or actions, with no evidence that the knowledge was shared with others.' | Handing out Medical Supplies : The testimonial focuses entirely on malaria education, symptoms, first aid measures (sponging, hydration), and referral to health centers. There is no mention of distributing, providing, or handing out any medical supplies, medications, or materials to community members.</t>
+          <t>[Group Based Health Education] The testimonial describes malaria symptoms, treatment, and the CHW's role in managing cases, but contains no evidence of group-based health education activities. The CHW discusses individual patient care (sponging, first aid, referral) and one-on-one diagnosis, which are explicitly excluded from this concept. There is no mention of conducting group sessions, workshops, or community education meetings about malaria. [Individualized Support and Health Education] The testimonial primarily describes general malaria symptoms, transmission, and standard first aid responses that would apply to any malaria patient. While the CHW mentions probing clients and immediate referral actions, there is no evidence of personalized guidance adapted to specific individuals' needs, backgrounds, or unique situations. The content represents general health education rather than individualized support. [Cholera Education and Prevention] The testimonial is entirely focused on malaria - its causes, symptoms, and management. There is no mention of cholera, cholera prevention, or any cholera-related education activities. While the CHW discusses some symptoms that could overlap with cholera (diarrhea, vomiting), these are explicitly discussed in the context of malaria, not cholera. This clearly falls under the exclusion criteria as it is general health education with no reference to cholera. [Direct Intervention for Cholera Cases] The testimonial focuses entirely on malaria - its causes, symptoms, and treatment. There is no mention of cholera, cholera cases, or cholera-specific interventions. While the CHW describes giving first aid for symptoms like vomiting and diarrhea (which could occur in cholera), these are explicitly described in the context of malaria treatment, not cholera. This clearly falls under the exclusion criteria of 'treating unrelated conditions.' [Diabetes Education and Prevention] This testimonial is entirely focused on malaria - its causes, symptoms, treatment, and prevention. There is no mention of diabetes, blood sugar, diet, exercise, or any metabolic health topics. The CHW discusses malaria education, first aid, and referral practices, which clearly falls under the exclusion criteria of 'health education unrelated to diabetes.' [HIV/AIDS Education and Prevention] The testimonial is entirely focused on malaria education, including its causes, symptoms, prevention, and treatment. There is no mention of HIV/AIDS, HIV transmission, testing, or any HIV-related topics. This clearly falls under the exclusion criteria as it is general health education without any reference to HIV/AIDS. [Infectious Disease Prevention] While the testimonial extensively discusses malaria as an infectious disease, it focuses primarily on symptom identification, first aid treatment, and clinical management rather than prevention education. The only preventive measures mentioned are sleeping under treated mosquito nets and vector control, but these are presented as aftercare instructions rather than the CHW actively providing prevention education. The testimonial emphasizes diagnosis and referral over teaching general infectious disease prevention strategies. [Tuberculosis Education and Prevention] The testimonial is entirely focused on malaria education, prevention, and management. There is no mention of tuberculosis, TB symptoms, TB transmission, or any TB-related topics. The CHW discusses malaria symptoms, prevention measures (mosquito nets), and treatment approaches, which falls under the exclusion criteria of 'other infectious disease education without mention of TB.'</t>
         </is>
       </c>
     </row>
@@ -1539,16 +1597,20 @@
       <c r="C18" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.9,
-  "Referrals and Advocacy": 0.95,
-  "Community Empowerment Through Education": 0.9,
-  "Handing out Medical Supplies ": 0.2
+  "Group Based Health Education": 0.65,
+  "Individualized Support and Health Education": 0.8,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.6,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The CHW explicitly states, “During the week I took my training emphasizing on how to use nets to help in preventing the spread of malaria,” indicating they personally received training that enhanced their capacity to educate and refer patients. This directly matches the concept’s definition and inclusion criteria. | Referrals and Advocacy: The CHW explicitly states, “I referred the person to Thoamogi Oginga Teaching and Referral Hospital,” which is a clear example of assisting with a referral and navigating the health system. This aligns directly with the concept’s inclusion criteria of accompanying or referring someone for care. Therefore, it is a strong, unambiguous match. | Community Empowerment Through Education: The CHW states, “I took my training emphasizing on how to use nets to help in preventing the spread of malaria,” indicating she actively provided instruction to community participants about mosquito-net use. This is a clear example of health education delivered to improve community practices, matching the inclusion criteria for the concept. Hence a strong direct alignment merits a high score. | Handing out Medical Supplies : The testimonial focuses on educating people about using bed nets and referring a sick participant to a hospital. There is no explicit mention that the CHW physically distributed nets, medicines, or other supplies. Any alignment with handing out medical supplies is minimal and indirect, so a low score is appropriate.</t>
+          <t>[Group Based Health Education] The CHW states, “During the week I took my training emphasizing on how to use nets…,” and later refers to “one of my participants,” implying the existence of a training session with multiple participants (a group). However, the testimonial does not explicitly describe the session’s group nature, size, or facilitation details. This provides moderate—but not definitive—evidence of group-based health education, warranting a mid-range score. [Individualized Support and Health Education] The CHW provided tailored guidance to a specific participant who was self-medicating for malaria, advising and arranging a referral for proper testing and treatment. This fits the inclusion criterion of one-on-one support adapted to an individual's situation. While the testimonial also mentions general education about bed-net use, the personalized referral demonstrates strong direct alignment with the concept. [Cholera Education and Prevention] The testimonial focuses exclusively on malaria prevention (mosquito nets) and referral for malaria treatment. There is no mention of cholera, its transmission, symptoms, or related hygiene practices, so the concept does not apply. [Direct Intervention for Cholera Cases] The testimonial describes malaria prevention education and referral for a malaria case, with no mention of cholera or related care. According to the exclusion criteria, interventions for unrelated conditions like malaria do not count toward the cholera-focused concept. [Diabetes Education and Prevention] The testimonial focuses on malaria prevention (use of nets) and referral for malaria treatment, with no mention of diabetes, diet, exercise, or metabolic health. Therefore, it does not align with the Diabetes Education and Prevention concept. [HIV/AIDS Education and Prevention] The testimonial exclusively discusses malaria prevention, diagnosis, and treatment. There is no mention of HIV/AIDS, testing, stigma, or related education. Therefore, the concept does not apply. [Infectious Disease Prevention] The CHW gives advice on using bed nets to avoid mosquito bites, which is education aimed at preventing the transmission of an infectious disease (malaria). This fits the idea of reducing spread of communicable illness, but it is centered on a single disease rather than broad hygiene or multi-disease messaging, so alignment is moderate rather than perfect. [Tuberculosis Education and Prevention] The testimonial exclusively discusses malaria prevention and treatment; there is no mention of tuberculosis symptoms, transmission, or education. Therefore, the concept does not apply.</t>
         </is>
       </c>
     </row>
@@ -1560,22 +1622,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.2,
-  "Referrals and Advocacy": 0.9,
-  "Community Empowerment Through Education": 0.8,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.0,
+  "Individualized Support and Health Education": 0.8,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.9,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial mentions 'I took my training' but this appears to refer to conducting/delivering training to others about malaria prevention, not receiving training. The CHW demonstrates competence in making referrals and educating about malaria prevention, but there is no clear evidence they received CHW training themselves. This aligns with the exclusion criteria of 'delivering training to others without evidence of having received CHW training.' | Referrals and Advocacy: Strong direct alignment with the concept. The CHW explicitly states 'I referred the person to Thoamogi Oginga Teaching and Referral Hospital for the malaria test' which demonstrates clear referral action. The testimonial shows the CHW identified someone self-medicating with over-the-counter drugs and actively connected them to formal healthcare services, resulting in proper testing and treatment. This matches the example 'I identified disease symptoms and referred the person for testing' which scores 0.9. | Community Empowerment Through Education: The testimonial shows strong evidence of education delivery. The CHW explicitly states 'I took my training emphasizing on how to use nets to help in preventing the spread of malaria,' which demonstrates active knowledge sharing about malaria prevention methods. This aligns well with the concept's definition of providing health education to help community members improve health practices. The score is 0.8 rather than higher because while the education component is clear, the testimonial doesn't provide extensive detail about the educational interaction or its scope. | Handing out Medical Supplies : The testimonial describes malaria prevention education and referring a patient to a hospital for testing and treatment. While the CHW mentions training on using nets for malaria prevention, there is no evidence of actually distributing or handing out medical supplies. The patient received prescriptions and treatment at the hospital, not from the CHW directly.</t>
+          <t>[Group Based Health Education] The testimonial describes 'training' and meeting 'one of my participants' who had malaria, but provides no evidence of group-based health education. The CHW's interaction was one-on-one (referring a single person to the hospital), which is explicitly excluded from this concept. While the CHW mentions conducting training about using nets, there is no indication this was done in a group setting. [Individualized Support and Health Education] The testimonial shows strong evidence of individualized support. The CHW identified a specific participant who was self-medicating for malaria with over-the-counter drugs, then provided personalized guidance by referring them to a specific hospital for proper testing and treatment. The CHW followed up on this individual's progress and noted their positive response to medication. While the testimonial also mentions general community education about mosquito nets, the core narrative focuses on tailored intervention for one person's specific health situation, making this a strong match for the concept. [Cholera Education and Prevention] The testimonial focuses entirely on malaria prevention and treatment, with no mention of cholera, cholera-related symptoms, water sanitation, or hygiene practices related to cholera prevention. While the CHW discusses flooding and stagnant water, these are presented in the context of mosquito breeding for malaria, not as risk factors for cholera transmission. [Direct Intervention for Cholera Cases] The testimonial describes a malaria case intervention, not cholera. The CHW refers a patient with malaria to a hospital for testing and treatment. This falls under the exclusion criteria of 'treating unrelated conditions (e.g., malaria, TB)' and there is no mention of cholera, ORS administration, or cholera-related symptoms. [Diabetes Education and Prevention] The testimonial focuses entirely on malaria prevention and treatment, including mosquito net usage, referral for malaria testing, and malaria medication. There is no mention of diabetes, metabolic health, diet, exercise, blood sugar, or any diabetes-related education. This clearly falls under the exclusion criteria as 'health education unrelated to diabetes.' [HIV/AIDS Education and Prevention] The testimonial focuses entirely on malaria prevention and treatment, with no mention of HIV/AIDS education, prevention, testing, or related activities. The CHW discusses mosquito net usage for malaria prevention and refers a patient for malaria testing and treatment. This clearly falls under the exclusion criteria as it is health education without any reference to HIV/AIDS. [Infectious Disease Prevention] Strong direct alignment with the concept. The testimonial describes educating people on using mosquito nets to prevent malaria transmission, which is a communicable disease. The CHW is providing specific prevention education (mosquito net usage) aimed at reducing the spread of malaria, fitting well within the concept's definition of 'education or advice aimed at reducing the spread of communicable diseases.' While focused on malaria specifically, the prevention education aspect aligns with the inclusion criteria. [Tuberculosis Education and Prevention] The testimonial focuses exclusively on malaria education and prevention, including mosquito net usage and referring a patient for malaria testing and treatment. There is no mention of tuberculosis, TB symptoms, TB transmission, or any TB-related education. This clearly falls under the exclusion criteria of 'other infectious disease education without mention of TB.'</t>
         </is>
       </c>
     </row>
@@ -1593,16 +1659,20 @@
       <c r="C20" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.88,
-  "Referrals and Advocacy": 0.0,
-  "Community Empowerment Through Education": 0.95,
-  "Handing out Medical Supplies ": 0.05
+  "Group Based Health Education": 0.5,
+  "Individualized Support and Health Education": 0.1,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.8,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial explicitly states \ | Referrals and Advocacy: The testimonial focuses exclusively on providing malaria prevention education (e.g., using nets, clearing bushes). It does not describe any referrals, appointment setting, accompaniment, or advocacy within the health system, which the concept specifically requires. Therefore, the concept is not present. | Community Empowerment Through Education: Testimonial states: \ | Handing out Medical Supplies : The testimonial discusses educating community members about malaria prevention measures (e.g., sleeping under treated mosquito nets, eliminating mosquito breeding sites). It does not describe the CHW distributing or providing any physical medical supplies such as nets, medicines, or other items. Therefore, only a minimal, indirect connection exists (mention of mosquito nets), giving it a very weak alignment with the concept of actually handing out medical supplies.</t>
+          <t>[Group Based Health Education] The CHW states that they have been "training my community members" and "share with them" malaria-prevention information, implying some form of organized education that involves multiple people. However, the testimonial does not clearly describe a structured group session (e.g., number of participants, a workshop, or facilitation details). Because the evidence of an actual group setting is implied but not explicit, the alignment is moderate, not strong. [Individualized Support and Health Education] The CHW describes providing malaria prevention advice to community members in general terms (e.g., teaching the importance of bed nets and environmental cleanup). This is broad, group-oriented education rather than personalized guidance adapted to an individual’s specific needs. Because individualized support is not evident, alignment with the concept is very weak. [Cholera Education and Prevention] The testimonial discusses malaria experiences and prevention education, with no mention of cholera, its symptoms, or prevention. According to the exclusion criteria, general health education unrelated to cholera does not apply. [Direct Intervention for Cholera Cases] The testimonial discusses personal experiences with malaria and community education on malaria prevention, with no mention of cholera cases or direct care for cholera patients. Therefore, the concept is not present. [Diabetes Education and Prevention] The testimonial focuses exclusively on malaria experience and prevention strategies (e.g., mosquito nets, clearing bushes). It does not mention diabetes, blood sugar, diet, exercise, or any education related to diabetes awareness or prevention. [HIV/AIDS Education and Prevention] The testimonial focuses exclusively on malaria prevention (mosquito nets, clearing bushes, draining stagnant water). There is no mention of HIV/AIDS, testing, transmission, or related education. Therefore, the HIV/AIDS Education and Prevention concept is not present. [Infectious Disease Prevention] The CHW describes educating community members on how to avoid contracting malaria—an infectious, mosquito-borne disease—by using treated nets, clearing bushes, draining stagnant water, and keeping the surroundings clean. These actions are hygiene/sanitation measures aimed at stopping transmission of a communicable illness, fitting the concept’s inclusion criteria. While the advice is directed at one specific disease rather than communicable diseases in general, it still constitutes infectious disease prevention, warranting a strong (though not perfect) match. [Tuberculosis Education and Prevention] The testimonial discusses malaria symptoms, treatment, and preventive education, with no mention of tuberculosis. Per exclusion criteria, education about other infectious diseases without reference to TB does not apply.</t>
         </is>
       </c>
     </row>
@@ -1614,22 +1684,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.9,
-  "Referrals and Advocacy": 0.0,
-  "Community Empowerment Through Education": 0.8,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.5,
+  "Individualized Support and Health Education": 0.2,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.8,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial contains strong direct evidence of CHW training received. The CHW explicitly states 'Now that I am a trained Community Health Worker' and describes how this training transformed their ability to serve - from having 'no information about malaria' before training to now 'training my community members on how they can prevent contacting malaria.' This shows enhanced capacity to educate others as a direct result of receiving CHW training, which aligns strongly with the concept definition. | Referrals and Advocacy: The testimonial describes the CHW's personal malaria experience and their current role in educating community members about malaria prevention. While they mention training people on prevention methods (sleeping under nets, clearing bushes, draining water), there is no mention of referring people for testing, setting appointments, accompanying anyone to care, or advocating within the healthcare system. The focus is entirely on preventive education without any system navigation activities. | Community Empowerment Through Education: Strong direct alignment. The CHW explicitly states 'I have been training my community members on how they can prevent contacting malaria' and describes sharing specific prevention methods including 'the importance of sleeping under treated mosquito nets, clearing of bushy surroundings, draining stagnant waters, and also keeping the surroundings clean.' This clearly shows active knowledge sharing through training sessions, not just possessing knowledge themselves. | Handing out Medical Supplies : The testimonial describes the CHW's personal experience with malaria and their educational activities (training community members on prevention methods like using mosquito nets, clearing bushes, and draining water). There is no mention of distributing, handing out, or providing any medical supplies to community members. The CHW focuses solely on education and training, not supply distribution.</t>
+          <t>[Group Based Health Education] The testimonial mentions 'I have been training my community members' which suggests group education activities, but lacks specific details about group settings, number of participants, or structured sessions. The phrase could refer to either group sessions or individual encounters, making it moderately aligned with the concept. [Individualized Support and Health Education] The testimonial primarily describes community-wide malaria prevention education rather than individualized support. The CHW mentions 'training my community members' and shares general prevention strategies (mosquito nets, clearing bushes, draining water) that apply to everyone, not tailored to specific individuals or households. This aligns with the exclusion criteria of 'group education or community-wide support.' The slight score above 0.0 reflects that the CHW draws from personal experience to inform their teaching, but this doesn't constitute personalized guidance to individuals. [Cholera Education and Prevention] The testimonial focuses entirely on malaria prevention education, with no mention of cholera, cholera symptoms, water purification, or cholera-related sanitation practices. The CHW explicitly states they are training community members about malaria prevention through mosquito control measures. This clearly falls under the exclusion criteria of 'general health education with no reference to cholera.' [Direct Intervention for Cholera Cases] The testimonial focuses entirely on the CHW's personal experience with malaria and their subsequent work in malaria prevention education. There is no mention of cholera, cholera cases, cholera symptoms, or any direct intervention related to cholera. The exclusion criteria specifically states 'treating unrelated conditions (e.g., malaria, TB)' which directly applies here. [Diabetes Education and Prevention] The testimonial is entirely focused on malaria - the CHW's personal experience with malaria and their subsequent work educating communities about malaria prevention (mosquito nets, clearing bushes, draining water). There is no mention of diabetes, blood sugar, diet, exercise, or any metabolic health topics. This clearly falls under the exclusion criteria of 'health education unrelated to diabetes.' [HIV/AIDS Education and Prevention] The testimonial is entirely focused on malaria prevention and the CHW's personal experience with malaria. There is no mention of HIV/AIDS, HIV transmission, testing, or any HIV-related topics. The CHW discusses training community members specifically about malaria prevention methods (mosquito nets, clearing bushes, draining water). This falls under the exclusion criteria as it is general health education without any reference to HIV/AIDS. [Infectious Disease Prevention] Strong direct alignment. The CHW explicitly states they train community members on malaria prevention methods including sleeping under treated mosquito nets, clearing bushy surroundings, draining stagnant waters, and keeping surroundings clean to prevent mosquito breeding. While focused on malaria specifically, these are broad prevention strategies that align with communicable disease prevention education. [Tuberculosis Education and Prevention] The testimonial exclusively focuses on malaria - the CHW's personal experience with malaria and their current work educating community members about malaria prevention (mosquito nets, clearing bushes, draining water). There is no mention of tuberculosis, TB symptoms, TB transmission, or any TB-related education, making this a clear non-match for the TB education concept.</t>
         </is>
       </c>
     </row>
@@ -1647,16 +1721,20 @@
       <c r="C22" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.1,
-  "Referrals and Advocacy": 0.85,
-  "Community Empowerment Through Education": 0.97,
-  "Handing out Medical Supplies ": 0.05
+  "Group Based Health Education": 0.85,
+  "Individualized Support and Health Education": 0.9,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.85,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The narrative shows the CHW educating the community and recognizing malaria symptoms, but it never explicitly states that the CHW attended or completed any CHW training. Knowledge alone, without a clear mention of received training, falls under the exclusion criteria. Only a vague phrase ('during my health education') could imply training, but it is not specific enough, so alignment is very weak. | Referrals and Advocacy: The CHW identified possible malaria in a child and explicitly advised the caregiver to take the child to the nearest health facility, then followed up to confirm treatment—actions that constitute making a referral and navigating care, aligning strongly with the concept. | Community Empowerment Through Education: The testimonial explicitly describes the CHW giving a malaria health talk to residents (group education) and individually explaining symptoms, home care (sponging), and referral to a mother. This is clear, unambiguous evidence of actively sharing health knowledge to improve community practices, matching the concept’s definition and inclusion criteria. | Handing out Medical Supplies : The CHW provided health education and referred the child to a facility, but did not distribute any physical supplies such as medicine, nets, or test kits herself. Only advice and referral are mentioned, so evidence for handing out medical supplies is essentially absent.</t>
+          <t>[Group Based Health Education] The CHW describes conducting a ‘malaria talk’ for the residents of Bandani Slums, which indicates an organized educational session directed at a group rather than an individual. This aligns closely with the definition and inclusion criteria for Group Based Health Education, though the testimonial does not specify exact group size or structure, so a score slightly below perfect (0.85) is appropriate. [Individualized Support and Health Education] After giving a general malaria talk, the CHW provided personalized guidance to Mrs. Onyango by visiting her home, assessing the child’s specific symptoms, recommending sponging, and advising referral to a health facility, followed by a tailored follow-up visit. This one-on-one, context-specific support matches the definition and inclusion criteria for individualized support and health education. [Cholera Education and Prevention] The testimonial exclusively discusses malaria education, symptoms, and referral, with no mention of cholera, water sanitation, or related prevention strategies. According to the concept’s exclusion criteria, general health education unrelated to cholera receives a score of 0. [Direct Intervention for Cholera Cases] The testimonial exclusively addresses malaria education, assessment, and referral. There is no mention of suspected or confirmed cholera cases or cholera-specific care, so the concept does not apply. [Diabetes Education and Prevention] The testimonial focuses solely on malaria education, symptoms, and referral; there is no discussion of diabetes, its risk factors, or prevention. Health education unrelated to diabetes is explicitly excluded from the concept. [HIV/AIDS Education and Prevention] The testimonial focuses exclusively on malaria education, symptoms, and treatment with no reference to HIV/AIDS transmission, testing, prevention, or related topics; therefore the HIV/AIDS Education and Prevention concept is not applicable. [Infectious Disease Prevention] The CHW describes giving a community talk on causes and prevention of malaria (e.g., sleeping under treated mosquito nets, vector control) and advising a caregiver on home measures and seeking treatment. This is education aimed at reducing the spread of a communicable disease, fitting the concept’s inclusion of advice on preventing transmission of illnesses. The focus is on a specific infectious disease but still squarely within disease‐prevention education, so the alignment is strong though not perfect. [Tuberculosis Education and Prevention] Testimonial exclusively discusses malaria education, symptoms, and treatment. No mention of tuberculosis or related guidance; therefore the concept does not apply.</t>
         </is>
       </c>
     </row>
@@ -1668,22 +1746,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.2,
-  "Referrals and Advocacy": 0.7,
-  "Community Empowerment Through Education": 0.9,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.9,
+  "Individualized Support and Health Education": 0.8,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.1,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial describes a CHW conducting health education and applying knowledge about malaria, but contains no explicit mention of the CHW having received training. While the CHW demonstrates competence in recognizing symptoms and making referrals, this falls under the exclusion criteria of 'outcomes or competence without mention of received training.' The narrative focuses on the CHW delivering education to others, which aligns with the example 'I conducted a training and later helped a TB patient' (0.2). | Referrals and Advocacy: The CHW advised the mother to take her child to the nearest health facility and conducted a follow-up visit to check on the child's progress. This shows moderate alignment with the concept as it includes a referral recommendation and follow-up, though the CHW did not directly assist with the referral process or accompany them to care. | Community Empowerment Through Education: Strong direct alignment. The CHW conducted a health education session at Bandani Slums where they actively taught residents about malaria - explaining signs/symptoms (fever, shaking, chills, muscle pain), treatment options, and causes (including not using treated mosquito nets). The education was effective enough that Mrs. Mary Onyango could recognize symptoms in her daughter based on the CHW's teaching. The CHW also provided practical instruction to the mother (sponging to reduce fever) and advised seeking medical care. This demonstrates active knowledge sharing through group education and one-on-one instruction. | Handing out Medical Supplies : The testimonial describes a CHW providing health education about malaria and advising a mother to take her sick child to a health facility. The CHW explicitly states they 'advised the mother to take her to the nearest health facility for further management' rather than providing any medical supplies themselves. The CHW's role was limited to education, assessment, and referral - not distribution of medical supplies.</t>
+          <t>[Group Based Health Education] The testimonial clearly describes conducting 'health education at Bandani Slums' where the CHW was 'giving malaria talk to the residents' (plural), indicating a group setting. The CHW delivered structured content on malaria signs, symptoms, treatment and causes to multiple community members. The fact that Mrs. Mary Onyango approached after 'completion' of the session further confirms this was a formal group education event. This aligns strongly with the concept definition of facilitating health education sessions with groups of community members. [Individualized Support and Health Education] Strong alignment with personalized support. The CHW initially provided general malaria education to a group, but then responded to Mrs. Mary Onyango's specific request for help with her daughter. The CHW visited their home, assessed the child's individual symptoms, provided personalized advice (sponging for fever), recommended facility care, and conducted a follow-up visit. This demonstrates adaptation from general education to individualized care based on the family's specific needs and situation. [Cholera Education and Prevention] The testimonial focuses entirely on malaria education, symptoms, and case management. There is no mention of cholera, cholera prevention strategies, water sanitation, or any cholera-related hygiene practices. While diarrhea is mentioned as a malaria symptom, this is not in the context of cholera education or prevention. [Direct Intervention for Cholera Cases] The testimonial describes a CHW providing direct intervention for a suspected malaria case, not cholera. The CHW identifies malaria symptoms (fever, shivering, vomiting, headache), advises fever management, and refers the child to a health facility. This falls under the exclusion criteria of 'treating unrelated conditions (e.g., malaria, TB)' with no mention of cholera whatsoever. [Diabetes Education and Prevention] The testimonial focuses entirely on malaria education, symptoms, and care. There is no mention of diabetes, blood sugar, diet, exercise, or any metabolic health topics. This clearly falls under the exclusion criteria of 'health education unrelated to diabetes.' [HIV/AIDS Education and Prevention] The testimonial is entirely focused on malaria education, symptoms, and treatment. There is no mention of HIV/AIDS, HIV transmission, testing, prevention methods, or any HIV-related topics. This clearly falls under the exclusion criteria of 'general health education without a reference to HIV/AIDS.' [Infectious Disease Prevention] This testimonial focuses specifically on malaria education and treatment, not general infectious disease prevention. While malaria is a communicable disease, the CHW's education centered on a single specific condition (its symptoms, causes, and treatment) rather than broad prevention strategies for multiple communicable diseases. The concept explicitly requires education 'without focusing on a specific condition,' which excludes this malaria-specific talk. The score of 0.1 reflects minimal alignment since malaria is technically an infectious disease, but the approach doesn't match the concept's requirement for general prevention education. [Tuberculosis Education and Prevention] The testimonial exclusively focuses on malaria education, symptoms, and treatment. There is no mention of tuberculosis, TB symptoms, TB prevention, or any TB-related topics. This clearly falls under the exclusion criteria of 'other infectious disease education without mention of TB.'</t>
         </is>
       </c>
     </row>
@@ -1701,16 +1783,20 @@
       <c r="C24" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.1,
-  "Referrals and Advocacy": 0.2,
-  "Community Empowerment Through Education": 0.85,
-  "Handing out Medical Supplies ": 0.85
+  "Group Based Health Education": 0.8,
+  "Individualized Support and Health Education": 0.2,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.05,
+  "Infectious Disease Prevention": 0.1,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial describes the CHW’s outreach, fundraising, and sensitization activities but does not clearly state that the CHW attended or received any training. The mention of activism events and meetings could theoretically have included learning opportunities, but this is not explicitly connected to CHW training. Therefore, only a very weak alignment with the concept is present. | Referrals and Advocacy: The CHW conducted community education and fundraising for menstrual pads, which is a form of general advocacy, but there is no evidence of navigating the health system, making referrals, setting appointments, or advocating for a specific client within healthcare. Thus, alignment with the concept is weak. | Community Empowerment Through Education: The CHW describes organizing Google-meet and physical sessions with more than 50 girls, conducting ‘chit chats,’ and sensitizing men and adults about menstruation—activities that involve actively sharing knowledge and raising awareness about menstrual hygiene and teenage pregnancy. This fits the inclusion criteria of providing group education/health talks. No contradiction or exclusion noted, so a strong (though not perfect, as teaching details are limited) alignment is appropriate. | Handing out Medical Supplies : The CHW describes partnering to fund-raise and distribute sanitary pads to adolescent girls experiencing ‘menstrual poverty.’ This is a direct instance of providing a health-related supply (menstrual hygiene products) to the community, fitting the concept of handing out medical or health supplies. The match is clear and specific, though pads are hygiene rather than clinical items, so a score of 0.85 (strong alignment) is appropriate.</t>
+          <t>[Group Based Health Education] The CHW describes participating in 16-day activism activities that included Google Meet and physical meetings where she 'reached out to more than 50 girls' and 'sensitized' men and adults about menstruation. These statements imply she facilitated or led health discussions with groups rather than one-on-one counseling, matching the inclusion criteria for group-based health education. While the structure of the sessions is not detailed, the testimonial clearly indicates group outreach and education, warranting a strong but not perfect score. [Individualized Support and Health Education] The CHW describes reaching more than 50 girls, fundraising for pads, and conducting community sensitization. These are primarily group-level or community interventions rather than advice or care tailored to a specific individual or household. Only vague mention of having 'chit chats' is provided, with no clear indication of personalized guidance. Therefore, alignment with individualized support is weak. [Cholera Education and Prevention] The testimonial focuses exclusively on menstrual hygiene and teenage pregnancy, with no mention of cholera, its symptoms, water sanitation, or prevention. Therefore the concept is not present. [Direct Intervention for Cholera Cases] The testimonial discusses menstrual hygiene, teenage pregnancy, and fundraising for sanitary pads. There is no mention of cholera cases, dehydration, ORS, or any direct care related to cholera. Therefore, the concept does not apply. [Diabetes Education and Prevention] The testimonial discusses menstrual hygiene, menstrual poverty, and teenage pregnancy—topics unrelated to diabetes education, prevention, or metabolic health. Therefore, the concept does not apply. [HIV/AIDS Education and Prevention] The testimonial focuses on menstrual hygiene, teenage pregnancy, and fundraising for sanitary products. There is no explicit discussion of HIV/AIDS transmission, testing, stigma reduction, or prevention strategies. Any link to HIV/AIDS is only speculative (e.g., transactional sex could increase HIV risk), but this is not mentioned. Therefore the alignment with HIV/AIDS education and prevention is very weak. [Infectious Disease Prevention] Testimonial centers on menstrual hygiene, menstrual poverty, and teenage pregnancy. While the word 'hygiene' appears, the discussion is about providing sanitary pads and reducing pregnancy risk, not about preventing the transmission of communicable diseases through general hygiene education. Only a minimal, indirect connection to hygiene exists, so alignment with infectious disease prevention is very weak. [Tuberculosis Education and Prevention] The testimonial discusses menstrual hygiene and teenage pregnancy without any mention of tuberculosis symptoms, transmission, prevention, or treatment. Therefore, the TB education concept does not apply.</t>
         </is>
       </c>
     </row>
@@ -1722,22 +1808,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.0,
-  "Referrals and Advocacy": 0.7,
-  "Community Empowerment Through Education": 0.8,
-  "Handing out Medical Supplies ": 0.9
+  "Group Based Health Education": 0.85,
+  "Individualized Support and Health Education": 0.3,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.1,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial describes the CHW's activities in addressing menstrual poverty and teenage pregnancy through community engagement, fundraising, and sensitization. However, there is no mention of the CHW receiving any training, attending workshops, or participating in educational programs that enhanced their capacity. The CHW describes their own initiatives and actions but does not reference any structured learning experience they underwent. | Referrals and Advocacy: The testimonial shows moderate alignment with advocacy work. The CHW advocates for teenage girls by raising awareness about menstrual poverty, organizing meetings, and partnering with others to fundraise for sanitary pads. While this demonstrates strong advocacy for a vulnerable population, there is no explicit mention of referrals to health services, appointment setting, or direct navigation within the healthcare system. The work focuses more on community mobilization and resource provision rather than healthcare system navigation. | Community Empowerment Through Education: Strong alignment with the concept. The CHW explicitly states they 'had some chit chats' with over 50 girls about menstrual poverty and teenage pregnancy. They also 'sensitized' men and adults that menstruation is a human issue requiring support. These activities demonstrate active knowledge sharing through discussions and awareness-raising, though the testimonial lacks specific details about the educational content or methods used. | Handing out Medical Supplies : Strong direct alignment. The CHW explicitly describes fundraising for and distributing sanitary pads/towels to address menstrual poverty. These menstrual hygiene products qualify as medical/health supplies being handed out to community members in need. The testimonial clearly indicates the CHW's role in organizing the distribution of these supplies to help prevent teenage pregnancies caused by transactional sex.</t>
+          <t>[Group Based Health Education] Strong evidence of group-based education. The CHW explicitly mentions conducting 'Google meets and physical meetings' that reached 'more than 50 girls' and having 'chit chats' with them about menstrual poverty and teenage pregnancy. Additionally, they mention sensitizing 'men and adults' about menstruation, suggesting multiple group education efforts. The structured nature of these interactions during the 16-day activism period and the educational focus on health topics clearly aligns with the concept definition. [Individualized Support and Health Education] While the CHW engaged in one-on-one 'chit chats' with over 50 girls to understand their individual situations regarding menstrual poverty, the primary activities described are community-wide interventions (fundraising for pads, sensitizing men and adults). The testimonial focuses more on group education and community-level support rather than personalized guidance adapted to individual needs. The interactions helped identify a common issue but didn't result in individualized support plans or tailored education for specific girls or families. [Cholera Education and Prevention] The testimonial focuses entirely on menstrual hygiene, teenage pregnancy prevention, and related issues. There is no mention of cholera, cholera symptoms, water sanitation, or any cholera-related prevention strategies. The content clearly falls under the exclusion criteria as it represents general health education with no reference to cholera. [Direct Intervention for Cholera Cases] The testimonial focuses entirely on menstrual hygiene, teenage pregnancy prevention, and providing sanitary products to girls. There is no mention of cholera, cholera symptoms, ORS administration, or any cholera-related interventions. The CHW's work involves addressing menstrual poverty and conducting awareness sessions, which falls under the exclusion criteria as it deals with unrelated conditions. [Diabetes Education and Prevention] The testimonial focuses entirely on menstrual hygiene, menstrual poverty, and teenage pregnancy prevention. There is no mention of diabetes, blood sugar, diet, exercise, or any metabolic health topics. The content explicitly deals with reproductive health education, which falls outside the scope of diabetes education and prevention. [HIV/AIDS Education and Prevention] The testimonial focuses entirely on menstrual hygiene, menstrual poverty, and teenage pregnancy prevention. While it mentions transactional sex as a risk factor for teenage pregnancy, there is no reference to HIV/AIDS education, prevention, testing, or awareness. The content is about reproductive health and menstrual support, which falls under the exclusion criteria of 'general health education without a reference to HIV/AIDS.' [Infectious Disease Prevention] The testimonial focuses primarily on menstrual hygiene education and teenage pregnancy prevention through addressing menstrual poverty. While menstrual hygiene is mentioned, the context is about access to sanitary products and preventing transactional sex rather than preventing disease transmission. The hygiene aspect here relates to personal menstrual management, not the spread of communicable diseases. This aligns weakly with the concept, similar to the diabetes example (0.1). [Tuberculosis Education and Prevention] The testimonial focuses entirely on menstrual hygiene, menstrual poverty, and teenage pregnancy prevention. There is no mention of tuberculosis, TB symptoms, TB transmission, or any TB-related education or prevention activities. The content explicitly deals with reproductive health issues, not respiratory or infectious disease education.</t>
         </is>
       </c>
     </row>
@@ -1755,16 +1845,20 @@
       <c r="C26" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.05,
-  "Referrals and Advocacy": 0.85,
-  "Community Empowerment Through Education": 0.95,
-  "Handing out Medical Supplies ": 0.2
+  "Group Based Health Education": 0.2,
+  "Individualized Support and Health Education": 0.75,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.8,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: Testimonial shows the speaker educating the community about malaria but never mentions that they themselves attended or received any CHW training. Providing information alone does not meet inclusion criteria, so alignment is very weak. | Referrals and Advocacy: The CHW states, “I do advise people with malaria symptoms to go for a test… I also take an action by taking some of them in hospitals so that they can get treatment,” which shows direct involvement in referring and accompanying clients to health facilities—clear system navigation/advocacy behavior. This aligns strongly with the concept’s inclusion criteria, though details are limited, so a score slightly below perfect is appropriate. | Community Empowerment Through Education: The speaker actively explains what malaria is, its symptoms, why testing is needed before treatment, how to complete medication, and multiple prevention strategies (nets, repellents, long-sleeved clothes, ANC for pregnant women). They explicitly state “I do advise people…”, “I tell the community…”, showing direct health education to others, which fits the inclusion criteria for Community Empowerment Through Education. No conflicting exclusions are present, so alignment is very strong. | Handing out Medical Supplies : The CHW discusses advising community members to use mosquito nets, insect repellent, and to complete malaria medication, but there is no explicit mention of physically distributing these items. Because there is only an implication of encouraging their use rather than handing them out, alignment is weak.</t>
+          <t>[Group Based Health Education] The testimonial contains health advice addressed to 'people' and 'the community,' but it never explicitly states that the CHW facilitated an educational session with a group. Because the definition requires evidence of a group talk or workshop, this is at most minimal indirect evidence, yielding a weak alignment. [Individualized Support and Health Education] The CHW is not only giving general information about malaria but also describes person-specific actions: advising ‘people with malaria symptoms’ to test before medication, personally taking some individuals to the hospital, ensuring they finish their treatment, and giving special instructions to pregnant mothers. These elements show tailoring of guidance to individuals’ conditions, though much of the narrative is still general education. Hence a moderate–strong fit (≈0.75). [Cholera Education and Prevention] The testimonial focuses exclusively on malaria education and prevention without any mention of cholera, its symptoms, transmission, or specific hygiene measures for cholera. According to the concept’s exclusion criteria, general health education unrelated to cholera should receive a score of 0. [Direct Intervention for Cholera Cases] The testimonial focuses entirely on malaria—symptoms, prevention, and advising patients to seek treatment. No suspected or confirmed cholera cases are mentioned, nor any cholera-specific actions such as ORS administration or referrals. Treating unrelated conditions like malaria is explicitly excluded from this concept. [Diabetes Education and Prevention] The testimonial exclusively discusses malaria symptoms, treatment, and prevention, with no mention of diabetes, diet, exercise, or blood-sugar management. Health education is present but is unrelated to diabetes, which falls under the exclusion criteria. [HIV/AIDS Education and Prevention] The testimonial exclusively discusses malaria symptoms, treatment, and prevention with no reference to HIV/AIDS education, testing, stigma, or prevention. According to the exclusion criteria, general health education not mentioning HIV/AIDS scores 0.0. [Infectious Disease Prevention] The CHW is clearly giving education on how to prevent transmission of malaria—an infectious, communicable disease—by advising insect-repellent use, bed nets, long-sleeved clothing, and prompt testing. This aligns with the concept’s inclusion of advice aimed at reducing spread of infectious illnesses. Although the focus is on a single disease rather than hygiene in general, it still constitutes strong infectious-disease prevention guidance, warranting a high (but not perfect) score. [Tuberculosis Education and Prevention] The testimonial focuses exclusively on malaria—its symptoms, testing, treatment adherence, and prevention measures. Tuberculosis is never mentioned, so the concept of TB education and prevention is not present, aligning with the exclusion criterion.</t>
         </is>
       </c>
     </row>
@@ -1776,22 +1870,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.0,
-  "Referrals and Advocacy": 0.8,
-  "Community Empowerment Through Education": 0.8,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.0,
+  "Individualized Support and Health Education": 0.7,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.9,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial contains no evidence that the CHW received any training. While the CHW demonstrates knowledge about malaria and describes actions they take (advising patients, taking them to hospitals, educating about prevention), there is no mention of attending training, workshops, or any structured educational experience that enhanced their capacity. The knowledge displayed could come from personal experience or other sources, but without explicit reference to receiving CHW training, the concept does not apply. | Referrals and Advocacy: Strong direct alignment. The CHW explicitly states 'I also take an action by taking some of them in hospitals so that they can get treatment,' which demonstrates direct involvement in accompanying patients to healthcare facilities. Additionally, they advise people to go for testing and tell pregnant mothers to go for check-ups, showing active referral behavior. This goes beyond general health education to include actual system navigation and patient accompaniment. | Community Empowerment Through Education: The testimonial shows strong evidence of the CHW actively educating community members about malaria. The CHW explicitly states 'I do advise people with malaria symptoms to go for a test before taking any painkiller' and 'I assure them to finish the malaria dose.' They also mention educating pregnant mothers about check-ups and risks. The CHW describes sharing knowledge about prevention methods like using insect repellent and nets. While much of the text describes the CHW's own knowledge about malaria, there is clear evidence of active knowledge transfer to the community through advising, assuring, and telling community members about health practices. | Handing out Medical Supplies : The testimonial focuses entirely on malaria education, symptoms, prevention advice, and encouraging people to seek medical care at hospitals. While the CHW mentions 'taking some of them in hospitals' for treatment, this refers to accompanying patients to facilities rather than distributing medical supplies. There is no mention of the CHW providing, distributing, or handing out any medical supplies, medications, or materials to community members.</t>
+          <t>[Group Based Health Education] The testimonial describes the CHW's knowledge about malaria and mentions advising 'people' and 'the community,' but provides no evidence of conducting group education sessions. The CHW discusses one-on-one actions like 'taking some of them to hospitals' and giving individual advice. Without any mention of workshops, group talks, or collective learning settings, this clearly falls under the exclusion criteria of 'general mentions of educating people or the community without evidence of a group setting.' [Individualized Support and Health Education] The testimonial shows moderate alignment with individualized support. The CHW mentions 'I do advise people with malaria symptoms' and 'I also take an action by taking some of them in hospitals,' indicating personalized interactions. There's specific mention of tailored advice for pregnant mothers ('For pregnant mothers, I tell them to go for check-up'). However, much of the content is general health education about malaria rather than clearly adapted individual guidance, preventing a higher score. [Cholera Education and Prevention] This testimonial is entirely focused on malaria - its causes, symptoms, treatment, and prevention. There is no mention of cholera, cholera-specific symptoms, or cholera prevention strategies like water purification or sanitation. While the CHW discusses disease education and prevention, it is specifically about malaria, not cholera, which clearly falls under the exclusion criteria. [Direct Intervention for Cholera Cases] The testimonial exclusively discusses malaria - its causes, symptoms, prevention, and treatment. There is no mention of cholera, cholera symptoms, or any cholera-related interventions. While the CHW describes direct interventions (taking patients to hospitals, advising on treatment), these are specifically for malaria cases, which falls under the exclusion criteria of 'treating unrelated conditions.' [Diabetes Education and Prevention] The testimonial is entirely focused on malaria - its causes, symptoms, treatment, and prevention. There is no mention of diabetes, blood sugar, diet related to diabetes prevention, or any metabolic health topics. The content explicitly falls under the exclusion criteria as it is health education unrelated to diabetes. [HIV/AIDS Education and Prevention] The testimonial is entirely focused on malaria education, prevention, and treatment. While it mentions blood transmission through 'unclean needles or unscreened blood' as a transmission route for malaria, there is no reference to HIV/AIDS education, prevention, testing, or awareness. The content exclusively addresses malaria-related health education, which falls under the exclusion criteria of 'general health education without a reference to HIV/AIDS.' [Infectious Disease Prevention] Strong direct alignment. The testimonial extensively discusses malaria prevention education, including avoiding mosquito bites through insect repellent, wearing protective clothing, using bed nets, and maintaining cleanliness. While focused on malaria specifically, the CHW describes providing general prevention advice about reducing disease transmission through environmental measures and hygiene ('Observe cleanliness at all cost to prevent more infections'), which aligns with the concept's inclusion of education aimed at reducing spread of communicable diseases. [Tuberculosis Education and Prevention] The testimonial focuses exclusively on malaria education and prevention. There is no mention of tuberculosis, TB symptoms, TB transmission, or TB treatment. The content describes malaria symptoms, transmission, treatment, and prevention in detail, which falls under the exclusion criteria of 'other infectious disease education without mention of TB.'</t>
         </is>
       </c>
     </row>
@@ -1809,16 +1907,20 @@
       <c r="C28" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.0,
-  "Referrals and Advocacy": 0.1,
-  "Community Empowerment Through Education": 0.6,
-  "Handing out Medical Supplies ": 0.05
+  "Group Based Health Education": 0.05,
+  "Individualized Support and Health Education": 0.1,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.05,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial is a personal account of malaria symptoms and self-care practices; it contains no mention of the speaker being a community health worker or receiving any CHW training. Therefore, the concept is not present. | Referrals and Advocacy: The testimonial mostly provides personal experience and general advice about malaria treatment (e.g., visit the hospital before taking Coartem). It does not describe the speaker facilitating referrals, setting appointments, accompanying others, or actively navigating the health system for someone else. This is general advice without CHW-led system navigation, so alignment with the concept is very weak. | Community Empowerment Through Education: The narrator offers explicit advice to others on how to manage suspected malaria (e.g., avoid using Coartem without first visiting a hospital, use painkillers for relief). This constitutes sharing health information intended to influence community members’ practices, fitting the education/empowerment definition. However, the testimonial is mostly a personal illness story with only a brief educational component, so alignment is moderate rather than strong. | Handing out Medical Supplies : The testimonial is a personal narrative about experiencing and self-managing malaria. It mentions medications (Coartem, painkillers) but does not describe the speaker distributing or providing medical supplies to others, which is required for the concept.</t>
+          <t>[Group Based Health Education] The testimonial is an individual’s personal experience and advice about malaria treatment. There is no mention of a CHW facilitating or teaching a group session. Therefore, evidence for group-based health education is virtually absent, warranting a very low score. [Individualized Support and Health Education] The testimonial is a personal account of managing malaria and offers general advice to ‘people’ rather than describing a CHW providing tailored guidance to a specific individual or household. Any educational content is generic, not personalized, so evidence for individualized support is minimal. [Cholera Education and Prevention] The testimonial discusses personal experiences, symptom management, and advice related to malaria, with no mention of cholera, sanitation, water safety, or cholera‐specific education. According to the concept definition and exclusion criteria, general health information not related to cholera should receive a score of 0. [Direct Intervention for Cholera Cases] The testimonial discusses personal experiences with malaria management and gives advice to others about treating malaria. There is no mention of cholera cases or any direct intervention related to cholera, so the concept does not apply. [Diabetes Education and Prevention] The testimonial focuses solely on personal experiences and advice related to malaria diagnosis and treatment, with no mention of diabetes, its risk factors, or preventive education. [HIV/AIDS Education and Prevention] The testimonial discusses personal experiences and advice related to malaria treatment and prevention, with no mention of HIV, AIDS, testing, transmission, or any other aspect of HIV/AIDS education. Therefore, the concept does not apply. [Infectious Disease Prevention] The testimonial discusses personal experiences and treatment choices for malaria, a specific infectious disease, rather than providing general hygiene or broad infection-control advice. The concept definition emphasizes non-specific, general prevention guidance (e.g., handwashing, cough etiquette). Since the content focuses on disease management for one condition and not on preventing spread in general, alignment is minimal. [Tuberculosis Education and Prevention] The testimonial focuses exclusively on personal experiences and advice regarding malaria treatment and symptom management. There is no mention of tuberculosis symptoms, transmission, testing, or prevention, so the concept does not apply.</t>
         </is>
       </c>
     </row>
@@ -1830,22 +1932,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.0,
-  "Referrals and Advocacy": 0.0,
-  "Community Empowerment Through Education": 0.1,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.0,
+  "Individualized Support and Health Education": 0.0,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.1,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial describes personal experiences with malaria and self-care practices but contains no evidence of receiving CHW training. The narrator discusses their symptoms, self-treatment methods, and advice based on personal experience, but never mentions attending training, workshops, or any structured educational program related to their CHW role. This clearly falls under the exclusion criteria of 'outcomes or competence without mention of received training.' | Referrals and Advocacy: The testimonial is a personal account of the speaker's own experience with malaria and their self-care practices. There is no mention of the speaker acting as a CHW or helping others navigate the healthcare system. The advice given ('avoid using Coartem without visiting the hospital') is general health education without any CHW involvement in referrals, advocacy, or system navigation. | Community Empowerment Through Education: The testimonial primarily describes the CHW's personal experience with malaria and their own self-care practices. While there is one instance of advice ('My advice to people is always to avoid using Coartem without visiting the hospital at first and rather use painkillers to relief pain'), this represents minimal evidence of active knowledge sharing or education. The testimonial lacks clear examples of the CHW conducting training sessions, explaining health topics to others, or demonstrating proper health practices to community members. | Handing out Medical Supplies : The testimonial is entirely about the speaker's personal experience with malaria and their self-treatment methods. There is no mention of distributing, handing out, or providing medical supplies to others. The speaker only discusses their own use of thermometers, painkillers, and Coartem for personal treatment.</t>
+          <t>[Group Based Health Education] The testimonial is entirely a personal narrative about the individual's own experience with malaria, symptoms, and self-treatment. There is no mention of conducting any health education sessions, facilitating group discussions, or teaching others. The text only contains advice ('My advice to people...') but shows no evidence of actual group education delivery by a CHW. [Individualized Support and Health Education] This testimonial describes the CHW's personal experience with malaria and their self-care practices. While they offer general advice about avoiding Coartem without medical consultation, there is no evidence of providing personalized guidance, education, or care adapted to specific individuals or households. The advice given is generic and not tailored to anyone's unique situation or needs. [Cholera Education and Prevention] The testimonial focuses entirely on personal experiences with malaria - symptoms, self-treatment, and advice about malaria management. There is no mention of cholera, cholera prevention, water safety, sanitation, or any cholera-related education activities. This clearly falls under the exclusion criteria as it contains general health content with no reference to cholera. [Direct Intervention for Cholera Cases] The testimonial exclusively discusses the CHW's personal experience with malaria, including symptoms, self-treatment, and advice about malaria management. There is no mention of cholera, cholera symptoms, or any cholera-related interventions. This clearly falls under the exclusion criteria of 'treating unrelated conditions (e.g., malaria, TB)' and contains no evidence of direct intervention for cholera cases. [Diabetes Education and Prevention] The testimonial is entirely focused on the CHW's personal experience with malaria, including symptoms, self-treatment, and advice about malaria management. There is no mention of diabetes, blood sugar, diet related to diabetes prevention, or any metabolic health education. This clearly falls under the exclusion criteria as health education unrelated to diabetes. [HIV/AIDS Education and Prevention] The testimonial is entirely focused on the CHW's personal experience with malaria - its symptoms, treatment approaches, and advice about malaria management. There is no mention of HIV/AIDS education, prevention, testing, or any HIV-related topics whatsoever. This clearly falls under the exclusion criteria as it represents general health content without any reference to HIV/AIDS. [Infectious Disease Prevention] The testimonial focuses entirely on personal experience with malaria symptoms and treatment, not on preventing disease transmission. While the CHW advises against self-medication with Coartem, this is treatment guidance rather than prevention education. There is no mention of preventing malaria spread (e.g., mosquito nets, standing water elimination) or general infectious disease prevention measures like hygiene or sanitation. [Tuberculosis Education and Prevention] The testimonial focuses entirely on the CHW's personal experience with malaria, including symptoms, self-treatment practices, and advice about malaria management. There is no mention of tuberculosis, TB symptoms, TB prevention, or any TB-related education. This clearly falls under the exclusion criteria as it discusses another infectious disease (malaria) without any reference to TB.</t>
         </is>
       </c>
     </row>
@@ -1863,16 +1969,20 @@
       <c r="C30" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.0,
-  "Referrals and Advocacy": 0.5,
-  "Community Empowerment Through Education": 1.0,
-  "Handing out Medical Supplies ": 0.2
+  "Group Based Health Education": 0.6,
+  "Individualized Support and Health Education": 0.25,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.95,
+  "Infectious Disease Prevention": 0.3,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial describes the CHW educating teens about HIV prevention, but there is no mention that the CHW themselves received any training. According to the concept definition, evidence of the CHW having attended or completed training is required; therefore the concept is not present. | Referrals and Advocacy: The CHW encourages teens to go for HIV testing and to start PrEP, which shows some navigation/advocacy toward health services, similar to the example “I encouraged someone to go to the clinic.” However, there is no explicit referral, appointment setting, or accompanying, so alignment is moderate rather than strong. | Community Empowerment Through Education: The CHW explicitly describes educating teenagers about HIV testing and PREP, including detailed information on who should take PREP, how it is administered, and its limitations. This is direct, proactive health education aimed at improving community health practices, fitting squarely within the concept’s definition and inclusion criteria. | Handing out Medical Supplies : The CHW educates teenagers about PrEP and encourages them to obtain it, but there is no explicit mention of physically distributing PrEP or any other medical supplies. This shows only minimal, indirect alignment with the concept of handing out medical supplies.</t>
+          <t>[Group Based Health Education] The CHW states, “I educated the teens…” following a World AIDS Day celebration, implying education delivered to multiple teenagers at once, which suggests a group context. However, the narrative does not explicitly describe a structured group session (e.g., a workshop or group discussion) nor specify the size of the audience, so evidence of active facilitation in a group setting is moderate rather than definitive. [Individualized Support and Health Education] The testimonial mainly describes group education provided to multiple teenagers (“I educated the teens…”, “I encouraged the teens to go for PREP”). Although a few teens disclosed having multiple partners, the advice offered (use of PREP) remains generic rather than tailored to a specific individual’s unique circumstances. Therefore, only weak evidence of truly individualized support is present. [Cholera Education and Prevention] The testimonial focuses on HIV/AIDS prevention and PrEP education with no mention of cholera, water safety, sanitation, or related topics. According to the exclusion criteria, general health education not referencing cholera scores 0.0. [Direct Intervention for Cholera Cases] The testimonial discusses HIV education and PrEP for teenagers, without any mention of cholera cases or direct care for cholera patients. Therefore the concept does not apply. [Diabetes Education and Prevention] The testimonial focuses solely on HIV/AIDS prevention and PrEP education; there is no mention of diabetes, diet, exercise, or blood-sugar awareness, so the diabetes concept is not applicable. [HIV/AIDS Education and Prevention] The CHW explicitly describes educating teens about HIV testing, partner testing, and the use of PrEP as a prevention method. They clarify who should take PrEP, its effectiveness timeline, and its limitations—activities that align directly with HIV/AIDS awareness, prevention, and stigma reduction. This is an unambiguous, detailed match to the concept’s definition and inclusion criteria. [Infectious Disease Prevention] The CHW is providing education aimed at preventing HIV transmission, which is indeed a communicable disease. However, the concept definition emphasizes broad, non-disease-specific hygiene or sanitation advice, whereas this testimonial focuses narrowly on a single condition (HIV) and a specific biomedical intervention (PrEP). Therefore alignment is only partial and merits a low score. [Tuberculosis Education and Prevention] The testimonial discusses HIV/AIDS testing and PrEP usage, with no mention of tuberculosis symptoms, transmission, or prevention. According to the exclusion criteria, education about other infectious diseases without TB reference does not qualify.</t>
         </is>
       </c>
     </row>
@@ -1884,22 +1994,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.0,
-  "Referrals and Advocacy": 0.2,
-  "Community Empowerment Through Education": 0.9,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.8,
+  "Individualized Support and Health Education": 0.7,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.9,
+  "Infectious Disease Prevention": 0.8,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial describes the CHW educating teens about HIV testing and PREP, but contains no evidence that the CHW personally received any training. The narrative focuses entirely on the CHW's educational activities without mentioning attending workshops, completing courses, or receiving mentorship that enhanced their capacity to serve. | Referrals and Advocacy: The testimonial primarily focuses on health education about HIV testing and PrEP. While the CHW encourages teens to go for HIV tests and suggests PrEP as a solution, there is no mention of actual referrals, appointments, or direct system navigation. The CHW provides advice and education but doesn't describe facilitating connections to services or advocating within the healthcare system. This aligns with the example 'I told people they should consider family planning' → 0.2. | Community Empowerment Through Education: Strong direct alignment. The CHW explicitly states 'I educated the teens on the importance of going for HIV tests' and 'I educated the teens how PREP is used' with detailed explanations about what PREP is, who can use it, and how it works. The testimonial shows active knowledge sharing through education about HIV testing and prevention methods to a specific group (teenagers), which directly aligns with the concept definition of providing health education to help community members gain knowledge to improve health practices. | Handing out Medical Supplies : The testimonial describes educating teenagers about HIV testing and PREP (pre-exposure prophylaxis), but there is no mention of physically distributing or handing out any medical supplies. The CHW's activities are focused on education, counseling, and advising teens to seek PREP from appropriate sources, not on the distribution of medical supplies themselves.</t>
+          <t>[Group Based Health Education] The CHW conducted education sessions with teenagers about HIV/AIDS and PREP. The use of 'educated the teens' (plural) and the context of following up after World AIDS Day celebration suggests group settings. The interactive nature where 'some teenagers shared with me' indicates group discussions where the CHW actively facilitated. While not explicitly stating group size or formal session structure, the testimonial strongly implies collective education sessions with multiple teenagers. [Individualized Support and Health Education] The testimonial shows moderate alignment with individualized support. While the CHW begins with general education about HIV testing after World AIDS Day, they adapt their approach based on specific feedback from teens about partner resistance. The CHW provides personalized guidance by recommending PrEP specifically to teens who disclosed having multiple partners, showing responsiveness to individual circumstances. However, much of the content remains general health education about PrEP usage rather than deeply personalized care plans for specific individuals. [Cholera Education and Prevention] The testimonial focuses exclusively on HIV/AIDS education, PREP medication, and teenage pregnancy prevention. There is no mention of cholera, water safety, sanitation, or any cholera-related symptoms or prevention strategies. This clearly falls under the exclusion criteria as it is general health education with no reference to cholera. [Direct Intervention for Cholera Cases] The testimonial focuses entirely on teenage pregnancy and HIV/AIDS education, including promoting PREP (pre-exposure prophylaxis) for HIV prevention. There is no mention of cholera, cholera symptoms, oral rehydration, or any cholera-related interventions. The content explicitly deals with a different health condition (HIV/AIDS), which falls under the exclusion criteria of 'treating unrelated conditions.' [Diabetes Education and Prevention] The testimonial focuses entirely on HIV/AIDS prevention and teenage pregnancy education. There is no mention of diabetes, blood sugar, diet for metabolic health, or any diabetes-related risk factors. The content explicitly deals with sexual health education and HIV prevention strategies (PREP), which falls under the exclusion criteria of 'health education unrelated to diabetes.' [HIV/AIDS Education and Prevention] This testimonial demonstrates strong direct alignment with HIV/AIDS education and prevention. The CHW explicitly educated teens about HIV testing importance, provided detailed information about PrEP (pre-exposure prophylaxis) as HIV prevention, explained how PrEP works for HIV-negative individuals at high risk, and addressed the connection between teenage pregnancy and HIV risk. The education covered multiple aspects of HIV prevention including testing, medication, and risk factors, making this a near-perfect match for the concept. [Infectious Disease Prevention] Strong direct alignment. The testimonial focuses on educating teens about HIV/AIDS prevention through testing and PrEP (pre-exposure prophylaxis), which is clearly aimed at reducing the spread of a communicable disease. The CHW provides specific education on how to prevent HIV transmission, including encouraging testing with partners and explaining PrEP as a prevention method. While focused on a specific disease (HIV), the education is preventive in nature and addresses transmission reduction strategies. [Tuberculosis Education and Prevention] The testimonial focuses exclusively on HIV/AIDS education, teenage pregnancy, and PREP (pre-exposure prophylaxis for HIV prevention). There is no mention of tuberculosis, TB symptoms, TB prevention, or any TB-related topics. This clearly falls under the exclusion criteria as it discusses 'other infectious disease education without mention of TB.'</t>
         </is>
       </c>
     </row>
@@ -1917,16 +2031,20 @@
       <c r="C32" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.0,
-  "Referrals and Advocacy": 0.5,
-  "Community Empowerment Through Education": 0.85,
-  "Handing out Medical Supplies ": 0.05
+  "Group Based Health Education": 0.6,
+  "Individualized Support and Health Education": 0.2,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.3,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial discusses malaria symptoms, vaccine information, and the CHW urging prevention, but there is no mention that the CHW personally attended or received any CHW training. Therefore the concept is not present. | Referrals and Advocacy: The CHW urges people with malaria symptoms to visit health centers, which reflects encouraging care-seeking. This corresponds to the concept example “I encouraged someone to go to the clinic” (scored 0.5). There is no direct mention of making formal referrals, setting appointments, or accompanying the client, so alignment is moderate rather than strong. | Community Empowerment Through Education: The testimonial explicitly mentions a \ | Handing out Medical Supplies : The testimonial discusses malaria symptoms, vaccines, and encouragement to seek medical attention but does not describe the CHW distributing or providing any medical supplies. Very weak alignment.</t>
+          <t>[Group Based Health Education] The CHW refers to "our health education session," indicating they were facilitating some form of organized educational activity rather than a purely one-on-one encounter. However, the testimonial only cites a single client’s comments and does not explicitly state that multiple participants were present, so the evidence that it was truly a group session is moderate but not definitive. Thus, the concept is partially, but not strongly, supported. [Individualized Support and Health Education] The testimonial mentions talking with an individual client, but it only recounts the client’s symptoms and then gives a generic recommendation (“visit health centers whenever they experience such symptoms”). There is no clear evidence of tailored advice or support specific to that client’s situation. Thus, only minimal alignment with individualized support is present. [Cholera Education and Prevention] The testimonial exclusively discusses malaria, its symptoms, vaccine introduction, and advice on seeking medical attention. There is no mention of cholera, its prevention, hygiene practices, or related education, so the concept does not apply. [Direct Intervention for Cholera Cases] The testimonial discusses malaria experiences and prevention; there is no mention of cholera cases or any direct care actions related to cholera. Therefore, the concept is not applicable. [Diabetes Education and Prevention] The testimonial exclusively discusses malaria symptoms, vaccination, and prevention, with no mention of diabetes, its risk factors, or related education. Per the exclusion criteria, health education unrelated to diabetes should receive a score of 0. [HIV/AIDS Education and Prevention] The testimonial focuses exclusively on malaria symptoms, vaccination, and prevention with no reference to HIV/AIDS education, testing, or stigma reduction. According to the exclusion criteria, general health education without HIV/AIDS mention should receive a score near 0. [Infectious Disease Prevention] The testimonial discusses preventing a single disease (malaria) by vaccination and seeking treatment when symptomatic. The concept definition emphasizes broad, non-disease-specific hygiene or sanitation measures. Because the advice is narrowly focused on malaria rather than general communicable-disease prevention practices, alignment is weak but not entirely absent, warranting a low score. [Tuberculosis Education and Prevention] The testimonial discusses malaria symptoms, prevention, and vaccination with no mention of tuberculosis. According to the exclusion criteria, education about other infectious diseases without TB reference does not apply.</t>
         </is>
       </c>
     </row>
@@ -1938,22 +2056,26 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.0,
-  "Referrals and Advocacy": 0.2,
-  "Community Empowerment Through Education": 0.8,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.9,
+  "Individualized Support and Health Education": 0.2,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.3,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial contains no evidence that the CHW received any training. While the CHW mentions conducting health education sessions and identifies as a CHW who urges people to seek medical care, there is no mention of attending, completing, or receiving any CHW training, workshops, or educational experiences that enhanced their capacity to serve. The testimonial focuses on malaria symptoms and personal experiences with the disease rather than any training received. | Referrals and Advocacy: The testimonial shows minimal evidence of referrals and advocacy. While the CHW mentions urging people to 'visit health centers whenever they experience such symptoms,' this is general health advice rather than active system navigation. The client's story mentions she 'went to seek medical attention,' but there's no indication the CHW facilitated this referral or provided any advocacy support. This aligns with the example 'I told people they should consider family planning' → 0.2, as both involve general recommendations without direct CHW involvement in connecting people to services. | Community Empowerment Through Education: The testimonial provides strong evidence of health education delivery. The CHW explicitly mentions conducting a 'health education session' where they met with a client and discussed malaria experiences. The final sentence shows the CHW actively educates people ('we urge people to prevent themselves from malaria by visiting health centers'), demonstrating knowledge sharing about seeking medical care. While the testimonial focuses heavily on describing malaria symptoms and personal experiences, it clearly indicates the CHW conducts educational sessions and provides guidance to community members. | Handing out Medical Supplies : The testimonial focuses entirely on malaria symptoms, personal experiences with the disease, and health education activities. There is no mention of distributing, providing, or handing out any medical supplies, medications, or materials. The CHW discusses educating people and urging them to visit health centers, but does not describe giving out any physical medical items.</t>
+          <t>[Group Based Health Education] The testimonial explicitly mentions 'our health education session' where the CHW met with a client, indicating a structured educational setting. The use of 'our' suggests a group context, and the CHW discusses educating 'people' (plural) about malaria prevention. This aligns strongly with the concept definition of facilitating health education in group settings. [Individualized Support and Health Education] While the CHW discusses a specific client's malaria experience during a health education session, the support described is general rather than personalized. The CHW recounts the client's symptoms and shares their own experience, but provides only generic advice to 'visit health centers whenever they experience such symptoms.' There is no evidence of tailored guidance, adapted care plans, or individualized recommendations based on this client's specific needs or circumstances. [Cholera Education and Prevention] The testimonial focuses entirely on malaria education, prevention, and personal experiences with malaria. There is no mention of cholera, cholera symptoms, water purification, sanitation practices, or any cholera-related prevention strategies. This is clearly general health education about malaria, which falls under the exclusion criteria. [Direct Intervention for Cholera Cases] The testimonial exclusively discusses malaria - its symptoms, prevention through vaccination, and personal experiences with the disease. There is no mention of cholera, cholera symptoms, or any cholera-related interventions. The exclusion criteria explicitly states 'treating unrelated conditions (e.g., malaria, TB)' which directly applies here. [Diabetes Education and Prevention] The testimonial is entirely focused on malaria - its symptoms, vaccine, prevention, and personal experiences with the disease. There is no mention of diabetes, blood sugar, diet in relation to metabolic health, or any diabetes-related risk factors. The health education described is specifically about malaria prevention and seeking medical attention for malaria symptoms, which falls under the exclusion criteria of 'health education unrelated to diabetes'. [HIV/AIDS Education and Prevention] The testimonial focuses entirely on malaria education, symptoms, and prevention. There is no mention of HIV/AIDS, HIV transmission, testing, or any HIV-related topics. This clearly falls under the exclusion criteria of 'general health education without a reference to HIV/AIDS.' [Infectious Disease Prevention] The testimonial focuses primarily on describing malaria symptoms and personal experiences with the disease rather than prevention education. While the CHW mentions 'we urge people to prevent themselves from malaria by visiting health centers,' this is more about seeking treatment than preventing transmission. The content lacks general hygiene education, sanitation practices, or advice on preventing disease spread that would align with the concept definition. [Tuberculosis Education and Prevention] This testimonial focuses exclusively on malaria education, symptoms, and prevention. There is no mention of tuberculosis, TB symptoms, TB transmission, or TB prevention. The content clearly falls under the exclusion criteria as it discusses 'other infectious disease education without mention of TB.'</t>
         </is>
       </c>
     </row>
@@ -1971,16 +2093,20 @@
       <c r="C34" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.0,
-  "Referrals and Advocacy": 0.5,
-  "Community Empowerment Through Education": 0.7,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.05,
+  "Individualized Support and Health Education": 0.9,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.0,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: Testimonial mentions the CHW having limited knowledge about fibroids but gives no indication that this knowledge came from any CHW training, course, or mentorship. Therefore, there is no evidence of the CHW being empowered through training. | Referrals and Advocacy: The CHW encourages the woman to start seeking treatment and plans to follow up, showing some advocacy/navigation of care but no explicit referral or appointment-setting. This aligns with the example “I encouraged someone to go to the clinic” (moderate alignment), so a mid‐range score is appropriate. | Community Empowerment Through Education: The CHW shared health information with the woman, explaining that fibroids are non-cancerous and encouraging her to seek treatment. This one-on-one explanation fits the inclusion criteria for providing health education, but the encounter was brief and limited in scope, so alignment is moderate rather than perfect. | Handing out Medical Supplies : The testimonial describes providing emotional support and health education about fibroids; there is no mention of distributing medicines, equipment, or other medical supplies.</t>
+          <t>[Group Based Health Education] The testimonial describes one-on-one counseling of a single woman about fibroids. There is no indication of a group session or collective education, which is required for the Group Based Health Education concept. This minimally aligns, so a very low score is assigned. [Individualized Support and Health Education] The CHW provided one-on-one reassurance and information to a specific woman about her fibroids, addressed her personal fears, encouraged treatment, and plans follow-up emotional support. This is clearly personalized guidance rather than generic education, matching the concept’s definition and inclusion criteria. [Cholera Education and Prevention] The testimonial discusses supporting a woman with fibroids and boosting her self-esteem; it contains no information or education related to cholera awareness, prevention, symptoms, or hygiene practices. Therefore, the concept is not applicable. [Direct Intervention for Cholera Cases] The testimonial describes providing emotional support to a woman with fibroids, an unrelated condition. There is no mention of cholera, dehydration management, ORS, or referral for cholera treatment, which are required for this concept. [Diabetes Education and Prevention] The testimonial discusses counseling a woman about uterine fibroids and reassuring her they are non-cancerous. There is no content related to diabetes, its risk factors, prevention, or lifestyle education. Therefore the concept does not apply. [HIV/AIDS Education and Prevention] The testimonial concerns counseling a woman about fibroids and reassuring her they are non-cancerous. There is no mention of HIV/AIDS, prevention, testing, or related education, so the concept is not present. [Infectious Disease Prevention] The testimonial discusses supporting a woman with fibroids, a non-communicable condition. It contains no education or advice about preventing the spread of infectious diseases, hygiene, or sanitation. [Tuberculosis Education and Prevention] The testimonial discusses counseling a woman about fibroids and her self-esteem. There is no mention of tuberculosis symptoms, transmission, prevention, or treatment, so the concept does not apply.</t>
         </is>
       </c>
     </row>
@@ -1992,22 +2118,26 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.0,
-  "Referrals and Advocacy": 0.2,
-  "Community Empowerment Through Education": 0.7,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.0,
+  "Individualized Support and Health Education": 0.9,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.0,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial contains no evidence that the CHW received any training. The CHW explicitly states 'I don't know much about fibroids' and only used 'the little I know' to help the patient. There is no mention of attending CHW training, workshops, or any structured educational experience. The CHW's knowledge appears to be informal rather than from formal CHW training. | Referrals and Advocacy: The testimonial shows minimal alignment with referrals and advocacy. While the CHW provided emotional support and health education about fibroids, there is no mention of actively referring the woman to services, setting appointments, or navigating the healthcare system. The woman was already aware of her diagnosis and had seen a doctor previously. The CHW's promise to 'check up on her' suggests future support but does not constitute active system navigation or advocacy within healthcare settings. | Community Empowerment Through Education: The CHW actively shared knowledge by explaining that fibroids are non-cancerous growths, helping correct the woman's misconception that she had untreatable cancer. This educational intervention directly addressed her health understanding and motivated her to seek treatment. While the CHW admits limited knowledge about fibroids, they still provided crucial health education that empowered the woman to change her perspective and health-seeking behavior. The score is moderate (0.7) rather than higher because the education was limited in scope and the CHW acknowledged incomplete knowledge of the topic. | Handing out Medical Supplies : The testimonial describes a CHW providing emotional support and health education to a woman with fibroids, helping her understand her condition and encouraging treatment adherence. There is no mention of distributing, delivering, or handing out any medical supplies, medications, or physical health materials. The interaction is entirely focused on counseling and information sharing.</t>
+          <t>[Group Based Health Education] This testimonial clearly describes a one-on-one interaction between the CHW and a single woman suffering from fibroids. The CHW explicitly states 'I came across this woman' and describes a personal conversation where they provided individual counseling and education. This falls under the exclusion criteria of 'one-on-one education' and there is no evidence of a group setting, making this a clear non-match for Group Based Health Education. [Individualized Support and Health Education] This testimonial demonstrates strong individualized support. The CHW provided personalized emotional support and health education to a specific woman suffering from fibroids who had low self-esteem and misconceptions about her condition. The CHW adapted their approach to address her specific fears (believing she had cancer), provided reassurance tailored to her concerns, and committed to ongoing personalized follow-up 'to lift up her spirits.' This goes beyond generic health education to provide care specifically adapted to this individual's emotional and informational needs. [Cholera Education and Prevention] This testimonial describes a CHW counseling a woman about fibroids, a non-cancerous growth condition. There is no mention of cholera, cholera prevention, water safety, sanitation, or any cholera-related symptoms or education. The testimonial clearly falls under the exclusion criteria as it contains general health education with no reference to cholera. [Direct Intervention for Cholera Cases] The testimonial describes a CHW providing emotional support and health education to a woman suffering from fibroids, not cholera. There is no mention of cholera symptoms, cases, or cholera-related interventions. This clearly falls under the exclusion criteria as it involves treating an unrelated condition (fibroids). [Diabetes Education and Prevention] The testimonial focuses entirely on counseling a woman about fibroids, which is a gynecological condition unrelated to diabetes. There is no mention of diabetes education, prevention, blood sugar, diet, exercise, or any metabolic health topics. This clearly falls under the exclusion criteria as 'health education unrelated to diabetes.' [HIV/AIDS Education and Prevention] The testimonial focuses entirely on educating a woman about fibroids, explaining they are non-cancerous growths. There is no mention of HIV/AIDS, transmission, testing, prevention methods, or any HIV-related topics. This falls under the exclusion criteria as it represents general health education without reference to HIV/AIDS. [Infectious Disease Prevention] The testimonial focuses entirely on counseling a woman about fibroids, which are non-cancerous growths and a non-communicable condition. There is no mention of hygiene education, sanitation practices, or preventing transmission of infectious diseases. This clearly falls under the exclusion criteria as it deals with non-communicable disease education. [Tuberculosis Education and Prevention] The testimonial exclusively discusses fibroids and cancer concerns with no mention of tuberculosis, TB symptoms, transmission, or prevention. The CHW provides education about fibroids being non-cancerous, which falls under general health education but is completely unrelated to TB education and prevention.</t>
         </is>
       </c>
     </row>
@@ -2025,16 +2155,20 @@
       <c r="C36" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.1,
-  "Referrals and Advocacy": 0.0,
-  "Community Empowerment Through Education": 0.9,
-  "Handing out Medical Supplies ": 0.05
+  "Group Based Health Education": 0.05,
+  "Individualized Support and Health Education": 0.9,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.0,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial describes the CHW providing first-aid advice for a nosebleed, but it never states that the CHW attended or received any training that enabled this knowledge. Because evidence of received CHW training is required and is only implicitly assumed (if at all), alignment with the concept is very weak. | Referrals and Advocacy: The testimonial only describes providing first-aid instructions for a nosebleed—general health advice with no mention of referring the patient to services, setting appointments, accompanying them, or advocating within the health system. This fits the exclusion criteria, so the concept is not present. | Community Empowerment Through Education: The CHW explicitly taught a patient several step-by-step techniques to stop a nosebleed (pinching nose, leaning forward, applying ice, staying upright). This is direct one-on-one health education that enabled the patient to manage her condition, fitting the inclusion criteria for Community Empowerment Through Education. No purely clinical action without explanation is described, so alignment is strong and unambiguous, warranting a high score (0.9). | Handing out Medical Supplies : The testimonial describes giving first-aid advice for managing a nosebleed, with no mention of actually distributing or providing any medical supplies to the patient. Therefore, alignment with the concept of 'Handing out Medical Supplies' is minimal.</t>
+          <t>[Group Based Health Education] The testimonial describes educating a single patient about first-aid for nosebleeds, which is explicitly excluded from the concept (one-on-one education). There is no indication of a group session or facilitated group learning. [Individualized Support and Health Education] The CHW describes meeting one patient who repeatedly experienced nosebleeds and provided step-by-step instructions tailored to that individual’s immediate problem. This is personalized, one-on-one health education rather than generic or group advice, fitting the concept’s inclusion criteria. [Cholera Education and Prevention] The testimonial discusses first aid for nosebleeds and contains no information or education related to cholera symptoms, transmission, or prevention. Therefore it does not align with the Cholera Education and Prevention concept. [Direct Intervention for Cholera Cases] The testimonial describes providing first‐aid instructions for a nosebleed, which is unrelated to cholera. The concept specifically concerns direct care for suspected or confirmed cholera cases; treating an unrelated condition is explicitly excluded. [Diabetes Education and Prevention] The testimonial is exclusively about first-aid measures for a nosebleed and contains no information or education related to diabetes awareness, prevention, diet, exercise, or blood sugar monitoring. Therefore it does not align with the Diabetes Education and Prevention concept. [HIV/AIDS Education and Prevention] The testimonial discusses first-aid steps for nosebleeds and contains no information about HIV/AIDS transmission, prevention, testing, or stigma. Therefore, the concept is not present. [Infectious Disease Prevention] The testimonial focuses on first-aid steps to control an individual’s nosebleed, not on preventing transmission of communicable diseases or providing hygiene education. Therefore it does not align with the infectious disease prevention concept. [Tuberculosis Education and Prevention] The testimonial discusses first-aid steps for managing a nosebleed and does not mention tuberculosis symptoms, transmission, treatment, or testing. Therefore, it does not align with the concept of Tuberculosis Education and Prevention.</t>
         </is>
       </c>
     </row>
@@ -2046,22 +2180,26 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.0,
-  "Referrals and Advocacy": 0.0,
-  "Community Empowerment Through Education": 0.8,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.0,
+  "Individualized Support and Health Education": 0.8,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.0,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial describes a CHW providing first aid advice for nosebleeds to a patient, but contains no evidence that the CHW received any training. There is no mention of attending courses, workshops, or any structured educational experience. The CHW demonstrates knowledge and helps a patient, but this falls under the exclusion criteria of 'outcomes or competence without mention of received training.' | Referrals and Advocacy: The testimonial describes providing first aid instructions for nosebleeds but contains no evidence of referrals, appointments, accompanying to care, or advocating within the health system. The CHW only provided direct health education and self-care advice without any system navigation or connection to healthcare services. | Community Empowerment Through Education: Strong direct alignment. The CHW clearly provided detailed health education to a patient about managing nosebleeds, including specific step-by-step instructions (pinching nose, leaning forward, using ice, staying upright). The testimonial shows active knowledge sharing through explanation and practical guidance, resulting in the patient learning how to manage the condition independently. This aligns well with the concept's definition of CHWs helping community members gain knowledge to improve health practices. | Handing out Medical Supplies : The testimonial describes providing first aid instructions and guidance for managing nosebleeds, but does not mention distributing, giving, or handing out any medical supplies or materials. The CHW only provided verbal advice and demonstration of techniques using items the patient already had (ice, towel). Since no medical supplies were distributed, this concept is not present.</t>
+          <t>[Group Based Health Education] This testimonial clearly describes a one-on-one interaction between the CHW and a single patient who had recurring nosebleeds. The CHW states 'I came across a patient' and 'I told her,' indicating individual instruction rather than group education. This falls under the exclusion criteria of 'one-on-one education' and therefore does not align with the concept of Group Based Health Education. [Individualized Support and Health Education] This testimonial demonstrates strong personalized support. The CHW provided one-on-one guidance to a specific patient who experienced recurring nose bleeds and 'did not know what to do.' The CHW tailored their intervention to this individual's specific problem, provided detailed personalized instruction, and followed up to note the patient's improvement ('she got relieved... nose bleed occurring rarely'). While the advice itself is standard first aid, the delivery was clearly adapted to this individual's needs and situation, similar to the example of helping a pregnant woman with personalized explanations (0.8). [Cholera Education and Prevention] The testimonial describes providing first aid education for nose bleeds with no mention of cholera, water safety, sanitation, or any cholera-related topics. This falls under the exclusion criteria of 'general health education with no reference to cholera.' [Direct Intervention for Cholera Cases] The testimonial describes providing first aid for nosebleeds, which is completely unrelated to cholera. There is no mention of cholera symptoms, dehydration, ORS administration, or any cholera-related care. This falls under the exclusion criteria of 'treating unrelated conditions.' [Diabetes Education and Prevention] This testimonial is entirely focused on providing first aid instructions for nosebleeds. There is no mention of diabetes, blood sugar, diet, exercise, or any metabolic health topics. The content is exclusively about managing nosebleeds, which falls under general first aid education and is unrelated to diabetes prevention or education. [HIV/AIDS Education and Prevention] The testimonial describes providing first aid education for nosebleeds. There is no mention of HIV/AIDS, transmission, testing, prevention methods, or any HIV-related topics. This is general health education explicitly excluded by the concept definition. [Infectious Disease Prevention] The testimonial describes first aid treatment for nosebleeds, which is not related to infectious disease prevention. Nosebleeds are not a communicable disease, and the advice given (pinching nose, using ice, positioning) is medical first aid rather than hygiene or disease transmission prevention education. This clearly falls outside the concept's definition and inclusion criteria. [Tuberculosis Education and Prevention] The testimonial describes providing first aid education for nosebleeds, with no mention of tuberculosis, TB symptoms, transmission, prevention, or any TB-related topics. This clearly falls under the exclusion criteria as it discusses a different health issue entirely.</t>
         </is>
       </c>
     </row>
@@ -2079,16 +2217,20 @@
       <c r="C38" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.0,
-  "Referrals and Advocacy": 0.05,
-  "Community Empowerment Through Education": 0.65,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.05,
+  "Individualized Support and Health Education": 0.8,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.6,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.0,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial describes the CHW advising a community member on obesity but contains no mention of the CHW having attended or received any training. Therefore, the concept is not present. | Referrals and Advocacy: The CHW only provided lifestyle advice (exercise and diet) without helping the woman navigate the health system or referring her to services, which falls under the exclusion criteria. Virtually no advocacy or referral activity is described. | Community Empowerment Through Education: The CHW gave the woman advice on managing obesity through exercise, diet change, and faith—directly sharing health knowledge to improve practices. This is one-on-one health education, matching the concept’s inclusion criteria. The interaction is brief and lacks detail of broader instruction, so alignment is moderate (similar to the 0.6 ORS example). | Handing out Medical Supplies : The testimonial describes giving lifestyle advice (exercise, diet, faith) to address obesity; there is no mention of distributing or providing any medical supplies, so the concept does not apply.</t>
+          <t>[Group Based Health Education] The testimonial describes a one-on-one interaction with a single woman about obesity, fitting the exclusion criteria for individual counseling. There is no indication the CHW facilitated a group session, so only a minimal score is assigned. [Individualized Support and Health Education] The CHW interacts with one woman who is struggling with obesity and offers personalized guidance—advice on exercise, diet change, and maintaining faith—tailored to her specific situation. This fits the inclusion criteria of one-on-one, individualized support rather than generic community education, aligning strongly with the concept. [Cholera Education and Prevention] The testimonial discusses advising a woman on obesity, exercise, and diet. There is no mention of cholera, hygiene, water safety, or related prevention education. Therefore the concept is not present. [Direct Intervention for Cholera Cases] The testimonial discusses advising a client on obesity management through exercise and diet. There is no mention of cholera, dehydration, ORS, or any intervention for suspected/confirmed cholera cases. Therefore the concept does not apply. [Diabetes Education and Prevention] The CHW counsels a woman on exercise and diet to address obesity. While diabetes is not explicitly named, the advice targets modifiable lifestyle factors (diet, physical activity) that fall under the concept’s inclusion of ‘risk factors, dietary changes, exercise, or general metabolic health.’ Because the link to diabetes prevention is implicit rather than explicit, alignment is moderate, not strong. [HIV/AIDS Education and Prevention] The testimonial discusses advising a woman about obesity, diet, and exercise with no mention of HIV/AIDS, transmission, testing, or related education, so the concept is not present. [Infectious Disease Prevention] The testimonial focuses exclusively on advising a client about obesity, a non-communicable condition. The concept explicitly excludes education related to non-communicable diseases, so no evidence of infectious-disease prevention is present. [Tuberculosis Education and Prevention] The testimonial discusses obesity management through diet and exercise with no mention of tuberculosis symptoms, transmission, testing, or treatment guidance. Therefore, the concept does not apply.</t>
         </is>
       </c>
     </row>
@@ -2100,22 +2242,26 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.0,
-  "Referrals and Advocacy": 0.1,
-  "Community Empowerment Through Education": 0.7,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.0,
+  "Individualized Support and Health Education": 0.8,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.6,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.0,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial contains no evidence that the CHW received any training. While the CHW provides health advice about obesity management (exercise and diet), there is no mention of having attended CHW training, workshops, or any structured educational experience. The CHW's knowledge and advice-giving alone, without reference to received training, falls under the exclusion criteria. | Referrals and Advocacy: The testimonial shows minimal alignment with referrals and advocacy. The CHW provides direct health advice (exercise and diet change) but does not mention referring the woman to healthcare services, setting appointments, or navigating the health system. This is similar to the example 'I told people they should consider family planning' (0.2), as it involves giving advice without system navigation or referral components. | Community Empowerment Through Education: The CHW actively provided health education by explaining to the woman that 'the only thing she needed was exercise and a change of diet.' This represents direct knowledge sharing about proper weight management approaches, moving away from ineffective remedies. The score is moderate (0.7) rather than higher because the education was brief and focused on general advice rather than detailed instruction or demonstration of specific exercises or dietary plans. | Handing out Medical Supplies : The testimonial describes a CHW providing advice about exercise and diet changes to address obesity, but contains no mention of distributing, handing out, or providing any medical supplies. The interaction is purely consultative and educational in nature.</t>
+          <t>[Group Based Health Education] This testimonial clearly describes a one-on-one interaction between the CHW and a single woman seeking help for obesity. The CHW provided individual counseling about exercise and diet change. This explicitly falls under the exclusion criteria of 'One-on-one education' and contains no evidence of group facilitation, workshops, or collective learning settings. [Individualized Support and Health Education] The CHW provided personalized guidance to a specific woman struggling with obesity, adapting advice to her unique situation after learning about her failed attempts with various remedies. The one-on-one counseling included tailored recommendations for exercise and dietary changes, showing strong alignment with individualized support despite not detailing the specific personalized plan. [Cholera Education and Prevention] The testimonial focuses entirely on obesity counseling, discussing diet, exercise, and weight loss strategies. There is no mention of cholera, cholera symptoms, water sanitation, hygiene practices, or any cholera-related prevention education. This clearly falls under the exclusion criteria as it represents general health education with no reference to cholera. [Direct Intervention for Cholera Cases] The testimonial describes a CHW counseling a woman about obesity through diet and exercise recommendations. There is no mention of cholera, cholera symptoms, oral rehydration, or any cholera-related interventions. The health issue addressed (obesity) is completely unrelated to cholera, meeting the exclusion criteria of 'treating unrelated conditions.' [Diabetes Education and Prevention] The testimonial shows moderate alignment with diabetes education and prevention. While the CHW provides health counseling about diet and exercise (key components of diabetes prevention), the focus is specifically on obesity management rather than diabetes education. Since obesity is a major risk factor for diabetes and the advice given (diet change and exercise) directly relates to diabetes prevention strategies, there is partial alignment. However, there is no explicit mention of diabetes, blood sugar, or metabolic health education, which prevents a higher score. [HIV/AIDS Education and Prevention] The testimonial focuses entirely on obesity counseling, discussing diet, exercise, and weight loss methods. There is no mention of HIV/AIDS, HIV transmission, testing, prevention methods, or any HIV-related topics. This clearly falls under the exclusion criteria of 'general health education without a reference to HIV/AIDS.' [Infectious Disease Prevention] The testimonial focuses entirely on obesity, which is a non-communicable disease. The CHW provides advice on diet and exercise for weight management, not on preventing the spread of infectious diseases. This falls under the exclusion criteria as non-communicable disease education. [Tuberculosis Education and Prevention] The testimonial focuses entirely on obesity counseling, with no mention of tuberculosis, TB symptoms, transmission, prevention, or treatment. The CHW discusses diet, exercise, and weight management strategies, which falls under the exclusion criteria as it involves health education without any reference to TB.</t>
         </is>
       </c>
     </row>
@@ -2133,16 +2279,20 @@
       <c r="C40" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.1,
-  "Referrals and Advocacy": 1.0,
-  "Community Empowerment Through Education": 0.2,
-  "Handing out Medical Supplies ": 0.2
+  "Group Based Health Education": 0.0,
+  "Individualized Support and Health Education": 0.8,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.1,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial shows the CHW correctly recognized malaria symptoms and facilitated care, but there is no mention that this ability came from training the CHW received. Competence without explicit reference to training only weakly suggests the concept. | Referrals and Advocacy: The CHW recognized malaria symptoms, took the client to the hospital for testing and treatment, and ensured completion of the medication—clear, unambiguous evidence of accompanying and advocating for the client within the health system, fitting the inclusion criteria for referrals and advocacy. | Community Empowerment Through Education: The testimonial mainly describes escorting a patient to the hospital and ensuring medication adherence. There is only an implied reminder to finish the antimalarial dose, with no clear description of teaching, explaining, or broader health education. This provides minimal evidence of active knowledge sharing, yielding a weak alignment with the concept. | Handing out Medical Supplies : The CHW accompanied the client to a health facility where antimalarial drugs were provided, but the testimonial does not describe the CHW personally distributing or supplying the medication. This is only an indirect connection to handing out medical supplies, so alignment is weak.</t>
+          <t>[Group Based Health Education] The testimonial describes assisting a single sick client and accompanying her to the hospital; there is no mention of the CHW facilitating any group health education session. This is a one-on-one interaction, which is explicitly excluded from the concept. [Individualized Support and Health Education] The CHW responded to a single client at night, assessed her symptoms, transported her to the hospital, and personally ensured she finished the antimalarial treatment—actions that constitute one-on-one, tailored support and follow-up care. This matches the inclusion criteria of individualized guidance adapted to an individual’s situation, though explicit health education is only implicit, so the score is strong but not perfect. [Cholera Education and Prevention] The testimonial describes identifying and facilitating treatment for a malaria case. There is no mention of cholera, education about cholera, or preventive hygiene practices related to cholera. Therefore the concept is not present. [Direct Intervention for Cholera Cases] The testimonial describes assisting a client with malaria, not cholera. Treating unrelated conditions is explicitly excluded from this concept. [Diabetes Education and Prevention] The testimonial focuses exclusively on identifying and facilitating treatment for malaria; there is no discussion of diabetes, its risk factors, or preventive education. Therefore the concept is not present. [HIV/AIDS Education and Prevention] The testimonial solely discusses identifying and treating a malaria case; there is no mention of HIV/AIDS education, prevention, testing, or related activities. [Infectious Disease Prevention] The testimonial centers on identifying a malaria case, taking the client to the hospital, and ensuring medication adherence—activities related to treatment rather than preventive education. Although malaria is an infectious disease, there is no mention of hygiene, vector control, or other advice aimed at preventing transmission, so only minimal relevance to the prevention concept exists. [Tuberculosis Education and Prevention] The testimonial focuses solely on malaria—recognizing malaria symptoms, taking the client for testing, and ensuring completion of antimalarial treatment. Tuberculosis is not mentioned, so the concept is not applicable.</t>
         </is>
       </c>
     </row>
@@ -2154,22 +2304,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.2,
-  "Referrals and Advocacy": 0.9,
-  "Community Empowerment Through Education": 0.1,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.0,
+  "Individualized Support and Health Education": 0.7,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.1,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial describes a CHW recognizing malaria symptoms and facilitating hospital care, but contains no explicit mention of receiving CHW training. While the CHW demonstrates competence in identifying symptoms and ensuring medication compliance, these actions alone do not provide evidence of formal or informal training received. The concept requires clear reference to the CHW having attended or completed training, which is absent from this testimonial. | Referrals and Advocacy: Strong direct alignment with the concept. The CHW explicitly states 'I took her to the nearest hospital for medication' which demonstrates direct involvement in system navigation by physically accompanying the client to care. The CHW also ensured follow-up by making sure the client completed the prescribed medication. This closely matches the example 'I identified disease symptoms and referred the person for testing' which scores 0.9. | Community Empowerment Through Education: The testimonial describes a CHW responding to a medical emergency and facilitating hospital care, but contains no evidence of education or knowledge sharing. The CHW recognized symptoms, transported the patient, and ensured medication compliance, but there's no mention of explaining malaria prevention, symptoms, or treatment to the patient or community. This aligns with the exclusion criteria of 'purely clinical tasks without any explanation or teaching.' | Handing out Medical Supplies : The testimonial describes a CHW responding to a malaria case and taking the patient to a hospital where medication was provided by medical staff. The CHW ensured medication compliance but did not personally hand out medical supplies. The drugs were given by the hospital/doctor, not distributed by the CHW.</t>
+          <t>[Group Based Health Education] The testimonial describes a one-on-one emergency response to a malaria case, with the CHW visiting a single client at night and taking them to the hospital. There is no mention of group settings, health education sessions, workshops, or collective learning activities. This is explicitly excluded by the concept's exclusion criteria which states 'One-on-one education.' [Individualized Support and Health Education] The testimonial shows moderate alignment with individualized support. The CHW responded to a specific client's nighttime call, assessed her individual symptoms, accompanied her to the hospital, and followed up to ensure she completed her medication regimen. This demonstrates personalized care and support adapted to one person's needs. However, the score is not higher because there's no evidence of tailored education or advice beyond ensuring medication compliance, and the support provided was primarily clinical assistance rather than customized health education. [Cholera Education and Prevention] The testimonial focuses entirely on malaria identification and treatment, with no mention of cholera, water sanitation, hygiene practices, or any cholera-related education. This clearly falls under the exclusion criteria as it deals with a different disease entirely. [Direct Intervention for Cholera Cases] The testimonial explicitly describes a malaria case, not cholera. The CHW responds to malaria symptoms (shivering, fever, headache) and facilitates malaria testing and antimalarial treatment. This falls under the exclusion criteria of 'treating unrelated conditions (e.g., malaria, TB)' with no mention of cholera, diarrhea, dehydration, or ORS. [Diabetes Education and Prevention] The testimonial exclusively describes a malaria case - symptoms, diagnosis, and treatment. There is no mention of diabetes education, prevention, diet, exercise, or metabolic health. This clearly falls under the exclusion criteria as it is health-related work unrelated to diabetes. [HIV/AIDS Education and Prevention] The testimonial focuses exclusively on a malaria case - identifying symptoms, facilitating hospital care, and ensuring medication compliance. There is no mention of HIV/AIDS education, prevention, testing, or any HIV-related activities, clearly placing this outside the concept's scope. [Infectious Disease Prevention] This testimonial describes responding to an active malaria case and ensuring treatment, but does not mention any prevention education or advice. The CHW focused on recognizing symptoms, facilitating treatment, and ensuring medication compliance rather than teaching prevention strategies like bed net use or mosquito control. This represents minimal alignment with the concept definition. [Tuberculosis Education and Prevention] The testimonial exclusively discusses malaria - its symptoms (shivering, cold, high temperature, headache, sweating), testing, and treatment with antimalarial drugs. There is no mention of tuberculosis, TB symptoms, TB prevention, or any TB-related education. This falls under the exclusion criteria as it discusses 'other infectious disease education without mention of TB.'</t>
         </is>
       </c>
     </row>
@@ -2187,16 +2341,20 @@
       <c r="C42" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.05,
-  "Referrals and Advocacy": 0.5,
-  "Community Empowerment Through Education": 0.8,
-  "Handing out Medical Supplies ": 0.1
+  "Group Based Health Education": 0.2,
+  "Individualized Support and Health Education": 0.25,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.6,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial describes malaria prevention actions and advice given by the CHW but contains no statement that the CHW attended or received any form of training. Therefore, there is virtually no evidence of empowerment through training. | Referrals and Advocacy: The CHW mainly provides advice—encouraging people to take preventive measures and to go for check-ups. This resembles the example “I encouraged someone to go to the clinic,” which is considered a partial match (0.5). There is no explicit mention of arranging referrals or accompanying clients, so alignment is moderate rather than strong. | Community Empowerment Through Education: The CHW describes not only practicing malaria-prevention behaviors (clearing bushes, removing breeding sites, using nets, seeking check-ups) but explicitly states, “I also advise people to do the same.” This shows active sharing of health knowledge with the community, fitting the concept’s inclusion criteria of providing education or advice. The description is brief and lacks detail about format or audience, so scored as strong but not perfect (0.8). | Handing out Medical Supplies : The CHW talks about personal practices (clearing bushes, using a treated mosquito net, seeking check-ups) and advising others to adopt similar behaviors. There is no explicit mention of giving or distributing physical items (e.g., nets, medicines) to community members. Any alignment is very tenuous, based only on the mention of using a mosquito net, not handing it out.</t>
+          <t>[Group Based Health Education] The CHW mentions that they "advise people" on malaria prevention, but there is no clear indication that this advice occurs in organized group sessions. It could just as easily be individual advice. Therefore, only weak, indirect evidence of group‐based health education is present. [Individualized Support and Health Education] The CHW describes general preventive practices for malaria (clearing bushes, sleeping under nets) and says she "advise[s] people to do the same." There is no indication that the advice is tailored to a specific individual’s circumstances; it appears generic community guidance. Therefore, only weak evidence of individualized support is present. [Cholera Education and Prevention] The testimonial discusses malaria prevention activities (clearing mosquito breeding sites, using bed nets, advising others) and does not mention cholera, its symptoms, or related hygiene practices. According to the exclusion criteria, general health education not referencing cholera does not qualify. [Direct Intervention for Cholera Cases] The testimonial discusses malaria prevention and personal experiences with malaria cases, with no mention of cholera nor any direct care actions for cholera patients. According to the concept’s exclusion criteria, treating unrelated conditions such as malaria does not qualify. [Diabetes Education and Prevention] The testimonial focuses exclusively on malaria prevention (clearing mosquito breeding sites, using bed nets, advising others about these measures). There is no mention of diabetes, its risk factors, diet, exercise, or blood sugar monitoring. Therefore the concept does not apply. [HIV/AIDS Education and Prevention] The testimonial discusses malaria prevention measures (clearing bushes, using bed nets, seeking treatment) and advising others to do the same. There is no mention of HIV/AIDS, transmission, testing, or related education. General health education about malaria is explicitly excluded from this concept, so the score is 0.0. [Infectious Disease Prevention] The CHW describes actions and advice aimed at preventing the spread of malaria (clearing mosquito breeding sites, using treated nets, encouraging check-ups). Malaria is a communicable disease, so the content fits infectious-disease prevention, but it is focused on a single condition rather than general hygiene or broad practices. Therefore the alignment is moderate rather than strong. [Tuberculosis Education and Prevention] The testimonial exclusively discusses malaria prevention and treatment practices, with no mention of TB symptoms, transmission, medication adherence, or testing. Therefore it does not align with the Tuberculosis Education and Prevention concept.</t>
         </is>
       </c>
     </row>
@@ -2208,22 +2366,26 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.0,
-  "Referrals and Advocacy": 0.2,
-  "Community Empowerment Through Education": 0.7,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.1,
+  "Individualized Support and Health Education": 0.2,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.7,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial describes the CHW's activities in malaria prevention and education but contains no evidence that the CHW received any training. The CHW discusses their practices (clearing bushes, using mosquito nets, advising others) but never mentions attending training, workshops, or any educational experience that enhanced their capacity. This aligns with the exclusion criteria of 'outcomes or competence without mention of received training.' | Referrals and Advocacy: The testimonial shows minimal alignment with referrals and advocacy. While the CHW mentions advising people to 'go for check-ups' when experiencing malaria symptoms, this is general health advice rather than active system navigation or advocacy. The CHW does not describe assisting with referrals, setting appointments, or accompanying anyone to care. The focus is primarily on prevention education (clearing bushes, using mosquito nets) rather than connecting people to healthcare services. | Community Empowerment Through Education: The testimonial shows moderate alignment with the concept. The CHW explicitly states 'I also advise people to do the same' regarding malaria prevention practices (clearing bushes, removing mosquito breeding sites, using treated nets, and seeking check-ups). This indicates active knowledge sharing with community members. However, the education component is mentioned briefly at the end without detailed examples of how the advice was given or specific teaching interactions, which prevents a higher score. | Handing out Medical Supplies : The testimonial does not mention distributing, handing out, or providing any medical supplies to community members. The CHW describes preventive activities (clearing bushes, using mosquito nets) and giving advice, but there is no evidence of distributing medical supplies, medications, or health-related materials to others.</t>
+          <t>[Group Based Health Education] The testimonial mentions 'I also advise people to do the same' which suggests educating multiple people, but provides no evidence of group sessions or structured collective learning. The CHW describes individual prevention activities and general advice-giving without any indication of facilitating group health talks, workshops, or community education sessions as defined in the concept. [Individualized Support and Health Education] The testimonial primarily describes general community-wide malaria prevention activities (clearing bushes, mosquito breeding sites) and generic advice given to 'people' without personalization. While the CHW mentions advising people, there's no evidence of tailoring this advice to individual needs, circumstances, or households. The advice appears to be the same standard recommendations given to everyone, which aligns with the exclusion criteria of 'generic or not clearly personalized' support. [Cholera Education and Prevention] The testimonial exclusively focuses on malaria prevention and education, with no mention of cholera, cholera symptoms, water purification, or cholera-related hygiene practices. The CHW discusses clearing mosquito breeding sites and using mosquito nets - all malaria-specific interventions. This clearly falls under the exclusion criteria as it is general health education with no reference to cholera. [Direct Intervention for Cholera Cases] The testimonial exclusively discusses malaria cases, prevention strategies, and health education related to malaria. There is no mention of cholera, cholera symptoms, ORS administration, or any intervention related to cholera cases. The concept explicitly excludes treating unrelated conditions like malaria. [Diabetes Education and Prevention] The testimonial focuses entirely on malaria prevention and management, including clearing mosquito breeding sites, using mosquito nets, and advising others about malaria. There is no mention of diabetes, blood sugar, diet, exercise, or any metabolic health topics. This clearly falls under the exclusion criteria as health education unrelated to diabetes. [HIV/AIDS Education and Prevention] The testimonial focuses entirely on malaria prevention and education, including clearing mosquito breeding sites, using treated nets, and seeking medical care for malaria symptoms. There is no mention of HIV/AIDS, HIV transmission, testing, or any HIV-related education activities. This clearly falls under the exclusion criteria of 'general health education without a reference to HIV/AIDS.' [Infectious Disease Prevention] The testimonial shows moderate alignment with infectious disease prevention. The CHW describes preventive measures for malaria (clearing bushes, eliminating mosquito breeding sites, using treated nets) and advises others to do the same. While malaria is a specific disease, the focus is on general prevention strategies that could apply to vector-borne diseases broadly. The score is not higher because the focus is specifically on malaria rather than communicable diseases in general. [Tuberculosis Education and Prevention] The testimonial exclusively discusses malaria prevention and education, including clearing mosquito breeding sites, using treated nets, and advising on malaria symptoms. There is no mention of tuberculosis, TB symptoms, TB transmission, or any TB-related education activities, clearly meeting the exclusion criteria of 'other infectious disease education without mention of TB.'</t>
         </is>
       </c>
     </row>
@@ -2241,16 +2403,20 @@
       <c r="C44" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.1,
-  "Referrals and Advocacy": 0.5,
-  "Community Empowerment Through Education": 0.8,
-  "Handing out Medical Supplies ": 0.05
+  "Group Based Health Education": 0.2,
+  "Individualized Support and Health Education": 0.2,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.8,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial identifies the speaker as a Community Health Worker and discusses malaria education efforts, but there is no explicit mention of the CHW having attended or received any form of CHW training. Because the definition requires evidence of received training, alignment is minimal. | Referrals and Advocacy: The CHW encourages community members to seek medical advice and care when they experience malaria symptoms, which aligns with the example of urging someone to go to the clinic (scored 0.5). However, there is no description of making specific referrals, setting appointments, or directly navigating the health system, so the alignment is only moderate. | Community Empowerment Through Education: The testimonial is largely an educational narrative about malaria—symptoms, risks, treatment, prevention—and the CHW explicitly states that they \ | Handing out Medical Supplies : The testimonial discusses malaria symptoms, seeking medical advice, over-the-counter self-treatment, and the existence of a vaccine, but it does not indicate that the CHW distributes medicines, nets, or any other medical supplies to others. Therefore, evidence for the concept is essentially absent.</t>
+          <t>[Group Based Health Education] The CHW states they would "create awareness of the disease to the community," which implies some form of education, but no explicit mention is made of conducting or facilitating a group session, workshop, or talk. Because the reference to education is vague and could equally describe one-on-one interactions or general outreach, alignment with the Group Based Health Education concept is weak. [Individualized Support and Health Education] The testimonial provides general information about malaria (symptoms, importance of seeking care, community awareness) and states that the CHW would ‘create awareness of the disease to the community.’ There is no description of tailoring advice to a specific person or household. Because the content is generic rather than individualized, alignment with the concept is weak, warranting a low score. [Cholera Education and Prevention] The testimonial focuses exclusively on malaria awareness, symptoms, and treatment. There is no mention of cholera or related prevention education, so the concept is clearly absent. [Direct Intervention for Cholera Cases] The testimonial discusses malaria education and personal experiences, with no mention of cholera cases or any direct care actions related to cholera. Treating unrelated conditions is explicitly excluded from the concept. [Diabetes Education and Prevention] The testimonial exclusively discusses malaria awareness, symptoms, and prevention. There is no mention of diabetes, its risk factors, diet, exercise, or blood sugar. Therefore the concept is not present. [HIV/AIDS Education and Prevention] The testimonial focuses solely on malaria awareness, symptoms, and prevention. There is no mention of HIV/AIDS, testing, stigma, or related preventive measures. General health education not referencing HIV/AIDS is explicitly excluded from this concept. [Infectious Disease Prevention] The CHW describes creating community awareness about malaria, discussing its symptoms, the need for precautions to avoid infection, and the role of vaccination. This is education aimed at preventing transmission of a communicable disease, fitting the concept. Although the focus is on one specific illness rather than general hygiene practices, it still aligns strongly with infectious-disease prevention. [Tuberculosis Education and Prevention] The testimonial exclusively discusses malaria education and prevention without any mention of tuberculosis symptoms, transmission, or treatment. According to the concept’s exclusion criteria, education about other infectious diseases does not count toward Tuberculosis Education and Prevention.</t>
         </is>
       </c>
     </row>
@@ -2262,22 +2428,26 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.0,
-  "Referrals and Advocacy": 0.1,
-  "Community Empowerment Through Education": 0.7,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.2,
+  "Individualized Support and Health Education": 0.1,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.9,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial contains no evidence that the CHW received any training. While they identify as a Community Health Worker and describe their approach to malaria education and awareness, there is no mention of attending, completing, or receiving any CHW training, workshops, or educational programs. The knowledge shared appears to come from personal experience as a malaria patient rather than from structured CHW training. | Referrals and Advocacy: The testimonial primarily focuses on malaria education and personal experience with the disease. While the CHW mentions creating awareness and states that people 'should seek medical advice immediately' and describes where 'one can seek medical care at the medical centers,' there is no evidence of the CHW actively assisting with referrals, setting appointments, accompanying patients, or advocating on their behalf. The content is general health education without CHW involvement in system navigation. | Community Empowerment Through Education: The testimonial shows strong intent and commitment to education ('As a Community Health Worker, I would first create awareness of the disease to the community') and outlines specific educational content about malaria (symptoms, treatment, prevention). However, the CHW uses conditional language ('I would') rather than describing actual education delivered, suggesting this is their approach rather than a specific instance of teaching. The detailed knowledge about malaria and clear educational framework warrant a moderate-to-strong score despite the lack of concrete examples of education provided. | Handing out Medical Supplies : The testimonial focuses on malaria education, awareness creation, and personal experiences with the disease. While the CHW mentions self-treatment with over-the-counter drugs and seeking medical care, there is no mention of distributing, handing out, or providing medical supplies to community members. The CHW's role as described is educational rather than supply distribution.</t>
+          <t>[Group Based Health Education] The testimonial mentions the CHW would 'create awareness of the disease to the community' and educate 'members,' but provides no specific evidence of group sessions or structured group education activities. The language is too general and could refer to various educational approaches including one-on-one interactions. This aligns with the exclusion criteria of 'general mentions of educating the community without evidence of a group setting.' [Individualized Support and Health Education] The testimonial primarily discusses general malaria information and community-wide awareness efforts. The CHW mentions creating awareness for 'the community' and provides generic information about malaria symptoms, treatment, and prevention. While they share personal experience as a malaria victim, this is not individualized support to others. The only personalized element is their own self-treatment approach, which doesn't constitute providing individualized support to community members. This aligns with the exclusion criteria of 'general health education' and 'community-wide support.' [Cholera Education and Prevention] The testimonial exclusively discusses malaria - its symptoms, treatment, prevention, and the CHW's role in malaria education. There is no mention of cholera, cholera-related symptoms, water purification, sanitation practices, or any other cholera prevention strategies. The content clearly falls under the exclusion criteria as it focuses on a different disease entirely. [Direct Intervention for Cholera Cases] The testimonial exclusively discusses malaria - its symptoms, treatment, and prevention. There is no mention of cholera, cholera cases, or any cholera-related interventions. The CHW describes awareness creation and treatment approaches specifically for malaria, which falls under the exclusion criteria of 'treating unrelated conditions.' [Diabetes Education and Prevention] The testimonial is entirely focused on malaria - its causes, symptoms, prevention, and treatment. There is no mention of diabetes, blood sugar, diet, exercise, or any metabolic health topics. This clearly falls under the exclusion criteria of 'health education unrelated to diabetes.' [HIV/AIDS Education and Prevention] The testimonial focuses entirely on malaria - its symptoms, treatment, prevention, and the CHW's role in malaria education. There is no mention of HIV/AIDS, HIV transmission, testing, or any HIV-related education activities. This clearly falls under the exclusion criteria as it is health education without any reference to HIV/AIDS. [Infectious Disease Prevention] Strong direct alignment. The testimonial focuses extensively on malaria, a communicable disease spread by parasites through mosquito vectors. The CHW explicitly states they 'create awareness of the disease to the community' including 'what are the precautions one needs in order not to get the disease,' which directly aligns with providing education aimed at reducing the spread of a communicable disease. While the focus is on a specific disease (malaria) rather than general infectious disease prevention, the educational approach about prevention measures clearly fits the concept definition. [Tuberculosis Education and Prevention] The testimonial focuses exclusively on malaria education, including its symptoms, transmission, and prevention. There is no mention of tuberculosis, TB symptoms, TB treatment, or any TB-related topics. This clearly falls under the exclusion criteria of 'other infectious disease education without mention of TB.'</t>
         </is>
       </c>
     </row>
@@ -2295,16 +2465,20 @@
       <c r="C46" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.1,
-  "Referrals and Advocacy": 0.5,
-  "Community Empowerment Through Education": 0.95,
-  "Handing out Medical Supplies ": 0.05
+  "Group Based Health Education": 0.7,
+  "Individualized Support and Health Education": 0.3,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 1.0,
+  "Infectious Disease Prevention": 0.35,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial describes the CHW educating teenagers about HIV testing and PrEP, but there is no explicit statement that the CHW attended or received any CHW training. Therefore only minimal, indirect evidence of training exists, resulting in a weak alignment score. | Referrals and Advocacy: The CHW encourages teens to seek HIV testing and to obtain PrEP, which shows some advocacy and a mild form of referral to services, but there is no evidence of concrete system navigation such as making appointments or accompanying them. This aligns with the example “I encouraged someone to go to the clinic.” scored at 0.5. | Community Empowerment Through Education: The CHW explicitly states that after World AIDS Day she \ | Handing out Medical Supplies : The testimonial focuses on educating teenagers about HIV testing and recommending PrEP, but there is no indication that the CHW physically distributed PrEP or any other medical supplies. Thus, there is only a very weak, indirect connection to the concept.</t>
+          <t>[Group Based Health Education] The CHW states "I educated the teens" and describes providing information to multiple teenagers following a World AIDS Day event, implying a group setting rather than one-on-one counseling. While the size or structure of the session is not detailed, the wording suggests collective education consistent with the concept’s inclusion criteria. Evidence is moderate but not completely explicit, so a score of 0.7 is appropriate. [Individualized Support and Health Education] The CHW describes educating “the teens” as a group about HIV testing and PrEP. This is largely general health education aimed at a demographic group rather than personalized, one-on-one guidance. Although she notes that “some teenagers shared with me the numerous partners they have” and she advised PrEP because of this, the narrative does not clearly show individualized care tailored to a specific person or household. Therefore, only weak evidence of individualized support is present. [Cholera Education and Prevention] The testimonial focuses entirely on teenage pregnancy, HIV testing, and PrEP use; it contains no information, education, or guidance related to cholera. Therefore it does not meet the inclusion criteria for Cholera Education and Prevention. [Direct Intervention for Cholera Cases] The testimonial focuses on HIV prevention and PrEP counseling for teenagers; there is no mention of cholera cases, dehydration, ORS, or any direct care related to cholera. [Diabetes Education and Prevention] The testimonial focuses on HIV prevention, PREP, and teenage pregnancy. There is no discussion of diabetes, diet, exercise, or blood-sugar monitoring. Health education provided is unrelated to diabetes, so the concept is not present. [HIV/AIDS Education and Prevention] The CHW explicitly describes educating teenagers about HIV testing with partners, explaining PrEP as an HIV-prevention method, clarifying who should take it, and its effectiveness. This is a direct, unambiguous example of providing HIV/AIDS awareness, prevention, and testing information, matching the concept definition and inclusion criteria perfectly. [Infectious Disease Prevention] The CHW is educating teens on preventing HIV infection (a communicable disease), which relates to disease prevention. However, the concept definition emphasizes broad, non-disease-specific hygiene or sanitation messages, whereas this testimonial focuses narrowly on HIV and PrEP. Therefore, alignment is weak-to-moderate rather than strong. [Tuberculosis Education and Prevention] The testimonial discusses HIV testing, PrEP, and teenage pregnancy. It contains no references to tuberculosis symptoms, transmission, or treatment, so the concept is not present.</t>
         </is>
       </c>
     </row>
@@ -2316,22 +2490,26 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.0,
-  "Referrals and Advocacy": 0.2,
-  "Community Empowerment Through Education": 0.9,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.8,
+  "Individualized Support and Health Education": 0.8,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.9,
+  "Infectious Disease Prevention": 0.7,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial describes the CHW educating teens about HIV testing and PrEP, but contains no evidence that the CHW personally received any CHW training. While the CHW demonstrates knowledge and educates others, there is no mention of attending training, workshops, or any structured educational experience that enhanced their capacity. The concept explicitly excludes 'delivering training to others without evidence of having received CHW training.' | Referrals and Advocacy: The testimonial primarily focuses on health education about HIV testing and PrEP. While the CHW 'encouraged the teens to go for PREP,' this is general advice rather than active system navigation, referral assistance, or advocacy. There is no mention of helping set appointments, accompanying teens to services, or following up on referrals. This aligns with the example 'I told people they should consider family planning' → 0.2, as both involve suggesting health services without direct CHW involvement in connecting people to care. | Community Empowerment Through Education: Strong direct alignment. The CHW explicitly states 'I educated the teens' multiple times, describing detailed health education about HIV testing and PrEP (pre-exposure prophylaxis). The testimonial shows active knowledge sharing through explanation of how PrEP works, who can use it, and its limitations. The CHW also provided practical advice and problem-solving strategies when teens faced resistance from partners about testing. This clearly demonstrates empowerment through education with specific health information being conveyed to improve practices. | Handing out Medical Supplies : The testimonial describes educating teenagers about HIV testing and PREP (pre-exposure prophylaxis), but there is no mention of physically distributing or handing out any medical supplies. The CHW's role is purely educational - advising teens to seek PREP from appropriate medical facilities rather than providing it directly.</t>
+          <t>[Group Based Health Education] Strong evidence of group-based education. The CHW explicitly states 'I educated the teens' following a World AIDS Day celebration, and describes interactive dialogue where 'some said the partners they have do not buy the idea.' The context suggests a structured group session where multiple teenagers were present, sharing experiences and receiving education about HIV testing and PREP. The plural references throughout and the mention of 'some teenagers shared with me' indicates a group setting rather than individual consultations. [Individualized Support and Health Education] The CHW provides personalized guidance to teenagers based on their specific situations and concerns. The testimonial shows adaptation to individual needs when teens shared that their partners refuse HIV testing, leading the CHW to recommend PrEP as an alternative solution. The advice is further tailored based on teens sharing about having 'numerous partners.' While the education includes some general information about PrEP, the core approach is individualized problem-solving based on the specific barriers and risks the teens disclosed. [Cholera Education and Prevention] The testimonial focuses entirely on teenage pregnancy and HIV/AIDS prevention education, with no mention of cholera, water safety, sanitation, or any cholera-related symptoms or prevention strategies. This clearly falls under the exclusion criteria of 'general health education with no reference to cholera.' [Direct Intervention for Cholera Cases] The testimonial focuses entirely on teenage pregnancy, HIV prevention, and PREP education. There is no mention of cholera, cholera symptoms, oral rehydration, or any cholera-related interventions. The CHW is addressing HIV/AIDS prevention, not providing any direct care for cholera cases. [Diabetes Education and Prevention] The testimonial focuses entirely on teenage pregnancy prevention and HIV/AIDS education, including PREP (Pre-Exposure Prophylaxis) for HIV prevention. There is no mention of diabetes, blood sugar, diet related to diabetes prevention, exercise for metabolic health, or any other diabetes-related topics. The content is explicitly about sexual health education, which falls under the exclusion criteria of 'health education unrelated to diabetes.' [HIV/AIDS Education and Prevention] Strong direct alignment with the concept. The CHW explicitly educated teens about HIV testing with partners, addressed barriers to testing, and provided detailed education about PrEP (Pre-Exposure Prophylaxis) as HIV prevention. The testimonial includes teaching about HIV transmission risks, promoting prevention methods, and encouraging testing - all core elements of HIV/AIDS education. The focus is specifically on HIV/AIDS prevention in the context of teenage pregnancy and multiple partners. [Infectious Disease Prevention] The testimonial shows moderate alignment with infectious disease prevention. The CHW educates teenagers about HIV testing and PREP (pre-exposure prophylaxis) to prevent HIV transmission, which is clearly communicable disease prevention. However, the focus is specifically on HIV/AIDS prevention rather than broad infectious disease prevention education. The content aligns with the inclusion criteria of 'advice on preventing transmission of illnesses' but is narrower in scope than the general hygiene and sanitation practices mentioned in the definition. [Tuberculosis Education and Prevention] This testimonial focuses entirely on teenage pregnancy prevention and HIV/AIDS education, including PREP (Pre-Exposure Prophylaxis) for HIV prevention. There is no mention of tuberculosis, TB symptoms, TB testing, or any TB-related education. The content explicitly deals with HIV/AIDS prevention, which falls under 'other infectious disease education' as noted in the exclusion criteria.</t>
         </is>
       </c>
     </row>
@@ -2349,16 +2527,20 @@
       <c r="C48" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.1,
-  "Referrals and Advocacy": 0.1,
-  "Community Empowerment Through Education": 0.4,
-  "Handing out Medical Supplies ": 0.1
+  "Group Based Health Education": 0.25,
+  "Individualized Support and Health Education": 0.2,
+  "Cholera Education and Prevention": 0.05,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.1,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.1,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial thanks KUAP for providing nutrition programs and teaching to young mothers, but it does not state that the CHW personally attended or received any CHW training. Any link to CHW capacity-building is only speculative, so alignment with the concept is minimal. | Referrals and Advocacy: The testimonial discusses the importance of nutrition programs and expresses gratitude to an organization that provides them, but it does not explicitly state that the CHW referred clients, made appointments, accompanied them, or advocated within the health system. Any linkage is only implied, so alignment with the Referrals and Advocacy concept is weak. | Community Empowerment Through Education: The testimonial discusses nutrition awareness programs that educate parents and mentions that KUAP ‘offers nutrition programs and teaching to young mothers.’ However, it is not explicitly stated that the CHW personally delivers this education; the CHW only expresses appreciation for programs run by another organization. There is some indication of educational activity relevant to the community, but the CHW’s direct role in providing that education is unclear, giving only weak-to-moderate evidence for the concept. | Handing out Medical Supplies : The testimonial talks about nutrition programs, school feeding, and educating parents, but it does not mention distributing medicines, health commodities, or other medical supplies. Providing food is not clearly classified as handing out medical supplies under the concept, so only a very weak alignment is present.</t>
+          <t>[Group Based Health Education] The testimonial generally discusses nutrition programs and mentions that KUAP provides "teaching to young mothers," but it never explicitly states that the CHW personally facilitated or led a group education session. This offers minimal, indirect evidence of group-based health education, falling short of the clear inclusion criteria. [Individualized Support and Health Education] The testimonial discusses general nutrition programs, school feeding initiatives, and teaching sessions for young mothers. It does not describe one-on-one or tailored guidance to a specific individual or household. Any education mentioned appears to be group-oriented and generic, so only weak evidence of individualized support is present. [Cholera Education and Prevention] The testimonial discusses child nutrition programs and briefly mentions provision of clear drinking water, but there is no reference to cholera, its symptoms, transmission, or specific prevention education. According to the concept’s exclusion criteria, general health or nutrition education without explicit cholera content should not be classified under Cholera Education and Prevention, so only a negligible score is assigned. [Direct Intervention for Cholera Cases] The testimonial discusses nutrition programs and education for parents, with no mention of cholera cases, dehydration, ORS, or any direct care for cholera patients. This falls outside the concept’s inclusion criteria and matches the exclusion criteria of preventive education unrelated to cholera. [Diabetes Education and Prevention] The testimonial discusses general child nutrition programs and teaching mothers about adequate and nutritious food, with no explicit mention of diabetes, blood sugar, or diabetes-specific prevention. Nutrition education alone, when not linked to diabetes, is excluded from this concept, so only a weak incidental connection warrants a very low score. [HIV/AIDS Education and Prevention] The testimonial discusses child nutrition programs and education for mothers, with no mention of HIV/AIDS, prevention, testing, or related topics. According to the exclusion criteria, general health education that does not reference HIV/AIDS should receive a score of 0.0. [Infectious Disease Prevention] The testimonial focuses on child nutrition programs and feeding initiatives. Although it briefly mentions provision of clear drinking water, there is no explicit education or advice aimed at preventing the spread of communicable diseases. Nutrition education is explicitly excluded from the Infectious Disease Prevention concept, so only a very weak alignment is present. [Tuberculosis Education and Prevention] The testimonial discusses child nutrition programs and feeding initiatives, with no mention of tuberculosis symptoms, transmission, treatment, or prevention. Therefore, the concept is not present.</t>
         </is>
       </c>
     </row>
@@ -2370,22 +2552,26 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.0,
-  "Referrals and Advocacy": 0.0,
-  "Community Empowerment Through Education": 0.8,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.6,
+  "Individualized Support and Health Education": 0.2,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.1,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.0,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial does not contain any evidence that the CHW personally received training. While the CHW mentions being thankful to KUAP for offering nutrition programs and teaching to young mothers, there is no indication that the CHW themselves attended or received any training. The focus is on programs being delivered to community members, not on the CHW's own educational experiences or capacity building through training. | Referrals and Advocacy: The testimonial discusses nutrition programs and education but contains no evidence of the CHW acting as an intermediary, advocate, or navigator within the health system. There are no mentions of referrals, appointments, accompanying patients, or advocating on behalf of individuals. The CHW only expresses gratitude for nutrition programs and education provided to mothers, which falls under general health education excluded by the concept definition. | Community Empowerment Through Education: The testimonial strongly aligns with the concept. The CHW explicitly mentions that their organization (KUAP) offers 'nutrition programs and teaching to young mothers on how they can handle their little ones.' This directly indicates education being provided to community members (young mothers) about nutrition and childcare. Additionally, the testimonial references 'nutrition awareness programs that educate parents,' further supporting the educational component. The score is 0.8 rather than higher because while the educational activities are clearly mentioned, the CHW's personal role in delivering this education could be more explicit. | Handing out Medical Supplies : The testimonial focuses entirely on nutrition education, feeding programs, and teaching mothers about child nutrition. There is no mention of distributing, handing out, or providing any medical supplies. The CHW describes educational and awareness programs rather than supply distribution activities.</t>
+          <t>[Group Based Health Education] The testimonial mentions 'nutrition programs and teaching to young mothers' provided by KUAP, which suggests group-based education activities. However, it lacks explicit confirmation that these are group sessions rather than individual consultations. The reference to 'mothers' (plural) and 'programs' implies a collective setting, but without clear evidence of the CHW personally facilitating group sessions, the score reflects moderate alignment. [Individualized Support and Health Education] The testimonial primarily discusses general nutrition programs and community-wide education initiatives. While the CHW mentions 'teaching to young mothers on how they can handle their little ones,' this appears to be group education rather than individualized support. The content focuses on broad policy issues, school feeding programs, and general nutrition awareness programs - all of which fall under the exclusion criteria of 'group education or community-wide support.' There is no evidence of one-on-one tailoring or personalized guidance to specific individuals or families. [Cholera Education and Prevention] The testimonial focuses entirely on child nutrition, food security, and general nutrition education programs. There is no mention of cholera, cholera prevention, water purification for cholera prevention, or any cholera-related symptoms or hygiene practices. While 'clear drinking water' is mentioned, it's in the context of general nutrition needs, not cholera prevention specifically. [Direct Intervention for Cholera Cases] The testimonial focuses entirely on child nutrition programs, food security, and nutrition education for mothers. There is no mention of cholera, diarrheal diseases, ORS administration, dehydration treatment, or any emergency interventions related to cholera cases. The content explicitly addresses nutrition support and education, which falls outside the scope of direct cholera intervention. [Diabetes Education and Prevention] The testimonial focuses exclusively on child nutrition programs and education for young mothers about feeding their children. While nutrition education is mentioned, there is no reference to diabetes prevention, blood sugar, metabolic health, or any diabetes-related risk factors. The nutrition content is specifically about child feeding and general nourishment, not diabetes prevention strategies. [HIV/AIDS Education and Prevention] The testimonial focuses entirely on child nutrition, food security, and nutrition education programs for young mothers. There is no mention of HIV/AIDS, HIV transmission, testing, prevention methods, or any HIV-related topics. This clearly falls under the exclusion criteria of 'general health education without a reference to HIV/AIDS.' [Infectious Disease Prevention] The testimonial focuses entirely on child nutrition, food security, and nutritional education for mothers. There is no mention of hygiene, sanitation, disease transmission prevention, or any communicable disease-related topics. The content explicitly deals with nutrition programs and food supplementation, which falls outside the scope of infectious disease prevention. [Tuberculosis Education and Prevention] The testimonial focuses exclusively on child nutrition, food access, and nutrition education programs. There is no mention of tuberculosis, TB symptoms, transmission, prevention, or any related topics. The content explicitly discusses nutrition support and feeding programs, which falls outside the scope of TB education.</t>
         </is>
       </c>
     </row>
@@ -2403,16 +2589,20 @@
       <c r="C50" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 1.0,
-  "Referrals and Advocacy": 0.9,
-  "Community Empowerment Through Education": 0.9,
-  "Handing out Medical Supplies ": 0.05
+  "Group Based Health Education": 0.3,
+  "Individualized Support and Health Education": 0.55,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.05,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.6,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: The testimonial repeatedly states the CHW personally received training (e.g., \ | Referrals and Advocacy: The testimonial explicitly states that after training the CHW now \ | Community Empowerment Through Education: The testimonial repeatedly states that after receiving training, the CHW began “giving health information” to the community, enabling people to seek care and requesting further teaching. This is clear evidence that the CHW actively shares knowledge with community members to improve health practices, matching the definition and inclusion criteria for Community Empowerment Through Education; no conflicting exclusions are present. | Handing out Medical Supplies : The testimonial focuses on receiving training, providing health information, performing first aid, and making referrals. It does not mention distributing or handing out any medical supplies such as medications, PPE, or equipment. Therefore, alignment with the concept is minimal.</t>
+          <t>[Group Based Health Education] The testimonial mentions ‘giving health information’ to the community and that community members are eager to be taught, but it never explicitly states that the CHW facilitated a health talk or workshop with a group. Because group delivery is implied only vaguely and not confirmed, evidence is weak, meriting a low score. [Individualized Support and Health Education] The CHW describes being able to perform patient assessment, give first aid, and decide when to refer—activities that imply one-on-one, situation-specific care rather than generic outreach. However, most of the testimonial emphasizes general community health information and gratitude for training, with few concrete examples of personalized guidance to a specific individual or household. Therefore, alignment with the concept is moderate but not strong. [Cholera Education and Prevention] The testimonial discusses CHW training, general health information, COVID-19, first aid, and referrals, but it never mentions cholera or related prevention topics. According to the exclusion criteria, general health education without any reference to cholera should receive a score of 0. [Direct Intervention for Cholera Cases] The testimonial discusses training, COVID-19 information, first aid, and general referrals but never mentions cholera or care for cholera patients. Therefore, the concept of direct intervention for cholera cases is not present. [Diabetes Education and Prevention] The testimonial describes general CHW training, COVID-19 information, first aid, and patient assessment, with no mention of diabetes, diet, exercise, or blood-sugar education. Therefore there is virtually no alignment with the Diabetes Education and Prevention concept. [HIV/AIDS Education and Prevention] The testimonial discusses training and sharing health information mainly related to COVID-19, first aid, and general patient assessment. There is no mention of HIV/AIDS, its transmission, prevention, testing, or stigma reduction, which are required for this concept. Therefore, the concept is not present. [Infectious Disease Prevention] The CHW highlights receiving and sharing information on COVID-19 with the community. COVID-19 is a communicable respiratory disease, so education about it fits the idea of preventing infectious disease transmission. However, the testimonial centers on one specific illness rather than general hygiene or broad disease-prevention practices, so alignment with the concept is moderate rather than perfect. [Tuberculosis Education and Prevention] The testimonial discusses training related to general health information, COVID-19 management, first aid, and patient assessment, but it contains no mention of tuberculosis education, symptoms, transmission, or prevention. Therefore the concept is not present.</t>
         </is>
       </c>
     </row>
@@ -2424,22 +2614,26 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>claude-3-opus-20240229</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
           <t>{
-  "CHW Empowered Through Training": 0.9,
-  "Referrals and Advocacy": 0.9,
-  "Community Empowerment Through Education": 0.9,
-  "Handing out Medical Supplies ": 0.0
+  "Group Based Health Education": 0.2,
+  "Individualized Support and Health Education": 0.2,
+  "Cholera Education and Prevention": 0.0,
+  "Direct Intervention for Cholera Cases": 0.0,
+  "Diabetes Education and Prevention": 0.0,
+  "HIV/AIDS Education and Prevention": 0.0,
+  "Infectious Disease Prevention": 0.8,
+  "Tuberculosis Education and Prevention": 0.0
 }</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training: Strong direct alignment. The testimonial explicitly states 'after the training' multiple times and describes specific skills gained through CHW training: COVID-19 management, first aid skills, patient assessment abilities, and health information delivery. The CHW clearly received structured training from named instructors (Madam Winnie and Mr. Kituli) and directly attributes their enhanced capacity to serve the community to this training. The testimonial follows the pattern of the 0.9 examples by showing how received training led to improved service delivery. | Referrals and Advocacy: The testimonial contains multiple explicit mentions of referrals as a core CHW activity. The CHW states 'we do referrals' and 'I do referrals to the facility' after providing first aid. They also describe identifying symptoms and referring for testing, which directly aligns with the concept definition of CHWs acting as intermediaries within the health system. This represents strong direct alignment with the concept. | Community Empowerment Through Education: Strong direct alignment with the concept. The CHW explicitly states they are 'giving health information' to the community and that 'we are able to give back to the community the information we get.' They describe how the community is 'very eager to be taught more and more about the health issues' and how they fulfill this need. The testimonial provides clear evidence of active knowledge sharing, community education about health topics including COVID-19, and the community's positive response to receiving this information. This aligns closely with the concept's definition of CHWs providing health education to help community members gain knowledge to improve health practices. | Handing out Medical Supplies : The testimonial focuses entirely on health education, information sharing, training, and referrals. There is no mention of distributing, handing out, or providing any physical medical supplies or materials to community members. The CHW describes giving health information and performing first aid, but not distributing medical supplies.</t>
+          <t>[Group Based Health Education] The testimonial mentions that the CHW gives health information to the community and that community members 'are very eager to be taught more and more about the health issues.' However, there is no explicit evidence of group sessions, workshops, or structured group education settings. The references to 'giving health information' and the community being 'taught' could involve one-on-one interactions or group settings, but without specific mention of group activities, this aligns weakly with the concept. [Individualized Support and Health Education] The testimonial primarily describes general community health education and group-level interventions rather than individualized support. While the CHW mentions doing patient assessments and referrals, these appear to be standard procedures rather than personalized care. The testimonial emphasizes community-wide information sharing ('giving health information', 'the community is changing gradually', 'give back to the community') which aligns with the exclusion criteria of 'group education or community-wide support.' There is minimal evidence of one-on-one tailoring or adaptation to individual needs. [Cholera Education and Prevention] The testimonial focuses on general health information, COVID-19 management, first aid, and patient assessment. There is no mention of cholera, cholera symptoms, water purification for cholera prevention, or any cholera-related education activities. While the CHW discusses providing health information to the community, it appears to be general health education rather than cholera-specific content, which falls under the exclusion criteria. [Direct Intervention for Cholera Cases] The testimonial does not mention cholera at all. While the CHW describes gaining skills in first aid, patient assessment, and making referrals, these are general healthcare activities. The specific health issues mentioned are COVID-19 and general health information dissemination. There is no evidence of direct intervention for cholera cases, which would require mention of ORS administration, cholera symptoms, dehydration management, or cholera-specific patient care. [Diabetes Education and Prevention] The testimonial does not mention diabetes, blood sugar, diet, exercise for metabolic health, or any diabetes-related education. The CHW discusses COVID-19 management, first aid, patient assessment, and general health information delivery, but there is no evidence of diabetes education or prevention activities. [HIV/AIDS Education and Prevention] The testimonial does not mention HIV/AIDS education or prevention at any point. The CHW discusses general health information, COVID-19 management, first aid, patient assessment, and referrals, but makes no reference to HIV transmission, testing, condom use, or any HIV/AIDS-related topics. This clearly falls under the exclusion criteria of 'general health education without a reference to HIV/AIDS.' [Infectious Disease Prevention] The testimonial shows strong alignment with infectious disease prevention. The CHW explicitly mentions receiving training on COVID-19 management and prevention 'even before the government COVID lockdown,' which directly relates to preventing the spread of a communicable disease. While the testimonial doesn't detail specific prevention techniques taught (like hand hygiene or cough etiquette), the focus on COVID-19 education and management clearly falls within the concept of infectious disease prevention education. [Tuberculosis Education and Prevention] The testimonial does not mention tuberculosis, TB symptoms, TB transmission, or any TB-related education or prevention activities. The CHW discusses general health information, COVID-19, first aid, and patient assessment, but there is no evidence of TB-specific education or prevention work.</t>
         </is>
       </c>
     </row>
